--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,10 +416,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -433,7 +433,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>price_00:00</t>
+          <t>price_00:15</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -454,13 +454,13 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>70554.7</v>
+        <v>70545.39999999999</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>70554.7</v>
+        <v>70545.39999999999</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>70554.7</v>
+        <v>70545.39999999999</v>
       </c>
     </row>
     <row r="3">
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>2073.55</v>
+        <v>2072.31</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>2073.55</v>
+        <v>2072.31</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2073.55</v>
+        <v>2072.31</v>
       </c>
     </row>
     <row r="4">
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>86.67</v>
+        <v>86.72</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>86.67</v>
+        <v>86.72</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>86.67</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="5">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>4.024</v>
+        <v>4.039</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>4.024</v>
+        <v>4.039</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4.024</v>
+        <v>4.039</v>
       </c>
     </row>
     <row r="6">
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.09487</v>
+        <v>0.09485</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.09487</v>
+        <v>0.09485</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.09487</v>
+        <v>0.09485</v>
       </c>
     </row>
     <row r="7">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1.3894</v>
+        <v>1.388</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1.3894</v>
+        <v>1.388</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.3894</v>
+        <v>1.388</v>
       </c>
     </row>
     <row r="8">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>22.954</v>
+        <v>22.657</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>22.954</v>
+        <v>22.657</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>22.954</v>
+        <v>22.657</v>
       </c>
     </row>
     <row r="9">
@@ -566,13 +566,13 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.002306</v>
+        <v>0.002119</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0.002306</v>
+        <v>0.002119</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.002306</v>
+        <v>0.002119</v>
       </c>
     </row>
     <row r="10">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.010858</v>
+        <v>0.01067</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0.010858</v>
+        <v>0.01067</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.010858</v>
+        <v>0.01067</v>
       </c>
     </row>
     <row r="11">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.1679</v>
+        <v>0.1709</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.1679</v>
+        <v>0.1709</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.1679</v>
+        <v>0.1709</v>
       </c>
     </row>
     <row r="12">
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.0122</v>
+        <v>0.01197</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.0122</v>
+        <v>0.01197</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.0122</v>
+        <v>0.01197</v>
       </c>
     </row>
     <row r="13">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>37.976</v>
+        <v>37.988</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>37.976</v>
+        <v>37.988</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>37.976</v>
+        <v>37.988</v>
       </c>
     </row>
     <row r="14">
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>653.3</v>
+        <v>652.8</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>653.3</v>
+        <v>652.8</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>653.3</v>
+        <v>652.8</v>
       </c>
     </row>
     <row r="15">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>209.05</v>
+        <v>209.13</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>209.05</v>
+        <v>209.13</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>209.05</v>
+        <v>209.13</v>
       </c>
     </row>
     <row r="16">
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.0033469</v>
+        <v>0.0033417</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.0033469</v>
+        <v>0.0033417</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.0033469</v>
+        <v>0.0033417</v>
       </c>
     </row>
     <row r="17">
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>233.71</v>
+        <v>234.47</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>233.71</v>
+        <v>234.47</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>233.71</v>
+        <v>234.47</v>
       </c>
     </row>
     <row r="18">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.9868</v>
+        <v>0.987</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.9868</v>
+        <v>0.987</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.9868</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="19">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>1.0261</v>
+        <v>1.0322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>1.0261</v>
+        <v>1.0322</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>1.0261</v>
+        <v>1.0322</v>
       </c>
     </row>
     <row r="20">
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.2604</v>
+        <v>0.2608</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.2604</v>
+        <v>0.2608</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.2604</v>
+        <v>0.2608</v>
       </c>
     </row>
     <row r="21">
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.6079</v>
+        <v>0.60985</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.6079</v>
+        <v>0.60985</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.6079</v>
+        <v>0.60985</v>
       </c>
     </row>
     <row r="22">
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>8.997</v>
+        <v>8.991</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>8.997</v>
+        <v>8.991</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>8.997</v>
+        <v>8.991</v>
       </c>
     </row>
     <row r="23">
@@ -790,13 +790,13 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.02409</v>
+        <v>0.02425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0.02409</v>
+        <v>0.02425</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.02409</v>
+        <v>0.02425</v>
       </c>
     </row>
     <row r="24">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>9.555</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>9.555</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>9.555</v>
+        <v>9.555999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>1.214</v>
+        <v>1.218</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>1.214</v>
+        <v>1.218</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>1.214</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="26">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.07042</v>
+        <v>0.07160999999999999</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.07042</v>
+        <v>0.07160999999999999</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.07042</v>
+        <v>0.07160999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>1.43</v>
+        <v>1.428</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1.43</v>
+        <v>1.428</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.43</v>
+        <v>1.428</v>
       </c>
     </row>
     <row r="28">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>461.19</v>
+        <v>461.74</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>461.19</v>
+        <v>461.74</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>461.19</v>
+        <v>461.74</v>
       </c>
     </row>
     <row r="30">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>1.2781</v>
+        <v>1.2764</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>1.2781</v>
+        <v>1.2764</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.2781</v>
+        <v>1.2764</v>
       </c>
     </row>
     <row r="31">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>5028.11</v>
+        <v>5024.91</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>5028.11</v>
+        <v>5024.91</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>5028.11</v>
+        <v>5024.91</v>
       </c>
     </row>
     <row r="32">
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.868</v>
+        <v>0.867</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.868</v>
+        <v>0.867</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.868</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="33">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.001972</v>
+        <v>0.001971</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.001972</v>
+        <v>0.001971</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.001972</v>
+        <v>0.001971</v>
       </c>
     </row>
     <row r="34">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.17355</v>
+        <v>0.17091</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.17355</v>
+        <v>0.17091</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.17355</v>
+        <v>0.17091</v>
       </c>
     </row>
     <row r="35">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.29816</v>
+        <v>0.2982</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0.29816</v>
+        <v>0.2982</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.29816</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="36">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
     </row>
     <row r="37">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>110.55</v>
+        <v>110.25</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>110.55</v>
+        <v>110.25</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>110.55</v>
+        <v>110.25</v>
       </c>
     </row>
     <row r="38">
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.22744</v>
+        <v>0.22651</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0.22744</v>
+        <v>0.22651</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.22744</v>
+        <v>0.22651</v>
       </c>
     </row>
     <row r="39">
@@ -1046,13 +1046,13 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.1076</v>
+        <v>0.1078</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.1076</v>
+        <v>0.1078</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.1076</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="40">
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.36803</v>
+        <v>0.37042</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.36803</v>
+        <v>0.37042</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.36803</v>
+        <v>0.37042</v>
       </c>
     </row>
     <row r="41">
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>54.43</v>
+        <v>54.45</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>54.43</v>
+        <v>54.45</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>54.43</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="42">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.0010835</v>
+        <v>0.0010838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.0010835</v>
+        <v>0.0010838</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.0010835</v>
+        <v>0.0010838</v>
       </c>
     </row>
     <row r="43">
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>6.46</v>
+        <v>6.588</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>6.46</v>
+        <v>6.588</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>6.46</v>
+        <v>6.588</v>
       </c>
     </row>
     <row r="44">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.6403</v>
+        <v>0.6409</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.6403</v>
+        <v>0.6409</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.6403</v>
+        <v>0.6409</v>
       </c>
     </row>
     <row r="45">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.3528</v>
+        <v>0.3539</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0.3528</v>
+        <v>0.3539</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.3528</v>
+        <v>0.3539</v>
       </c>
     </row>
     <row r="46">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.03254</v>
+        <v>0.0326</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.03254</v>
+        <v>0.0326</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.03254</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="47">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.07467</v>
+        <v>0.07371</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.07467</v>
+        <v>0.07371</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.07467</v>
+        <v>0.07371</v>
       </c>
     </row>
     <row r="48">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.7024</v>
+        <v>0.7008</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.7024</v>
+        <v>0.7008</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.7024</v>
+        <v>0.7008</v>
       </c>
     </row>
     <row r="49">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.00457</v>
+        <v>0.00463</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.00457</v>
+        <v>0.00463</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.00457</v>
+        <v>0.00463</v>
       </c>
     </row>
     <row r="50">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.104</v>
+        <v>0.1041</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.104</v>
+        <v>0.1041</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.104</v>
+        <v>0.1041</v>
       </c>
     </row>
     <row r="51">
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>0.04025</v>
+        <v>0.04036</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>0.04025</v>
+        <v>0.04036</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.04025</v>
+        <v>0.04036</v>
       </c>
     </row>
     <row r="52">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0.1662</v>
+        <v>0.1667</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.1662</v>
+        <v>0.1667</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.1662</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="53">
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0.0226</v>
+        <v>0.02164</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0.0226</v>
+        <v>0.02164</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.0226</v>
+        <v>0.02164</v>
       </c>
     </row>
     <row r="54">
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0.007215</v>
+        <v>0.007221</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.007215</v>
+        <v>0.007221</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.007215</v>
+        <v>0.007221</v>
       </c>
     </row>
     <row r="55">
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>3.93</v>
+        <v>3.925</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>3.93</v>
+        <v>3.925</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>3.93</v>
+        <v>3.925</v>
       </c>
     </row>
     <row r="56">
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>0.017358</v>
+        <v>0.017208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0.017358</v>
+        <v>0.017208</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.017358</v>
+        <v>0.017208</v>
       </c>
     </row>
     <row r="57">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>0.1094</v>
+        <v>0.1095</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0.1094</v>
+        <v>0.1095</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0.1094</v>
+        <v>0.1095</v>
       </c>
     </row>
     <row r="58">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>2.638</v>
+        <v>2.643</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>2.638</v>
+        <v>2.643</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.638</v>
+        <v>2.643</v>
       </c>
     </row>
     <row r="59">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0.09215</v>
+        <v>0.09204</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.09215</v>
+        <v>0.09204</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>0.09215</v>
+        <v>0.09204</v>
       </c>
     </row>
     <row r="62">
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0.9093</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.9093</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0.9093</v>
+        <v>0.9118000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0.777</v>
+        <v>0.774</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0.777</v>
+        <v>0.774</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>0.777</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="64">
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>0.04586</v>
+        <v>0.04674</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0.04586</v>
+        <v>0.04674</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0.04586</v>
+        <v>0.04674</v>
       </c>
     </row>
     <row r="65">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>355.99</v>
+        <v>355.34</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>355.99</v>
+        <v>355.34</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>355.99</v>
+        <v>355.34</v>
       </c>
     </row>
     <row r="66">
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>0.12758</v>
+        <v>0.12788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0.12758</v>
+        <v>0.12788</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>0.12758</v>
+        <v>0.12788</v>
       </c>
     </row>
     <row r="67">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>0.2389</v>
+        <v>0.2446</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0.2389</v>
+        <v>0.2446</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>0.2389</v>
+        <v>0.2446</v>
       </c>
     </row>
     <row r="68">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>0.1755</v>
+        <v>0.1759</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0.1755</v>
+        <v>0.1759</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>0.1755</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="70">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>0.16355</v>
+        <v>0.16422</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>0.16355</v>
+        <v>0.16422</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>0.16355</v>
+        <v>0.16422</v>
       </c>
     </row>
     <row r="71">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>0.3588</v>
+        <v>0.3541</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>0.3588</v>
+        <v>0.3541</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>0.3588</v>
+        <v>0.3541</v>
       </c>
     </row>
     <row r="72">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.00861</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.00861</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.00861</v>
       </c>
     </row>
     <row r="74">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>0.006004</v>
+        <v>0.006002</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0.006004</v>
+        <v>0.006002</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>0.006004</v>
+        <v>0.006002</v>
       </c>
     </row>
     <row r="75">
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>0.3028</v>
+        <v>0.3033</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>0.3028</v>
+        <v>0.3033</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>0.3028</v>
+        <v>0.3033</v>
       </c>
     </row>
     <row r="77">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1001</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1001</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1001</v>
       </c>
     </row>
     <row r="78">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>0.1226</v>
+        <v>0.1227</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>0.1226</v>
+        <v>0.1227</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>0.1226</v>
+        <v>0.1227</v>
       </c>
     </row>
     <row r="79">
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>0.04665</v>
+        <v>0.04696</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>0.04665</v>
+        <v>0.04696</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>0.04665</v>
+        <v>0.04696</v>
       </c>
     </row>
     <row r="81">
@@ -1734,13 +1734,13 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>8.218999999999999</v>
+        <v>8.215</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>8.218999999999999</v>
+        <v>8.215</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>8.218999999999999</v>
+        <v>8.215</v>
       </c>
     </row>
     <row r="83">
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>0.0006019</v>
+        <v>0.0006002</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>0.0006019</v>
+        <v>0.0006002</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>0.0006019</v>
+        <v>0.0006002</v>
       </c>
     </row>
     <row r="84">
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>0.4147</v>
+        <v>0.4212</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>0.4147</v>
+        <v>0.4212</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>0.4147</v>
+        <v>0.4212</v>
       </c>
     </row>
     <row r="85">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>0.06245</v>
+        <v>0.06243</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>0.06245</v>
+        <v>0.06243</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>0.06245</v>
+        <v>0.06243</v>
       </c>
     </row>
     <row r="86">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>0.05515</v>
+        <v>0.05509</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>0.05515</v>
+        <v>0.05509</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>0.05515</v>
+        <v>0.05509</v>
       </c>
     </row>
     <row r="87">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>0.003346</v>
+        <v>0.003329</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>0.003346</v>
+        <v>0.003329</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>0.003346</v>
+        <v>0.003329</v>
       </c>
     </row>
     <row r="88">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>0.04939</v>
+        <v>0.04971</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>0.04939</v>
+        <v>0.04971</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>0.04939</v>
+        <v>0.04971</v>
       </c>
     </row>
     <row r="89">
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>0.03017</v>
+        <v>0.03031</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>0.03017</v>
+        <v>0.03031</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>0.03017</v>
+        <v>0.03031</v>
       </c>
     </row>
     <row r="90">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>0.3462</v>
+        <v>0.3473</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>0.3462</v>
+        <v>0.3473</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>0.3462</v>
+        <v>0.3473</v>
       </c>
     </row>
     <row r="91">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>0.06021</v>
+        <v>0.06078</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>0.06021</v>
+        <v>0.06078</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>0.06021</v>
+        <v>0.06078</v>
       </c>
     </row>
     <row r="92">
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>0.3473</v>
+        <v>0.3421</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>0.3473</v>
+        <v>0.3421</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>0.3473</v>
+        <v>0.3421</v>
       </c>
     </row>
     <row r="93">
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>1.9711</v>
+        <v>1.966</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>1.9711</v>
+        <v>1.966</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>1.9711</v>
+        <v>1.966</v>
       </c>
     </row>
     <row r="94">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>0.2588</v>
+        <v>0.2589</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>0.2588</v>
+        <v>0.2589</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>0.2588</v>
+        <v>0.2589</v>
       </c>
     </row>
     <row r="95">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>0.04553</v>
+        <v>0.04525</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>0.04553</v>
+        <v>0.04525</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>0.04553</v>
+        <v>0.04525</v>
       </c>
     </row>
     <row r="96">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>0.005742</v>
+        <v>0.005831</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>0.005742</v>
+        <v>0.005831</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>0.005742</v>
+        <v>0.005831</v>
       </c>
     </row>
     <row r="97">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>0.001752</v>
+        <v>0.001746</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>0.001752</v>
+        <v>0.001746</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>0.001752</v>
+        <v>0.001746</v>
       </c>
     </row>
     <row r="98">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>5.318</v>
+        <v>5.284</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>5.318</v>
+        <v>5.284</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>5.318</v>
+        <v>5.284</v>
       </c>
     </row>
     <row r="99">
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>0.5488</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>0.5488</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>0.5488</v>
+        <v>0.5508999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>0.0912</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>0.0912</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>0.0912</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>32.38</v>
+        <v>32.48</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>32.38</v>
+        <v>32.48</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>32.38</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="103">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>0.03341</v>
+        <v>0.032</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>0.03341</v>
+        <v>0.032</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>0.03341</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="104">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>0.06602</v>
+        <v>0.06582</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>0.06602</v>
+        <v>0.06582</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>0.06602</v>
+        <v>0.06582</v>
       </c>
     </row>
     <row r="105">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>1.3009</v>
+        <v>1.2981</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>1.3009</v>
+        <v>1.2981</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>1.3009</v>
+        <v>1.2981</v>
       </c>
     </row>
     <row r="106">
@@ -2118,13 +2118,13 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>0.1183</v>
+        <v>0.1186</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>0.1183</v>
+        <v>0.1186</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>0.1183</v>
+        <v>0.1186</v>
       </c>
     </row>
     <row r="107">
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="108">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>0.09576</v>
+        <v>0.09589</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0.09576</v>
+        <v>0.09589</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>0.09576</v>
+        <v>0.09589</v>
       </c>
     </row>
     <row r="109">
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>0.14225</v>
+        <v>0.14276</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0.14225</v>
+        <v>0.14276</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>0.14225</v>
+        <v>0.14276</v>
       </c>
     </row>
     <row r="110">
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>5.531</v>
+        <v>5.546</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>5.531</v>
+        <v>5.546</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>5.531</v>
+        <v>5.546</v>
       </c>
     </row>
     <row r="111">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>1.084</v>
+        <v>1.082</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>1.084</v>
+        <v>1.082</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>1.084</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="112">
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>0.029581</v>
+        <v>0.029692</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0.029581</v>
+        <v>0.029692</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>0.029581</v>
+        <v>0.029692</v>
       </c>
     </row>
     <row r="113">
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>0.06047</v>
+        <v>0.06108</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0.06047</v>
+        <v>0.06108</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>0.06047</v>
+        <v>0.06108</v>
       </c>
     </row>
     <row r="115">
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>0.12888</v>
+        <v>0.12932</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0.12888</v>
+        <v>0.12932</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>0.12888</v>
+        <v>0.12932</v>
       </c>
     </row>
     <row r="116">
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>1.1057</v>
+        <v>1.1095</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>1.1057</v>
+        <v>1.1095</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>1.1057</v>
+        <v>1.1095</v>
       </c>
     </row>
     <row r="117">
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>0.1533</v>
+        <v>0.156</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0.1533</v>
+        <v>0.156</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>0.1533</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="118">
@@ -2310,13 +2310,13 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>0.1589</v>
+        <v>0.1584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0.1589</v>
+        <v>0.1584</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>0.1589</v>
+        <v>0.1584</v>
       </c>
     </row>
     <row r="119">
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04587</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04587</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04587</v>
       </c>
     </row>
     <row r="120">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>3.02</v>
+        <v>3.018</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>3.02</v>
+        <v>3.018</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>3.02</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="121">
@@ -2358,13 +2358,6765 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>0.2952</v>
+        <v>0.2957</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>0.2952</v>
+        <v>0.2957</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>0.2952</v>
+        <v>0.2957</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>0GUSDT</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>0.5826</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>0.5826</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>0.5826</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1000000BOBUSDT</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1000000MOGUSDT</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1000CATUSDT</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>0.001778</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>0.001778</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>0.001778</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1000CHEEMSUSDT</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>0.0004894</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>0.0004894</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>0.0004894</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1000FLOKIUSDT</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>0.02949</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>0.02949</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>0.02949</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1000LUNCUSDT</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>0.04119</v>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>0.04119</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>0.04119</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1000RATSUSDT</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>0.04887</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>0.04887</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>0.04887</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1000SATSUSDT</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>1.24e-05</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>1.24e-05</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>1.24e-05</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1000WHYUSDT</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>7.2e-06</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>7.2e-06</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>7.2e-06</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1000XECUSDT</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1INCHUSDT</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1MBABYDOGEUSDT</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>0.0004099</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>0.0004099</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>0.0004099</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2ZUSDT</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>0.08391999999999999</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>0.08391999999999999</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>0.08391999999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4USDT</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>0.007984</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>0.007984</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>0.007984</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>A2ZUSDT</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>0.000816</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>0.000816</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>0.000816</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ACEUSDT</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>0.1483</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ACHUSDT</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>0.006726</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>0.006726</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>0.006726</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ACTUSDT</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ACUUSDT</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>0.09848999999999999</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>0.09848999999999999</v>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>0.09848999999999999</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AERGOUSDT</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>0.05405</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>0.05405</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>0.05405</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AEROUSDT</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>0.3237</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AEVOUSDT</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>0.02576</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AGLDUSDT</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>0.238</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AGTUSDT</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>0.007066</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>0.007066</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>0.007066</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AIAUSDT</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>0.08695</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AINUSDT</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>0.05024</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>0.05024</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>0.05024</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AIOTUSDT</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>0.02394</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>0.02394</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>0.02394</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AIOUSDT</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>0.08646</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>0.08646</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>0.08646</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AIUSDT</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AIXBTUSDT</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>0.02577</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AKEUSDT</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>0.0002102</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>0.0002102</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>0.0002102</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AKTUSDT</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>0.4406</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ALCHUSDT</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>0.06741999999999999</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>0.06741999999999999</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>0.06741999999999999</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ALLOUSDT</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>0.12825</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ALLUSDT</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>0.4844</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ALPINEUSDT</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>0.4465</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ALTUSDT</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>0.007528</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>0.007528</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>0.007528</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ANIMEUSDT</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>0.004628</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>0.004628</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>0.004628</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ANKRUSDT</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>APEUSDT</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>API3USDT</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ARKMUSDT</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ARKUSDT</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ARPAUSDT</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>0.01006</v>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>0.01006</v>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>0.01006</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ARUSDT</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>1.829</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ASRUSDT</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>1.339</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ASTRUSDT</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="n">
+        <v>0.007321</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>0.007321</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>0.007321</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ATAUSDT</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ATHUSDT</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="n">
+        <v>0.005796</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>0.005796</v>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>0.005796</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ATUSDT</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>0.14615</v>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>0.14615</v>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>0.14615</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AUCTIONUSDT</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>4.871</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AUSDT</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AVAAIUSDT</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="n">
+        <v>0.007488</v>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>0.007488</v>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>0.007488</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AVAUSDT</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="D176" s="1" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AWEUSDT</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>0.05175</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AXLUSDT</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="n">
+        <v>0.05458</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>0.05458</v>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>0.05458</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AZTECUSDT</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="n">
+        <v>0.02338</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>0.02338</v>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>0.02338</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>B2USDT</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>0.694</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>B3USDT</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="n">
+        <v>0.0003727</v>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>0.0003727</v>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>0.0003727</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BABYUSDT</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="n">
+        <v>0.01287</v>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>0.01287</v>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>0.01287</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BANANAUSDT</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>4.271</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BANDUSDT</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>BANKUSDT</t>
+        </is>
+      </c>
+      <c r="B185" s="1" t="n">
+        <v>0.03782</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>0.03782</v>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>0.03782</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BANUSDT</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="n">
+        <v>0.11619</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>0.11619</v>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>0.11619</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>BASUSDT</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="n">
+        <v>0.009277000000000001</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>0.009277000000000001</v>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>0.009277000000000001</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>BATUSDT</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BBUSDT</t>
+        </is>
+      </c>
+      <c r="B189" s="1" t="n">
+        <v>0.02774</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>0.02774</v>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>0.02774</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>BDXNUSDT</t>
+        </is>
+      </c>
+      <c r="B190" s="1" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BEAMXUSDT</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>0.001949</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>0.001949</v>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>0.001949</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>BELUSDT</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BICOUSDT</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BIGTIMEUSDT</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BIOUSDT</t>
+        </is>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BIRBUSDT</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>0.1698</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BLUAIUSDT</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>0.007454</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>0.007454</v>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>0.007454</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BLURUSDT</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BMTUSDT</t>
+        </is>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BNTUSDT</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BOBUSDT</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>0.006231</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>0.006231</v>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>0.006231</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BOMEUSDT</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>0.0004448</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>0.0004448</v>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>0.0004448</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BRETTUSDT</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>0.007312</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>0.007312</v>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>0.007312</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BREVUSDT</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>0.1282</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BROCCOLI714USDT</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>0.01457</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BROCCOLIF3BUSDT</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>0.003605</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>0.003605</v>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>0.003605</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BRUSDT</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>0.05944</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>0.05944</v>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>0.05944</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BSVUSDT</t>
+        </is>
+      </c>
+      <c r="B208" s="1" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BTCDOMUSDT</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="n">
+        <v>5186.2</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>5186.2</v>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>5186.2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BTRUSDT</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="n">
+        <v>0.11988</v>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>0.11988</v>
+      </c>
+      <c r="D210" s="1" t="n">
+        <v>0.11988</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>BUSDT</t>
+        </is>
+      </c>
+      <c r="B211" s="1" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="D211" s="1" t="n">
+        <v>0.1838</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>C98USDT</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CAKEUSDT</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>1.3921</v>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>1.3921</v>
+      </c>
+      <c r="D213" s="1" t="n">
+        <v>1.3921</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CARVUSDT</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>0.05661</v>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>0.05661</v>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>0.05661</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CATIUSDT</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="D215" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CCUSDT</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="D216" s="1" t="n">
+        <v>0.15121</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CELOUSDT</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CELRUSDT</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="D218" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CETUSUSDT</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="D219" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CFXUSDT</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="D220" s="1" t="n">
+        <v>0.05509</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CGPTUSDT</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>0.02182</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CHILLGUYUSDT</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CHRUSDT</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CHZUSDT</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CKBUSDT</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="n">
+        <v>0.001526</v>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>0.001526</v>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>0.001526</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLANKERUSDT</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="D226" s="1" t="n">
+        <v>27.12</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLOUSDT</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>0.0702</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>COAIUSDT</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="D228" s="1" t="n">
+        <v>0.3111</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>COMPUSDT</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="D229" s="1" t="n">
+        <v>18.42</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>COOKIEUSDT</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="n">
+        <v>0.01947</v>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>0.01947</v>
+      </c>
+      <c r="D230" s="1" t="n">
+        <v>0.01947</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>COTIUSDT</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="D231" s="1" t="n">
+        <v>0.01221</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>COWUSDT</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="D232" s="1" t="n">
+        <v>0.2285</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CROSSUSDT</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="n">
+        <v>0.07113999999999999</v>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>0.07113999999999999</v>
+      </c>
+      <c r="D233" s="1" t="n">
+        <v>0.07113999999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CTKUSDT</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="D234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CTSIUSDT</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="D235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CVCUSDT</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="n">
+        <v>0.03006</v>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>0.03006</v>
+      </c>
+      <c r="D236" s="1" t="n">
+        <v>0.03006</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CVXUSDT</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="C237" s="1" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="D237" s="1" t="n">
+        <v>1.984</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CYSUSDT</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="C238" s="1" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="D238" s="1" t="n">
+        <v>0.4281</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>DAMUSDT</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="n">
+        <v>0.03376</v>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>0.03376</v>
+      </c>
+      <c r="D239" s="1" t="n">
+        <v>0.03376</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>DEEPUSDT</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="D240" s="1" t="n">
+        <v>0.0338</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>DEGENUSDT</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="n">
+        <v>0.0007509</v>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>0.0007509</v>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>0.0007509</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>DIAUSDT</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="D242" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>DODOXUSDT</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="n">
+        <v>0.014827</v>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>0.014827</v>
+      </c>
+      <c r="D243" s="1" t="n">
+        <v>0.014827</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>DOGSUSDT</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="D244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>DOLOUSDT</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="D245" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>DRIFTUSDT</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="n">
+        <v>0.08046</v>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>0.08046</v>
+      </c>
+      <c r="D246" s="1" t="n">
+        <v>0.08046</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>DUSDT</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="n">
+        <v>0.007518</v>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>0.007518</v>
+      </c>
+      <c r="D247" s="1" t="n">
+        <v>0.007518</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>DUSKUSDT</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="n">
+        <v>0.09798999999999999</v>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>0.09798999999999999</v>
+      </c>
+      <c r="D248" s="1" t="n">
+        <v>0.09798999999999999</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>DYDXUSDT</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="D249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>DYMUSDT</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="n">
+        <v>0.03504</v>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>0.03504</v>
+      </c>
+      <c r="D250" s="1" t="n">
+        <v>0.03504</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>EDENUSDT</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="n">
+        <v>0.04058</v>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>0.04058</v>
+      </c>
+      <c r="D251" s="1" t="n">
+        <v>0.04058</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>EDUUSDT</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="D252" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>EGLDUSDT</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="n">
+        <v>4.058</v>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>4.058</v>
+      </c>
+      <c r="D253" s="1" t="n">
+        <v>4.058</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>EIGENUSDT</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="D254" s="1" t="n">
+        <v>0.1866</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ELSAUSDT</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="n">
+        <v>0.07278</v>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>0.07278</v>
+      </c>
+      <c r="D255" s="1" t="n">
+        <v>0.07278</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ENJUSDT</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="D256" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ENSUSDT</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="n">
+        <v>5.942</v>
+      </c>
+      <c r="C257" s="1" t="n">
+        <v>5.942</v>
+      </c>
+      <c r="D257" s="1" t="n">
+        <v>5.942</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>EPICUSDT</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="C258" s="1" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="D258" s="1" t="n">
+        <v>0.2617</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ERAUSDT</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="C259" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="D259" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ESPORTSUSDT</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="D260" s="1" t="n">
+        <v>0.30595</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ESPUSDT</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="n">
+        <v>0.09809</v>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>0.09809</v>
+      </c>
+      <c r="D261" s="1" t="n">
+        <v>0.09809</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ETHFIUSDT</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="C262" s="1" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="D262" s="1" t="n">
+        <v>0.5409</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ETHWUSDT</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="C263" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="D263" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>EULUSDT</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="D264" s="1" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>EVAAUSDT</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="C265" s="1" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="D265" s="1" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FFUSDT</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="C266" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="D266" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FHEUSDT</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="C267" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="D267" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FIDAUSDT</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="C268" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="D268" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FIGHTUSDT</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="n">
+        <v>0.003717</v>
+      </c>
+      <c r="C269" s="1" t="n">
+        <v>0.003717</v>
+      </c>
+      <c r="D269" s="1" t="n">
+        <v>0.003717</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FIOUSDT</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="C270" s="1" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="D270" s="1" t="n">
+        <v>0.00787</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FLOCKUSDT</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="n">
+        <v>0.05495</v>
+      </c>
+      <c r="C271" s="1" t="n">
+        <v>0.05495</v>
+      </c>
+      <c r="D271" s="1" t="n">
+        <v>0.05495</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FLUIDUSDT</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C272" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D272" s="1" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FLUXUSDT</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="n">
+        <v>0.05431</v>
+      </c>
+      <c r="C273" s="1" t="n">
+        <v>0.05431</v>
+      </c>
+      <c r="D273" s="1" t="n">
+        <v>0.05431</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FOGOUSDT</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="C274" s="1" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="D274" s="1" t="n">
+        <v>0.02286</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FOLKSUSDT</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="D275" s="1" t="n">
+        <v>1.185</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>FORMUSDT</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="D276" s="1" t="n">
+        <v>0.2728</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>FORTHUSDT</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>0.953</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>FRAXUSDT</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="n">
+        <v>0.6228</v>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>0.6228</v>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>0.6228</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FUNUSDT</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="n">
+        <v>0.00135</v>
+      </c>
+      <c r="C279" s="1" t="n">
+        <v>0.00135</v>
+      </c>
+      <c r="D279" s="1" t="n">
+        <v>0.00135</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>FUSDT</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="n">
+        <v>0.00554</v>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>0.00554</v>
+      </c>
+      <c r="D280" s="1" t="n">
+        <v>0.00554</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>GASUSDT</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="C281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="D281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>GIGGLEUSDT</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="D282" s="1" t="n">
+        <v>28.36</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>GLMUSDT</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="n">
+        <v>0.12935</v>
+      </c>
+      <c r="C283" s="1" t="n">
+        <v>0.12935</v>
+      </c>
+      <c r="D283" s="1" t="n">
+        <v>0.12935</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>GMTUSDT</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="C284" s="1" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="D284" s="1" t="n">
+        <v>0.01111</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>GMXUSDT</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="n">
+        <v>6.487</v>
+      </c>
+      <c r="C285" s="1" t="n">
+        <v>6.487</v>
+      </c>
+      <c r="D285" s="1" t="n">
+        <v>6.487</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>GOATUSDT</t>
+        </is>
+      </c>
+      <c r="B286" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="C286" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="D286" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>GPSUSDT</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="n">
+        <v>0.008477</v>
+      </c>
+      <c r="C287" s="1" t="n">
+        <v>0.008477</v>
+      </c>
+      <c r="D287" s="1" t="n">
+        <v>0.008477</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>GRASSUSDT</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="C288" s="1" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="D288" s="1" t="n">
+        <v>0.3929</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>GRIFFAINUSDT</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="n">
+        <v>0.010535</v>
+      </c>
+      <c r="C289" s="1" t="n">
+        <v>0.010535</v>
+      </c>
+      <c r="D289" s="1" t="n">
+        <v>0.010535</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>GRTUSDT</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="n">
+        <v>0.02613</v>
+      </c>
+      <c r="C290" s="1" t="n">
+        <v>0.02613</v>
+      </c>
+      <c r="D290" s="1" t="n">
+        <v>0.02613</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>GTCUSDT</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="D291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>GUAUSDT</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="C292" s="1" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="D292" s="1" t="n">
+        <v>0.28585</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>GUNUSDT</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="C293" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="D293" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>GUSDT</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="n">
+        <v>0.003412</v>
+      </c>
+      <c r="C294" s="1" t="n">
+        <v>0.003412</v>
+      </c>
+      <c r="D294" s="1" t="n">
+        <v>0.003412</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>GWEIUSDT</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="n">
+        <v>0.043493</v>
+      </c>
+      <c r="C295" s="1" t="n">
+        <v>0.043493</v>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>0.043493</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>HAEDALUSDT</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="n">
+        <v>0.02953</v>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>0.02953</v>
+      </c>
+      <c r="D296" s="1" t="n">
+        <v>0.02953</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>HANAUSDT</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="C297" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="D297" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>HEIUSDT</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="n">
+        <v>0.08326</v>
+      </c>
+      <c r="C298" s="1" t="n">
+        <v>0.08326</v>
+      </c>
+      <c r="D298" s="1" t="n">
+        <v>0.08326</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>HEMIUSDT</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="C299" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="D299" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>HFTUSDT</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="C300" s="1" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>0.01519</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>HIGHUSDT</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="C301" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>HIPPOUSDT</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="n">
+        <v>0.0006538</v>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>0.0006538</v>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>0.0006538</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>HIVEUSDT</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="C303" s="1" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>0.0621</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>HMSTRUSDT</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="n">
+        <v>0.0001634</v>
+      </c>
+      <c r="C304" s="1" t="n">
+        <v>0.0001634</v>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>0.0001634</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>HOLOUSDT</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="n">
+        <v>0.06086</v>
+      </c>
+      <c r="C305" s="1" t="n">
+        <v>0.06086</v>
+      </c>
+      <c r="D305" s="1" t="n">
+        <v>0.06086</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>HOMEUSDT</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="C306" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="D306" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>HOOKUSDT</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="C307" s="1" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>0.02388</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>HOTUSDT</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="C308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="D308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>HYPERUSDT</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="C309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="D309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ICNTUSDT</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="C310" s="1" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="D310" s="1" t="n">
+        <v>0.387</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ICXUSDT</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="C311" s="1" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="D311" s="1" t="n">
+        <v>0.0357</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>IDOLUSDT</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="n">
+        <v>0.02445</v>
+      </c>
+      <c r="C312" s="1" t="n">
+        <v>0.02445</v>
+      </c>
+      <c r="D312" s="1" t="n">
+        <v>0.02445</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>IDUSDT</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="n">
+        <v>0.04143</v>
+      </c>
+      <c r="C313" s="1" t="n">
+        <v>0.04143</v>
+      </c>
+      <c r="D313" s="1" t="n">
+        <v>0.04143</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ILVUSDT</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="n">
+        <v>3.998</v>
+      </c>
+      <c r="C314" s="1" t="n">
+        <v>3.998</v>
+      </c>
+      <c r="D314" s="1" t="n">
+        <v>3.998</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>IMXUSDT</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="C315" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="D315" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>INITUSDT</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="n">
+        <v>0.08852</v>
+      </c>
+      <c r="C316" s="1" t="n">
+        <v>0.08852</v>
+      </c>
+      <c r="D316" s="1" t="n">
+        <v>0.08852</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>INUSDT</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="n">
+        <v>0.06827999999999999</v>
+      </c>
+      <c r="C317" s="1" t="n">
+        <v>0.06827999999999999</v>
+      </c>
+      <c r="D317" s="1" t="n">
+        <v>0.06827999999999999</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>INXUSDT</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="C318" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="D318" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>IOSTUSDT</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="n">
+        <v>0.001135</v>
+      </c>
+      <c r="C319" s="1" t="n">
+        <v>0.001135</v>
+      </c>
+      <c r="D319" s="1" t="n">
+        <v>0.001135</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>IOTAUSDT</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="C320" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="D320" s="1" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>IOTXUSDT</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="C321" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="D321" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>IOUSDT</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="C322" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="D322" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>IRUSDT</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="n">
+        <v>0.04171</v>
+      </c>
+      <c r="C323" s="1" t="n">
+        <v>0.04171</v>
+      </c>
+      <c r="D323" s="1" t="n">
+        <v>0.04171</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>IRYSUSDT</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+      <c r="C324" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+      <c r="D324" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>JASMYUSDT</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="n">
+        <v>0.005695</v>
+      </c>
+      <c r="C325" s="1" t="n">
+        <v>0.005695</v>
+      </c>
+      <c r="D325" s="1" t="n">
+        <v>0.005695</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>JCTUSDT</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="n">
+        <v>0.001771</v>
+      </c>
+      <c r="C326" s="1" t="n">
+        <v>0.001771</v>
+      </c>
+      <c r="D326" s="1" t="n">
+        <v>0.001771</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>JOEUSDT</t>
+        </is>
+      </c>
+      <c r="B327" s="1" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="C327" s="1" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="D327" s="1" t="n">
+        <v>0.04076</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>JSTUSDT</t>
+        </is>
+      </c>
+      <c r="B328" s="1" t="n">
+        <v>0.053964</v>
+      </c>
+      <c r="C328" s="1" t="n">
+        <v>0.053964</v>
+      </c>
+      <c r="D328" s="1" t="n">
+        <v>0.053964</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>JTOUSDT</t>
+        </is>
+      </c>
+      <c r="B329" s="1" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="C329" s="1" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="D329" s="1" t="n">
+        <v>0.2779</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>JUPUSDT</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="C330" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="D330" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>KAIAUSDT</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="n">
+        <v>0.05348</v>
+      </c>
+      <c r="C331" s="1" t="n">
+        <v>0.05348</v>
+      </c>
+      <c r="D331" s="1" t="n">
+        <v>0.05348</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>KAITOUSDT</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="C332" s="1" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="D332" s="1" t="n">
+        <v>0.3594</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>KASUSDT</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="C333" s="1" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="D333" s="1" t="n">
+        <v>0.03041</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>KATUSDT</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="C334" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="D334" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>KAVAUSDT</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="C335" s="1" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="D335" s="1" t="n">
+        <v>0.0574</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>KERNELUSDT</t>
+        </is>
+      </c>
+      <c r="B336" s="1" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="C336" s="1" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="D336" s="1" t="n">
+        <v>0.09117</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>KGENUSDT</t>
+        </is>
+      </c>
+      <c r="B337" s="1" t="n">
+        <v>0.17619</v>
+      </c>
+      <c r="C337" s="1" t="n">
+        <v>0.17619</v>
+      </c>
+      <c r="D337" s="1" t="n">
+        <v>0.17619</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>KMNOUSDT</t>
+        </is>
+      </c>
+      <c r="B338" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="C338" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="D338" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>KNCUSDT</t>
+        </is>
+      </c>
+      <c r="B339" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="C339" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="D339" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>KOMAUSDT</t>
+        </is>
+      </c>
+      <c r="B340" s="1" t="n">
+        <v>0.008108000000000001</v>
+      </c>
+      <c r="C340" s="1" t="n">
+        <v>0.008108000000000001</v>
+      </c>
+      <c r="D340" s="1" t="n">
+        <v>0.008108000000000001</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>KSMUSDT</t>
+        </is>
+      </c>
+      <c r="B341" s="1" t="n">
+        <v>4.382</v>
+      </c>
+      <c r="C341" s="1" t="n">
+        <v>4.382</v>
+      </c>
+      <c r="D341" s="1" t="n">
+        <v>4.382</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>LABUSDT</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="n">
+        <v>0.19148</v>
+      </c>
+      <c r="C342" s="1" t="n">
+        <v>0.19148</v>
+      </c>
+      <c r="D342" s="1" t="n">
+        <v>0.19148</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>LAYERUSDT</t>
+        </is>
+      </c>
+      <c r="B343" s="1" t="n">
+        <v>0.08266999999999999</v>
+      </c>
+      <c r="C343" s="1" t="n">
+        <v>0.08266999999999999</v>
+      </c>
+      <c r="D343" s="1" t="n">
+        <v>0.08266999999999999</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>LIGHTUSDT</t>
+        </is>
+      </c>
+      <c r="B344" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="C344" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="D344" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>LINEAUSDT</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="n">
+        <v>0.003245</v>
+      </c>
+      <c r="C345" s="1" t="n">
+        <v>0.003245</v>
+      </c>
+      <c r="D345" s="1" t="n">
+        <v>0.003245</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>LISTAUSDT</t>
+        </is>
+      </c>
+      <c r="B346" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="C346" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="D346" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>LPTUSDT</t>
+        </is>
+      </c>
+      <c r="B347" s="1" t="n">
+        <v>2.254</v>
+      </c>
+      <c r="C347" s="1" t="n">
+        <v>2.254</v>
+      </c>
+      <c r="D347" s="1" t="n">
+        <v>2.254</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>LQTYUSDT</t>
+        </is>
+      </c>
+      <c r="B348" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="C348" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="D348" s="1" t="n">
+        <v>0.304</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>LRCUSDT</t>
+        </is>
+      </c>
+      <c r="B349" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="C349" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="D349" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>LSKUSDT</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="C350" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="D350" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>LUMIAUSDT</t>
+        </is>
+      </c>
+      <c r="B351" s="1" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+      <c r="C351" s="1" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+      <c r="D351" s="1" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>LUNA2USDT</t>
+        </is>
+      </c>
+      <c r="B352" s="1" t="n">
+        <v>0.06236</v>
+      </c>
+      <c r="C352" s="1" t="n">
+        <v>0.06236</v>
+      </c>
+      <c r="D352" s="1" t="n">
+        <v>0.06236</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>MAGICUSDT</t>
+        </is>
+      </c>
+      <c r="B353" s="1" t="n">
+        <v>0.06375</v>
+      </c>
+      <c r="C353" s="1" t="n">
+        <v>0.06375</v>
+      </c>
+      <c r="D353" s="1" t="n">
+        <v>0.06375</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>MAGMAUSDT</t>
+        </is>
+      </c>
+      <c r="B354" s="1" t="n">
+        <v>0.10405</v>
+      </c>
+      <c r="C354" s="1" t="n">
+        <v>0.10405</v>
+      </c>
+      <c r="D354" s="1" t="n">
+        <v>0.10405</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>MANAUSDT</t>
+        </is>
+      </c>
+      <c r="B355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="C355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="D355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>MANTAUSDT</t>
+        </is>
+      </c>
+      <c r="B356" s="1" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+      <c r="C356" s="1" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+      <c r="D356" s="1" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>MASKUSDT</t>
+        </is>
+      </c>
+      <c r="B357" s="1" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="C357" s="1" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="D357" s="1" t="n">
+        <v>0.4523</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>MAVIAUSDT</t>
+        </is>
+      </c>
+      <c r="B358" s="1" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="C358" s="1" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="D358" s="1" t="n">
+        <v>0.03517</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>MAVUSDT</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="C359" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="D359" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>MEGAUSDT</t>
+        </is>
+      </c>
+      <c r="B360" s="1" t="n">
+        <v>0.13306</v>
+      </c>
+      <c r="C360" s="1" t="n">
+        <v>0.13306</v>
+      </c>
+      <c r="D360" s="1" t="n">
+        <v>0.13306</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>MEMEUSDT</t>
+        </is>
+      </c>
+      <c r="B361" s="1" t="n">
+        <v>0.0005848</v>
+      </c>
+      <c r="C361" s="1" t="n">
+        <v>0.0005848</v>
+      </c>
+      <c r="D361" s="1" t="n">
+        <v>0.0005848</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>MERLUSDT</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="C362" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="D362" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>METISUSDT</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="C363" s="1" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="D363" s="1" t="n">
+        <v>3.223</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>METUSDT</t>
+        </is>
+      </c>
+      <c r="B364" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="C364" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="D364" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>MEUSDT</t>
+        </is>
+      </c>
+      <c r="B365" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="C365" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="D365" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>MEWUSDT</t>
+        </is>
+      </c>
+      <c r="B366" s="1" t="n">
+        <v>0.0006419</v>
+      </c>
+      <c r="C366" s="1" t="n">
+        <v>0.0006419</v>
+      </c>
+      <c r="D366" s="1" t="n">
+        <v>0.0006419</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>MINAUSDT</t>
+        </is>
+      </c>
+      <c r="B367" s="1" t="n">
+        <v>0.05956</v>
+      </c>
+      <c r="C367" s="1" t="n">
+        <v>0.05956</v>
+      </c>
+      <c r="D367" s="1" t="n">
+        <v>0.05956</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>MIRAUSDT</t>
+        </is>
+      </c>
+      <c r="B368" s="1" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="C368" s="1" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="D368" s="1" t="n">
+        <v>0.0825</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>MITOUSDT</t>
+        </is>
+      </c>
+      <c r="B369" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="C369" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="D369" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>MLNUSDT</t>
+        </is>
+      </c>
+      <c r="B370" s="1" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="C370" s="1" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="D370" s="1" t="n">
+        <v>3.727</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>MMTUSDT</t>
+        </is>
+      </c>
+      <c r="B371" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="C371" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="D371" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>MOCAUSDT</t>
+        </is>
+      </c>
+      <c r="B372" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="C372" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="D372" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>MONUSDT</t>
+        </is>
+      </c>
+      <c r="B373" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="C373" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="D373" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>MORPHOUSDT</t>
+        </is>
+      </c>
+      <c r="B374" s="1" t="n">
+        <v>1.8539</v>
+      </c>
+      <c r="C374" s="1" t="n">
+        <v>1.8539</v>
+      </c>
+      <c r="D374" s="1" t="n">
+        <v>1.8539</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>MOVEUSDT</t>
+        </is>
+      </c>
+      <c r="B375" s="1" t="n">
+        <v>0.02095</v>
+      </c>
+      <c r="C375" s="1" t="n">
+        <v>0.02095</v>
+      </c>
+      <c r="D375" s="1" t="n">
+        <v>0.02095</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>MOVRUSDT</t>
+        </is>
+      </c>
+      <c r="B376" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="C376" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="D376" s="1" t="n">
+        <v>1.296</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>MTLUSDT</t>
+        </is>
+      </c>
+      <c r="B377" s="1" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="C377" s="1" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="D377" s="1" t="n">
+        <v>0.2845</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>MUBARAKUSDT</t>
+        </is>
+      </c>
+      <c r="B378" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="C378" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="D378" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>MUSDT</t>
+        </is>
+      </c>
+      <c r="B379" s="1" t="n">
+        <v>1.5349</v>
+      </c>
+      <c r="C379" s="1" t="n">
+        <v>1.5349</v>
+      </c>
+      <c r="D379" s="1" t="n">
+        <v>1.5349</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>NEIROUSDT</t>
+        </is>
+      </c>
+      <c r="B380" s="1" t="n">
+        <v>6.962e-05</v>
+      </c>
+      <c r="C380" s="1" t="n">
+        <v>6.962e-05</v>
+      </c>
+      <c r="D380" s="1" t="n">
+        <v>6.962e-05</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>NEOUSDT</t>
+        </is>
+      </c>
+      <c r="B381" s="1" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="C381" s="1" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="D381" s="1" t="n">
+        <v>2.551</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>NEWTUSDT</t>
+        </is>
+      </c>
+      <c r="B382" s="1" t="n">
+        <v>0.06745</v>
+      </c>
+      <c r="C382" s="1" t="n">
+        <v>0.06745</v>
+      </c>
+      <c r="D382" s="1" t="n">
+        <v>0.06745</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>NFPUSDT</t>
+        </is>
+      </c>
+      <c r="B383" s="1" t="n">
+        <v>0.01745</v>
+      </c>
+      <c r="C383" s="1" t="n">
+        <v>0.01745</v>
+      </c>
+      <c r="D383" s="1" t="n">
+        <v>0.01745</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>NILUSDT</t>
+        </is>
+      </c>
+      <c r="B384" s="1" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="C384" s="1" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="D384" s="1" t="n">
+        <v>0.05065</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>NMRUSDT</t>
+        </is>
+      </c>
+      <c r="B385" s="1" t="n">
+        <v>7.554</v>
+      </c>
+      <c r="C385" s="1" t="n">
+        <v>7.554</v>
+      </c>
+      <c r="D385" s="1" t="n">
+        <v>7.554</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>NOMUSDT</t>
+        </is>
+      </c>
+      <c r="B386" s="1" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="C386" s="1" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="D386" s="1" t="n">
+        <v>0.00327</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>NOTUSDT</t>
+        </is>
+      </c>
+      <c r="B387" s="1" t="n">
+        <v>0.0003838</v>
+      </c>
+      <c r="C387" s="1" t="n">
+        <v>0.0003838</v>
+      </c>
+      <c r="D387" s="1" t="n">
+        <v>0.0003838</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>NTRNUSDT</t>
+        </is>
+      </c>
+      <c r="B388" s="1" t="n">
+        <v>0.009769999999999999</v>
+      </c>
+      <c r="C388" s="1" t="n">
+        <v>0.009769999999999999</v>
+      </c>
+      <c r="D388" s="1" t="n">
+        <v>0.009769999999999999</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>NXPCUSDT</t>
+        </is>
+      </c>
+      <c r="B389" s="1" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="C389" s="1" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="D389" s="1" t="n">
+        <v>0.2889</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>OGNUSDT</t>
+        </is>
+      </c>
+      <c r="B390" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="C390" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="D390" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>OGUSDT</t>
+        </is>
+      </c>
+      <c r="B391" s="1" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="C391" s="1" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="D391" s="1" t="n">
+        <v>2.815</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>OLUSDT</t>
+        </is>
+      </c>
+      <c r="B392" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="C392" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="D392" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>ONEUSDT</t>
+        </is>
+      </c>
+      <c r="B393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="C393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ONGUSDT</t>
+        </is>
+      </c>
+      <c r="B394" s="1" t="n">
+        <v>0.05922</v>
+      </c>
+      <c r="C394" s="1" t="n">
+        <v>0.05922</v>
+      </c>
+      <c r="D394" s="1" t="n">
+        <v>0.05922</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>ONTUSDT</t>
+        </is>
+      </c>
+      <c r="B395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="C395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="D395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>ONUSDT</t>
+        </is>
+      </c>
+      <c r="B396" s="1" t="n">
+        <v>0.09127</v>
+      </c>
+      <c r="C396" s="1" t="n">
+        <v>0.09127</v>
+      </c>
+      <c r="D396" s="1" t="n">
+        <v>0.09127</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>OPENUSDT</t>
+        </is>
+      </c>
+      <c r="B397" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="C397" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="D397" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>ORCAUSDT</t>
+        </is>
+      </c>
+      <c r="B398" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="C398" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="D398" s="1" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ORDERUSDT</t>
+        </is>
+      </c>
+      <c r="B399" s="1" t="n">
+        <v>0.05215</v>
+      </c>
+      <c r="C399" s="1" t="n">
+        <v>0.05215</v>
+      </c>
+      <c r="D399" s="1" t="n">
+        <v>0.05215</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ORDIUSDT</t>
+        </is>
+      </c>
+      <c r="B400" s="1" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="C400" s="1" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="D400" s="1" t="n">
+        <v>2.517</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>OXTUSDT</t>
+        </is>
+      </c>
+      <c r="B401" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="C401" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="D401" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>PARTIUSDT</t>
+        </is>
+      </c>
+      <c r="B402" s="1" t="n">
+        <v>0.07953</v>
+      </c>
+      <c r="C402" s="1" t="n">
+        <v>0.07953</v>
+      </c>
+      <c r="D402" s="1" t="n">
+        <v>0.07953</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>PENDLEUSDT</t>
+        </is>
+      </c>
+      <c r="B403" s="1" t="n">
+        <v>1.2484</v>
+      </c>
+      <c r="C403" s="1" t="n">
+        <v>1.2484</v>
+      </c>
+      <c r="D403" s="1" t="n">
+        <v>1.2484</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>PEOPLEUSDT</t>
+        </is>
+      </c>
+      <c r="B404" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="C404" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="D404" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>PIEVERSEUSDT</t>
+        </is>
+      </c>
+      <c r="B405" s="1" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="C405" s="1" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="D405" s="1" t="n">
+        <v>0.4987</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>PLUMEUSDT</t>
+        </is>
+      </c>
+      <c r="B406" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="C406" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="D406" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>PNUTUSDT</t>
+        </is>
+      </c>
+      <c r="B407" s="1" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="C407" s="1" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="D407" s="1" t="n">
+        <v>0.0464</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>POLYXUSDT</t>
+        </is>
+      </c>
+      <c r="B408" s="1" t="n">
+        <v>0.03947</v>
+      </c>
+      <c r="C408" s="1" t="n">
+        <v>0.03947</v>
+      </c>
+      <c r="D408" s="1" t="n">
+        <v>0.03947</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>POPCATUSDT</t>
+        </is>
+      </c>
+      <c r="B409" s="1" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="C409" s="1" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="D409" s="1" t="n">
+        <v>0.05276</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>PORTALUSDT</t>
+        </is>
+      </c>
+      <c r="B410" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="C410" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="D410" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>POWRUSDT</t>
+        </is>
+      </c>
+      <c r="B411" s="1" t="n">
+        <v>0.06378</v>
+      </c>
+      <c r="C411" s="1" t="n">
+        <v>0.06378</v>
+      </c>
+      <c r="D411" s="1" t="n">
+        <v>0.06378</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>PROMPTUSDT</t>
+        </is>
+      </c>
+      <c r="B412" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="C412" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="D412" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>PROMUSDT</t>
+        </is>
+      </c>
+      <c r="B413" s="1" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="C413" s="1" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="D413" s="1" t="n">
+        <v>1.117</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>PROVEUSDT</t>
+        </is>
+      </c>
+      <c r="B414" s="1" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="C414" s="1" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="D414" s="1" t="n">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>PTBUSDT</t>
+        </is>
+      </c>
+      <c r="B415" s="1" t="n">
+        <v>0.001222</v>
+      </c>
+      <c r="C415" s="1" t="n">
+        <v>0.001222</v>
+      </c>
+      <c r="D415" s="1" t="n">
+        <v>0.001222</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>PUFFERUSDT</t>
+        </is>
+      </c>
+      <c r="B416" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="C416" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="D416" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>PUMPBTCUSDT</t>
+        </is>
+      </c>
+      <c r="B417" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="C417" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="D417" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>PUNDIXUSDT</t>
+        </is>
+      </c>
+      <c r="B418" s="1" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="C418" s="1" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="D418" s="1" t="n">
+        <v>0.1479</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>PYTHUSDT</t>
+        </is>
+      </c>
+      <c r="B419" s="1" t="n">
+        <v>0.04862</v>
+      </c>
+      <c r="C419" s="1" t="n">
+        <v>0.04862</v>
+      </c>
+      <c r="D419" s="1" t="n">
+        <v>0.04862</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>QNTUSDT</t>
+        </is>
+      </c>
+      <c r="B420" s="1" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="C420" s="1" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="D420" s="1" t="n">
+        <v>65.70999999999999</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>QTUMUSDT</t>
+        </is>
+      </c>
+      <c r="B421" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C421" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D421" s="1" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>QUSDT</t>
+        </is>
+      </c>
+      <c r="B422" s="1" t="n">
+        <v>0.012972</v>
+      </c>
+      <c r="C422" s="1" t="n">
+        <v>0.012972</v>
+      </c>
+      <c r="D422" s="1" t="n">
+        <v>0.012972</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>RAREUSDT</t>
+        </is>
+      </c>
+      <c r="B423" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="C423" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="D423" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>RAVEUSDT</t>
+        </is>
+      </c>
+      <c r="B424" s="1" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="C424" s="1" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="D424" s="1" t="n">
+        <v>0.26036</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>RAYSOLUSDT</t>
+        </is>
+      </c>
+      <c r="B425" s="1" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="C425" s="1" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="D425" s="1" t="n">
+        <v>0.599</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>RDNTUSDT</t>
+        </is>
+      </c>
+      <c r="B426" s="1" t="n">
+        <v>0.005657</v>
+      </c>
+      <c r="C426" s="1" t="n">
+        <v>0.005657</v>
+      </c>
+      <c r="D426" s="1" t="n">
+        <v>0.005657</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>RECALLUSDT</t>
+        </is>
+      </c>
+      <c r="B427" s="1" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="C427" s="1" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="D427" s="1" t="n">
+        <v>0.04899</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>REDUSDT</t>
+        </is>
+      </c>
+      <c r="B428" s="1" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="C428" s="1" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="D428" s="1" t="n">
+        <v>0.1254</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>REZUSDT</t>
+        </is>
+      </c>
+      <c r="B429" s="1" t="n">
+        <v>0.003197</v>
+      </c>
+      <c r="C429" s="1" t="n">
+        <v>0.003197</v>
+      </c>
+      <c r="D429" s="1" t="n">
+        <v>0.003197</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>RIFUSDT</t>
+        </is>
+      </c>
+      <c r="B430" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="C430" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="D430" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>RLCUSDT</t>
+        </is>
+      </c>
+      <c r="B431" s="1" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="C431" s="1" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="D431" s="1" t="n">
+        <v>0.401</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>RLSUSDT</t>
+        </is>
+      </c>
+      <c r="B432" s="1" t="n">
+        <v>0.004519</v>
+      </c>
+      <c r="C432" s="1" t="n">
+        <v>0.004519</v>
+      </c>
+      <c r="D432" s="1" t="n">
+        <v>0.004519</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>RONINUSDT</t>
+        </is>
+      </c>
+      <c r="B433" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="C433" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="D433" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>ROSEUSDT</t>
+        </is>
+      </c>
+      <c r="B434" s="1" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="C434" s="1" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="D434" s="1" t="n">
+        <v>0.01238</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>RPLUSDT</t>
+        </is>
+      </c>
+      <c r="B435" s="1" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="C435" s="1" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="D435" s="1" t="n">
+        <v>1.968</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>RSRUSDT</t>
+        </is>
+      </c>
+      <c r="B436" s="1" t="n">
+        <v>0.001848</v>
+      </c>
+      <c r="C436" s="1" t="n">
+        <v>0.001848</v>
+      </c>
+      <c r="D436" s="1" t="n">
+        <v>0.001848</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>RUNEUSDT</t>
+        </is>
+      </c>
+      <c r="B437" s="1" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="C437" s="1" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="D437" s="1" t="n">
+        <v>0.4417</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>RVNUSDT</t>
+        </is>
+      </c>
+      <c r="B438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="C438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="D438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>SAFEUSDT</t>
+        </is>
+      </c>
+      <c r="B439" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="C439" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="D439" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>SAGAUSDT</t>
+        </is>
+      </c>
+      <c r="B440" s="1" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="C440" s="1" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="D440" s="1" t="n">
+        <v>0.0342</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>SANDUSDT</t>
+        </is>
+      </c>
+      <c r="B441" s="1" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="C441" s="1" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="D441" s="1" t="n">
+        <v>0.08201</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>SANTOSUSDT</t>
+        </is>
+      </c>
+      <c r="B442" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="C442" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="D442" s="1" t="n">
+        <v>1.307</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>SAPIENUSDT</t>
+        </is>
+      </c>
+      <c r="B443" s="1" t="n">
+        <v>0.07550999999999999</v>
+      </c>
+      <c r="C443" s="1" t="n">
+        <v>0.07550999999999999</v>
+      </c>
+      <c r="D443" s="1" t="n">
+        <v>0.07550999999999999</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>SCRTUSDT</t>
+        </is>
+      </c>
+      <c r="B444" s="1" t="n">
+        <v>0.07661</v>
+      </c>
+      <c r="C444" s="1" t="n">
+        <v>0.07661</v>
+      </c>
+      <c r="D444" s="1" t="n">
+        <v>0.07661</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>SCRUSDT</t>
+        </is>
+      </c>
+      <c r="B445" s="1" t="n">
+        <v>0.04357</v>
+      </c>
+      <c r="C445" s="1" t="n">
+        <v>0.04357</v>
+      </c>
+      <c r="D445" s="1" t="n">
+        <v>0.04357</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>SENTUSDT</t>
+        </is>
+      </c>
+      <c r="B446" s="1" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="C446" s="1" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="D446" s="1" t="n">
+        <v>0.0216</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>SFPUSDT</t>
+        </is>
+      </c>
+      <c r="B447" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="C447" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="D447" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>SHELLUSDT</t>
+        </is>
+      </c>
+      <c r="B448" s="1" t="n">
+        <v>0.03141</v>
+      </c>
+      <c r="C448" s="1" t="n">
+        <v>0.03141</v>
+      </c>
+      <c r="D448" s="1" t="n">
+        <v>0.03141</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>SKLUSDT</t>
+        </is>
+      </c>
+      <c r="B449" s="1" t="n">
+        <v>0.00642</v>
+      </c>
+      <c r="C449" s="1" t="n">
+        <v>0.00642</v>
+      </c>
+      <c r="D449" s="1" t="n">
+        <v>0.00642</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>SKRUSDT</t>
+        </is>
+      </c>
+      <c r="B450" s="1" t="n">
+        <v>0.022879</v>
+      </c>
+      <c r="C450" s="1" t="n">
+        <v>0.022879</v>
+      </c>
+      <c r="D450" s="1" t="n">
+        <v>0.022879</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>SKYAIUSDT</t>
+        </is>
+      </c>
+      <c r="B451" s="1" t="n">
+        <v>0.04223</v>
+      </c>
+      <c r="C451" s="1" t="n">
+        <v>0.04223</v>
+      </c>
+      <c r="D451" s="1" t="n">
+        <v>0.04223</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>SKYUSDT</t>
+        </is>
+      </c>
+      <c r="B452" s="1" t="n">
+        <v>0.07363</v>
+      </c>
+      <c r="C452" s="1" t="n">
+        <v>0.07363</v>
+      </c>
+      <c r="D452" s="1" t="n">
+        <v>0.07363</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>SLPUSDT</t>
+        </is>
+      </c>
+      <c r="B453" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+      <c r="C453" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+      <c r="D453" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>SNXUSDT</t>
+        </is>
+      </c>
+      <c r="B454" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="C454" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="D454" s="1" t="n">
+        <v>0.307</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>SOLVUSDT</t>
+        </is>
+      </c>
+      <c r="B455" s="1" t="n">
+        <v>0.004208</v>
+      </c>
+      <c r="C455" s="1" t="n">
+        <v>0.004208</v>
+      </c>
+      <c r="D455" s="1" t="n">
+        <v>0.004208</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>SOMIUSDT</t>
+        </is>
+      </c>
+      <c r="B456" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="C456" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="D456" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>SONICUSDT</t>
+        </is>
+      </c>
+      <c r="B457" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="C457" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="D457" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>SOONUSDT</t>
+        </is>
+      </c>
+      <c r="B458" s="1" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="C458" s="1" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="D458" s="1" t="n">
+        <v>0.1459</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>SOPHUSDT</t>
+        </is>
+      </c>
+      <c r="B459" s="1" t="n">
+        <v>0.008574</v>
+      </c>
+      <c r="C459" s="1" t="n">
+        <v>0.008574</v>
+      </c>
+      <c r="D459" s="1" t="n">
+        <v>0.008574</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>SPACEUSDT</t>
+        </is>
+      </c>
+      <c r="B460" s="1" t="n">
+        <v>0.007521</v>
+      </c>
+      <c r="C460" s="1" t="n">
+        <v>0.007521</v>
+      </c>
+      <c r="D460" s="1" t="n">
+        <v>0.007521</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>SPELLUSDT</t>
+        </is>
+      </c>
+      <c r="B461" s="1" t="n">
+        <v>0.0001722</v>
+      </c>
+      <c r="C461" s="1" t="n">
+        <v>0.0001722</v>
+      </c>
+      <c r="D461" s="1" t="n">
+        <v>0.0001722</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>SPKUSDT</t>
+        </is>
+      </c>
+      <c r="B462" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="C462" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="D462" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>SPORTFUNUSDT</t>
+        </is>
+      </c>
+      <c r="B463" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="C463" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="D463" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>SPXUSDT</t>
+        </is>
+      </c>
+      <c r="B464" s="1" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="C464" s="1" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="D464" s="1" t="n">
+        <v>0.3031</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>SQDUSDT</t>
+        </is>
+      </c>
+      <c r="B465" s="1" t="n">
+        <v>0.03923</v>
+      </c>
+      <c r="C465" s="1" t="n">
+        <v>0.03923</v>
+      </c>
+      <c r="D465" s="1" t="n">
+        <v>0.03923</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>SSVUSDT</t>
+        </is>
+      </c>
+      <c r="B466" s="1" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="C466" s="1" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="D466" s="1" t="n">
+        <v>2.682</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>STBLUSDT</t>
+        </is>
+      </c>
+      <c r="B467" s="1" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="C467" s="1" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="D467" s="1" t="n">
+        <v>0.0337</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>STGUSDT</t>
+        </is>
+      </c>
+      <c r="B468" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="C468" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="D468" s="1" t="n">
+        <v>0.176</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>STORJUSDT</t>
+        </is>
+      </c>
+      <c r="B469" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="C469" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="D469" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>STOUSDT</t>
+        </is>
+      </c>
+      <c r="B470" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="C470" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="D470" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>STRKUSDT</t>
+        </is>
+      </c>
+      <c r="B471" s="1" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="C471" s="1" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="D471" s="1" t="n">
+        <v>0.03978</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>STXUSDT</t>
+        </is>
+      </c>
+      <c r="B472" s="1" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="D472" s="1" t="n">
+        <v>0.2477</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>SUNUSDT</t>
+        </is>
+      </c>
+      <c r="B473" s="1" t="n">
+        <v>0.016588</v>
+      </c>
+      <c r="C473" s="1" t="n">
+        <v>0.016588</v>
+      </c>
+      <c r="D473" s="1" t="n">
+        <v>0.016588</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>SUPERUSDT</t>
+        </is>
+      </c>
+      <c r="B474" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="C474" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="D474" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>SUSDT</t>
+        </is>
+      </c>
+      <c r="B475" s="1" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="C475" s="1" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="D475" s="1" t="n">
+        <v>0.04264</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>SUSHIUSDT</t>
+        </is>
+      </c>
+      <c r="B476" s="1" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="C476" s="1" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="D476" s="1" t="n">
+        <v>0.2071</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>SWARMSUSDT</t>
+        </is>
+      </c>
+      <c r="B477" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+      <c r="C477" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+      <c r="D477" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>SXTUSDT</t>
+        </is>
+      </c>
+      <c r="B478" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="C478" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="D478" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>SYNUSDT</t>
+        </is>
+      </c>
+      <c r="B479" s="1" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="C479" s="1" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="D479" s="1" t="n">
+        <v>0.0473</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>SYRUPUSDT</t>
+        </is>
+      </c>
+      <c r="B480" s="1" t="n">
+        <v>0.25884</v>
+      </c>
+      <c r="C480" s="1" t="n">
+        <v>0.25884</v>
+      </c>
+      <c r="D480" s="1" t="n">
+        <v>0.25884</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>SYSUSDT</t>
+        </is>
+      </c>
+      <c r="B481" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="C481" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="D481" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>TACUSDT</t>
+        </is>
+      </c>
+      <c r="B482" s="1" t="n">
+        <v>0.004063</v>
+      </c>
+      <c r="C482" s="1" t="n">
+        <v>0.004063</v>
+      </c>
+      <c r="D482" s="1" t="n">
+        <v>0.004063</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>TAIKOUSDT</t>
+        </is>
+      </c>
+      <c r="B483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="C483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="D483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>TAKEUSDT</t>
+        </is>
+      </c>
+      <c r="B484" s="1" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="C484" s="1" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="D484" s="1" t="n">
+        <v>0.02166</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>TAUSDT</t>
+        </is>
+      </c>
+      <c r="B485" s="1" t="n">
+        <v>0.04638</v>
+      </c>
+      <c r="C485" s="1" t="n">
+        <v>0.04638</v>
+      </c>
+      <c r="D485" s="1" t="n">
+        <v>0.04638</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>THETAUSDT</t>
+        </is>
+      </c>
+      <c r="B486" s="1" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="C486" s="1" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="D486" s="1" t="n">
+        <v>0.1732</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>THEUSDT</t>
+        </is>
+      </c>
+      <c r="B487" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="C487" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="D487" s="1" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>TNSRUSDT</t>
+        </is>
+      </c>
+      <c r="B488" s="1" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="C488" s="1" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="D488" s="1" t="n">
+        <v>0.04625</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>TOSHIUSDT</t>
+        </is>
+      </c>
+      <c r="B489" s="1" t="n">
+        <v>0.0002151</v>
+      </c>
+      <c r="C489" s="1" t="n">
+        <v>0.0002151</v>
+      </c>
+      <c r="D489" s="1" t="n">
+        <v>0.0002151</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>TRADOORUSDT</t>
+        </is>
+      </c>
+      <c r="B490" s="1" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="C490" s="1" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="D490" s="1" t="n">
+        <v>1.762</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>TRBUSDT</t>
+        </is>
+      </c>
+      <c r="B491" s="1" t="n">
+        <v>15.996</v>
+      </c>
+      <c r="C491" s="1" t="n">
+        <v>15.996</v>
+      </c>
+      <c r="D491" s="1" t="n">
+        <v>15.996</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>TREEUSDT</t>
+        </is>
+      </c>
+      <c r="B492" s="1" t="n">
+        <v>0.06648</v>
+      </c>
+      <c r="C492" s="1" t="n">
+        <v>0.06648</v>
+      </c>
+      <c r="D492" s="1" t="n">
+        <v>0.06648</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>TRUSTUSDT</t>
+        </is>
+      </c>
+      <c r="B493" s="1" t="n">
+        <v>0.06734999999999999</v>
+      </c>
+      <c r="C493" s="1" t="n">
+        <v>0.06734999999999999</v>
+      </c>
+      <c r="D493" s="1" t="n">
+        <v>0.06734999999999999</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>TRUTHUSDT</t>
+        </is>
+      </c>
+      <c r="B494" s="1" t="n">
+        <v>0.009375</v>
+      </c>
+      <c r="C494" s="1" t="n">
+        <v>0.009375</v>
+      </c>
+      <c r="D494" s="1" t="n">
+        <v>0.009375</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>TRUUSDT</t>
+        </is>
+      </c>
+      <c r="B495" s="1" t="n">
+        <v>0.005936</v>
+      </c>
+      <c r="C495" s="1" t="n">
+        <v>0.005936</v>
+      </c>
+      <c r="D495" s="1" t="n">
+        <v>0.005936</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>TSTUSDT</t>
+        </is>
+      </c>
+      <c r="B496" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="C496" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="D496" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>TURTLEUSDT</t>
+        </is>
+      </c>
+      <c r="B497" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="C497" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="D497" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>TUSDT</t>
+        </is>
+      </c>
+      <c r="B498" s="1" t="n">
+        <v>0.006405</v>
+      </c>
+      <c r="C498" s="1" t="n">
+        <v>0.006405</v>
+      </c>
+      <c r="D498" s="1" t="n">
+        <v>0.006405</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>TUTUSDT</t>
+        </is>
+      </c>
+      <c r="B499" s="1" t="n">
+        <v>0.01044</v>
+      </c>
+      <c r="C499" s="1" t="n">
+        <v>0.01044</v>
+      </c>
+      <c r="D499" s="1" t="n">
+        <v>0.01044</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>TWTUSDT</t>
+        </is>
+      </c>
+      <c r="B500" s="1" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="C500" s="1" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="D500" s="1" t="n">
+        <v>0.5089</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>UBUSDT</t>
+        </is>
+      </c>
+      <c r="B501" s="1" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="C501" s="1" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="D501" s="1" t="n">
+        <v>0.03205</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>UMAUSDT</t>
+        </is>
+      </c>
+      <c r="B502" s="1" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="C502" s="1" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="D502" s="1" t="n">
+        <v>0.4359</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>USDCUSDT</t>
+        </is>
+      </c>
+      <c r="B503" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="C503" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="D503" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>USELESSUSDT</t>
+        </is>
+      </c>
+      <c r="B504" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="C504" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="D504" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>USTCUSDT</t>
+        </is>
+      </c>
+      <c r="B505" s="1" t="n">
+        <v>0.004893</v>
+      </c>
+      <c r="C505" s="1" t="n">
+        <v>0.004893</v>
+      </c>
+      <c r="D505" s="1" t="n">
+        <v>0.004893</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>USUALUSDT</t>
+        </is>
+      </c>
+      <c r="B506" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="C506" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="D506" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>USUSDT</t>
+        </is>
+      </c>
+      <c r="B507" s="1" t="n">
+        <v>0.003478</v>
+      </c>
+      <c r="C507" s="1" t="n">
+        <v>0.003478</v>
+      </c>
+      <c r="D507" s="1" t="n">
+        <v>0.003478</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>VANAUSDT</t>
+        </is>
+      </c>
+      <c r="B508" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="C508" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="D508" s="1" t="n">
+        <v>1.417</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>VANRYUSDT</t>
+        </is>
+      </c>
+      <c r="B509" s="1" t="n">
+        <v>0.005102</v>
+      </c>
+      <c r="C509" s="1" t="n">
+        <v>0.005102</v>
+      </c>
+      <c r="D509" s="1" t="n">
+        <v>0.005102</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>VELODROMEUSDT</t>
+        </is>
+      </c>
+      <c r="B510" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="C510" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="D510" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>VELVETUSDT</t>
+        </is>
+      </c>
+      <c r="B511" s="1" t="n">
+        <v>0.08361</v>
+      </c>
+      <c r="C511" s="1" t="n">
+        <v>0.08361</v>
+      </c>
+      <c r="D511" s="1" t="n">
+        <v>0.08361</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>VETUSDT</t>
+        </is>
+      </c>
+      <c r="B512" s="1" t="n">
+        <v>0.007105</v>
+      </c>
+      <c r="C512" s="1" t="n">
+        <v>0.007105</v>
+      </c>
+      <c r="D512" s="1" t="n">
+        <v>0.007105</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>VFYUSDT</t>
+        </is>
+      </c>
+      <c r="B513" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="C513" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="D513" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>VICUSDT</t>
+        </is>
+      </c>
+      <c r="B514" s="1" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="C514" s="1" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="D514" s="1" t="n">
+        <v>0.04768</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>VINEUSDT</t>
+        </is>
+      </c>
+      <c r="B515" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="C515" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="D515" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>VTHOUSDT</t>
+        </is>
+      </c>
+      <c r="B516" s="1" t="n">
+        <v>0.0005792</v>
+      </c>
+      <c r="C516" s="1" t="n">
+        <v>0.0005792</v>
+      </c>
+      <c r="D516" s="1" t="n">
+        <v>0.0005792</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>WALUSDT</t>
+        </is>
+      </c>
+      <c r="B517" s="1" t="n">
+        <v>0.07829</v>
+      </c>
+      <c r="C517" s="1" t="n">
+        <v>0.07829</v>
+      </c>
+      <c r="D517" s="1" t="n">
+        <v>0.07829</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>WAXPUSDT</t>
+        </is>
+      </c>
+      <c r="B518" s="1" t="n">
+        <v>0.006386</v>
+      </c>
+      <c r="C518" s="1" t="n">
+        <v>0.006386</v>
+      </c>
+      <c r="D518" s="1" t="n">
+        <v>0.006386</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>WCTUSDT</t>
+        </is>
+      </c>
+      <c r="B519" s="1" t="n">
+        <v>0.05803</v>
+      </c>
+      <c r="C519" s="1" t="n">
+        <v>0.05803</v>
+      </c>
+      <c r="D519" s="1" t="n">
+        <v>0.05803</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>WETUSDT</t>
+        </is>
+      </c>
+      <c r="B520" s="1" t="n">
+        <v>0.10496</v>
+      </c>
+      <c r="C520" s="1" t="n">
+        <v>0.10496</v>
+      </c>
+      <c r="D520" s="1" t="n">
+        <v>0.10496</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>WOOUSDT</t>
+        </is>
+      </c>
+      <c r="B521" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="C521" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="D521" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>WUSDT</t>
+        </is>
+      </c>
+      <c r="B522" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="C522" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="D522" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>XAIUSDT</t>
+        </is>
+      </c>
+      <c r="B523" s="1" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="C523" s="1" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="D523" s="1" t="n">
+        <v>0.01083</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>XANUSDT</t>
+        </is>
+      </c>
+      <c r="B524" s="1" t="n">
+        <v>0.006771</v>
+      </c>
+      <c r="C524" s="1" t="n">
+        <v>0.006771</v>
+      </c>
+      <c r="D524" s="1" t="n">
+        <v>0.006771</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>XNYUSDT</t>
+        </is>
+      </c>
+      <c r="B525" s="1" t="n">
+        <v>0.005998</v>
+      </c>
+      <c r="C525" s="1" t="n">
+        <v>0.005998</v>
+      </c>
+      <c r="D525" s="1" t="n">
+        <v>0.005998</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>XPINUSDT</t>
+        </is>
+      </c>
+      <c r="B526" s="1" t="n">
+        <v>0.001449</v>
+      </c>
+      <c r="C526" s="1" t="n">
+        <v>0.001449</v>
+      </c>
+      <c r="D526" s="1" t="n">
+        <v>0.001449</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>XTZUSDT</t>
+        </is>
+      </c>
+      <c r="B527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="C527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="D527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>XVGUSDT</t>
+        </is>
+      </c>
+      <c r="B528" s="1" t="n">
+        <v>0.005138</v>
+      </c>
+      <c r="C528" s="1" t="n">
+        <v>0.005138</v>
+      </c>
+      <c r="D528" s="1" t="n">
+        <v>0.005138</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>XVSUSDT</t>
+        </is>
+      </c>
+      <c r="B529" s="1" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="C529" s="1" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="D529" s="1" t="n">
+        <v>2.917</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>YBUSDT</t>
+        </is>
+      </c>
+      <c r="B530" s="1" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="C530" s="1" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="D530" s="1" t="n">
+        <v>0.1554</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>YFIUSDT</t>
+        </is>
+      </c>
+      <c r="B531" s="1" t="n">
+        <v>2540</v>
+      </c>
+      <c r="C531" s="1" t="n">
+        <v>2540</v>
+      </c>
+      <c r="D531" s="1" t="n">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>YGGUSDT</t>
+        </is>
+      </c>
+      <c r="B532" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="C532" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="D532" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>ZAMAUSDT</t>
+        </is>
+      </c>
+      <c r="B533" s="1" t="n">
+        <v>0.02157</v>
+      </c>
+      <c r="C533" s="1" t="n">
+        <v>0.02157</v>
+      </c>
+      <c r="D533" s="1" t="n">
+        <v>0.02157</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>ZBTUSDT</t>
+        </is>
+      </c>
+      <c r="B534" s="1" t="n">
+        <v>0.07267</v>
+      </c>
+      <c r="C534" s="1" t="n">
+        <v>0.07267</v>
+      </c>
+      <c r="D534" s="1" t="n">
+        <v>0.07267</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>ZEREBROUSDT</t>
+        </is>
+      </c>
+      <c r="B535" s="1" t="n">
+        <v>0.007766</v>
+      </c>
+      <c r="C535" s="1" t="n">
+        <v>0.007766</v>
+      </c>
+      <c r="D535" s="1" t="n">
+        <v>0.007766</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>ZETAUSDT</t>
+        </is>
+      </c>
+      <c r="B536" s="1" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="C536" s="1" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="D536" s="1" t="n">
+        <v>0.05002</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ZILUSDT</t>
+        </is>
+      </c>
+      <c r="B537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="C537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="D537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>ZKCUSDT</t>
+        </is>
+      </c>
+      <c r="B538" s="1" t="n">
+        <v>0.08284</v>
+      </c>
+      <c r="C538" s="1" t="n">
+        <v>0.08284</v>
+      </c>
+      <c r="D538" s="1" t="n">
+        <v>0.08284</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>ZKJUSDT</t>
+        </is>
+      </c>
+      <c r="B539" s="1" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="C539" s="1" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="D539" s="1" t="n">
+        <v>0.02499</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ZKPUSDT</t>
+        </is>
+      </c>
+      <c r="B540" s="1" t="n">
+        <v>0.08461</v>
+      </c>
+      <c r="C540" s="1" t="n">
+        <v>0.08461</v>
+      </c>
+      <c r="D540" s="1" t="n">
+        <v>0.08461</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>ZKUSDT</t>
+        </is>
+      </c>
+      <c r="B541" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="C541" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="D541" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ZORAUSDT</t>
+        </is>
+      </c>
+      <c r="B542" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="C542" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="D542" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ZRXUSDT</t>
+        </is>
+      </c>
+      <c r="B543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="C543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="D543" s="1" t="n">
+        <v>0.1047</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,14 +416,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E543"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,10 +445,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>price_00:45</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -466,9 +472,12 @@
         <v>70623.2</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>70610</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>70623.2</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="F2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -485,9 +494,12 @@
         <v>2074.4</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2074.4</v>
+        <v>2074.43</v>
       </c>
       <c r="E3" s="1" t="n">
+        <v>2074.43</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -504,9 +516,12 @@
         <v>86.86</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>86.86</v>
+        <v>86.89</v>
       </c>
       <c r="E4" s="1" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -523,9 +538,12 @@
         <v>4.022</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>4.039</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -542,9 +560,12 @@
         <v>0.09515</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.09515</v>
+        <v>0.09519</v>
       </c>
       <c r="E6" s="1" t="n">
+        <v>0.09519</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>0.09485</v>
       </c>
     </row>
@@ -561,9 +582,12 @@
         <v>1.3892</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.3892</v>
+        <v>1.3902</v>
       </c>
       <c r="E7" s="1" t="n">
+        <v>1.3902</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -580,10 +604,13 @@
         <v>22.485</v>
       </c>
       <c r="D8" s="1" t="n">
+        <v>22.204</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>22.657</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>22.485</v>
+      <c r="F8" s="1" t="n">
+        <v>22.204</v>
       </c>
     </row>
     <row r="9">
@@ -599,9 +626,12 @@
         <v>0.00215</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>0.002135</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>0.00215</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.002119</v>
       </c>
     </row>
@@ -618,9 +648,12 @@
         <v>0.009129</v>
       </c>
       <c r="D10" s="1" t="n">
+        <v>0.010041</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -637,9 +670,12 @@
         <v>0.16978</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>0.17048</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>0.1709</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>0.16978</v>
       </c>
     </row>
@@ -656,10 +692,13 @@
         <v>0.012009</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>0.011888</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>0.01197</v>
+      <c r="F12" s="1" t="n">
+        <v>0.011888</v>
       </c>
     </row>
     <row r="13">
@@ -675,9 +714,12 @@
         <v>38.402</v>
       </c>
       <c r="D13" s="1" t="n">
+        <v>38.306</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="F13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -694,9 +736,12 @@
         <v>653.52</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>653.52</v>
+        <v>653.8099999999999</v>
       </c>
       <c r="E14" s="1" t="n">
+        <v>653.8099999999999</v>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -713,9 +758,12 @@
         <v>209.41</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>209.41</v>
+        <v>209.91</v>
       </c>
       <c r="E15" s="1" t="n">
+        <v>209.91</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -732,9 +780,12 @@
         <v>0.0033503</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.0033503</v>
+        <v>0.0033535</v>
       </c>
       <c r="E16" s="1" t="n">
+        <v>0.0033535</v>
+      </c>
+      <c r="F16" s="1" t="n">
         <v>0.0033417</v>
       </c>
     </row>
@@ -751,9 +802,12 @@
         <v>235.2</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>235.2</v>
+        <v>237</v>
       </c>
       <c r="E17" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -770,9 +824,12 @@
         <v>0.9913</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.9913</v>
+        <v>0.9943</v>
       </c>
       <c r="E18" s="1" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="F18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -789,9 +846,12 @@
         <v>1.0184</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>1.0322</v>
+        <v>1.0722</v>
       </c>
       <c r="E19" s="1" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="F19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -808,9 +868,12 @@
         <v>0.2612</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="F20" s="1" t="n">
         <v>0.2608</v>
       </c>
     </row>
@@ -827,9 +890,12 @@
         <v>0.60434</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>0.60529</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>0.60434</v>
       </c>
     </row>
@@ -846,9 +912,12 @@
         <v>9.013</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>9.013</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="E22" s="1" t="n">
+        <v>9.026999999999999</v>
+      </c>
+      <c r="F22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -865,10 +934,13 @@
         <v>0.02441</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>0.02421</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>0.02425</v>
+      <c r="F23" s="1" t="n">
+        <v>0.02421</v>
       </c>
     </row>
     <row r="24">
@@ -884,9 +956,12 @@
         <v>9.579000000000001</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>9.579000000000001</v>
+        <v>9.586</v>
       </c>
       <c r="E24" s="1" t="n">
+        <v>9.586</v>
+      </c>
+      <c r="F24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -903,9 +978,12 @@
         <v>1.222</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>1.222</v>
+        <v>1.224</v>
       </c>
       <c r="E25" s="1" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="F25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -922,10 +1000,13 @@
         <v>0.07106</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>0.07076</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0.07160999999999999</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>0.07106</v>
+      <c r="F26" s="1" t="n">
+        <v>0.07076</v>
       </c>
     </row>
     <row r="27">
@@ -941,11 +1022,14 @@
         <v>1.428</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.428</v>
+        <v>1.424</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>1.428</v>
       </c>
+      <c r="F27" s="1" t="n">
+        <v>1.424</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -963,6 +1047,9 @@
         <v>1.312</v>
       </c>
       <c r="E28" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F28" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -979,9 +1066,12 @@
         <v>461.93</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>461.93</v>
+        <v>462.18</v>
       </c>
       <c r="E29" s="1" t="n">
+        <v>462.18</v>
+      </c>
+      <c r="F29" s="1" t="n">
         <v>461.74</v>
       </c>
     </row>
@@ -998,9 +1088,12 @@
         <v>1.2786</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>1.2767</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>1.2786</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="F30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1017,9 +1110,12 @@
         <v>5022.05</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>5023.41</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="F31" s="1" t="n">
         <v>5022.05</v>
       </c>
     </row>
@@ -1036,9 +1132,12 @@
         <v>0.872</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.872</v>
+        <v>0.873</v>
       </c>
       <c r="E32" s="1" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="F32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1055,9 +1154,12 @@
         <v>0.001981</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>0.001981</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="F33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1074,9 +1176,12 @@
         <v>0.16678</v>
       </c>
       <c r="D34" s="1" t="n">
+        <v>0.16972</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>0.17091</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="F34" s="1" t="n">
         <v>0.16678</v>
       </c>
     </row>
@@ -1093,9 +1198,12 @@
         <v>0.29856</v>
       </c>
       <c r="D35" s="1" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>0.29856</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="F35" s="1" t="n">
         <v>0.2982</v>
       </c>
     </row>
@@ -1112,9 +1220,12 @@
         <v>1.787</v>
       </c>
       <c r="D36" s="1" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="E36" s="1" t="n">
         <v>1.793</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="F36" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1131,9 +1242,12 @@
         <v>110.66</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>110.66</v>
+        <v>110.86</v>
       </c>
       <c r="E37" s="1" t="n">
+        <v>110.86</v>
+      </c>
+      <c r="F37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1150,10 +1264,13 @@
         <v>0.22687</v>
       </c>
       <c r="D38" s="1" t="n">
+        <v>0.22488</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>0.22651</v>
+      <c r="F38" s="1" t="n">
+        <v>0.22488</v>
       </c>
     </row>
     <row r="39">
@@ -1172,6 +1289,9 @@
         <v>0.1082</v>
       </c>
       <c r="E39" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -1188,9 +1308,12 @@
         <v>0.37297</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.37297</v>
+        <v>0.37392</v>
       </c>
       <c r="E40" s="1" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="F40" s="1" t="n">
         <v>0.37042</v>
       </c>
     </row>
@@ -1207,9 +1330,12 @@
         <v>54.52</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>54.52</v>
+        <v>54.53</v>
       </c>
       <c r="E41" s="1" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="F41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1226,9 +1352,12 @@
         <v>0.0010793</v>
       </c>
       <c r="D42" s="1" t="n">
+        <v>0.001081</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="F42" s="1" t="n">
         <v>0.0010793</v>
       </c>
     </row>
@@ -1245,10 +1374,13 @@
         <v>6.531</v>
       </c>
       <c r="D43" s="1" t="n">
+        <v>6.462</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>6.531</v>
+      <c r="F43" s="1" t="n">
+        <v>6.462</v>
       </c>
     </row>
     <row r="44">
@@ -1264,10 +1396,13 @@
         <v>0.6451</v>
       </c>
       <c r="D44" s="1" t="n">
+        <v>0.6401</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>0.6409</v>
+      <c r="F44" s="1" t="n">
+        <v>0.6401</v>
       </c>
     </row>
     <row r="45">
@@ -1283,9 +1418,12 @@
         <v>0.354</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.354</v>
+        <v>0.3552</v>
       </c>
       <c r="E45" s="1" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="F45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -1302,10 +1440,13 @@
         <v>0.03257</v>
       </c>
       <c r="D46" s="1" t="n">
+        <v>0.03237</v>
+      </c>
+      <c r="E46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>0.03257</v>
+      <c r="F46" s="1" t="n">
+        <v>0.03237</v>
       </c>
     </row>
     <row r="47">
@@ -1321,10 +1462,13 @@
         <v>0.07321</v>
       </c>
       <c r="D47" s="1" t="n">
+        <v>0.07267</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>0.07321</v>
+      <c r="F47" s="1" t="n">
+        <v>0.07267</v>
       </c>
     </row>
     <row r="48">
@@ -1340,9 +1484,12 @@
         <v>0.7035</v>
       </c>
       <c r="D48" s="1" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>0.7035</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="F48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -1359,10 +1506,13 @@
         <v>0.00462</v>
       </c>
       <c r="D49" s="1" t="n">
+        <v>0.004564</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>0.00462</v>
+      <c r="F49" s="1" t="n">
+        <v>0.004564</v>
       </c>
     </row>
     <row r="50">
@@ -1378,9 +1528,12 @@
         <v>0.1043</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.1043</v>
+        <v>0.1049</v>
       </c>
       <c r="E50" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="F50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -1397,10 +1550,13 @@
         <v>0.04047</v>
       </c>
       <c r="D51" s="1" t="n">
+        <v>0.04023</v>
+      </c>
+      <c r="E51" s="1" t="n">
         <v>0.04047</v>
       </c>
-      <c r="E51" s="1" t="n">
-        <v>0.04036</v>
+      <c r="F51" s="1" t="n">
+        <v>0.04023</v>
       </c>
     </row>
     <row r="52">
@@ -1416,9 +1572,12 @@
         <v>0.1672</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.1672</v>
+        <v>0.1688</v>
       </c>
       <c r="E52" s="1" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="F52" s="1" t="n">
         <v>0.1667</v>
       </c>
     </row>
@@ -1435,9 +1594,12 @@
         <v>0.0222</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="F53" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -1454,9 +1616,12 @@
         <v>0.007229</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.007229</v>
+        <v>0.007261</v>
       </c>
       <c r="E54" s="1" t="n">
+        <v>0.007261</v>
+      </c>
+      <c r="F54" s="1" t="n">
         <v>0.007221</v>
       </c>
     </row>
@@ -1473,9 +1638,12 @@
         <v>3.933</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="F55" s="1" t="n">
         <v>3.925</v>
       </c>
     </row>
@@ -1492,10 +1660,13 @@
         <v>0.017126</v>
       </c>
       <c r="D56" s="1" t="n">
+        <v>0.017082</v>
+      </c>
+      <c r="E56" s="1" t="n">
         <v>0.017208</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>0.017126</v>
+      <c r="F56" s="1" t="n">
+        <v>0.017082</v>
       </c>
     </row>
     <row r="57">
@@ -1511,9 +1682,12 @@
         <v>0.1103</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0.1103</v>
+        <v>0.111</v>
       </c>
       <c r="E57" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="F57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -1530,9 +1704,12 @@
         <v>2.656</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.656</v>
+        <v>2.659</v>
       </c>
       <c r="E58" s="1" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="F58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -1549,9 +1726,12 @@
         <v>0.16</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>0.16</v>
+        <v>0.1604</v>
       </c>
       <c r="E59" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -1568,9 +1748,12 @@
         <v>0.005918</v>
       </c>
       <c r="D60" s="1" t="n">
+        <v>0.005915</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>0.005918</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="F60" s="1" t="n">
         <v>0.005914</v>
       </c>
     </row>
@@ -1590,6 +1773,9 @@
         <v>0.09209000000000001</v>
       </c>
       <c r="E61" s="1" t="n">
+        <v>0.09209000000000001</v>
+      </c>
+      <c r="F61" s="1" t="n">
         <v>0.09204</v>
       </c>
     </row>
@@ -1606,9 +1792,12 @@
         <v>0.9151</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0.9151</v>
+        <v>0.9154</v>
       </c>
       <c r="E62" s="1" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="F62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -1625,9 +1814,12 @@
         <v>0.774</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="E63" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="F63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -1644,10 +1836,13 @@
         <v>0.04677</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>0.04677</v>
       </c>
-      <c r="E64" s="1" t="n">
-        <v>0.04674</v>
+      <c r="F64" s="1" t="n">
+        <v>0.04623</v>
       </c>
     </row>
     <row r="65">
@@ -1663,9 +1858,12 @@
         <v>357.03</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>357.03</v>
+        <v>357.66</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="F65" s="1" t="n">
         <v>355.34</v>
       </c>
     </row>
@@ -1682,10 +1880,13 @@
         <v>0.12814</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>0.12782</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="E66" s="1" t="n">
-        <v>0.12788</v>
+      <c r="F66" s="1" t="n">
+        <v>0.12782</v>
       </c>
     </row>
     <row r="67">
@@ -1701,9 +1902,12 @@
         <v>0.2418</v>
       </c>
       <c r="D67" s="1" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="E67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="F67" s="1" t="n">
         <v>0.2418</v>
       </c>
     </row>
@@ -1720,9 +1924,12 @@
         <v>0.00342</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>0.00342</v>
+        <v>0.00343</v>
       </c>
       <c r="E68" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="F68" s="1" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -1739,9 +1946,12 @@
         <v>0.1762</v>
       </c>
       <c r="D69" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="E69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="F69" s="1" t="n">
         <v>0.1759</v>
       </c>
     </row>
@@ -1758,10 +1968,13 @@
         <v>0.16434</v>
       </c>
       <c r="D70" s="1" t="n">
+        <v>0.16421</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>0.16434</v>
       </c>
-      <c r="E70" s="1" t="n">
-        <v>0.16422</v>
+      <c r="F70" s="1" t="n">
+        <v>0.16421</v>
       </c>
     </row>
     <row r="71">
@@ -1777,10 +1990,13 @@
         <v>0.3523</v>
       </c>
       <c r="D71" s="1" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="E71" s="1" t="n">
         <v>0.3541</v>
       </c>
-      <c r="E71" s="1" t="n">
-        <v>0.3523</v>
+      <c r="F71" s="1" t="n">
+        <v>0.3517</v>
       </c>
     </row>
     <row r="72">
@@ -1796,9 +2012,12 @@
         <v>0.7067</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>0.7067</v>
+        <v>0.7078</v>
       </c>
       <c r="E72" s="1" t="n">
+        <v>0.7078</v>
+      </c>
+      <c r="F72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -1815,9 +2034,12 @@
         <v>0.00859</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>0.00861</v>
+        <v>0.00873</v>
       </c>
       <c r="E73" s="1" t="n">
+        <v>0.00873</v>
+      </c>
+      <c r="F73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -1834,9 +2056,12 @@
         <v>0.006005</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>0.006005</v>
+        <v>0.006018</v>
       </c>
       <c r="E74" s="1" t="n">
+        <v>0.006018</v>
+      </c>
+      <c r="F74" s="1" t="n">
         <v>0.006002</v>
       </c>
     </row>
@@ -1853,9 +2078,12 @@
         <v>0.226</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="E75" s="1" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="F75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -1872,9 +2100,12 @@
         <v>0.3025</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>0.3033</v>
+        <v>0.3074</v>
       </c>
       <c r="E76" s="1" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="F76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -1891,9 +2122,12 @@
         <v>0.1003</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1006</v>
       </c>
       <c r="E77" s="1" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="F77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -1910,9 +2144,12 @@
         <v>0.1231</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>0.1231</v>
+        <v>0.1233</v>
       </c>
       <c r="E78" s="1" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="F78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -1929,9 +2166,12 @@
         <v>0.06873</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>0.06877999999999999</v>
+        <v>0.06933</v>
       </c>
       <c r="E79" s="1" t="n">
+        <v>0.06933</v>
+      </c>
+      <c r="F79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -1948,10 +2188,13 @@
         <v>0.04659</v>
       </c>
       <c r="D80" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="E80" s="1" t="n">
         <v>0.04696</v>
       </c>
-      <c r="E80" s="1" t="n">
-        <v>0.04659</v>
+      <c r="F80" s="1" t="n">
+        <v>0.04655</v>
       </c>
     </row>
     <row r="81">
@@ -1967,10 +2210,13 @@
         <v>0.000232</v>
       </c>
       <c r="D81" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="E81" s="1" t="n">
         <v>0.000234</v>
       </c>
-      <c r="E81" s="1" t="n">
-        <v>0.000232</v>
+      <c r="F81" s="1" t="n">
+        <v>0.000231</v>
       </c>
     </row>
     <row r="82">
@@ -1986,9 +2232,12 @@
         <v>8.231</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>8.231</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="E82" s="1" t="n">
+        <v>8.231999999999999</v>
+      </c>
+      <c r="F82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -2005,10 +2254,13 @@
         <v>0.0005992</v>
       </c>
       <c r="D83" s="1" t="n">
+        <v>0.000594</v>
+      </c>
+      <c r="E83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="E83" s="1" t="n">
-        <v>0.0005992</v>
+      <c r="F83" s="1" t="n">
+        <v>0.000594</v>
       </c>
     </row>
     <row r="84">
@@ -2024,10 +2276,13 @@
         <v>0.4158</v>
       </c>
       <c r="D84" s="1" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="E84" s="1" t="n">
         <v>0.4212</v>
       </c>
-      <c r="E84" s="1" t="n">
-        <v>0.4158</v>
+      <c r="F84" s="1" t="n">
+        <v>0.4149</v>
       </c>
     </row>
     <row r="85">
@@ -2043,9 +2298,12 @@
         <v>0.06254</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>0.06254</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="E85" s="1" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="F85" s="1" t="n">
         <v>0.06243</v>
       </c>
     </row>
@@ -2062,10 +2320,13 @@
         <v>0.05465</v>
       </c>
       <c r="D86" s="1" t="n">
+        <v>0.05455</v>
+      </c>
+      <c r="E86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="E86" s="1" t="n">
-        <v>0.05465</v>
+      <c r="F86" s="1" t="n">
+        <v>0.05455</v>
       </c>
     </row>
     <row r="87">
@@ -2081,9 +2342,12 @@
         <v>0.003345</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>0.003345</v>
+        <v>0.003353</v>
       </c>
       <c r="E87" s="1" t="n">
+        <v>0.003353</v>
+      </c>
+      <c r="F87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -2100,9 +2364,12 @@
         <v>0.04964</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>0.04971</v>
+        <v>0.04994</v>
       </c>
       <c r="E88" s="1" t="n">
+        <v>0.04994</v>
+      </c>
+      <c r="F88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -2119,9 +2386,12 @@
         <v>0.03065</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>0.03065</v>
+        <v>0.03077</v>
       </c>
       <c r="E89" s="1" t="n">
+        <v>0.03077</v>
+      </c>
+      <c r="F89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -2138,9 +2408,12 @@
         <v>0.3483</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>0.3483</v>
+        <v>0.3491</v>
       </c>
       <c r="E90" s="1" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="F90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -2157,9 +2430,12 @@
         <v>0.06074</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>0.06078</v>
+        <v>0.061</v>
       </c>
       <c r="E91" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="F91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -2176,9 +2452,12 @@
         <v>0.3454</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>0.3454</v>
+        <v>0.3527</v>
       </c>
       <c r="E92" s="1" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="F92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -2198,6 +2477,9 @@
         <v>1.9716</v>
       </c>
       <c r="E93" s="1" t="n">
+        <v>1.9716</v>
+      </c>
+      <c r="F93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -2214,9 +2496,12 @@
         <v>0.2596</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>0.2596</v>
+        <v>0.2599</v>
       </c>
       <c r="E94" s="1" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="F94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -2233,10 +2518,13 @@
         <v>0.04516</v>
       </c>
       <c r="D95" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>0.04525</v>
       </c>
-      <c r="E95" s="1" t="n">
-        <v>0.04516</v>
+      <c r="F95" s="1" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="96">
@@ -2252,9 +2540,12 @@
         <v>0.006006</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>0.006006</v>
+        <v>0.006176</v>
       </c>
       <c r="E96" s="1" t="n">
+        <v>0.006176</v>
+      </c>
+      <c r="F96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -2271,10 +2562,13 @@
         <v>0.001748</v>
       </c>
       <c r="D97" s="1" t="n">
+        <v>0.001739</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="E97" s="1" t="n">
-        <v>0.001746</v>
+      <c r="F97" s="1" t="n">
+        <v>0.001739</v>
       </c>
     </row>
     <row r="98">
@@ -2290,9 +2584,12 @@
         <v>5.251</v>
       </c>
       <c r="D98" s="1" t="n">
+        <v>5.255</v>
+      </c>
+      <c r="E98" s="1" t="n">
         <v>5.284</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="F98" s="1" t="n">
         <v>5.251</v>
       </c>
     </row>
@@ -2309,9 +2606,12 @@
         <v>0.01516</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>0.01516</v>
+        <v>0.01523</v>
       </c>
       <c r="E99" s="1" t="n">
+        <v>0.01523</v>
+      </c>
+      <c r="F99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -2328,9 +2628,12 @@
         <v>0.5515</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>0.5515</v>
+        <v>0.552</v>
       </c>
       <c r="E100" s="1" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="F100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -2347,10 +2650,13 @@
         <v>0.0912</v>
       </c>
       <c r="D101" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="E101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="E101" s="1" t="n">
-        <v>0.0912</v>
+      <c r="F101" s="1" t="n">
+        <v>0.091</v>
       </c>
     </row>
     <row r="102">
@@ -2366,9 +2672,12 @@
         <v>32.53</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>32.53</v>
+        <v>32.59</v>
       </c>
       <c r="E102" s="1" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="F102" s="1" t="n">
         <v>32.48</v>
       </c>
     </row>
@@ -2385,9 +2694,12 @@
         <v>0.03251</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>0.03251</v>
+        <v>0.03258</v>
       </c>
       <c r="E103" s="1" t="n">
+        <v>0.03258</v>
+      </c>
+      <c r="F103" s="1" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -2404,9 +2716,12 @@
         <v>0.06598999999999999</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>0.06598999999999999</v>
+        <v>0.06614</v>
       </c>
       <c r="E104" s="1" t="n">
+        <v>0.06614</v>
+      </c>
+      <c r="F104" s="1" t="n">
         <v>0.06582</v>
       </c>
     </row>
@@ -2423,9 +2738,12 @@
         <v>1.3037</v>
       </c>
       <c r="D105" s="1" t="n">
+        <v>1.3036</v>
+      </c>
+      <c r="E105" s="1" t="n">
         <v>1.3037</v>
       </c>
-      <c r="E105" s="1" t="n">
+      <c r="F105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -2442,9 +2760,12 @@
         <v>0.1183</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>0.1186</v>
+        <v>0.119</v>
       </c>
       <c r="E106" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -2466,6 +2787,9 @@
       <c r="E107" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="F107" s="1" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2480,9 +2804,12 @@
         <v>0.09616</v>
       </c>
       <c r="D108" s="1" t="n">
+        <v>0.09593</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="F108" s="1" t="n">
         <v>0.09589</v>
       </c>
     </row>
@@ -2499,10 +2826,13 @@
         <v>0.14064</v>
       </c>
       <c r="D109" s="1" t="n">
+        <v>0.13861</v>
+      </c>
+      <c r="E109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="E109" s="1" t="n">
-        <v>0.14064</v>
+      <c r="F109" s="1" t="n">
+        <v>0.13861</v>
       </c>
     </row>
     <row r="110">
@@ -2518,9 +2848,12 @@
         <v>5.57</v>
       </c>
       <c r="D110" s="1" t="n">
+        <v>5.566</v>
+      </c>
+      <c r="E110" s="1" t="n">
         <v>5.57</v>
       </c>
-      <c r="E110" s="1" t="n">
+      <c r="F110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -2537,9 +2870,12 @@
         <v>1.092</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>1.092</v>
+        <v>1.109</v>
       </c>
       <c r="E111" s="1" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="F111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -2556,10 +2892,13 @@
         <v>0.029743</v>
       </c>
       <c r="D112" s="1" t="n">
+        <v>0.029647</v>
+      </c>
+      <c r="E112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="E112" s="1" t="n">
-        <v>0.029692</v>
+      <c r="F112" s="1" t="n">
+        <v>0.029647</v>
       </c>
     </row>
     <row r="113">
@@ -2575,9 +2914,12 @@
         <v>1.879</v>
       </c>
       <c r="D113" s="1" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>1.879</v>
       </c>
-      <c r="E113" s="1" t="n">
+      <c r="F113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -2594,10 +2936,13 @@
         <v>0.06009</v>
       </c>
       <c r="D114" s="1" t="n">
+        <v>0.05997</v>
+      </c>
+      <c r="E114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="E114" s="1" t="n">
-        <v>0.06009</v>
+      <c r="F114" s="1" t="n">
+        <v>0.05997</v>
       </c>
     </row>
     <row r="115">
@@ -2613,10 +2958,13 @@
         <v>0.12981</v>
       </c>
       <c r="D115" s="1" t="n">
+        <v>0.12862</v>
+      </c>
+      <c r="E115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="E115" s="1" t="n">
-        <v>0.12932</v>
+      <c r="F115" s="1" t="n">
+        <v>0.12862</v>
       </c>
     </row>
     <row r="116">
@@ -2632,9 +2980,12 @@
         <v>1.1135</v>
       </c>
       <c r="D116" s="1" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="E116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="E116" s="1" t="n">
+      <c r="F116" s="1" t="n">
         <v>1.1095</v>
       </c>
     </row>
@@ -2651,9 +3002,12 @@
         <v>0.1537</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>0.156</v>
+        <v>0.1561</v>
       </c>
       <c r="E117" s="1" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="F117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -2670,9 +3024,12 @@
         <v>0.1582</v>
       </c>
       <c r="D118" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="E118" s="1" t="n">
         <v>0.1584</v>
       </c>
-      <c r="E118" s="1" t="n">
+      <c r="F118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -2689,9 +3046,12 @@
         <v>0.04566</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>0.04587</v>
+        <v>0.04588</v>
       </c>
       <c r="E119" s="1" t="n">
+        <v>0.04588</v>
+      </c>
+      <c r="F119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -2708,9 +3068,12 @@
         <v>3.022</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>3.022</v>
+        <v>3.029</v>
       </c>
       <c r="E120" s="1" t="n">
+        <v>3.029</v>
+      </c>
+      <c r="F120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -2727,9 +3090,12 @@
         <v>0.297</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>0.297</v>
+        <v>0.2972</v>
       </c>
       <c r="E121" s="1" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="F121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -2746,9 +3112,12 @@
         <v>0.5831</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>0.5831</v>
+        <v>0.585</v>
       </c>
       <c r="E122" s="1" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="F122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -2765,11 +3134,14 @@
         <v>0.01263</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>0.01263</v>
+        <v>0.01261</v>
       </c>
       <c r="E123" s="1" t="n">
         <v>0.01263</v>
       </c>
+      <c r="F123" s="1" t="n">
+        <v>0.01261</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2784,9 +3156,12 @@
         <v>0.1591</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>0.1591</v>
+        <v>0.1595</v>
       </c>
       <c r="E124" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="F124" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -2806,6 +3181,9 @@
         <v>0.001783</v>
       </c>
       <c r="E125" s="1" t="n">
+        <v>0.001783</v>
+      </c>
+      <c r="F125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -2822,9 +3200,12 @@
         <v>0.0004906</v>
       </c>
       <c r="D126" s="1" t="n">
+        <v>0.0004903</v>
+      </c>
+      <c r="E126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="E126" s="1" t="n">
+      <c r="F126" s="1" t="n">
         <v>0.0004894</v>
       </c>
     </row>
@@ -2841,9 +3222,12 @@
         <v>0.02957</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>0.02957</v>
+        <v>0.02958</v>
       </c>
       <c r="E127" s="1" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="F127" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -2860,9 +3244,12 @@
         <v>0.04122</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>0.04122</v>
+        <v>0.04128</v>
       </c>
       <c r="E128" s="1" t="n">
+        <v>0.04128</v>
+      </c>
+      <c r="F128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -2879,9 +3266,12 @@
         <v>0.04871</v>
       </c>
       <c r="D129" s="1" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="E129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="E129" s="1" t="n">
+      <c r="F129" s="1" t="n">
         <v>0.04871</v>
       </c>
     </row>
@@ -2898,9 +3288,12 @@
         <v>1.24e-05</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>1.24e-05</v>
+        <v>1.25e-05</v>
       </c>
       <c r="E130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="F130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -2917,10 +3310,13 @@
         <v>7.1e-06</v>
       </c>
       <c r="D131" s="1" t="n">
+        <v>6.7e-06</v>
+      </c>
+      <c r="E131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="E131" s="1" t="n">
-        <v>7.1e-06</v>
+      <c r="F131" s="1" t="n">
+        <v>6.7e-06</v>
       </c>
     </row>
     <row r="132">
@@ -2936,9 +3332,12 @@
         <v>0.007</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>0.007</v>
+        <v>0.00702</v>
       </c>
       <c r="E132" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="F132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -2955,9 +3354,12 @@
         <v>0.0969</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>0.0969</v>
+        <v>0.097</v>
       </c>
       <c r="E133" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -2974,9 +3376,12 @@
         <v>0.0004113</v>
       </c>
       <c r="D134" s="1" t="n">
+        <v>0.0004104</v>
+      </c>
+      <c r="E134" s="1" t="n">
         <v>0.0004113</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="F134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -2993,9 +3398,12 @@
         <v>0.08344</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>0.08391999999999999</v>
+        <v>0.08408</v>
       </c>
       <c r="E135" s="1" t="n">
+        <v>0.08408</v>
+      </c>
+      <c r="F135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -3012,9 +3420,12 @@
         <v>0.007990000000000001</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>0.007990000000000001</v>
+        <v>0.008005</v>
       </c>
       <c r="E136" s="1" t="n">
+        <v>0.008005</v>
+      </c>
+      <c r="F136" s="1" t="n">
         <v>0.007984</v>
       </c>
     </row>
@@ -3031,9 +3442,12 @@
         <v>0.0008262</v>
       </c>
       <c r="D137" s="1" t="n">
+        <v>0.0008195</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <v>0.0008262</v>
       </c>
-      <c r="E137" s="1" t="n">
+      <c r="F137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -3053,6 +3467,9 @@
         <v>0.1484</v>
       </c>
       <c r="E138" s="1" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="F138" s="1" t="n">
         <v>0.1483</v>
       </c>
     </row>
@@ -3069,9 +3486,12 @@
         <v>0.006725</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>0.006726</v>
+        <v>0.00673</v>
       </c>
       <c r="E139" s="1" t="n">
+        <v>0.00673</v>
+      </c>
+      <c r="F139" s="1" t="n">
         <v>0.006725</v>
       </c>
     </row>
@@ -3088,9 +3508,12 @@
         <v>0.01389</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>0.01389</v>
+        <v>0.01391</v>
       </c>
       <c r="E140" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="F140" s="1" t="n">
         <v>0.01387</v>
       </c>
     </row>
@@ -3107,10 +3530,13 @@
         <v>0.09816</v>
       </c>
       <c r="D141" s="1" t="n">
+        <v>0.09807</v>
+      </c>
+      <c r="E141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="E141" s="1" t="n">
-        <v>0.09816</v>
+      <c r="F141" s="1" t="n">
+        <v>0.09807</v>
       </c>
     </row>
     <row r="142">
@@ -3126,9 +3552,12 @@
         <v>0.05415</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>0.05415</v>
+        <v>0.05416</v>
       </c>
       <c r="E142" s="1" t="n">
+        <v>0.05416</v>
+      </c>
+      <c r="F142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -3145,9 +3574,12 @@
         <v>0.3241</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>0.3241</v>
+        <v>0.3256</v>
       </c>
       <c r="E143" s="1" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="F143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -3164,9 +3596,12 @@
         <v>0.02586</v>
       </c>
       <c r="D144" s="1" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="E144" s="1" t="n">
+      <c r="F144" s="1" t="n">
         <v>0.02576</v>
       </c>
     </row>
@@ -3183,10 +3618,13 @@
         <v>0.2378</v>
       </c>
       <c r="D145" s="1" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="E145" s="1" t="n">
         <v>0.238</v>
       </c>
-      <c r="E145" s="1" t="n">
-        <v>0.2378</v>
+      <c r="F145" s="1" t="n">
+        <v>0.2377</v>
       </c>
     </row>
     <row r="146">
@@ -3202,9 +3640,12 @@
         <v>0.0071</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>0.0071</v>
+        <v>0.007125</v>
       </c>
       <c r="E146" s="1" t="n">
+        <v>0.007125</v>
+      </c>
+      <c r="F146" s="1" t="n">
         <v>0.007066</v>
       </c>
     </row>
@@ -3221,9 +3662,12 @@
         <v>0.08721</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>0.08721</v>
+        <v>0.08734</v>
       </c>
       <c r="E147" s="1" t="n">
+        <v>0.08734</v>
+      </c>
+      <c r="F147" s="1" t="n">
         <v>0.08695</v>
       </c>
     </row>
@@ -3240,9 +3684,12 @@
         <v>0.05072</v>
       </c>
       <c r="D148" s="1" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="E148" s="1" t="n">
         <v>0.05072</v>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="F148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -3259,10 +3706,13 @@
         <v>0.02393</v>
       </c>
       <c r="D149" s="1" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="E149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="E149" s="1" t="n">
-        <v>0.02393</v>
+      <c r="F149" s="1" t="n">
+        <v>0.02391</v>
       </c>
     </row>
     <row r="150">
@@ -3278,10 +3728,13 @@
         <v>0.0867</v>
       </c>
       <c r="D150" s="1" t="n">
+        <v>0.08608</v>
+      </c>
+      <c r="E150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="E150" s="1" t="n">
-        <v>0.08646</v>
+      <c r="F150" s="1" t="n">
+        <v>0.08608</v>
       </c>
     </row>
     <row r="151">
@@ -3297,9 +3750,12 @@
         <v>0.02352</v>
       </c>
       <c r="D151" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="E151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="E151" s="1" t="n">
+      <c r="F151" s="1" t="n">
         <v>0.02341</v>
       </c>
     </row>
@@ -3316,9 +3772,12 @@
         <v>0.02586</v>
       </c>
       <c r="D152" s="1" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="E152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="E152" s="1" t="n">
+      <c r="F152" s="1" t="n">
         <v>0.02577</v>
       </c>
     </row>
@@ -3335,9 +3794,12 @@
         <v>0.0002082</v>
       </c>
       <c r="D153" s="1" t="n">
+        <v>0.0002098</v>
+      </c>
+      <c r="E153" s="1" t="n">
         <v>0.0002102</v>
       </c>
-      <c r="E153" s="1" t="n">
+      <c r="F153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -3354,9 +3816,12 @@
         <v>0.4419</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>0.4419</v>
+        <v>0.4442</v>
       </c>
       <c r="E154" s="1" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="F154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -3373,10 +3838,13 @@
         <v>0.06714000000000001</v>
       </c>
       <c r="D155" s="1" t="n">
+        <v>0.06693</v>
+      </c>
+      <c r="E155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="E155" s="1" t="n">
-        <v>0.06714000000000001</v>
+      <c r="F155" s="1" t="n">
+        <v>0.06693</v>
       </c>
     </row>
     <row r="156">
@@ -3392,9 +3860,12 @@
         <v>0.12859</v>
       </c>
       <c r="D156" s="1" t="n">
+        <v>0.12833</v>
+      </c>
+      <c r="E156" s="1" t="n">
         <v>0.12859</v>
       </c>
-      <c r="E156" s="1" t="n">
+      <c r="F156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -3411,9 +3882,12 @@
         <v>0.4847</v>
       </c>
       <c r="D157" s="1" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="E157" s="1" t="n">
+      <c r="F157" s="1" t="n">
         <v>0.4844</v>
       </c>
     </row>
@@ -3430,9 +3904,12 @@
         <v>0.4479</v>
       </c>
       <c r="D158" s="1" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="E158" s="1" t="n">
         <v>0.4479</v>
       </c>
-      <c r="E158" s="1" t="n">
+      <c r="F158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -3449,9 +3926,12 @@
         <v>0.007557</v>
       </c>
       <c r="D159" s="1" t="n">
+        <v>0.007533</v>
+      </c>
+      <c r="E159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="E159" s="1" t="n">
+      <c r="F159" s="1" t="n">
         <v>0.007528</v>
       </c>
     </row>
@@ -3468,9 +3948,12 @@
         <v>0.004641</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>0.004641</v>
+        <v>0.00465</v>
       </c>
       <c r="E160" s="1" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="F160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -3487,9 +3970,12 @@
         <v>0.004306</v>
       </c>
       <c r="D161" s="1" t="n">
+        <v>0.004304</v>
+      </c>
+      <c r="E161" s="1" t="n">
         <v>0.004306</v>
       </c>
-      <c r="E161" s="1" t="n">
+      <c r="F161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -3506,9 +3992,12 @@
         <v>0.0961</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>0.0961</v>
+        <v>0.0964</v>
       </c>
       <c r="E162" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="F162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -3525,9 +4014,12 @@
         <v>0.286</v>
       </c>
       <c r="D163" s="1" t="n">
-        <v>0.286</v>
+        <v>0.2861</v>
       </c>
       <c r="E163" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="F163" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -3544,9 +4036,12 @@
         <v>0.1148</v>
       </c>
       <c r="D164" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="E164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="E164" s="1" t="n">
+      <c r="F164" s="1" t="n">
         <v>0.1145</v>
       </c>
     </row>
@@ -3566,6 +4061,9 @@
         <v>0.1758</v>
       </c>
       <c r="E165" s="1" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="F165" s="1" t="n">
         <v>0.1756</v>
       </c>
     </row>
@@ -3582,9 +4080,12 @@
         <v>0.01008</v>
       </c>
       <c r="D166" s="1" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="E166" s="1" t="n">
         <v>0.01008</v>
       </c>
-      <c r="E166" s="1" t="n">
+      <c r="F166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -3601,9 +4102,12 @@
         <v>1.827</v>
       </c>
       <c r="D167" s="1" t="n">
-        <v>1.829</v>
+        <v>1.834</v>
       </c>
       <c r="E167" s="1" t="n">
+        <v>1.834</v>
+      </c>
+      <c r="F167" s="1" t="n">
         <v>1.827</v>
       </c>
     </row>
@@ -3620,9 +4124,12 @@
         <v>1.337</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>1.339</v>
+        <v>1.35</v>
       </c>
       <c r="E168" s="1" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -3639,9 +4146,12 @@
         <v>0.007328</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>0.007328</v>
+        <v>0.007333</v>
       </c>
       <c r="E169" s="1" t="n">
+        <v>0.007333</v>
+      </c>
+      <c r="F169" s="1" t="n">
         <v>0.007321</v>
       </c>
     </row>
@@ -3658,9 +4168,12 @@
         <v>0.0117</v>
       </c>
       <c r="D170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="E170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="E170" s="1" t="n">
+      <c r="F170" s="1" t="n">
         <v>0.0116</v>
       </c>
     </row>
@@ -3677,9 +4190,12 @@
         <v>0.005805</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>0.005805</v>
+        <v>0.005827</v>
       </c>
       <c r="E171" s="1" t="n">
+        <v>0.005827</v>
+      </c>
+      <c r="F171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -3696,9 +4212,12 @@
         <v>0.14704</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>0.14704</v>
+        <v>0.14737</v>
       </c>
       <c r="E172" s="1" t="n">
+        <v>0.14737</v>
+      </c>
+      <c r="F172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -3715,9 +4234,12 @@
         <v>4.886</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>4.886</v>
+        <v>4.9</v>
       </c>
       <c r="E173" s="1" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -3734,9 +4256,12 @@
         <v>0.07912</v>
       </c>
       <c r="D174" s="1" t="n">
-        <v>0.07912</v>
+        <v>0.07982</v>
       </c>
       <c r="E174" s="1" t="n">
+        <v>0.07982</v>
+      </c>
+      <c r="F174" s="1" t="n">
         <v>0.07868</v>
       </c>
     </row>
@@ -3753,9 +4278,12 @@
         <v>0.007513</v>
       </c>
       <c r="D175" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="E175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="E175" s="1" t="n">
+      <c r="F175" s="1" t="n">
         <v>0.007488</v>
       </c>
     </row>
@@ -3772,10 +4300,13 @@
         <v>0.202</v>
       </c>
       <c r="D176" s="1" t="n">
+        <v>0.2016</v>
+      </c>
+      <c r="E176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="E176" s="1" t="n">
-        <v>0.202</v>
+      <c r="F176" s="1" t="n">
+        <v>0.2016</v>
       </c>
     </row>
     <row r="177">
@@ -3791,9 +4322,12 @@
         <v>0.05187</v>
       </c>
       <c r="D177" s="1" t="n">
-        <v>0.05187</v>
+        <v>0.0519</v>
       </c>
       <c r="E177" s="1" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="F177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -3810,10 +4344,13 @@
         <v>0.05465</v>
       </c>
       <c r="D178" s="1" t="n">
+        <v>0.05455</v>
+      </c>
+      <c r="E178" s="1" t="n">
         <v>0.05465</v>
       </c>
-      <c r="E178" s="1" t="n">
-        <v>0.05458</v>
+      <c r="F178" s="1" t="n">
+        <v>0.05455</v>
       </c>
     </row>
     <row r="179">
@@ -3829,10 +4366,13 @@
         <v>0.02332</v>
       </c>
       <c r="D179" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="E179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="E179" s="1" t="n">
-        <v>0.02332</v>
+      <c r="F179" s="1" t="n">
+        <v>0.02324</v>
       </c>
     </row>
     <row r="180">
@@ -3848,9 +4388,12 @@
         <v>0.6951000000000001</v>
       </c>
       <c r="D180" s="1" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="E180" s="1" t="n">
         <v>0.6951000000000001</v>
       </c>
-      <c r="E180" s="1" t="n">
+      <c r="F180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -3867,10 +4410,13 @@
         <v>0.0003731</v>
       </c>
       <c r="D181" s="1" t="n">
+        <v>0.0003724</v>
+      </c>
+      <c r="E181" s="1" t="n">
         <v>0.0003731</v>
       </c>
-      <c r="E181" s="1" t="n">
-        <v>0.0003727</v>
+      <c r="F181" s="1" t="n">
+        <v>0.0003724</v>
       </c>
     </row>
     <row r="182">
@@ -3886,9 +4432,12 @@
         <v>0.01273</v>
       </c>
       <c r="D182" s="1" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="E182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="E182" s="1" t="n">
+      <c r="F182" s="1" t="n">
         <v>0.01273</v>
       </c>
     </row>
@@ -3905,9 +4454,12 @@
         <v>4.265</v>
       </c>
       <c r="D183" s="1" t="n">
-        <v>4.271</v>
+        <v>4.277</v>
       </c>
       <c r="E183" s="1" t="n">
+        <v>4.277</v>
+      </c>
+      <c r="F183" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -3924,10 +4476,13 @@
         <v>0.2392</v>
       </c>
       <c r="D184" s="1" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="E184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="E184" s="1" t="n">
-        <v>0.2382</v>
+      <c r="F184" s="1" t="n">
+        <v>0.2369</v>
       </c>
     </row>
     <row r="185">
@@ -3943,9 +4498,12 @@
         <v>0.03769</v>
       </c>
       <c r="D185" s="1" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="E185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="E185" s="1" t="n">
+      <c r="F185" s="1" t="n">
         <v>0.03769</v>
       </c>
     </row>
@@ -3962,10 +4520,13 @@
         <v>0.11591</v>
       </c>
       <c r="D186" s="1" t="n">
+        <v>0.11573</v>
+      </c>
+      <c r="E186" s="1" t="n">
         <v>0.11619</v>
       </c>
-      <c r="E186" s="1" t="n">
-        <v>0.11591</v>
+      <c r="F186" s="1" t="n">
+        <v>0.11573</v>
       </c>
     </row>
     <row r="187">
@@ -3981,10 +4542,13 @@
         <v>0.009265000000000001</v>
       </c>
       <c r="D187" s="1" t="n">
+        <v>0.009131</v>
+      </c>
+      <c r="E187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="E187" s="1" t="n">
-        <v>0.009265000000000001</v>
+      <c r="F187" s="1" t="n">
+        <v>0.009131</v>
       </c>
     </row>
     <row r="188">
@@ -4003,6 +4567,9 @@
         <v>0.0977</v>
       </c>
       <c r="E188" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="F188" s="1" t="n">
         <v>0.0975</v>
       </c>
     </row>
@@ -4019,9 +4586,12 @@
         <v>0.02801</v>
       </c>
       <c r="D189" s="1" t="n">
-        <v>0.02801</v>
+        <v>0.02808</v>
       </c>
       <c r="E189" s="1" t="n">
+        <v>0.02808</v>
+      </c>
+      <c r="F189" s="1" t="n">
         <v>0.02774</v>
       </c>
     </row>
@@ -4038,9 +4608,12 @@
         <v>0.00873</v>
       </c>
       <c r="D190" s="1" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="E190" s="1" t="n">
         <v>0.008840000000000001</v>
       </c>
-      <c r="E190" s="1" t="n">
+      <c r="F190" s="1" t="n">
         <v>0.00873</v>
       </c>
     </row>
@@ -4057,9 +4630,12 @@
         <v>0.001953</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>0.001953</v>
+        <v>0.001956</v>
       </c>
       <c r="E191" s="1" t="n">
+        <v>0.001956</v>
+      </c>
+      <c r="F191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -4076,9 +4652,12 @@
         <v>0.1005</v>
       </c>
       <c r="D192" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="E192" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="E192" s="1" t="n">
+      <c r="F192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -4095,9 +4674,12 @@
         <v>0.02334</v>
       </c>
       <c r="D193" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="E193" s="1" t="n">
         <v>0.02334</v>
       </c>
-      <c r="E193" s="1" t="n">
+      <c r="F193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -4117,6 +4699,9 @@
         <v>0.01351</v>
       </c>
       <c r="E194" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="F194" s="1" t="n">
         <v>0.01349</v>
       </c>
     </row>
@@ -4133,10 +4718,13 @@
         <v>0.02105</v>
       </c>
       <c r="D195" s="1" t="n">
+        <v>0.02095</v>
+      </c>
+      <c r="E195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="E195" s="1" t="n">
-        <v>0.02103</v>
+      <c r="F195" s="1" t="n">
+        <v>0.02095</v>
       </c>
     </row>
     <row r="196">
@@ -4152,9 +4740,12 @@
         <v>0.17003</v>
       </c>
       <c r="D196" s="1" t="n">
-        <v>0.17003</v>
+        <v>0.17143</v>
       </c>
       <c r="E196" s="1" t="n">
+        <v>0.17143</v>
+      </c>
+      <c r="F196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -4171,10 +4762,13 @@
         <v>0.007482</v>
       </c>
       <c r="D197" s="1" t="n">
+        <v>0.007351</v>
+      </c>
+      <c r="E197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="E197" s="1" t="n">
-        <v>0.007454</v>
+      <c r="F197" s="1" t="n">
+        <v>0.007351</v>
       </c>
     </row>
     <row r="198">
@@ -4190,9 +4784,12 @@
         <v>0.01908</v>
       </c>
       <c r="D198" s="1" t="n">
-        <v>0.01908</v>
+        <v>0.01909</v>
       </c>
       <c r="E198" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="F198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -4209,10 +4806,13 @@
         <v>0.01639</v>
       </c>
       <c r="D199" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="E199" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="E199" s="1" t="n">
-        <v>0.01639</v>
+      <c r="F199" s="1" t="n">
+        <v>0.01634</v>
       </c>
     </row>
     <row r="200">
@@ -4228,9 +4828,12 @@
         <v>0.2975</v>
       </c>
       <c r="D200" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="E200" s="1" t="n">
         <v>0.2975</v>
       </c>
-      <c r="E200" s="1" t="n">
+      <c r="F200" s="1" t="n">
         <v>0.2966</v>
       </c>
     </row>
@@ -4247,9 +4850,12 @@
         <v>0.006237</v>
       </c>
       <c r="D201" s="1" t="n">
+        <v>0.006235</v>
+      </c>
+      <c r="E201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="E201" s="1" t="n">
+      <c r="F201" s="1" t="n">
         <v>0.006231</v>
       </c>
     </row>
@@ -4266,9 +4872,12 @@
         <v>0.0004463</v>
       </c>
       <c r="D202" s="1" t="n">
+        <v>0.0004457</v>
+      </c>
+      <c r="E202" s="1" t="n">
         <v>0.0004463</v>
       </c>
-      <c r="E202" s="1" t="n">
+      <c r="F202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -4285,9 +4894,12 @@
         <v>0.007344</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>0.007344</v>
+        <v>0.007385</v>
       </c>
       <c r="E203" s="1" t="n">
+        <v>0.007385</v>
+      </c>
+      <c r="F203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -4304,9 +4916,12 @@
         <v>0.1286</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>0.1286</v>
+        <v>0.1289</v>
       </c>
       <c r="E204" s="1" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="F204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -4323,10 +4938,13 @@
         <v>0.01446</v>
       </c>
       <c r="D205" s="1" t="n">
+        <v>0.01444</v>
+      </c>
+      <c r="E205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="E205" s="1" t="n">
-        <v>0.01446</v>
+      <c r="F205" s="1" t="n">
+        <v>0.01444</v>
       </c>
     </row>
     <row r="206">
@@ -4342,10 +4960,13 @@
         <v>0.00361</v>
       </c>
       <c r="D206" s="1" t="n">
+        <v>0.003599</v>
+      </c>
+      <c r="E206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="E206" s="1" t="n">
-        <v>0.003605</v>
+      <c r="F206" s="1" t="n">
+        <v>0.003599</v>
       </c>
     </row>
     <row r="207">
@@ -4361,9 +4982,12 @@
         <v>0.0594</v>
       </c>
       <c r="D207" s="1" t="n">
-        <v>0.05944</v>
+        <v>0.05974</v>
       </c>
       <c r="E207" s="1" t="n">
+        <v>0.05974</v>
+      </c>
+      <c r="F207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -4380,9 +5004,12 @@
         <v>15.4</v>
       </c>
       <c r="D208" s="1" t="n">
-        <v>15.4</v>
+        <v>15.42</v>
       </c>
       <c r="E208" s="1" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="F208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -4399,9 +5026,12 @@
         <v>5185.6</v>
       </c>
       <c r="D209" s="1" t="n">
+        <v>5185.7</v>
+      </c>
+      <c r="E209" s="1" t="n">
         <v>5186.2</v>
       </c>
-      <c r="E209" s="1" t="n">
+      <c r="F209" s="1" t="n">
         <v>5185.6</v>
       </c>
     </row>
@@ -4418,9 +5048,12 @@
         <v>0.12039</v>
       </c>
       <c r="D210" s="1" t="n">
+        <v>0.12006</v>
+      </c>
+      <c r="E210" s="1" t="n">
         <v>0.12039</v>
       </c>
-      <c r="E210" s="1" t="n">
+      <c r="F210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -4437,9 +5070,12 @@
         <v>0.1832</v>
       </c>
       <c r="D211" s="1" t="n">
-        <v>0.1838</v>
+        <v>0.1839</v>
       </c>
       <c r="E211" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="F211" s="1" t="n">
         <v>0.1832</v>
       </c>
     </row>
@@ -4456,10 +5092,13 @@
         <v>0.0302</v>
       </c>
       <c r="D212" s="1" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="E212" s="1" t="n">
         <v>0.0302</v>
       </c>
-      <c r="E212" s="1" t="n">
-        <v>0.0301</v>
+      <c r="F212" s="1" t="n">
+        <v>0.0298</v>
       </c>
     </row>
     <row r="213">
@@ -4475,9 +5114,12 @@
         <v>1.3958</v>
       </c>
       <c r="D213" s="1" t="n">
-        <v>1.3958</v>
+        <v>1.3966</v>
       </c>
       <c r="E213" s="1" t="n">
+        <v>1.3966</v>
+      </c>
+      <c r="F213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -4494,9 +5136,12 @@
         <v>0.05658</v>
       </c>
       <c r="D214" s="1" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="E214" s="1" t="n">
         <v>0.05661</v>
       </c>
-      <c r="E214" s="1" t="n">
+      <c r="F214" s="1" t="n">
         <v>0.05658</v>
       </c>
     </row>
@@ -4513,9 +5158,12 @@
         <v>0.04376</v>
       </c>
       <c r="D215" s="1" t="n">
-        <v>0.04376</v>
+        <v>0.04385</v>
       </c>
       <c r="E215" s="1" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="F215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -4532,9 +5180,12 @@
         <v>0.15102</v>
       </c>
       <c r="D216" s="1" t="n">
+        <v>0.15108</v>
+      </c>
+      <c r="E216" s="1" t="n">
         <v>0.15121</v>
       </c>
-      <c r="E216" s="1" t="n">
+      <c r="F216" s="1" t="n">
         <v>0.15102</v>
       </c>
     </row>
@@ -4551,9 +5202,12 @@
         <v>0.073</v>
       </c>
       <c r="D217" s="1" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="E217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -4573,6 +5227,9 @@
         <v>0.00267</v>
       </c>
       <c r="E218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="F218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -4589,9 +5246,12 @@
         <v>0.01721</v>
       </c>
       <c r="D219" s="1" t="n">
+        <v>0.01719</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="E219" s="1" t="n">
+      <c r="F219" s="1" t="n">
         <v>0.01716</v>
       </c>
     </row>
@@ -4608,9 +5268,12 @@
         <v>0.05524</v>
       </c>
       <c r="D220" s="1" t="n">
-        <v>0.05524</v>
+        <v>0.05533</v>
       </c>
       <c r="E220" s="1" t="n">
+        <v>0.05533</v>
+      </c>
+      <c r="F220" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -4627,9 +5290,12 @@
         <v>0.02189</v>
       </c>
       <c r="D221" s="1" t="n">
-        <v>0.02189</v>
+        <v>0.0219</v>
       </c>
       <c r="E221" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="F221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -4646,9 +5312,12 @@
         <v>0.00942</v>
       </c>
       <c r="D222" s="1" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="E222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="E222" s="1" t="n">
+      <c r="F222" s="1" t="n">
         <v>0.009379999999999999</v>
       </c>
     </row>
@@ -4670,6 +5339,9 @@
       <c r="E223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="F223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4684,9 +5356,12 @@
         <v>0.03797</v>
       </c>
       <c r="D224" s="1" t="n">
-        <v>0.038</v>
+        <v>0.0383</v>
       </c>
       <c r="E224" s="1" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="F224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -4703,9 +5378,12 @@
         <v>0.001529</v>
       </c>
       <c r="D225" s="1" t="n">
-        <v>0.001529</v>
+        <v>0.00153</v>
       </c>
       <c r="E225" s="1" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="F225" s="1" t="n">
         <v>0.001526</v>
       </c>
     </row>
@@ -4722,9 +5400,12 @@
         <v>27.1</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>27.12</v>
+        <v>27.18</v>
       </c>
       <c r="E226" s="1" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="F226" s="1" t="n">
         <v>27.1</v>
       </c>
     </row>
@@ -4741,9 +5422,12 @@
         <v>0.07020999999999999</v>
       </c>
       <c r="D227" s="1" t="n">
-        <v>0.07020999999999999</v>
+        <v>0.07027</v>
       </c>
       <c r="E227" s="1" t="n">
+        <v>0.07027</v>
+      </c>
+      <c r="F227" s="1" t="n">
         <v>0.0702</v>
       </c>
     </row>
@@ -4760,9 +5444,12 @@
         <v>0.3131</v>
       </c>
       <c r="D228" s="1" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="E228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="E228" s="1" t="n">
+      <c r="F228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -4779,9 +5466,12 @@
         <v>18.46</v>
       </c>
       <c r="D229" s="1" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="E229" s="1" t="n">
+      <c r="F229" s="1" t="n">
         <v>18.42</v>
       </c>
     </row>
@@ -4798,10 +5488,13 @@
         <v>0.01952</v>
       </c>
       <c r="D230" s="1" t="n">
+        <v>0.01946</v>
+      </c>
+      <c r="E230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="E230" s="1" t="n">
-        <v>0.01947</v>
+      <c r="F230" s="1" t="n">
+        <v>0.01946</v>
       </c>
     </row>
     <row r="231">
@@ -4817,9 +5510,12 @@
         <v>0.01222</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>0.01222</v>
+        <v>0.01224</v>
       </c>
       <c r="E231" s="1" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="F231" s="1" t="n">
         <v>0.01221</v>
       </c>
     </row>
@@ -4836,9 +5532,12 @@
         <v>0.229</v>
       </c>
       <c r="D232" s="1" t="n">
-        <v>0.229</v>
+        <v>0.2293</v>
       </c>
       <c r="E232" s="1" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="F232" s="1" t="n">
         <v>0.2285</v>
       </c>
     </row>
@@ -4855,9 +5554,12 @@
         <v>0.07124999999999999</v>
       </c>
       <c r="D233" s="1" t="n">
-        <v>0.07124999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="E233" s="1" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="F233" s="1" t="n">
         <v>0.07113999999999999</v>
       </c>
     </row>
@@ -4877,6 +5579,9 @@
         <v>0.1704</v>
       </c>
       <c r="E234" s="1" t="n">
+        <v>0.1704</v>
+      </c>
+      <c r="F234" s="1" t="n">
         <v>0.1701</v>
       </c>
     </row>
@@ -4893,9 +5598,12 @@
         <v>0.0253</v>
       </c>
       <c r="D235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="E235" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="E235" s="1" t="n">
+      <c r="F235" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -4912,9 +5620,12 @@
         <v>0.03006</v>
       </c>
       <c r="D236" s="1" t="n">
-        <v>0.03006</v>
+        <v>0.03013</v>
       </c>
       <c r="E236" s="1" t="n">
+        <v>0.03013</v>
+      </c>
+      <c r="F236" s="1" t="n">
         <v>0.03006</v>
       </c>
     </row>
@@ -4934,6 +5645,9 @@
         <v>1.987</v>
       </c>
       <c r="E237" s="1" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="F237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -4950,9 +5664,12 @@
         <v>0.4268</v>
       </c>
       <c r="D238" s="1" t="n">
-        <v>0.4281</v>
+        <v>0.4295</v>
       </c>
       <c r="E238" s="1" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="F238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -4969,9 +5686,12 @@
         <v>0.03367</v>
       </c>
       <c r="D239" s="1" t="n">
+        <v>0.03374</v>
+      </c>
+      <c r="E239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="E239" s="1" t="n">
+      <c r="F239" s="1" t="n">
         <v>0.03367</v>
       </c>
     </row>
@@ -4988,9 +5708,12 @@
         <v>0.03391</v>
       </c>
       <c r="D240" s="1" t="n">
-        <v>0.03391</v>
+        <v>0.03408</v>
       </c>
       <c r="E240" s="1" t="n">
+        <v>0.03408</v>
+      </c>
+      <c r="F240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -5007,9 +5730,12 @@
         <v>0.0007509</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>0.0007509</v>
+        <v>0.0007551</v>
       </c>
       <c r="E241" s="1" t="n">
+        <v>0.0007551</v>
+      </c>
+      <c r="F241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -5026,9 +5752,12 @@
         <v>0.1834</v>
       </c>
       <c r="D242" s="1" t="n">
-        <v>0.1834</v>
+        <v>0.1839</v>
       </c>
       <c r="E242" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="F242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -5045,9 +5774,12 @@
         <v>0.014839</v>
       </c>
       <c r="D243" s="1" t="n">
+        <v>0.014828</v>
+      </c>
+      <c r="E243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="E243" s="1" t="n">
+      <c r="F243" s="1" t="n">
         <v>0.014827</v>
       </c>
     </row>
@@ -5064,9 +5796,12 @@
         <v>3.09e-05</v>
       </c>
       <c r="D244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="E244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="E244" s="1" t="n">
+      <c r="F244" s="1" t="n">
         <v>3.08e-05</v>
       </c>
     </row>
@@ -5083,9 +5818,12 @@
         <v>0.03543</v>
       </c>
       <c r="D245" s="1" t="n">
+        <v>0.03523</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="E245" s="1" t="n">
+      <c r="F245" s="1" t="n">
         <v>0.03521</v>
       </c>
     </row>
@@ -5102,9 +5840,12 @@
         <v>0.08039</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>0.08046</v>
+        <v>0.08066</v>
       </c>
       <c r="E246" s="1" t="n">
+        <v>0.08066</v>
+      </c>
+      <c r="F246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -5121,10 +5862,13 @@
         <v>0.007522</v>
       </c>
       <c r="D247" s="1" t="n">
+        <v>0.007318</v>
+      </c>
+      <c r="E247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="E247" s="1" t="n">
-        <v>0.007518</v>
+      <c r="F247" s="1" t="n">
+        <v>0.007318</v>
       </c>
     </row>
     <row r="248">
@@ -5140,9 +5884,12 @@
         <v>0.09717000000000001</v>
       </c>
       <c r="D248" s="1" t="n">
-        <v>0.09798999999999999</v>
+        <v>0.09855999999999999</v>
       </c>
       <c r="E248" s="1" t="n">
+        <v>0.09855999999999999</v>
+      </c>
+      <c r="F248" s="1" t="n">
         <v>0.09717000000000001</v>
       </c>
     </row>
@@ -5159,9 +5906,12 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="D249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="E249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="E249" s="1" t="n">
+      <c r="F249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -5178,9 +5928,12 @@
         <v>0.0351</v>
       </c>
       <c r="D250" s="1" t="n">
-        <v>0.0351</v>
+        <v>0.03516</v>
       </c>
       <c r="E250" s="1" t="n">
+        <v>0.03516</v>
+      </c>
+      <c r="F250" s="1" t="n">
         <v>0.03504</v>
       </c>
     </row>
@@ -5197,9 +5950,12 @@
         <v>0.04079</v>
       </c>
       <c r="D251" s="1" t="n">
-        <v>0.04079</v>
+        <v>0.04086</v>
       </c>
       <c r="E251" s="1" t="n">
+        <v>0.04086</v>
+      </c>
+      <c r="F251" s="1" t="n">
         <v>0.04058</v>
       </c>
     </row>
@@ -5216,9 +5972,12 @@
         <v>0.0893</v>
       </c>
       <c r="D252" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="E252" s="1" t="n">
         <v>0.0893</v>
       </c>
-      <c r="E252" s="1" t="n">
+      <c r="F252" s="1" t="n">
         <v>0.0891</v>
       </c>
     </row>
@@ -5235,9 +5994,12 @@
         <v>4.071</v>
       </c>
       <c r="D253" s="1" t="n">
-        <v>4.071</v>
+        <v>4.085</v>
       </c>
       <c r="E253" s="1" t="n">
+        <v>4.085</v>
+      </c>
+      <c r="F253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -5254,9 +6016,12 @@
         <v>0.1872</v>
       </c>
       <c r="D254" s="1" t="n">
-        <v>0.1872</v>
+        <v>0.1874</v>
       </c>
       <c r="E254" s="1" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="F254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -5273,10 +6038,13 @@
         <v>0.07283000000000001</v>
       </c>
       <c r="D255" s="1" t="n">
+        <v>0.07275</v>
+      </c>
+      <c r="E255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="E255" s="1" t="n">
-        <v>0.07278</v>
+      <c r="F255" s="1" t="n">
+        <v>0.07275</v>
       </c>
     </row>
     <row r="256">
@@ -5295,6 +6063,9 @@
         <v>0.01817</v>
       </c>
       <c r="E256" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="F256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -5311,9 +6082,12 @@
         <v>5.956</v>
       </c>
       <c r="D257" s="1" t="n">
+        <v>5.955</v>
+      </c>
+      <c r="E257" s="1" t="n">
         <v>5.956</v>
       </c>
-      <c r="E257" s="1" t="n">
+      <c r="F257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -5330,9 +6104,12 @@
         <v>0.2639</v>
       </c>
       <c r="D258" s="1" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="E258" s="1" t="n">
         <v>0.2639</v>
       </c>
-      <c r="E258" s="1" t="n">
+      <c r="F258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -5349,9 +6126,12 @@
         <v>0.1364</v>
       </c>
       <c r="D259" s="1" t="n">
-        <v>0.1364</v>
+        <v>0.1365</v>
       </c>
       <c r="E259" s="1" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="F259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -5368,10 +6148,13 @@
         <v>0.30555</v>
       </c>
       <c r="D260" s="1" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="E260" s="1" t="n">
         <v>0.30595</v>
       </c>
-      <c r="E260" s="1" t="n">
-        <v>0.30555</v>
+      <c r="F260" s="1" t="n">
+        <v>0.30537</v>
       </c>
     </row>
     <row r="261">
@@ -5387,9 +6170,12 @@
         <v>0.09787</v>
       </c>
       <c r="D261" s="1" t="n">
-        <v>0.09809</v>
+        <v>0.09828000000000001</v>
       </c>
       <c r="E261" s="1" t="n">
+        <v>0.09828000000000001</v>
+      </c>
+      <c r="F261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -5406,9 +6192,12 @@
         <v>0.5422</v>
       </c>
       <c r="D262" s="1" t="n">
-        <v>0.5422</v>
+        <v>0.544</v>
       </c>
       <c r="E262" s="1" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="F262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -5425,9 +6214,12 @@
         <v>0.293</v>
       </c>
       <c r="D263" s="1" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="E263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="E263" s="1" t="n">
+      <c r="F263" s="1" t="n">
         <v>0.2923</v>
       </c>
     </row>
@@ -5444,9 +6236,12 @@
         <v>0.949</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>0.949</v>
+        <v>0.951</v>
       </c>
       <c r="E264" s="1" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="F264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -5463,10 +6258,13 @@
         <v>0.5431</v>
       </c>
       <c r="D265" s="1" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="E265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="E265" s="1" t="n">
-        <v>0.5427999999999999</v>
+      <c r="F265" s="1" t="n">
+        <v>0.5405</v>
       </c>
     </row>
     <row r="266">
@@ -5482,9 +6280,12 @@
         <v>0.07381</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>0.07381</v>
+        <v>0.07388</v>
       </c>
       <c r="E266" s="1" t="n">
+        <v>0.07388</v>
+      </c>
+      <c r="F266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -5501,9 +6302,12 @@
         <v>0.02127</v>
       </c>
       <c r="D267" s="1" t="n">
-        <v>0.0213</v>
+        <v>0.02142</v>
       </c>
       <c r="E267" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="F267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -5520,9 +6324,12 @@
         <v>0.01622</v>
       </c>
       <c r="D268" s="1" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>0.01622</v>
       </c>
-      <c r="E268" s="1" t="n">
+      <c r="F268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -5539,10 +6346,13 @@
         <v>0.003715</v>
       </c>
       <c r="D269" s="1" t="n">
+        <v>0.003708</v>
+      </c>
+      <c r="E269" s="1" t="n">
         <v>0.003717</v>
       </c>
-      <c r="E269" s="1" t="n">
-        <v>0.003715</v>
+      <c r="F269" s="1" t="n">
+        <v>0.003708</v>
       </c>
     </row>
     <row r="270">
@@ -5558,10 +6368,13 @@
         <v>0.0078</v>
       </c>
       <c r="D270" s="1" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="E270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="E270" s="1" t="n">
-        <v>0.0078</v>
+      <c r="F270" s="1" t="n">
+        <v>0.00779</v>
       </c>
     </row>
     <row r="271">
@@ -5577,9 +6390,12 @@
         <v>0.05509</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>0.05509</v>
+        <v>0.0551</v>
       </c>
       <c r="E271" s="1" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="F271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -5596,9 +6412,12 @@
         <v>2.3</v>
       </c>
       <c r="D272" s="1" t="n">
-        <v>2.3</v>
+        <v>2.301</v>
       </c>
       <c r="E272" s="1" t="n">
+        <v>2.301</v>
+      </c>
+      <c r="F272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -5615,9 +6434,12 @@
         <v>0.05452</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>0.05452</v>
+        <v>0.05464</v>
       </c>
       <c r="E273" s="1" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="F273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -5634,9 +6456,12 @@
         <v>0.02289</v>
       </c>
       <c r="D274" s="1" t="n">
-        <v>0.02289</v>
+        <v>0.02291</v>
       </c>
       <c r="E274" s="1" t="n">
+        <v>0.02291</v>
+      </c>
+      <c r="F274" s="1" t="n">
         <v>0.02286</v>
       </c>
     </row>
@@ -5653,9 +6478,12 @@
         <v>1.19</v>
       </c>
       <c r="D275" s="1" t="n">
-        <v>1.19</v>
+        <v>1.193</v>
       </c>
       <c r="E275" s="1" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="F275" s="1" t="n">
         <v>1.185</v>
       </c>
     </row>
@@ -5672,9 +6500,12 @@
         <v>0.2731</v>
       </c>
       <c r="D276" s="1" t="n">
-        <v>0.2731</v>
+        <v>0.2732</v>
       </c>
       <c r="E276" s="1" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="F276" s="1" t="n">
         <v>0.2728</v>
       </c>
     </row>
@@ -5691,10 +6522,13 @@
         <v>0.956</v>
       </c>
       <c r="D277" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="E277" s="1" t="n">
-        <v>0.953</v>
+      <c r="F277" s="1" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="278">
@@ -5710,9 +6544,12 @@
         <v>0.6248</v>
       </c>
       <c r="D278" s="1" t="n">
-        <v>0.6248</v>
+        <v>0.6256</v>
       </c>
       <c r="E278" s="1" t="n">
+        <v>0.6256</v>
+      </c>
+      <c r="F278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -5729,9 +6566,12 @@
         <v>0.00135</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>0.00135</v>
+        <v>0.001353</v>
       </c>
       <c r="E279" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="F279" s="1" t="n">
         <v>0.00135</v>
       </c>
     </row>
@@ -5748,9 +6588,12 @@
         <v>0.005551</v>
       </c>
       <c r="D280" s="1" t="n">
-        <v>0.005551</v>
+        <v>0.005553</v>
       </c>
       <c r="E280" s="1" t="n">
+        <v>0.005553</v>
+      </c>
+      <c r="F280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -5770,6 +6613,9 @@
         <v>1.525</v>
       </c>
       <c r="E281" s="1" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="F281" s="1" t="n">
         <v>1.522</v>
       </c>
     </row>
@@ -5786,9 +6632,12 @@
         <v>28.47</v>
       </c>
       <c r="D282" s="1" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="E282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="E282" s="1" t="n">
+      <c r="F282" s="1" t="n">
         <v>28.36</v>
       </c>
     </row>
@@ -5805,9 +6654,12 @@
         <v>0.12939</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>0.12939</v>
+        <v>0.12942</v>
       </c>
       <c r="E283" s="1" t="n">
+        <v>0.12942</v>
+      </c>
+      <c r="F283" s="1" t="n">
         <v>0.12935</v>
       </c>
     </row>
@@ -5824,9 +6676,12 @@
         <v>0.01113</v>
       </c>
       <c r="D284" s="1" t="n">
+        <v>0.01112</v>
+      </c>
+      <c r="E284" s="1" t="n">
         <v>0.01113</v>
       </c>
-      <c r="E284" s="1" t="n">
+      <c r="F284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -5843,9 +6698,12 @@
         <v>6.501</v>
       </c>
       <c r="D285" s="1" t="n">
-        <v>6.501</v>
+        <v>6.509</v>
       </c>
       <c r="E285" s="1" t="n">
+        <v>6.509</v>
+      </c>
+      <c r="F285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -5862,9 +6720,12 @@
         <v>0.01848</v>
       </c>
       <c r="D286" s="1" t="n">
-        <v>0.01849</v>
+        <v>0.01857</v>
       </c>
       <c r="E286" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="F286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -5881,10 +6742,13 @@
         <v>0.008486</v>
       </c>
       <c r="D287" s="1" t="n">
+        <v>0.008437999999999999</v>
+      </c>
+      <c r="E287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="E287" s="1" t="n">
-        <v>0.008477</v>
+      <c r="F287" s="1" t="n">
+        <v>0.008437999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -5900,10 +6764,13 @@
         <v>0.3917</v>
       </c>
       <c r="D288" s="1" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="E288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="E288" s="1" t="n">
-        <v>0.3917</v>
+      <c r="F288" s="1" t="n">
+        <v>0.3894</v>
       </c>
     </row>
     <row r="289">
@@ -5919,10 +6786,13 @@
         <v>0.010539</v>
       </c>
       <c r="D289" s="1" t="n">
+        <v>0.010496</v>
+      </c>
+      <c r="E289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="E289" s="1" t="n">
-        <v>0.010535</v>
+      <c r="F289" s="1" t="n">
+        <v>0.010496</v>
       </c>
     </row>
     <row r="290">
@@ -5938,9 +6808,12 @@
         <v>0.0262</v>
       </c>
       <c r="D290" s="1" t="n">
-        <v>0.0262</v>
+        <v>0.02626</v>
       </c>
       <c r="E290" s="1" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="F290" s="1" t="n">
         <v>0.02613</v>
       </c>
     </row>
@@ -5960,6 +6833,9 @@
         <v>0.097</v>
       </c>
       <c r="E291" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -5976,10 +6852,13 @@
         <v>0.2861</v>
       </c>
       <c r="D292" s="1" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="E292" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="E292" s="1" t="n">
-        <v>0.28585</v>
+      <c r="F292" s="1" t="n">
+        <v>0.28557</v>
       </c>
     </row>
     <row r="293">
@@ -5995,9 +6874,12 @@
         <v>0.01548</v>
       </c>
       <c r="D293" s="1" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="E293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="E293" s="1" t="n">
+      <c r="F293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -6017,6 +6899,9 @@
         <v>0.003416</v>
       </c>
       <c r="E294" s="1" t="n">
+        <v>0.003416</v>
+      </c>
+      <c r="F294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -6033,9 +6918,12 @@
         <v>0.043723</v>
       </c>
       <c r="D295" s="1" t="n">
+        <v>0.043601</v>
+      </c>
+      <c r="E295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="E295" s="1" t="n">
+      <c r="F295" s="1" t="n">
         <v>0.043493</v>
       </c>
     </row>
@@ -6052,10 +6940,13 @@
         <v>0.03007</v>
       </c>
       <c r="D296" s="1" t="n">
+        <v>0.02943</v>
+      </c>
+      <c r="E296" s="1" t="n">
         <v>0.03007</v>
       </c>
-      <c r="E296" s="1" t="n">
-        <v>0.02953</v>
+      <c r="F296" s="1" t="n">
+        <v>0.02943</v>
       </c>
     </row>
     <row r="297">
@@ -6071,9 +6962,12 @@
         <v>0.03983</v>
       </c>
       <c r="D297" s="1" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="E297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="E297" s="1" t="n">
+      <c r="F297" s="1" t="n">
         <v>0.03983</v>
       </c>
     </row>
@@ -6090,9 +6984,12 @@
         <v>0.08359</v>
       </c>
       <c r="D298" s="1" t="n">
+        <v>0.08338</v>
+      </c>
+      <c r="E298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="E298" s="1" t="n">
+      <c r="F298" s="1" t="n">
         <v>0.08326</v>
       </c>
     </row>
@@ -6109,9 +7006,12 @@
         <v>0.00764</v>
       </c>
       <c r="D299" s="1" t="n">
-        <v>0.00764</v>
+        <v>0.00766</v>
       </c>
       <c r="E299" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="F299" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -6128,9 +7028,12 @@
         <v>0.01524</v>
       </c>
       <c r="D300" s="1" t="n">
-        <v>0.01524</v>
+        <v>0.01532</v>
       </c>
       <c r="E300" s="1" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="F300" s="1" t="n">
         <v>0.01519</v>
       </c>
     </row>
@@ -6147,9 +7050,12 @@
         <v>0.142</v>
       </c>
       <c r="D301" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="E301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="E301" s="1" t="n">
+      <c r="F301" s="1" t="n">
         <v>0.1416</v>
       </c>
     </row>
@@ -6166,9 +7072,12 @@
         <v>0.0006511000000000001</v>
       </c>
       <c r="D302" s="1" t="n">
+        <v>0.0006518</v>
+      </c>
+      <c r="E302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="E302" s="1" t="n">
+      <c r="F302" s="1" t="n">
         <v>0.0006511000000000001</v>
       </c>
     </row>
@@ -6185,9 +7094,12 @@
         <v>0.06235</v>
       </c>
       <c r="D303" s="1" t="n">
+        <v>0.06232</v>
+      </c>
+      <c r="E303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="E303" s="1" t="n">
+      <c r="F303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -6204,9 +7116,12 @@
         <v>0.0001639</v>
       </c>
       <c r="D304" s="1" t="n">
+        <v>0.0001638</v>
+      </c>
+      <c r="E304" s="1" t="n">
         <v>0.0001639</v>
       </c>
-      <c r="E304" s="1" t="n">
+      <c r="F304" s="1" t="n">
         <v>0.0001634</v>
       </c>
     </row>
@@ -6223,10 +7138,13 @@
         <v>0.0609</v>
       </c>
       <c r="D305" s="1" t="n">
+        <v>0.06078</v>
+      </c>
+      <c r="E305" s="1" t="n">
         <v>0.0609</v>
       </c>
-      <c r="E305" s="1" t="n">
-        <v>0.06086</v>
+      <c r="F305" s="1" t="n">
+        <v>0.06078</v>
       </c>
     </row>
     <row r="306">
@@ -6242,10 +7160,13 @@
         <v>0.022667</v>
       </c>
       <c r="D306" s="1" t="n">
+        <v>0.022477</v>
+      </c>
+      <c r="E306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="E306" s="1" t="n">
-        <v>0.02265</v>
+      <c r="F306" s="1" t="n">
+        <v>0.022477</v>
       </c>
     </row>
     <row r="307">
@@ -6261,10 +7182,13 @@
         <v>0.02414</v>
       </c>
       <c r="D307" s="1" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="E307" s="1" t="n">
         <v>0.02414</v>
       </c>
-      <c r="E307" s="1" t="n">
-        <v>0.02388</v>
+      <c r="F307" s="1" t="n">
+        <v>0.02367</v>
       </c>
     </row>
     <row r="308">
@@ -6280,9 +7204,12 @@
         <v>0.000411</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>0.000411</v>
+        <v>0.000412</v>
       </c>
       <c r="E308" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="F308" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -6299,9 +7226,12 @@
         <v>0.0898</v>
       </c>
       <c r="D309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="E309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="E309" s="1" t="n">
+      <c r="F309" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -6318,10 +7248,13 @@
         <v>0.3882</v>
       </c>
       <c r="D310" s="1" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="E310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="E310" s="1" t="n">
-        <v>0.387</v>
+      <c r="F310" s="1" t="n">
+        <v>0.3831</v>
       </c>
     </row>
     <row r="311">
@@ -6337,9 +7270,12 @@
         <v>0.0357</v>
       </c>
       <c r="D311" s="1" t="n">
-        <v>0.0357</v>
+        <v>0.0358</v>
       </c>
       <c r="E311" s="1" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="F311" s="1" t="n">
         <v>0.0357</v>
       </c>
     </row>
@@ -6356,9 +7292,12 @@
         <v>0.02445</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>0.02445</v>
+        <v>0.02458</v>
       </c>
       <c r="E312" s="1" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="F312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -6375,10 +7314,13 @@
         <v>0.04147</v>
       </c>
       <c r="D313" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="E313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="E313" s="1" t="n">
-        <v>0.04143</v>
+      <c r="F313" s="1" t="n">
+        <v>0.04139</v>
       </c>
     </row>
     <row r="314">
@@ -6394,9 +7336,12 @@
         <v>4.009</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>4.009</v>
+        <v>4.015</v>
       </c>
       <c r="E314" s="1" t="n">
+        <v>4.015</v>
+      </c>
+      <c r="F314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -6413,9 +7358,12 @@
         <v>0.1601</v>
       </c>
       <c r="D315" s="1" t="n">
-        <v>0.1601</v>
+        <v>0.1604</v>
       </c>
       <c r="E315" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="F315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -6432,10 +7380,13 @@
         <v>0.08825</v>
       </c>
       <c r="D316" s="1" t="n">
+        <v>0.08819</v>
+      </c>
+      <c r="E316" s="1" t="n">
         <v>0.08852</v>
       </c>
-      <c r="E316" s="1" t="n">
-        <v>0.08825</v>
+      <c r="F316" s="1" t="n">
+        <v>0.08819</v>
       </c>
     </row>
     <row r="317">
@@ -6451,9 +7402,12 @@
         <v>0.06814000000000001</v>
       </c>
       <c r="D317" s="1" t="n">
+        <v>0.06816</v>
+      </c>
+      <c r="E317" s="1" t="n">
         <v>0.06827999999999999</v>
       </c>
-      <c r="E317" s="1" t="n">
+      <c r="F317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -6470,10 +7424,13 @@
         <v>0.012661</v>
       </c>
       <c r="D318" s="1" t="n">
+        <v>0.012643</v>
+      </c>
+      <c r="E318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="E318" s="1" t="n">
-        <v>0.012661</v>
+      <c r="F318" s="1" t="n">
+        <v>0.012643</v>
       </c>
     </row>
     <row r="319">
@@ -6489,9 +7446,12 @@
         <v>0.001135</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>0.001135</v>
+        <v>0.001136</v>
       </c>
       <c r="E319" s="1" t="n">
+        <v>0.001136</v>
+      </c>
+      <c r="F319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -6508,9 +7468,12 @@
         <v>0.063</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="F320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -6527,9 +7490,12 @@
         <v>0.00524</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>0.00524</v>
+        <v>0.00525</v>
       </c>
       <c r="E321" s="1" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="F321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -6546,10 +7512,13 @@
         <v>0.1115</v>
       </c>
       <c r="D322" s="1" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="E322" s="1" t="n">
         <v>0.1116</v>
       </c>
-      <c r="E322" s="1" t="n">
-        <v>0.1115</v>
+      <c r="F322" s="1" t="n">
+        <v>0.1114</v>
       </c>
     </row>
     <row r="323">
@@ -6565,9 +7534,12 @@
         <v>0.04225</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>0.04225</v>
+        <v>0.04246</v>
       </c>
       <c r="E323" s="1" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="F323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -6584,9 +7556,12 @@
         <v>0.01777</v>
       </c>
       <c r="D324" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="E324" s="1" t="n">
         <v>0.01777</v>
       </c>
-      <c r="E324" s="1" t="n">
+      <c r="F324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -6603,9 +7578,12 @@
         <v>0.00569</v>
       </c>
       <c r="D325" s="1" t="n">
+        <v>0.00569</v>
+      </c>
+      <c r="E325" s="1" t="n">
         <v>0.005695</v>
       </c>
-      <c r="E325" s="1" t="n">
+      <c r="F325" s="1" t="n">
         <v>0.00569</v>
       </c>
     </row>
@@ -6622,10 +7600,13 @@
         <v>0.001779</v>
       </c>
       <c r="D326" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="E326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="E326" s="1" t="n">
-        <v>0.001771</v>
+      <c r="F326" s="1" t="n">
+        <v>0.001767</v>
       </c>
     </row>
     <row r="327">
@@ -6641,9 +7622,12 @@
         <v>0.04083</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>0.04083</v>
+        <v>0.04085</v>
       </c>
       <c r="E327" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="F327" s="1" t="n">
         <v>0.04076</v>
       </c>
     </row>
@@ -6660,9 +7644,12 @@
         <v>0.05395</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>0.053964</v>
+        <v>0.054034</v>
       </c>
       <c r="E328" s="1" t="n">
+        <v>0.054034</v>
+      </c>
+      <c r="F328" s="1" t="n">
         <v>0.05395</v>
       </c>
     </row>
@@ -6679,9 +7666,12 @@
         <v>0.2789</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>0.2789</v>
+        <v>0.279</v>
       </c>
       <c r="E329" s="1" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="F329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -6698,9 +7688,12 @@
         <v>0.1599</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>0.1599</v>
+        <v>0.1601</v>
       </c>
       <c r="E330" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="F330" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -6717,9 +7710,12 @@
         <v>0.05356</v>
       </c>
       <c r="D331" s="1" t="n">
+        <v>0.05355</v>
+      </c>
+      <c r="E331" s="1" t="n">
         <v>0.05356</v>
       </c>
-      <c r="E331" s="1" t="n">
+      <c r="F331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -6736,9 +7732,12 @@
         <v>0.3607</v>
       </c>
       <c r="D332" s="1" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="E332" s="1" t="n">
         <v>0.3607</v>
       </c>
-      <c r="E332" s="1" t="n">
+      <c r="F332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -6755,9 +7754,12 @@
         <v>0.03046</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>0.03046</v>
+        <v>0.03048</v>
       </c>
       <c r="E333" s="1" t="n">
+        <v>0.03048</v>
+      </c>
+      <c r="F333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -6774,9 +7776,12 @@
         <v>0.01766</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>0.01766</v>
+        <v>0.01797</v>
       </c>
       <c r="E334" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="F334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -6793,9 +7798,12 @@
         <v>0.0577</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>0.0577</v>
+        <v>0.0579</v>
       </c>
       <c r="E335" s="1" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="F335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -6812,9 +7820,12 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.09182</v>
       </c>
       <c r="E336" s="1" t="n">
+        <v>0.09182</v>
+      </c>
+      <c r="F336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -6831,9 +7842,12 @@
         <v>0.17441</v>
       </c>
       <c r="D337" s="1" t="n">
+        <v>0.17548</v>
+      </c>
+      <c r="E337" s="1" t="n">
         <v>0.17619</v>
       </c>
-      <c r="E337" s="1" t="n">
+      <c r="F337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -6850,10 +7864,13 @@
         <v>0.02134</v>
       </c>
       <c r="D338" s="1" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="E338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="E338" s="1" t="n">
-        <v>0.02134</v>
+      <c r="F338" s="1" t="n">
+        <v>0.02122</v>
       </c>
     </row>
     <row r="339">
@@ -6872,6 +7889,9 @@
         <v>0.1315</v>
       </c>
       <c r="E339" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="F339" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -6888,10 +7908,13 @@
         <v>0.008114</v>
       </c>
       <c r="D340" s="1" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="E340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="E340" s="1" t="n">
-        <v>0.008108000000000001</v>
+      <c r="F340" s="1" t="n">
+        <v>0.0081</v>
       </c>
     </row>
     <row r="341">
@@ -6907,9 +7930,12 @@
         <v>4.393</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>4.393</v>
+        <v>4.401</v>
       </c>
       <c r="E341" s="1" t="n">
+        <v>4.401</v>
+      </c>
+      <c r="F341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -6926,9 +7952,12 @@
         <v>0.19353</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>0.19353</v>
+        <v>0.19496</v>
       </c>
       <c r="E342" s="1" t="n">
+        <v>0.19496</v>
+      </c>
+      <c r="F342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -6945,9 +7974,12 @@
         <v>0.08291999999999999</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>0.08291999999999999</v>
+        <v>0.08325</v>
       </c>
       <c r="E343" s="1" t="n">
+        <v>0.08325</v>
+      </c>
+      <c r="F343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -6964,9 +7996,12 @@
         <v>0.183</v>
       </c>
       <c r="D344" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="E344" s="1" t="n">
         <v>0.183</v>
       </c>
-      <c r="E344" s="1" t="n">
+      <c r="F344" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -6983,9 +8018,12 @@
         <v>0.00325</v>
       </c>
       <c r="D345" s="1" t="n">
-        <v>0.00325</v>
+        <v>0.003252</v>
       </c>
       <c r="E345" s="1" t="n">
+        <v>0.003252</v>
+      </c>
+      <c r="F345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -7002,9 +8040,12 @@
         <v>0.09085</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>0.09085</v>
+        <v>0.09118</v>
       </c>
       <c r="E346" s="1" t="n">
+        <v>0.09118</v>
+      </c>
+      <c r="F346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -7021,9 +8062,12 @@
         <v>2.258</v>
       </c>
       <c r="D347" s="1" t="n">
-        <v>2.258</v>
+        <v>2.259</v>
       </c>
       <c r="E347" s="1" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="F347" s="1" t="n">
         <v>2.254</v>
       </c>
     </row>
@@ -7040,9 +8084,12 @@
         <v>0.3038</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>0.304</v>
+        <v>0.3041</v>
       </c>
       <c r="E348" s="1" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="F348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -7059,10 +8106,13 @@
         <v>0.02987</v>
       </c>
       <c r="D349" s="1" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="E349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="E349" s="1" t="n">
-        <v>0.02987</v>
+      <c r="F349" s="1" t="n">
+        <v>0.02982</v>
       </c>
     </row>
     <row r="350">
@@ -7078,9 +8128,12 @@
         <v>0.1277</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>0.1277</v>
+        <v>0.1281</v>
       </c>
       <c r="E350" s="1" t="n">
+        <v>0.1281</v>
+      </c>
+      <c r="F350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -7097,9 +8150,12 @@
         <v>0.06696000000000001</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="E351" s="1" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="F351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -7116,9 +8172,12 @@
         <v>0.06244</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>0.06244</v>
+        <v>0.06251</v>
       </c>
       <c r="E352" s="1" t="n">
+        <v>0.06251</v>
+      </c>
+      <c r="F352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -7135,9 +8194,12 @@
         <v>0.06387</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>0.06387</v>
+        <v>0.0639</v>
       </c>
       <c r="E353" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="F353" s="1" t="n">
         <v>0.06375</v>
       </c>
     </row>
@@ -7154,9 +8216,12 @@
         <v>0.10433</v>
       </c>
       <c r="D354" s="1" t="n">
+        <v>0.10425</v>
+      </c>
+      <c r="E354" s="1" t="n">
         <v>0.10433</v>
       </c>
-      <c r="E354" s="1" t="n">
+      <c r="F354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -7176,6 +8241,9 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="E355" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="F355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -7192,10 +8260,13 @@
         <v>0.07054000000000001</v>
       </c>
       <c r="D356" s="1" t="n">
+        <v>0.06997</v>
+      </c>
+      <c r="E356" s="1" t="n">
         <v>0.07054000000000001</v>
       </c>
-      <c r="E356" s="1" t="n">
-        <v>0.07036000000000001</v>
+      <c r="F356" s="1" t="n">
+        <v>0.06997</v>
       </c>
     </row>
     <row r="357">
@@ -7211,9 +8282,12 @@
         <v>0.4541</v>
       </c>
       <c r="D357" s="1" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="E357" s="1" t="n">
         <v>0.4541</v>
       </c>
-      <c r="E357" s="1" t="n">
+      <c r="F357" s="1" t="n">
         <v>0.4523</v>
       </c>
     </row>
@@ -7230,9 +8304,12 @@
         <v>0.03527</v>
       </c>
       <c r="D358" s="1" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="E358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="E358" s="1" t="n">
+      <c r="F358" s="1" t="n">
         <v>0.03517</v>
       </c>
     </row>
@@ -7249,9 +8326,12 @@
         <v>0.01481</v>
       </c>
       <c r="D359" s="1" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="E359" s="1" t="n">
         <v>0.01481</v>
       </c>
-      <c r="E359" s="1" t="n">
+      <c r="F359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -7268,9 +8348,12 @@
         <v>0.13283</v>
       </c>
       <c r="D360" s="1" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>0.13306</v>
       </c>
-      <c r="E360" s="1" t="n">
+      <c r="F360" s="1" t="n">
         <v>0.13283</v>
       </c>
     </row>
@@ -7287,9 +8370,12 @@
         <v>0.000587</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>0.000587</v>
+        <v>0.0005883</v>
       </c>
       <c r="E361" s="1" t="n">
+        <v>0.0005883</v>
+      </c>
+      <c r="F361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -7306,9 +8392,12 @@
         <v>0.03878</v>
       </c>
       <c r="D362" s="1" t="n">
+        <v>0.03881</v>
+      </c>
+      <c r="E362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="E362" s="1" t="n">
+      <c r="F362" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -7325,10 +8414,13 @@
         <v>3.214</v>
       </c>
       <c r="D363" s="1" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="E363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="E363" s="1" t="n">
-        <v>3.214</v>
+      <c r="F363" s="1" t="n">
+        <v>3.208</v>
       </c>
     </row>
     <row r="364">
@@ -7344,9 +8436,12 @@
         <v>0.1663</v>
       </c>
       <c r="D364" s="1" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="E364" s="1" t="n">
         <v>0.1663</v>
       </c>
-      <c r="E364" s="1" t="n">
+      <c r="F364" s="1" t="n">
         <v>0.1657</v>
       </c>
     </row>
@@ -7363,9 +8458,12 @@
         <v>0.1133</v>
       </c>
       <c r="D365" s="1" t="n">
-        <v>0.1133</v>
+        <v>0.1135</v>
       </c>
       <c r="E365" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="F365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -7382,9 +8480,12 @@
         <v>0.0006434</v>
       </c>
       <c r="D366" s="1" t="n">
-        <v>0.0006434</v>
+        <v>0.0006438</v>
       </c>
       <c r="E366" s="1" t="n">
+        <v>0.0006438</v>
+      </c>
+      <c r="F366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -7401,9 +8502,12 @@
         <v>0.05961</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>0.05961</v>
+        <v>0.05979</v>
       </c>
       <c r="E367" s="1" t="n">
+        <v>0.05979</v>
+      </c>
+      <c r="F367" s="1" t="n">
         <v>0.05956</v>
       </c>
     </row>
@@ -7420,9 +8524,12 @@
         <v>0.08289000000000001</v>
       </c>
       <c r="D368" s="1" t="n">
-        <v>0.08289000000000001</v>
+        <v>0.08298</v>
       </c>
       <c r="E368" s="1" t="n">
+        <v>0.08298</v>
+      </c>
+      <c r="F368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -7439,9 +8546,12 @@
         <v>0.0398</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>0.0398</v>
+        <v>0.04</v>
       </c>
       <c r="E369" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F369" s="1" t="n">
         <v>0.03979</v>
       </c>
     </row>
@@ -7458,9 +8568,12 @@
         <v>3.709</v>
       </c>
       <c r="D370" s="1" t="n">
+        <v>3.713</v>
+      </c>
+      <c r="E370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="E370" s="1" t="n">
+      <c r="F370" s="1" t="n">
         <v>3.709</v>
       </c>
     </row>
@@ -7477,9 +8590,12 @@
         <v>0.1227</v>
       </c>
       <c r="D371" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="E371" s="1" t="n">
         <v>0.1227</v>
       </c>
-      <c r="E371" s="1" t="n">
+      <c r="F371" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -7496,9 +8612,12 @@
         <v>0.01473</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>0.01473</v>
+        <v>0.01474</v>
       </c>
       <c r="E372" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="F372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -7515,9 +8634,12 @@
         <v>0.02205</v>
       </c>
       <c r="D373" s="1" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="E373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="E373" s="1" t="n">
+      <c r="F373" s="1" t="n">
         <v>0.02197</v>
       </c>
     </row>
@@ -7534,10 +8656,13 @@
         <v>1.8584</v>
       </c>
       <c r="D374" s="1" t="n">
+        <v>1.8537</v>
+      </c>
+      <c r="E374" s="1" t="n">
         <v>1.8584</v>
       </c>
-      <c r="E374" s="1" t="n">
-        <v>1.8539</v>
+      <c r="F374" s="1" t="n">
+        <v>1.8537</v>
       </c>
     </row>
     <row r="375">
@@ -7553,9 +8678,12 @@
         <v>0.02106</v>
       </c>
       <c r="D375" s="1" t="n">
+        <v>0.02102</v>
+      </c>
+      <c r="E375" s="1" t="n">
         <v>0.02106</v>
       </c>
-      <c r="E375" s="1" t="n">
+      <c r="F375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -7572,9 +8700,12 @@
         <v>1.301</v>
       </c>
       <c r="D376" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="E376" s="1" t="n">
         <v>1.301</v>
       </c>
-      <c r="E376" s="1" t="n">
+      <c r="F376" s="1" t="n">
         <v>1.296</v>
       </c>
     </row>
@@ -7591,9 +8722,12 @@
         <v>0.2837</v>
       </c>
       <c r="D377" s="1" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="E377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="E377" s="1" t="n">
+      <c r="F377" s="1" t="n">
         <v>0.2837</v>
       </c>
     </row>
@@ -7610,10 +8744,13 @@
         <v>0.01567</v>
       </c>
       <c r="D378" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="E378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="E378" s="1" t="n">
-        <v>0.01567</v>
+      <c r="F378" s="1" t="n">
+        <v>0.01563</v>
       </c>
     </row>
     <row r="379">
@@ -7629,10 +8766,13 @@
         <v>1.5325</v>
       </c>
       <c r="D379" s="1" t="n">
+        <v>1.5275</v>
+      </c>
+      <c r="E379" s="1" t="n">
         <v>1.5349</v>
       </c>
-      <c r="E379" s="1" t="n">
-        <v>1.5325</v>
+      <c r="F379" s="1" t="n">
+        <v>1.5275</v>
       </c>
     </row>
     <row r="380">
@@ -7648,9 +8788,12 @@
         <v>6.969000000000001e-05</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>6.969000000000001e-05</v>
+        <v>6.972e-05</v>
       </c>
       <c r="E380" s="1" t="n">
+        <v>6.972e-05</v>
+      </c>
+      <c r="F380" s="1" t="n">
         <v>6.962e-05</v>
       </c>
     </row>
@@ -7667,9 +8810,12 @@
         <v>2.555</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>2.555</v>
+        <v>2.559</v>
       </c>
       <c r="E381" s="1" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="F381" s="1" t="n">
         <v>2.551</v>
       </c>
     </row>
@@ -7686,9 +8832,12 @@
         <v>0.06753000000000001</v>
       </c>
       <c r="D382" s="1" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="E382" s="1" t="n">
         <v>0.06753000000000001</v>
       </c>
-      <c r="E382" s="1" t="n">
+      <c r="F382" s="1" t="n">
         <v>0.06745</v>
       </c>
     </row>
@@ -7705,10 +8854,13 @@
         <v>0.01758</v>
       </c>
       <c r="D383" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="E383" s="1" t="n">
         <v>0.01758</v>
       </c>
-      <c r="E383" s="1" t="n">
-        <v>0.01745</v>
+      <c r="F383" s="1" t="n">
+        <v>0.01716</v>
       </c>
     </row>
     <row r="384">
@@ -7724,9 +8876,12 @@
         <v>0.05055</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>0.05065</v>
+        <v>0.05066</v>
       </c>
       <c r="E384" s="1" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="F384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -7743,9 +8898,12 @@
         <v>7.572</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>7.572</v>
+        <v>7.576</v>
       </c>
       <c r="E385" s="1" t="n">
+        <v>7.576</v>
+      </c>
+      <c r="F385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -7762,9 +8920,12 @@
         <v>0.003292</v>
       </c>
       <c r="D386" s="1" t="n">
-        <v>0.003292</v>
+        <v>0.003299</v>
       </c>
       <c r="E386" s="1" t="n">
+        <v>0.003299</v>
+      </c>
+      <c r="F386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -7781,9 +8942,12 @@
         <v>0.0003847</v>
       </c>
       <c r="D387" s="1" t="n">
-        <v>0.0003847</v>
+        <v>0.0003848</v>
       </c>
       <c r="E387" s="1" t="n">
+        <v>0.0003848</v>
+      </c>
+      <c r="F387" s="1" t="n">
         <v>0.0003838</v>
       </c>
     </row>
@@ -7800,9 +8964,12 @@
         <v>0.009889999999999999</v>
       </c>
       <c r="D388" s="1" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="E388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="E388" s="1" t="n">
+      <c r="F388" s="1" t="n">
         <v>0.009769999999999999</v>
       </c>
     </row>
@@ -7819,10 +8986,13 @@
         <v>0.2891</v>
       </c>
       <c r="D389" s="1" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="E389" s="1" t="n">
         <v>0.2891</v>
       </c>
-      <c r="E389" s="1" t="n">
-        <v>0.2889</v>
+      <c r="F389" s="1" t="n">
+        <v>0.2888</v>
       </c>
     </row>
     <row r="390">
@@ -7838,10 +9008,13 @@
         <v>0.0248</v>
       </c>
       <c r="D390" s="1" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="E390" s="1" t="n">
         <v>0.0249</v>
       </c>
-      <c r="E390" s="1" t="n">
-        <v>0.0248</v>
+      <c r="F390" s="1" t="n">
+        <v>0.0247</v>
       </c>
     </row>
     <row r="391">
@@ -7857,9 +9030,12 @@
         <v>2.818</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>2.818</v>
+        <v>2.819</v>
       </c>
       <c r="E391" s="1" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="F391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -7879,6 +9055,9 @@
         <v>0.01351</v>
       </c>
       <c r="E392" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="F392" s="1" t="n">
         <v>0.01343</v>
       </c>
     </row>
@@ -7895,9 +9074,12 @@
         <v>0.00235</v>
       </c>
       <c r="D393" s="1" t="n">
-        <v>0.00235</v>
+        <v>0.00236</v>
       </c>
       <c r="E393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="F393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -7914,9 +9096,12 @@
         <v>0.05951</v>
       </c>
       <c r="D394" s="1" t="n">
+        <v>0.05949</v>
+      </c>
+      <c r="E394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="E394" s="1" t="n">
+      <c r="F394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -7938,6 +9123,9 @@
       <c r="E395" s="1" t="n">
         <v>0.0405</v>
       </c>
+      <c r="F395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7952,10 +9140,13 @@
         <v>0.09134</v>
       </c>
       <c r="D396" s="1" t="n">
+        <v>0.09107999999999999</v>
+      </c>
+      <c r="E396" s="1" t="n">
         <v>0.09134</v>
       </c>
-      <c r="E396" s="1" t="n">
-        <v>0.09127</v>
+      <c r="F396" s="1" t="n">
+        <v>0.09107999999999999</v>
       </c>
     </row>
     <row r="397">
@@ -7971,9 +9162,12 @@
         <v>0.1521</v>
       </c>
       <c r="D397" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="E397" s="1" t="n">
         <v>0.1521</v>
       </c>
-      <c r="E397" s="1" t="n">
+      <c r="F397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -7990,9 +9184,12 @@
         <v>0.926</v>
       </c>
       <c r="D398" s="1" t="n">
-        <v>0.926</v>
+        <v>0.928</v>
       </c>
       <c r="E398" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="F398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -8009,9 +9206,12 @@
         <v>0.05242</v>
       </c>
       <c r="D399" s="1" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="E399" s="1" t="n">
         <v>0.05242</v>
       </c>
-      <c r="E399" s="1" t="n">
+      <c r="F399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -8028,9 +9228,12 @@
         <v>2.523</v>
       </c>
       <c r="D400" s="1" t="n">
-        <v>2.523</v>
+        <v>2.525</v>
       </c>
       <c r="E400" s="1" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="F400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -8047,9 +9250,12 @@
         <v>0.01814</v>
       </c>
       <c r="D401" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="E401" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="E401" s="1" t="n">
+      <c r="F401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -8066,9 +9272,12 @@
         <v>0.07958999999999999</v>
       </c>
       <c r="D402" s="1" t="n">
-        <v>0.07958999999999999</v>
+        <v>0.08044999999999999</v>
       </c>
       <c r="E402" s="1" t="n">
+        <v>0.08044999999999999</v>
+      </c>
+      <c r="F402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -8085,9 +9294,12 @@
         <v>1.2515</v>
       </c>
       <c r="D403" s="1" t="n">
-        <v>1.2515</v>
+        <v>1.252</v>
       </c>
       <c r="E403" s="1" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="F403" s="1" t="n">
         <v>1.2484</v>
       </c>
     </row>
@@ -8104,9 +9316,12 @@
         <v>0.00715</v>
       </c>
       <c r="D404" s="1" t="n">
-        <v>0.00716</v>
+        <v>0.00717</v>
       </c>
       <c r="E404" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="F404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -8123,10 +9338,13 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="D405" s="1" t="n">
+        <v>0.4966</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="E405" s="1" t="n">
-        <v>0.4987</v>
+      <c r="F405" s="1" t="n">
+        <v>0.4966</v>
       </c>
     </row>
     <row r="406">
@@ -8142,9 +9360,12 @@
         <v>0.01146</v>
       </c>
       <c r="D406" s="1" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="E406" s="1" t="n">
         <v>0.01151</v>
       </c>
-      <c r="E406" s="1" t="n">
+      <c r="F406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -8161,9 +9382,12 @@
         <v>0.04649</v>
       </c>
       <c r="D407" s="1" t="n">
-        <v>0.04649</v>
+        <v>0.0465</v>
       </c>
       <c r="E407" s="1" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="F407" s="1" t="n">
         <v>0.0464</v>
       </c>
     </row>
@@ -8180,9 +9404,12 @@
         <v>0.03955</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>0.03955</v>
+        <v>0.03964</v>
       </c>
       <c r="E408" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="F408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -8199,9 +9426,12 @@
         <v>0.05283</v>
       </c>
       <c r="D409" s="1" t="n">
-        <v>0.05283</v>
+        <v>0.05285</v>
       </c>
       <c r="E409" s="1" t="n">
+        <v>0.05285</v>
+      </c>
+      <c r="F409" s="1" t="n">
         <v>0.05276</v>
       </c>
     </row>
@@ -8218,9 +9448,12 @@
         <v>0.01256</v>
       </c>
       <c r="D410" s="1" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="E410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="E410" s="1" t="n">
+      <c r="F410" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -8237,9 +9470,12 @@
         <v>0.06396</v>
       </c>
       <c r="D411" s="1" t="n">
-        <v>0.06396</v>
+        <v>0.06401</v>
       </c>
       <c r="E411" s="1" t="n">
+        <v>0.06401</v>
+      </c>
+      <c r="F411" s="1" t="n">
         <v>0.06378</v>
       </c>
     </row>
@@ -8256,9 +9492,12 @@
         <v>0.04144</v>
       </c>
       <c r="D412" s="1" t="n">
-        <v>0.04144</v>
+        <v>0.04146</v>
       </c>
       <c r="E412" s="1" t="n">
+        <v>0.04146</v>
+      </c>
+      <c r="F412" s="1" t="n">
         <v>0.0414</v>
       </c>
     </row>
@@ -8275,9 +9514,12 @@
         <v>1.118</v>
       </c>
       <c r="D413" s="1" t="n">
-        <v>1.118</v>
+        <v>1.122</v>
       </c>
       <c r="E413" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="F413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -8294,10 +9536,13 @@
         <v>0.2644</v>
       </c>
       <c r="D414" s="1" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="E414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="E414" s="1" t="n">
-        <v>0.2639</v>
+      <c r="F414" s="1" t="n">
+        <v>0.2637</v>
       </c>
     </row>
     <row r="415">
@@ -8313,9 +9558,12 @@
         <v>0.001221</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>0.001222</v>
+        <v>0.001223</v>
       </c>
       <c r="E415" s="1" t="n">
+        <v>0.001223</v>
+      </c>
+      <c r="F415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -8332,10 +9580,13 @@
         <v>0.0319</v>
       </c>
       <c r="D416" s="1" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="E416" s="1" t="n">
         <v>0.03196</v>
       </c>
-      <c r="E416" s="1" t="n">
-        <v>0.0319</v>
+      <c r="F416" s="1" t="n">
+        <v>0.03179</v>
       </c>
     </row>
     <row r="417">
@@ -8351,9 +9602,12 @@
         <v>0.01454</v>
       </c>
       <c r="D417" s="1" t="n">
+        <v>0.01462</v>
+      </c>
+      <c r="E417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="E417" s="1" t="n">
+      <c r="F417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -8370,9 +9624,12 @@
         <v>0.148</v>
       </c>
       <c r="D418" s="1" t="n">
-        <v>0.148</v>
+        <v>0.1482</v>
       </c>
       <c r="E418" s="1" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="F418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -8389,9 +9646,12 @@
         <v>0.04884</v>
       </c>
       <c r="D419" s="1" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="E419" s="1" t="n">
         <v>0.04884</v>
       </c>
-      <c r="E419" s="1" t="n">
+      <c r="F419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -8408,9 +9668,12 @@
         <v>66</v>
       </c>
       <c r="D420" s="1" t="n">
-        <v>66</v>
+        <v>66.34</v>
       </c>
       <c r="E420" s="1" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="F420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -8427,9 +9690,12 @@
         <v>0.875</v>
       </c>
       <c r="D421" s="1" t="n">
-        <v>0.875</v>
+        <v>0.879</v>
       </c>
       <c r="E421" s="1" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="F421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -8446,10 +9712,13 @@
         <v>0.012969</v>
       </c>
       <c r="D422" s="1" t="n">
+        <v>0.012932</v>
+      </c>
+      <c r="E422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="E422" s="1" t="n">
-        <v>0.012969</v>
+      <c r="F422" s="1" t="n">
+        <v>0.012932</v>
       </c>
     </row>
     <row r="423">
@@ -8468,6 +9737,9 @@
         <v>0.01597</v>
       </c>
       <c r="E423" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="F423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -8484,9 +9756,12 @@
         <v>0.25951</v>
       </c>
       <c r="D424" s="1" t="n">
-        <v>0.26036</v>
+        <v>0.26204</v>
       </c>
       <c r="E424" s="1" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="F424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -8503,9 +9778,12 @@
         <v>0.6007</v>
       </c>
       <c r="D425" s="1" t="n">
-        <v>0.6007</v>
+        <v>0.601</v>
       </c>
       <c r="E425" s="1" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="F425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -8522,10 +9800,13 @@
         <v>0.005653</v>
       </c>
       <c r="D426" s="1" t="n">
+        <v>0.005617</v>
+      </c>
+      <c r="E426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="E426" s="1" t="n">
-        <v>0.005653</v>
+      <c r="F426" s="1" t="n">
+        <v>0.005617</v>
       </c>
     </row>
     <row r="427">
@@ -8541,10 +9822,13 @@
         <v>0.04916</v>
       </c>
       <c r="D427" s="1" t="n">
+        <v>0.04892</v>
+      </c>
+      <c r="E427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="E427" s="1" t="n">
-        <v>0.04899</v>
+      <c r="F427" s="1" t="n">
+        <v>0.04892</v>
       </c>
     </row>
     <row r="428">
@@ -8560,9 +9844,12 @@
         <v>0.1259</v>
       </c>
       <c r="D428" s="1" t="n">
-        <v>0.1259</v>
+        <v>0.1261</v>
       </c>
       <c r="E428" s="1" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="F428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -8579,9 +9866,12 @@
         <v>0.0032</v>
       </c>
       <c r="D429" s="1" t="n">
+        <v>0.003197</v>
+      </c>
+      <c r="E429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="E429" s="1" t="n">
+      <c r="F429" s="1" t="n">
         <v>0.003197</v>
       </c>
     </row>
@@ -8598,10 +9888,13 @@
         <v>0.03678</v>
       </c>
       <c r="D430" s="1" t="n">
+        <v>0.03655</v>
+      </c>
+      <c r="E430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="E430" s="1" t="n">
-        <v>0.03673</v>
+      <c r="F430" s="1" t="n">
+        <v>0.03655</v>
       </c>
     </row>
     <row r="431">
@@ -8617,10 +9910,13 @@
         <v>0.4011</v>
       </c>
       <c r="D431" s="1" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="E431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="E431" s="1" t="n">
-        <v>0.401</v>
+      <c r="F431" s="1" t="n">
+        <v>0.4009</v>
       </c>
     </row>
     <row r="432">
@@ -8639,6 +9935,9 @@
         <v>0.004542</v>
       </c>
       <c r="E432" s="1" t="n">
+        <v>0.004542</v>
+      </c>
+      <c r="F432" s="1" t="n">
         <v>0.004519</v>
       </c>
     </row>
@@ -8655,9 +9954,12 @@
         <v>0.0978</v>
       </c>
       <c r="D433" s="1" t="n">
-        <v>0.0978</v>
+        <v>0.098</v>
       </c>
       <c r="E433" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="F433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -8674,9 +9976,12 @@
         <v>0.01239</v>
       </c>
       <c r="D434" s="1" t="n">
-        <v>0.01239</v>
+        <v>0.01244</v>
       </c>
       <c r="E434" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="F434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -8693,9 +9998,12 @@
         <v>1.978</v>
       </c>
       <c r="D435" s="1" t="n">
-        <v>1.978</v>
+        <v>1.981</v>
       </c>
       <c r="E435" s="1" t="n">
+        <v>1.981</v>
+      </c>
+      <c r="F435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -8712,9 +10020,12 @@
         <v>0.001833</v>
       </c>
       <c r="D436" s="1" t="n">
+        <v>0.001839</v>
+      </c>
+      <c r="E436" s="1" t="n">
         <v>0.001848</v>
       </c>
-      <c r="E436" s="1" t="n">
+      <c r="F436" s="1" t="n">
         <v>0.001833</v>
       </c>
     </row>
@@ -8734,6 +10045,9 @@
         <v>0.4423</v>
       </c>
       <c r="E437" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="F437" s="1" t="n">
         <v>0.4417</v>
       </c>
     </row>
@@ -8750,9 +10064,12 @@
         <v>0.00535</v>
       </c>
       <c r="D438" s="1" t="n">
-        <v>0.00535</v>
+        <v>0.00537</v>
       </c>
       <c r="E438" s="1" t="n">
+        <v>0.00537</v>
+      </c>
+      <c r="F438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -8769,9 +10086,12 @@
         <v>0.1033</v>
       </c>
       <c r="D439" s="1" t="n">
-        <v>0.1033</v>
+        <v>0.1034</v>
       </c>
       <c r="E439" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="F439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -8788,9 +10108,12 @@
         <v>0.03431</v>
       </c>
       <c r="D440" s="1" t="n">
+        <v>0.03423</v>
+      </c>
+      <c r="E440" s="1" t="n">
         <v>0.03431</v>
       </c>
-      <c r="E440" s="1" t="n">
+      <c r="F440" s="1" t="n">
         <v>0.0342</v>
       </c>
     </row>
@@ -8807,9 +10130,12 @@
         <v>0.08209</v>
       </c>
       <c r="D441" s="1" t="n">
-        <v>0.08209</v>
+        <v>0.08215</v>
       </c>
       <c r="E441" s="1" t="n">
+        <v>0.08215</v>
+      </c>
+      <c r="F441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -8826,9 +10152,12 @@
         <v>1.305</v>
       </c>
       <c r="D442" s="1" t="n">
-        <v>1.307</v>
+        <v>1.308</v>
       </c>
       <c r="E442" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="F442" s="1" t="n">
         <v>1.305</v>
       </c>
     </row>
@@ -8845,9 +10174,12 @@
         <v>0.07571</v>
       </c>
       <c r="D443" s="1" t="n">
+        <v>0.07566000000000001</v>
+      </c>
+      <c r="E443" s="1" t="n">
         <v>0.07571</v>
       </c>
-      <c r="E443" s="1" t="n">
+      <c r="F443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -8864,9 +10196,12 @@
         <v>0.07692</v>
       </c>
       <c r="D444" s="1" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="E444" s="1" t="n">
         <v>0.07692</v>
       </c>
-      <c r="E444" s="1" t="n">
+      <c r="F444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -8883,9 +10218,12 @@
         <v>0.04377</v>
       </c>
       <c r="D445" s="1" t="n">
-        <v>0.04377</v>
+        <v>0.04386</v>
       </c>
       <c r="E445" s="1" t="n">
+        <v>0.04386</v>
+      </c>
+      <c r="F445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -8902,10 +10240,13 @@
         <v>0.0217</v>
       </c>
       <c r="D446" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="E446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="E446" s="1" t="n">
-        <v>0.0216</v>
+      <c r="F446" s="1" t="n">
+        <v>0.02154</v>
       </c>
     </row>
     <row r="447">
@@ -8921,9 +10262,12 @@
         <v>0.2797</v>
       </c>
       <c r="D447" s="1" t="n">
-        <v>0.2797</v>
+        <v>0.2806</v>
       </c>
       <c r="E447" s="1" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="F447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -8940,9 +10284,12 @@
         <v>0.03146</v>
       </c>
       <c r="D448" s="1" t="n">
+        <v>0.03144</v>
+      </c>
+      <c r="E448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="E448" s="1" t="n">
+      <c r="F448" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -8959,9 +10306,12 @@
         <v>0.00644</v>
       </c>
       <c r="D449" s="1" t="n">
-        <v>0.00644</v>
+        <v>0.00646</v>
       </c>
       <c r="E449" s="1" t="n">
+        <v>0.00646</v>
+      </c>
+      <c r="F449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -8978,9 +10328,12 @@
         <v>0.022916</v>
       </c>
       <c r="D450" s="1" t="n">
-        <v>0.022916</v>
+        <v>0.022996</v>
       </c>
       <c r="E450" s="1" t="n">
+        <v>0.022996</v>
+      </c>
+      <c r="F450" s="1" t="n">
         <v>0.022879</v>
       </c>
     </row>
@@ -8997,9 +10350,12 @@
         <v>0.04232</v>
       </c>
       <c r="D451" s="1" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>0.04232</v>
       </c>
-      <c r="E451" s="1" t="n">
+      <c r="F451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -9016,10 +10372,13 @@
         <v>0.07346999999999999</v>
       </c>
       <c r="D452" s="1" t="n">
+        <v>0.07319000000000001</v>
+      </c>
+      <c r="E452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="E452" s="1" t="n">
-        <v>0.07346999999999999</v>
+      <c r="F452" s="1" t="n">
+        <v>0.07319000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -9035,9 +10394,12 @@
         <v>0.0005931000000000001</v>
       </c>
       <c r="D453" s="1" t="n">
-        <v>0.0005931000000000001</v>
+        <v>0.0005935</v>
       </c>
       <c r="E453" s="1" t="n">
+        <v>0.0005935</v>
+      </c>
+      <c r="F453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -9054,9 +10416,12 @@
         <v>0.307</v>
       </c>
       <c r="D454" s="1" t="n">
-        <v>0.307</v>
+        <v>0.308</v>
       </c>
       <c r="E454" s="1" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="F454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -9073,9 +10438,12 @@
         <v>0.004228</v>
       </c>
       <c r="D455" s="1" t="n">
-        <v>0.004228</v>
+        <v>0.004249</v>
       </c>
       <c r="E455" s="1" t="n">
+        <v>0.004249</v>
+      </c>
+      <c r="F455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -9092,9 +10460,12 @@
         <v>0.1843</v>
       </c>
       <c r="D456" s="1" t="n">
-        <v>0.1843</v>
+        <v>0.1844</v>
       </c>
       <c r="E456" s="1" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="F456" s="1" t="n">
         <v>0.1835</v>
       </c>
     </row>
@@ -9114,6 +10485,9 @@
         <v>0.04284</v>
       </c>
       <c r="E457" s="1" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="F457" s="1" t="n">
         <v>0.04278</v>
       </c>
     </row>
@@ -9130,9 +10504,12 @@
         <v>0.1463</v>
       </c>
       <c r="D458" s="1" t="n">
-        <v>0.1463</v>
+        <v>0.1465</v>
       </c>
       <c r="E458" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="F458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -9149,9 +10526,12 @@
         <v>0.008583</v>
       </c>
       <c r="D459" s="1" t="n">
-        <v>0.008583</v>
+        <v>0.008600999999999999</v>
       </c>
       <c r="E459" s="1" t="n">
+        <v>0.008600999999999999</v>
+      </c>
+      <c r="F459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -9168,9 +10548,12 @@
         <v>0.007458</v>
       </c>
       <c r="D460" s="1" t="n">
+        <v>0.007494</v>
+      </c>
+      <c r="E460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="E460" s="1" t="n">
+      <c r="F460" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -9187,9 +10570,12 @@
         <v>0.0001736</v>
       </c>
       <c r="D461" s="1" t="n">
+        <v>0.0001727</v>
+      </c>
+      <c r="E461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="E461" s="1" t="n">
+      <c r="F461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -9206,9 +10592,12 @@
         <v>0.02246</v>
       </c>
       <c r="D462" s="1" t="n">
-        <v>0.02246</v>
+        <v>0.02256</v>
       </c>
       <c r="E462" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="F462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -9225,9 +10614,12 @@
         <v>0.03777</v>
       </c>
       <c r="D463" s="1" t="n">
+        <v>0.03762</v>
+      </c>
+      <c r="E463" s="1" t="n">
         <v>0.03777</v>
       </c>
-      <c r="E463" s="1" t="n">
+      <c r="F463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -9244,9 +10636,12 @@
         <v>0.3038</v>
       </c>
       <c r="D464" s="1" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="E464" s="1" t="n">
         <v>0.3038</v>
       </c>
-      <c r="E464" s="1" t="n">
+      <c r="F464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -9263,11 +10658,14 @@
         <v>0.03923</v>
       </c>
       <c r="D465" s="1" t="n">
-        <v>0.03923</v>
+        <v>0.03911</v>
       </c>
       <c r="E465" s="1" t="n">
         <v>0.03923</v>
       </c>
+      <c r="F465" s="1" t="n">
+        <v>0.03911</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -9282,9 +10680,12 @@
         <v>2.687</v>
       </c>
       <c r="D466" s="1" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="E466" s="1" t="n">
         <v>2.687</v>
       </c>
-      <c r="E466" s="1" t="n">
+      <c r="F466" s="1" t="n">
         <v>2.682</v>
       </c>
     </row>
@@ -9301,9 +10702,12 @@
         <v>0.03394</v>
       </c>
       <c r="D467" s="1" t="n">
-        <v>0.03394</v>
+        <v>0.03397</v>
       </c>
       <c r="E467" s="1" t="n">
+        <v>0.03397</v>
+      </c>
+      <c r="F467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -9320,9 +10724,12 @@
         <v>0.1763</v>
       </c>
       <c r="D468" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="E468" s="1" t="n">
         <v>0.1763</v>
       </c>
-      <c r="E468" s="1" t="n">
+      <c r="F468" s="1" t="n">
         <v>0.176</v>
       </c>
     </row>
@@ -9339,9 +10746,12 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="D469" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="E469" s="1" t="n">
         <v>0.09569999999999999</v>
       </c>
-      <c r="E469" s="1" t="n">
+      <c r="F469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -9358,9 +10768,12 @@
         <v>0.06745</v>
       </c>
       <c r="D470" s="1" t="n">
-        <v>0.06748999999999999</v>
+        <v>0.06757000000000001</v>
       </c>
       <c r="E470" s="1" t="n">
+        <v>0.06757000000000001</v>
+      </c>
+      <c r="F470" s="1" t="n">
         <v>0.06745</v>
       </c>
     </row>
@@ -9377,9 +10790,12 @@
         <v>0.03983</v>
       </c>
       <c r="D471" s="1" t="n">
-        <v>0.03983</v>
+        <v>0.03996</v>
       </c>
       <c r="E471" s="1" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="F471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -9396,10 +10812,13 @@
         <v>0.2481</v>
       </c>
       <c r="D472" s="1" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="E472" s="1" t="n">
         <v>0.2481</v>
       </c>
-      <c r="E472" s="1" t="n">
-        <v>0.2477</v>
+      <c r="F472" s="1" t="n">
+        <v>0.2475</v>
       </c>
     </row>
     <row r="473">
@@ -9415,10 +10834,13 @@
         <v>0.016545</v>
       </c>
       <c r="D473" s="1" t="n">
+        <v>0.016522</v>
+      </c>
+      <c r="E473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="E473" s="1" t="n">
-        <v>0.016545</v>
+      <c r="F473" s="1" t="n">
+        <v>0.016522</v>
       </c>
     </row>
     <row r="474">
@@ -9434,9 +10856,12 @@
         <v>0.1149</v>
       </c>
       <c r="D474" s="1" t="n">
-        <v>0.1149</v>
+        <v>0.1152</v>
       </c>
       <c r="E474" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="F474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -9453,9 +10878,12 @@
         <v>0.04293</v>
       </c>
       <c r="D475" s="1" t="n">
-        <v>0.04293</v>
+        <v>0.04304</v>
       </c>
       <c r="E475" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="F475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -9472,9 +10900,12 @@
         <v>0.2075</v>
       </c>
       <c r="D476" s="1" t="n">
-        <v>0.2075</v>
+        <v>0.2078</v>
       </c>
       <c r="E476" s="1" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="F476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -9491,9 +10922,12 @@
         <v>0.006817</v>
       </c>
       <c r="D477" s="1" t="n">
-        <v>0.00682</v>
+        <v>0.006833</v>
       </c>
       <c r="E477" s="1" t="n">
+        <v>0.006833</v>
+      </c>
+      <c r="F477" s="1" t="n">
         <v>0.006817</v>
       </c>
     </row>
@@ -9510,11 +10944,14 @@
         <v>0.01814</v>
       </c>
       <c r="D478" s="1" t="n">
-        <v>0.01814</v>
+        <v>0.01811</v>
       </c>
       <c r="E478" s="1" t="n">
         <v>0.01814</v>
       </c>
+      <c r="F478" s="1" t="n">
+        <v>0.01811</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9529,9 +10966,12 @@
         <v>0.04738</v>
       </c>
       <c r="D479" s="1" t="n">
+        <v>0.04731</v>
+      </c>
+      <c r="E479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="E479" s="1" t="n">
+      <c r="F479" s="1" t="n">
         <v>0.0473</v>
       </c>
     </row>
@@ -9548,9 +10988,12 @@
         <v>0.25959</v>
       </c>
       <c r="D480" s="1" t="n">
-        <v>0.25959</v>
+        <v>0.26054</v>
       </c>
       <c r="E480" s="1" t="n">
+        <v>0.26054</v>
+      </c>
+      <c r="F480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -9567,10 +11010,13 @@
         <v>0.01253</v>
       </c>
       <c r="D481" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="E481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="E481" s="1" t="n">
-        <v>0.01241</v>
+      <c r="F481" s="1" t="n">
+        <v>0.01235</v>
       </c>
     </row>
     <row r="482">
@@ -9586,9 +11032,12 @@
         <v>0.004069</v>
       </c>
       <c r="D482" s="1" t="n">
+        <v>0.004066</v>
+      </c>
+      <c r="E482" s="1" t="n">
         <v>0.004069</v>
       </c>
-      <c r="E482" s="1" t="n">
+      <c r="F482" s="1" t="n">
         <v>0.004063</v>
       </c>
     </row>
@@ -9608,6 +11057,9 @@
         <v>0.1232</v>
       </c>
       <c r="E483" s="1" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="F483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -9624,9 +11076,12 @@
         <v>0.02164</v>
       </c>
       <c r="D484" s="1" t="n">
-        <v>0.02166</v>
+        <v>0.02187</v>
       </c>
       <c r="E484" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="F484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -9643,9 +11098,12 @@
         <v>0.04607</v>
       </c>
       <c r="D485" s="1" t="n">
+        <v>0.04616</v>
+      </c>
+      <c r="E485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="E485" s="1" t="n">
+      <c r="F485" s="1" t="n">
         <v>0.04607</v>
       </c>
     </row>
@@ -9662,9 +11120,12 @@
         <v>0.1734</v>
       </c>
       <c r="D486" s="1" t="n">
-        <v>0.1734</v>
+        <v>0.1735</v>
       </c>
       <c r="E486" s="1" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="F486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -9681,9 +11142,12 @@
         <v>0.2733</v>
       </c>
       <c r="D487" s="1" t="n">
-        <v>0.2733</v>
+        <v>0.2735</v>
       </c>
       <c r="E487" s="1" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="F487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -9700,9 +11164,12 @@
         <v>0.04628</v>
       </c>
       <c r="D488" s="1" t="n">
-        <v>0.04628</v>
+        <v>0.0463</v>
       </c>
       <c r="E488" s="1" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="F488" s="1" t="n">
         <v>0.04625</v>
       </c>
     </row>
@@ -9719,9 +11186,12 @@
         <v>0.0002152</v>
       </c>
       <c r="D489" s="1" t="n">
-        <v>0.0002152</v>
+        <v>0.0002158</v>
       </c>
       <c r="E489" s="1" t="n">
+        <v>0.0002158</v>
+      </c>
+      <c r="F489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -9738,10 +11208,13 @@
         <v>1.761</v>
       </c>
       <c r="D490" s="1" t="n">
+        <v>1.759</v>
+      </c>
+      <c r="E490" s="1" t="n">
         <v>1.762</v>
       </c>
-      <c r="E490" s="1" t="n">
-        <v>1.761</v>
+      <c r="F490" s="1" t="n">
+        <v>1.759</v>
       </c>
     </row>
     <row r="491">
@@ -9757,9 +11230,12 @@
         <v>16.049</v>
       </c>
       <c r="D491" s="1" t="n">
-        <v>16.049</v>
+        <v>16.062</v>
       </c>
       <c r="E491" s="1" t="n">
+        <v>16.062</v>
+      </c>
+      <c r="F491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -9776,9 +11252,12 @@
         <v>0.06664</v>
       </c>
       <c r="D492" s="1" t="n">
-        <v>0.06664</v>
+        <v>0.06673999999999999</v>
       </c>
       <c r="E492" s="1" t="n">
+        <v>0.06673999999999999</v>
+      </c>
+      <c r="F492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -9795,9 +11274,12 @@
         <v>0.06766</v>
       </c>
       <c r="D493" s="1" t="n">
-        <v>0.06766</v>
+        <v>0.06768</v>
       </c>
       <c r="E493" s="1" t="n">
+        <v>0.06768</v>
+      </c>
+      <c r="F493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -9814,9 +11296,12 @@
         <v>0.009416000000000001</v>
       </c>
       <c r="D494" s="1" t="n">
-        <v>0.009416000000000001</v>
+        <v>0.009438999999999999</v>
       </c>
       <c r="E494" s="1" t="n">
+        <v>0.009438999999999999</v>
+      </c>
+      <c r="F494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -9833,9 +11318,12 @@
         <v>0.006116</v>
       </c>
       <c r="D495" s="1" t="n">
+        <v>0.005944</v>
+      </c>
+      <c r="E495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="E495" s="1" t="n">
+      <c r="F495" s="1" t="n">
         <v>0.005936</v>
       </c>
     </row>
@@ -9852,9 +11340,12 @@
         <v>0.00993</v>
       </c>
       <c r="D496" s="1" t="n">
-        <v>0.00993</v>
+        <v>0.009939999999999999</v>
       </c>
       <c r="E496" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="F496" s="1" t="n">
         <v>0.00992</v>
       </c>
     </row>
@@ -9871,10 +11362,13 @@
         <v>0.04395</v>
       </c>
       <c r="D497" s="1" t="n">
+        <v>0.04389</v>
+      </c>
+      <c r="E497" s="1" t="n">
         <v>0.04395</v>
       </c>
-      <c r="E497" s="1" t="n">
-        <v>0.04394</v>
+      <c r="F497" s="1" t="n">
+        <v>0.04389</v>
       </c>
     </row>
     <row r="498">
@@ -9890,9 +11384,12 @@
         <v>0.006405</v>
       </c>
       <c r="D498" s="1" t="n">
-        <v>0.006405</v>
+        <v>0.006407</v>
       </c>
       <c r="E498" s="1" t="n">
+        <v>0.006407</v>
+      </c>
+      <c r="F498" s="1" t="n">
         <v>0.006405</v>
       </c>
     </row>
@@ -9909,9 +11406,12 @@
         <v>0.01047</v>
       </c>
       <c r="D499" s="1" t="n">
+        <v>0.01046</v>
+      </c>
+      <c r="E499" s="1" t="n">
         <v>0.01047</v>
       </c>
-      <c r="E499" s="1" t="n">
+      <c r="F499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -9928,9 +11428,12 @@
         <v>0.5122</v>
       </c>
       <c r="D500" s="1" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="E500" s="1" t="n">
         <v>0.5122</v>
       </c>
-      <c r="E500" s="1" t="n">
+      <c r="F500" s="1" t="n">
         <v>0.5089</v>
       </c>
     </row>
@@ -9947,10 +11450,13 @@
         <v>0.03212</v>
       </c>
       <c r="D501" s="1" t="n">
+        <v>0.03199</v>
+      </c>
+      <c r="E501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="E501" s="1" t="n">
-        <v>0.03205</v>
+      <c r="F501" s="1" t="n">
+        <v>0.03199</v>
       </c>
     </row>
     <row r="502">
@@ -9966,9 +11472,12 @@
         <v>0.4356</v>
       </c>
       <c r="D502" s="1" t="n">
-        <v>0.4359</v>
+        <v>0.4367</v>
       </c>
       <c r="E502" s="1" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="F502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -9988,6 +11497,9 @@
         <v>0.999401</v>
       </c>
       <c r="E503" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="F503" s="1" t="n">
         <v>0.9994</v>
       </c>
     </row>
@@ -10004,9 +11516,12 @@
         <v>0.03525</v>
       </c>
       <c r="D504" s="1" t="n">
-        <v>0.03534</v>
+        <v>0.03545</v>
       </c>
       <c r="E504" s="1" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="F504" s="1" t="n">
         <v>0.03525</v>
       </c>
     </row>
@@ -10023,9 +11538,12 @@
         <v>0.004926</v>
       </c>
       <c r="D505" s="1" t="n">
-        <v>0.004926</v>
+        <v>0.00495</v>
       </c>
       <c r="E505" s="1" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="F505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -10042,9 +11560,12 @@
         <v>0.01394</v>
       </c>
       <c r="D506" s="1" t="n">
-        <v>0.01394</v>
+        <v>0.01396</v>
       </c>
       <c r="E506" s="1" t="n">
+        <v>0.01396</v>
+      </c>
+      <c r="F506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -10061,9 +11582,12 @@
         <v>0.00347</v>
       </c>
       <c r="D507" s="1" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="E507" s="1" t="n">
         <v>0.003478</v>
       </c>
-      <c r="E507" s="1" t="n">
+      <c r="F507" s="1" t="n">
         <v>0.00347</v>
       </c>
     </row>
@@ -10080,9 +11604,12 @@
         <v>1.42</v>
       </c>
       <c r="D508" s="1" t="n">
-        <v>1.42</v>
+        <v>1.421</v>
       </c>
       <c r="E508" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="F508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -10099,10 +11626,13 @@
         <v>0.005124</v>
       </c>
       <c r="D509" s="1" t="n">
+        <v>0.005101</v>
+      </c>
+      <c r="E509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="E509" s="1" t="n">
-        <v>0.005102</v>
+      <c r="F509" s="1" t="n">
+        <v>0.005101</v>
       </c>
     </row>
     <row r="510">
@@ -10121,6 +11651,9 @@
         <v>0.01576</v>
       </c>
       <c r="E510" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="F510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -10137,9 +11670,12 @@
         <v>0.08319</v>
       </c>
       <c r="D511" s="1" t="n">
+        <v>0.08323999999999999</v>
+      </c>
+      <c r="E511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="E511" s="1" t="n">
+      <c r="F511" s="1" t="n">
         <v>0.08319</v>
       </c>
     </row>
@@ -10156,9 +11692,12 @@
         <v>0.007112</v>
       </c>
       <c r="D512" s="1" t="n">
-        <v>0.007112</v>
+        <v>0.007114</v>
       </c>
       <c r="E512" s="1" t="n">
+        <v>0.007114</v>
+      </c>
+      <c r="F512" s="1" t="n">
         <v>0.007105</v>
       </c>
     </row>
@@ -10175,9 +11714,12 @@
         <v>0.01468</v>
       </c>
       <c r="D513" s="1" t="n">
-        <v>0.01469</v>
+        <v>0.0147</v>
       </c>
       <c r="E513" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -10194,10 +11736,13 @@
         <v>0.04787</v>
       </c>
       <c r="D514" s="1" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="E514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="E514" s="1" t="n">
-        <v>0.04768</v>
+      <c r="F514" s="1" t="n">
+        <v>0.04758</v>
       </c>
     </row>
     <row r="515">
@@ -10213,9 +11758,12 @@
         <v>0.01826</v>
       </c>
       <c r="D515" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="E515" s="1" t="n">
         <v>0.01826</v>
       </c>
-      <c r="E515" s="1" t="n">
+      <c r="F515" s="1" t="n">
         <v>0.01824</v>
       </c>
     </row>
@@ -10232,9 +11780,12 @@
         <v>0.0005801</v>
       </c>
       <c r="D516" s="1" t="n">
-        <v>0.0005801</v>
+        <v>0.0005808</v>
       </c>
       <c r="E516" s="1" t="n">
+        <v>0.0005808</v>
+      </c>
+      <c r="F516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -10251,9 +11802,12 @@
         <v>0.07869</v>
       </c>
       <c r="D517" s="1" t="n">
-        <v>0.07869</v>
+        <v>0.07904</v>
       </c>
       <c r="E517" s="1" t="n">
+        <v>0.07904</v>
+      </c>
+      <c r="F517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -10270,9 +11824,12 @@
         <v>0.006392</v>
       </c>
       <c r="D518" s="1" t="n">
-        <v>0.006392</v>
+        <v>0.006395</v>
       </c>
       <c r="E518" s="1" t="n">
+        <v>0.006395</v>
+      </c>
+      <c r="F518" s="1" t="n">
         <v>0.006386</v>
       </c>
     </row>
@@ -10289,9 +11846,12 @@
         <v>0.0581</v>
       </c>
       <c r="D519" s="1" t="n">
-        <v>0.0581</v>
+        <v>0.05819</v>
       </c>
       <c r="E519" s="1" t="n">
+        <v>0.05819</v>
+      </c>
+      <c r="F519" s="1" t="n">
         <v>0.05803</v>
       </c>
     </row>
@@ -10308,9 +11868,12 @@
         <v>0.10531</v>
       </c>
       <c r="D520" s="1" t="n">
+        <v>0.10519</v>
+      </c>
+      <c r="E520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="E520" s="1" t="n">
+      <c r="F520" s="1" t="n">
         <v>0.10496</v>
       </c>
     </row>
@@ -10327,9 +11890,12 @@
         <v>0.01793</v>
       </c>
       <c r="D521" s="1" t="n">
-        <v>0.01793</v>
+        <v>0.01799</v>
       </c>
       <c r="E521" s="1" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="F521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -10346,9 +11912,12 @@
         <v>0.0165</v>
       </c>
       <c r="D522" s="1" t="n">
-        <v>0.0165</v>
+        <v>0.01653</v>
       </c>
       <c r="E522" s="1" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="F522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -10365,9 +11934,12 @@
         <v>0.01085</v>
       </c>
       <c r="D523" s="1" t="n">
-        <v>0.01085</v>
+        <v>0.01089</v>
       </c>
       <c r="E523" s="1" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="F523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -10384,9 +11956,12 @@
         <v>0.006859</v>
       </c>
       <c r="D524" s="1" t="n">
-        <v>0.006859</v>
+        <v>0.006863</v>
       </c>
       <c r="E524" s="1" t="n">
+        <v>0.006863</v>
+      </c>
+      <c r="F524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -10403,10 +11978,13 @@
         <v>0.005997</v>
       </c>
       <c r="D525" s="1" t="n">
+        <v>0.005964</v>
+      </c>
+      <c r="E525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="E525" s="1" t="n">
-        <v>0.005997</v>
+      <c r="F525" s="1" t="n">
+        <v>0.005964</v>
       </c>
     </row>
     <row r="526">
@@ -10425,6 +12003,9 @@
         <v>0.001449</v>
       </c>
       <c r="E526" s="1" t="n">
+        <v>0.001449</v>
+      </c>
+      <c r="F526" s="1" t="n">
         <v>0.001437</v>
       </c>
     </row>
@@ -10441,9 +12022,12 @@
         <v>0.372</v>
       </c>
       <c r="D527" s="1" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="E527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="F527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -10460,9 +12044,12 @@
         <v>0.005159</v>
       </c>
       <c r="D528" s="1" t="n">
-        <v>0.005159</v>
+        <v>0.00518</v>
       </c>
       <c r="E528" s="1" t="n">
+        <v>0.00518</v>
+      </c>
+      <c r="F528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -10479,9 +12066,12 @@
         <v>2.918</v>
       </c>
       <c r="D529" s="1" t="n">
-        <v>2.918</v>
+        <v>2.922</v>
       </c>
       <c r="E529" s="1" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="F529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -10501,6 +12091,9 @@
         <v>0.1559</v>
       </c>
       <c r="E530" s="1" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="F530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -10517,10 +12110,13 @@
         <v>2544</v>
       </c>
       <c r="D531" s="1" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="E531" s="1" t="n">
-        <v>2540</v>
+      <c r="F531" s="1" t="n">
+        <v>2537</v>
       </c>
     </row>
     <row r="532">
@@ -10536,10 +12132,13 @@
         <v>0.03928</v>
       </c>
       <c r="D532" s="1" t="n">
+        <v>0.03923</v>
+      </c>
+      <c r="E532" s="1" t="n">
         <v>0.03928</v>
       </c>
-      <c r="E532" s="1" t="n">
-        <v>0.03927</v>
+      <c r="F532" s="1" t="n">
+        <v>0.03923</v>
       </c>
     </row>
     <row r="533">
@@ -10555,9 +12154,12 @@
         <v>0.02183</v>
       </c>
       <c r="D533" s="1" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="E533" s="1" t="n">
         <v>0.02183</v>
       </c>
-      <c r="E533" s="1" t="n">
+      <c r="F533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -10574,9 +12176,12 @@
         <v>0.0727</v>
       </c>
       <c r="D534" s="1" t="n">
-        <v>0.0727</v>
+        <v>0.07273</v>
       </c>
       <c r="E534" s="1" t="n">
+        <v>0.07273</v>
+      </c>
+      <c r="F534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -10593,9 +12198,12 @@
         <v>0.007801</v>
       </c>
       <c r="D535" s="1" t="n">
-        <v>0.007801</v>
+        <v>0.007877</v>
       </c>
       <c r="E535" s="1" t="n">
+        <v>0.007877</v>
+      </c>
+      <c r="F535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -10612,9 +12220,12 @@
         <v>0.0504</v>
       </c>
       <c r="D536" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="E536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="E536" s="1" t="n">
+      <c r="F536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -10631,9 +12242,12 @@
         <v>0.00406</v>
       </c>
       <c r="D537" s="1" t="n">
-        <v>0.00406</v>
+        <v>0.00408</v>
       </c>
       <c r="E537" s="1" t="n">
+        <v>0.00408</v>
+      </c>
+      <c r="F537" s="1" t="n">
         <v>0.00406</v>
       </c>
     </row>
@@ -10650,9 +12264,12 @@
         <v>0.0832</v>
       </c>
       <c r="D538" s="1" t="n">
+        <v>0.08308</v>
+      </c>
+      <c r="E538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="E538" s="1" t="n">
+      <c r="F538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -10672,6 +12289,9 @@
         <v>0.02502</v>
       </c>
       <c r="E539" s="1" t="n">
+        <v>0.02502</v>
+      </c>
+      <c r="F539" s="1" t="n">
         <v>0.02499</v>
       </c>
     </row>
@@ -10688,9 +12308,12 @@
         <v>0.08469</v>
       </c>
       <c r="D540" s="1" t="n">
-        <v>0.08469</v>
+        <v>0.08488</v>
       </c>
       <c r="E540" s="1" t="n">
+        <v>0.08488</v>
+      </c>
+      <c r="F540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -10710,6 +12333,9 @@
         <v>0.019</v>
       </c>
       <c r="E541" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F541" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -10726,9 +12352,12 @@
         <v>0.01698</v>
       </c>
       <c r="D542" s="1" t="n">
-        <v>0.01698</v>
+        <v>0.017</v>
       </c>
       <c r="E542" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F542" s="1" t="n">
         <v>0.01698</v>
       </c>
     </row>
@@ -10745,9 +12374,12 @@
         <v>0.1049</v>
       </c>
       <c r="D543" s="1" t="n">
-        <v>0.1049</v>
+        <v>0.105</v>
       </c>
       <c r="E543" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="F543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:I543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,9 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,10 +463,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>price_01:30</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -493,9 +499,12 @@
         <v>70651.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>70651.2</v>
+        <v>70693.10000000001</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>70693.10000000001</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -521,9 +530,12 @@
         <v>2076.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2076.36</v>
+        <v>2076.79</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>2076.79</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -549,9 +561,12 @@
         <v>86.95999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -577,9 +592,12 @@
         <v>4.028</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>4.039</v>
+        <v>4.122</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>4.122</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -605,9 +623,12 @@
         <v>0.09507</v>
       </c>
       <c r="G6" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.09485</v>
       </c>
     </row>
@@ -633,9 +654,12 @@
         <v>1.3924</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>1.3911</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -661,9 +685,12 @@
         <v>22.292</v>
       </c>
       <c r="G8" s="1" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>22.657</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -689,9 +716,12 @@
         <v>0.002157</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.002175</v>
+        <v>0.002194</v>
       </c>
       <c r="H9" s="1" t="n">
+        <v>0.002194</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>0.002119</v>
       </c>
     </row>
@@ -717,9 +747,12 @@
         <v>0.010415</v>
       </c>
       <c r="G10" s="1" t="n">
+        <v>0.01033</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -745,10 +778,13 @@
         <v>0.16834</v>
       </c>
       <c r="G11" s="1" t="n">
+        <v>0.15789</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>0.16834</v>
+      <c r="I11" s="1" t="n">
+        <v>0.15789</v>
       </c>
     </row>
     <row r="12">
@@ -773,10 +809,13 @@
         <v>0.011696</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>0.011696</v>
+      <c r="I12" s="1" t="n">
+        <v>0.01154</v>
       </c>
     </row>
     <row r="13">
@@ -801,9 +840,12 @@
         <v>38.192</v>
       </c>
       <c r="G13" s="1" t="n">
+        <v>38.195</v>
+      </c>
+      <c r="H13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -829,9 +871,12 @@
         <v>653.84</v>
       </c>
       <c r="G14" s="1" t="n">
+        <v>653.86</v>
+      </c>
+      <c r="H14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="I14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -857,9 +902,12 @@
         <v>209.79</v>
       </c>
       <c r="G15" s="1" t="n">
+        <v>209.33</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -885,9 +933,12 @@
         <v>0.0033453</v>
       </c>
       <c r="G16" s="1" t="n">
+        <v>0.0033487</v>
+      </c>
+      <c r="H16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="I16" s="1" t="n">
         <v>0.0033417</v>
       </c>
     </row>
@@ -913,9 +964,12 @@
         <v>237.54</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>237.54</v>
+        <v>238.32</v>
       </c>
       <c r="H17" s="1" t="n">
+        <v>238.32</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -941,9 +995,12 @@
         <v>0.9926</v>
       </c>
       <c r="G18" s="1" t="n">
+        <v>0.9933999999999999</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -969,9 +1026,12 @@
         <v>1.0477</v>
       </c>
       <c r="G19" s="1" t="n">
+        <v>1.0432</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="I19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -997,10 +1057,13 @@
         <v>0.2605</v>
       </c>
       <c r="G20" s="1" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="H20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>0.2605</v>
+      <c r="I20" s="1" t="n">
+        <v>0.2604</v>
       </c>
     </row>
     <row r="21">
@@ -1025,10 +1088,13 @@
         <v>0.60234</v>
       </c>
       <c r="G21" s="1" t="n">
+        <v>0.59972</v>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>0.60234</v>
+      <c r="I21" s="1" t="n">
+        <v>0.59972</v>
       </c>
     </row>
     <row r="22">
@@ -1053,9 +1119,12 @@
         <v>9.037000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>9.037000000000001</v>
+        <v>9.042</v>
       </c>
       <c r="H22" s="1" t="n">
+        <v>9.042</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1081,9 +1150,12 @@
         <v>0.02404</v>
       </c>
       <c r="G23" s="1" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="I23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1109,9 +1181,12 @@
         <v>9.589</v>
       </c>
       <c r="G24" s="1" t="n">
+        <v>9.586</v>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="I24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -1137,9 +1212,12 @@
         <v>1.218</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="H25" s="1" t="n">
         <v>1.224</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="I25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1165,9 +1243,12 @@
         <v>0.07023</v>
       </c>
       <c r="G26" s="1" t="n">
+        <v>0.07043000000000001</v>
+      </c>
+      <c r="H26" s="1" t="n">
         <v>0.07160999999999999</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="I26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1193,9 +1274,12 @@
         <v>1.427</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>1.428</v>
+        <v>1.43</v>
       </c>
       <c r="H27" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>1.424</v>
       </c>
     </row>
@@ -1221,9 +1305,12 @@
         <v>1.31</v>
       </c>
       <c r="G28" s="1" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="I28" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -1249,9 +1336,12 @@
         <v>461.75</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>462.44</v>
+        <v>463.21</v>
       </c>
       <c r="H29" s="1" t="n">
+        <v>463.21</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>461.74</v>
       </c>
     </row>
@@ -1277,9 +1367,12 @@
         <v>1.2824</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>1.2824</v>
+        <v>1.2887</v>
       </c>
       <c r="H30" s="1" t="n">
+        <v>1.2887</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1305,9 +1398,12 @@
         <v>5021.91</v>
       </c>
       <c r="G31" s="1" t="n">
+        <v>5023.04</v>
+      </c>
+      <c r="H31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="I31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1333,9 +1429,12 @@
         <v>0.873</v>
       </c>
       <c r="G32" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H32" s="1" t="n">
         <v>0.877</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="I32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1361,9 +1460,12 @@
         <v>0.001981</v>
       </c>
       <c r="G33" s="1" t="n">
+        <v>0.001979</v>
+      </c>
+      <c r="H33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="I33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1389,9 +1491,12 @@
         <v>0.16527</v>
       </c>
       <c r="G34" s="1" t="n">
+        <v>0.16692</v>
+      </c>
+      <c r="H34" s="1" t="n">
         <v>0.17091</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="I34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -1417,10 +1522,13 @@
         <v>0.29802</v>
       </c>
       <c r="G35" s="1" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="H35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>0.29802</v>
+      <c r="I35" s="1" t="n">
+        <v>0.29735</v>
       </c>
     </row>
     <row r="36">
@@ -1445,9 +1553,12 @@
         <v>1.795</v>
       </c>
       <c r="G36" s="1" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="H36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="I36" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1473,9 +1584,12 @@
         <v>110.56</v>
       </c>
       <c r="G37" s="1" t="n">
+        <v>110.81</v>
+      </c>
+      <c r="H37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="I37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1501,10 +1615,13 @@
         <v>0.22414</v>
       </c>
       <c r="G38" s="1" t="n">
+        <v>0.22314</v>
+      </c>
+      <c r="H38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="H38" s="1" t="n">
-        <v>0.22414</v>
+      <c r="I38" s="1" t="n">
+        <v>0.22314</v>
       </c>
     </row>
     <row r="39">
@@ -1529,9 +1646,12 @@
         <v>0.108</v>
       </c>
       <c r="G39" s="1" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="H39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="I39" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -1557,9 +1677,12 @@
         <v>0.37212</v>
       </c>
       <c r="G40" s="1" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="H40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="I40" s="1" t="n">
         <v>0.37042</v>
       </c>
     </row>
@@ -1585,9 +1708,12 @@
         <v>54.62</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>54.62</v>
+        <v>54.66</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="I41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1613,9 +1739,12 @@
         <v>0.0010732</v>
       </c>
       <c r="G42" s="1" t="n">
+        <v>0.0010744</v>
+      </c>
+      <c r="H42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="I42" s="1" t="n">
         <v>0.0010732</v>
       </c>
     </row>
@@ -1641,10 +1770,13 @@
         <v>6.438</v>
       </c>
       <c r="G43" s="1" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="H43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="H43" s="1" t="n">
-        <v>6.438</v>
+      <c r="I43" s="1" t="n">
+        <v>6.414</v>
       </c>
     </row>
     <row r="44">
@@ -1669,10 +1801,13 @@
         <v>0.6399</v>
       </c>
       <c r="G44" s="1" t="n">
+        <v>0.6373</v>
+      </c>
+      <c r="H44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="H44" s="1" t="n">
-        <v>0.6399</v>
+      <c r="I44" s="1" t="n">
+        <v>0.6373</v>
       </c>
     </row>
     <row r="45">
@@ -1700,6 +1835,9 @@
         <v>0.3557</v>
       </c>
       <c r="H45" s="1" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="I45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -1725,10 +1863,13 @@
         <v>0.03234</v>
       </c>
       <c r="G46" s="1" t="n">
+        <v>0.03228</v>
+      </c>
+      <c r="H46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="H46" s="1" t="n">
-        <v>0.03234</v>
+      <c r="I46" s="1" t="n">
+        <v>0.03228</v>
       </c>
     </row>
     <row r="47">
@@ -1753,10 +1894,13 @@
         <v>0.07163</v>
       </c>
       <c r="G47" s="1" t="n">
+        <v>0.07151</v>
+      </c>
+      <c r="H47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="H47" s="1" t="n">
-        <v>0.07163</v>
+      <c r="I47" s="1" t="n">
+        <v>0.07151</v>
       </c>
     </row>
     <row r="48">
@@ -1781,9 +1925,12 @@
         <v>0.7042</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.7057</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H48" s="1" t="n">
+        <v>0.7060999999999999</v>
+      </c>
+      <c r="I48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -1809,10 +1956,13 @@
         <v>0.004568</v>
       </c>
       <c r="G49" s="1" t="n">
+        <v>0.004518</v>
+      </c>
+      <c r="H49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="H49" s="1" t="n">
-        <v>0.004564</v>
+      <c r="I49" s="1" t="n">
+        <v>0.004518</v>
       </c>
     </row>
     <row r="50">
@@ -1837,9 +1987,12 @@
         <v>0.1046</v>
       </c>
       <c r="G50" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="H50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="I50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -1868,6 +2021,9 @@
         <v>0.04047</v>
       </c>
       <c r="H51" s="1" t="n">
+        <v>0.04047</v>
+      </c>
+      <c r="I51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -1893,9 +2049,12 @@
         <v>0.1665</v>
       </c>
       <c r="G52" s="1" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="H52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="H52" s="1" t="n">
+      <c r="I52" s="1" t="n">
         <v>0.1665</v>
       </c>
     </row>
@@ -1921,10 +2080,13 @@
         <v>0.02137</v>
       </c>
       <c r="G53" s="1" t="n">
+        <v>0.02128</v>
+      </c>
+      <c r="H53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="H53" s="1" t="n">
-        <v>0.02137</v>
+      <c r="I53" s="1" t="n">
+        <v>0.02128</v>
       </c>
     </row>
     <row r="54">
@@ -1949,9 +2111,12 @@
         <v>0.007246</v>
       </c>
       <c r="G54" s="1" t="n">
+        <v>0.007247</v>
+      </c>
+      <c r="H54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="I54" s="1" t="n">
         <v>0.007221</v>
       </c>
     </row>
@@ -1977,9 +2142,12 @@
         <v>3.926</v>
       </c>
       <c r="G55" s="1" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="H55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="I55" s="1" t="n">
         <v>3.925</v>
       </c>
     </row>
@@ -2005,9 +2173,12 @@
         <v>0.017197</v>
       </c>
       <c r="G56" s="1" t="n">
+        <v>0.017187</v>
+      </c>
+      <c r="H56" s="1" t="n">
         <v>0.017208</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="I56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -2033,9 +2204,12 @@
         <v>0.1118</v>
       </c>
       <c r="G57" s="1" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="H57" s="1" t="n">
         <v>0.1118</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="I57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -2061,9 +2235,12 @@
         <v>2.647</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>2.659</v>
+        <v>2.662</v>
       </c>
       <c r="H58" s="1" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="I58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -2089,9 +2266,12 @@
         <v>0.16</v>
       </c>
       <c r="G59" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="H59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="I59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -2117,9 +2297,12 @@
         <v>0.005918</v>
       </c>
       <c r="G60" s="1" t="n">
+        <v>0.005923</v>
+      </c>
+      <c r="H60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="I60" s="1" t="n">
         <v>0.005914</v>
       </c>
     </row>
@@ -2145,9 +2328,12 @@
         <v>0.09206</v>
       </c>
       <c r="G61" s="1" t="n">
+        <v>0.09204</v>
+      </c>
+      <c r="H61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="H61" s="1" t="n">
+      <c r="I61" s="1" t="n">
         <v>0.09204</v>
       </c>
     </row>
@@ -2173,9 +2359,12 @@
         <v>0.9145</v>
       </c>
       <c r="G62" s="1" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="H62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="I62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -2201,9 +2390,12 @@
         <v>0.777</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="H63" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -2229,9 +2421,12 @@
         <v>0.04753</v>
       </c>
       <c r="G64" s="1" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="H64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="I64" s="1" t="n">
         <v>0.04623</v>
       </c>
     </row>
@@ -2257,9 +2452,12 @@
         <v>354.23</v>
       </c>
       <c r="G65" s="1" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="H65" s="1" t="n">
         <v>357.66</v>
       </c>
-      <c r="H65" s="1" t="n">
+      <c r="I65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -2285,10 +2483,13 @@
         <v>0.12516</v>
       </c>
       <c r="G66" s="1" t="n">
+        <v>0.12495</v>
+      </c>
+      <c r="H66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="H66" s="1" t="n">
-        <v>0.12516</v>
+      <c r="I66" s="1" t="n">
+        <v>0.12495</v>
       </c>
     </row>
     <row r="67">
@@ -2313,10 +2514,13 @@
         <v>0.2398</v>
       </c>
       <c r="G67" s="1" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="H67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="H67" s="1" t="n">
-        <v>0.2398</v>
+      <c r="I67" s="1" t="n">
+        <v>0.2383</v>
       </c>
     </row>
     <row r="68">
@@ -2341,9 +2545,12 @@
         <v>0.00341</v>
       </c>
       <c r="G68" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="H68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="I68" s="1" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -2369,10 +2576,13 @@
         <v>0.1755</v>
       </c>
       <c r="G69" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="H69" s="1" t="n">
-        <v>0.1755</v>
+      <c r="I69" s="1" t="n">
+        <v>0.175</v>
       </c>
     </row>
     <row r="70">
@@ -2397,9 +2607,12 @@
         <v>0.1649</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>0.1649</v>
+        <v>0.16506</v>
       </c>
       <c r="H70" s="1" t="n">
+        <v>0.16506</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>0.16421</v>
       </c>
     </row>
@@ -2425,9 +2638,12 @@
         <v>0.3574</v>
       </c>
       <c r="G71" s="1" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="H71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="I71" s="1" t="n">
         <v>0.3517</v>
       </c>
     </row>
@@ -2453,9 +2669,12 @@
         <v>0.7097</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>0.7097</v>
+        <v>0.7104</v>
       </c>
       <c r="H72" s="1" t="n">
+        <v>0.7104</v>
+      </c>
+      <c r="I72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -2481,9 +2700,12 @@
         <v>0.00864</v>
       </c>
       <c r="G73" s="1" t="n">
+        <v>0.008630000000000001</v>
+      </c>
+      <c r="H73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="I73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -2509,10 +2731,13 @@
         <v>0.006003</v>
       </c>
       <c r="G74" s="1" t="n">
+        <v>0.005999</v>
+      </c>
+      <c r="H74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="H74" s="1" t="n">
-        <v>0.006002</v>
+      <c r="I74" s="1" t="n">
+        <v>0.005999</v>
       </c>
     </row>
     <row r="75">
@@ -2537,9 +2762,12 @@
         <v>0.227</v>
       </c>
       <c r="G75" s="1" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="I75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -2565,9 +2793,12 @@
         <v>0.3103</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>0.3103</v>
+        <v>0.3126</v>
       </c>
       <c r="H76" s="1" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="I76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -2593,9 +2824,12 @@
         <v>0.1005</v>
       </c>
       <c r="G77" s="1" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="H77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="I77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -2621,9 +2855,12 @@
         <v>0.1232</v>
       </c>
       <c r="G78" s="1" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="H78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="I78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -2649,9 +2886,12 @@
         <v>0.06879</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>0.06933</v>
+        <v>0.06955</v>
       </c>
       <c r="H79" s="1" t="n">
+        <v>0.06955</v>
+      </c>
+      <c r="I79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -2677,9 +2917,12 @@
         <v>0.04709</v>
       </c>
       <c r="G80" s="1" t="n">
+        <v>0.04688</v>
+      </c>
+      <c r="H80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="H80" s="1" t="n">
+      <c r="I80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -2705,9 +2948,12 @@
         <v>0.000242</v>
       </c>
       <c r="G81" s="1" t="n">
+        <v>0.000238</v>
+      </c>
+      <c r="H81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="H81" s="1" t="n">
+      <c r="I81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -2733,9 +2979,12 @@
         <v>8.233000000000001</v>
       </c>
       <c r="G82" s="1" t="n">
+        <v>8.231999999999999</v>
+      </c>
+      <c r="H82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="I82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -2761,9 +3010,12 @@
         <v>0.0005831</v>
       </c>
       <c r="G83" s="1" t="n">
+        <v>0.000584</v>
+      </c>
+      <c r="H83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="H83" s="1" t="n">
+      <c r="I83" s="1" t="n">
         <v>0.0005831</v>
       </c>
     </row>
@@ -2789,9 +3041,12 @@
         <v>0.4207</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>0.4212</v>
+        <v>0.4268</v>
       </c>
       <c r="H84" s="1" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="I84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -2817,9 +3072,12 @@
         <v>0.06249</v>
       </c>
       <c r="G85" s="1" t="n">
+        <v>0.06257</v>
+      </c>
+      <c r="H85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="H85" s="1" t="n">
+      <c r="I85" s="1" t="n">
         <v>0.06243</v>
       </c>
     </row>
@@ -2845,9 +3103,12 @@
         <v>0.05465</v>
       </c>
       <c r="G86" s="1" t="n">
+        <v>0.05472</v>
+      </c>
+      <c r="H86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="I86" s="1" t="n">
         <v>0.05447</v>
       </c>
     </row>
@@ -2873,9 +3134,12 @@
         <v>0.00334</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>0.003356</v>
+        <v>0.003364</v>
       </c>
       <c r="H87" s="1" t="n">
+        <v>0.003364</v>
+      </c>
+      <c r="I87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -2901,9 +3165,12 @@
         <v>0.05073</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>0.05073</v>
+        <v>0.0514</v>
       </c>
       <c r="H88" s="1" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="I88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -2929,9 +3196,12 @@
         <v>0.0306</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>0.03086</v>
+        <v>0.031</v>
       </c>
       <c r="H89" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -2957,9 +3227,12 @@
         <v>0.3476</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>0.3491</v>
+        <v>0.3498</v>
       </c>
       <c r="H90" s="1" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="I90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -2985,9 +3258,12 @@
         <v>0.06163</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>0.06163</v>
+        <v>0.0625</v>
       </c>
       <c r="H91" s="1" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="I91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -3013,9 +3289,12 @@
         <v>0.349</v>
       </c>
       <c r="G92" s="1" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="H92" s="1" t="n">
         <v>0.3527</v>
       </c>
-      <c r="H92" s="1" t="n">
+      <c r="I92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -3041,9 +3320,12 @@
         <v>1.9671</v>
       </c>
       <c r="G93" s="1" t="n">
+        <v>1.9741</v>
+      </c>
+      <c r="H93" s="1" t="n">
         <v>1.9753</v>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="I93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -3069,9 +3351,12 @@
         <v>0.2595</v>
       </c>
       <c r="G94" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="H94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="H94" s="1" t="n">
+      <c r="I94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -3097,9 +3382,12 @@
         <v>0.04531</v>
       </c>
       <c r="G95" s="1" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="H95" s="1" t="n">
         <v>0.04542</v>
       </c>
-      <c r="H95" s="1" t="n">
+      <c r="I95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -3125,9 +3413,12 @@
         <v>0.006205</v>
       </c>
       <c r="G96" s="1" t="n">
+        <v>0.00623</v>
+      </c>
+      <c r="H96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="I96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -3153,9 +3444,12 @@
         <v>0.001739</v>
       </c>
       <c r="G97" s="1" t="n">
+        <v>0.001736</v>
+      </c>
+      <c r="H97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="I97" s="1" t="n">
         <v>0.001732</v>
       </c>
     </row>
@@ -3181,9 +3475,12 @@
         <v>5.243</v>
       </c>
       <c r="G98" s="1" t="n">
+        <v>5.248</v>
+      </c>
+      <c r="H98" s="1" t="n">
         <v>5.284</v>
       </c>
-      <c r="H98" s="1" t="n">
+      <c r="I98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -3209,9 +3506,12 @@
         <v>0.01523</v>
       </c>
       <c r="G99" s="1" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="H99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="H99" s="1" t="n">
+      <c r="I99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -3237,9 +3537,12 @@
         <v>0.5523</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>0.5523</v>
+        <v>0.5533</v>
       </c>
       <c r="H100" s="1" t="n">
+        <v>0.5533</v>
+      </c>
+      <c r="I100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -3268,6 +3571,9 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="H101" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="I101" s="1" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -3293,9 +3599,12 @@
         <v>32.51</v>
       </c>
       <c r="G102" s="1" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="H102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="I102" s="1" t="n">
         <v>32.48</v>
       </c>
     </row>
@@ -3321,9 +3630,12 @@
         <v>0.0322</v>
       </c>
       <c r="G103" s="1" t="n">
+        <v>0.03206</v>
+      </c>
+      <c r="H103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="I103" s="1" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -3349,9 +3661,12 @@
         <v>0.06601</v>
       </c>
       <c r="G104" s="1" t="n">
+        <v>0.06594999999999999</v>
+      </c>
+      <c r="H104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="H104" s="1" t="n">
+      <c r="I104" s="1" t="n">
         <v>0.06582</v>
       </c>
     </row>
@@ -3377,9 +3692,12 @@
         <v>1.3037</v>
       </c>
       <c r="G105" s="1" t="n">
+        <v>1.3023</v>
+      </c>
+      <c r="H105" s="1" t="n">
         <v>1.3041</v>
       </c>
-      <c r="H105" s="1" t="n">
+      <c r="I105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -3405,9 +3723,12 @@
         <v>0.12</v>
       </c>
       <c r="G106" s="1" t="n">
-        <v>0.12</v>
+        <v>0.1223</v>
       </c>
       <c r="H106" s="1" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="I106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -3433,9 +3754,12 @@
         <v>0.119</v>
       </c>
       <c r="G107" s="1" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="H107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="I107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -3461,9 +3785,12 @@
         <v>0.09597</v>
       </c>
       <c r="G108" s="1" t="n">
+        <v>0.09606000000000001</v>
+      </c>
+      <c r="H108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="H108" s="1" t="n">
+      <c r="I108" s="1" t="n">
         <v>0.09589</v>
       </c>
     </row>
@@ -3489,9 +3816,12 @@
         <v>0.1411</v>
       </c>
       <c r="G109" s="1" t="n">
+        <v>0.14066</v>
+      </c>
+      <c r="H109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="H109" s="1" t="n">
+      <c r="I109" s="1" t="n">
         <v>0.13861</v>
       </c>
     </row>
@@ -3517,9 +3847,12 @@
         <v>5.566</v>
       </c>
       <c r="G110" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="H110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="H110" s="1" t="n">
+      <c r="I110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -3545,9 +3878,12 @@
         <v>1.109</v>
       </c>
       <c r="G111" s="1" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="H111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="I111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -3573,9 +3909,12 @@
         <v>0.029256</v>
       </c>
       <c r="G112" s="1" t="n">
+        <v>0.029273</v>
+      </c>
+      <c r="H112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="H112" s="1" t="n">
+      <c r="I112" s="1" t="n">
         <v>0.029256</v>
       </c>
     </row>
@@ -3601,9 +3940,12 @@
         <v>1.877</v>
       </c>
       <c r="G113" s="1" t="n">
-        <v>1.879</v>
+        <v>1.884</v>
       </c>
       <c r="H113" s="1" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="I113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -3629,10 +3971,13 @@
         <v>0.05903</v>
       </c>
       <c r="G114" s="1" t="n">
+        <v>0.05848</v>
+      </c>
+      <c r="H114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="H114" s="1" t="n">
-        <v>0.05903</v>
+      <c r="I114" s="1" t="n">
+        <v>0.05848</v>
       </c>
     </row>
     <row r="115">
@@ -3657,9 +4002,12 @@
         <v>0.12732</v>
       </c>
       <c r="G115" s="1" t="n">
+        <v>0.12841</v>
+      </c>
+      <c r="H115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="H115" s="1" t="n">
+      <c r="I115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -3685,9 +4033,12 @@
         <v>1.1064</v>
       </c>
       <c r="G116" s="1" t="n">
+        <v>1.1078</v>
+      </c>
+      <c r="H116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="I116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -3713,9 +4064,12 @@
         <v>0.161</v>
       </c>
       <c r="G117" s="1" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="H117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="H117" s="1" t="n">
+      <c r="I117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -3741,9 +4095,12 @@
         <v>0.1589</v>
       </c>
       <c r="G118" s="1" t="n">
-        <v>0.1589</v>
+        <v>0.1599</v>
       </c>
       <c r="H118" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="I118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -3772,6 +4129,9 @@
         <v>0.04596</v>
       </c>
       <c r="H119" s="1" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="I119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -3797,9 +4157,12 @@
         <v>3.026</v>
       </c>
       <c r="G120" s="1" t="n">
+        <v>3.028</v>
+      </c>
+      <c r="H120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="H120" s="1" t="n">
+      <c r="I120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -3825,9 +4188,12 @@
         <v>0.2977</v>
       </c>
       <c r="G121" s="1" t="n">
-        <v>0.2977</v>
+        <v>0.2979</v>
       </c>
       <c r="H121" s="1" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="I121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -3853,9 +4219,12 @@
         <v>0.5841</v>
       </c>
       <c r="G122" s="1" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="H122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="H122" s="1" t="n">
+      <c r="I122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -3881,10 +4250,13 @@
         <v>0.01262</v>
       </c>
       <c r="G123" s="1" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="H123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="H123" s="1" t="n">
-        <v>0.0126</v>
+      <c r="I123" s="1" t="n">
+        <v>0.01258</v>
       </c>
     </row>
     <row r="124">
@@ -3909,9 +4281,12 @@
         <v>0.1593</v>
       </c>
       <c r="G124" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="H124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="H124" s="1" t="n">
+      <c r="I124" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -3937,9 +4312,12 @@
         <v>0.001779</v>
       </c>
       <c r="G125" s="1" t="n">
+        <v>0.001783</v>
+      </c>
+      <c r="H125" s="1" t="n">
         <v>0.001785</v>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="I125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -3965,10 +4343,13 @@
         <v>0.0004881</v>
       </c>
       <c r="G126" s="1" t="n">
+        <v>0.0004867</v>
+      </c>
+      <c r="H126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="H126" s="1" t="n">
-        <v>0.0004881</v>
+      <c r="I126" s="1" t="n">
+        <v>0.0004867</v>
       </c>
     </row>
     <row r="127">
@@ -3993,9 +4374,12 @@
         <v>0.02955</v>
       </c>
       <c r="G127" s="1" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="H127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="H127" s="1" t="n">
+      <c r="I127" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -4021,9 +4405,12 @@
         <v>0.04134</v>
       </c>
       <c r="G128" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="H128" s="1" t="n">
         <v>0.04134</v>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="I128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -4049,9 +4436,12 @@
         <v>0.04838</v>
       </c>
       <c r="G129" s="1" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="H129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="H129" s="1" t="n">
+      <c r="I129" s="1" t="n">
         <v>0.04838</v>
       </c>
     </row>
@@ -4080,6 +4470,9 @@
         <v>1.25e-05</v>
       </c>
       <c r="H130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="I130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -4105,9 +4498,12 @@
         <v>6.9e-06</v>
       </c>
       <c r="G131" s="1" t="n">
+        <v>6.9e-06</v>
+      </c>
+      <c r="H131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="H131" s="1" t="n">
+      <c r="I131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -4133,9 +4529,12 @@
         <v>0.00702</v>
       </c>
       <c r="G132" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="H132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="H132" s="1" t="n">
+      <c r="I132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -4164,6 +4563,9 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="H133" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="I133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -4189,9 +4591,12 @@
         <v>0.0004103</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>0.0004113</v>
+        <v>0.0004114</v>
       </c>
       <c r="H134" s="1" t="n">
+        <v>0.0004114</v>
+      </c>
+      <c r="I134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -4217,9 +4622,12 @@
         <v>0.08468000000000001</v>
       </c>
       <c r="G135" s="1" t="n">
+        <v>0.08445999999999999</v>
+      </c>
+      <c r="H135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="H135" s="1" t="n">
+      <c r="I135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -4245,9 +4653,12 @@
         <v>0.007891</v>
       </c>
       <c r="G136" s="1" t="n">
+        <v>0.007971000000000001</v>
+      </c>
+      <c r="H136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="H136" s="1" t="n">
+      <c r="I136" s="1" t="n">
         <v>0.007891</v>
       </c>
     </row>
@@ -4273,9 +4684,12 @@
         <v>0.0008233</v>
       </c>
       <c r="G137" s="1" t="n">
-        <v>0.0008262</v>
+        <v>0.000827</v>
       </c>
       <c r="H137" s="1" t="n">
+        <v>0.000827</v>
+      </c>
+      <c r="I137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -4301,10 +4715,13 @@
         <v>0.1482</v>
       </c>
       <c r="G138" s="1" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="H138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="H138" s="1" t="n">
-        <v>0.1482</v>
+      <c r="I138" s="1" t="n">
+        <v>0.1475</v>
       </c>
     </row>
     <row r="139">
@@ -4329,10 +4746,13 @@
         <v>0.006728</v>
       </c>
       <c r="G139" s="1" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="H139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="H139" s="1" t="n">
-        <v>0.006725</v>
+      <c r="I139" s="1" t="n">
+        <v>0.00672</v>
       </c>
     </row>
     <row r="140">
@@ -4357,9 +4777,12 @@
         <v>0.01383</v>
       </c>
       <c r="G140" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="H140" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="H140" s="1" t="n">
+      <c r="I140" s="1" t="n">
         <v>0.01383</v>
       </c>
     </row>
@@ -4385,9 +4808,12 @@
         <v>0.09758</v>
       </c>
       <c r="G141" s="1" t="n">
+        <v>0.09768</v>
+      </c>
+      <c r="H141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="H141" s="1" t="n">
+      <c r="I141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -4413,9 +4839,12 @@
         <v>0.05412</v>
       </c>
       <c r="G142" s="1" t="n">
-        <v>0.05416</v>
+        <v>0.05421</v>
       </c>
       <c r="H142" s="1" t="n">
+        <v>0.05421</v>
+      </c>
+      <c r="I142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -4441,9 +4870,12 @@
         <v>0.3246</v>
       </c>
       <c r="G143" s="1" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="H143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="H143" s="1" t="n">
+      <c r="I143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -4469,9 +4901,12 @@
         <v>0.02572</v>
       </c>
       <c r="G144" s="1" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="H144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="H144" s="1" t="n">
+      <c r="I144" s="1" t="n">
         <v>0.02572</v>
       </c>
     </row>
@@ -4497,9 +4932,12 @@
         <v>0.2378</v>
       </c>
       <c r="G145" s="1" t="n">
-        <v>0.238</v>
+        <v>0.2382</v>
       </c>
       <c r="H145" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="I145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -4525,10 +4963,13 @@
         <v>0.007052</v>
       </c>
       <c r="G146" s="1" t="n">
+        <v>0.007047</v>
+      </c>
+      <c r="H146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="H146" s="1" t="n">
-        <v>0.007052</v>
+      <c r="I146" s="1" t="n">
+        <v>0.007047</v>
       </c>
     </row>
     <row r="147">
@@ -4553,10 +4994,13 @@
         <v>0.08659</v>
       </c>
       <c r="G147" s="1" t="n">
+        <v>0.08655</v>
+      </c>
+      <c r="H147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="H147" s="1" t="n">
-        <v>0.08659</v>
+      <c r="I147" s="1" t="n">
+        <v>0.08655</v>
       </c>
     </row>
     <row r="148">
@@ -4581,9 +5025,12 @@
         <v>0.0503</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>0.05072</v>
+        <v>0.05073</v>
       </c>
       <c r="H148" s="1" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="I148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -4609,9 +5056,12 @@
         <v>0.02386</v>
       </c>
       <c r="G149" s="1" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="H149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="H149" s="1" t="n">
+      <c r="I149" s="1" t="n">
         <v>0.02386</v>
       </c>
     </row>
@@ -4637,9 +5087,12 @@
         <v>0.08495</v>
       </c>
       <c r="G150" s="1" t="n">
+        <v>0.08556</v>
+      </c>
+      <c r="H150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="H150" s="1" t="n">
+      <c r="I150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -4665,9 +5118,12 @@
         <v>0.0232</v>
       </c>
       <c r="G151" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="H151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="H151" s="1" t="n">
+      <c r="I151" s="1" t="n">
         <v>0.0232</v>
       </c>
     </row>
@@ -4693,9 +5149,12 @@
         <v>0.02571</v>
       </c>
       <c r="G152" s="1" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="H152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="H152" s="1" t="n">
+      <c r="I152" s="1" t="n">
         <v>0.02571</v>
       </c>
     </row>
@@ -4721,9 +5180,12 @@
         <v>0.0002145</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>0.0002145</v>
+        <v>0.0002183</v>
       </c>
       <c r="H153" s="1" t="n">
+        <v>0.0002183</v>
+      </c>
+      <c r="I153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -4749,9 +5211,12 @@
         <v>0.4474</v>
       </c>
       <c r="G154" s="1" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="H154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="H154" s="1" t="n">
+      <c r="I154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -4777,9 +5242,12 @@
         <v>0.06716</v>
       </c>
       <c r="G155" s="1" t="n">
+        <v>0.06701</v>
+      </c>
+      <c r="H155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="H155" s="1" t="n">
+      <c r="I155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -4808,6 +5276,9 @@
         <v>0.12938</v>
       </c>
       <c r="H156" s="1" t="n">
+        <v>0.12938</v>
+      </c>
+      <c r="I156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -4833,9 +5304,12 @@
         <v>0.4843</v>
       </c>
       <c r="G157" s="1" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="H157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="H157" s="1" t="n">
+      <c r="I157" s="1" t="n">
         <v>0.4843</v>
       </c>
     </row>
@@ -4861,9 +5335,12 @@
         <v>0.4496</v>
       </c>
       <c r="G158" s="1" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="H158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="H158" s="1" t="n">
+      <c r="I158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -4889,9 +5366,12 @@
         <v>0.007523</v>
       </c>
       <c r="G159" s="1" t="n">
+        <v>0.007529</v>
+      </c>
+      <c r="H159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="H159" s="1" t="n">
+      <c r="I159" s="1" t="n">
         <v>0.007523</v>
       </c>
     </row>
@@ -4917,9 +5397,12 @@
         <v>0.004653</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>0.004655</v>
+        <v>0.004664</v>
       </c>
       <c r="H160" s="1" t="n">
+        <v>0.004664</v>
+      </c>
+      <c r="I160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -4945,9 +5428,12 @@
         <v>0.004306</v>
       </c>
       <c r="G161" s="1" t="n">
+        <v>0.004304</v>
+      </c>
+      <c r="H161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="H161" s="1" t="n">
+      <c r="I161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -4973,9 +5459,12 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="G162" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="H162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="H162" s="1" t="n">
+      <c r="I162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -5001,9 +5490,12 @@
         <v>0.286</v>
       </c>
       <c r="G163" s="1" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="H163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="H163" s="1" t="n">
+      <c r="I163" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -5032,6 +5524,9 @@
         <v>0.1148</v>
       </c>
       <c r="H164" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="I164" s="1" t="n">
         <v>0.1144</v>
       </c>
     </row>
@@ -5057,9 +5552,12 @@
         <v>0.1757</v>
       </c>
       <c r="G165" s="1" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="H165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="H165" s="1" t="n">
+      <c r="I165" s="1" t="n">
         <v>0.1756</v>
       </c>
     </row>
@@ -5088,6 +5586,9 @@
         <v>0.01009</v>
       </c>
       <c r="H166" s="1" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="I166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -5116,6 +5617,9 @@
         <v>1.836</v>
       </c>
       <c r="H167" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="I167" s="1" t="n">
         <v>1.827</v>
       </c>
     </row>
@@ -5141,9 +5645,12 @@
         <v>1.351</v>
       </c>
       <c r="G168" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="H168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="H168" s="1" t="n">
+      <c r="I168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -5169,10 +5676,13 @@
         <v>0.007319</v>
       </c>
       <c r="G169" s="1" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="H169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="H169" s="1" t="n">
-        <v>0.007319</v>
+      <c r="I169" s="1" t="n">
+        <v>0.00731</v>
       </c>
     </row>
     <row r="170">
@@ -5197,9 +5707,12 @@
         <v>0.0116</v>
       </c>
       <c r="G170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="H170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="H170" s="1" t="n">
+      <c r="I170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -5225,9 +5738,12 @@
         <v>0.005826</v>
       </c>
       <c r="G171" s="1" t="n">
+        <v>0.005817</v>
+      </c>
+      <c r="H171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="H171" s="1" t="n">
+      <c r="I171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -5253,9 +5769,12 @@
         <v>0.14787</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>0.14796</v>
+        <v>0.14806</v>
       </c>
       <c r="H172" s="1" t="n">
+        <v>0.14806</v>
+      </c>
+      <c r="I172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -5281,9 +5800,12 @@
         <v>4.89</v>
       </c>
       <c r="G173" s="1" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="H173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="H173" s="1" t="n">
+      <c r="I173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -5309,9 +5831,12 @@
         <v>0.07949000000000001</v>
       </c>
       <c r="G174" s="1" t="n">
+        <v>0.07906000000000001</v>
+      </c>
+      <c r="H174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="H174" s="1" t="n">
+      <c r="I174" s="1" t="n">
         <v>0.07868</v>
       </c>
     </row>
@@ -5337,9 +5862,12 @@
         <v>0.007485</v>
       </c>
       <c r="G175" s="1" t="n">
+        <v>0.007496</v>
+      </c>
+      <c r="H175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="H175" s="1" t="n">
+      <c r="I175" s="1" t="n">
         <v>0.007485</v>
       </c>
     </row>
@@ -5365,9 +5893,12 @@
         <v>0.202</v>
       </c>
       <c r="G176" s="1" t="n">
+        <v>0.2017</v>
+      </c>
+      <c r="H176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="H176" s="1" t="n">
+      <c r="I176" s="1" t="n">
         <v>0.2016</v>
       </c>
     </row>
@@ -5393,9 +5924,12 @@
         <v>0.05184</v>
       </c>
       <c r="G177" s="1" t="n">
+        <v>0.05187</v>
+      </c>
+      <c r="H177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="H177" s="1" t="n">
+      <c r="I177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -5421,9 +5955,12 @@
         <v>0.05459</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>0.05465</v>
+        <v>0.05468</v>
       </c>
       <c r="H178" s="1" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="I178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -5449,9 +5986,12 @@
         <v>0.02333</v>
       </c>
       <c r="G179" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="H179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="H179" s="1" t="n">
+      <c r="I179" s="1" t="n">
         <v>0.02324</v>
       </c>
     </row>
@@ -5477,9 +6017,12 @@
         <v>0.6958</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>0.6958</v>
+        <v>0.6962</v>
       </c>
       <c r="H180" s="1" t="n">
+        <v>0.6962</v>
+      </c>
+      <c r="I180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -5505,9 +6048,12 @@
         <v>0.0003716</v>
       </c>
       <c r="G181" s="1" t="n">
+        <v>0.0003728</v>
+      </c>
+      <c r="H181" s="1" t="n">
         <v>0.0003731</v>
       </c>
-      <c r="H181" s="1" t="n">
+      <c r="I181" s="1" t="n">
         <v>0.0003716</v>
       </c>
     </row>
@@ -5533,9 +6079,12 @@
         <v>0.01266</v>
       </c>
       <c r="G182" s="1" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="H182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="H182" s="1" t="n">
+      <c r="I182" s="1" t="n">
         <v>0.01266</v>
       </c>
     </row>
@@ -5561,10 +6110,13 @@
         <v>4.261</v>
       </c>
       <c r="G183" s="1" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="H183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="H183" s="1" t="n">
-        <v>4.261</v>
+      <c r="I183" s="1" t="n">
+        <v>4.26</v>
       </c>
     </row>
     <row r="184">
@@ -5589,9 +6141,12 @@
         <v>0.2378</v>
       </c>
       <c r="G184" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="H184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="H184" s="1" t="n">
+      <c r="I184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -5617,10 +6172,13 @@
         <v>0.03764</v>
       </c>
       <c r="G185" s="1" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="H185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="H185" s="1" t="n">
-        <v>0.03764</v>
+      <c r="I185" s="1" t="n">
+        <v>0.03755</v>
       </c>
     </row>
     <row r="186">
@@ -5645,9 +6203,12 @@
         <v>0.11626</v>
       </c>
       <c r="G186" s="1" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="H186" s="1" t="n">
         <v>0.11628</v>
       </c>
-      <c r="H186" s="1" t="n">
+      <c r="I186" s="1" t="n">
         <v>0.11573</v>
       </c>
     </row>
@@ -5673,9 +6234,12 @@
         <v>0.009018999999999999</v>
       </c>
       <c r="G187" s="1" t="n">
+        <v>0.009056</v>
+      </c>
+      <c r="H187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="H187" s="1" t="n">
+      <c r="I187" s="1" t="n">
         <v>0.009018999999999999</v>
       </c>
     </row>
@@ -5701,9 +6265,12 @@
         <v>0.0977</v>
       </c>
       <c r="G188" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="H188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="H188" s="1" t="n">
+      <c r="I188" s="1" t="n">
         <v>0.0975</v>
       </c>
     </row>
@@ -5729,9 +6296,12 @@
         <v>0.02773</v>
       </c>
       <c r="G189" s="1" t="n">
+        <v>0.02799</v>
+      </c>
+      <c r="H189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="H189" s="1" t="n">
+      <c r="I189" s="1" t="n">
         <v>0.02773</v>
       </c>
     </row>
@@ -5757,9 +6327,12 @@
         <v>0.008829999999999999</v>
       </c>
       <c r="G190" s="1" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="H190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="H190" s="1" t="n">
+      <c r="I190" s="1" t="n">
         <v>0.00873</v>
       </c>
     </row>
@@ -5788,6 +6361,9 @@
         <v>0.001956</v>
       </c>
       <c r="H191" s="1" t="n">
+        <v>0.001956</v>
+      </c>
+      <c r="I191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -5813,9 +6389,12 @@
         <v>0.1007</v>
       </c>
       <c r="G192" s="1" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="H192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="H192" s="1" t="n">
+      <c r="I192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -5841,9 +6420,12 @@
         <v>0.02336</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>0.02336</v>
+        <v>0.02347</v>
       </c>
       <c r="H193" s="1" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="I193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -5869,9 +6451,12 @@
         <v>0.01346</v>
       </c>
       <c r="G194" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="H194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="H194" s="1" t="n">
+      <c r="I194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -5897,9 +6482,12 @@
         <v>0.02095</v>
       </c>
       <c r="G195" s="1" t="n">
+        <v>0.02096</v>
+      </c>
+      <c r="H195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="H195" s="1" t="n">
+      <c r="I195" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -5925,9 +6513,12 @@
         <v>0.17484</v>
       </c>
       <c r="G196" s="1" t="n">
+        <v>0.17376</v>
+      </c>
+      <c r="H196" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="H196" s="1" t="n">
+      <c r="I196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -5953,9 +6544,12 @@
         <v>0.007358</v>
       </c>
       <c r="G197" s="1" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="H197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="H197" s="1" t="n">
+      <c r="I197" s="1" t="n">
         <v>0.007292</v>
       </c>
     </row>
@@ -5981,9 +6575,12 @@
         <v>0.01909</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>0.0191</v>
+        <v>0.01912</v>
       </c>
       <c r="H198" s="1" t="n">
+        <v>0.01912</v>
+      </c>
+      <c r="I198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -6009,10 +6606,13 @@
         <v>0.01631</v>
       </c>
       <c r="G199" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="H199" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="H199" s="1" t="n">
-        <v>0.01631</v>
+      <c r="I199" s="1" t="n">
+        <v>0.01626</v>
       </c>
     </row>
     <row r="200">
@@ -6037,9 +6637,12 @@
         <v>0.2965</v>
       </c>
       <c r="G200" s="1" t="n">
-        <v>0.2975</v>
+        <v>0.2979</v>
       </c>
       <c r="H200" s="1" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="I200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -6065,9 +6668,12 @@
         <v>0.006229</v>
       </c>
       <c r="G201" s="1" t="n">
+        <v>0.006236</v>
+      </c>
+      <c r="H201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="H201" s="1" t="n">
+      <c r="I201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -6093,9 +6699,12 @@
         <v>0.0004451</v>
       </c>
       <c r="G202" s="1" t="n">
-        <v>0.0004463</v>
+        <v>0.0004464</v>
       </c>
       <c r="H202" s="1" t="n">
+        <v>0.0004464</v>
+      </c>
+      <c r="I202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -6121,9 +6730,12 @@
         <v>0.007365</v>
       </c>
       <c r="G203" s="1" t="n">
+        <v>0.007364</v>
+      </c>
+      <c r="H203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="H203" s="1" t="n">
+      <c r="I203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -6149,9 +6761,12 @@
         <v>0.1295</v>
       </c>
       <c r="G204" s="1" t="n">
-        <v>0.1295</v>
+        <v>0.1301</v>
       </c>
       <c r="H204" s="1" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="I204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -6177,10 +6792,13 @@
         <v>0.01444</v>
       </c>
       <c r="G205" s="1" t="n">
+        <v>0.01442</v>
+      </c>
+      <c r="H205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="H205" s="1" t="n">
-        <v>0.01444</v>
+      <c r="I205" s="1" t="n">
+        <v>0.01442</v>
       </c>
     </row>
     <row r="206">
@@ -6205,9 +6823,12 @@
         <v>0.003583</v>
       </c>
       <c r="G206" s="1" t="n">
+        <v>0.003586</v>
+      </c>
+      <c r="H206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="H206" s="1" t="n">
+      <c r="I206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -6233,9 +6854,12 @@
         <v>0.05952</v>
       </c>
       <c r="G207" s="1" t="n">
+        <v>0.05947</v>
+      </c>
+      <c r="H207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="H207" s="1" t="n">
+      <c r="I207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -6261,9 +6885,12 @@
         <v>15.47</v>
       </c>
       <c r="G208" s="1" t="n">
-        <v>15.47</v>
+        <v>15.49</v>
       </c>
       <c r="H208" s="1" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="I208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -6289,9 +6916,12 @@
         <v>5183.4</v>
       </c>
       <c r="G209" s="1" t="n">
+        <v>5185.8</v>
+      </c>
+      <c r="H209" s="1" t="n">
         <v>5186.2</v>
       </c>
-      <c r="H209" s="1" t="n">
+      <c r="I209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -6317,9 +6947,12 @@
         <v>0.11988</v>
       </c>
       <c r="G210" s="1" t="n">
+        <v>0.11994</v>
+      </c>
+      <c r="H210" s="1" t="n">
         <v>0.12042</v>
       </c>
-      <c r="H210" s="1" t="n">
+      <c r="I210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -6345,10 +6978,13 @@
         <v>0.1824</v>
       </c>
       <c r="G211" s="1" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="H211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="H211" s="1" t="n">
-        <v>0.1824</v>
+      <c r="I211" s="1" t="n">
+        <v>0.1822</v>
       </c>
     </row>
     <row r="212">
@@ -6373,9 +7009,12 @@
         <v>0.0303</v>
       </c>
       <c r="G212" s="1" t="n">
-        <v>0.0303</v>
+        <v>0.0304</v>
       </c>
       <c r="H212" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="I212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -6404,6 +7043,9 @@
         <v>1.3976</v>
       </c>
       <c r="H213" s="1" t="n">
+        <v>1.3976</v>
+      </c>
+      <c r="I213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -6429,9 +7071,12 @@
         <v>0.05664</v>
       </c>
       <c r="G214" s="1" t="n">
-        <v>0.05664</v>
+        <v>0.05673</v>
       </c>
       <c r="H214" s="1" t="n">
+        <v>0.05673</v>
+      </c>
+      <c r="I214" s="1" t="n">
         <v>0.05658</v>
       </c>
     </row>
@@ -6457,9 +7102,12 @@
         <v>0.04371</v>
       </c>
       <c r="G215" s="1" t="n">
+        <v>0.04375</v>
+      </c>
+      <c r="H215" s="1" t="n">
         <v>0.04385</v>
       </c>
-      <c r="H215" s="1" t="n">
+      <c r="I215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -6485,10 +7133,13 @@
         <v>0.1517</v>
       </c>
       <c r="G216" s="1" t="n">
+        <v>0.15045</v>
+      </c>
+      <c r="H216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="H216" s="1" t="n">
-        <v>0.15102</v>
+      <c r="I216" s="1" t="n">
+        <v>0.15045</v>
       </c>
     </row>
     <row r="217">
@@ -6513,9 +7164,12 @@
         <v>0.073</v>
       </c>
       <c r="G217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="H217" s="1" t="n">
+      <c r="I217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -6544,6 +7198,9 @@
         <v>0.00269</v>
       </c>
       <c r="H218" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="I218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -6569,9 +7226,12 @@
         <v>0.01715</v>
       </c>
       <c r="G219" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="H219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="H219" s="1" t="n">
+      <c r="I219" s="1" t="n">
         <v>0.01715</v>
       </c>
     </row>
@@ -6600,6 +7260,9 @@
         <v>0.05535</v>
       </c>
       <c r="H220" s="1" t="n">
+        <v>0.05535</v>
+      </c>
+      <c r="I220" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -6628,6 +7291,9 @@
         <v>0.02196</v>
       </c>
       <c r="H221" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="I221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -6653,9 +7319,12 @@
         <v>0.009350000000000001</v>
       </c>
       <c r="G222" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="H222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="H222" s="1" t="n">
+      <c r="I222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -6686,6 +7355,9 @@
       <c r="H223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="I223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6709,9 +7381,12 @@
         <v>0.03826</v>
       </c>
       <c r="G224" s="1" t="n">
+        <v>0.03834</v>
+      </c>
+      <c r="H224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="H224" s="1" t="n">
+      <c r="I224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -6737,9 +7412,12 @@
         <v>0.001528</v>
       </c>
       <c r="G225" s="1" t="n">
+        <v>0.001528</v>
+      </c>
+      <c r="H225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="H225" s="1" t="n">
+      <c r="I225" s="1" t="n">
         <v>0.001526</v>
       </c>
     </row>
@@ -6765,10 +7443,13 @@
         <v>26.99</v>
       </c>
       <c r="G226" s="1" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="H226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="H226" s="1" t="n">
-        <v>26.99</v>
+      <c r="I226" s="1" t="n">
+        <v>26.95</v>
       </c>
     </row>
     <row r="227">
@@ -6793,9 +7474,12 @@
         <v>0.07015</v>
       </c>
       <c r="G227" s="1" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="H227" s="1" t="n">
         <v>0.07027</v>
       </c>
-      <c r="H227" s="1" t="n">
+      <c r="I227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -6821,9 +7505,12 @@
         <v>0.3125</v>
       </c>
       <c r="G228" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="H228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="H228" s="1" t="n">
+      <c r="I228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -6852,6 +7539,9 @@
         <v>18.46</v>
       </c>
       <c r="H229" s="1" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="I229" s="1" t="n">
         <v>18.42</v>
       </c>
     </row>
@@ -6877,9 +7567,12 @@
         <v>0.01932</v>
       </c>
       <c r="G230" s="1" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="H230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="H230" s="1" t="n">
+      <c r="I230" s="1" t="n">
         <v>0.01932</v>
       </c>
     </row>
@@ -6905,9 +7598,12 @@
         <v>0.01221</v>
       </c>
       <c r="G231" s="1" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="H231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="H231" s="1" t="n">
+      <c r="I231" s="1" t="n">
         <v>0.01221</v>
       </c>
     </row>
@@ -6933,9 +7629,12 @@
         <v>0.2287</v>
       </c>
       <c r="G232" s="1" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="H232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="H232" s="1" t="n">
+      <c r="I232" s="1" t="n">
         <v>0.2285</v>
       </c>
     </row>
@@ -6961,9 +7660,12 @@
         <v>0.07101</v>
       </c>
       <c r="G233" s="1" t="n">
+        <v>0.07103</v>
+      </c>
+      <c r="H233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="H233" s="1" t="n">
+      <c r="I233" s="1" t="n">
         <v>0.07101</v>
       </c>
     </row>
@@ -6989,9 +7691,12 @@
         <v>0.1701</v>
       </c>
       <c r="G234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="H234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="H234" s="1" t="n">
+      <c r="I234" s="1" t="n">
         <v>0.1701</v>
       </c>
     </row>
@@ -7017,9 +7722,12 @@
         <v>0.0253</v>
       </c>
       <c r="G235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="H235" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="H235" s="1" t="n">
+      <c r="I235" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -7045,10 +7753,13 @@
         <v>0.03005</v>
       </c>
       <c r="G236" s="1" t="n">
+        <v>0.03004</v>
+      </c>
+      <c r="H236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="H236" s="1" t="n">
-        <v>0.03005</v>
+      <c r="I236" s="1" t="n">
+        <v>0.03004</v>
       </c>
     </row>
     <row r="237">
@@ -7073,9 +7784,12 @@
         <v>1.988</v>
       </c>
       <c r="G237" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="H237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="H237" s="1" t="n">
+      <c r="I237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -7101,9 +7815,12 @@
         <v>0.4312</v>
       </c>
       <c r="G238" s="1" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="H238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="H238" s="1" t="n">
+      <c r="I238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -7129,9 +7846,12 @@
         <v>0.03343</v>
       </c>
       <c r="G239" s="1" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="H239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="H239" s="1" t="n">
+      <c r="I239" s="1" t="n">
         <v>0.03343</v>
       </c>
     </row>
@@ -7157,9 +7877,12 @@
         <v>0.0341</v>
       </c>
       <c r="G240" s="1" t="n">
+        <v>0.03407</v>
+      </c>
+      <c r="H240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="H240" s="1" t="n">
+      <c r="I240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -7185,9 +7908,12 @@
         <v>0.0007531</v>
       </c>
       <c r="G241" s="1" t="n">
+        <v>0.0007541</v>
+      </c>
+      <c r="H241" s="1" t="n">
         <v>0.0007551</v>
       </c>
-      <c r="H241" s="1" t="n">
+      <c r="I241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -7213,9 +7939,12 @@
         <v>0.184</v>
       </c>
       <c r="G242" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="H242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="H242" s="1" t="n">
+      <c r="I242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -7241,9 +7970,12 @@
         <v>0.014816</v>
       </c>
       <c r="G243" s="1" t="n">
+        <v>0.014831</v>
+      </c>
+      <c r="H243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="H243" s="1" t="n">
+      <c r="I243" s="1" t="n">
         <v>0.014816</v>
       </c>
     </row>
@@ -7269,9 +8001,12 @@
         <v>3.08e-05</v>
       </c>
       <c r="G244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="H244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="H244" s="1" t="n">
+      <c r="I244" s="1" t="n">
         <v>3.08e-05</v>
       </c>
     </row>
@@ -7297,9 +8032,12 @@
         <v>0.03526</v>
       </c>
       <c r="G245" s="1" t="n">
+        <v>0.03522</v>
+      </c>
+      <c r="H245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="H245" s="1" t="n">
+      <c r="I245" s="1" t="n">
         <v>0.03521</v>
       </c>
     </row>
@@ -7325,9 +8063,12 @@
         <v>0.08068</v>
       </c>
       <c r="G246" s="1" t="n">
+        <v>0.08071</v>
+      </c>
+      <c r="H246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="H246" s="1" t="n">
+      <c r="I246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -7353,10 +8094,13 @@
         <v>0.007347</v>
       </c>
       <c r="G247" s="1" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="H247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="H247" s="1" t="n">
-        <v>0.007318</v>
+      <c r="I247" s="1" t="n">
+        <v>0.00728</v>
       </c>
     </row>
     <row r="248">
@@ -7381,9 +8125,12 @@
         <v>0.09499</v>
       </c>
       <c r="G248" s="1" t="n">
+        <v>0.09583</v>
+      </c>
+      <c r="H248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="H248" s="1" t="n">
+      <c r="I248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -7412,6 +8159,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="H249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="I249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -7437,9 +8187,12 @@
         <v>0.03512</v>
       </c>
       <c r="G250" s="1" t="n">
+        <v>0.03509</v>
+      </c>
+      <c r="H250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="H250" s="1" t="n">
+      <c r="I250" s="1" t="n">
         <v>0.03504</v>
       </c>
     </row>
@@ -7465,9 +8218,12 @@
         <v>0.04078</v>
       </c>
       <c r="G251" s="1" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="H251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="H251" s="1" t="n">
+      <c r="I251" s="1" t="n">
         <v>0.04058</v>
       </c>
     </row>
@@ -7493,9 +8249,12 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="G252" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="H252" s="1" t="n">
         <v>0.08939999999999999</v>
       </c>
-      <c r="H252" s="1" t="n">
+      <c r="I252" s="1" t="n">
         <v>0.0891</v>
       </c>
     </row>
@@ -7521,9 +8280,12 @@
         <v>4.095</v>
       </c>
       <c r="G253" s="1" t="n">
-        <v>4.095</v>
+        <v>4.096</v>
       </c>
       <c r="H253" s="1" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="I253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -7552,6 +8314,9 @@
         <v>0.1875</v>
       </c>
       <c r="H254" s="1" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="I254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -7577,10 +8342,13 @@
         <v>0.07274</v>
       </c>
       <c r="G255" s="1" t="n">
+        <v>0.07214</v>
+      </c>
+      <c r="H255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="H255" s="1" t="n">
-        <v>0.07273</v>
+      <c r="I255" s="1" t="n">
+        <v>0.07214</v>
       </c>
     </row>
     <row r="256">
@@ -7605,9 +8373,12 @@
         <v>0.01827</v>
       </c>
       <c r="G256" s="1" t="n">
-        <v>0.01828</v>
+        <v>0.01831</v>
       </c>
       <c r="H256" s="1" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="I256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -7633,9 +8404,12 @@
         <v>5.962</v>
       </c>
       <c r="G257" s="1" t="n">
-        <v>5.962</v>
+        <v>5.964</v>
       </c>
       <c r="H257" s="1" t="n">
+        <v>5.964</v>
+      </c>
+      <c r="I257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -7661,9 +8435,12 @@
         <v>0.2626</v>
       </c>
       <c r="G258" s="1" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="H258" s="1" t="n">
         <v>0.2639</v>
       </c>
-      <c r="H258" s="1" t="n">
+      <c r="I258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -7689,9 +8466,12 @@
         <v>0.1366</v>
       </c>
       <c r="G259" s="1" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="H259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="H259" s="1" t="n">
+      <c r="I259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -7717,9 +8497,12 @@
         <v>0.30525</v>
       </c>
       <c r="G260" s="1" t="n">
-        <v>0.30606</v>
+        <v>0.30612</v>
       </c>
       <c r="H260" s="1" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="I260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -7745,9 +8528,12 @@
         <v>0.09858</v>
       </c>
       <c r="G261" s="1" t="n">
-        <v>0.09862</v>
+        <v>0.09878000000000001</v>
       </c>
       <c r="H261" s="1" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="I261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -7773,9 +8559,12 @@
         <v>0.5423</v>
       </c>
       <c r="G262" s="1" t="n">
+        <v>0.5426</v>
+      </c>
+      <c r="H262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="H262" s="1" t="n">
+      <c r="I262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -7801,9 +8590,12 @@
         <v>0.2923</v>
       </c>
       <c r="G263" s="1" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="H263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="H263" s="1" t="n">
+      <c r="I263" s="1" t="n">
         <v>0.2923</v>
       </c>
     </row>
@@ -7829,9 +8621,12 @@
         <v>0.952</v>
       </c>
       <c r="G264" s="1" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="H264" s="1" t="n">
         <v>0.953</v>
       </c>
-      <c r="H264" s="1" t="n">
+      <c r="I264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -7857,9 +8652,12 @@
         <v>0.541</v>
       </c>
       <c r="G265" s="1" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="H265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="H265" s="1" t="n">
+      <c r="I265" s="1" t="n">
         <v>0.5405</v>
       </c>
     </row>
@@ -7885,9 +8683,12 @@
         <v>0.074</v>
       </c>
       <c r="G266" s="1" t="n">
+        <v>0.07396999999999999</v>
+      </c>
+      <c r="H266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="H266" s="1" t="n">
+      <c r="I266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -7916,6 +8717,9 @@
         <v>0.02151</v>
       </c>
       <c r="H267" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="I267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -7941,9 +8745,12 @@
         <v>0.01606</v>
       </c>
       <c r="G268" s="1" t="n">
-        <v>0.01622</v>
+        <v>0.01633</v>
       </c>
       <c r="H268" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="I268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -7969,9 +8776,12 @@
         <v>0.003702</v>
       </c>
       <c r="G269" s="1" t="n">
+        <v>0.003706</v>
+      </c>
+      <c r="H269" s="1" t="n">
         <v>0.003717</v>
       </c>
-      <c r="H269" s="1" t="n">
+      <c r="I269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -7997,9 +8807,12 @@
         <v>0.0077</v>
       </c>
       <c r="G270" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="H270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="H270" s="1" t="n">
+      <c r="I270" s="1" t="n">
         <v>0.00769</v>
       </c>
     </row>
@@ -8025,9 +8838,12 @@
         <v>0.05502</v>
       </c>
       <c r="G271" s="1" t="n">
-        <v>0.0551</v>
+        <v>0.05512</v>
       </c>
       <c r="H271" s="1" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="I271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -8053,9 +8869,12 @@
         <v>2.317</v>
       </c>
       <c r="G272" s="1" t="n">
-        <v>2.317</v>
+        <v>2.318</v>
       </c>
       <c r="H272" s="1" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="I272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -8081,9 +8900,12 @@
         <v>0.05467</v>
       </c>
       <c r="G273" s="1" t="n">
-        <v>0.0547</v>
+        <v>0.05471</v>
       </c>
       <c r="H273" s="1" t="n">
+        <v>0.05471</v>
+      </c>
+      <c r="I273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -8109,9 +8931,12 @@
         <v>0.02283</v>
       </c>
       <c r="G274" s="1" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="H274" s="1" t="n">
         <v>0.02291</v>
       </c>
-      <c r="H274" s="1" t="n">
+      <c r="I274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -8137,9 +8962,12 @@
         <v>1.182</v>
       </c>
       <c r="G275" s="1" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="H275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="H275" s="1" t="n">
+      <c r="I275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -8165,10 +8993,13 @@
         <v>0.2723</v>
       </c>
       <c r="G276" s="1" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="H276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="H276" s="1" t="n">
-        <v>0.2723</v>
+      <c r="I276" s="1" t="n">
+        <v>0.2722</v>
       </c>
     </row>
     <row r="277">
@@ -8193,9 +9024,12 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="G277" s="1" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="H277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="H277" s="1" t="n">
+      <c r="I277" s="1" t="n">
         <v>0.9419999999999999</v>
       </c>
     </row>
@@ -8221,9 +9055,12 @@
         <v>0.6274</v>
       </c>
       <c r="G278" s="1" t="n">
-        <v>0.6274</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="H278" s="1" t="n">
+        <v>0.6274999999999999</v>
+      </c>
+      <c r="I278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -8249,9 +9086,12 @@
         <v>0.00136</v>
       </c>
       <c r="G279" s="1" t="n">
+        <v>0.001354</v>
+      </c>
+      <c r="H279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="H279" s="1" t="n">
+      <c r="I279" s="1" t="n">
         <v>0.00135</v>
       </c>
     </row>
@@ -8277,9 +9117,12 @@
         <v>0.005551</v>
       </c>
       <c r="G280" s="1" t="n">
-        <v>0.005553</v>
+        <v>0.005557</v>
       </c>
       <c r="H280" s="1" t="n">
+        <v>0.005557</v>
+      </c>
+      <c r="I280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -8305,9 +9148,12 @@
         <v>1.524</v>
       </c>
       <c r="G281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="H281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="H281" s="1" t="n">
+      <c r="I281" s="1" t="n">
         <v>1.522</v>
       </c>
     </row>
@@ -8333,9 +9179,12 @@
         <v>28.32</v>
       </c>
       <c r="G282" s="1" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="H282" s="1" t="n">
+      <c r="I282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -8361,9 +9210,12 @@
         <v>0.12922</v>
       </c>
       <c r="G283" s="1" t="n">
+        <v>0.12935</v>
+      </c>
+      <c r="H283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="H283" s="1" t="n">
+      <c r="I283" s="1" t="n">
         <v>0.12922</v>
       </c>
     </row>
@@ -8389,9 +9241,12 @@
         <v>0.01115</v>
       </c>
       <c r="G284" s="1" t="n">
-        <v>0.01115</v>
+        <v>0.01116</v>
       </c>
       <c r="H284" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="I284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -8417,9 +9272,12 @@
         <v>6.54</v>
       </c>
       <c r="G285" s="1" t="n">
+        <v>6.542</v>
+      </c>
+      <c r="H285" s="1" t="n">
         <v>6.544</v>
       </c>
-      <c r="H285" s="1" t="n">
+      <c r="I285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -8445,9 +9303,12 @@
         <v>0.01852</v>
       </c>
       <c r="G286" s="1" t="n">
+        <v>0.01855</v>
+      </c>
+      <c r="H286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="H286" s="1" t="n">
+      <c r="I286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -8473,9 +9334,12 @@
         <v>0.008404999999999999</v>
       </c>
       <c r="G287" s="1" t="n">
+        <v>0.008416999999999999</v>
+      </c>
+      <c r="H287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="H287" s="1" t="n">
+      <c r="I287" s="1" t="n">
         <v>0.008404999999999999</v>
       </c>
     </row>
@@ -8501,10 +9365,13 @@
         <v>0.3889</v>
       </c>
       <c r="G288" s="1" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="H288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="H288" s="1" t="n">
-        <v>0.3879</v>
+      <c r="I288" s="1" t="n">
+        <v>0.3856</v>
       </c>
     </row>
     <row r="289">
@@ -8529,10 +9396,13 @@
         <v>0.010267</v>
       </c>
       <c r="G289" s="1" t="n">
+        <v>0.010213</v>
+      </c>
+      <c r="H289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="H289" s="1" t="n">
-        <v>0.010267</v>
+      <c r="I289" s="1" t="n">
+        <v>0.010213</v>
       </c>
     </row>
     <row r="290">
@@ -8557,9 +9427,12 @@
         <v>0.02617</v>
       </c>
       <c r="G290" s="1" t="n">
+        <v>0.02622</v>
+      </c>
+      <c r="H290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="H290" s="1" t="n">
+      <c r="I290" s="1" t="n">
         <v>0.02613</v>
       </c>
     </row>
@@ -8588,6 +9461,9 @@
         <v>0.097</v>
       </c>
       <c r="H291" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -8613,9 +9489,12 @@
         <v>0.28497</v>
       </c>
       <c r="G292" s="1" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="H292" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="H292" s="1" t="n">
+      <c r="I292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -8641,9 +9520,12 @@
         <v>0.01543</v>
       </c>
       <c r="G293" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="H293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="H293" s="1" t="n">
+      <c r="I293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -8669,9 +9551,12 @@
         <v>0.00342</v>
       </c>
       <c r="G294" s="1" t="n">
-        <v>0.00342</v>
+        <v>0.003425</v>
       </c>
       <c r="H294" s="1" t="n">
+        <v>0.003425</v>
+      </c>
+      <c r="I294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -8697,10 +9582,13 @@
         <v>0.043462</v>
       </c>
       <c r="G295" s="1" t="n">
+        <v>0.043361</v>
+      </c>
+      <c r="H295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="H295" s="1" t="n">
-        <v>0.043462</v>
+      <c r="I295" s="1" t="n">
+        <v>0.043361</v>
       </c>
     </row>
     <row r="296">
@@ -8725,10 +9613,13 @@
         <v>0.0295</v>
       </c>
       <c r="G296" s="1" t="n">
+        <v>0.02941</v>
+      </c>
+      <c r="H296" s="1" t="n">
         <v>0.03007</v>
       </c>
-      <c r="H296" s="1" t="n">
-        <v>0.02943</v>
+      <c r="I296" s="1" t="n">
+        <v>0.02941</v>
       </c>
     </row>
     <row r="297">
@@ -8753,10 +9644,13 @@
         <v>0.03857</v>
       </c>
       <c r="G297" s="1" t="n">
+        <v>0.03786</v>
+      </c>
+      <c r="H297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="H297" s="1" t="n">
-        <v>0.03857</v>
+      <c r="I297" s="1" t="n">
+        <v>0.03786</v>
       </c>
     </row>
     <row r="298">
@@ -8781,9 +9675,12 @@
         <v>0.08305999999999999</v>
       </c>
       <c r="G298" s="1" t="n">
+        <v>0.08341999999999999</v>
+      </c>
+      <c r="H298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="H298" s="1" t="n">
+      <c r="I298" s="1" t="n">
         <v>0.08305999999999999</v>
       </c>
     </row>
@@ -8809,10 +9706,13 @@
         <v>0.00765</v>
       </c>
       <c r="G299" s="1" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="H299" s="1" t="n">
         <v>0.00766</v>
       </c>
-      <c r="H299" s="1" t="n">
-        <v>0.00762</v>
+      <c r="I299" s="1" t="n">
+        <v>0.00761</v>
       </c>
     </row>
     <row r="300">
@@ -8837,9 +9737,12 @@
         <v>0.01521</v>
       </c>
       <c r="G300" s="1" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="H300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="H300" s="1" t="n">
+      <c r="I300" s="1" t="n">
         <v>0.01519</v>
       </c>
     </row>
@@ -8865,9 +9768,12 @@
         <v>0.141</v>
       </c>
       <c r="G301" s="1" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="H301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="H301" s="1" t="n">
+      <c r="I301" s="1" t="n">
         <v>0.141</v>
       </c>
     </row>
@@ -8893,10 +9799,13 @@
         <v>0.0006401</v>
       </c>
       <c r="G302" s="1" t="n">
+        <v>0.0006305</v>
+      </c>
+      <c r="H302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="H302" s="1" t="n">
-        <v>0.0006401</v>
+      <c r="I302" s="1" t="n">
+        <v>0.0006305</v>
       </c>
     </row>
     <row r="303">
@@ -8921,9 +9830,12 @@
         <v>0.06222</v>
       </c>
       <c r="G303" s="1" t="n">
+        <v>0.06227</v>
+      </c>
+      <c r="H303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="H303" s="1" t="n">
+      <c r="I303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -8949,9 +9861,12 @@
         <v>0.0001626</v>
       </c>
       <c r="G304" s="1" t="n">
+        <v>0.0001632</v>
+      </c>
+      <c r="H304" s="1" t="n">
         <v>0.0001639</v>
       </c>
-      <c r="H304" s="1" t="n">
+      <c r="I304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -8977,9 +9892,12 @@
         <v>0.06121</v>
       </c>
       <c r="G305" s="1" t="n">
-        <v>0.06134</v>
+        <v>0.06144</v>
       </c>
       <c r="H305" s="1" t="n">
+        <v>0.06144</v>
+      </c>
+      <c r="I305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -9005,9 +9923,12 @@
         <v>0.022133</v>
       </c>
       <c r="G306" s="1" t="n">
+        <v>0.022443</v>
+      </c>
+      <c r="H306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="H306" s="1" t="n">
+      <c r="I306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -9033,10 +9954,13 @@
         <v>0.02346</v>
       </c>
       <c r="G307" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="H307" s="1" t="n">
         <v>0.02414</v>
       </c>
-      <c r="H307" s="1" t="n">
-        <v>0.02346</v>
+      <c r="I307" s="1" t="n">
+        <v>0.02332</v>
       </c>
     </row>
     <row r="308">
@@ -9061,9 +9985,12 @@
         <v>0.000412</v>
       </c>
       <c r="G308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="H308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="H308" s="1" t="n">
+      <c r="I308" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -9089,9 +10016,12 @@
         <v>0.0897</v>
       </c>
       <c r="G309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="H309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="H309" s="1" t="n">
+      <c r="I309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -9117,9 +10047,12 @@
         <v>0.3854</v>
       </c>
       <c r="G310" s="1" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="H310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="H310" s="1" t="n">
+      <c r="I310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -9145,10 +10078,13 @@
         <v>0.0358</v>
       </c>
       <c r="G311" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="H311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="H311" s="1" t="n">
-        <v>0.0357</v>
+      <c r="I311" s="1" t="n">
+        <v>0.0356</v>
       </c>
     </row>
     <row r="312">
@@ -9173,9 +10109,12 @@
         <v>0.02485</v>
       </c>
       <c r="G312" s="1" t="n">
+        <v>0.02478</v>
+      </c>
+      <c r="H312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="H312" s="1" t="n">
+      <c r="I312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -9201,10 +10140,13 @@
         <v>0.04134</v>
       </c>
       <c r="G313" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="H313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="H313" s="1" t="n">
-        <v>0.04134</v>
+      <c r="I313" s="1" t="n">
+        <v>0.04131</v>
       </c>
     </row>
     <row r="314">
@@ -9229,9 +10171,12 @@
         <v>4.014</v>
       </c>
       <c r="G314" s="1" t="n">
+        <v>4.012</v>
+      </c>
+      <c r="H314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="H314" s="1" t="n">
+      <c r="I314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -9257,9 +10202,12 @@
         <v>0.1602</v>
       </c>
       <c r="G315" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="H315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="H315" s="1" t="n">
+      <c r="I315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -9285,9 +10233,12 @@
         <v>0.08834</v>
       </c>
       <c r="G316" s="1" t="n">
-        <v>0.08852</v>
+        <v>0.08884</v>
       </c>
       <c r="H316" s="1" t="n">
+        <v>0.08884</v>
+      </c>
+      <c r="I316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -9313,9 +10264,12 @@
         <v>0.06837</v>
       </c>
       <c r="G317" s="1" t="n">
-        <v>0.06837</v>
+        <v>0.06847</v>
       </c>
       <c r="H317" s="1" t="n">
+        <v>0.06847</v>
+      </c>
+      <c r="I317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -9341,10 +10295,13 @@
         <v>0.01261</v>
       </c>
       <c r="G318" s="1" t="n">
+        <v>0.012549</v>
+      </c>
+      <c r="H318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="H318" s="1" t="n">
-        <v>0.01261</v>
+      <c r="I318" s="1" t="n">
+        <v>0.012549</v>
       </c>
     </row>
     <row r="319">
@@ -9369,9 +10326,12 @@
         <v>0.001136</v>
       </c>
       <c r="G319" s="1" t="n">
+        <v>0.001137</v>
+      </c>
+      <c r="H319" s="1" t="n">
         <v>0.001138</v>
       </c>
-      <c r="H319" s="1" t="n">
+      <c r="I319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -9397,9 +10357,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="G320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="H320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="H320" s="1" t="n">
+      <c r="I320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -9425,9 +10388,12 @@
         <v>0.00526</v>
       </c>
       <c r="G321" s="1" t="n">
-        <v>0.00526</v>
+        <v>0.00527</v>
       </c>
       <c r="H321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="I321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -9453,9 +10419,12 @@
         <v>0.1114</v>
       </c>
       <c r="G322" s="1" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="H322" s="1" t="n">
         <v>0.1116</v>
       </c>
-      <c r="H322" s="1" t="n">
+      <c r="I322" s="1" t="n">
         <v>0.1114</v>
       </c>
     </row>
@@ -9481,9 +10450,12 @@
         <v>0.04266</v>
       </c>
       <c r="G323" s="1" t="n">
-        <v>0.04266</v>
+        <v>0.04274</v>
       </c>
       <c r="H323" s="1" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="I323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -9512,6 +10484,9 @@
         <v>0.0179</v>
       </c>
       <c r="H324" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="I324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -9537,9 +10512,12 @@
         <v>0.005693</v>
       </c>
       <c r="G325" s="1" t="n">
-        <v>0.005695</v>
+        <v>0.005699</v>
       </c>
       <c r="H325" s="1" t="n">
+        <v>0.005699</v>
+      </c>
+      <c r="I325" s="1" t="n">
         <v>0.005689</v>
       </c>
     </row>
@@ -9565,9 +10543,12 @@
         <v>0.001765</v>
       </c>
       <c r="G326" s="1" t="n">
+        <v>0.001769</v>
+      </c>
+      <c r="H326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="H326" s="1" t="n">
+      <c r="I326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -9593,10 +10574,13 @@
         <v>0.04071</v>
       </c>
       <c r="G327" s="1" t="n">
+        <v>0.04069</v>
+      </c>
+      <c r="H327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="H327" s="1" t="n">
-        <v>0.04071</v>
+      <c r="I327" s="1" t="n">
+        <v>0.04069</v>
       </c>
     </row>
     <row r="328">
@@ -9621,10 +10605,13 @@
         <v>0.05398</v>
       </c>
       <c r="G328" s="1" t="n">
+        <v>0.053889</v>
+      </c>
+      <c r="H328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="H328" s="1" t="n">
-        <v>0.05395</v>
+      <c r="I328" s="1" t="n">
+        <v>0.053889</v>
       </c>
     </row>
     <row r="329">
@@ -9649,9 +10636,12 @@
         <v>0.2792</v>
       </c>
       <c r="G329" s="1" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="H329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="H329" s="1" t="n">
+      <c r="I329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -9680,6 +10670,9 @@
         <v>0.1601</v>
       </c>
       <c r="H330" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="I330" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -9705,9 +10698,12 @@
         <v>0.05358</v>
       </c>
       <c r="G331" s="1" t="n">
+        <v>0.05357</v>
+      </c>
+      <c r="H331" s="1" t="n">
         <v>0.05358</v>
       </c>
-      <c r="H331" s="1" t="n">
+      <c r="I331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -9733,9 +10729,12 @@
         <v>0.3601</v>
       </c>
       <c r="G332" s="1" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="H332" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="H332" s="1" t="n">
+      <c r="I332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -9761,9 +10760,12 @@
         <v>0.03043</v>
       </c>
       <c r="G333" s="1" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="H333" s="1" t="n">
         <v>0.03048</v>
       </c>
-      <c r="H333" s="1" t="n">
+      <c r="I333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -9789,9 +10791,12 @@
         <v>0.01804</v>
       </c>
       <c r="G334" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="H334" s="1" t="n">
         <v>0.01832</v>
       </c>
-      <c r="H334" s="1" t="n">
+      <c r="I334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -9817,9 +10822,12 @@
         <v>0.058</v>
       </c>
       <c r="G335" s="1" t="n">
-        <v>0.0581</v>
+        <v>0.0582</v>
       </c>
       <c r="H335" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="I335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -9845,9 +10853,12 @@
         <v>0.09171</v>
       </c>
       <c r="G336" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="H336" s="1" t="n">
         <v>0.09182</v>
       </c>
-      <c r="H336" s="1" t="n">
+      <c r="I336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -9873,9 +10884,12 @@
         <v>0.17762</v>
       </c>
       <c r="G337" s="1" t="n">
-        <v>0.1777</v>
+        <v>0.17938</v>
       </c>
       <c r="H337" s="1" t="n">
+        <v>0.17938</v>
+      </c>
+      <c r="I337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -9901,10 +10915,13 @@
         <v>0.02111</v>
       </c>
       <c r="G338" s="1" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="H338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="H338" s="1" t="n">
-        <v>0.02111</v>
+      <c r="I338" s="1" t="n">
+        <v>0.0211</v>
       </c>
     </row>
     <row r="339">
@@ -9929,9 +10946,12 @@
         <v>0.1313</v>
       </c>
       <c r="G339" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="H339" s="1" t="n">
         <v>0.1315</v>
       </c>
-      <c r="H339" s="1" t="n">
+      <c r="I339" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -9957,10 +10977,13 @@
         <v>0.008005999999999999</v>
       </c>
       <c r="G340" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="H340" s="1" t="n">
-        <v>0.008005999999999999</v>
+      <c r="I340" s="1" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="341">
@@ -9985,9 +11008,12 @@
         <v>4.399</v>
       </c>
       <c r="G341" s="1" t="n">
-        <v>4.403</v>
+        <v>4.407</v>
       </c>
       <c r="H341" s="1" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="I341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -10013,9 +11039,12 @@
         <v>0.19466</v>
       </c>
       <c r="G342" s="1" t="n">
+        <v>0.19329</v>
+      </c>
+      <c r="H342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="H342" s="1" t="n">
+      <c r="I342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -10044,6 +11073,9 @@
         <v>0.08325</v>
       </c>
       <c r="H343" s="1" t="n">
+        <v>0.08325</v>
+      </c>
+      <c r="I343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -10069,9 +11101,12 @@
         <v>0.1842</v>
       </c>
       <c r="G344" s="1" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="H344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="H344" s="1" t="n">
+      <c r="I344" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -10097,9 +11132,12 @@
         <v>0.003256</v>
       </c>
       <c r="G345" s="1" t="n">
+        <v>0.003256</v>
+      </c>
+      <c r="H345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="H345" s="1" t="n">
+      <c r="I345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -10125,9 +11163,12 @@
         <v>0.09168999999999999</v>
       </c>
       <c r="G346" s="1" t="n">
-        <v>0.09168999999999999</v>
+        <v>0.09204</v>
       </c>
       <c r="H346" s="1" t="n">
+        <v>0.09204</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -10153,10 +11194,13 @@
         <v>2.254</v>
       </c>
       <c r="G347" s="1" t="n">
+        <v>2.252</v>
+      </c>
+      <c r="H347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="H347" s="1" t="n">
-        <v>2.254</v>
+      <c r="I347" s="1" t="n">
+        <v>2.252</v>
       </c>
     </row>
     <row r="348">
@@ -10181,9 +11225,12 @@
         <v>0.3054</v>
       </c>
       <c r="G348" s="1" t="n">
-        <v>0.3054</v>
+        <v>0.3059</v>
       </c>
       <c r="H348" s="1" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="I348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -10212,6 +11259,9 @@
         <v>0.02991</v>
       </c>
       <c r="H349" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="I349" s="1" t="n">
         <v>0.02981</v>
       </c>
     </row>
@@ -10237,9 +11287,12 @@
         <v>0.128</v>
       </c>
       <c r="G350" s="1" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="H350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="H350" s="1" t="n">
+      <c r="I350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -10265,9 +11318,12 @@
         <v>0.06748999999999999</v>
       </c>
       <c r="G351" s="1" t="n">
+        <v>0.06729</v>
+      </c>
+      <c r="H351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="H351" s="1" t="n">
+      <c r="I351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -10293,9 +11349,12 @@
         <v>0.06244</v>
       </c>
       <c r="G352" s="1" t="n">
+        <v>0.06242</v>
+      </c>
+      <c r="H352" s="1" t="n">
         <v>0.06251</v>
       </c>
-      <c r="H352" s="1" t="n">
+      <c r="I352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -10321,10 +11380,13 @@
         <v>0.06371</v>
       </c>
       <c r="G353" s="1" t="n">
+        <v>0.06368</v>
+      </c>
+      <c r="H353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="H353" s="1" t="n">
-        <v>0.06371</v>
+      <c r="I353" s="1" t="n">
+        <v>0.06368</v>
       </c>
     </row>
     <row r="354">
@@ -10349,9 +11411,12 @@
         <v>0.10451</v>
       </c>
       <c r="G354" s="1" t="n">
+        <v>0.10509</v>
+      </c>
+      <c r="H354" s="1" t="n">
         <v>0.10569</v>
       </c>
-      <c r="H354" s="1" t="n">
+      <c r="I354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -10377,9 +11442,12 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="G355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="H355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="H355" s="1" t="n">
+      <c r="I355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -10405,9 +11473,12 @@
         <v>0.07003</v>
       </c>
       <c r="G356" s="1" t="n">
+        <v>0.07002</v>
+      </c>
+      <c r="H356" s="1" t="n">
         <v>0.07054000000000001</v>
       </c>
-      <c r="H356" s="1" t="n">
+      <c r="I356" s="1" t="n">
         <v>0.06988</v>
       </c>
     </row>
@@ -10433,9 +11504,12 @@
         <v>0.4539</v>
       </c>
       <c r="G357" s="1" t="n">
-        <v>0.4541</v>
+        <v>0.4544</v>
       </c>
       <c r="H357" s="1" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="I357" s="1" t="n">
         <v>0.4523</v>
       </c>
     </row>
@@ -10461,9 +11535,12 @@
         <v>0.03496</v>
       </c>
       <c r="G358" s="1" t="n">
+        <v>0.03491</v>
+      </c>
+      <c r="H358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="H358" s="1" t="n">
+      <c r="I358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -10489,9 +11566,12 @@
         <v>0.0148</v>
       </c>
       <c r="G359" s="1" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="H359" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="H359" s="1" t="n">
+      <c r="I359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -10517,9 +11597,12 @@
         <v>0.13305</v>
       </c>
       <c r="G360" s="1" t="n">
-        <v>0.13306</v>
+        <v>0.13376</v>
       </c>
       <c r="H360" s="1" t="n">
+        <v>0.13376</v>
+      </c>
+      <c r="I360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -10545,9 +11628,12 @@
         <v>0.0005883</v>
       </c>
       <c r="G361" s="1" t="n">
-        <v>0.0005885</v>
+        <v>0.0005913</v>
       </c>
       <c r="H361" s="1" t="n">
+        <v>0.0005913</v>
+      </c>
+      <c r="I361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -10573,9 +11659,12 @@
         <v>0.03882</v>
       </c>
       <c r="G362" s="1" t="n">
+        <v>0.03868</v>
+      </c>
+      <c r="H362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="H362" s="1" t="n">
+      <c r="I362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -10601,9 +11690,12 @@
         <v>3.207</v>
       </c>
       <c r="G363" s="1" t="n">
+        <v>3.212</v>
+      </c>
+      <c r="H363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="H363" s="1" t="n">
+      <c r="I363" s="1" t="n">
         <v>3.207</v>
       </c>
     </row>
@@ -10629,9 +11721,12 @@
         <v>0.1656</v>
       </c>
       <c r="G364" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="H364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="H364" s="1" t="n">
+      <c r="I364" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -10657,9 +11752,12 @@
         <v>0.1134</v>
       </c>
       <c r="G365" s="1" t="n">
-        <v>0.1135</v>
+        <v>0.1136</v>
       </c>
       <c r="H365" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="I365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -10685,9 +11783,12 @@
         <v>0.0006445</v>
       </c>
       <c r="G366" s="1" t="n">
+        <v>0.0006442</v>
+      </c>
+      <c r="H366" s="1" t="n">
         <v>0.0006445</v>
       </c>
-      <c r="H366" s="1" t="n">
+      <c r="I366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -10713,9 +11814,12 @@
         <v>0.05982</v>
       </c>
       <c r="G367" s="1" t="n">
+        <v>0.05962</v>
+      </c>
+      <c r="H367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="H367" s="1" t="n">
+      <c r="I367" s="1" t="n">
         <v>0.05956</v>
       </c>
     </row>
@@ -10741,9 +11845,12 @@
         <v>0.08345</v>
       </c>
       <c r="G368" s="1" t="n">
+        <v>0.08305</v>
+      </c>
+      <c r="H368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="H368" s="1" t="n">
+      <c r="I368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -10769,9 +11876,12 @@
         <v>0.03992</v>
       </c>
       <c r="G369" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="H369" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="H369" s="1" t="n">
+      <c r="I369" s="1" t="n">
         <v>0.03979</v>
       </c>
     </row>
@@ -10797,9 +11907,12 @@
         <v>3.722</v>
       </c>
       <c r="G370" s="1" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="H370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="H370" s="1" t="n">
+      <c r="I370" s="1" t="n">
         <v>3.709</v>
       </c>
     </row>
@@ -10825,9 +11938,12 @@
         <v>0.1222</v>
       </c>
       <c r="G371" s="1" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="H371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="H371" s="1" t="n">
+      <c r="I371" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -10856,6 +11972,9 @@
         <v>0.01479</v>
       </c>
       <c r="H372" s="1" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="I372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -10881,9 +12000,12 @@
         <v>0.02192</v>
       </c>
       <c r="G373" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="H373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="H373" s="1" t="n">
+      <c r="I373" s="1" t="n">
         <v>0.02192</v>
       </c>
     </row>
@@ -10909,9 +12031,12 @@
         <v>1.8579</v>
       </c>
       <c r="G374" s="1" t="n">
-        <v>1.8584</v>
+        <v>1.859</v>
       </c>
       <c r="H374" s="1" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="I374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -10937,9 +12062,12 @@
         <v>0.02104</v>
       </c>
       <c r="G375" s="1" t="n">
-        <v>0.02108</v>
+        <v>0.02112</v>
       </c>
       <c r="H375" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="I375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -10968,6 +12096,9 @@
         <v>1.301</v>
       </c>
       <c r="H376" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="I376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -10993,10 +12124,13 @@
         <v>0.2837</v>
       </c>
       <c r="G377" s="1" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="H377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="H377" s="1" t="n">
-        <v>0.2837</v>
+      <c r="I377" s="1" t="n">
+        <v>0.283</v>
       </c>
     </row>
     <row r="378">
@@ -11021,9 +12155,12 @@
         <v>0.01558</v>
       </c>
       <c r="G378" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="H378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="H378" s="1" t="n">
+      <c r="I378" s="1" t="n">
         <v>0.01558</v>
       </c>
     </row>
@@ -11049,9 +12186,12 @@
         <v>1.5387</v>
       </c>
       <c r="G379" s="1" t="n">
+        <v>1.5328</v>
+      </c>
+      <c r="H379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="H379" s="1" t="n">
+      <c r="I379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -11077,9 +12217,12 @@
         <v>6.955e-05</v>
       </c>
       <c r="G380" s="1" t="n">
+        <v>6.965e-05</v>
+      </c>
+      <c r="H380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="H380" s="1" t="n">
+      <c r="I380" s="1" t="n">
         <v>6.955e-05</v>
       </c>
     </row>
@@ -11105,9 +12248,12 @@
         <v>2.552</v>
       </c>
       <c r="G381" s="1" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="H381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="H381" s="1" t="n">
+      <c r="I381" s="1" t="n">
         <v>2.551</v>
       </c>
     </row>
@@ -11133,9 +12279,12 @@
         <v>0.06752</v>
       </c>
       <c r="G382" s="1" t="n">
-        <v>0.06753000000000001</v>
+        <v>0.06765</v>
       </c>
       <c r="H382" s="1" t="n">
+        <v>0.06765</v>
+      </c>
+      <c r="I382" s="1" t="n">
         <v>0.06738</v>
       </c>
     </row>
@@ -11161,9 +12310,12 @@
         <v>0.01723</v>
       </c>
       <c r="G383" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="H383" s="1" t="n">
         <v>0.01758</v>
       </c>
-      <c r="H383" s="1" t="n">
+      <c r="I383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -11192,6 +12344,9 @@
         <v>0.05086</v>
       </c>
       <c r="H384" s="1" t="n">
+        <v>0.05086</v>
+      </c>
+      <c r="I384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -11220,6 +12375,9 @@
         <v>7.585</v>
       </c>
       <c r="H385" s="1" t="n">
+        <v>7.585</v>
+      </c>
+      <c r="I385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -11248,6 +12406,9 @@
         <v>0.003299</v>
       </c>
       <c r="H386" s="1" t="n">
+        <v>0.003299</v>
+      </c>
+      <c r="I386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -11273,9 +12434,12 @@
         <v>0.0003845</v>
       </c>
       <c r="G387" s="1" t="n">
+        <v>0.0003843</v>
+      </c>
+      <c r="H387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="H387" s="1" t="n">
+      <c r="I387" s="1" t="n">
         <v>0.0003838</v>
       </c>
     </row>
@@ -11301,9 +12465,12 @@
         <v>0.00966</v>
       </c>
       <c r="G388" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="H388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="H388" s="1" t="n">
+      <c r="I388" s="1" t="n">
         <v>0.00966</v>
       </c>
     </row>
@@ -11329,9 +12496,12 @@
         <v>0.288</v>
       </c>
       <c r="G389" s="1" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="H389" s="1" t="n">
         <v>0.2891</v>
       </c>
-      <c r="H389" s="1" t="n">
+      <c r="I389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -11357,9 +12527,12 @@
         <v>0.0249</v>
       </c>
       <c r="G390" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="H390" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="H390" s="1" t="n">
+      <c r="I390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -11388,6 +12561,9 @@
         <v>2.832</v>
       </c>
       <c r="H391" s="1" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="I391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -11413,9 +12589,12 @@
         <v>0.0134</v>
       </c>
       <c r="G392" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="H392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="H392" s="1" t="n">
+      <c r="I392" s="1" t="n">
         <v>0.0134</v>
       </c>
     </row>
@@ -11441,9 +12620,12 @@
         <v>0.00236</v>
       </c>
       <c r="G393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="H393" s="1" t="n">
         <v>0.00236</v>
       </c>
-      <c r="H393" s="1" t="n">
+      <c r="I393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -11469,9 +12651,12 @@
         <v>0.05941</v>
       </c>
       <c r="G394" s="1" t="n">
+        <v>0.05939</v>
+      </c>
+      <c r="H394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="H394" s="1" t="n">
+      <c r="I394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -11497,11 +12682,14 @@
         <v>0.0405</v>
       </c>
       <c r="G395" s="1" t="n">
-        <v>0.0405</v>
+        <v>0.0404</v>
       </c>
       <c r="H395" s="1" t="n">
         <v>0.0405</v>
       </c>
+      <c r="I395" s="1" t="n">
+        <v>0.0404</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -11525,9 +12713,12 @@
         <v>0.09188</v>
       </c>
       <c r="G396" s="1" t="n">
+        <v>0.09182</v>
+      </c>
+      <c r="H396" s="1" t="n">
         <v>0.09188</v>
       </c>
-      <c r="H396" s="1" t="n">
+      <c r="I396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -11553,9 +12744,12 @@
         <v>0.1521</v>
       </c>
       <c r="G397" s="1" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="H397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="H397" s="1" t="n">
+      <c r="I397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -11581,9 +12775,12 @@
         <v>0.929</v>
       </c>
       <c r="G398" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="H398" s="1" t="n">
         <v>0.929</v>
       </c>
-      <c r="H398" s="1" t="n">
+      <c r="I398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -11609,9 +12806,12 @@
         <v>0.05245</v>
       </c>
       <c r="G399" s="1" t="n">
+        <v>0.05249</v>
+      </c>
+      <c r="H399" s="1" t="n">
         <v>0.0525</v>
       </c>
-      <c r="H399" s="1" t="n">
+      <c r="I399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -11637,9 +12837,12 @@
         <v>2.52</v>
       </c>
       <c r="G400" s="1" t="n">
-        <v>2.525</v>
+        <v>2.526</v>
       </c>
       <c r="H400" s="1" t="n">
+        <v>2.526</v>
+      </c>
+      <c r="I400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -11665,9 +12868,12 @@
         <v>0.01812</v>
       </c>
       <c r="G401" s="1" t="n">
+        <v>0.01802</v>
+      </c>
+      <c r="H401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="H401" s="1" t="n">
+      <c r="I401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -11693,9 +12899,12 @@
         <v>0.0809</v>
       </c>
       <c r="G402" s="1" t="n">
-        <v>0.08097</v>
+        <v>0.08111</v>
       </c>
       <c r="H402" s="1" t="n">
+        <v>0.08111</v>
+      </c>
+      <c r="I402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -11721,9 +12930,12 @@
         <v>1.2512</v>
       </c>
       <c r="G403" s="1" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="H403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="H403" s="1" t="n">
+      <c r="I403" s="1" t="n">
         <v>1.2484</v>
       </c>
     </row>
@@ -11749,9 +12961,12 @@
         <v>0.00719</v>
       </c>
       <c r="G404" s="1" t="n">
-        <v>0.00719</v>
+        <v>0.00721</v>
       </c>
       <c r="H404" s="1" t="n">
+        <v>0.00721</v>
+      </c>
+      <c r="I404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -11777,9 +12992,12 @@
         <v>0.4934</v>
       </c>
       <c r="G405" s="1" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="H405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="H405" s="1" t="n">
+      <c r="I405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -11805,9 +13023,12 @@
         <v>0.01149</v>
       </c>
       <c r="G406" s="1" t="n">
-        <v>0.01151</v>
+        <v>0.01152</v>
       </c>
       <c r="H406" s="1" t="n">
+        <v>0.01152</v>
+      </c>
+      <c r="I406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -11833,9 +13054,12 @@
         <v>0.04639</v>
       </c>
       <c r="G407" s="1" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="H407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="H407" s="1" t="n">
+      <c r="I407" s="1" t="n">
         <v>0.04639</v>
       </c>
     </row>
@@ -11861,9 +13085,12 @@
         <v>0.03958</v>
       </c>
       <c r="G408" s="1" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="H408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="H408" s="1" t="n">
+      <c r="I408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -11889,9 +13116,12 @@
         <v>0.05262</v>
       </c>
       <c r="G409" s="1" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="H409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="H409" s="1" t="n">
+      <c r="I409" s="1" t="n">
         <v>0.05262</v>
       </c>
     </row>
@@ -11917,10 +13147,13 @@
         <v>0.01252</v>
       </c>
       <c r="G410" s="1" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="H410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="H410" s="1" t="n">
-        <v>0.01247</v>
+      <c r="I410" s="1" t="n">
+        <v>0.01245</v>
       </c>
     </row>
     <row r="411">
@@ -11945,9 +13178,12 @@
         <v>0.06396</v>
       </c>
       <c r="G411" s="1" t="n">
-        <v>0.06401</v>
+        <v>0.06404</v>
       </c>
       <c r="H411" s="1" t="n">
+        <v>0.06404</v>
+      </c>
+      <c r="I411" s="1" t="n">
         <v>0.06378</v>
       </c>
     </row>
@@ -11973,9 +13209,12 @@
         <v>0.04126</v>
       </c>
       <c r="G412" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="H412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="H412" s="1" t="n">
+      <c r="I412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -12004,6 +13243,9 @@
         <v>1.122</v>
       </c>
       <c r="H413" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="I413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -12029,9 +13271,12 @@
         <v>0.2633</v>
       </c>
       <c r="G414" s="1" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="H414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="H414" s="1" t="n">
+      <c r="I414" s="1" t="n">
         <v>0.2633</v>
       </c>
     </row>
@@ -12057,9 +13302,12 @@
         <v>0.001238</v>
       </c>
       <c r="G415" s="1" t="n">
+        <v>0.001231</v>
+      </c>
+      <c r="H415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="H415" s="1" t="n">
+      <c r="I415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -12085,9 +13333,12 @@
         <v>0.03175</v>
       </c>
       <c r="G416" s="1" t="n">
+        <v>0.03193</v>
+      </c>
+      <c r="H416" s="1" t="n">
         <v>0.03196</v>
       </c>
-      <c r="H416" s="1" t="n">
+      <c r="I416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -12113,9 +13364,12 @@
         <v>0.01464</v>
       </c>
       <c r="G417" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="H417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="H417" s="1" t="n">
+      <c r="I417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -12141,9 +13395,12 @@
         <v>0.1481</v>
       </c>
       <c r="G418" s="1" t="n">
-        <v>0.1482</v>
+        <v>0.1483</v>
       </c>
       <c r="H418" s="1" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="I418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -12169,9 +13426,12 @@
         <v>0.04894</v>
       </c>
       <c r="G419" s="1" t="n">
-        <v>0.04894</v>
+        <v>0.04923</v>
       </c>
       <c r="H419" s="1" t="n">
+        <v>0.04923</v>
+      </c>
+      <c r="I419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -12197,9 +13457,12 @@
         <v>66.7</v>
       </c>
       <c r="G420" s="1" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="H420" s="1" t="n">
         <v>66.7</v>
       </c>
-      <c r="H420" s="1" t="n">
+      <c r="I420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -12228,6 +13491,9 @@
         <v>0.879</v>
       </c>
       <c r="H421" s="1" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="I421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -12253,9 +13519,12 @@
         <v>0.012813</v>
       </c>
       <c r="G422" s="1" t="n">
+        <v>0.01282</v>
+      </c>
+      <c r="H422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="H422" s="1" t="n">
+      <c r="I422" s="1" t="n">
         <v>0.012813</v>
       </c>
     </row>
@@ -12281,9 +13550,12 @@
         <v>0.01597</v>
       </c>
       <c r="G423" s="1" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="H423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="H423" s="1" t="n">
+      <c r="I423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -12309,9 +13581,12 @@
         <v>0.26855</v>
       </c>
       <c r="G424" s="1" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="H424" s="1" t="n">
         <v>0.26855</v>
       </c>
-      <c r="H424" s="1" t="n">
+      <c r="I424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -12337,9 +13612,12 @@
         <v>0.6019</v>
       </c>
       <c r="G425" s="1" t="n">
-        <v>0.6019</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H425" s="1" t="n">
+        <v>0.6022999999999999</v>
+      </c>
+      <c r="I425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -12365,10 +13643,13 @@
         <v>0.005577</v>
       </c>
       <c r="G426" s="1" t="n">
+        <v>0.005557</v>
+      </c>
+      <c r="H426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="H426" s="1" t="n">
-        <v>0.005577</v>
+      <c r="I426" s="1" t="n">
+        <v>0.005557</v>
       </c>
     </row>
     <row r="427">
@@ -12393,9 +13674,12 @@
         <v>0.04902</v>
       </c>
       <c r="G427" s="1" t="n">
+        <v>0.04902</v>
+      </c>
+      <c r="H427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="H427" s="1" t="n">
+      <c r="I427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -12421,9 +13705,12 @@
         <v>0.1264</v>
       </c>
       <c r="G428" s="1" t="n">
-        <v>0.1264</v>
+        <v>0.1265</v>
       </c>
       <c r="H428" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="I428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -12449,9 +13736,12 @@
         <v>0.003192</v>
       </c>
       <c r="G429" s="1" t="n">
+        <v>0.003192</v>
+      </c>
+      <c r="H429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="H429" s="1" t="n">
+      <c r="I429" s="1" t="n">
         <v>0.003192</v>
       </c>
     </row>
@@ -12477,9 +13767,12 @@
         <v>0.03652</v>
       </c>
       <c r="G430" s="1" t="n">
+        <v>0.03656</v>
+      </c>
+      <c r="H430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="H430" s="1" t="n">
+      <c r="I430" s="1" t="n">
         <v>0.03652</v>
       </c>
     </row>
@@ -12505,9 +13798,12 @@
         <v>0.4004</v>
       </c>
       <c r="G431" s="1" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="H431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="H431" s="1" t="n">
+      <c r="I431" s="1" t="n">
         <v>0.4004</v>
       </c>
     </row>
@@ -12533,10 +13829,13 @@
         <v>0.004543</v>
       </c>
       <c r="G432" s="1" t="n">
+        <v>0.004518</v>
+      </c>
+      <c r="H432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="H432" s="1" t="n">
-        <v>0.004519</v>
+      <c r="I432" s="1" t="n">
+        <v>0.004518</v>
       </c>
     </row>
     <row r="433">
@@ -12564,6 +13863,9 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="H433" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="I433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -12589,9 +13891,12 @@
         <v>0.0124</v>
       </c>
       <c r="G434" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="H434" s="1" t="n">
         <v>0.01244</v>
       </c>
-      <c r="H434" s="1" t="n">
+      <c r="I434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -12617,9 +13922,12 @@
         <v>1.981</v>
       </c>
       <c r="G435" s="1" t="n">
-        <v>1.981</v>
+        <v>1.983</v>
       </c>
       <c r="H435" s="1" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="I435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -12645,9 +13953,12 @@
         <v>0.00184</v>
       </c>
       <c r="G436" s="1" t="n">
-        <v>0.001848</v>
+        <v>0.001859</v>
       </c>
       <c r="H436" s="1" t="n">
+        <v>0.001859</v>
+      </c>
+      <c r="I436" s="1" t="n">
         <v>0.001833</v>
       </c>
     </row>
@@ -12673,9 +13984,12 @@
         <v>0.4426</v>
       </c>
       <c r="G437" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="H437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="H437" s="1" t="n">
+      <c r="I437" s="1" t="n">
         <v>0.4417</v>
       </c>
     </row>
@@ -12701,9 +14015,12 @@
         <v>0.00535</v>
       </c>
       <c r="G438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="H438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="H438" s="1" t="n">
+      <c r="I438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -12729,9 +14046,12 @@
         <v>0.1035</v>
       </c>
       <c r="G439" s="1" t="n">
-        <v>0.1035</v>
+        <v>0.1036</v>
       </c>
       <c r="H439" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="I439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -12757,9 +14077,12 @@
         <v>0.03418</v>
       </c>
       <c r="G440" s="1" t="n">
-        <v>0.03431</v>
+        <v>0.03432</v>
       </c>
       <c r="H440" s="1" t="n">
+        <v>0.03432</v>
+      </c>
+      <c r="I440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -12785,9 +14108,12 @@
         <v>0.08207</v>
       </c>
       <c r="G441" s="1" t="n">
-        <v>0.08215</v>
+        <v>0.08218</v>
       </c>
       <c r="H441" s="1" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="I441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -12813,9 +14139,12 @@
         <v>1.306</v>
       </c>
       <c r="G442" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="H442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="H442" s="1" t="n">
+      <c r="I442" s="1" t="n">
         <v>1.305</v>
       </c>
     </row>
@@ -12841,9 +14170,12 @@
         <v>0.07557</v>
       </c>
       <c r="G443" s="1" t="n">
+        <v>0.07565</v>
+      </c>
+      <c r="H443" s="1" t="n">
         <v>0.07573000000000001</v>
       </c>
-      <c r="H443" s="1" t="n">
+      <c r="I443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -12869,9 +14201,12 @@
         <v>0.07688</v>
       </c>
       <c r="G444" s="1" t="n">
-        <v>0.07692</v>
+        <v>0.07693</v>
       </c>
       <c r="H444" s="1" t="n">
+        <v>0.07693</v>
+      </c>
+      <c r="I444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -12897,9 +14232,12 @@
         <v>0.04373</v>
       </c>
       <c r="G445" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="H445" s="1" t="n">
         <v>0.04386</v>
       </c>
-      <c r="H445" s="1" t="n">
+      <c r="I445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -12925,9 +14263,12 @@
         <v>0.02153</v>
       </c>
       <c r="G446" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="H446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="H446" s="1" t="n">
+      <c r="I446" s="1" t="n">
         <v>0.02153</v>
       </c>
     </row>
@@ -12956,6 +14297,9 @@
         <v>0.2811</v>
       </c>
       <c r="H447" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="I447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -12981,9 +14325,12 @@
         <v>0.03109</v>
       </c>
       <c r="G448" s="1" t="n">
+        <v>0.03124</v>
+      </c>
+      <c r="H448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="H448" s="1" t="n">
+      <c r="I448" s="1" t="n">
         <v>0.03109</v>
       </c>
     </row>
@@ -13009,9 +14356,12 @@
         <v>0.00643</v>
       </c>
       <c r="G449" s="1" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="H449" s="1" t="n">
         <v>0.00646</v>
       </c>
-      <c r="H449" s="1" t="n">
+      <c r="I449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -13037,9 +14387,12 @@
         <v>0.022858</v>
       </c>
       <c r="G450" s="1" t="n">
+        <v>0.022865</v>
+      </c>
+      <c r="H450" s="1" t="n">
         <v>0.022996</v>
       </c>
-      <c r="H450" s="1" t="n">
+      <c r="I450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -13065,9 +14418,12 @@
         <v>0.04244</v>
       </c>
       <c r="G451" s="1" t="n">
-        <v>0.04244</v>
+        <v>0.04245</v>
       </c>
       <c r="H451" s="1" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="I451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -13093,9 +14449,12 @@
         <v>0.07231</v>
       </c>
       <c r="G452" s="1" t="n">
+        <v>0.07242</v>
+      </c>
+      <c r="H452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="H452" s="1" t="n">
+      <c r="I452" s="1" t="n">
         <v>0.07231</v>
       </c>
     </row>
@@ -13121,9 +14480,12 @@
         <v>0.0005934</v>
       </c>
       <c r="G453" s="1" t="n">
+        <v>0.0005928</v>
+      </c>
+      <c r="H453" s="1" t="n">
         <v>0.0005935</v>
       </c>
-      <c r="H453" s="1" t="n">
+      <c r="I453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -13152,6 +14514,9 @@
         <v>0.31</v>
       </c>
       <c r="H454" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -13177,9 +14542,12 @@
         <v>0.004253</v>
       </c>
       <c r="G455" s="1" t="n">
-        <v>0.004265</v>
+        <v>0.004275</v>
       </c>
       <c r="H455" s="1" t="n">
+        <v>0.004275</v>
+      </c>
+      <c r="I455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -13205,9 +14573,12 @@
         <v>0.1836</v>
       </c>
       <c r="G456" s="1" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="H456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="H456" s="1" t="n">
+      <c r="I456" s="1" t="n">
         <v>0.1835</v>
       </c>
     </row>
@@ -13233,9 +14604,12 @@
         <v>0.04279</v>
       </c>
       <c r="G457" s="1" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="H457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="H457" s="1" t="n">
+      <c r="I457" s="1" t="n">
         <v>0.04278</v>
       </c>
     </row>
@@ -13261,9 +14635,12 @@
         <v>0.1463</v>
       </c>
       <c r="G458" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="H458" s="1" t="n">
+      <c r="I458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -13289,9 +14666,12 @@
         <v>0.008611000000000001</v>
       </c>
       <c r="G459" s="1" t="n">
-        <v>0.008611000000000001</v>
+        <v>0.008616</v>
       </c>
       <c r="H459" s="1" t="n">
+        <v>0.008616</v>
+      </c>
+      <c r="I459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -13317,9 +14697,12 @@
         <v>0.007494</v>
       </c>
       <c r="G460" s="1" t="n">
+        <v>0.007477</v>
+      </c>
+      <c r="H460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="H460" s="1" t="n">
+      <c r="I460" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -13345,9 +14728,12 @@
         <v>0.000173</v>
       </c>
       <c r="G461" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="H461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="H461" s="1" t="n">
+      <c r="I461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -13373,9 +14759,12 @@
         <v>0.02265</v>
       </c>
       <c r="G462" s="1" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="H462" s="1" t="n">
         <v>0.02265</v>
       </c>
-      <c r="H462" s="1" t="n">
+      <c r="I462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -13401,9 +14790,12 @@
         <v>0.03772</v>
       </c>
       <c r="G463" s="1" t="n">
+        <v>0.03748</v>
+      </c>
+      <c r="H463" s="1" t="n">
         <v>0.03777</v>
       </c>
-      <c r="H463" s="1" t="n">
+      <c r="I463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -13429,9 +14821,12 @@
         <v>0.3038</v>
       </c>
       <c r="G464" s="1" t="n">
-        <v>0.3043</v>
+        <v>0.3046</v>
       </c>
       <c r="H464" s="1" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="I464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -13457,9 +14852,12 @@
         <v>0.03892</v>
       </c>
       <c r="G465" s="1" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="H465" s="1" t="n">
         <v>0.03923</v>
       </c>
-      <c r="H465" s="1" t="n">
+      <c r="I465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -13485,9 +14883,12 @@
         <v>2.683</v>
       </c>
       <c r="G466" s="1" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="H466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="H466" s="1" t="n">
+      <c r="I466" s="1" t="n">
         <v>2.682</v>
       </c>
     </row>
@@ -13513,9 +14914,12 @@
         <v>0.03418</v>
       </c>
       <c r="G467" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="H467" s="1" t="n">
         <v>0.03435</v>
       </c>
-      <c r="H467" s="1" t="n">
+      <c r="I467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -13541,9 +14945,12 @@
         <v>0.1758</v>
       </c>
       <c r="G468" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="H468" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="H468" s="1" t="n">
+      <c r="I468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -13569,9 +14976,12 @@
         <v>0.0956</v>
       </c>
       <c r="G469" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="H469" s="1" t="n">
         <v>0.0958</v>
       </c>
-      <c r="H469" s="1" t="n">
+      <c r="I469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -13597,10 +15007,13 @@
         <v>0.06748999999999999</v>
       </c>
       <c r="G470" s="1" t="n">
+        <v>0.06733</v>
+      </c>
+      <c r="H470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="H470" s="1" t="n">
-        <v>0.06745</v>
+      <c r="I470" s="1" t="n">
+        <v>0.06733</v>
       </c>
     </row>
     <row r="471">
@@ -13625,9 +15038,12 @@
         <v>0.03996</v>
       </c>
       <c r="G471" s="1" t="n">
-        <v>0.03998</v>
+        <v>0.04004</v>
       </c>
       <c r="H471" s="1" t="n">
+        <v>0.04004</v>
+      </c>
+      <c r="I471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -13653,9 +15069,12 @@
         <v>0.248</v>
       </c>
       <c r="G472" s="1" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="H472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="H472" s="1" t="n">
+      <c r="I472" s="1" t="n">
         <v>0.2475</v>
       </c>
     </row>
@@ -13681,9 +15100,12 @@
         <v>0.016552</v>
       </c>
       <c r="G473" s="1" t="n">
+        <v>0.016538</v>
+      </c>
+      <c r="H473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="H473" s="1" t="n">
+      <c r="I473" s="1" t="n">
         <v>0.016522</v>
       </c>
     </row>
@@ -13712,6 +15134,9 @@
         <v>0.1157</v>
       </c>
       <c r="H474" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="I474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -13737,9 +15162,12 @@
         <v>0.04281</v>
       </c>
       <c r="G475" s="1" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="H475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="H475" s="1" t="n">
+      <c r="I475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -13765,9 +15193,12 @@
         <v>0.2078</v>
       </c>
       <c r="G476" s="1" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="H476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="H476" s="1" t="n">
+      <c r="I476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -13793,9 +15224,12 @@
         <v>0.006798</v>
       </c>
       <c r="G477" s="1" t="n">
+        <v>0.006799</v>
+      </c>
+      <c r="H477" s="1" t="n">
         <v>0.006833</v>
       </c>
-      <c r="H477" s="1" t="n">
+      <c r="I477" s="1" t="n">
         <v>0.006798</v>
       </c>
     </row>
@@ -13821,9 +15255,12 @@
         <v>0.01809</v>
       </c>
       <c r="G478" s="1" t="n">
+        <v>0.01809</v>
+      </c>
+      <c r="H478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="H478" s="1" t="n">
+      <c r="I478" s="1" t="n">
         <v>0.01809</v>
       </c>
     </row>
@@ -13849,10 +15286,13 @@
         <v>0.04692</v>
       </c>
       <c r="G479" s="1" t="n">
+        <v>0.04691</v>
+      </c>
+      <c r="H479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="H479" s="1" t="n">
-        <v>0.04692</v>
+      <c r="I479" s="1" t="n">
+        <v>0.04691</v>
       </c>
     </row>
     <row r="480">
@@ -13877,9 +15317,12 @@
         <v>0.26147</v>
       </c>
       <c r="G480" s="1" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="H480" s="1" t="n">
         <v>0.26166</v>
       </c>
-      <c r="H480" s="1" t="n">
+      <c r="I480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -13905,9 +15348,12 @@
         <v>0.0124</v>
       </c>
       <c r="G481" s="1" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="H481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="H481" s="1" t="n">
+      <c r="I481" s="1" t="n">
         <v>0.01235</v>
       </c>
     </row>
@@ -13933,9 +15379,12 @@
         <v>0.004101</v>
       </c>
       <c r="G482" s="1" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="H482" s="1" t="n">
         <v>0.004101</v>
       </c>
-      <c r="H482" s="1" t="n">
+      <c r="I482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -13964,6 +15413,9 @@
         <v>0.1233</v>
       </c>
       <c r="H483" s="1" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="I483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -13989,9 +15441,12 @@
         <v>0.02209</v>
       </c>
       <c r="G484" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="H484" s="1" t="n">
+      <c r="I484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -14017,10 +15472,13 @@
         <v>0.0456</v>
       </c>
       <c r="G485" s="1" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="H485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="H485" s="1" t="n">
-        <v>0.0456</v>
+      <c r="I485" s="1" t="n">
+        <v>0.04548</v>
       </c>
     </row>
     <row r="486">
@@ -14048,6 +15506,9 @@
         <v>0.1736</v>
       </c>
       <c r="H486" s="1" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="I486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -14073,9 +15534,12 @@
         <v>0.2734</v>
       </c>
       <c r="G487" s="1" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="H487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="H487" s="1" t="n">
+      <c r="I487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -14101,9 +15565,12 @@
         <v>0.04611</v>
       </c>
       <c r="G488" s="1" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="H488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="H488" s="1" t="n">
+      <c r="I488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -14129,9 +15596,12 @@
         <v>0.0002159</v>
       </c>
       <c r="G489" s="1" t="n">
+        <v>0.0002157</v>
+      </c>
+      <c r="H489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="H489" s="1" t="n">
+      <c r="I489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -14157,9 +15627,12 @@
         <v>1.763</v>
       </c>
       <c r="G490" s="1" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="H490" s="1" t="n">
         <v>1.765</v>
       </c>
-      <c r="H490" s="1" t="n">
+      <c r="I490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -14185,9 +15658,12 @@
         <v>16.059</v>
       </c>
       <c r="G491" s="1" t="n">
+        <v>16.073</v>
+      </c>
+      <c r="H491" s="1" t="n">
         <v>16.083</v>
       </c>
-      <c r="H491" s="1" t="n">
+      <c r="I491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -14213,9 +15689,12 @@
         <v>0.06679</v>
       </c>
       <c r="G492" s="1" t="n">
-        <v>0.06680999999999999</v>
+        <v>0.06685000000000001</v>
       </c>
       <c r="H492" s="1" t="n">
+        <v>0.06685000000000001</v>
+      </c>
+      <c r="I492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -14241,9 +15720,12 @@
         <v>0.06756</v>
       </c>
       <c r="G493" s="1" t="n">
+        <v>0.06738</v>
+      </c>
+      <c r="H493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="H493" s="1" t="n">
+      <c r="I493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -14269,9 +15751,12 @@
         <v>0.009456000000000001</v>
       </c>
       <c r="G494" s="1" t="n">
-        <v>0.009456000000000001</v>
+        <v>0.009457999999999999</v>
       </c>
       <c r="H494" s="1" t="n">
+        <v>0.009457999999999999</v>
+      </c>
+      <c r="I494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -14297,10 +15782,13 @@
         <v>0.005939</v>
       </c>
       <c r="G495" s="1" t="n">
+        <v>0.005925</v>
+      </c>
+      <c r="H495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="H495" s="1" t="n">
-        <v>0.00593</v>
+      <c r="I495" s="1" t="n">
+        <v>0.005925</v>
       </c>
     </row>
     <row r="496">
@@ -14325,9 +15813,12 @@
         <v>0.00993</v>
       </c>
       <c r="G496" s="1" t="n">
+        <v>0.00993</v>
+      </c>
+      <c r="H496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="H496" s="1" t="n">
+      <c r="I496" s="1" t="n">
         <v>0.00992</v>
       </c>
     </row>
@@ -14353,9 +15844,12 @@
         <v>0.04396</v>
       </c>
       <c r="G497" s="1" t="n">
+        <v>0.04395</v>
+      </c>
+      <c r="H497" s="1" t="n">
         <v>0.04404</v>
       </c>
-      <c r="H497" s="1" t="n">
+      <c r="I497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -14381,9 +15875,12 @@
         <v>0.006402</v>
       </c>
       <c r="G498" s="1" t="n">
+        <v>0.006402</v>
+      </c>
+      <c r="H498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="H498" s="1" t="n">
+      <c r="I498" s="1" t="n">
         <v>0.006402</v>
       </c>
     </row>
@@ -14409,9 +15906,12 @@
         <v>0.01047</v>
       </c>
       <c r="G499" s="1" t="n">
-        <v>0.01048</v>
+        <v>0.01049</v>
       </c>
       <c r="H499" s="1" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="I499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -14437,9 +15937,12 @@
         <v>0.5134</v>
       </c>
       <c r="G500" s="1" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="H500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="H500" s="1" t="n">
+      <c r="I500" s="1" t="n">
         <v>0.5089</v>
       </c>
     </row>
@@ -14465,9 +15968,12 @@
         <v>0.03203</v>
       </c>
       <c r="G501" s="1" t="n">
+        <v>0.03204</v>
+      </c>
+      <c r="H501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="H501" s="1" t="n">
+      <c r="I501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -14493,9 +15999,12 @@
         <v>0.4385</v>
       </c>
       <c r="G502" s="1" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="H502" s="1" t="n">
         <v>0.4385</v>
       </c>
-      <c r="H502" s="1" t="n">
+      <c r="I502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -14521,9 +16030,12 @@
         <v>0.999342</v>
       </c>
       <c r="G503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="H503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="H503" s="1" t="n">
+      <c r="I503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -14549,9 +16061,12 @@
         <v>0.03554</v>
       </c>
       <c r="G504" s="1" t="n">
-        <v>0.03554</v>
+        <v>0.03555</v>
       </c>
       <c r="H504" s="1" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="I504" s="1" t="n">
         <v>0.03525</v>
       </c>
     </row>
@@ -14577,9 +16092,12 @@
         <v>0.004932</v>
       </c>
       <c r="G505" s="1" t="n">
+        <v>0.004931</v>
+      </c>
+      <c r="H505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="H505" s="1" t="n">
+      <c r="I505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -14605,9 +16123,12 @@
         <v>0.01393</v>
       </c>
       <c r="G506" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="H506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="H506" s="1" t="n">
+      <c r="I506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -14633,9 +16154,12 @@
         <v>0.003453</v>
       </c>
       <c r="G507" s="1" t="n">
+        <v>0.003466</v>
+      </c>
+      <c r="H507" s="1" t="n">
         <v>0.003478</v>
       </c>
-      <c r="H507" s="1" t="n">
+      <c r="I507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -14661,9 +16185,12 @@
         <v>1.42</v>
       </c>
       <c r="G508" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="H508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="H508" s="1" t="n">
+      <c r="I508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -14689,9 +16216,12 @@
         <v>0.005076</v>
       </c>
       <c r="G509" s="1" t="n">
+        <v>0.005077</v>
+      </c>
+      <c r="H509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="H509" s="1" t="n">
+      <c r="I509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -14717,9 +16247,12 @@
         <v>0.01573</v>
       </c>
       <c r="G510" s="1" t="n">
-        <v>0.01576</v>
+        <v>0.01577</v>
       </c>
       <c r="H510" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="I510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -14745,10 +16278,13 @@
         <v>0.08339000000000001</v>
       </c>
       <c r="G511" s="1" t="n">
+        <v>0.08244</v>
+      </c>
+      <c r="H511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="H511" s="1" t="n">
-        <v>0.08319</v>
+      <c r="I511" s="1" t="n">
+        <v>0.08244</v>
       </c>
     </row>
     <row r="512">
@@ -14773,9 +16309,12 @@
         <v>0.007117</v>
       </c>
       <c r="G512" s="1" t="n">
+        <v>0.007117</v>
+      </c>
+      <c r="H512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="H512" s="1" t="n">
+      <c r="I512" s="1" t="n">
         <v>0.007105</v>
       </c>
     </row>
@@ -14801,9 +16340,12 @@
         <v>0.01483</v>
       </c>
       <c r="G513" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="H513" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="H513" s="1" t="n">
+      <c r="I513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -14829,9 +16371,12 @@
         <v>0.04748</v>
       </c>
       <c r="G514" s="1" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="H514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="H514" s="1" t="n">
+      <c r="I514" s="1" t="n">
         <v>0.04748</v>
       </c>
     </row>
@@ -14857,9 +16402,12 @@
         <v>0.01818</v>
       </c>
       <c r="G515" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="H515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="H515" s="1" t="n">
+      <c r="I515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -14885,9 +16433,12 @@
         <v>0.0005806</v>
       </c>
       <c r="G516" s="1" t="n">
+        <v>0.0005807</v>
+      </c>
+      <c r="H516" s="1" t="n">
         <v>0.0005808</v>
       </c>
-      <c r="H516" s="1" t="n">
+      <c r="I516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -14913,9 +16464,12 @@
         <v>0.07886</v>
       </c>
       <c r="G517" s="1" t="n">
+        <v>0.07894</v>
+      </c>
+      <c r="H517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="H517" s="1" t="n">
+      <c r="I517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -14941,9 +16495,12 @@
         <v>0.006378</v>
       </c>
       <c r="G518" s="1" t="n">
+        <v>0.006387</v>
+      </c>
+      <c r="H518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="H518" s="1" t="n">
+      <c r="I518" s="1" t="n">
         <v>0.006378</v>
       </c>
     </row>
@@ -14969,9 +16526,12 @@
         <v>0.05813</v>
       </c>
       <c r="G519" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="H519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="H519" s="1" t="n">
+      <c r="I519" s="1" t="n">
         <v>0.05803</v>
       </c>
     </row>
@@ -14997,10 +16557,13 @@
         <v>0.10513</v>
       </c>
       <c r="G520" s="1" t="n">
+        <v>0.10495</v>
+      </c>
+      <c r="H520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="H520" s="1" t="n">
-        <v>0.10496</v>
+      <c r="I520" s="1" t="n">
+        <v>0.10495</v>
       </c>
     </row>
     <row r="521">
@@ -15028,6 +16591,9 @@
         <v>0.01799</v>
       </c>
       <c r="H521" s="1" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="I521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -15053,9 +16619,12 @@
         <v>0.01651</v>
       </c>
       <c r="G522" s="1" t="n">
+        <v>0.01652</v>
+      </c>
+      <c r="H522" s="1" t="n">
         <v>0.01653</v>
       </c>
-      <c r="H522" s="1" t="n">
+      <c r="I522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -15081,9 +16650,12 @@
         <v>0.01092</v>
       </c>
       <c r="G523" s="1" t="n">
-        <v>0.01092</v>
+        <v>0.01093</v>
       </c>
       <c r="H523" s="1" t="n">
+        <v>0.01093</v>
+      </c>
+      <c r="I523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -15109,9 +16681,12 @@
         <v>0.006993</v>
       </c>
       <c r="G524" s="1" t="n">
-        <v>0.006993</v>
+        <v>0.007138</v>
       </c>
       <c r="H524" s="1" t="n">
+        <v>0.007138</v>
+      </c>
+      <c r="I524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -15137,9 +16712,12 @@
         <v>0.005958</v>
       </c>
       <c r="G525" s="1" t="n">
+        <v>0.005946</v>
+      </c>
+      <c r="H525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="H525" s="1" t="n">
+      <c r="I525" s="1" t="n">
         <v>0.005938</v>
       </c>
     </row>
@@ -15165,9 +16743,12 @@
         <v>0.001444</v>
       </c>
       <c r="G526" s="1" t="n">
+        <v>0.001445</v>
+      </c>
+      <c r="H526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="H526" s="1" t="n">
+      <c r="I526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -15193,9 +16774,12 @@
         <v>0.372</v>
       </c>
       <c r="G527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="H527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="H527" s="1" t="n">
+      <c r="I527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -15221,9 +16805,12 @@
         <v>0.005207</v>
       </c>
       <c r="G528" s="1" t="n">
-        <v>0.005207</v>
+        <v>0.00521</v>
       </c>
       <c r="H528" s="1" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="I528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -15249,9 +16836,12 @@
         <v>2.936</v>
       </c>
       <c r="G529" s="1" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="H529" s="1" t="n">
         <v>2.942</v>
       </c>
-      <c r="H529" s="1" t="n">
+      <c r="I529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -15277,9 +16867,12 @@
         <v>0.1556</v>
       </c>
       <c r="G530" s="1" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="H530" s="1" t="n">
         <v>0.156</v>
       </c>
-      <c r="H530" s="1" t="n">
+      <c r="I530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -15305,9 +16898,12 @@
         <v>2531</v>
       </c>
       <c r="G531" s="1" t="n">
+        <v>2535</v>
+      </c>
+      <c r="H531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="H531" s="1" t="n">
+      <c r="I531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -15333,9 +16929,12 @@
         <v>0.03923</v>
       </c>
       <c r="G532" s="1" t="n">
-        <v>0.03928</v>
+        <v>0.03929</v>
       </c>
       <c r="H532" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="I532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -15361,9 +16960,12 @@
         <v>0.0219</v>
       </c>
       <c r="G533" s="1" t="n">
-        <v>0.0219</v>
+        <v>0.02191</v>
       </c>
       <c r="H533" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="I533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -15389,9 +16991,12 @@
         <v>0.07334</v>
       </c>
       <c r="G534" s="1" t="n">
-        <v>0.07334</v>
+        <v>0.07348</v>
       </c>
       <c r="H534" s="1" t="n">
+        <v>0.07348</v>
+      </c>
+      <c r="I534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -15417,9 +17022,12 @@
         <v>0.007842999999999999</v>
       </c>
       <c r="G535" s="1" t="n">
+        <v>0.007837999999999999</v>
+      </c>
+      <c r="H535" s="1" t="n">
         <v>0.007877</v>
       </c>
-      <c r="H535" s="1" t="n">
+      <c r="I535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -15445,9 +17053,12 @@
         <v>0.05029</v>
       </c>
       <c r="G536" s="1" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="H536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="H536" s="1" t="n">
+      <c r="I536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -15473,9 +17084,12 @@
         <v>0.00406</v>
       </c>
       <c r="G537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="H537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="H537" s="1" t="n">
+      <c r="I537" s="1" t="n">
         <v>0.00406</v>
       </c>
     </row>
@@ -15501,9 +17115,12 @@
         <v>0.08296000000000001</v>
       </c>
       <c r="G538" s="1" t="n">
+        <v>0.08305999999999999</v>
+      </c>
+      <c r="H538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="H538" s="1" t="n">
+      <c r="I538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -15529,9 +17146,12 @@
         <v>0.02485</v>
       </c>
       <c r="G539" s="1" t="n">
+        <v>0.02497</v>
+      </c>
+      <c r="H539" s="1" t="n">
         <v>0.02502</v>
       </c>
-      <c r="H539" s="1" t="n">
+      <c r="I539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -15557,9 +17177,12 @@
         <v>0.08498</v>
       </c>
       <c r="G540" s="1" t="n">
+        <v>0.08497</v>
+      </c>
+      <c r="H540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="H540" s="1" t="n">
+      <c r="I540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -15585,9 +17208,12 @@
         <v>0.01898</v>
       </c>
       <c r="G541" s="1" t="n">
+        <v>0.01897</v>
+      </c>
+      <c r="H541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="H541" s="1" t="n">
+      <c r="I541" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -15613,9 +17239,12 @@
         <v>0.01698</v>
       </c>
       <c r="G542" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="H542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="H542" s="1" t="n">
+      <c r="I542" s="1" t="n">
         <v>0.01698</v>
       </c>
     </row>
@@ -15644,6 +17273,9 @@
         <v>0.105</v>
       </c>
       <c r="H543" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M543"/>
+  <dimension ref="A1:N543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -430,8 +430,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,10 +493,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>price_02:45</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -538,9 +544,12 @@
         <v>70582.7</v>
       </c>
       <c r="L2" s="1" t="n">
+        <v>70614.8</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="N2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -581,9 +590,12 @@
         <v>2072.9</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>2074.69</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="N3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -624,9 +636,12 @@
         <v>86.87</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -667,9 +682,12 @@
         <v>4.048</v>
       </c>
       <c r="L5" s="1" t="n">
+        <v>4.037</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>4.02</v>
       </c>
     </row>
@@ -710,9 +728,12 @@
         <v>0.09444</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>0.09458999999999999</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -753,9 +774,12 @@
         <v>1.3894</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>1.3901</v>
+      </c>
+      <c r="M7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -796,9 +820,12 @@
         <v>22.518</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>22.652</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>22.688</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="N8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -839,9 +866,12 @@
         <v>0.001987</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>0.002046</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.001977</v>
       </c>
     </row>
@@ -882,9 +912,12 @@
         <v>0.010102</v>
       </c>
       <c r="L10" s="1" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="M10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -925,9 +958,12 @@
         <v>0.16059</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>0.15933</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.15789</v>
       </c>
     </row>
@@ -968,9 +1004,12 @@
         <v>0.011387</v>
       </c>
       <c r="L12" s="1" t="n">
+        <v>0.011602</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -1011,10 +1050,13 @@
         <v>37.817</v>
       </c>
       <c r="L13" s="1" t="n">
+        <v>37.812</v>
+      </c>
+      <c r="M13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>37.817</v>
+      <c r="N13" s="1" t="n">
+        <v>37.812</v>
       </c>
     </row>
     <row r="14">
@@ -1054,9 +1096,12 @@
         <v>652.41</v>
       </c>
       <c r="L14" s="1" t="n">
+        <v>653.09</v>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="N14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1097,9 +1142,12 @@
         <v>209.25</v>
       </c>
       <c r="L15" s="1" t="n">
+        <v>209.36</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="N15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1140,10 +1188,13 @@
         <v>0.0033227</v>
       </c>
       <c r="L16" s="1" t="n">
+        <v>0.0033224</v>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="M16" s="1" t="n">
-        <v>0.0033227</v>
+      <c r="N16" s="1" t="n">
+        <v>0.0033224</v>
       </c>
     </row>
     <row r="17">
@@ -1183,9 +1234,12 @@
         <v>239.55</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>238.81</v>
+      </c>
+      <c r="M17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="N17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1226,9 +1280,12 @@
         <v>0.989</v>
       </c>
       <c r="L18" s="1" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="N18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1269,9 +1326,12 @@
         <v>1.0541</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>1.0645</v>
+      </c>
+      <c r="M19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="N19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1312,9 +1372,12 @@
         <v>0.2592</v>
       </c>
       <c r="L20" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="M20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="N20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1355,9 +1418,12 @@
         <v>0.59476</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>0.5994</v>
+      </c>
+      <c r="M21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="N21" s="1" t="n">
         <v>0.59476</v>
       </c>
     </row>
@@ -1398,9 +1464,12 @@
         <v>9.002000000000001</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="M22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="N22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1441,9 +1510,12 @@
         <v>0.02413</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="M23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="N23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1484,9 +1556,12 @@
         <v>9.56</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>9.571999999999999</v>
+      </c>
+      <c r="M24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="N24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1527,9 +1602,12 @@
         <v>1.222</v>
       </c>
       <c r="L25" s="1" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="M25" s="1" t="n">
         <v>1.228</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="N25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1570,9 +1648,12 @@
         <v>0.07061000000000001</v>
       </c>
       <c r="L26" s="1" t="n">
+        <v>0.07113999999999999</v>
+      </c>
+      <c r="M26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="N26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1613,9 +1694,12 @@
         <v>1.423</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="N27" s="1" t="n">
         <v>1.423</v>
       </c>
     </row>
@@ -1656,9 +1740,12 @@
         <v>1.302</v>
       </c>
       <c r="L28" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="M28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="N28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -1699,9 +1786,12 @@
         <v>462.28</v>
       </c>
       <c r="L29" s="1" t="n">
+        <v>462.74</v>
+      </c>
+      <c r="M29" s="1" t="n">
         <v>463.21</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="N29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -1742,9 +1832,12 @@
         <v>1.2939</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.2939</v>
+        <v>1.2992</v>
       </c>
       <c r="M30" s="1" t="n">
+        <v>1.2992</v>
+      </c>
+      <c r="N30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1785,9 +1878,12 @@
         <v>5023.09</v>
       </c>
       <c r="L31" s="1" t="n">
+        <v>5023.85</v>
+      </c>
+      <c r="M31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="N31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1828,9 +1924,12 @@
         <v>0.876</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>0.877</v>
+        <v>0.903</v>
       </c>
       <c r="M32" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="N32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1871,9 +1970,12 @@
         <v>0.001974</v>
       </c>
       <c r="L33" s="1" t="n">
+        <v>0.001973</v>
+      </c>
+      <c r="M33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="N33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1914,9 +2016,12 @@
         <v>0.16845</v>
       </c>
       <c r="L34" s="1" t="n">
+        <v>0.16907</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>0.17106</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="N34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -1957,10 +2062,13 @@
         <v>0.29697</v>
       </c>
       <c r="L35" s="1" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="M35" s="1" t="n">
-        <v>0.29697</v>
+      <c r="N35" s="1" t="n">
+        <v>0.2967</v>
       </c>
     </row>
     <row r="36">
@@ -2000,9 +2108,12 @@
         <v>1.779</v>
       </c>
       <c r="L36" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="N36" s="1" t="n">
         <v>1.779</v>
       </c>
     </row>
@@ -2043,9 +2154,12 @@
         <v>110.27</v>
       </c>
       <c r="L37" s="1" t="n">
+        <v>110.42</v>
+      </c>
+      <c r="M37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="N37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -2086,9 +2200,12 @@
         <v>0.22314</v>
       </c>
       <c r="L38" s="1" t="n">
+        <v>0.22241</v>
+      </c>
+      <c r="M38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="N38" s="1" t="n">
         <v>0.22169</v>
       </c>
     </row>
@@ -2129,9 +2246,12 @@
         <v>0.1074</v>
       </c>
       <c r="L39" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="M39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="N39" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -2172,9 +2292,12 @@
         <v>0.37371</v>
       </c>
       <c r="L40" s="1" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="M40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="N40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2215,9 +2338,12 @@
         <v>54.6</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>54.66</v>
+        <v>54.7</v>
       </c>
       <c r="M41" s="1" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="N41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2258,9 +2384,12 @@
         <v>0.0010687</v>
       </c>
       <c r="L42" s="1" t="n">
+        <v>0.0010704</v>
+      </c>
+      <c r="M42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="N42" s="1" t="n">
         <v>0.0010666</v>
       </c>
     </row>
@@ -2301,10 +2430,13 @@
         <v>6.425</v>
       </c>
       <c r="L43" s="1" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="M43" s="1" t="n">
-        <v>6.414</v>
+      <c r="N43" s="1" t="n">
+        <v>6.41</v>
       </c>
     </row>
     <row r="44">
@@ -2344,9 +2476,12 @@
         <v>0.6343</v>
       </c>
       <c r="L44" s="1" t="n">
+        <v>0.6352</v>
+      </c>
+      <c r="M44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="N44" s="1" t="n">
         <v>0.6324</v>
       </c>
     </row>
@@ -2387,9 +2522,12 @@
         <v>0.3533</v>
       </c>
       <c r="L45" s="1" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="M45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="N45" s="1" t="n">
         <v>0.3533</v>
       </c>
     </row>
@@ -2430,9 +2568,12 @@
         <v>0.03266</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>0.03266</v>
+        <v>0.03294</v>
       </c>
       <c r="M46" s="1" t="n">
+        <v>0.03294</v>
+      </c>
+      <c r="N46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2473,9 +2614,12 @@
         <v>0.07179000000000001</v>
       </c>
       <c r="L47" s="1" t="n">
+        <v>0.07209</v>
+      </c>
+      <c r="M47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="N47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -2516,9 +2660,12 @@
         <v>0.7067</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>0.7068</v>
+        <v>0.7071</v>
       </c>
       <c r="M48" s="1" t="n">
+        <v>0.7071</v>
+      </c>
+      <c r="N48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -2559,9 +2706,12 @@
         <v>0.004374</v>
       </c>
       <c r="L49" s="1" t="n">
+        <v>0.004405</v>
+      </c>
+      <c r="M49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="N49" s="1" t="n">
         <v>0.004361</v>
       </c>
     </row>
@@ -2602,10 +2752,13 @@
         <v>0.104</v>
       </c>
       <c r="L50" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="M50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="M50" s="1" t="n">
-        <v>0.104</v>
+      <c r="N50" s="1" t="n">
+        <v>0.1037</v>
       </c>
     </row>
     <row r="51">
@@ -2645,9 +2798,12 @@
         <v>0.04069</v>
       </c>
       <c r="L51" s="1" t="n">
+        <v>0.04066</v>
+      </c>
+      <c r="M51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="N51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -2688,9 +2844,12 @@
         <v>0.1647</v>
       </c>
       <c r="L52" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="M52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="N52" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -2731,9 +2890,12 @@
         <v>0.02032</v>
       </c>
       <c r="L53" s="1" t="n">
+        <v>0.02016</v>
+      </c>
+      <c r="M53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="N53" s="1" t="n">
         <v>0.02003</v>
       </c>
     </row>
@@ -2774,9 +2936,12 @@
         <v>0.007199</v>
       </c>
       <c r="L54" s="1" t="n">
+        <v>0.007206</v>
+      </c>
+      <c r="M54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="N54" s="1" t="n">
         <v>0.007198</v>
       </c>
     </row>
@@ -2817,9 +2982,12 @@
         <v>3.911</v>
       </c>
       <c r="L55" s="1" t="n">
+        <v>3.916</v>
+      </c>
+      <c r="M55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="N55" s="1" t="n">
         <v>3.911</v>
       </c>
     </row>
@@ -2860,9 +3028,12 @@
         <v>0.017202</v>
       </c>
       <c r="L56" s="1" t="n">
+        <v>0.017192</v>
+      </c>
+      <c r="M56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="N56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -2903,9 +3074,12 @@
         <v>0.1095</v>
       </c>
       <c r="L57" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="M57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="N57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -2946,9 +3120,12 @@
         <v>2.647</v>
       </c>
       <c r="L58" s="1" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="M58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="N58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -2989,9 +3166,12 @@
         <v>0.1589</v>
       </c>
       <c r="L59" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="M59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="N59" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -3032,10 +3212,13 @@
         <v>0.005883</v>
       </c>
       <c r="L60" s="1" t="n">
+        <v>0.005882</v>
+      </c>
+      <c r="M60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="M60" s="1" t="n">
-        <v>0.005883</v>
+      <c r="N60" s="1" t="n">
+        <v>0.005882</v>
       </c>
     </row>
     <row r="61">
@@ -3075,9 +3258,12 @@
         <v>0.09193999999999999</v>
       </c>
       <c r="L61" s="1" t="n">
+        <v>0.09200999999999999</v>
+      </c>
+      <c r="M61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="N61" s="1" t="n">
         <v>0.09188</v>
       </c>
     </row>
@@ -3118,9 +3304,12 @@
         <v>0.9112</v>
       </c>
       <c r="L62" s="1" t="n">
+        <v>0.9127999999999999</v>
+      </c>
+      <c r="M62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="N62" s="1" t="n">
         <v>0.9112</v>
       </c>
     </row>
@@ -3161,9 +3350,12 @@
         <v>0.78</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="M63" s="1" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="N63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -3204,9 +3396,12 @@
         <v>0.04572</v>
       </c>
       <c r="L64" s="1" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="M64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="N64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -3247,9 +3442,12 @@
         <v>357.32</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>357.88</v>
+        <v>358.18</v>
       </c>
       <c r="M65" s="1" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="N65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -3290,9 +3488,12 @@
         <v>0.12444</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>0.12432</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="N66" s="1" t="n">
         <v>0.12419</v>
       </c>
     </row>
@@ -3333,10 +3534,13 @@
         <v>0.2317</v>
       </c>
       <c r="L67" s="1" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="M67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="M67" s="1" t="n">
-        <v>0.2317</v>
+      <c r="N67" s="1" t="n">
+        <v>0.2291</v>
       </c>
     </row>
     <row r="68">
@@ -3376,9 +3580,12 @@
         <v>0.00339</v>
       </c>
       <c r="L68" s="1" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="M68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="N68" s="1" t="n">
         <v>0.00339</v>
       </c>
     </row>
@@ -3419,10 +3626,13 @@
         <v>0.1738</v>
       </c>
       <c r="L69" s="1" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="M69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="M69" s="1" t="n">
-        <v>0.1738</v>
+      <c r="N69" s="1" t="n">
+        <v>0.1735</v>
       </c>
     </row>
     <row r="70">
@@ -3462,9 +3672,12 @@
         <v>0.16403</v>
       </c>
       <c r="L70" s="1" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="M70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="N70" s="1" t="n">
         <v>0.1639</v>
       </c>
     </row>
@@ -3505,9 +3718,12 @@
         <v>0.356</v>
       </c>
       <c r="L71" s="1" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="M71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="N71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -3548,9 +3764,12 @@
         <v>0.7096</v>
       </c>
       <c r="L72" s="1" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="M72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="N72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -3591,9 +3810,12 @@
         <v>0.00868</v>
       </c>
       <c r="L73" s="1" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="M73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="N73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -3634,9 +3856,12 @@
         <v>0.005967</v>
       </c>
       <c r="L74" s="1" t="n">
+        <v>0.005985</v>
+      </c>
+      <c r="M74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="N74" s="1" t="n">
         <v>0.005967</v>
       </c>
     </row>
@@ -3677,9 +3902,12 @@
         <v>0.227</v>
       </c>
       <c r="L75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="M75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="N75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -3720,9 +3948,12 @@
         <v>0.3229</v>
       </c>
       <c r="L76" s="1" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="M76" s="1" t="n">
         <v>0.3265</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="N76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -3763,9 +3994,12 @@
         <v>0.1002</v>
       </c>
       <c r="L77" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="M77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="N77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -3806,9 +4040,12 @@
         <v>0.1227</v>
       </c>
       <c r="L78" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="M78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="N78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -3849,9 +4086,12 @@
         <v>0.07129000000000001</v>
       </c>
       <c r="L79" s="1" t="n">
+        <v>0.07181999999999999</v>
+      </c>
+      <c r="M79" s="1" t="n">
         <v>0.07277</v>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="N79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -3892,9 +4132,12 @@
         <v>0.04705</v>
       </c>
       <c r="L80" s="1" t="n">
+        <v>0.04698</v>
+      </c>
+      <c r="M80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="N80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -3935,9 +4178,12 @@
         <v>0.000235</v>
       </c>
       <c r="L81" s="1" t="n">
+        <v>0.000236</v>
+      </c>
+      <c r="M81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="N81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -3978,9 +4224,12 @@
         <v>8.212999999999999</v>
       </c>
       <c r="L82" s="1" t="n">
+        <v>8.227</v>
+      </c>
+      <c r="M82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="N82" s="1" t="n">
         <v>8.206</v>
       </c>
     </row>
@@ -4021,10 +4270,13 @@
         <v>0.0005765</v>
       </c>
       <c r="L83" s="1" t="n">
+        <v>0.0005756</v>
+      </c>
+      <c r="M83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="M83" s="1" t="n">
-        <v>0.0005765</v>
+      <c r="N83" s="1" t="n">
+        <v>0.0005756</v>
       </c>
     </row>
     <row r="84">
@@ -4064,9 +4316,12 @@
         <v>0.4445</v>
       </c>
       <c r="L84" s="1" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="M84" s="1" t="n">
         <v>0.4457</v>
       </c>
-      <c r="M84" s="1" t="n">
+      <c r="N84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4107,9 +4362,12 @@
         <v>0.06242</v>
       </c>
       <c r="L85" s="1" t="n">
+        <v>0.06243</v>
+      </c>
+      <c r="M85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="N85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -4150,9 +4408,12 @@
         <v>0.05435</v>
       </c>
       <c r="L86" s="1" t="n">
+        <v>0.05456</v>
+      </c>
+      <c r="M86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="N86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -4193,9 +4454,12 @@
         <v>0.003334</v>
       </c>
       <c r="L87" s="1" t="n">
+        <v>0.003353</v>
+      </c>
+      <c r="M87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="N87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -4236,9 +4500,12 @@
         <v>0.05068</v>
       </c>
       <c r="L88" s="1" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="M88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="N88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -4279,9 +4546,12 @@
         <v>0.0305</v>
       </c>
       <c r="L89" s="1" t="n">
+        <v>0.03078</v>
+      </c>
+      <c r="M89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="N89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -4322,9 +4592,12 @@
         <v>0.3471</v>
       </c>
       <c r="L90" s="1" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="M90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="N90" s="1" t="n">
         <v>0.3471</v>
       </c>
     </row>
@@ -4365,9 +4638,12 @@
         <v>0.07622</v>
       </c>
       <c r="L91" s="1" t="n">
+        <v>0.07876</v>
+      </c>
+      <c r="M91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="N91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -4408,9 +4684,12 @@
         <v>0.3513</v>
       </c>
       <c r="L92" s="1" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="M92" s="1" t="n">
         <v>0.3551</v>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="N92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -4451,9 +4730,12 @@
         <v>1.9763</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>1.9779</v>
+        <v>1.9795</v>
       </c>
       <c r="M93" s="1" t="n">
+        <v>1.9795</v>
+      </c>
+      <c r="N93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -4494,9 +4776,12 @@
         <v>0.2586</v>
       </c>
       <c r="L94" s="1" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="M94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="N94" s="1" t="n">
         <v>0.2586</v>
       </c>
     </row>
@@ -4537,9 +4822,12 @@
         <v>0.0458</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>0.0458</v>
+        <v>0.04647</v>
       </c>
       <c r="M95" s="1" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="N95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -4580,9 +4868,12 @@
         <v>0.006186</v>
       </c>
       <c r="L96" s="1" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="M96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="N96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -4623,9 +4914,12 @@
         <v>0.001729</v>
       </c>
       <c r="L97" s="1" t="n">
+        <v>0.001732</v>
+      </c>
+      <c r="M97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="N97" s="1" t="n">
         <v>0.001729</v>
       </c>
     </row>
@@ -4666,9 +4960,12 @@
         <v>5.244</v>
       </c>
       <c r="L98" s="1" t="n">
+        <v>5.259</v>
+      </c>
+      <c r="M98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="N98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -4709,9 +5006,12 @@
         <v>0.01518</v>
       </c>
       <c r="L99" s="1" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="M99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="N99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -4752,9 +5052,12 @@
         <v>0.5531</v>
       </c>
       <c r="L100" s="1" t="n">
+        <v>0.5537</v>
+      </c>
+      <c r="M100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="N100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -4795,10 +5098,13 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="L101" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="M101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="M101" s="1" t="n">
-        <v>0.09089999999999999</v>
+      <c r="N101" s="1" t="n">
+        <v>0.0907</v>
       </c>
     </row>
     <row r="102">
@@ -4838,9 +5144,12 @@
         <v>32.45</v>
       </c>
       <c r="L102" s="1" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="M102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="N102" s="1" t="n">
         <v>32.42</v>
       </c>
     </row>
@@ -4881,9 +5190,12 @@
         <v>0.03147</v>
       </c>
       <c r="L103" s="1" t="n">
+        <v>0.03147</v>
+      </c>
+      <c r="M103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="N103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -4924,9 +5236,12 @@
         <v>0.06562999999999999</v>
       </c>
       <c r="L104" s="1" t="n">
+        <v>0.06568</v>
+      </c>
+      <c r="M104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="N104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -4967,9 +5282,12 @@
         <v>1.3045</v>
       </c>
       <c r="L105" s="1" t="n">
+        <v>1.3043</v>
+      </c>
+      <c r="M105" s="1" t="n">
         <v>1.3046</v>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="N105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -5010,9 +5328,12 @@
         <v>0.1205</v>
       </c>
       <c r="L106" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="M106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="N106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -5056,6 +5377,9 @@
         <v>0.121</v>
       </c>
       <c r="M107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="N107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -5096,9 +5420,12 @@
         <v>0.09583</v>
       </c>
       <c r="L108" s="1" t="n">
+        <v>0.09582</v>
+      </c>
+      <c r="M108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="N108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -5139,9 +5466,12 @@
         <v>0.13923</v>
       </c>
       <c r="L109" s="1" t="n">
+        <v>0.13964</v>
+      </c>
+      <c r="M109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="N109" s="1" t="n">
         <v>0.13853</v>
       </c>
     </row>
@@ -5182,9 +5512,12 @@
         <v>5.559</v>
       </c>
       <c r="L110" s="1" t="n">
+        <v>5.575</v>
+      </c>
+      <c r="M110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="N110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -5225,9 +5558,12 @@
         <v>1.099</v>
       </c>
       <c r="L111" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="M111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="M111" s="1" t="n">
+      <c r="N111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -5268,10 +5604,13 @@
         <v>0.029119</v>
       </c>
       <c r="L112" s="1" t="n">
+        <v>0.029053</v>
+      </c>
+      <c r="M112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="M112" s="1" t="n">
-        <v>0.029118</v>
+      <c r="N112" s="1" t="n">
+        <v>0.029053</v>
       </c>
     </row>
     <row r="113">
@@ -5311,10 +5650,13 @@
         <v>1.875</v>
       </c>
       <c r="L113" s="1" t="n">
+        <v>1.871</v>
+      </c>
+      <c r="M113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="M113" s="1" t="n">
-        <v>1.874</v>
+      <c r="N113" s="1" t="n">
+        <v>1.871</v>
       </c>
     </row>
     <row r="114">
@@ -5354,9 +5696,12 @@
         <v>0.05928</v>
       </c>
       <c r="L114" s="1" t="n">
+        <v>0.05932</v>
+      </c>
+      <c r="M114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="N114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -5397,9 +5742,12 @@
         <v>0.12885</v>
       </c>
       <c r="L115" s="1" t="n">
+        <v>0.12893</v>
+      </c>
+      <c r="M115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="N115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -5440,9 +5788,12 @@
         <v>1.1106</v>
       </c>
       <c r="L116" s="1" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="M116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="N116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -5483,9 +5834,12 @@
         <v>0.1543</v>
       </c>
       <c r="L117" s="1" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="M117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="N117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -5526,9 +5880,12 @@
         <v>0.1598</v>
       </c>
       <c r="L118" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="M118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="M118" s="1" t="n">
+      <c r="N118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -5569,9 +5926,12 @@
         <v>0.04747</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>0.04747</v>
+        <v>0.04766</v>
       </c>
       <c r="M119" s="1" t="n">
+        <v>0.04766</v>
+      </c>
+      <c r="N119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -5612,9 +5972,12 @@
         <v>3.021</v>
       </c>
       <c r="L120" s="1" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="M120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="N120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -5655,9 +6018,12 @@
         <v>0.2968</v>
       </c>
       <c r="L121" s="1" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="M121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="N121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -5698,9 +6064,12 @@
         <v>0.5837</v>
       </c>
       <c r="L122" s="1" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="M122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="M122" s="1" t="n">
+      <c r="N122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -5741,9 +6110,12 @@
         <v>0.01258</v>
       </c>
       <c r="L123" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="M123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="N123" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -5784,9 +6156,12 @@
         <v>0.1577</v>
       </c>
       <c r="L124" s="1" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="M124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="N124" s="1" t="n">
         <v>0.1577</v>
       </c>
     </row>
@@ -5827,9 +6202,12 @@
         <v>0.001782</v>
       </c>
       <c r="L125" s="1" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="M125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="N125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -5870,9 +6248,12 @@
         <v>0.0004862</v>
       </c>
       <c r="L126" s="1" t="n">
+        <v>0.0004865</v>
+      </c>
+      <c r="M126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="M126" s="1" t="n">
+      <c r="N126" s="1" t="n">
         <v>0.0004859</v>
       </c>
     </row>
@@ -5913,9 +6294,12 @@
         <v>0.02938</v>
       </c>
       <c r="L127" s="1" t="n">
+        <v>0.02939</v>
+      </c>
+      <c r="M127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="M127" s="1" t="n">
+      <c r="N127" s="1" t="n">
         <v>0.02938</v>
       </c>
     </row>
@@ -5956,9 +6340,12 @@
         <v>0.04132</v>
       </c>
       <c r="L128" s="1" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="M128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="N128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -5999,9 +6386,12 @@
         <v>0.04837</v>
       </c>
       <c r="L129" s="1" t="n">
+        <v>0.04848</v>
+      </c>
+      <c r="M129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="M129" s="1" t="n">
+      <c r="N129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -6042,9 +6432,12 @@
         <v>1.25e-05</v>
       </c>
       <c r="L130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="M130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="N130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -6085,9 +6478,12 @@
         <v>6.9e-06</v>
       </c>
       <c r="L131" s="1" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="M131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="N131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -6128,9 +6524,12 @@
         <v>0.007</v>
       </c>
       <c r="L132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="M132" s="1" t="n">
+      <c r="N132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -6174,6 +6573,9 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="M133" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="N133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -6214,9 +6616,12 @@
         <v>0.0004093</v>
       </c>
       <c r="L134" s="1" t="n">
+        <v>0.0004094</v>
+      </c>
+      <c r="M134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="N134" s="1" t="n">
         <v>0.0004093</v>
       </c>
     </row>
@@ -6257,9 +6662,12 @@
         <v>0.08334</v>
       </c>
       <c r="L135" s="1" t="n">
+        <v>0.08351</v>
+      </c>
+      <c r="M135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="N135" s="1" t="n">
         <v>0.08334</v>
       </c>
     </row>
@@ -6300,10 +6708,13 @@
         <v>0.007913</v>
       </c>
       <c r="L136" s="1" t="n">
+        <v>0.007868999999999999</v>
+      </c>
+      <c r="M136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="M136" s="1" t="n">
-        <v>0.007891</v>
+      <c r="N136" s="1" t="n">
+        <v>0.007868999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -6343,9 +6754,12 @@
         <v>0.0008192</v>
       </c>
       <c r="L137" s="1" t="n">
+        <v>0.0008168</v>
+      </c>
+      <c r="M137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="N137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -6386,9 +6800,12 @@
         <v>0.1468</v>
       </c>
       <c r="L138" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="M138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="N138" s="1" t="n">
         <v>0.1468</v>
       </c>
     </row>
@@ -6429,10 +6846,13 @@
         <v>0.006719</v>
       </c>
       <c r="L139" s="1" t="n">
+        <v>0.006712</v>
+      </c>
+      <c r="M139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="M139" s="1" t="n">
-        <v>0.006714</v>
+      <c r="N139" s="1" t="n">
+        <v>0.006712</v>
       </c>
     </row>
     <row r="140">
@@ -6472,9 +6892,12 @@
         <v>0.01392</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>0.01392</v>
+        <v>0.01393</v>
       </c>
       <c r="M140" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="N140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -6515,9 +6938,12 @@
         <v>0.09766</v>
       </c>
       <c r="L141" s="1" t="n">
+        <v>0.09766</v>
+      </c>
+      <c r="M141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="M141" s="1" t="n">
+      <c r="N141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -6558,9 +6984,12 @@
         <v>0.0542</v>
       </c>
       <c r="L142" s="1" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="M142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="N142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -6601,10 +7030,13 @@
         <v>0.324</v>
       </c>
       <c r="L143" s="1" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="M143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="M143" s="1" t="n">
-        <v>0.3237</v>
+      <c r="N143" s="1" t="n">
+        <v>0.3233</v>
       </c>
     </row>
     <row r="144">
@@ -6644,10 +7076,13 @@
         <v>0.02581</v>
       </c>
       <c r="L144" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="M144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="M144" s="1" t="n">
-        <v>0.02572</v>
+      <c r="N144" s="1" t="n">
+        <v>0.0257</v>
       </c>
     </row>
     <row r="145">
@@ -6687,10 +7122,13 @@
         <v>0.238</v>
       </c>
       <c r="L145" s="1" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="M145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="M145" s="1" t="n">
-        <v>0.2377</v>
+      <c r="N145" s="1" t="n">
+        <v>0.2375</v>
       </c>
     </row>
     <row r="146">
@@ -6730,9 +7168,12 @@
         <v>0.006989</v>
       </c>
       <c r="L146" s="1" t="n">
+        <v>0.006994</v>
+      </c>
+      <c r="M146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="N146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -6773,9 +7214,12 @@
         <v>0.08723</v>
       </c>
       <c r="L147" s="1" t="n">
+        <v>0.08692</v>
+      </c>
+      <c r="M147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="N147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -6816,9 +7260,12 @@
         <v>0.05203</v>
       </c>
       <c r="L148" s="1" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="M148" s="1" t="n">
         <v>0.05217</v>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="N148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -6859,10 +7306,13 @@
         <v>0.02383</v>
       </c>
       <c r="L149" s="1" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="M149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="M149" s="1" t="n">
-        <v>0.02381</v>
+      <c r="N149" s="1" t="n">
+        <v>0.02379</v>
       </c>
     </row>
     <row r="150">
@@ -6902,9 +7352,12 @@
         <v>0.08563</v>
       </c>
       <c r="L150" s="1" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="M150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="M150" s="1" t="n">
+      <c r="N150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -6945,9 +7398,12 @@
         <v>0.02329</v>
       </c>
       <c r="L151" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="M151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="N151" s="1" t="n">
         <v>0.0232</v>
       </c>
     </row>
@@ -6988,9 +7444,12 @@
         <v>0.02552</v>
       </c>
       <c r="L152" s="1" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="M152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="N152" s="1" t="n">
         <v>0.02552</v>
       </c>
     </row>
@@ -7031,9 +7490,12 @@
         <v>0.0002152</v>
       </c>
       <c r="L153" s="1" t="n">
+        <v>0.0002165</v>
+      </c>
+      <c r="M153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="N153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -7074,9 +7536,12 @@
         <v>0.4407</v>
       </c>
       <c r="L154" s="1" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="M154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="N154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -7117,9 +7582,12 @@
         <v>0.06673</v>
       </c>
       <c r="L155" s="1" t="n">
+        <v>0.06716</v>
+      </c>
+      <c r="M155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="M155" s="1" t="n">
+      <c r="N155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -7160,9 +7628,12 @@
         <v>0.1282</v>
       </c>
       <c r="L156" s="1" t="n">
+        <v>0.12838</v>
+      </c>
+      <c r="M156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="M156" s="1" t="n">
+      <c r="N156" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -7203,9 +7674,12 @@
         <v>0.4839</v>
       </c>
       <c r="L157" s="1" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="M157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="M157" s="1" t="n">
+      <c r="N157" s="1" t="n">
         <v>0.4839</v>
       </c>
     </row>
@@ -7246,9 +7720,12 @@
         <v>0.4481</v>
       </c>
       <c r="L158" s="1" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="M158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="M158" s="1" t="n">
+      <c r="N158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -7289,9 +7766,12 @@
         <v>0.007501</v>
       </c>
       <c r="L159" s="1" t="n">
+        <v>0.007498</v>
+      </c>
+      <c r="M159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="M159" s="1" t="n">
+      <c r="N159" s="1" t="n">
         <v>0.007493</v>
       </c>
     </row>
@@ -7332,9 +7812,12 @@
         <v>0.004699</v>
       </c>
       <c r="L160" s="1" t="n">
+        <v>0.004687</v>
+      </c>
+      <c r="M160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="N160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -7375,9 +7858,12 @@
         <v>0.004294</v>
       </c>
       <c r="L161" s="1" t="n">
+        <v>0.004296</v>
+      </c>
+      <c r="M161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="M161" s="1" t="n">
+      <c r="N161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -7418,9 +7904,12 @@
         <v>0.0958</v>
       </c>
       <c r="L162" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="M162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="N162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -7461,9 +7950,12 @@
         <v>0.2858</v>
       </c>
       <c r="L163" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="M163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="M163" s="1" t="n">
+      <c r="N163" s="1" t="n">
         <v>0.2852</v>
       </c>
     </row>
@@ -7504,9 +7996,12 @@
         <v>0.1143</v>
       </c>
       <c r="L164" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="M164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="N164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -7547,9 +8042,12 @@
         <v>0.1753</v>
       </c>
       <c r="L165" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="M165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="M165" s="1" t="n">
+      <c r="N165" s="1" t="n">
         <v>0.1753</v>
       </c>
     </row>
@@ -7590,9 +8088,12 @@
         <v>0.01011</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>0.01011</v>
+        <v>0.01014</v>
       </c>
       <c r="M166" s="1" t="n">
+        <v>0.01014</v>
+      </c>
+      <c r="N166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -7633,9 +8134,12 @@
         <v>1.827</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>1.837</v>
+        <v>1.842</v>
       </c>
       <c r="M167" s="1" t="n">
+        <v>1.842</v>
+      </c>
+      <c r="N167" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -7676,9 +8180,12 @@
         <v>1.333</v>
       </c>
       <c r="L168" s="1" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="M168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="M168" s="1" t="n">
+      <c r="N168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -7719,9 +8226,12 @@
         <v>0.007313</v>
       </c>
       <c r="L169" s="1" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="M169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="N169" s="1" t="n">
         <v>0.007304</v>
       </c>
     </row>
@@ -7762,9 +8272,12 @@
         <v>0.0116</v>
       </c>
       <c r="L170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="M170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="M170" s="1" t="n">
+      <c r="N170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -7805,9 +8318,12 @@
         <v>0.005794</v>
       </c>
       <c r="L171" s="1" t="n">
+        <v>0.005805</v>
+      </c>
+      <c r="M171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="M171" s="1" t="n">
+      <c r="N171" s="1" t="n">
         <v>0.005794</v>
       </c>
     </row>
@@ -7848,9 +8364,12 @@
         <v>0.14718</v>
       </c>
       <c r="L172" s="1" t="n">
+        <v>0.14738</v>
+      </c>
+      <c r="M172" s="1" t="n">
         <v>0.14806</v>
       </c>
-      <c r="M172" s="1" t="n">
+      <c r="N172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -7891,9 +8410,12 @@
         <v>4.873</v>
       </c>
       <c r="L173" s="1" t="n">
+        <v>4.887</v>
+      </c>
+      <c r="M173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="M173" s="1" t="n">
+      <c r="N173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -7934,9 +8456,12 @@
         <v>0.0784</v>
       </c>
       <c r="L174" s="1" t="n">
+        <v>0.07844</v>
+      </c>
+      <c r="M174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="N174" s="1" t="n">
         <v>0.0784</v>
       </c>
     </row>
@@ -7977,10 +8502,13 @@
         <v>0.007464</v>
       </c>
       <c r="L175" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="M175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="M175" s="1" t="n">
-        <v>0.007464</v>
+      <c r="N175" s="1" t="n">
+        <v>0.00745</v>
       </c>
     </row>
     <row r="176">
@@ -8020,9 +8548,12 @@
         <v>0.2011</v>
       </c>
       <c r="L176" s="1" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="M176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="N176" s="1" t="n">
         <v>0.2011</v>
       </c>
     </row>
@@ -8063,9 +8594,12 @@
         <v>0.05183</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>0.0519</v>
+        <v>0.05196</v>
       </c>
       <c r="M177" s="1" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="N177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -8106,9 +8640,12 @@
         <v>0.05473</v>
       </c>
       <c r="L178" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="M178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="M178" s="1" t="n">
+      <c r="N178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -8149,9 +8686,12 @@
         <v>0.02326</v>
       </c>
       <c r="L179" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="M179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="M179" s="1" t="n">
+      <c r="N179" s="1" t="n">
         <v>0.02321</v>
       </c>
     </row>
@@ -8192,9 +8732,12 @@
         <v>0.6944</v>
       </c>
       <c r="L180" s="1" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="M180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="M180" s="1" t="n">
+      <c r="N180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -8235,9 +8778,12 @@
         <v>0.0003743</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>0.0003743</v>
+        <v>0.0003744</v>
       </c>
       <c r="M181" s="1" t="n">
+        <v>0.0003744</v>
+      </c>
+      <c r="N181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -8278,9 +8824,12 @@
         <v>0.01256</v>
       </c>
       <c r="L182" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="M182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="N182" s="1" t="n">
         <v>0.01256</v>
       </c>
     </row>
@@ -8321,9 +8870,12 @@
         <v>4.23</v>
       </c>
       <c r="L183" s="1" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="M183" s="1" t="n">
+      <c r="N183" s="1" t="n">
         <v>4.23</v>
       </c>
     </row>
@@ -8364,9 +8916,12 @@
         <v>0.2368</v>
       </c>
       <c r="L184" s="1" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="M184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="M184" s="1" t="n">
+      <c r="N184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -8407,9 +8962,12 @@
         <v>0.03694</v>
       </c>
       <c r="L185" s="1" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="M185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="M185" s="1" t="n">
+      <c r="N185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -8450,9 +9008,12 @@
         <v>0.11614</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>0.11628</v>
+        <v>0.11632</v>
       </c>
       <c r="M186" s="1" t="n">
+        <v>0.11632</v>
+      </c>
+      <c r="N186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -8493,9 +9054,12 @@
         <v>0.009063</v>
       </c>
       <c r="L187" s="1" t="n">
+        <v>0.009117999999999999</v>
+      </c>
+      <c r="M187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="N187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -8536,9 +9100,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="L188" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="M188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="M188" s="1" t="n">
+      <c r="N188" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -8579,9 +9146,12 @@
         <v>0.02767</v>
       </c>
       <c r="L189" s="1" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="M189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="M189" s="1" t="n">
+      <c r="N189" s="1" t="n">
         <v>0.02767</v>
       </c>
     </row>
@@ -8622,10 +9192,13 @@
         <v>0.00874</v>
       </c>
       <c r="L190" s="1" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="M190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="M190" s="1" t="n">
-        <v>0.008699999999999999</v>
+      <c r="N190" s="1" t="n">
+        <v>0.00864</v>
       </c>
     </row>
     <row r="191">
@@ -8665,9 +9238,12 @@
         <v>0.00195</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>0.001956</v>
+        <v>0.001959</v>
       </c>
       <c r="M191" s="1" t="n">
+        <v>0.001959</v>
+      </c>
+      <c r="N191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -8708,9 +9284,12 @@
         <v>0.1007</v>
       </c>
       <c r="L192" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="M192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="M192" s="1" t="n">
+      <c r="N192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -8751,9 +9330,12 @@
         <v>0.02336</v>
       </c>
       <c r="L193" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="M193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="M193" s="1" t="n">
+      <c r="N193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -8794,9 +9376,12 @@
         <v>0.01348</v>
       </c>
       <c r="L194" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="M194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="M194" s="1" t="n">
+      <c r="N194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -8837,9 +9422,12 @@
         <v>0.02089</v>
       </c>
       <c r="L195" s="1" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="M195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="M195" s="1" t="n">
+      <c r="N195" s="1" t="n">
         <v>0.02089</v>
       </c>
     </row>
@@ -8880,9 +9468,12 @@
         <v>0.17201</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>0.17484</v>
+        <v>0.17509</v>
       </c>
       <c r="M196" s="1" t="n">
+        <v>0.17509</v>
+      </c>
+      <c r="N196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -8923,9 +9514,12 @@
         <v>0.007345</v>
       </c>
       <c r="L197" s="1" t="n">
+        <v>0.007352</v>
+      </c>
+      <c r="M197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="M197" s="1" t="n">
+      <c r="N197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -8966,9 +9560,12 @@
         <v>0.01906</v>
       </c>
       <c r="L198" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="M198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="M198" s="1" t="n">
+      <c r="N198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -9009,9 +9606,12 @@
         <v>0.01728</v>
       </c>
       <c r="L199" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="M199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="M199" s="1" t="n">
+      <c r="N199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -9052,9 +9652,12 @@
         <v>0.2974</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>0.2979</v>
+        <v>0.298</v>
       </c>
       <c r="M200" s="1" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="N200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -9095,9 +9698,12 @@
         <v>0.006242</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>0.006242</v>
+        <v>0.006258</v>
       </c>
       <c r="M201" s="1" t="n">
+        <v>0.006258</v>
+      </c>
+      <c r="N201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -9138,10 +9744,13 @@
         <v>0.0004435</v>
       </c>
       <c r="L202" s="1" t="n">
+        <v>0.0004433</v>
+      </c>
+      <c r="M202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="M202" s="1" t="n">
-        <v>0.0004435</v>
+      <c r="N202" s="1" t="n">
+        <v>0.0004433</v>
       </c>
     </row>
     <row r="203">
@@ -9181,10 +9790,13 @@
         <v>0.007302</v>
       </c>
       <c r="L203" s="1" t="n">
+        <v>0.007273</v>
+      </c>
+      <c r="M203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="M203" s="1" t="n">
-        <v>0.007302</v>
+      <c r="N203" s="1" t="n">
+        <v>0.007273</v>
       </c>
     </row>
     <row r="204">
@@ -9224,9 +9836,12 @@
         <v>0.1308</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>0.1314</v>
+        <v>0.1317</v>
       </c>
       <c r="M204" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="N204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -9267,9 +9882,12 @@
         <v>0.01417</v>
       </c>
       <c r="L205" s="1" t="n">
+        <v>0.01427</v>
+      </c>
+      <c r="M205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="M205" s="1" t="n">
+      <c r="N205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -9310,9 +9928,12 @@
         <v>0.003591</v>
       </c>
       <c r="L206" s="1" t="n">
+        <v>0.00359</v>
+      </c>
+      <c r="M206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="M206" s="1" t="n">
+      <c r="N206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -9353,9 +9974,12 @@
         <v>0.05992</v>
       </c>
       <c r="L207" s="1" t="n">
+        <v>0.05998</v>
+      </c>
+      <c r="M207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="M207" s="1" t="n">
+      <c r="N207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -9396,9 +10020,12 @@
         <v>15.55</v>
       </c>
       <c r="L208" s="1" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="M208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="M208" s="1" t="n">
+      <c r="N208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -9439,9 +10066,12 @@
         <v>5192.8</v>
       </c>
       <c r="L209" s="1" t="n">
+        <v>5191.6</v>
+      </c>
+      <c r="M209" s="1" t="n">
         <v>5192.8</v>
       </c>
-      <c r="M209" s="1" t="n">
+      <c r="N209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -9482,9 +10112,12 @@
         <v>0.12065</v>
       </c>
       <c r="L210" s="1" t="n">
+        <v>0.12027</v>
+      </c>
+      <c r="M210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="M210" s="1" t="n">
+      <c r="N210" s="1" t="n">
         <v>0.11963</v>
       </c>
     </row>
@@ -9525,9 +10158,12 @@
         <v>0.1815</v>
       </c>
       <c r="L211" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="M211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="M211" s="1" t="n">
+      <c r="N211" s="1" t="n">
         <v>0.1815</v>
       </c>
     </row>
@@ -9568,9 +10204,12 @@
         <v>0.0308</v>
       </c>
       <c r="L212" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="M212" s="1" t="n">
         <v>0.0308</v>
       </c>
-      <c r="M212" s="1" t="n">
+      <c r="N212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -9611,9 +10250,12 @@
         <v>1.3947</v>
       </c>
       <c r="L213" s="1" t="n">
+        <v>1.3973</v>
+      </c>
+      <c r="M213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="M213" s="1" t="n">
+      <c r="N213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -9654,10 +10296,13 @@
         <v>0.05649</v>
       </c>
       <c r="L214" s="1" t="n">
+        <v>0.05645</v>
+      </c>
+      <c r="M214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="M214" s="1" t="n">
-        <v>0.05646</v>
+      <c r="N214" s="1" t="n">
+        <v>0.05645</v>
       </c>
     </row>
     <row r="215">
@@ -9697,9 +10342,12 @@
         <v>0.04405</v>
       </c>
       <c r="L215" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="M215" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="M215" s="1" t="n">
+      <c r="N215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -9740,9 +10388,12 @@
         <v>0.14989</v>
       </c>
       <c r="L216" s="1" t="n">
+        <v>0.15059</v>
+      </c>
+      <c r="M216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="M216" s="1" t="n">
+      <c r="N216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -9783,9 +10434,12 @@
         <v>0.073</v>
       </c>
       <c r="L217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="M217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="M217" s="1" t="n">
+      <c r="N217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -9829,6 +10483,9 @@
         <v>0.00269</v>
       </c>
       <c r="M218" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="N218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -9869,9 +10526,12 @@
         <v>0.01717</v>
       </c>
       <c r="L219" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="M219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="M219" s="1" t="n">
+      <c r="N219" s="1" t="n">
         <v>0.01715</v>
       </c>
     </row>
@@ -9912,9 +10572,12 @@
         <v>0.05522</v>
       </c>
       <c r="L220" s="1" t="n">
+        <v>0.05527</v>
+      </c>
+      <c r="M220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="M220" s="1" t="n">
+      <c r="N220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -9955,9 +10618,12 @@
         <v>0.02182</v>
       </c>
       <c r="L221" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="M221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="M221" s="1" t="n">
+      <c r="N221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -9998,9 +10664,12 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="L222" s="1" t="n">
+        <v>0.009390000000000001</v>
+      </c>
+      <c r="M222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="M222" s="1" t="n">
+      <c r="N222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -10041,9 +10710,12 @@
         <v>0.0164</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>0.0164</v>
+        <v>0.0165</v>
       </c>
       <c r="M223" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="N223" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -10084,9 +10756,12 @@
         <v>0.03817</v>
       </c>
       <c r="L224" s="1" t="n">
+        <v>0.03814</v>
+      </c>
+      <c r="M224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="M224" s="1" t="n">
+      <c r="N224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -10130,6 +10805,9 @@
         <v>0.00153</v>
       </c>
       <c r="M225" s="1" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="N225" s="1" t="n">
         <v>0.001525</v>
       </c>
     </row>
@@ -10170,9 +10848,12 @@
         <v>27.01</v>
       </c>
       <c r="L226" s="1" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="M226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="M226" s="1" t="n">
+      <c r="N226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -10213,9 +10894,12 @@
         <v>0.0707</v>
       </c>
       <c r="L227" s="1" t="n">
+        <v>0.07071</v>
+      </c>
+      <c r="M227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="M227" s="1" t="n">
+      <c r="N227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -10256,9 +10940,12 @@
         <v>0.314</v>
       </c>
       <c r="L228" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="M228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="M228" s="1" t="n">
+      <c r="N228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -10299,9 +10986,12 @@
         <v>18.35</v>
       </c>
       <c r="L229" s="1" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="M229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="M229" s="1" t="n">
+      <c r="N229" s="1" t="n">
         <v>18.35</v>
       </c>
     </row>
@@ -10342,9 +11032,12 @@
         <v>0.01926</v>
       </c>
       <c r="L230" s="1" t="n">
+        <v>0.01936</v>
+      </c>
+      <c r="M230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="M230" s="1" t="n">
+      <c r="N230" s="1" t="n">
         <v>0.01926</v>
       </c>
     </row>
@@ -10385,9 +11078,12 @@
         <v>0.01216</v>
       </c>
       <c r="L231" s="1" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="M231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="M231" s="1" t="n">
+      <c r="N231" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -10428,9 +11124,12 @@
         <v>0.2274</v>
       </c>
       <c r="L232" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="M232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="M232" s="1" t="n">
+      <c r="N232" s="1" t="n">
         <v>0.2274</v>
       </c>
     </row>
@@ -10471,9 +11170,12 @@
         <v>0.07103</v>
       </c>
       <c r="L233" s="1" t="n">
+        <v>0.07108</v>
+      </c>
+      <c r="M233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="M233" s="1" t="n">
+      <c r="N233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -10514,9 +11216,12 @@
         <v>0.1702</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>0.1704</v>
+        <v>0.1706</v>
       </c>
       <c r="M234" s="1" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="N234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -10557,9 +11262,12 @@
         <v>0.0254</v>
       </c>
       <c r="L235" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="M235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="M235" s="1" t="n">
+      <c r="N235" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -10600,9 +11308,12 @@
         <v>0.02998</v>
       </c>
       <c r="L236" s="1" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="M236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="M236" s="1" t="n">
+      <c r="N236" s="1" t="n">
         <v>0.02998</v>
       </c>
     </row>
@@ -10643,9 +11354,12 @@
         <v>1.98</v>
       </c>
       <c r="L237" s="1" t="n">
+        <v>1.991</v>
+      </c>
+      <c r="M237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="M237" s="1" t="n">
+      <c r="N237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -10686,10 +11400,13 @@
         <v>0.4263</v>
       </c>
       <c r="L238" s="1" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="M238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="M238" s="1" t="n">
-        <v>0.4263</v>
+      <c r="N238" s="1" t="n">
+        <v>0.4241</v>
       </c>
     </row>
     <row r="239">
@@ -10729,9 +11446,12 @@
         <v>0.0335</v>
       </c>
       <c r="L239" s="1" t="n">
+        <v>0.03354</v>
+      </c>
+      <c r="M239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="M239" s="1" t="n">
+      <c r="N239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -10772,9 +11492,12 @@
         <v>0.03401</v>
       </c>
       <c r="L240" s="1" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="M240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="M240" s="1" t="n">
+      <c r="N240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -10815,9 +11538,12 @@
         <v>0.0007541</v>
       </c>
       <c r="L241" s="1" t="n">
+        <v>0.0007538999999999999</v>
+      </c>
+      <c r="M241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="M241" s="1" t="n">
+      <c r="N241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -10858,9 +11584,12 @@
         <v>0.1843</v>
       </c>
       <c r="L242" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="M242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="M242" s="1" t="n">
+      <c r="N242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -10901,9 +11630,12 @@
         <v>0.014798</v>
       </c>
       <c r="L243" s="1" t="n">
+        <v>0.014823</v>
+      </c>
+      <c r="M243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="M243" s="1" t="n">
+      <c r="N243" s="1" t="n">
         <v>0.014772</v>
       </c>
     </row>
@@ -10944,9 +11676,12 @@
         <v>3.01e-05</v>
       </c>
       <c r="L244" s="1" t="n">
+        <v>3.02e-05</v>
+      </c>
+      <c r="M244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="M244" s="1" t="n">
+      <c r="N244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -10987,9 +11722,12 @@
         <v>0.03514</v>
       </c>
       <c r="L245" s="1" t="n">
+        <v>0.03524</v>
+      </c>
+      <c r="M245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="M245" s="1" t="n">
+      <c r="N245" s="1" t="n">
         <v>0.03514</v>
       </c>
     </row>
@@ -11030,9 +11768,12 @@
         <v>0.08037999999999999</v>
       </c>
       <c r="L246" s="1" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="M246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="M246" s="1" t="n">
+      <c r="N246" s="1" t="n">
         <v>0.08037999999999999</v>
       </c>
     </row>
@@ -11073,9 +11814,12 @@
         <v>0.007359</v>
       </c>
       <c r="L247" s="1" t="n">
+        <v>0.007373</v>
+      </c>
+      <c r="M247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="M247" s="1" t="n">
+      <c r="N247" s="1" t="n">
         <v>0.00728</v>
       </c>
     </row>
@@ -11116,9 +11860,12 @@
         <v>0.09596</v>
       </c>
       <c r="L248" s="1" t="n">
+        <v>0.09531000000000001</v>
+      </c>
+      <c r="M248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="M248" s="1" t="n">
+      <c r="N248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -11162,6 +11909,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="M249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -11202,9 +11952,12 @@
         <v>0.03496</v>
       </c>
       <c r="L250" s="1" t="n">
+        <v>0.03506</v>
+      </c>
+      <c r="M250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="M250" s="1" t="n">
+      <c r="N250" s="1" t="n">
         <v>0.03496</v>
       </c>
     </row>
@@ -11245,9 +11998,12 @@
         <v>0.03953</v>
       </c>
       <c r="L251" s="1" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="M251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="M251" s="1" t="n">
+      <c r="N251" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -11291,6 +12047,9 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="M252" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="N252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -11331,9 +12090,12 @@
         <v>4.071</v>
       </c>
       <c r="L253" s="1" t="n">
+        <v>4.071</v>
+      </c>
+      <c r="M253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="M253" s="1" t="n">
+      <c r="N253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -11374,9 +12136,12 @@
         <v>0.187</v>
       </c>
       <c r="L254" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="M254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M254" s="1" t="n">
+      <c r="N254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -11417,9 +12182,12 @@
         <v>0.07228</v>
       </c>
       <c r="L255" s="1" t="n">
+        <v>0.07238</v>
+      </c>
+      <c r="M255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="M255" s="1" t="n">
+      <c r="N255" s="1" t="n">
         <v>0.07214</v>
       </c>
     </row>
@@ -11460,9 +12228,12 @@
         <v>0.01828</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>0.01833</v>
+        <v>0.01835</v>
       </c>
       <c r="M256" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="N256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -11503,9 +12274,12 @@
         <v>5.944</v>
       </c>
       <c r="L257" s="1" t="n">
+        <v>5.951</v>
+      </c>
+      <c r="M257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="M257" s="1" t="n">
+      <c r="N257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -11546,9 +12320,12 @@
         <v>0.2658</v>
       </c>
       <c r="L258" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="M258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="M258" s="1" t="n">
+      <c r="N258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -11589,9 +12366,12 @@
         <v>0.136</v>
       </c>
       <c r="L259" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="M259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="M259" s="1" t="n">
+      <c r="N259" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -11632,9 +12412,12 @@
         <v>0.3065</v>
       </c>
       <c r="L260" s="1" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="M260" s="1" t="n">
         <v>0.30667</v>
       </c>
-      <c r="M260" s="1" t="n">
+      <c r="N260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -11675,9 +12458,12 @@
         <v>0.09898</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>0.099</v>
+        <v>0.09934</v>
       </c>
       <c r="M261" s="1" t="n">
+        <v>0.09934</v>
+      </c>
+      <c r="N261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -11718,10 +12504,13 @@
         <v>0.5409</v>
       </c>
       <c r="L262" s="1" t="n">
+        <v>0.5401</v>
+      </c>
+      <c r="M262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="M262" s="1" t="n">
-        <v>0.5409</v>
+      <c r="N262" s="1" t="n">
+        <v>0.5401</v>
       </c>
     </row>
     <row r="263">
@@ -11764,6 +12553,9 @@
         <v>0.293</v>
       </c>
       <c r="M263" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="N263" s="1" t="n">
         <v>0.2914</v>
       </c>
     </row>
@@ -11804,9 +12596,12 @@
         <v>0.964</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>0.964</v>
+        <v>0.972</v>
       </c>
       <c r="M264" s="1" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="N264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -11847,9 +12642,12 @@
         <v>0.5415</v>
       </c>
       <c r="L265" s="1" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="M265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="M265" s="1" t="n">
+      <c r="N265" s="1" t="n">
         <v>0.5403</v>
       </c>
     </row>
@@ -11890,9 +12688,12 @@
         <v>0.07373</v>
       </c>
       <c r="L266" s="1" t="n">
+        <v>0.07382</v>
+      </c>
+      <c r="M266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="M266" s="1" t="n">
+      <c r="N266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -11933,9 +12734,12 @@
         <v>0.0218</v>
       </c>
       <c r="L267" s="1" t="n">
+        <v>0.02163</v>
+      </c>
+      <c r="M267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="M267" s="1" t="n">
+      <c r="N267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -11976,9 +12780,12 @@
         <v>0.01623</v>
       </c>
       <c r="L268" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="M268" s="1" t="n">
         <v>0.01633</v>
       </c>
-      <c r="M268" s="1" t="n">
+      <c r="N268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -12019,9 +12826,12 @@
         <v>0.003753</v>
       </c>
       <c r="L269" s="1" t="n">
+        <v>0.003763</v>
+      </c>
+      <c r="M269" s="1" t="n">
         <v>0.003765</v>
       </c>
-      <c r="M269" s="1" t="n">
+      <c r="N269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -12062,9 +12872,12 @@
         <v>0.00762</v>
       </c>
       <c r="L270" s="1" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="M270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="M270" s="1" t="n">
+      <c r="N270" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -12105,9 +12918,12 @@
         <v>0.05508</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>0.05512</v>
+        <v>0.05525</v>
       </c>
       <c r="M271" s="1" t="n">
+        <v>0.05525</v>
+      </c>
+      <c r="N271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -12148,9 +12964,12 @@
         <v>2.303</v>
       </c>
       <c r="L272" s="1" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="M272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="M272" s="1" t="n">
+      <c r="N272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -12191,9 +13010,12 @@
         <v>0.05488</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>0.05488</v>
+        <v>0.05504</v>
       </c>
       <c r="M273" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="N273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -12234,9 +13056,12 @@
         <v>0.02312</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>0.02312</v>
+        <v>0.02333</v>
       </c>
       <c r="M274" s="1" t="n">
+        <v>0.02333</v>
+      </c>
+      <c r="N274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -12277,9 +13102,12 @@
         <v>1.184</v>
       </c>
       <c r="L275" s="1" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="M275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="M275" s="1" t="n">
+      <c r="N275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -12320,9 +13148,12 @@
         <v>0.2726</v>
       </c>
       <c r="L276" s="1" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="M276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="M276" s="1" t="n">
+      <c r="N276" s="1" t="n">
         <v>0.2722</v>
       </c>
     </row>
@@ -12363,9 +13194,12 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="L277" s="1" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="M277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="M277" s="1" t="n">
+      <c r="N277" s="1" t="n">
         <v>0.9360000000000001</v>
       </c>
     </row>
@@ -12406,10 +13240,13 @@
         <v>0.6294999999999999</v>
       </c>
       <c r="L278" s="1" t="n">
+        <v>0.6224</v>
+      </c>
+      <c r="M278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="M278" s="1" t="n">
-        <v>0.6228</v>
+      <c r="N278" s="1" t="n">
+        <v>0.6224</v>
       </c>
     </row>
     <row r="279">
@@ -12449,9 +13286,12 @@
         <v>0.001347</v>
       </c>
       <c r="L279" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="M279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="M279" s="1" t="n">
+      <c r="N279" s="1" t="n">
         <v>0.001344</v>
       </c>
     </row>
@@ -12492,9 +13332,12 @@
         <v>0.005557</v>
       </c>
       <c r="L280" s="1" t="n">
+        <v>0.005561</v>
+      </c>
+      <c r="M280" s="1" t="n">
         <v>0.005567</v>
       </c>
-      <c r="M280" s="1" t="n">
+      <c r="N280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -12535,9 +13378,12 @@
         <v>1.522</v>
       </c>
       <c r="L281" s="1" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="M281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="M281" s="1" t="n">
+      <c r="N281" s="1" t="n">
         <v>1.521</v>
       </c>
     </row>
@@ -12578,9 +13424,12 @@
         <v>28.34</v>
       </c>
       <c r="L282" s="1" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="M282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="M282" s="1" t="n">
+      <c r="N282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -12621,10 +13470,13 @@
         <v>0.12866</v>
       </c>
       <c r="L283" s="1" t="n">
+        <v>0.12856</v>
+      </c>
+      <c r="M283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="M283" s="1" t="n">
-        <v>0.12866</v>
+      <c r="N283" s="1" t="n">
+        <v>0.12856</v>
       </c>
     </row>
     <row r="284">
@@ -12667,6 +13519,9 @@
         <v>0.01116</v>
       </c>
       <c r="M284" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="N284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -12707,9 +13562,12 @@
         <v>6.575</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>6.577</v>
+        <v>6.598</v>
       </c>
       <c r="M285" s="1" t="n">
+        <v>6.598</v>
+      </c>
+      <c r="N285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -12750,9 +13608,12 @@
         <v>0.01844</v>
       </c>
       <c r="L286" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="M286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="M286" s="1" t="n">
+      <c r="N286" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -12793,9 +13654,12 @@
         <v>0.008385</v>
       </c>
       <c r="L287" s="1" t="n">
+        <v>0.008385999999999999</v>
+      </c>
+      <c r="M287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="M287" s="1" t="n">
+      <c r="N287" s="1" t="n">
         <v>0.008378</v>
       </c>
     </row>
@@ -12836,9 +13700,12 @@
         <v>0.3883</v>
       </c>
       <c r="L288" s="1" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="M288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="M288" s="1" t="n">
+      <c r="N288" s="1" t="n">
         <v>0.3846</v>
       </c>
     </row>
@@ -12879,9 +13746,12 @@
         <v>0.010005</v>
       </c>
       <c r="L289" s="1" t="n">
+        <v>0.010043</v>
+      </c>
+      <c r="M289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="M289" s="1" t="n">
+      <c r="N289" s="1" t="n">
         <v>0.010005</v>
       </c>
     </row>
@@ -12922,10 +13792,13 @@
         <v>0.02591</v>
       </c>
       <c r="L290" s="1" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="M290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="M290" s="1" t="n">
-        <v>0.02591</v>
+      <c r="N290" s="1" t="n">
+        <v>0.02588</v>
       </c>
     </row>
     <row r="291">
@@ -12965,9 +13838,12 @@
         <v>0.095</v>
       </c>
       <c r="L291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="M291" s="1" t="n">
+      <c r="N291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -13008,9 +13884,12 @@
         <v>0.28566</v>
       </c>
       <c r="L292" s="1" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="M292" s="1" t="n">
         <v>0.28632</v>
       </c>
-      <c r="M292" s="1" t="n">
+      <c r="N292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -13051,9 +13930,12 @@
         <v>0.01547</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>0.01548</v>
+        <v>0.01551</v>
       </c>
       <c r="M293" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="N293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -13094,9 +13976,12 @@
         <v>0.00344</v>
       </c>
       <c r="L294" s="1" t="n">
+        <v>0.003435</v>
+      </c>
+      <c r="M294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="M294" s="1" t="n">
+      <c r="N294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -13137,9 +14022,12 @@
         <v>0.042792</v>
       </c>
       <c r="L295" s="1" t="n">
+        <v>0.042824</v>
+      </c>
+      <c r="M295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="M295" s="1" t="n">
+      <c r="N295" s="1" t="n">
         <v>0.042792</v>
       </c>
     </row>
@@ -13180,9 +14068,12 @@
         <v>0.02982</v>
       </c>
       <c r="L296" s="1" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="M296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="M296" s="1" t="n">
+      <c r="N296" s="1" t="n">
         <v>0.02929</v>
       </c>
     </row>
@@ -13223,9 +14114,12 @@
         <v>0.03799</v>
       </c>
       <c r="L297" s="1" t="n">
+        <v>0.03791</v>
+      </c>
+      <c r="M297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="M297" s="1" t="n">
+      <c r="N297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -13266,10 +14160,13 @@
         <v>0.08407000000000001</v>
       </c>
       <c r="L298" s="1" t="n">
+        <v>0.08248</v>
+      </c>
+      <c r="M298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="M298" s="1" t="n">
-        <v>0.08305999999999999</v>
+      <c r="N298" s="1" t="n">
+        <v>0.08248</v>
       </c>
     </row>
     <row r="299">
@@ -13309,9 +14206,12 @@
         <v>0.00779</v>
       </c>
       <c r="L299" s="1" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="M299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="M299" s="1" t="n">
+      <c r="N299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -13352,9 +14252,12 @@
         <v>0.01513</v>
       </c>
       <c r="L300" s="1" t="n">
+        <v>0.01515</v>
+      </c>
+      <c r="M300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="M300" s="1" t="n">
+      <c r="N300" s="1" t="n">
         <v>0.01512</v>
       </c>
     </row>
@@ -13395,9 +14298,12 @@
         <v>0.1411</v>
       </c>
       <c r="L301" s="1" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="M301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="M301" s="1" t="n">
+      <c r="N301" s="1" t="n">
         <v>0.141</v>
       </c>
     </row>
@@ -13438,9 +14344,12 @@
         <v>0.0006349</v>
       </c>
       <c r="L302" s="1" t="n">
+        <v>0.0006351</v>
+      </c>
+      <c r="M302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="M302" s="1" t="n">
+      <c r="N302" s="1" t="n">
         <v>0.0006284</v>
       </c>
     </row>
@@ -13481,9 +14390,12 @@
         <v>0.06223</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>0.06235</v>
+        <v>0.0624</v>
       </c>
       <c r="M303" s="1" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="N303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -13524,9 +14436,12 @@
         <v>0.0001635</v>
       </c>
       <c r="L304" s="1" t="n">
+        <v>0.0001633</v>
+      </c>
+      <c r="M304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="M304" s="1" t="n">
+      <c r="N304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -13567,9 +14482,12 @@
         <v>0.06139</v>
       </c>
       <c r="L305" s="1" t="n">
+        <v>0.06115</v>
+      </c>
+      <c r="M305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="M305" s="1" t="n">
+      <c r="N305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -13610,9 +14528,12 @@
         <v>0.022229</v>
       </c>
       <c r="L306" s="1" t="n">
+        <v>0.022181</v>
+      </c>
+      <c r="M306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="M306" s="1" t="n">
+      <c r="N306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -13653,9 +14574,12 @@
         <v>0.02365</v>
       </c>
       <c r="L307" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="M307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="M307" s="1" t="n">
+      <c r="N307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -13696,9 +14620,12 @@
         <v>0.000411</v>
       </c>
       <c r="L308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="M308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="M308" s="1" t="n">
+      <c r="N308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -13742,6 +14669,9 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="M309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="N309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -13782,9 +14712,12 @@
         <v>0.3844</v>
       </c>
       <c r="L310" s="1" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="M310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="M310" s="1" t="n">
+      <c r="N310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -13825,9 +14758,12 @@
         <v>0.0356</v>
       </c>
       <c r="L311" s="1" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="M311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="M311" s="1" t="n">
+      <c r="N311" s="1" t="n">
         <v>0.0355</v>
       </c>
     </row>
@@ -13868,9 +14804,12 @@
         <v>0.02452</v>
       </c>
       <c r="L312" s="1" t="n">
+        <v>0.02454</v>
+      </c>
+      <c r="M312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="M312" s="1" t="n">
+      <c r="N312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -13911,9 +14850,12 @@
         <v>0.04132</v>
       </c>
       <c r="L313" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="M313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="M313" s="1" t="n">
+      <c r="N313" s="1" t="n">
         <v>0.04129</v>
       </c>
     </row>
@@ -13954,10 +14896,13 @@
         <v>4</v>
       </c>
       <c r="L314" s="1" t="n">
+        <v>3.985</v>
+      </c>
+      <c r="M314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="M314" s="1" t="n">
-        <v>3.998</v>
+      <c r="N314" s="1" t="n">
+        <v>3.985</v>
       </c>
     </row>
     <row r="315">
@@ -13997,9 +14942,12 @@
         <v>0.1602</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>0.1604</v>
+        <v>0.1605</v>
       </c>
       <c r="M315" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="N315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -14040,9 +14988,12 @@
         <v>0.08977</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>0.08977</v>
+        <v>0.09085</v>
       </c>
       <c r="M316" s="1" t="n">
+        <v>0.09085</v>
+      </c>
+      <c r="N316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -14083,9 +15034,12 @@
         <v>0.06852999999999999</v>
       </c>
       <c r="L317" s="1" t="n">
+        <v>0.06856</v>
+      </c>
+      <c r="M317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="M317" s="1" t="n">
+      <c r="N317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -14126,10 +15080,13 @@
         <v>0.012426</v>
       </c>
       <c r="L318" s="1" t="n">
+        <v>0.012414</v>
+      </c>
+      <c r="M318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="M318" s="1" t="n">
-        <v>0.012426</v>
+      <c r="N318" s="1" t="n">
+        <v>0.012414</v>
       </c>
     </row>
     <row r="319">
@@ -14169,9 +15126,12 @@
         <v>0.001137</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>0.001138</v>
+        <v>0.00114</v>
       </c>
       <c r="M319" s="1" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="N319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -14212,9 +15172,12 @@
         <v>0.0629</v>
       </c>
       <c r="L320" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="M320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="M320" s="1" t="n">
+      <c r="N320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -14255,9 +15218,12 @@
         <v>0.00527</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>0.00527</v>
+        <v>0.00528</v>
       </c>
       <c r="M321" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="N321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -14298,9 +15264,12 @@
         <v>0.1113</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>0.1116</v>
+        <v>0.1121</v>
       </c>
       <c r="M322" s="1" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="N322" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
@@ -14341,9 +15310,12 @@
         <v>0.04304</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>0.04304</v>
+        <v>0.0434</v>
       </c>
       <c r="M323" s="1" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="N323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -14384,9 +15356,12 @@
         <v>0.01767</v>
       </c>
       <c r="L324" s="1" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="M324" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="M324" s="1" t="n">
+      <c r="N324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -14427,9 +15402,12 @@
         <v>0.005672</v>
       </c>
       <c r="L325" s="1" t="n">
+        <v>0.005671</v>
+      </c>
+      <c r="M325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="M325" s="1" t="n">
+      <c r="N325" s="1" t="n">
         <v>0.005663</v>
       </c>
     </row>
@@ -14470,9 +15448,12 @@
         <v>0.001776</v>
       </c>
       <c r="L326" s="1" t="n">
+        <v>0.001775</v>
+      </c>
+      <c r="M326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="M326" s="1" t="n">
+      <c r="N326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -14513,9 +15494,12 @@
         <v>0.04049</v>
       </c>
       <c r="L327" s="1" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="M327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="M327" s="1" t="n">
+      <c r="N327" s="1" t="n">
         <v>0.04047</v>
       </c>
     </row>
@@ -14556,10 +15540,13 @@
         <v>0.053576</v>
       </c>
       <c r="L328" s="1" t="n">
+        <v>0.053566</v>
+      </c>
+      <c r="M328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="M328" s="1" t="n">
-        <v>0.053576</v>
+      <c r="N328" s="1" t="n">
+        <v>0.053566</v>
       </c>
     </row>
     <row r="329">
@@ -14599,9 +15586,12 @@
         <v>0.2783</v>
       </c>
       <c r="L329" s="1" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="M329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="M329" s="1" t="n">
+      <c r="N329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -14642,9 +15632,12 @@
         <v>0.1588</v>
       </c>
       <c r="L330" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="M330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="M330" s="1" t="n">
+      <c r="N330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -14685,9 +15678,12 @@
         <v>0.05368</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>0.05368</v>
+        <v>0.0538</v>
       </c>
       <c r="M331" s="1" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="N331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -14728,9 +15724,12 @@
         <v>0.3617</v>
       </c>
       <c r="L332" s="1" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="M332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="M332" s="1" t="n">
+      <c r="N332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -14774,6 +15773,9 @@
         <v>0.03051</v>
       </c>
       <c r="M333" s="1" t="n">
+        <v>0.03051</v>
+      </c>
+      <c r="N333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -14814,9 +15816,12 @@
         <v>0.01796</v>
       </c>
       <c r="L334" s="1" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="M334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="M334" s="1" t="n">
+      <c r="N334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -14857,9 +15862,12 @@
         <v>0.0581</v>
       </c>
       <c r="L335" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="M335" s="1" t="n">
+      <c r="N335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -14900,10 +15908,13 @@
         <v>0.09132999999999999</v>
       </c>
       <c r="L336" s="1" t="n">
+        <v>0.09107999999999999</v>
+      </c>
+      <c r="M336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="M336" s="1" t="n">
-        <v>0.09117</v>
+      <c r="N336" s="1" t="n">
+        <v>0.09107999999999999</v>
       </c>
     </row>
     <row r="337">
@@ -14943,9 +15954,12 @@
         <v>0.17792</v>
       </c>
       <c r="L337" s="1" t="n">
+        <v>0.17867</v>
+      </c>
+      <c r="M337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="M337" s="1" t="n">
+      <c r="N337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -14986,9 +16000,12 @@
         <v>0.02092</v>
       </c>
       <c r="L338" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="M338" s="1" t="n">
+      <c r="N338" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -15032,6 +16049,9 @@
         <v>0.1318</v>
       </c>
       <c r="M339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="N339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -15072,10 +16092,13 @@
         <v>0.007929</v>
       </c>
       <c r="L340" s="1" t="n">
+        <v>0.007915999999999999</v>
+      </c>
+      <c r="M340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="M340" s="1" t="n">
-        <v>0.007929</v>
+      <c r="N340" s="1" t="n">
+        <v>0.007915999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -15115,9 +16138,12 @@
         <v>4.391</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>4.407</v>
+        <v>4.415</v>
       </c>
       <c r="M341" s="1" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="N341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -15158,10 +16184,13 @@
         <v>0.18973</v>
       </c>
       <c r="L342" s="1" t="n">
+        <v>0.18839</v>
+      </c>
+      <c r="M342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="M342" s="1" t="n">
-        <v>0.1889</v>
+      <c r="N342" s="1" t="n">
+        <v>0.18839</v>
       </c>
     </row>
     <row r="343">
@@ -15201,9 +16230,12 @@
         <v>0.08373999999999999</v>
       </c>
       <c r="L343" s="1" t="n">
+        <v>0.08371000000000001</v>
+      </c>
+      <c r="M343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="M343" s="1" t="n">
+      <c r="N343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -15244,9 +16276,12 @@
         <v>0.1828</v>
       </c>
       <c r="L344" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="M344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="M344" s="1" t="n">
+      <c r="N344" s="1" t="n">
         <v>0.1821</v>
       </c>
     </row>
@@ -15287,9 +16322,12 @@
         <v>0.003244</v>
       </c>
       <c r="L345" s="1" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="M345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="M345" s="1" t="n">
+      <c r="N345" s="1" t="n">
         <v>0.003244</v>
       </c>
     </row>
@@ -15330,9 +16368,12 @@
         <v>0.09163</v>
       </c>
       <c r="L346" s="1" t="n">
+        <v>0.09161999999999999</v>
+      </c>
+      <c r="M346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="M346" s="1" t="n">
+      <c r="N346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -15373,9 +16414,12 @@
         <v>2.243</v>
       </c>
       <c r="L347" s="1" t="n">
+        <v>2.246</v>
+      </c>
+      <c r="M347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="M347" s="1" t="n">
+      <c r="N347" s="1" t="n">
         <v>2.243</v>
       </c>
     </row>
@@ -15416,9 +16460,12 @@
         <v>0.3055</v>
       </c>
       <c r="L348" s="1" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="M348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="M348" s="1" t="n">
+      <c r="N348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -15459,9 +16506,12 @@
         <v>0.02979</v>
       </c>
       <c r="L349" s="1" t="n">
+        <v>0.02978</v>
+      </c>
+      <c r="M349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="M349" s="1" t="n">
+      <c r="N349" s="1" t="n">
         <v>0.02975</v>
       </c>
     </row>
@@ -15502,9 +16552,12 @@
         <v>0.1279</v>
       </c>
       <c r="L350" s="1" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="M350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="M350" s="1" t="n">
+      <c r="N350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -15545,9 +16598,12 @@
         <v>0.06698999999999999</v>
       </c>
       <c r="L351" s="1" t="n">
+        <v>0.06695</v>
+      </c>
+      <c r="M351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="M351" s="1" t="n">
+      <c r="N351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -15588,9 +16644,12 @@
         <v>0.06252000000000001</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>0.06252000000000001</v>
+        <v>0.06254</v>
       </c>
       <c r="M352" s="1" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="N352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -15631,9 +16690,12 @@
         <v>0.06353</v>
       </c>
       <c r="L353" s="1" t="n">
+        <v>0.06361</v>
+      </c>
+      <c r="M353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="M353" s="1" t="n">
+      <c r="N353" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -15674,9 +16736,12 @@
         <v>0.10501</v>
       </c>
       <c r="L354" s="1" t="n">
+        <v>0.10497</v>
+      </c>
+      <c r="M354" s="1" t="n">
         <v>0.10603</v>
       </c>
-      <c r="M354" s="1" t="n">
+      <c r="N354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -15717,9 +16782,12 @@
         <v>0.0901</v>
       </c>
       <c r="L355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="M355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="M355" s="1" t="n">
+      <c r="N355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -15760,9 +16828,12 @@
         <v>0.07041</v>
       </c>
       <c r="L356" s="1" t="n">
+        <v>0.07024</v>
+      </c>
+      <c r="M356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="M356" s="1" t="n">
+      <c r="N356" s="1" t="n">
         <v>0.06985</v>
       </c>
     </row>
@@ -15803,9 +16874,12 @@
         <v>0.4526</v>
       </c>
       <c r="L357" s="1" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="M357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="M357" s="1" t="n">
+      <c r="N357" s="1" t="n">
         <v>0.4521</v>
       </c>
     </row>
@@ -15846,9 +16920,12 @@
         <v>0.03523</v>
       </c>
       <c r="L358" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="M358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="M358" s="1" t="n">
+      <c r="N358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -15889,9 +16966,12 @@
         <v>0.01478</v>
       </c>
       <c r="L359" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="M359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="M359" s="1" t="n">
+      <c r="N359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -15932,9 +17012,12 @@
         <v>0.13355</v>
       </c>
       <c r="L360" s="1" t="n">
+        <v>0.13367</v>
+      </c>
+      <c r="M360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="M360" s="1" t="n">
+      <c r="N360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -15975,9 +17058,12 @@
         <v>0.0005872</v>
       </c>
       <c r="L361" s="1" t="n">
+        <v>0.0005874</v>
+      </c>
+      <c r="M361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="M361" s="1" t="n">
+      <c r="N361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -16018,9 +17104,12 @@
         <v>0.03884</v>
       </c>
       <c r="L362" s="1" t="n">
+        <v>0.03891</v>
+      </c>
+      <c r="M362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="M362" s="1" t="n">
+      <c r="N362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -16061,9 +17150,12 @@
         <v>3.213</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>3.223</v>
+        <v>3.226</v>
       </c>
       <c r="M363" s="1" t="n">
+        <v>3.226</v>
+      </c>
+      <c r="N363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -16104,9 +17196,12 @@
         <v>0.165</v>
       </c>
       <c r="L364" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="M364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="M364" s="1" t="n">
+      <c r="N364" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -16147,9 +17242,12 @@
         <v>0.1137</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>0.1137</v>
+        <v>0.1139</v>
       </c>
       <c r="M365" s="1" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="N365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -16190,10 +17288,13 @@
         <v>0.0006415</v>
       </c>
       <c r="L366" s="1" t="n">
+        <v>0.0006405</v>
+      </c>
+      <c r="M366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="M366" s="1" t="n">
-        <v>0.0006409</v>
+      <c r="N366" s="1" t="n">
+        <v>0.0006405</v>
       </c>
     </row>
     <row r="367">
@@ -16233,9 +17334,12 @@
         <v>0.05935</v>
       </c>
       <c r="L367" s="1" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="M367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="M367" s="1" t="n">
+      <c r="N367" s="1" t="n">
         <v>0.05927</v>
       </c>
     </row>
@@ -16276,10 +17380,13 @@
         <v>0.08219</v>
       </c>
       <c r="L368" s="1" t="n">
+        <v>0.08217000000000001</v>
+      </c>
+      <c r="M368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="M368" s="1" t="n">
-        <v>0.08219</v>
+      <c r="N368" s="1" t="n">
+        <v>0.08217000000000001</v>
       </c>
     </row>
     <row r="369">
@@ -16319,9 +17426,12 @@
         <v>0.0402</v>
       </c>
       <c r="L369" s="1" t="n">
+        <v>0.03991</v>
+      </c>
+      <c r="M369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="M369" s="1" t="n">
+      <c r="N369" s="1" t="n">
         <v>0.03976</v>
       </c>
     </row>
@@ -16362,9 +17472,12 @@
         <v>3.695</v>
       </c>
       <c r="L370" s="1" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="M370" s="1" t="n">
+      <c r="N370" s="1" t="n">
         <v>3.695</v>
       </c>
     </row>
@@ -16405,9 +17518,12 @@
         <v>0.122</v>
       </c>
       <c r="L371" s="1" t="n">
+        <v>0.1218</v>
+      </c>
+      <c r="M371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="M371" s="1" t="n">
+      <c r="N371" s="1" t="n">
         <v>0.1216</v>
       </c>
     </row>
@@ -16448,9 +17564,12 @@
         <v>0.01482</v>
       </c>
       <c r="L372" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="M372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="M372" s="1" t="n">
+      <c r="N372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -16491,10 +17610,13 @@
         <v>0.02194</v>
       </c>
       <c r="L373" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="M373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="M373" s="1" t="n">
-        <v>0.02192</v>
+      <c r="N373" s="1" t="n">
+        <v>0.02191</v>
       </c>
     </row>
     <row r="374">
@@ -16534,9 +17656,12 @@
         <v>1.8671</v>
       </c>
       <c r="L374" s="1" t="n">
+        <v>1.8635</v>
+      </c>
+      <c r="M374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="M374" s="1" t="n">
+      <c r="N374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -16577,9 +17702,12 @@
         <v>0.02105</v>
       </c>
       <c r="L375" s="1" t="n">
+        <v>0.02104</v>
+      </c>
+      <c r="M375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="M375" s="1" t="n">
+      <c r="N375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -16620,9 +17748,12 @@
         <v>1.31</v>
       </c>
       <c r="L376" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="M376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="M376" s="1" t="n">
+      <c r="N376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -16663,9 +17794,12 @@
         <v>0.2826</v>
       </c>
       <c r="L377" s="1" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="M377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="M377" s="1" t="n">
+      <c r="N377" s="1" t="n">
         <v>0.2826</v>
       </c>
     </row>
@@ -16706,9 +17840,12 @@
         <v>0.01551</v>
       </c>
       <c r="L378" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="M378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="M378" s="1" t="n">
+      <c r="N378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -16749,9 +17886,12 @@
         <v>1.5362</v>
       </c>
       <c r="L379" s="1" t="n">
+        <v>1.5309</v>
+      </c>
+      <c r="M379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="M379" s="1" t="n">
+      <c r="N379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -16792,9 +17932,12 @@
         <v>6.918e-05</v>
       </c>
       <c r="L380" s="1" t="n">
+        <v>6.931999999999999e-05</v>
+      </c>
+      <c r="M380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="M380" s="1" t="n">
+      <c r="N380" s="1" t="n">
         <v>6.918e-05</v>
       </c>
     </row>
@@ -16835,9 +17978,12 @@
         <v>2.546</v>
       </c>
       <c r="L381" s="1" t="n">
+        <v>2.552</v>
+      </c>
+      <c r="M381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="M381" s="1" t="n">
+      <c r="N381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -16878,10 +18024,13 @@
         <v>0.0673</v>
       </c>
       <c r="L382" s="1" t="n">
+        <v>0.06722</v>
+      </c>
+      <c r="M382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="M382" s="1" t="n">
-        <v>0.0673</v>
+      <c r="N382" s="1" t="n">
+        <v>0.06722</v>
       </c>
     </row>
     <row r="383">
@@ -16921,9 +18070,12 @@
         <v>0.01807</v>
       </c>
       <c r="L383" s="1" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="M383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="M383" s="1" t="n">
+      <c r="N383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -16964,9 +18116,12 @@
         <v>0.05224</v>
       </c>
       <c r="L384" s="1" t="n">
+        <v>0.05236</v>
+      </c>
+      <c r="M384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="M384" s="1" t="n">
+      <c r="N384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -17007,9 +18162,12 @@
         <v>7.585</v>
       </c>
       <c r="L385" s="1" t="n">
+        <v>7.585</v>
+      </c>
+      <c r="M385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="M385" s="1" t="n">
+      <c r="N385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -17050,9 +18208,12 @@
         <v>0.003296</v>
       </c>
       <c r="L386" s="1" t="n">
+        <v>0.003287</v>
+      </c>
+      <c r="M386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="M386" s="1" t="n">
+      <c r="N386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -17093,9 +18254,12 @@
         <v>0.0003818</v>
       </c>
       <c r="L387" s="1" t="n">
+        <v>0.0003827</v>
+      </c>
+      <c r="M387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="M387" s="1" t="n">
+      <c r="N387" s="1" t="n">
         <v>0.0003818</v>
       </c>
     </row>
@@ -17136,9 +18300,12 @@
         <v>0.009549999999999999</v>
       </c>
       <c r="L388" s="1" t="n">
+        <v>0.009549999999999999</v>
+      </c>
+      <c r="M388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="M388" s="1" t="n">
+      <c r="N388" s="1" t="n">
         <v>0.009549999999999999</v>
       </c>
     </row>
@@ -17179,9 +18346,12 @@
         <v>0.2885</v>
       </c>
       <c r="L389" s="1" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="M389" s="1" t="n">
         <v>0.2902</v>
       </c>
-      <c r="M389" s="1" t="n">
+      <c r="N389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -17222,9 +18392,12 @@
         <v>0.025</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>0.025</v>
+        <v>0.0252</v>
       </c>
       <c r="M390" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="N390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -17265,9 +18438,12 @@
         <v>2.819</v>
       </c>
       <c r="L391" s="1" t="n">
+        <v>2.818</v>
+      </c>
+      <c r="M391" s="1" t="n">
         <v>2.833</v>
       </c>
-      <c r="M391" s="1" t="n">
+      <c r="N391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -17308,9 +18484,12 @@
         <v>0.01346</v>
       </c>
       <c r="L392" s="1" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="M392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="M392" s="1" t="n">
+      <c r="N392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -17351,9 +18530,12 @@
         <v>0.00236</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>0.00236</v>
+        <v>0.00237</v>
       </c>
       <c r="M393" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="N393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -17394,9 +18576,12 @@
         <v>0.0594</v>
       </c>
       <c r="L394" s="1" t="n">
+        <v>0.05943</v>
+      </c>
+      <c r="M394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="M394" s="1" t="n">
+      <c r="N394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -17440,6 +18625,9 @@
         <v>0.0405</v>
       </c>
       <c r="M395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="N395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -17480,9 +18668,12 @@
         <v>0.09243999999999999</v>
       </c>
       <c r="L396" s="1" t="n">
+        <v>0.09231</v>
+      </c>
+      <c r="M396" s="1" t="n">
         <v>0.09272</v>
       </c>
-      <c r="M396" s="1" t="n">
+      <c r="N396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -17523,9 +18714,12 @@
         <v>0.1519</v>
       </c>
       <c r="L397" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="M397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="M397" s="1" t="n">
+      <c r="N397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -17569,6 +18763,9 @@
         <v>0.929</v>
       </c>
       <c r="M398" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="N398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -17609,9 +18806,12 @@
         <v>0.05245</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>0.05254</v>
+        <v>0.05255</v>
       </c>
       <c r="M399" s="1" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="N399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -17652,9 +18852,12 @@
         <v>2.517</v>
       </c>
       <c r="L400" s="1" t="n">
+        <v>2.521</v>
+      </c>
+      <c r="M400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="M400" s="1" t="n">
+      <c r="N400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -17695,9 +18898,12 @@
         <v>0.01799</v>
       </c>
       <c r="L401" s="1" t="n">
+        <v>0.01794</v>
+      </c>
+      <c r="M401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="M401" s="1" t="n">
+      <c r="N401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -17738,9 +18944,12 @@
         <v>0.08078</v>
       </c>
       <c r="L402" s="1" t="n">
+        <v>0.08044</v>
+      </c>
+      <c r="M402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="M402" s="1" t="n">
+      <c r="N402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -17781,9 +18990,12 @@
         <v>1.2455</v>
       </c>
       <c r="L403" s="1" t="n">
+        <v>1.2486</v>
+      </c>
+      <c r="M403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="M403" s="1" t="n">
+      <c r="N403" s="1" t="n">
         <v>1.2455</v>
       </c>
     </row>
@@ -17824,9 +19036,12 @@
         <v>0.00716</v>
       </c>
       <c r="L404" s="1" t="n">
+        <v>0.00715</v>
+      </c>
+      <c r="M404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="M404" s="1" t="n">
+      <c r="N404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -17867,9 +19082,12 @@
         <v>0.499</v>
       </c>
       <c r="L405" s="1" t="n">
+        <v>0.4973</v>
+      </c>
+      <c r="M405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="M405" s="1" t="n">
+      <c r="N405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -17913,6 +19131,9 @@
         <v>0.01153</v>
       </c>
       <c r="M406" s="1" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="N406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -17953,9 +19174,12 @@
         <v>0.04612</v>
       </c>
       <c r="L407" s="1" t="n">
+        <v>0.04614</v>
+      </c>
+      <c r="M407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="M407" s="1" t="n">
+      <c r="N407" s="1" t="n">
         <v>0.04612</v>
       </c>
     </row>
@@ -17996,9 +19220,12 @@
         <v>0.0394</v>
       </c>
       <c r="L408" s="1" t="n">
+        <v>0.03947</v>
+      </c>
+      <c r="M408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="M408" s="1" t="n">
+      <c r="N408" s="1" t="n">
         <v>0.0394</v>
       </c>
     </row>
@@ -18039,9 +19266,12 @@
         <v>0.05234</v>
       </c>
       <c r="L409" s="1" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="M409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="M409" s="1" t="n">
+      <c r="N409" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -18082,9 +19312,12 @@
         <v>0.01237</v>
       </c>
       <c r="L410" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="M410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="M410" s="1" t="n">
+      <c r="N410" s="1" t="n">
         <v>0.01237</v>
       </c>
     </row>
@@ -18125,9 +19358,12 @@
         <v>0.06367</v>
       </c>
       <c r="L411" s="1" t="n">
+        <v>0.06382</v>
+      </c>
+      <c r="M411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="M411" s="1" t="n">
+      <c r="N411" s="1" t="n">
         <v>0.06347</v>
       </c>
     </row>
@@ -18168,9 +19404,12 @@
         <v>0.04145</v>
       </c>
       <c r="L412" s="1" t="n">
-        <v>0.04146</v>
+        <v>0.04154</v>
       </c>
       <c r="M412" s="1" t="n">
+        <v>0.04154</v>
+      </c>
+      <c r="N412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -18214,6 +19453,9 @@
         <v>1.124</v>
       </c>
       <c r="M413" s="1" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="N413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -18254,9 +19496,12 @@
         <v>0.2625</v>
       </c>
       <c r="L414" s="1" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="M414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="M414" s="1" t="n">
+      <c r="N414" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -18297,9 +19542,12 @@
         <v>0.00122</v>
       </c>
       <c r="L415" s="1" t="n">
+        <v>0.001224</v>
+      </c>
+      <c r="M415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="M415" s="1" t="n">
+      <c r="N415" s="1" t="n">
         <v>0.00122</v>
       </c>
     </row>
@@ -18340,9 +19588,12 @@
         <v>0.03195</v>
       </c>
       <c r="L416" s="1" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="M416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="M416" s="1" t="n">
+      <c r="N416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -18383,9 +19634,12 @@
         <v>0.01467</v>
       </c>
       <c r="L417" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="M417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="M417" s="1" t="n">
+      <c r="N417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -18426,9 +19680,12 @@
         <v>0.1485</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>0.1486</v>
+        <v>0.1488</v>
       </c>
       <c r="M418" s="1" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="N418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -18469,9 +19726,12 @@
         <v>0.04943</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>0.04943</v>
+        <v>0.04952</v>
       </c>
       <c r="M419" s="1" t="n">
+        <v>0.04952</v>
+      </c>
+      <c r="N419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -18512,9 +19772,12 @@
         <v>66.62</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M420" s="1" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="N420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -18558,6 +19821,9 @@
         <v>0.879</v>
       </c>
       <c r="M421" s="1" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="N421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -18598,10 +19864,13 @@
         <v>0.01265</v>
       </c>
       <c r="L422" s="1" t="n">
+        <v>0.012567</v>
+      </c>
+      <c r="M422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="M422" s="1" t="n">
-        <v>0.012645</v>
+      <c r="N422" s="1" t="n">
+        <v>0.012567</v>
       </c>
     </row>
     <row r="423">
@@ -18641,9 +19910,12 @@
         <v>0.01596</v>
       </c>
       <c r="L423" s="1" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="M423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="M423" s="1" t="n">
+      <c r="N423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -18684,9 +19956,12 @@
         <v>0.27102</v>
       </c>
       <c r="L424" s="1" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="M424" s="1" t="n">
         <v>0.27102</v>
       </c>
-      <c r="M424" s="1" t="n">
+      <c r="N424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -18727,9 +20002,12 @@
         <v>0.5996</v>
       </c>
       <c r="L425" s="1" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="M425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="M425" s="1" t="n">
+      <c r="N425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -18770,9 +20048,12 @@
         <v>0.005566</v>
       </c>
       <c r="L426" s="1" t="n">
+        <v>0.005571</v>
+      </c>
+      <c r="M426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="M426" s="1" t="n">
+      <c r="N426" s="1" t="n">
         <v>0.005557</v>
       </c>
     </row>
@@ -18813,9 +20094,12 @@
         <v>0.0491</v>
       </c>
       <c r="L427" s="1" t="n">
-        <v>0.04916</v>
+        <v>0.04927</v>
       </c>
       <c r="M427" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="N427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -18856,9 +20140,12 @@
         <v>0.1266</v>
       </c>
       <c r="L428" s="1" t="n">
-        <v>0.1266</v>
+        <v>0.1272</v>
       </c>
       <c r="M428" s="1" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="N428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -18899,9 +20186,12 @@
         <v>0.003187</v>
       </c>
       <c r="L429" s="1" t="n">
+        <v>0.003188</v>
+      </c>
+      <c r="M429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="M429" s="1" t="n">
+      <c r="N429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -18942,9 +20232,12 @@
         <v>0.03647</v>
       </c>
       <c r="L430" s="1" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="M430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="M430" s="1" t="n">
+      <c r="N430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -18985,9 +20278,12 @@
         <v>0.3989</v>
       </c>
       <c r="L431" s="1" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="M431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="M431" s="1" t="n">
+      <c r="N431" s="1" t="n">
         <v>0.3982</v>
       </c>
     </row>
@@ -19028,9 +20324,12 @@
         <v>0.0045</v>
       </c>
       <c r="L432" s="1" t="n">
+        <v>0.004504</v>
+      </c>
+      <c r="M432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="M432" s="1" t="n">
+      <c r="N432" s="1" t="n">
         <v>0.0045</v>
       </c>
     </row>
@@ -19071,9 +20370,12 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="L433" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M433" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="M433" s="1" t="n">
+      <c r="N433" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -19114,9 +20416,12 @@
         <v>0.01243</v>
       </c>
       <c r="L434" s="1" t="n">
+        <v>0.01243</v>
+      </c>
+      <c r="M434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="M434" s="1" t="n">
+      <c r="N434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -19157,9 +20462,12 @@
         <v>1.981</v>
       </c>
       <c r="L435" s="1" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="M435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="M435" s="1" t="n">
+      <c r="N435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -19200,9 +20508,12 @@
         <v>0.00182</v>
       </c>
       <c r="L436" s="1" t="n">
+        <v>0.001825</v>
+      </c>
+      <c r="M436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="M436" s="1" t="n">
+      <c r="N436" s="1" t="n">
         <v>0.001813</v>
       </c>
     </row>
@@ -19243,9 +20554,12 @@
         <v>0.4419</v>
       </c>
       <c r="L437" s="1" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="M437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="M437" s="1" t="n">
+      <c r="N437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -19286,9 +20600,12 @@
         <v>0.00534</v>
       </c>
       <c r="L438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="M438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="M438" s="1" t="n">
+      <c r="N438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -19329,9 +20646,12 @@
         <v>0.1035</v>
       </c>
       <c r="L439" s="1" t="n">
-        <v>0.1036</v>
+        <v>0.1038</v>
       </c>
       <c r="M439" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="N439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -19372,9 +20692,12 @@
         <v>0.03442</v>
       </c>
       <c r="L440" s="1" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="M440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="M440" s="1" t="n">
+      <c r="N440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -19415,9 +20738,12 @@
         <v>0.08209</v>
       </c>
       <c r="L441" s="1" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="M441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="M441" s="1" t="n">
+      <c r="N441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -19458,9 +20784,12 @@
         <v>1.302</v>
       </c>
       <c r="L442" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="M442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="M442" s="1" t="n">
+      <c r="N442" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -19501,10 +20830,13 @@
         <v>0.07556</v>
       </c>
       <c r="L443" s="1" t="n">
+        <v>0.07549</v>
+      </c>
+      <c r="M443" s="1" t="n">
         <v>0.07581</v>
       </c>
-      <c r="M443" s="1" t="n">
-        <v>0.07550999999999999</v>
+      <c r="N443" s="1" t="n">
+        <v>0.07549</v>
       </c>
     </row>
     <row r="444">
@@ -19544,9 +20876,12 @@
         <v>0.07692</v>
       </c>
       <c r="L444" s="1" t="n">
+        <v>0.07697</v>
+      </c>
+      <c r="M444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="M444" s="1" t="n">
+      <c r="N444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -19587,9 +20922,12 @@
         <v>0.0437</v>
       </c>
       <c r="L445" s="1" t="n">
+        <v>0.04366</v>
+      </c>
+      <c r="M445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="M445" s="1" t="n">
+      <c r="N445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -19630,10 +20968,13 @@
         <v>0.02145</v>
       </c>
       <c r="L446" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="M446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="M446" s="1" t="n">
-        <v>0.02144</v>
+      <c r="N446" s="1" t="n">
+        <v>0.02142</v>
       </c>
     </row>
     <row r="447">
@@ -19673,9 +21014,12 @@
         <v>0.2807</v>
       </c>
       <c r="L447" s="1" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="M447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="M447" s="1" t="n">
+      <c r="N447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -19716,9 +21060,12 @@
         <v>0.0312</v>
       </c>
       <c r="L448" s="1" t="n">
+        <v>0.03123</v>
+      </c>
+      <c r="M448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="M448" s="1" t="n">
+      <c r="N448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -19762,6 +21109,9 @@
         <v>0.00647</v>
       </c>
       <c r="M449" s="1" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="N449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -19802,9 +21152,12 @@
         <v>0.022915</v>
       </c>
       <c r="L450" s="1" t="n">
-        <v>0.023016</v>
+        <v>0.023086</v>
       </c>
       <c r="M450" s="1" t="n">
+        <v>0.023086</v>
+      </c>
+      <c r="N450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -19845,9 +21198,12 @@
         <v>0.04241</v>
       </c>
       <c r="L451" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="M451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="M451" s="1" t="n">
+      <c r="N451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -19888,9 +21244,12 @@
         <v>0.07224</v>
       </c>
       <c r="L452" s="1" t="n">
+        <v>0.07246</v>
+      </c>
+      <c r="M452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="M452" s="1" t="n">
+      <c r="N452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -19931,9 +21290,12 @@
         <v>0.0005951</v>
       </c>
       <c r="L453" s="1" t="n">
+        <v>0.0005927</v>
+      </c>
+      <c r="M453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="M453" s="1" t="n">
+      <c r="N453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -19974,10 +21336,13 @@
         <v>0.307</v>
       </c>
       <c r="L454" s="1" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="M454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="M454" s="1" t="n">
-        <v>0.307</v>
+      <c r="N454" s="1" t="n">
+        <v>0.306</v>
       </c>
     </row>
     <row r="455">
@@ -20017,9 +21382,12 @@
         <v>0.004292</v>
       </c>
       <c r="L455" s="1" t="n">
+        <v>0.004292</v>
+      </c>
+      <c r="M455" s="1" t="n">
         <v>0.004324</v>
       </c>
-      <c r="M455" s="1" t="n">
+      <c r="N455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -20060,9 +21428,12 @@
         <v>0.183</v>
       </c>
       <c r="L456" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="M456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="M456" s="1" t="n">
+      <c r="N456" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -20103,9 +21474,12 @@
         <v>0.04268</v>
       </c>
       <c r="L457" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="M457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="M457" s="1" t="n">
+      <c r="N457" s="1" t="n">
         <v>0.04268</v>
       </c>
     </row>
@@ -20146,9 +21520,12 @@
         <v>0.1459</v>
       </c>
       <c r="L458" s="1" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="M458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="M458" s="1" t="n">
+      <c r="N458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -20189,9 +21566,12 @@
         <v>0.008618000000000001</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>0.008624</v>
+        <v>0.008635</v>
       </c>
       <c r="M459" s="1" t="n">
+        <v>0.008635</v>
+      </c>
+      <c r="N459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -20232,10 +21612,13 @@
         <v>0.007386</v>
       </c>
       <c r="L460" s="1" t="n">
+        <v>0.007357</v>
+      </c>
+      <c r="M460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="M460" s="1" t="n">
-        <v>0.007386</v>
+      <c r="N460" s="1" t="n">
+        <v>0.007357</v>
       </c>
     </row>
     <row r="461">
@@ -20275,9 +21658,12 @@
         <v>0.0001728</v>
       </c>
       <c r="L461" s="1" t="n">
+        <v>0.0001729</v>
+      </c>
+      <c r="M461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="M461" s="1" t="n">
+      <c r="N461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -20318,9 +21704,12 @@
         <v>0.02321</v>
       </c>
       <c r="L462" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="M462" s="1" t="n">
         <v>0.02321</v>
       </c>
-      <c r="M462" s="1" t="n">
+      <c r="N462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -20361,9 +21750,12 @@
         <v>0.03685</v>
       </c>
       <c r="L463" s="1" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="M463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="M463" s="1" t="n">
+      <c r="N463" s="1" t="n">
         <v>0.03685</v>
       </c>
     </row>
@@ -20404,10 +21796,13 @@
         <v>0.3021</v>
       </c>
       <c r="L464" s="1" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="M464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="M464" s="1" t="n">
-        <v>0.3021</v>
+      <c r="N464" s="1" t="n">
+        <v>0.3013</v>
       </c>
     </row>
     <row r="465">
@@ -20447,9 +21842,12 @@
         <v>0.03909</v>
       </c>
       <c r="L465" s="1" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="M465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="M465" s="1" t="n">
+      <c r="N465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -20490,9 +21888,12 @@
         <v>2.668</v>
       </c>
       <c r="L466" s="1" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="M466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="M466" s="1" t="n">
+      <c r="N466" s="1" t="n">
         <v>2.667</v>
       </c>
     </row>
@@ -20533,9 +21934,12 @@
         <v>0.03394</v>
       </c>
       <c r="L467" s="1" t="n">
+        <v>0.03402</v>
+      </c>
+      <c r="M467" s="1" t="n">
         <v>0.03436</v>
       </c>
-      <c r="M467" s="1" t="n">
+      <c r="N467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -20576,9 +21980,12 @@
         <v>0.1761</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>0.1765</v>
+        <v>0.1767</v>
       </c>
       <c r="M468" s="1" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="N468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -20619,9 +22026,12 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="M469" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="N469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -20662,9 +22072,12 @@
         <v>0.06748999999999999</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>0.06757000000000001</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="M470" s="1" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="N470" s="1" t="n">
         <v>0.06716999999999999</v>
       </c>
     </row>
@@ -20705,9 +22118,12 @@
         <v>0.04001</v>
       </c>
       <c r="L471" s="1" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="M471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="M471" s="1" t="n">
+      <c r="N471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -20748,9 +22164,12 @@
         <v>0.2472</v>
       </c>
       <c r="L472" s="1" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="M472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="M472" s="1" t="n">
+      <c r="N472" s="1" t="n">
         <v>0.2472</v>
       </c>
     </row>
@@ -20791,10 +22210,13 @@
         <v>0.016393</v>
       </c>
       <c r="L473" s="1" t="n">
+        <v>0.016367</v>
+      </c>
+      <c r="M473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="M473" s="1" t="n">
-        <v>0.016393</v>
+      <c r="N473" s="1" t="n">
+        <v>0.016367</v>
       </c>
     </row>
     <row r="474">
@@ -20834,9 +22256,12 @@
         <v>0.1156</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>0.1157</v>
+        <v>0.1158</v>
       </c>
       <c r="M474" s="1" t="n">
+        <v>0.1158</v>
+      </c>
+      <c r="N474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -20877,9 +22302,12 @@
         <v>0.04286</v>
       </c>
       <c r="L475" s="1" t="n">
+        <v>0.04299</v>
+      </c>
+      <c r="M475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="M475" s="1" t="n">
+      <c r="N475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -20920,9 +22348,12 @@
         <v>0.2072</v>
       </c>
       <c r="L476" s="1" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="M476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="M476" s="1" t="n">
+      <c r="N476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -20963,9 +22394,12 @@
         <v>0.006813</v>
       </c>
       <c r="L477" s="1" t="n">
+        <v>0.006833</v>
+      </c>
+      <c r="M477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="M477" s="1" t="n">
+      <c r="N477" s="1" t="n">
         <v>0.006796</v>
       </c>
     </row>
@@ -21006,9 +22440,12 @@
         <v>0.01784</v>
       </c>
       <c r="L478" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="M478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="M478" s="1" t="n">
+      <c r="N478" s="1" t="n">
         <v>0.01784</v>
       </c>
     </row>
@@ -21049,9 +22486,12 @@
         <v>0.04693</v>
       </c>
       <c r="L479" s="1" t="n">
+        <v>0.04688</v>
+      </c>
+      <c r="M479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="M479" s="1" t="n">
+      <c r="N479" s="1" t="n">
         <v>0.04683</v>
       </c>
     </row>
@@ -21092,9 +22532,12 @@
         <v>0.26161</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>0.26166</v>
+        <v>0.2618</v>
       </c>
       <c r="M480" s="1" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="N480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -21135,9 +22578,12 @@
         <v>0.01229</v>
       </c>
       <c r="L481" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="M481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="M481" s="1" t="n">
+      <c r="N481" s="1" t="n">
         <v>0.01229</v>
       </c>
     </row>
@@ -21178,9 +22624,12 @@
         <v>0.004097</v>
       </c>
       <c r="L482" s="1" t="n">
+        <v>0.004097</v>
+      </c>
+      <c r="M482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="M482" s="1" t="n">
+      <c r="N482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -21221,9 +22670,12 @@
         <v>0.1229</v>
       </c>
       <c r="L483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="M483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="M483" s="1" t="n">
+      <c r="N483" s="1" t="n">
         <v>0.1229</v>
       </c>
     </row>
@@ -21264,9 +22716,12 @@
         <v>0.02187</v>
       </c>
       <c r="L484" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="M484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="M484" s="1" t="n">
+      <c r="N484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -21307,10 +22762,13 @@
         <v>0.04552</v>
       </c>
       <c r="L485" s="1" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="M485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="M485" s="1" t="n">
-        <v>0.04548</v>
+      <c r="N485" s="1" t="n">
+        <v>0.04514</v>
       </c>
     </row>
     <row r="486">
@@ -21350,9 +22808,12 @@
         <v>0.1731</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>0.1736</v>
+        <v>0.1738</v>
       </c>
       <c r="M486" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="N486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -21393,9 +22854,12 @@
         <v>0.2726</v>
       </c>
       <c r="L487" s="1" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="M487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="M487" s="1" t="n">
+      <c r="N487" s="1" t="n">
         <v>0.2726</v>
       </c>
     </row>
@@ -21439,6 +22903,9 @@
         <v>0.0463</v>
       </c>
       <c r="M488" s="1" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="N488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -21479,10 +22946,13 @@
         <v>0.0002152</v>
       </c>
       <c r="L489" s="1" t="n">
+        <v>0.0002149</v>
+      </c>
+      <c r="M489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="M489" s="1" t="n">
-        <v>0.0002151</v>
+      <c r="N489" s="1" t="n">
+        <v>0.0002149</v>
       </c>
     </row>
     <row r="490">
@@ -21522,9 +22992,12 @@
         <v>1.777</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>1.778</v>
+        <v>1.779</v>
       </c>
       <c r="M490" s="1" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="N490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -21565,9 +23038,12 @@
         <v>16.058</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>16.083</v>
+        <v>16.087</v>
       </c>
       <c r="M491" s="1" t="n">
+        <v>16.087</v>
+      </c>
+      <c r="N491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -21608,9 +23084,12 @@
         <v>0.06677</v>
       </c>
       <c r="L492" s="1" t="n">
+        <v>0.06676</v>
+      </c>
+      <c r="M492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="M492" s="1" t="n">
+      <c r="N492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -21651,9 +23130,12 @@
         <v>0.06744</v>
       </c>
       <c r="L493" s="1" t="n">
+        <v>0.06756</v>
+      </c>
+      <c r="M493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="M493" s="1" t="n">
+      <c r="N493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -21694,9 +23176,12 @@
         <v>0.009461000000000001</v>
       </c>
       <c r="L494" s="1" t="n">
+        <v>0.009446</v>
+      </c>
+      <c r="M494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="M494" s="1" t="n">
+      <c r="N494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -21737,10 +23222,13 @@
         <v>0.005874</v>
       </c>
       <c r="L495" s="1" t="n">
+        <v>0.005829</v>
+      </c>
+      <c r="M495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="M495" s="1" t="n">
-        <v>0.005874</v>
+      <c r="N495" s="1" t="n">
+        <v>0.005829</v>
       </c>
     </row>
     <row r="496">
@@ -21780,9 +23268,12 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="L496" s="1" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="M496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="M496" s="1" t="n">
+      <c r="N496" s="1" t="n">
         <v>0.00987</v>
       </c>
     </row>
@@ -21823,9 +23314,12 @@
         <v>0.04412</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>0.04412</v>
+        <v>0.0449</v>
       </c>
       <c r="M497" s="1" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="N497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -21866,10 +23360,13 @@
         <v>0.006384</v>
       </c>
       <c r="L498" s="1" t="n">
+        <v>0.006374</v>
+      </c>
+      <c r="M498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="M498" s="1" t="n">
-        <v>0.006384</v>
+      <c r="N498" s="1" t="n">
+        <v>0.006374</v>
       </c>
     </row>
     <row r="499">
@@ -21909,9 +23406,12 @@
         <v>0.01046</v>
       </c>
       <c r="L499" s="1" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="M499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="M499" s="1" t="n">
+      <c r="N499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -21952,9 +23452,12 @@
         <v>0.5088</v>
       </c>
       <c r="L500" s="1" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="M500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="M500" s="1" t="n">
+      <c r="N500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -21995,9 +23498,12 @@
         <v>0.03206</v>
       </c>
       <c r="L501" s="1" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="M501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="M501" s="1" t="n">
+      <c r="N501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -22038,9 +23544,12 @@
         <v>0.4409</v>
       </c>
       <c r="L502" s="1" t="n">
-        <v>0.4409</v>
+        <v>0.4436</v>
       </c>
       <c r="M502" s="1" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="N502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -22081,9 +23590,12 @@
         <v>0.999341</v>
       </c>
       <c r="L503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="M503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="M503" s="1" t="n">
+      <c r="N503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -22124,10 +23636,13 @@
         <v>0.03514</v>
       </c>
       <c r="L504" s="1" t="n">
+        <v>0.03509</v>
+      </c>
+      <c r="M504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="M504" s="1" t="n">
-        <v>0.03514</v>
+      <c r="N504" s="1" t="n">
+        <v>0.03509</v>
       </c>
     </row>
     <row r="505">
@@ -22167,9 +23682,12 @@
         <v>0.004944</v>
       </c>
       <c r="L505" s="1" t="n">
-        <v>0.00495</v>
+        <v>0.004962</v>
       </c>
       <c r="M505" s="1" t="n">
+        <v>0.004962</v>
+      </c>
+      <c r="N505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -22213,6 +23731,9 @@
         <v>0.01397</v>
       </c>
       <c r="M506" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="N506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -22253,9 +23774,12 @@
         <v>0.003486</v>
       </c>
       <c r="L507" s="1" t="n">
+        <v>0.003477</v>
+      </c>
+      <c r="M507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="M507" s="1" t="n">
+      <c r="N507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -22296,9 +23820,12 @@
         <v>1.417</v>
       </c>
       <c r="L508" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="M508" s="1" t="n">
+      <c r="N508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -22339,9 +23866,12 @@
         <v>0.005076</v>
       </c>
       <c r="L509" s="1" t="n">
+        <v>0.005087</v>
+      </c>
+      <c r="M509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="M509" s="1" t="n">
+      <c r="N509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -22385,6 +23915,9 @@
         <v>0.01577</v>
       </c>
       <c r="M510" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="N510" s="1" t="n">
         <v>0.01571</v>
       </c>
     </row>
@@ -22425,9 +23958,12 @@
         <v>0.08248999999999999</v>
       </c>
       <c r="L511" s="1" t="n">
+        <v>0.08252</v>
+      </c>
+      <c r="M511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="M511" s="1" t="n">
+      <c r="N511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -22468,9 +24004,12 @@
         <v>0.007093</v>
       </c>
       <c r="L512" s="1" t="n">
+        <v>0.007101</v>
+      </c>
+      <c r="M512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="M512" s="1" t="n">
+      <c r="N512" s="1" t="n">
         <v>0.007093</v>
       </c>
     </row>
@@ -22511,9 +24050,12 @@
         <v>0.01489</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>0.01493</v>
+        <v>0.01495</v>
       </c>
       <c r="M513" s="1" t="n">
+        <v>0.01495</v>
+      </c>
+      <c r="N513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -22554,9 +24096,12 @@
         <v>0.04737</v>
       </c>
       <c r="L514" s="1" t="n">
+        <v>0.04754</v>
+      </c>
+      <c r="M514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="M514" s="1" t="n">
+      <c r="N514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -22600,6 +24145,9 @@
         <v>0.01827</v>
       </c>
       <c r="M515" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="N515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -22640,9 +24188,12 @@
         <v>0.0005792</v>
       </c>
       <c r="L516" s="1" t="n">
+        <v>0.0005792</v>
+      </c>
+      <c r="M516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="M516" s="1" t="n">
+      <c r="N516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -22683,9 +24234,12 @@
         <v>0.07857</v>
       </c>
       <c r="L517" s="1" t="n">
+        <v>0.07872</v>
+      </c>
+      <c r="M517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="M517" s="1" t="n">
+      <c r="N517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -22726,9 +24280,12 @@
         <v>0.006381</v>
       </c>
       <c r="L518" s="1" t="n">
+        <v>0.006387</v>
+      </c>
+      <c r="M518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="M518" s="1" t="n">
+      <c r="N518" s="1" t="n">
         <v>0.006373</v>
       </c>
     </row>
@@ -22769,9 +24326,12 @@
         <v>0.05784</v>
       </c>
       <c r="L519" s="1" t="n">
+        <v>0.05791</v>
+      </c>
+      <c r="M519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="M519" s="1" t="n">
+      <c r="N519" s="1" t="n">
         <v>0.05784</v>
       </c>
     </row>
@@ -22812,9 +24372,12 @@
         <v>0.10484</v>
       </c>
       <c r="L520" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="M520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="M520" s="1" t="n">
+      <c r="N520" s="1" t="n">
         <v>0.10469</v>
       </c>
     </row>
@@ -22855,9 +24418,12 @@
         <v>0.01797</v>
       </c>
       <c r="L521" s="1" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="M521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="M521" s="1" t="n">
+      <c r="N521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -22898,9 +24464,12 @@
         <v>0.01651</v>
       </c>
       <c r="L522" s="1" t="n">
+        <v>0.01652</v>
+      </c>
+      <c r="M522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="M522" s="1" t="n">
+      <c r="N522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -22941,9 +24510,12 @@
         <v>0.01091</v>
       </c>
       <c r="L523" s="1" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="M523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="M523" s="1" t="n">
+      <c r="N523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -22984,9 +24556,12 @@
         <v>0.007158</v>
       </c>
       <c r="L524" s="1" t="n">
+        <v>0.007108</v>
+      </c>
+      <c r="M524" s="1" t="n">
         <v>0.007158</v>
       </c>
-      <c r="M524" s="1" t="n">
+      <c r="N524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -23027,9 +24602,12 @@
         <v>0.005889</v>
       </c>
       <c r="L525" s="1" t="n">
+        <v>0.005908</v>
+      </c>
+      <c r="M525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="M525" s="1" t="n">
+      <c r="N525" s="1" t="n">
         <v>0.005889</v>
       </c>
     </row>
@@ -23070,9 +24648,12 @@
         <v>0.001439</v>
       </c>
       <c r="L526" s="1" t="n">
+        <v>0.001443</v>
+      </c>
+      <c r="M526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="M526" s="1" t="n">
+      <c r="N526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -23116,6 +24697,9 @@
         <v>0.374</v>
       </c>
       <c r="M527" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="N527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -23159,6 +24743,9 @@
         <v>0.00521</v>
       </c>
       <c r="M528" s="1" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="N528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -23199,9 +24786,12 @@
         <v>2.949</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>2.951</v>
+        <v>2.96</v>
       </c>
       <c r="M529" s="1" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -23242,9 +24832,12 @@
         <v>0.156</v>
       </c>
       <c r="L530" s="1" t="n">
-        <v>0.1562</v>
+        <v>0.1565</v>
       </c>
       <c r="M530" s="1" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="N530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -23285,9 +24878,12 @@
         <v>2539</v>
       </c>
       <c r="L531" s="1" t="n">
+        <v>2541</v>
+      </c>
+      <c r="M531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="M531" s="1" t="n">
+      <c r="N531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -23328,9 +24924,12 @@
         <v>0.03925</v>
       </c>
       <c r="L532" s="1" t="n">
-        <v>0.03929</v>
+        <v>0.0393</v>
       </c>
       <c r="M532" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="N532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -23371,9 +24970,12 @@
         <v>0.0217</v>
       </c>
       <c r="L533" s="1" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="M533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="M533" s="1" t="n">
+      <c r="N533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -23414,9 +25016,12 @@
         <v>0.07369000000000001</v>
       </c>
       <c r="L534" s="1" t="n">
-        <v>0.0737</v>
+        <v>0.07374</v>
       </c>
       <c r="M534" s="1" t="n">
+        <v>0.07374</v>
+      </c>
+      <c r="N534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -23457,9 +25062,12 @@
         <v>0.007931000000000001</v>
       </c>
       <c r="L535" s="1" t="n">
-        <v>0.007931000000000001</v>
+        <v>0.008029</v>
       </c>
       <c r="M535" s="1" t="n">
+        <v>0.008029</v>
+      </c>
+      <c r="N535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -23500,9 +25108,12 @@
         <v>0.05019</v>
       </c>
       <c r="L536" s="1" t="n">
+        <v>0.05021</v>
+      </c>
+      <c r="M536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="M536" s="1" t="n">
+      <c r="N536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -23543,9 +25154,12 @@
         <v>0.00404</v>
       </c>
       <c r="L537" s="1" t="n">
+        <v>0.00404</v>
+      </c>
+      <c r="M537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="M537" s="1" t="n">
+      <c r="N537" s="1" t="n">
         <v>0.00404</v>
       </c>
     </row>
@@ -23586,9 +25200,12 @@
         <v>0.08298</v>
       </c>
       <c r="L538" s="1" t="n">
+        <v>0.08296000000000001</v>
+      </c>
+      <c r="M538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="M538" s="1" t="n">
+      <c r="N538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -23629,9 +25246,12 @@
         <v>0.02505</v>
       </c>
       <c r="L539" s="1" t="n">
+        <v>0.02496</v>
+      </c>
+      <c r="M539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="M539" s="1" t="n">
+      <c r="N539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -23672,10 +25292,13 @@
         <v>0.08463</v>
       </c>
       <c r="L540" s="1" t="n">
+        <v>0.08433</v>
+      </c>
+      <c r="M540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="M540" s="1" t="n">
-        <v>0.08461</v>
+      <c r="N540" s="1" t="n">
+        <v>0.08433</v>
       </c>
     </row>
     <row r="541">
@@ -23715,10 +25338,13 @@
         <v>0.01892</v>
       </c>
       <c r="L541" s="1" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="M541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="M541" s="1" t="n">
-        <v>0.01891</v>
+      <c r="N541" s="1" t="n">
+        <v>0.0189</v>
       </c>
     </row>
     <row r="542">
@@ -23758,10 +25384,13 @@
         <v>0.01694</v>
       </c>
       <c r="L542" s="1" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="M542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="M542" s="1" t="n">
-        <v>0.01693</v>
+      <c r="N542" s="1" t="n">
+        <v>0.0169</v>
       </c>
     </row>
     <row r="543">
@@ -23801,9 +25430,12 @@
         <v>0.1047</v>
       </c>
       <c r="L543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="M543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="M543" s="1" t="n">
+      <c r="N543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N543"/>
+  <dimension ref="A1:O543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -431,8 +431,9 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,10 +499,15 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>price_03:00</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -547,9 +553,12 @@
         <v>70614.8</v>
       </c>
       <c r="M2" s="1" t="n">
+        <v>70623.5</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="O2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -593,9 +602,12 @@
         <v>2074.69</v>
       </c>
       <c r="M3" s="1" t="n">
+        <v>2075.73</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="O3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -639,9 +651,12 @@
         <v>86.94</v>
       </c>
       <c r="M4" s="1" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -685,9 +700,12 @@
         <v>4.037</v>
       </c>
       <c r="M5" s="1" t="n">
+        <v>4.022</v>
+      </c>
+      <c r="N5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>4.02</v>
       </c>
     </row>
@@ -731,9 +749,12 @@
         <v>0.09458999999999999</v>
       </c>
       <c r="M6" s="1" t="n">
+        <v>0.09464</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -777,9 +798,12 @@
         <v>1.3901</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>1.3903</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -823,9 +847,12 @@
         <v>22.652</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>22.688</v>
+        <v>22.772</v>
       </c>
       <c r="N8" s="1" t="n">
+        <v>22.772</v>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -869,9 +896,12 @@
         <v>0.002046</v>
       </c>
       <c r="M9" s="1" t="n">
+        <v>0.002003</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>0.001977</v>
       </c>
     </row>
@@ -915,9 +945,12 @@
         <v>0.00996</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>0.009712</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="O10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -961,10 +994,13 @@
         <v>0.15933</v>
       </c>
       <c r="M11" s="1" t="n">
+        <v>0.15764</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>0.15789</v>
+      <c r="O11" s="1" t="n">
+        <v>0.15764</v>
       </c>
     </row>
     <row r="12">
@@ -1007,9 +1043,12 @@
         <v>0.011602</v>
       </c>
       <c r="M12" s="1" t="n">
+        <v>0.011484</v>
+      </c>
+      <c r="N12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="O12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -1053,9 +1092,12 @@
         <v>37.812</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>37.976</v>
+      </c>
+      <c r="N13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="O13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1099,9 +1141,12 @@
         <v>653.09</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>653.1900000000001</v>
+      </c>
+      <c r="N14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="O14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1145,9 +1190,12 @@
         <v>209.36</v>
       </c>
       <c r="M15" s="1" t="n">
+        <v>209.43</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="O15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1191,9 +1239,12 @@
         <v>0.0033224</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>0.003323</v>
+      </c>
+      <c r="N16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="O16" s="1" t="n">
         <v>0.0033224</v>
       </c>
     </row>
@@ -1237,9 +1288,12 @@
         <v>238.81</v>
       </c>
       <c r="M17" s="1" t="n">
+        <v>238.42</v>
+      </c>
+      <c r="N17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="O17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1283,9 +1337,12 @@
         <v>0.9897</v>
       </c>
       <c r="M18" s="1" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="N18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="O18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1329,9 +1386,12 @@
         <v>1.0645</v>
       </c>
       <c r="M19" s="1" t="n">
+        <v>1.0532</v>
+      </c>
+      <c r="N19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="N19" s="1" t="n">
+      <c r="O19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1375,9 +1435,12 @@
         <v>0.2589</v>
       </c>
       <c r="M20" s="1" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="N20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="N20" s="1" t="n">
+      <c r="O20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1421,9 +1484,12 @@
         <v>0.5994</v>
       </c>
       <c r="M21" s="1" t="n">
+        <v>0.59712</v>
+      </c>
+      <c r="N21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="O21" s="1" t="n">
         <v>0.59476</v>
       </c>
     </row>
@@ -1467,9 +1533,12 @@
         <v>9.02</v>
       </c>
       <c r="M22" s="1" t="n">
+        <v>9.015000000000001</v>
+      </c>
+      <c r="N22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="O22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1513,9 +1582,12 @@
         <v>0.02414</v>
       </c>
       <c r="M23" s="1" t="n">
+        <v>0.02407</v>
+      </c>
+      <c r="N23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="O23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1559,9 +1631,12 @@
         <v>9.571999999999999</v>
       </c>
       <c r="M24" s="1" t="n">
+        <v>9.564</v>
+      </c>
+      <c r="N24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="N24" s="1" t="n">
+      <c r="O24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1605,9 +1680,12 @@
         <v>1.223</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>1.228</v>
+        <v>1.229</v>
       </c>
       <c r="N25" s="1" t="n">
+        <v>1.229</v>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1651,9 +1729,12 @@
         <v>0.07113999999999999</v>
       </c>
       <c r="M26" s="1" t="n">
+        <v>0.07086000000000001</v>
+      </c>
+      <c r="N26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="N26" s="1" t="n">
+      <c r="O26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1697,9 +1778,12 @@
         <v>1.424</v>
       </c>
       <c r="M27" s="1" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="N27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="N27" s="1" t="n">
+      <c r="O27" s="1" t="n">
         <v>1.423</v>
       </c>
     </row>
@@ -1743,9 +1827,12 @@
         <v>1.306</v>
       </c>
       <c r="M28" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="N28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="N28" s="1" t="n">
+      <c r="O28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -1789,9 +1876,12 @@
         <v>462.74</v>
       </c>
       <c r="M29" s="1" t="n">
+        <v>462.31</v>
+      </c>
+      <c r="N29" s="1" t="n">
         <v>463.21</v>
       </c>
-      <c r="N29" s="1" t="n">
+      <c r="O29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -1835,9 +1925,12 @@
         <v>1.2992</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>1.2992</v>
+        <v>1.3093</v>
       </c>
       <c r="N30" s="1" t="n">
+        <v>1.3093</v>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1881,9 +1974,12 @@
         <v>5023.85</v>
       </c>
       <c r="M31" s="1" t="n">
+        <v>5023.33</v>
+      </c>
+      <c r="N31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="N31" s="1" t="n">
+      <c r="O31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1927,9 +2023,12 @@
         <v>0.903</v>
       </c>
       <c r="M32" s="1" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="N32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="N32" s="1" t="n">
+      <c r="O32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1973,9 +2072,12 @@
         <v>0.001973</v>
       </c>
       <c r="M33" s="1" t="n">
+        <v>0.001975</v>
+      </c>
+      <c r="N33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="N33" s="1" t="n">
+      <c r="O33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -2019,9 +2121,12 @@
         <v>0.16907</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.17106</v>
+        <v>0.17183</v>
       </c>
       <c r="N34" s="1" t="n">
+        <v>0.17183</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2065,9 +2170,12 @@
         <v>0.2967</v>
       </c>
       <c r="M35" s="1" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="N35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="N35" s="1" t="n">
+      <c r="O35" s="1" t="n">
         <v>0.2967</v>
       </c>
     </row>
@@ -2111,9 +2219,12 @@
         <v>1.78</v>
       </c>
       <c r="M36" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="N36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="N36" s="1" t="n">
+      <c r="O36" s="1" t="n">
         <v>1.779</v>
       </c>
     </row>
@@ -2157,9 +2268,12 @@
         <v>110.42</v>
       </c>
       <c r="M37" s="1" t="n">
+        <v>110.32</v>
+      </c>
+      <c r="N37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="N37" s="1" t="n">
+      <c r="O37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -2203,10 +2317,13 @@
         <v>0.22241</v>
       </c>
       <c r="M38" s="1" t="n">
+        <v>0.22079</v>
+      </c>
+      <c r="N38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="N38" s="1" t="n">
-        <v>0.22169</v>
+      <c r="O38" s="1" t="n">
+        <v>0.22079</v>
       </c>
     </row>
     <row r="39">
@@ -2249,10 +2366,13 @@
         <v>0.1075</v>
       </c>
       <c r="M39" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="N39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="N39" s="1" t="n">
-        <v>0.1074</v>
+      <c r="O39" s="1" t="n">
+        <v>0.1073</v>
       </c>
     </row>
     <row r="40">
@@ -2295,9 +2415,12 @@
         <v>0.37324</v>
       </c>
       <c r="M40" s="1" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="N40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="N40" s="1" t="n">
+      <c r="O40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2344,6 +2467,9 @@
         <v>54.7</v>
       </c>
       <c r="N41" s="1" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="O41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2387,9 +2513,12 @@
         <v>0.0010704</v>
       </c>
       <c r="M42" s="1" t="n">
+        <v>0.0010695</v>
+      </c>
+      <c r="N42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="N42" s="1" t="n">
+      <c r="O42" s="1" t="n">
         <v>0.0010666</v>
       </c>
     </row>
@@ -2433,9 +2562,12 @@
         <v>6.41</v>
       </c>
       <c r="M43" s="1" t="n">
+        <v>6.441</v>
+      </c>
+      <c r="N43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="N43" s="1" t="n">
+      <c r="O43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -2479,9 +2611,12 @@
         <v>0.6352</v>
       </c>
       <c r="M44" s="1" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="N44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="N44" s="1" t="n">
+      <c r="O44" s="1" t="n">
         <v>0.6324</v>
       </c>
     </row>
@@ -2525,9 +2660,12 @@
         <v>0.3534</v>
       </c>
       <c r="M45" s="1" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="N45" s="1" t="n">
+      <c r="O45" s="1" t="n">
         <v>0.3533</v>
       </c>
     </row>
@@ -2571,9 +2709,12 @@
         <v>0.03294</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>0.03294</v>
+        <v>0.03298</v>
       </c>
       <c r="N46" s="1" t="n">
+        <v>0.03298</v>
+      </c>
+      <c r="O46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2617,9 +2758,12 @@
         <v>0.07209</v>
       </c>
       <c r="M47" s="1" t="n">
+        <v>0.07213</v>
+      </c>
+      <c r="N47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="N47" s="1" t="n">
+      <c r="O47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -2663,9 +2807,12 @@
         <v>0.7071</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.7071</v>
+        <v>0.7088</v>
       </c>
       <c r="N48" s="1" t="n">
+        <v>0.7088</v>
+      </c>
+      <c r="O48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -2709,9 +2856,12 @@
         <v>0.004405</v>
       </c>
       <c r="M49" s="1" t="n">
+        <v>0.00449</v>
+      </c>
+      <c r="N49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="N49" s="1" t="n">
+      <c r="O49" s="1" t="n">
         <v>0.004361</v>
       </c>
     </row>
@@ -2755,9 +2905,12 @@
         <v>0.1037</v>
       </c>
       <c r="M50" s="1" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="N50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="N50" s="1" t="n">
+      <c r="O50" s="1" t="n">
         <v>0.1037</v>
       </c>
     </row>
@@ -2801,9 +2954,12 @@
         <v>0.04066</v>
       </c>
       <c r="M51" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="N51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="N51" s="1" t="n">
+      <c r="O51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -2847,9 +3003,12 @@
         <v>0.1652</v>
       </c>
       <c r="M52" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="N52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="N52" s="1" t="n">
+      <c r="O52" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -2893,10 +3052,13 @@
         <v>0.02016</v>
       </c>
       <c r="M53" s="1" t="n">
+        <v>0.02002</v>
+      </c>
+      <c r="N53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="N53" s="1" t="n">
-        <v>0.02003</v>
+      <c r="O53" s="1" t="n">
+        <v>0.02002</v>
       </c>
     </row>
     <row r="54">
@@ -2939,9 +3101,12 @@
         <v>0.007206</v>
       </c>
       <c r="M54" s="1" t="n">
+        <v>0.007202</v>
+      </c>
+      <c r="N54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="N54" s="1" t="n">
+      <c r="O54" s="1" t="n">
         <v>0.007198</v>
       </c>
     </row>
@@ -2985,9 +3150,12 @@
         <v>3.916</v>
       </c>
       <c r="M55" s="1" t="n">
+        <v>3.915</v>
+      </c>
+      <c r="N55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="N55" s="1" t="n">
+      <c r="O55" s="1" t="n">
         <v>3.911</v>
       </c>
     </row>
@@ -3031,9 +3199,12 @@
         <v>0.017192</v>
       </c>
       <c r="M56" s="1" t="n">
+        <v>0.017133</v>
+      </c>
+      <c r="N56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="N56" s="1" t="n">
+      <c r="O56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -3077,10 +3248,13 @@
         <v>0.1096</v>
       </c>
       <c r="M57" s="1" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="N57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="N57" s="1" t="n">
-        <v>0.1095</v>
+      <c r="O57" s="1" t="n">
+        <v>0.1094</v>
       </c>
     </row>
     <row r="58">
@@ -3123,9 +3297,12 @@
         <v>2.658</v>
       </c>
       <c r="M58" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="N58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="N58" s="1" t="n">
+      <c r="O58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -3169,9 +3346,12 @@
         <v>0.1592</v>
       </c>
       <c r="M59" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="N59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="N59" s="1" t="n">
+      <c r="O59" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -3215,10 +3395,13 @@
         <v>0.005882</v>
       </c>
       <c r="M60" s="1" t="n">
+        <v>0.00588</v>
+      </c>
+      <c r="N60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="N60" s="1" t="n">
-        <v>0.005882</v>
+      <c r="O60" s="1" t="n">
+        <v>0.00588</v>
       </c>
     </row>
     <row r="61">
@@ -3261,9 +3444,12 @@
         <v>0.09200999999999999</v>
       </c>
       <c r="M61" s="1" t="n">
+        <v>0.09193</v>
+      </c>
+      <c r="N61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="N61" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>0.09188</v>
       </c>
     </row>
@@ -3307,9 +3493,12 @@
         <v>0.9127999999999999</v>
       </c>
       <c r="M62" s="1" t="n">
+        <v>0.9121</v>
+      </c>
+      <c r="N62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="N62" s="1" t="n">
+      <c r="O62" s="1" t="n">
         <v>0.9112</v>
       </c>
     </row>
@@ -3353,9 +3542,12 @@
         <v>0.781</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="N63" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="O63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -3399,9 +3591,12 @@
         <v>0.04649</v>
       </c>
       <c r="M64" s="1" t="n">
+        <v>0.04626</v>
+      </c>
+      <c r="N64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="N64" s="1" t="n">
+      <c r="O64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -3445,9 +3640,12 @@
         <v>358.18</v>
       </c>
       <c r="M65" s="1" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="N65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="N65" s="1" t="n">
+      <c r="O65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -3491,10 +3689,13 @@
         <v>0.12432</v>
       </c>
       <c r="M66" s="1" t="n">
+        <v>0.12395</v>
+      </c>
+      <c r="N66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="N66" s="1" t="n">
-        <v>0.12419</v>
+      <c r="O66" s="1" t="n">
+        <v>0.12395</v>
       </c>
     </row>
     <row r="67">
@@ -3537,10 +3738,13 @@
         <v>0.2291</v>
       </c>
       <c r="M67" s="1" t="n">
+        <v>0.2281</v>
+      </c>
+      <c r="N67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="N67" s="1" t="n">
-        <v>0.2291</v>
+      <c r="O67" s="1" t="n">
+        <v>0.2281</v>
       </c>
     </row>
     <row r="68">
@@ -3583,9 +3787,12 @@
         <v>0.0034</v>
       </c>
       <c r="M68" s="1" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="N68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="N68" s="1" t="n">
+      <c r="O68" s="1" t="n">
         <v>0.00339</v>
       </c>
     </row>
@@ -3629,10 +3836,13 @@
         <v>0.1735</v>
       </c>
       <c r="M69" s="1" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="N69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="N69" s="1" t="n">
-        <v>0.1735</v>
+      <c r="O69" s="1" t="n">
+        <v>0.1734</v>
       </c>
     </row>
     <row r="70">
@@ -3675,9 +3885,12 @@
         <v>0.1644</v>
       </c>
       <c r="M70" s="1" t="n">
+        <v>0.16463</v>
+      </c>
+      <c r="N70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="N70" s="1" t="n">
+      <c r="O70" s="1" t="n">
         <v>0.1639</v>
       </c>
     </row>
@@ -3721,9 +3934,12 @@
         <v>0.3562</v>
       </c>
       <c r="M71" s="1" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="N71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="N71" s="1" t="n">
+      <c r="O71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -3767,9 +3983,12 @@
         <v>0.7095</v>
       </c>
       <c r="M72" s="1" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="N72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="N72" s="1" t="n">
+      <c r="O72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -3813,9 +4032,12 @@
         <v>0.00869</v>
       </c>
       <c r="M73" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="N73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="N73" s="1" t="n">
+      <c r="O73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -3859,9 +4081,12 @@
         <v>0.005985</v>
       </c>
       <c r="M74" s="1" t="n">
+        <v>0.005984</v>
+      </c>
+      <c r="N74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="N74" s="1" t="n">
+      <c r="O74" s="1" t="n">
         <v>0.005967</v>
       </c>
     </row>
@@ -3905,9 +4130,12 @@
         <v>0.226</v>
       </c>
       <c r="M75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="N75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="N75" s="1" t="n">
+      <c r="O75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -3951,9 +4179,12 @@
         <v>0.3242</v>
       </c>
       <c r="M76" s="1" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="N76" s="1" t="n">
         <v>0.3265</v>
       </c>
-      <c r="N76" s="1" t="n">
+      <c r="O76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -3997,9 +4228,12 @@
         <v>0.1005</v>
       </c>
       <c r="M77" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="N77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="N77" s="1" t="n">
+      <c r="O77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -4043,9 +4277,12 @@
         <v>0.1231</v>
       </c>
       <c r="M78" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="N78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="N78" s="1" t="n">
+      <c r="O78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -4089,9 +4326,12 @@
         <v>0.07181999999999999</v>
       </c>
       <c r="M79" s="1" t="n">
-        <v>0.07277</v>
+        <v>0.07353</v>
       </c>
       <c r="N79" s="1" t="n">
+        <v>0.07353</v>
+      </c>
+      <c r="O79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -4135,9 +4375,12 @@
         <v>0.04698</v>
       </c>
       <c r="M80" s="1" t="n">
+        <v>0.04685</v>
+      </c>
+      <c r="N80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="N80" s="1" t="n">
+      <c r="O80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -4181,9 +4424,12 @@
         <v>0.000236</v>
       </c>
       <c r="M81" s="1" t="n">
+        <v>0.000233</v>
+      </c>
+      <c r="N81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="N81" s="1" t="n">
+      <c r="O81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -4227,9 +4473,12 @@
         <v>8.227</v>
       </c>
       <c r="M82" s="1" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="N82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="N82" s="1" t="n">
+      <c r="O82" s="1" t="n">
         <v>8.206</v>
       </c>
     </row>
@@ -4273,9 +4522,12 @@
         <v>0.0005756</v>
       </c>
       <c r="M83" s="1" t="n">
+        <v>0.0005816</v>
+      </c>
+      <c r="N83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="N83" s="1" t="n">
+      <c r="O83" s="1" t="n">
         <v>0.0005756</v>
       </c>
     </row>
@@ -4319,9 +4571,12 @@
         <v>0.444</v>
       </c>
       <c r="M84" s="1" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="N84" s="1" t="n">
         <v>0.4457</v>
       </c>
-      <c r="N84" s="1" t="n">
+      <c r="O84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4365,9 +4620,12 @@
         <v>0.06243</v>
       </c>
       <c r="M85" s="1" t="n">
+        <v>0.06251</v>
+      </c>
+      <c r="N85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="N85" s="1" t="n">
+      <c r="O85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -4411,9 +4669,12 @@
         <v>0.05456</v>
       </c>
       <c r="M86" s="1" t="n">
+        <v>0.05466</v>
+      </c>
+      <c r="N86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="N86" s="1" t="n">
+      <c r="O86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -4457,9 +4718,12 @@
         <v>0.003353</v>
       </c>
       <c r="M87" s="1" t="n">
+        <v>0.003345</v>
+      </c>
+      <c r="N87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="N87" s="1" t="n">
+      <c r="O87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -4503,9 +4767,12 @@
         <v>0.05046</v>
       </c>
       <c r="M88" s="1" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="N88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="N88" s="1" t="n">
+      <c r="O88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -4549,9 +4816,12 @@
         <v>0.03078</v>
       </c>
       <c r="M89" s="1" t="n">
+        <v>0.03037</v>
+      </c>
+      <c r="N89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="N89" s="1" t="n">
+      <c r="O89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -4595,9 +4865,12 @@
         <v>0.3477</v>
       </c>
       <c r="M90" s="1" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="N90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="N90" s="1" t="n">
+      <c r="O90" s="1" t="n">
         <v>0.3471</v>
       </c>
     </row>
@@ -4641,9 +4914,12 @@
         <v>0.07876</v>
       </c>
       <c r="M91" s="1" t="n">
+        <v>0.08159</v>
+      </c>
+      <c r="N91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="N91" s="1" t="n">
+      <c r="O91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -4687,9 +4963,12 @@
         <v>0.355</v>
       </c>
       <c r="M92" s="1" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="N92" s="1" t="n">
         <v>0.3551</v>
       </c>
-      <c r="N92" s="1" t="n">
+      <c r="O92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -4733,9 +5012,12 @@
         <v>1.9795</v>
       </c>
       <c r="M93" s="1" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="N93" s="1" t="n">
         <v>1.9795</v>
       </c>
-      <c r="N93" s="1" t="n">
+      <c r="O93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -4779,9 +5061,12 @@
         <v>0.259</v>
       </c>
       <c r="M94" s="1" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="N94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="N94" s="1" t="n">
+      <c r="O94" s="1" t="n">
         <v>0.2586</v>
       </c>
     </row>
@@ -4825,9 +5110,12 @@
         <v>0.04647</v>
       </c>
       <c r="M95" s="1" t="n">
-        <v>0.04647</v>
+        <v>0.04722</v>
       </c>
       <c r="N95" s="1" t="n">
+        <v>0.04722</v>
+      </c>
+      <c r="O95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -4871,9 +5159,12 @@
         <v>0.0062</v>
       </c>
       <c r="M96" s="1" t="n">
+        <v>0.006171</v>
+      </c>
+      <c r="N96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="N96" s="1" t="n">
+      <c r="O96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -4917,9 +5208,12 @@
         <v>0.001732</v>
       </c>
       <c r="M97" s="1" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="N97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="N97" s="1" t="n">
+      <c r="O97" s="1" t="n">
         <v>0.001729</v>
       </c>
     </row>
@@ -4963,10 +5257,13 @@
         <v>5.259</v>
       </c>
       <c r="M98" s="1" t="n">
+        <v>5.188</v>
+      </c>
+      <c r="N98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="N98" s="1" t="n">
-        <v>5.221</v>
+      <c r="O98" s="1" t="n">
+        <v>5.188</v>
       </c>
     </row>
     <row r="99">
@@ -5009,10 +5306,13 @@
         <v>0.01518</v>
       </c>
       <c r="M99" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="N99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="N99" s="1" t="n">
-        <v>0.01514</v>
+      <c r="O99" s="1" t="n">
+        <v>0.01511</v>
       </c>
     </row>
     <row r="100">
@@ -5055,9 +5355,12 @@
         <v>0.5537</v>
       </c>
       <c r="M100" s="1" t="n">
+        <v>0.5536</v>
+      </c>
+      <c r="N100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="N100" s="1" t="n">
+      <c r="O100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -5101,10 +5404,13 @@
         <v>0.0907</v>
       </c>
       <c r="M101" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="N101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="N101" s="1" t="n">
-        <v>0.0907</v>
+      <c r="O101" s="1" t="n">
+        <v>0.0905</v>
       </c>
     </row>
     <row r="102">
@@ -5147,9 +5453,12 @@
         <v>32.49</v>
       </c>
       <c r="M102" s="1" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="N102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="N102" s="1" t="n">
+      <c r="O102" s="1" t="n">
         <v>32.42</v>
       </c>
     </row>
@@ -5193,9 +5502,12 @@
         <v>0.03147</v>
       </c>
       <c r="M103" s="1" t="n">
+        <v>0.03147</v>
+      </c>
+      <c r="N103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="N103" s="1" t="n">
+      <c r="O103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -5239,9 +5551,12 @@
         <v>0.06568</v>
       </c>
       <c r="M104" s="1" t="n">
+        <v>0.06571</v>
+      </c>
+      <c r="N104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="N104" s="1" t="n">
+      <c r="O104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -5285,9 +5600,12 @@
         <v>1.3043</v>
       </c>
       <c r="M105" s="1" t="n">
+        <v>1.3036</v>
+      </c>
+      <c r="N105" s="1" t="n">
         <v>1.3046</v>
       </c>
-      <c r="N105" s="1" t="n">
+      <c r="O105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -5331,9 +5649,12 @@
         <v>0.1206</v>
       </c>
       <c r="M106" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="N106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="N106" s="1" t="n">
+      <c r="O106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -5380,6 +5701,9 @@
         <v>0.121</v>
       </c>
       <c r="N107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="O107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -5423,9 +5747,12 @@
         <v>0.09582</v>
       </c>
       <c r="M108" s="1" t="n">
+        <v>0.09587</v>
+      </c>
+      <c r="N108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="N108" s="1" t="n">
+      <c r="O108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -5469,9 +5796,12 @@
         <v>0.13964</v>
       </c>
       <c r="M109" s="1" t="n">
+        <v>0.13956</v>
+      </c>
+      <c r="N109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="N109" s="1" t="n">
+      <c r="O109" s="1" t="n">
         <v>0.13853</v>
       </c>
     </row>
@@ -5515,9 +5845,12 @@
         <v>5.575</v>
       </c>
       <c r="M110" s="1" t="n">
+        <v>5.561</v>
+      </c>
+      <c r="N110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="N110" s="1" t="n">
+      <c r="O110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -5561,9 +5894,12 @@
         <v>1.099</v>
       </c>
       <c r="M111" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="N111" s="1" t="n">
+      <c r="O111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -5607,10 +5943,13 @@
         <v>0.029053</v>
       </c>
       <c r="M112" s="1" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="N112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="N112" s="1" t="n">
-        <v>0.029053</v>
+      <c r="O112" s="1" t="n">
+        <v>0.0289</v>
       </c>
     </row>
     <row r="113">
@@ -5653,10 +5992,13 @@
         <v>1.871</v>
       </c>
       <c r="M113" s="1" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="N113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="N113" s="1" t="n">
-        <v>1.871</v>
+      <c r="O113" s="1" t="n">
+        <v>1.869</v>
       </c>
     </row>
     <row r="114">
@@ -5699,9 +6041,12 @@
         <v>0.05932</v>
       </c>
       <c r="M114" s="1" t="n">
+        <v>0.05942</v>
+      </c>
+      <c r="N114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="N114" s="1" t="n">
+      <c r="O114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -5745,9 +6090,12 @@
         <v>0.12893</v>
       </c>
       <c r="M115" s="1" t="n">
+        <v>0.12898</v>
+      </c>
+      <c r="N115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="N115" s="1" t="n">
+      <c r="O115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -5791,9 +6139,12 @@
         <v>1.1134</v>
       </c>
       <c r="M116" s="1" t="n">
+        <v>1.1102</v>
+      </c>
+      <c r="N116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="N116" s="1" t="n">
+      <c r="O116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -5837,9 +6188,12 @@
         <v>0.1555</v>
       </c>
       <c r="M117" s="1" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="N117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="N117" s="1" t="n">
+      <c r="O117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -5883,9 +6237,12 @@
         <v>0.1595</v>
       </c>
       <c r="M118" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="N118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="N118" s="1" t="n">
+      <c r="O118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -5929,9 +6286,12 @@
         <v>0.04766</v>
       </c>
       <c r="M119" s="1" t="n">
-        <v>0.04766</v>
+        <v>0.04769</v>
       </c>
       <c r="N119" s="1" t="n">
+        <v>0.04769</v>
+      </c>
+      <c r="O119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -5975,9 +6335,12 @@
         <v>3.023</v>
       </c>
       <c r="M120" s="1" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="N120" s="1" t="n">
+      <c r="O120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -6021,9 +6384,12 @@
         <v>0.2976</v>
       </c>
       <c r="M121" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="N121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="N121" s="1" t="n">
+      <c r="O121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -6067,9 +6433,12 @@
         <v>0.5837</v>
       </c>
       <c r="M122" s="1" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="N122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="N122" s="1" t="n">
+      <c r="O122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -6113,9 +6482,12 @@
         <v>0.01259</v>
       </c>
       <c r="M123" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="N123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="N123" s="1" t="n">
+      <c r="O123" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -6159,9 +6531,12 @@
         <v>0.1578</v>
       </c>
       <c r="M124" s="1" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="N124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="N124" s="1" t="n">
+      <c r="O124" s="1" t="n">
         <v>0.1577</v>
       </c>
     </row>
@@ -6205,9 +6580,12 @@
         <v>0.001785</v>
       </c>
       <c r="M125" s="1" t="n">
+        <v>0.001781</v>
+      </c>
+      <c r="N125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="N125" s="1" t="n">
+      <c r="O125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -6251,9 +6629,12 @@
         <v>0.0004865</v>
       </c>
       <c r="M126" s="1" t="n">
+        <v>0.000486</v>
+      </c>
+      <c r="N126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="N126" s="1" t="n">
+      <c r="O126" s="1" t="n">
         <v>0.0004859</v>
       </c>
     </row>
@@ -6297,9 +6678,12 @@
         <v>0.02939</v>
       </c>
       <c r="M127" s="1" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="N127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="N127" s="1" t="n">
+      <c r="O127" s="1" t="n">
         <v>0.02938</v>
       </c>
     </row>
@@ -6343,9 +6727,12 @@
         <v>0.04137</v>
       </c>
       <c r="M128" s="1" t="n">
+        <v>0.04129</v>
+      </c>
+      <c r="N128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="N128" s="1" t="n">
+      <c r="O128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -6389,9 +6776,12 @@
         <v>0.04848</v>
       </c>
       <c r="M129" s="1" t="n">
+        <v>0.04857</v>
+      </c>
+      <c r="N129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="N129" s="1" t="n">
+      <c r="O129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -6438,6 +6828,9 @@
         <v>1.26e-05</v>
       </c>
       <c r="N130" s="1" t="n">
+        <v>1.26e-05</v>
+      </c>
+      <c r="O130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -6481,9 +6874,12 @@
         <v>7e-06</v>
       </c>
       <c r="M131" s="1" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="N131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="N131" s="1" t="n">
+      <c r="O131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -6527,9 +6923,12 @@
         <v>0.007</v>
       </c>
       <c r="M132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="N132" s="1" t="n">
+      <c r="O132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -6576,6 +6975,9 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="N133" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="O133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -6619,10 +7021,13 @@
         <v>0.0004094</v>
       </c>
       <c r="M134" s="1" t="n">
+        <v>0.0004086</v>
+      </c>
+      <c r="N134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="N134" s="1" t="n">
-        <v>0.0004093</v>
+      <c r="O134" s="1" t="n">
+        <v>0.0004086</v>
       </c>
     </row>
     <row r="135">
@@ -6665,9 +7070,12 @@
         <v>0.08351</v>
       </c>
       <c r="M135" s="1" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="N135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="N135" s="1" t="n">
+      <c r="O135" s="1" t="n">
         <v>0.08334</v>
       </c>
     </row>
@@ -6711,9 +7119,12 @@
         <v>0.007868999999999999</v>
       </c>
       <c r="M136" s="1" t="n">
+        <v>0.007868999999999999</v>
+      </c>
+      <c r="N136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="N136" s="1" t="n">
+      <c r="O136" s="1" t="n">
         <v>0.007868999999999999</v>
       </c>
     </row>
@@ -6757,9 +7168,12 @@
         <v>0.0008168</v>
       </c>
       <c r="M137" s="1" t="n">
+        <v>0.0008232</v>
+      </c>
+      <c r="N137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="N137" s="1" t="n">
+      <c r="O137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -6803,9 +7217,12 @@
         <v>0.147</v>
       </c>
       <c r="M138" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="N138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="N138" s="1" t="n">
+      <c r="O138" s="1" t="n">
         <v>0.1468</v>
       </c>
     </row>
@@ -6849,10 +7266,13 @@
         <v>0.006712</v>
       </c>
       <c r="M139" s="1" t="n">
+        <v>0.006709</v>
+      </c>
+      <c r="N139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="N139" s="1" t="n">
-        <v>0.006712</v>
+      <c r="O139" s="1" t="n">
+        <v>0.006709</v>
       </c>
     </row>
     <row r="140">
@@ -6895,9 +7315,12 @@
         <v>0.01393</v>
       </c>
       <c r="M140" s="1" t="n">
-        <v>0.01393</v>
+        <v>0.01394</v>
       </c>
       <c r="N140" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="O140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -6941,9 +7364,12 @@
         <v>0.09766</v>
       </c>
       <c r="M141" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="N141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="N141" s="1" t="n">
+      <c r="O141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -6987,9 +7413,12 @@
         <v>0.05422</v>
       </c>
       <c r="M142" s="1" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="N142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="N142" s="1" t="n">
+      <c r="O142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -7033,9 +7462,12 @@
         <v>0.3233</v>
       </c>
       <c r="M143" s="1" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="N143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="N143" s="1" t="n">
+      <c r="O143" s="1" t="n">
         <v>0.3233</v>
       </c>
     </row>
@@ -7079,9 +7511,12 @@
         <v>0.0257</v>
       </c>
       <c r="M144" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="N144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="N144" s="1" t="n">
+      <c r="O144" s="1" t="n">
         <v>0.0257</v>
       </c>
     </row>
@@ -7125,10 +7560,13 @@
         <v>0.2375</v>
       </c>
       <c r="M145" s="1" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="N145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="N145" s="1" t="n">
-        <v>0.2375</v>
+      <c r="O145" s="1" t="n">
+        <v>0.2373</v>
       </c>
     </row>
     <row r="146">
@@ -7171,9 +7609,12 @@
         <v>0.006994</v>
       </c>
       <c r="M146" s="1" t="n">
+        <v>0.006995</v>
+      </c>
+      <c r="N146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="N146" s="1" t="n">
+      <c r="O146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -7217,9 +7658,12 @@
         <v>0.08692</v>
       </c>
       <c r="M147" s="1" t="n">
+        <v>0.08708</v>
+      </c>
+      <c r="N147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="N147" s="1" t="n">
+      <c r="O147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -7263,9 +7707,12 @@
         <v>0.05201</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>0.05217</v>
+        <v>0.05235</v>
       </c>
       <c r="N148" s="1" t="n">
+        <v>0.05235</v>
+      </c>
+      <c r="O148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -7309,9 +7756,12 @@
         <v>0.02379</v>
       </c>
       <c r="M149" s="1" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="N149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="N149" s="1" t="n">
+      <c r="O149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -7355,9 +7805,12 @@
         <v>0.08527</v>
       </c>
       <c r="M150" s="1" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="N150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="N150" s="1" t="n">
+      <c r="O150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -7401,10 +7854,13 @@
         <v>0.0233</v>
       </c>
       <c r="M151" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="N151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="N151" s="1" t="n">
-        <v>0.0232</v>
+      <c r="O151" s="1" t="n">
+        <v>0.02318</v>
       </c>
     </row>
     <row r="152">
@@ -7447,10 +7903,13 @@
         <v>0.02558</v>
       </c>
       <c r="M152" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="N152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="N152" s="1" t="n">
-        <v>0.02552</v>
+      <c r="O152" s="1" t="n">
+        <v>0.0255</v>
       </c>
     </row>
     <row r="153">
@@ -7493,9 +7952,12 @@
         <v>0.0002165</v>
       </c>
       <c r="M153" s="1" t="n">
+        <v>0.0002166</v>
+      </c>
+      <c r="N153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="N153" s="1" t="n">
+      <c r="O153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -7539,10 +8001,13 @@
         <v>0.4408</v>
       </c>
       <c r="M154" s="1" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="N154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="N154" s="1" t="n">
-        <v>0.4406</v>
+      <c r="O154" s="1" t="n">
+        <v>0.4404</v>
       </c>
     </row>
     <row r="155">
@@ -7585,9 +8050,12 @@
         <v>0.06716</v>
       </c>
       <c r="M155" s="1" t="n">
-        <v>0.06741999999999999</v>
+        <v>0.06744</v>
       </c>
       <c r="N155" s="1" t="n">
+        <v>0.06744</v>
+      </c>
+      <c r="O155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -7631,10 +8099,13 @@
         <v>0.12838</v>
       </c>
       <c r="M156" s="1" t="n">
+        <v>0.12781</v>
+      </c>
+      <c r="N156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="N156" s="1" t="n">
-        <v>0.1282</v>
+      <c r="O156" s="1" t="n">
+        <v>0.12781</v>
       </c>
     </row>
     <row r="157">
@@ -7677,9 +8148,12 @@
         <v>0.4839</v>
       </c>
       <c r="M157" s="1" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="N157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="N157" s="1" t="n">
+      <c r="O157" s="1" t="n">
         <v>0.4839</v>
       </c>
     </row>
@@ -7723,9 +8197,12 @@
         <v>0.4469</v>
       </c>
       <c r="M158" s="1" t="n">
+        <v>0.4467</v>
+      </c>
+      <c r="N158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="N158" s="1" t="n">
+      <c r="O158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -7769,9 +8246,12 @@
         <v>0.007498</v>
       </c>
       <c r="M159" s="1" t="n">
+        <v>0.007504</v>
+      </c>
+      <c r="N159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="N159" s="1" t="n">
+      <c r="O159" s="1" t="n">
         <v>0.007493</v>
       </c>
     </row>
@@ -7815,9 +8295,12 @@
         <v>0.004687</v>
       </c>
       <c r="M160" s="1" t="n">
+        <v>0.004675</v>
+      </c>
+      <c r="N160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="N160" s="1" t="n">
+      <c r="O160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -7861,9 +8344,12 @@
         <v>0.004296</v>
       </c>
       <c r="M161" s="1" t="n">
+        <v>0.004297</v>
+      </c>
+      <c r="N161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="N161" s="1" t="n">
+      <c r="O161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -7907,9 +8393,12 @@
         <v>0.0959</v>
       </c>
       <c r="M162" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="N162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="N162" s="1" t="n">
+      <c r="O162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -7953,9 +8442,12 @@
         <v>0.2861</v>
       </c>
       <c r="M163" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="N163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="N163" s="1" t="n">
+      <c r="O163" s="1" t="n">
         <v>0.2852</v>
       </c>
     </row>
@@ -7999,9 +8491,12 @@
         <v>0.114</v>
       </c>
       <c r="M164" s="1" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="N164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="N164" s="1" t="n">
+      <c r="O164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -8045,9 +8540,12 @@
         <v>0.1756</v>
       </c>
       <c r="M165" s="1" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="N165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="N165" s="1" t="n">
+      <c r="O165" s="1" t="n">
         <v>0.1753</v>
       </c>
     </row>
@@ -8091,9 +8589,12 @@
         <v>0.01014</v>
       </c>
       <c r="M166" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="N166" s="1" t="n">
         <v>0.01014</v>
       </c>
-      <c r="N166" s="1" t="n">
+      <c r="O166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -8137,9 +8638,12 @@
         <v>1.842</v>
       </c>
       <c r="M167" s="1" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="N167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="N167" s="1" t="n">
+      <c r="O167" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -8183,9 +8687,12 @@
         <v>1.334</v>
       </c>
       <c r="M168" s="1" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="N168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="N168" s="1" t="n">
+      <c r="O168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -8229,9 +8736,12 @@
         <v>0.00732</v>
       </c>
       <c r="M169" s="1" t="n">
+        <v>0.007317</v>
+      </c>
+      <c r="N169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="N169" s="1" t="n">
+      <c r="O169" s="1" t="n">
         <v>0.007304</v>
       </c>
     </row>
@@ -8275,9 +8785,12 @@
         <v>0.0116</v>
       </c>
       <c r="M170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="N170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="N170" s="1" t="n">
+      <c r="O170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -8321,10 +8834,13 @@
         <v>0.005805</v>
       </c>
       <c r="M171" s="1" t="n">
+        <v>0.005793</v>
+      </c>
+      <c r="N171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="N171" s="1" t="n">
-        <v>0.005794</v>
+      <c r="O171" s="1" t="n">
+        <v>0.005793</v>
       </c>
     </row>
     <row r="172">
@@ -8367,9 +8883,12 @@
         <v>0.14738</v>
       </c>
       <c r="M172" s="1" t="n">
+        <v>0.14733</v>
+      </c>
+      <c r="N172" s="1" t="n">
         <v>0.14806</v>
       </c>
-      <c r="N172" s="1" t="n">
+      <c r="O172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -8413,9 +8932,12 @@
         <v>4.887</v>
       </c>
       <c r="M173" s="1" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="N173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="N173" s="1" t="n">
+      <c r="O173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -8459,10 +8981,13 @@
         <v>0.07844</v>
       </c>
       <c r="M174" s="1" t="n">
+        <v>0.07839</v>
+      </c>
+      <c r="N174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="N174" s="1" t="n">
-        <v>0.0784</v>
+      <c r="O174" s="1" t="n">
+        <v>0.07839</v>
       </c>
     </row>
     <row r="175">
@@ -8505,10 +9030,13 @@
         <v>0.00745</v>
       </c>
       <c r="M175" s="1" t="n">
+        <v>0.007449</v>
+      </c>
+      <c r="N175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="N175" s="1" t="n">
-        <v>0.00745</v>
+      <c r="O175" s="1" t="n">
+        <v>0.007449</v>
       </c>
     </row>
     <row r="176">
@@ -8551,9 +9079,12 @@
         <v>0.2015</v>
       </c>
       <c r="M176" s="1" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="N176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="N176" s="1" t="n">
+      <c r="O176" s="1" t="n">
         <v>0.2011</v>
       </c>
     </row>
@@ -8597,9 +9128,12 @@
         <v>0.05196</v>
       </c>
       <c r="M177" s="1" t="n">
-        <v>0.05196</v>
+        <v>0.05197</v>
       </c>
       <c r="N177" s="1" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -8643,9 +9177,12 @@
         <v>0.05474</v>
       </c>
       <c r="M178" s="1" t="n">
+        <v>0.05466</v>
+      </c>
+      <c r="N178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="N178" s="1" t="n">
+      <c r="O178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -8689,10 +9226,13 @@
         <v>0.02326</v>
       </c>
       <c r="M179" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="N179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="N179" s="1" t="n">
-        <v>0.02321</v>
+      <c r="O179" s="1" t="n">
+        <v>0.02318</v>
       </c>
     </row>
     <row r="180">
@@ -8735,10 +9275,13 @@
         <v>0.6956</v>
       </c>
       <c r="M180" s="1" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="N180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="N180" s="1" t="n">
-        <v>0.694</v>
+      <c r="O180" s="1" t="n">
+        <v>0.6938</v>
       </c>
     </row>
     <row r="181">
@@ -8781,9 +9324,12 @@
         <v>0.0003744</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>0.0003744</v>
+        <v>0.0003749</v>
       </c>
       <c r="N181" s="1" t="n">
+        <v>0.0003749</v>
+      </c>
+      <c r="O181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -8827,9 +9373,12 @@
         <v>0.01263</v>
       </c>
       <c r="M182" s="1" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="N182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="N182" s="1" t="n">
+      <c r="O182" s="1" t="n">
         <v>0.01256</v>
       </c>
     </row>
@@ -8873,9 +9422,12 @@
         <v>4.236</v>
       </c>
       <c r="M183" s="1" t="n">
+        <v>4.238</v>
+      </c>
+      <c r="N183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="N183" s="1" t="n">
+      <c r="O183" s="1" t="n">
         <v>4.23</v>
       </c>
     </row>
@@ -8919,9 +9471,12 @@
         <v>0.2372</v>
       </c>
       <c r="M184" s="1" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="N184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="N184" s="1" t="n">
+      <c r="O184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -8965,9 +9520,12 @@
         <v>0.03716</v>
       </c>
       <c r="M185" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="N185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="N185" s="1" t="n">
+      <c r="O185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -9011,9 +9569,12 @@
         <v>0.11632</v>
       </c>
       <c r="M186" s="1" t="n">
+        <v>0.11612</v>
+      </c>
+      <c r="N186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="N186" s="1" t="n">
+      <c r="O186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -9057,9 +9618,12 @@
         <v>0.009117999999999999</v>
       </c>
       <c r="M187" s="1" t="n">
+        <v>0.009103</v>
+      </c>
+      <c r="N187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="N187" s="1" t="n">
+      <c r="O187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -9103,9 +9667,12 @@
         <v>0.0975</v>
       </c>
       <c r="M188" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="N188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="N188" s="1" t="n">
+      <c r="O188" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -9149,9 +9716,12 @@
         <v>0.0277</v>
       </c>
       <c r="M189" s="1" t="n">
+        <v>0.02771</v>
+      </c>
+      <c r="N189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="N189" s="1" t="n">
+      <c r="O189" s="1" t="n">
         <v>0.02767</v>
       </c>
     </row>
@@ -9195,9 +9765,12 @@
         <v>0.00864</v>
       </c>
       <c r="M190" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="N190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="N190" s="1" t="n">
+      <c r="O190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -9241,9 +9814,12 @@
         <v>0.001959</v>
       </c>
       <c r="M191" s="1" t="n">
-        <v>0.001959</v>
+        <v>0.001961</v>
       </c>
       <c r="N191" s="1" t="n">
+        <v>0.001961</v>
+      </c>
+      <c r="O191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -9287,9 +9863,12 @@
         <v>0.1004</v>
       </c>
       <c r="M192" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="N192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="N192" s="1" t="n">
+      <c r="O192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -9333,9 +9912,12 @@
         <v>0.02331</v>
       </c>
       <c r="M193" s="1" t="n">
+        <v>0.02333</v>
+      </c>
+      <c r="N193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="N193" s="1" t="n">
+      <c r="O193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -9379,9 +9961,12 @@
         <v>0.0135</v>
       </c>
       <c r="M194" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="N194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="N194" s="1" t="n">
+      <c r="O194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -9425,10 +10010,13 @@
         <v>0.02091</v>
       </c>
       <c r="M195" s="1" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="N195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="N195" s="1" t="n">
-        <v>0.02089</v>
+      <c r="O195" s="1" t="n">
+        <v>0.02088</v>
       </c>
     </row>
     <row r="196">
@@ -9471,9 +10059,12 @@
         <v>0.17509</v>
       </c>
       <c r="M196" s="1" t="n">
+        <v>0.17369</v>
+      </c>
+      <c r="N196" s="1" t="n">
         <v>0.17509</v>
       </c>
-      <c r="N196" s="1" t="n">
+      <c r="O196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -9517,9 +10108,12 @@
         <v>0.007352</v>
       </c>
       <c r="M197" s="1" t="n">
+        <v>0.007339</v>
+      </c>
+      <c r="N197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="N197" s="1" t="n">
+      <c r="O197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -9563,9 +10157,12 @@
         <v>0.01909</v>
       </c>
       <c r="M198" s="1" t="n">
+        <v>0.01907</v>
+      </c>
+      <c r="N198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="N198" s="1" t="n">
+      <c r="O198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -9609,9 +10206,12 @@
         <v>0.0168</v>
       </c>
       <c r="M199" s="1" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="N199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="N199" s="1" t="n">
+      <c r="O199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -9655,9 +10255,12 @@
         <v>0.298</v>
       </c>
       <c r="M200" s="1" t="n">
-        <v>0.298</v>
+        <v>0.2981</v>
       </c>
       <c r="N200" s="1" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="O200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -9701,9 +10304,12 @@
         <v>0.006258</v>
       </c>
       <c r="M201" s="1" t="n">
+        <v>0.006234</v>
+      </c>
+      <c r="N201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="N201" s="1" t="n">
+      <c r="O201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -9747,10 +10353,13 @@
         <v>0.0004433</v>
       </c>
       <c r="M202" s="1" t="n">
+        <v>0.000443</v>
+      </c>
+      <c r="N202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="N202" s="1" t="n">
-        <v>0.0004433</v>
+      <c r="O202" s="1" t="n">
+        <v>0.000443</v>
       </c>
     </row>
     <row r="203">
@@ -9793,10 +10402,13 @@
         <v>0.007273</v>
       </c>
       <c r="M203" s="1" t="n">
+        <v>0.007271</v>
+      </c>
+      <c r="N203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="N203" s="1" t="n">
-        <v>0.007273</v>
+      <c r="O203" s="1" t="n">
+        <v>0.007271</v>
       </c>
     </row>
     <row r="204">
@@ -9839,9 +10451,12 @@
         <v>0.1317</v>
       </c>
       <c r="M204" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="N204" s="1" t="n">
         <v>0.1317</v>
       </c>
-      <c r="N204" s="1" t="n">
+      <c r="O204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -9885,9 +10500,12 @@
         <v>0.01427</v>
       </c>
       <c r="M205" s="1" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="N205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="N205" s="1" t="n">
+      <c r="O205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -9931,9 +10549,12 @@
         <v>0.00359</v>
       </c>
       <c r="M206" s="1" t="n">
+        <v>0.003582</v>
+      </c>
+      <c r="N206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="N206" s="1" t="n">
+      <c r="O206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -9977,9 +10598,12 @@
         <v>0.05998</v>
       </c>
       <c r="M207" s="1" t="n">
+        <v>0.05964</v>
+      </c>
+      <c r="N207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="N207" s="1" t="n">
+      <c r="O207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -10023,9 +10647,12 @@
         <v>15.53</v>
       </c>
       <c r="M208" s="1" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="N208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="N208" s="1" t="n">
+      <c r="O208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -10069,9 +10696,12 @@
         <v>5191.6</v>
       </c>
       <c r="M209" s="1" t="n">
+        <v>5190.5</v>
+      </c>
+      <c r="N209" s="1" t="n">
         <v>5192.8</v>
       </c>
-      <c r="N209" s="1" t="n">
+      <c r="O209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -10115,9 +10745,12 @@
         <v>0.12027</v>
       </c>
       <c r="M210" s="1" t="n">
+        <v>0.11977</v>
+      </c>
+      <c r="N210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="N210" s="1" t="n">
+      <c r="O210" s="1" t="n">
         <v>0.11963</v>
       </c>
     </row>
@@ -10161,9 +10794,12 @@
         <v>0.1816</v>
       </c>
       <c r="M211" s="1" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="N211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="N211" s="1" t="n">
+      <c r="O211" s="1" t="n">
         <v>0.1815</v>
       </c>
     </row>
@@ -10207,9 +10843,12 @@
         <v>0.0303</v>
       </c>
       <c r="M212" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="N212" s="1" t="n">
         <v>0.0308</v>
       </c>
-      <c r="N212" s="1" t="n">
+      <c r="O212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -10253,9 +10892,12 @@
         <v>1.3973</v>
       </c>
       <c r="M213" s="1" t="n">
+        <v>1.3972</v>
+      </c>
+      <c r="N213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="N213" s="1" t="n">
+      <c r="O213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -10299,10 +10941,13 @@
         <v>0.05645</v>
       </c>
       <c r="M214" s="1" t="n">
+        <v>0.05644</v>
+      </c>
+      <c r="N214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="N214" s="1" t="n">
-        <v>0.05645</v>
+      <c r="O214" s="1" t="n">
+        <v>0.05644</v>
       </c>
     </row>
     <row r="215">
@@ -10345,9 +10990,12 @@
         <v>0.04404</v>
       </c>
       <c r="M215" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="N215" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="N215" s="1" t="n">
+      <c r="O215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -10391,9 +11039,12 @@
         <v>0.15059</v>
       </c>
       <c r="M216" s="1" t="n">
+        <v>0.15015</v>
+      </c>
+      <c r="N216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="N216" s="1" t="n">
+      <c r="O216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -10437,9 +11088,12 @@
         <v>0.073</v>
       </c>
       <c r="M217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="N217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="N217" s="1" t="n">
+      <c r="O217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -10483,9 +11137,12 @@
         <v>0.00269</v>
       </c>
       <c r="M218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="N218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="N218" s="1" t="n">
+      <c r="O218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -10529,10 +11186,13 @@
         <v>0.01715</v>
       </c>
       <c r="M219" s="1" t="n">
+        <v>0.01713</v>
+      </c>
+      <c r="N219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="N219" s="1" t="n">
-        <v>0.01715</v>
+      <c r="O219" s="1" t="n">
+        <v>0.01713</v>
       </c>
     </row>
     <row r="220">
@@ -10575,9 +11235,12 @@
         <v>0.05527</v>
       </c>
       <c r="M220" s="1" t="n">
+        <v>0.05516</v>
+      </c>
+      <c r="N220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="N220" s="1" t="n">
+      <c r="O220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -10621,9 +11284,12 @@
         <v>0.02188</v>
       </c>
       <c r="M221" s="1" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="N221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="N221" s="1" t="n">
+      <c r="O221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -10667,9 +11333,12 @@
         <v>0.009390000000000001</v>
       </c>
       <c r="M222" s="1" t="n">
+        <v>0.00936</v>
+      </c>
+      <c r="N222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="N222" s="1" t="n">
+      <c r="O222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -10713,9 +11382,12 @@
         <v>0.0165</v>
       </c>
       <c r="M223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="N223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="N223" s="1" t="n">
+      <c r="O223" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -10759,9 +11431,12 @@
         <v>0.03814</v>
       </c>
       <c r="M224" s="1" t="n">
+        <v>0.03818</v>
+      </c>
+      <c r="N224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="N224" s="1" t="n">
+      <c r="O224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -10805,9 +11480,12 @@
         <v>0.00153</v>
       </c>
       <c r="M225" s="1" t="n">
+        <v>0.001529</v>
+      </c>
+      <c r="N225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="N225" s="1" t="n">
+      <c r="O225" s="1" t="n">
         <v>0.001525</v>
       </c>
     </row>
@@ -10851,9 +11529,12 @@
         <v>27.15</v>
       </c>
       <c r="M226" s="1" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="N226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="N226" s="1" t="n">
+      <c r="O226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -10897,9 +11578,12 @@
         <v>0.07071</v>
       </c>
       <c r="M227" s="1" t="n">
+        <v>0.07069</v>
+      </c>
+      <c r="N227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="N227" s="1" t="n">
+      <c r="O227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -10943,9 +11627,12 @@
         <v>0.313</v>
       </c>
       <c r="M228" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="N228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="N228" s="1" t="n">
+      <c r="O228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -10989,9 +11676,12 @@
         <v>18.37</v>
       </c>
       <c r="M229" s="1" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="N229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="N229" s="1" t="n">
+      <c r="O229" s="1" t="n">
         <v>18.35</v>
       </c>
     </row>
@@ -11035,9 +11725,12 @@
         <v>0.01936</v>
       </c>
       <c r="M230" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="N230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="N230" s="1" t="n">
+      <c r="O230" s="1" t="n">
         <v>0.01926</v>
       </c>
     </row>
@@ -11081,9 +11774,12 @@
         <v>0.01217</v>
       </c>
       <c r="M231" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="N231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="N231" s="1" t="n">
+      <c r="O231" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -11127,9 +11823,12 @@
         <v>0.228</v>
       </c>
       <c r="M232" s="1" t="n">
+        <v>0.2278</v>
+      </c>
+      <c r="N232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="N232" s="1" t="n">
+      <c r="O232" s="1" t="n">
         <v>0.2274</v>
       </c>
     </row>
@@ -11173,9 +11872,12 @@
         <v>0.07108</v>
       </c>
       <c r="M233" s="1" t="n">
+        <v>0.0711</v>
+      </c>
+      <c r="N233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="N233" s="1" t="n">
+      <c r="O233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -11222,6 +11924,9 @@
         <v>0.1706</v>
       </c>
       <c r="N234" s="1" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="O234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -11265,9 +11970,12 @@
         <v>0.0253</v>
       </c>
       <c r="M235" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="N235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="N235" s="1" t="n">
+      <c r="O235" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -11311,9 +12019,12 @@
         <v>0.03001</v>
       </c>
       <c r="M236" s="1" t="n">
+        <v>0.02999</v>
+      </c>
+      <c r="N236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="N236" s="1" t="n">
+      <c r="O236" s="1" t="n">
         <v>0.02998</v>
       </c>
     </row>
@@ -11357,9 +12068,12 @@
         <v>1.991</v>
       </c>
       <c r="M237" s="1" t="n">
-        <v>1.993</v>
+        <v>1.994</v>
       </c>
       <c r="N237" s="1" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="O237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -11403,10 +12117,13 @@
         <v>0.4241</v>
       </c>
       <c r="M238" s="1" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="N238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="N238" s="1" t="n">
-        <v>0.4241</v>
+      <c r="O238" s="1" t="n">
+        <v>0.4236</v>
       </c>
     </row>
     <row r="239">
@@ -11449,9 +12166,12 @@
         <v>0.03354</v>
       </c>
       <c r="M239" s="1" t="n">
+        <v>0.03335</v>
+      </c>
+      <c r="N239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="N239" s="1" t="n">
+      <c r="O239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -11495,9 +12215,12 @@
         <v>0.03404</v>
       </c>
       <c r="M240" s="1" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="N240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="N240" s="1" t="n">
+      <c r="O240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -11541,9 +12264,12 @@
         <v>0.0007538999999999999</v>
       </c>
       <c r="M241" s="1" t="n">
+        <v>0.000752</v>
+      </c>
+      <c r="N241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="N241" s="1" t="n">
+      <c r="O241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -11587,9 +12313,12 @@
         <v>0.1839</v>
       </c>
       <c r="M242" s="1" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="N242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="N242" s="1" t="n">
+      <c r="O242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -11633,9 +12362,12 @@
         <v>0.014823</v>
       </c>
       <c r="M243" s="1" t="n">
+        <v>0.014801</v>
+      </c>
+      <c r="N243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="N243" s="1" t="n">
+      <c r="O243" s="1" t="n">
         <v>0.014772</v>
       </c>
     </row>
@@ -11679,9 +12411,12 @@
         <v>3.02e-05</v>
       </c>
       <c r="M244" s="1" t="n">
+        <v>3.02e-05</v>
+      </c>
+      <c r="N244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="N244" s="1" t="n">
+      <c r="O244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -11725,9 +12460,12 @@
         <v>0.03524</v>
       </c>
       <c r="M245" s="1" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="N245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="N245" s="1" t="n">
+      <c r="O245" s="1" t="n">
         <v>0.03514</v>
       </c>
     </row>
@@ -11771,9 +12509,12 @@
         <v>0.08053</v>
       </c>
       <c r="M246" s="1" t="n">
+        <v>0.08044</v>
+      </c>
+      <c r="N246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="N246" s="1" t="n">
+      <c r="O246" s="1" t="n">
         <v>0.08037999999999999</v>
       </c>
     </row>
@@ -11817,9 +12558,12 @@
         <v>0.007373</v>
       </c>
       <c r="M247" s="1" t="n">
+        <v>0.007338</v>
+      </c>
+      <c r="N247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="N247" s="1" t="n">
+      <c r="O247" s="1" t="n">
         <v>0.00728</v>
       </c>
     </row>
@@ -11863,9 +12607,12 @@
         <v>0.09531000000000001</v>
       </c>
       <c r="M248" s="1" t="n">
+        <v>0.09499</v>
+      </c>
+      <c r="N248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="N248" s="1" t="n">
+      <c r="O248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -11912,6 +12659,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="N249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="O249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -11955,9 +12705,12 @@
         <v>0.03506</v>
       </c>
       <c r="M250" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="N250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="N250" s="1" t="n">
+      <c r="O250" s="1" t="n">
         <v>0.03496</v>
       </c>
     </row>
@@ -12001,9 +12754,12 @@
         <v>0.03962</v>
       </c>
       <c r="M251" s="1" t="n">
+        <v>0.03966</v>
+      </c>
+      <c r="N251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="N251" s="1" t="n">
+      <c r="O251" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -12047,9 +12803,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="M252" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="N252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="N252" s="1" t="n">
+      <c r="O252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -12093,9 +12852,12 @@
         <v>4.071</v>
       </c>
       <c r="M253" s="1" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="N253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="N253" s="1" t="n">
+      <c r="O253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -12139,9 +12901,12 @@
         <v>0.1872</v>
       </c>
       <c r="M254" s="1" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="N254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="N254" s="1" t="n">
+      <c r="O254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -12185,10 +12950,13 @@
         <v>0.07238</v>
       </c>
       <c r="M255" s="1" t="n">
+        <v>0.07206</v>
+      </c>
+      <c r="N255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="N255" s="1" t="n">
-        <v>0.07214</v>
+      <c r="O255" s="1" t="n">
+        <v>0.07206</v>
       </c>
     </row>
     <row r="256">
@@ -12231,9 +12999,12 @@
         <v>0.01835</v>
       </c>
       <c r="M256" s="1" t="n">
+        <v>0.01829</v>
+      </c>
+      <c r="N256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="N256" s="1" t="n">
+      <c r="O256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -12277,9 +13048,12 @@
         <v>5.951</v>
       </c>
       <c r="M257" s="1" t="n">
+        <v>5.949</v>
+      </c>
+      <c r="N257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="N257" s="1" t="n">
+      <c r="O257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -12323,9 +13097,12 @@
         <v>0.2631</v>
       </c>
       <c r="M258" s="1" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="N258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="N258" s="1" t="n">
+      <c r="O258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -12369,9 +13146,12 @@
         <v>0.1362</v>
       </c>
       <c r="M259" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="N259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="N259" s="1" t="n">
+      <c r="O259" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -12415,9 +13195,12 @@
         <v>0.30613</v>
       </c>
       <c r="M260" s="1" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="N260" s="1" t="n">
         <v>0.30667</v>
       </c>
-      <c r="N260" s="1" t="n">
+      <c r="O260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -12461,9 +13244,12 @@
         <v>0.09934</v>
       </c>
       <c r="M261" s="1" t="n">
-        <v>0.09934</v>
+        <v>0.09941999999999999</v>
       </c>
       <c r="N261" s="1" t="n">
+        <v>0.09941999999999999</v>
+      </c>
+      <c r="O261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -12507,10 +13293,13 @@
         <v>0.5401</v>
       </c>
       <c r="M262" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="N262" s="1" t="n">
-        <v>0.5401</v>
+      <c r="O262" s="1" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="263">
@@ -12553,9 +13342,12 @@
         <v>0.293</v>
       </c>
       <c r="M263" s="1" t="n">
-        <v>0.293</v>
+        <v>0.2937</v>
       </c>
       <c r="N263" s="1" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="O263" s="1" t="n">
         <v>0.2914</v>
       </c>
     </row>
@@ -12599,9 +13391,12 @@
         <v>0.972</v>
       </c>
       <c r="M264" s="1" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="N264" s="1" t="n">
         <v>0.972</v>
       </c>
-      <c r="N264" s="1" t="n">
+      <c r="O264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -12645,9 +13440,12 @@
         <v>0.5414</v>
       </c>
       <c r="M265" s="1" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="N265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="N265" s="1" t="n">
+      <c r="O265" s="1" t="n">
         <v>0.5403</v>
       </c>
     </row>
@@ -12691,9 +13489,12 @@
         <v>0.07382</v>
       </c>
       <c r="M266" s="1" t="n">
+        <v>0.07371999999999999</v>
+      </c>
+      <c r="N266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="N266" s="1" t="n">
+      <c r="O266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -12737,9 +13538,12 @@
         <v>0.02163</v>
       </c>
       <c r="M267" s="1" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="N267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="N267" s="1" t="n">
+      <c r="O267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -12783,9 +13587,12 @@
         <v>0.01627</v>
       </c>
       <c r="M268" s="1" t="n">
-        <v>0.01633</v>
+        <v>0.01634</v>
       </c>
       <c r="N268" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="O268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -12829,9 +13636,12 @@
         <v>0.003763</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>0.003765</v>
+        <v>0.003785</v>
       </c>
       <c r="N269" s="1" t="n">
+        <v>0.003785</v>
+      </c>
+      <c r="O269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -12875,9 +13685,12 @@
         <v>0.00764</v>
       </c>
       <c r="M270" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="N270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="N270" s="1" t="n">
+      <c r="O270" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -12921,9 +13734,12 @@
         <v>0.05525</v>
       </c>
       <c r="M271" s="1" t="n">
+        <v>0.05522</v>
+      </c>
+      <c r="N271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="N271" s="1" t="n">
+      <c r="O271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -12967,9 +13783,12 @@
         <v>2.304</v>
       </c>
       <c r="M272" s="1" t="n">
+        <v>2.301</v>
+      </c>
+      <c r="N272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="N272" s="1" t="n">
+      <c r="O272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -13013,9 +13832,12 @@
         <v>0.05504</v>
       </c>
       <c r="M273" s="1" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="N273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="N273" s="1" t="n">
+      <c r="O273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -13059,9 +13881,12 @@
         <v>0.02333</v>
       </c>
       <c r="M274" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="N274" s="1" t="n">
         <v>0.02333</v>
       </c>
-      <c r="N274" s="1" t="n">
+      <c r="O274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -13105,9 +13930,12 @@
         <v>1.184</v>
       </c>
       <c r="M275" s="1" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="N275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="N275" s="1" t="n">
+      <c r="O275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -13151,9 +13979,12 @@
         <v>0.2727</v>
       </c>
       <c r="M276" s="1" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="N276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="N276" s="1" t="n">
+      <c r="O276" s="1" t="n">
         <v>0.2722</v>
       </c>
     </row>
@@ -13197,10 +14028,13 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="M277" s="1" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="N277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="N277" s="1" t="n">
-        <v>0.9360000000000001</v>
+      <c r="O277" s="1" t="n">
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="278">
@@ -13243,9 +14077,12 @@
         <v>0.6224</v>
       </c>
       <c r="M278" s="1" t="n">
+        <v>0.6236</v>
+      </c>
+      <c r="N278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="N278" s="1" t="n">
+      <c r="O278" s="1" t="n">
         <v>0.6224</v>
       </c>
     </row>
@@ -13289,9 +14126,12 @@
         <v>0.001353</v>
       </c>
       <c r="M279" s="1" t="n">
+        <v>0.001348</v>
+      </c>
+      <c r="N279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="N279" s="1" t="n">
+      <c r="O279" s="1" t="n">
         <v>0.001344</v>
       </c>
     </row>
@@ -13335,9 +14175,12 @@
         <v>0.005561</v>
       </c>
       <c r="M280" s="1" t="n">
+        <v>0.005565</v>
+      </c>
+      <c r="N280" s="1" t="n">
         <v>0.005567</v>
       </c>
-      <c r="N280" s="1" t="n">
+      <c r="O280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -13381,9 +14224,12 @@
         <v>1.523</v>
       </c>
       <c r="M281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="N281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="N281" s="1" t="n">
+      <c r="O281" s="1" t="n">
         <v>1.521</v>
       </c>
     </row>
@@ -13427,9 +14273,12 @@
         <v>28.33</v>
       </c>
       <c r="M282" s="1" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="N282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="N282" s="1" t="n">
+      <c r="O282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -13473,10 +14322,13 @@
         <v>0.12856</v>
       </c>
       <c r="M283" s="1" t="n">
+        <v>0.12855</v>
+      </c>
+      <c r="N283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="N283" s="1" t="n">
-        <v>0.12856</v>
+      <c r="O283" s="1" t="n">
+        <v>0.12855</v>
       </c>
     </row>
     <row r="284">
@@ -13519,9 +14371,12 @@
         <v>0.01116</v>
       </c>
       <c r="M284" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="N284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="N284" s="1" t="n">
+      <c r="O284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -13565,9 +14420,12 @@
         <v>6.598</v>
       </c>
       <c r="M285" s="1" t="n">
-        <v>6.598</v>
+        <v>6.601</v>
       </c>
       <c r="N285" s="1" t="n">
+        <v>6.601</v>
+      </c>
+      <c r="O285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -13611,9 +14469,12 @@
         <v>0.0185</v>
       </c>
       <c r="M286" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="N286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="N286" s="1" t="n">
+      <c r="O286" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -13657,9 +14518,12 @@
         <v>0.008385999999999999</v>
       </c>
       <c r="M287" s="1" t="n">
+        <v>0.008382000000000001</v>
+      </c>
+      <c r="N287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="N287" s="1" t="n">
+      <c r="O287" s="1" t="n">
         <v>0.008378</v>
       </c>
     </row>
@@ -13703,10 +14567,13 @@
         <v>0.3848</v>
       </c>
       <c r="M288" s="1" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="N288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="N288" s="1" t="n">
-        <v>0.3846</v>
+      <c r="O288" s="1" t="n">
+        <v>0.3827</v>
       </c>
     </row>
     <row r="289">
@@ -13749,10 +14616,13 @@
         <v>0.010043</v>
       </c>
       <c r="M289" s="1" t="n">
+        <v>0.009962</v>
+      </c>
+      <c r="N289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="N289" s="1" t="n">
-        <v>0.010005</v>
+      <c r="O289" s="1" t="n">
+        <v>0.009962</v>
       </c>
     </row>
     <row r="290">
@@ -13795,9 +14665,12 @@
         <v>0.02588</v>
       </c>
       <c r="M290" s="1" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="N290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="N290" s="1" t="n">
+      <c r="O290" s="1" t="n">
         <v>0.02588</v>
       </c>
     </row>
@@ -13841,9 +14714,12 @@
         <v>0.096</v>
       </c>
       <c r="M291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="N291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="N291" s="1" t="n">
+      <c r="O291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -13887,9 +14763,12 @@
         <v>0.28612</v>
       </c>
       <c r="M292" s="1" t="n">
-        <v>0.28632</v>
+        <v>0.28707</v>
       </c>
       <c r="N292" s="1" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="O292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -13933,9 +14812,12 @@
         <v>0.01551</v>
       </c>
       <c r="M293" s="1" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="N293" s="1" t="n">
         <v>0.01551</v>
       </c>
-      <c r="N293" s="1" t="n">
+      <c r="O293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -13979,9 +14861,12 @@
         <v>0.003435</v>
       </c>
       <c r="M294" s="1" t="n">
+        <v>0.003456</v>
+      </c>
+      <c r="N294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="N294" s="1" t="n">
+      <c r="O294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -14025,9 +14910,12 @@
         <v>0.042824</v>
       </c>
       <c r="M295" s="1" t="n">
+        <v>0.042876</v>
+      </c>
+      <c r="N295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="N295" s="1" t="n">
+      <c r="O295" s="1" t="n">
         <v>0.042792</v>
       </c>
     </row>
@@ -14071,9 +14959,12 @@
         <v>0.02968</v>
       </c>
       <c r="M296" s="1" t="n">
+        <v>0.02972</v>
+      </c>
+      <c r="N296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="N296" s="1" t="n">
+      <c r="O296" s="1" t="n">
         <v>0.02929</v>
       </c>
     </row>
@@ -14117,9 +15008,12 @@
         <v>0.03791</v>
       </c>
       <c r="M297" s="1" t="n">
+        <v>0.03785</v>
+      </c>
+      <c r="N297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="N297" s="1" t="n">
+      <c r="O297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -14163,9 +15057,12 @@
         <v>0.08248</v>
       </c>
       <c r="M298" s="1" t="n">
+        <v>0.08313</v>
+      </c>
+      <c r="N298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="N298" s="1" t="n">
+      <c r="O298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -14209,9 +15106,12 @@
         <v>0.00774</v>
       </c>
       <c r="M299" s="1" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="N299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="N299" s="1" t="n">
+      <c r="O299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -14255,9 +15155,12 @@
         <v>0.01515</v>
       </c>
       <c r="M300" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="N300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="N300" s="1" t="n">
+      <c r="O300" s="1" t="n">
         <v>0.01512</v>
       </c>
     </row>
@@ -14301,10 +15204,13 @@
         <v>0.1411</v>
       </c>
       <c r="M301" s="1" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="N301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="N301" s="1" t="n">
-        <v>0.141</v>
+      <c r="O301" s="1" t="n">
+        <v>0.1408</v>
       </c>
     </row>
     <row r="302">
@@ -14347,9 +15253,12 @@
         <v>0.0006351</v>
       </c>
       <c r="M302" s="1" t="n">
+        <v>0.0006322</v>
+      </c>
+      <c r="N302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="N302" s="1" t="n">
+      <c r="O302" s="1" t="n">
         <v>0.0006284</v>
       </c>
     </row>
@@ -14393,9 +15302,12 @@
         <v>0.0624</v>
       </c>
       <c r="M303" s="1" t="n">
+        <v>0.06234</v>
+      </c>
+      <c r="N303" s="1" t="n">
         <v>0.0624</v>
       </c>
-      <c r="N303" s="1" t="n">
+      <c r="O303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -14439,9 +15351,12 @@
         <v>0.0001633</v>
       </c>
       <c r="M304" s="1" t="n">
+        <v>0.0001633</v>
+      </c>
+      <c r="N304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="N304" s="1" t="n">
+      <c r="O304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -14485,9 +15400,12 @@
         <v>0.06115</v>
       </c>
       <c r="M305" s="1" t="n">
+        <v>0.06109</v>
+      </c>
+      <c r="N305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="N305" s="1" t="n">
+      <c r="O305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -14531,9 +15449,12 @@
         <v>0.022181</v>
       </c>
       <c r="M306" s="1" t="n">
+        <v>0.022267</v>
+      </c>
+      <c r="N306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="N306" s="1" t="n">
+      <c r="O306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -14577,9 +15498,12 @@
         <v>0.0238</v>
       </c>
       <c r="M307" s="1" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="N307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="N307" s="1" t="n">
+      <c r="O307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -14623,9 +15547,12 @@
         <v>0.000411</v>
       </c>
       <c r="M308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="N308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="N308" s="1" t="n">
+      <c r="O308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -14669,9 +15596,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="M309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="N309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="N309" s="1" t="n">
+      <c r="O309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -14715,9 +15645,12 @@
         <v>0.3837</v>
       </c>
       <c r="M310" s="1" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="N310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="N310" s="1" t="n">
+      <c r="O310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -14761,9 +15694,12 @@
         <v>0.0355</v>
       </c>
       <c r="M311" s="1" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="N311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="N311" s="1" t="n">
+      <c r="O311" s="1" t="n">
         <v>0.0355</v>
       </c>
     </row>
@@ -14807,9 +15743,12 @@
         <v>0.02454</v>
       </c>
       <c r="M312" s="1" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="N312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="N312" s="1" t="n">
+      <c r="O312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -14853,10 +15792,13 @@
         <v>0.04131</v>
       </c>
       <c r="M313" s="1" t="n">
+        <v>0.04128</v>
+      </c>
+      <c r="N313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="N313" s="1" t="n">
-        <v>0.04129</v>
+      <c r="O313" s="1" t="n">
+        <v>0.04128</v>
       </c>
     </row>
     <row r="314">
@@ -14899,10 +15841,13 @@
         <v>3.985</v>
       </c>
       <c r="M314" s="1" t="n">
+        <v>3.982</v>
+      </c>
+      <c r="N314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="N314" s="1" t="n">
-        <v>3.985</v>
+      <c r="O314" s="1" t="n">
+        <v>3.982</v>
       </c>
     </row>
     <row r="315">
@@ -14945,9 +15890,12 @@
         <v>0.1605</v>
       </c>
       <c r="M315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="N315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="N315" s="1" t="n">
+      <c r="O315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -14991,9 +15939,12 @@
         <v>0.09085</v>
       </c>
       <c r="M316" s="1" t="n">
-        <v>0.09085</v>
+        <v>0.09137000000000001</v>
       </c>
       <c r="N316" s="1" t="n">
+        <v>0.09137000000000001</v>
+      </c>
+      <c r="O316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -15037,9 +15988,12 @@
         <v>0.06856</v>
       </c>
       <c r="M317" s="1" t="n">
+        <v>0.06848</v>
+      </c>
+      <c r="N317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="N317" s="1" t="n">
+      <c r="O317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -15083,9 +16037,12 @@
         <v>0.012414</v>
       </c>
       <c r="M318" s="1" t="n">
+        <v>0.012454</v>
+      </c>
+      <c r="N318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="N318" s="1" t="n">
+      <c r="O318" s="1" t="n">
         <v>0.012414</v>
       </c>
     </row>
@@ -15129,9 +16086,12 @@
         <v>0.00114</v>
       </c>
       <c r="M319" s="1" t="n">
+        <v>0.001139</v>
+      </c>
+      <c r="N319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="N319" s="1" t="n">
+      <c r="O319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -15175,9 +16135,12 @@
         <v>0.0631</v>
       </c>
       <c r="M320" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="N320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="N320" s="1" t="n">
+      <c r="O320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -15221,9 +16184,12 @@
         <v>0.00528</v>
       </c>
       <c r="M321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="N321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="N321" s="1" t="n">
+      <c r="O321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -15267,9 +16233,12 @@
         <v>0.1121</v>
       </c>
       <c r="M322" s="1" t="n">
-        <v>0.1121</v>
+        <v>0.1124</v>
       </c>
       <c r="N322" s="1" t="n">
+        <v>0.1124</v>
+      </c>
+      <c r="O322" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
@@ -15313,9 +16282,12 @@
         <v>0.0434</v>
       </c>
       <c r="M323" s="1" t="n">
-        <v>0.0434</v>
+        <v>0.0437</v>
       </c>
       <c r="N323" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="O323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -15359,9 +16331,12 @@
         <v>0.01778</v>
       </c>
       <c r="M324" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="N324" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="N324" s="1" t="n">
+      <c r="O324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -15405,9 +16380,12 @@
         <v>0.005671</v>
       </c>
       <c r="M325" s="1" t="n">
+        <v>0.005672</v>
+      </c>
+      <c r="N325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="N325" s="1" t="n">
+      <c r="O325" s="1" t="n">
         <v>0.005663</v>
       </c>
     </row>
@@ -15451,9 +16429,12 @@
         <v>0.001775</v>
       </c>
       <c r="M326" s="1" t="n">
+        <v>0.001772</v>
+      </c>
+      <c r="N326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="N326" s="1" t="n">
+      <c r="O326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -15497,9 +16478,12 @@
         <v>0.0406</v>
       </c>
       <c r="M327" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="N327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="N327" s="1" t="n">
+      <c r="O327" s="1" t="n">
         <v>0.04047</v>
       </c>
     </row>
@@ -15543,10 +16527,13 @@
         <v>0.053566</v>
       </c>
       <c r="M328" s="1" t="n">
+        <v>0.053492</v>
+      </c>
+      <c r="N328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="N328" s="1" t="n">
-        <v>0.053566</v>
+      <c r="O328" s="1" t="n">
+        <v>0.053492</v>
       </c>
     </row>
     <row r="329">
@@ -15589,9 +16576,12 @@
         <v>0.2784</v>
       </c>
       <c r="M329" s="1" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="N329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="N329" s="1" t="n">
+      <c r="O329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -15635,9 +16625,12 @@
         <v>0.1594</v>
       </c>
       <c r="M330" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="N330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="N330" s="1" t="n">
+      <c r="O330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -15681,9 +16674,12 @@
         <v>0.0538</v>
       </c>
       <c r="M331" s="1" t="n">
-        <v>0.0538</v>
+        <v>0.05385</v>
       </c>
       <c r="N331" s="1" t="n">
+        <v>0.05385</v>
+      </c>
+      <c r="O331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -15727,9 +16723,12 @@
         <v>0.3607</v>
       </c>
       <c r="M332" s="1" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="N332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="N332" s="1" t="n">
+      <c r="O332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -15773,9 +16772,12 @@
         <v>0.03051</v>
       </c>
       <c r="M333" s="1" t="n">
+        <v>0.03048</v>
+      </c>
+      <c r="N333" s="1" t="n">
         <v>0.03051</v>
       </c>
-      <c r="N333" s="1" t="n">
+      <c r="O333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -15819,9 +16821,12 @@
         <v>0.01811</v>
       </c>
       <c r="M334" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="N334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="N334" s="1" t="n">
+      <c r="O334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -15865,9 +16870,12 @@
         <v>0.058</v>
       </c>
       <c r="M335" s="1" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="N335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="N335" s="1" t="n">
+      <c r="O335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -15911,10 +16919,13 @@
         <v>0.09107999999999999</v>
       </c>
       <c r="M336" s="1" t="n">
+        <v>0.09082</v>
+      </c>
+      <c r="N336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="N336" s="1" t="n">
-        <v>0.09107999999999999</v>
+      <c r="O336" s="1" t="n">
+        <v>0.09082</v>
       </c>
     </row>
     <row r="337">
@@ -15957,9 +16968,12 @@
         <v>0.17867</v>
       </c>
       <c r="M337" s="1" t="n">
+        <v>0.17936</v>
+      </c>
+      <c r="N337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="N337" s="1" t="n">
+      <c r="O337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -16003,9 +17017,12 @@
         <v>0.021</v>
       </c>
       <c r="M338" s="1" t="n">
+        <v>0.02096</v>
+      </c>
+      <c r="N338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="N338" s="1" t="n">
+      <c r="O338" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -16049,9 +17066,12 @@
         <v>0.1318</v>
       </c>
       <c r="M339" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="N339" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="N339" s="1" t="n">
+      <c r="O339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -16095,9 +17115,12 @@
         <v>0.007915999999999999</v>
       </c>
       <c r="M340" s="1" t="n">
+        <v>0.007926000000000001</v>
+      </c>
+      <c r="N340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="N340" s="1" t="n">
+      <c r="O340" s="1" t="n">
         <v>0.007915999999999999</v>
       </c>
     </row>
@@ -16141,9 +17164,12 @@
         <v>4.415</v>
       </c>
       <c r="M341" s="1" t="n">
-        <v>4.415</v>
+        <v>4.422</v>
       </c>
       <c r="N341" s="1" t="n">
+        <v>4.422</v>
+      </c>
+      <c r="O341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -16187,9 +17213,12 @@
         <v>0.18839</v>
       </c>
       <c r="M342" s="1" t="n">
+        <v>0.18981</v>
+      </c>
+      <c r="N342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="N342" s="1" t="n">
+      <c r="O342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -16233,9 +17262,12 @@
         <v>0.08371000000000001</v>
       </c>
       <c r="M343" s="1" t="n">
+        <v>0.08354</v>
+      </c>
+      <c r="N343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="N343" s="1" t="n">
+      <c r="O343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -16279,10 +17311,13 @@
         <v>0.1821</v>
       </c>
       <c r="M344" s="1" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="N344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="N344" s="1" t="n">
-        <v>0.1821</v>
+      <c r="O344" s="1" t="n">
+        <v>0.1819</v>
       </c>
     </row>
     <row r="345">
@@ -16325,10 +17360,13 @@
         <v>0.00325</v>
       </c>
       <c r="M345" s="1" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="N345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="N345" s="1" t="n">
-        <v>0.003244</v>
+      <c r="O345" s="1" t="n">
+        <v>0.00324</v>
       </c>
     </row>
     <row r="346">
@@ -16371,9 +17409,12 @@
         <v>0.09161999999999999</v>
       </c>
       <c r="M346" s="1" t="n">
+        <v>0.09127</v>
+      </c>
+      <c r="N346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="N346" s="1" t="n">
+      <c r="O346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -16417,9 +17458,12 @@
         <v>2.246</v>
       </c>
       <c r="M347" s="1" t="n">
+        <v>2.254</v>
+      </c>
+      <c r="N347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="N347" s="1" t="n">
+      <c r="O347" s="1" t="n">
         <v>2.243</v>
       </c>
     </row>
@@ -16463,10 +17507,13 @@
         <v>0.3056</v>
       </c>
       <c r="M348" s="1" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="N348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="N348" s="1" t="n">
-        <v>0.3038</v>
+      <c r="O348" s="1" t="n">
+        <v>0.3034</v>
       </c>
     </row>
     <row r="349">
@@ -16509,10 +17556,13 @@
         <v>0.02978</v>
       </c>
       <c r="M349" s="1" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="N349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="N349" s="1" t="n">
-        <v>0.02975</v>
+      <c r="O349" s="1" t="n">
+        <v>0.02969</v>
       </c>
     </row>
     <row r="350">
@@ -16555,9 +17605,12 @@
         <v>0.1279</v>
       </c>
       <c r="M350" s="1" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="N350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="N350" s="1" t="n">
+      <c r="O350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -16601,10 +17654,13 @@
         <v>0.06695</v>
       </c>
       <c r="M351" s="1" t="n">
+        <v>0.06682</v>
+      </c>
+      <c r="N351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="N351" s="1" t="n">
-        <v>0.06689000000000001</v>
+      <c r="O351" s="1" t="n">
+        <v>0.06682</v>
       </c>
     </row>
     <row r="352">
@@ -16647,9 +17703,12 @@
         <v>0.06254</v>
       </c>
       <c r="M352" s="1" t="n">
-        <v>0.06254</v>
+        <v>0.06259000000000001</v>
       </c>
       <c r="N352" s="1" t="n">
+        <v>0.06259000000000001</v>
+      </c>
+      <c r="O352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -16693,10 +17752,13 @@
         <v>0.06361</v>
       </c>
       <c r="M353" s="1" t="n">
+        <v>0.06346</v>
+      </c>
+      <c r="N353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="N353" s="1" t="n">
-        <v>0.06353</v>
+      <c r="O353" s="1" t="n">
+        <v>0.06346</v>
       </c>
     </row>
     <row r="354">
@@ -16739,9 +17801,12 @@
         <v>0.10497</v>
       </c>
       <c r="M354" s="1" t="n">
-        <v>0.10603</v>
+        <v>0.10819</v>
       </c>
       <c r="N354" s="1" t="n">
+        <v>0.10819</v>
+      </c>
+      <c r="O354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -16785,9 +17850,12 @@
         <v>0.0901</v>
       </c>
       <c r="M355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="N355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="N355" s="1" t="n">
+      <c r="O355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -16831,9 +17899,12 @@
         <v>0.07024</v>
       </c>
       <c r="M356" s="1" t="n">
+        <v>0.07026</v>
+      </c>
+      <c r="N356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="N356" s="1" t="n">
+      <c r="O356" s="1" t="n">
         <v>0.06985</v>
       </c>
     </row>
@@ -16877,9 +17948,12 @@
         <v>0.4536</v>
       </c>
       <c r="M357" s="1" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="N357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="N357" s="1" t="n">
+      <c r="O357" s="1" t="n">
         <v>0.4521</v>
       </c>
     </row>
@@ -16923,9 +17997,12 @@
         <v>0.03498</v>
       </c>
       <c r="M358" s="1" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="N358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="N358" s="1" t="n">
+      <c r="O358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -16969,9 +18046,12 @@
         <v>0.01482</v>
       </c>
       <c r="M359" s="1" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="N359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="N359" s="1" t="n">
+      <c r="O359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -17015,9 +18095,12 @@
         <v>0.13367</v>
       </c>
       <c r="M360" s="1" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="N360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="N360" s="1" t="n">
+      <c r="O360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -17061,9 +18144,12 @@
         <v>0.0005874</v>
       </c>
       <c r="M361" s="1" t="n">
+        <v>0.0005864000000000001</v>
+      </c>
+      <c r="N361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="N361" s="1" t="n">
+      <c r="O361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -17107,9 +18193,12 @@
         <v>0.03891</v>
       </c>
       <c r="M362" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="N362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="N362" s="1" t="n">
+      <c r="O362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -17153,9 +18242,12 @@
         <v>3.226</v>
       </c>
       <c r="M363" s="1" t="n">
-        <v>3.226</v>
+        <v>3.234</v>
       </c>
       <c r="N363" s="1" t="n">
+        <v>3.234</v>
+      </c>
+      <c r="O363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -17199,9 +18291,12 @@
         <v>0.165</v>
       </c>
       <c r="M364" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="N364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="N364" s="1" t="n">
+      <c r="O364" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -17245,9 +18340,12 @@
         <v>0.1139</v>
       </c>
       <c r="M365" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="N365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="N365" s="1" t="n">
+      <c r="O365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -17291,9 +18389,12 @@
         <v>0.0006405</v>
       </c>
       <c r="M366" s="1" t="n">
+        <v>0.0006405</v>
+      </c>
+      <c r="N366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="N366" s="1" t="n">
+      <c r="O366" s="1" t="n">
         <v>0.0006405</v>
       </c>
     </row>
@@ -17337,9 +18438,12 @@
         <v>0.05935</v>
       </c>
       <c r="M367" s="1" t="n">
+        <v>0.05944</v>
+      </c>
+      <c r="N367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="N367" s="1" t="n">
+      <c r="O367" s="1" t="n">
         <v>0.05927</v>
       </c>
     </row>
@@ -17383,10 +18487,13 @@
         <v>0.08217000000000001</v>
       </c>
       <c r="M368" s="1" t="n">
+        <v>0.08211</v>
+      </c>
+      <c r="N368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="N368" s="1" t="n">
-        <v>0.08217000000000001</v>
+      <c r="O368" s="1" t="n">
+        <v>0.08211</v>
       </c>
     </row>
     <row r="369">
@@ -17429,10 +18536,13 @@
         <v>0.03991</v>
       </c>
       <c r="M369" s="1" t="n">
+        <v>0.03965</v>
+      </c>
+      <c r="N369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="N369" s="1" t="n">
-        <v>0.03976</v>
+      <c r="O369" s="1" t="n">
+        <v>0.03965</v>
       </c>
     </row>
     <row r="370">
@@ -17475,9 +18585,12 @@
         <v>3.7</v>
       </c>
       <c r="M370" s="1" t="n">
+        <v>3.704</v>
+      </c>
+      <c r="N370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="N370" s="1" t="n">
+      <c r="O370" s="1" t="n">
         <v>3.695</v>
       </c>
     </row>
@@ -17521,9 +18634,12 @@
         <v>0.1218</v>
       </c>
       <c r="M371" s="1" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="N371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="N371" s="1" t="n">
+      <c r="O371" s="1" t="n">
         <v>0.1216</v>
       </c>
     </row>
@@ -17570,6 +18686,9 @@
         <v>0.01482</v>
       </c>
       <c r="N372" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="O372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -17613,9 +18732,12 @@
         <v>0.02191</v>
       </c>
       <c r="M373" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="N373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="N373" s="1" t="n">
+      <c r="O373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -17659,9 +18781,12 @@
         <v>1.8635</v>
       </c>
       <c r="M374" s="1" t="n">
+        <v>1.8663</v>
+      </c>
+      <c r="N374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="N374" s="1" t="n">
+      <c r="O374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -17705,9 +18830,12 @@
         <v>0.02104</v>
       </c>
       <c r="M375" s="1" t="n">
+        <v>0.02104</v>
+      </c>
+      <c r="N375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="N375" s="1" t="n">
+      <c r="O375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -17751,9 +18879,12 @@
         <v>1.306</v>
       </c>
       <c r="M376" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="N376" s="1" t="n">
+      <c r="O376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -17797,9 +18928,12 @@
         <v>0.2835</v>
       </c>
       <c r="M377" s="1" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="N377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="N377" s="1" t="n">
+      <c r="O377" s="1" t="n">
         <v>0.2826</v>
       </c>
     </row>
@@ -17843,9 +18977,12 @@
         <v>0.01563</v>
       </c>
       <c r="M378" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="N378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="N378" s="1" t="n">
+      <c r="O378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -17889,9 +19026,12 @@
         <v>1.5309</v>
       </c>
       <c r="M379" s="1" t="n">
+        <v>1.5303</v>
+      </c>
+      <c r="N379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="N379" s="1" t="n">
+      <c r="O379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -17935,9 +19075,12 @@
         <v>6.931999999999999e-05</v>
       </c>
       <c r="M380" s="1" t="n">
+        <v>6.931e-05</v>
+      </c>
+      <c r="N380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="N380" s="1" t="n">
+      <c r="O380" s="1" t="n">
         <v>6.918e-05</v>
       </c>
     </row>
@@ -17981,9 +19124,12 @@
         <v>2.552</v>
       </c>
       <c r="M381" s="1" t="n">
+        <v>2.552</v>
+      </c>
+      <c r="N381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="N381" s="1" t="n">
+      <c r="O381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -18027,10 +19173,13 @@
         <v>0.06722</v>
       </c>
       <c r="M382" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="N382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="N382" s="1" t="n">
-        <v>0.06722</v>
+      <c r="O382" s="1" t="n">
+        <v>0.06707</v>
       </c>
     </row>
     <row r="383">
@@ -18073,9 +19222,12 @@
         <v>0.01764</v>
       </c>
       <c r="M383" s="1" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="N383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="N383" s="1" t="n">
+      <c r="O383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -18119,9 +19271,12 @@
         <v>0.05236</v>
       </c>
       <c r="M384" s="1" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="N384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="N384" s="1" t="n">
+      <c r="O384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -18165,9 +19320,12 @@
         <v>7.585</v>
       </c>
       <c r="M385" s="1" t="n">
+        <v>7.582</v>
+      </c>
+      <c r="N385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="N385" s="1" t="n">
+      <c r="O385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -18211,9 +19369,12 @@
         <v>0.003287</v>
       </c>
       <c r="M386" s="1" t="n">
+        <v>0.003284</v>
+      </c>
+      <c r="N386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="N386" s="1" t="n">
+      <c r="O386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -18257,9 +19418,12 @@
         <v>0.0003827</v>
       </c>
       <c r="M387" s="1" t="n">
+        <v>0.0003818</v>
+      </c>
+      <c r="N387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="N387" s="1" t="n">
+      <c r="O387" s="1" t="n">
         <v>0.0003818</v>
       </c>
     </row>
@@ -18303,10 +19467,13 @@
         <v>0.009549999999999999</v>
       </c>
       <c r="M388" s="1" t="n">
+        <v>0.00953</v>
+      </c>
+      <c r="N388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="N388" s="1" t="n">
-        <v>0.009549999999999999</v>
+      <c r="O388" s="1" t="n">
+        <v>0.00953</v>
       </c>
     </row>
     <row r="389">
@@ -18349,9 +19516,12 @@
         <v>0.2886</v>
       </c>
       <c r="M389" s="1" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="N389" s="1" t="n">
         <v>0.2902</v>
       </c>
-      <c r="N389" s="1" t="n">
+      <c r="O389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -18395,9 +19565,12 @@
         <v>0.0252</v>
       </c>
       <c r="M390" s="1" t="n">
-        <v>0.0252</v>
+        <v>0.0253</v>
       </c>
       <c r="N390" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="O390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -18441,9 +19614,12 @@
         <v>2.818</v>
       </c>
       <c r="M391" s="1" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="N391" s="1" t="n">
         <v>2.833</v>
       </c>
-      <c r="N391" s="1" t="n">
+      <c r="O391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -18487,9 +19663,12 @@
         <v>0.01348</v>
       </c>
       <c r="M392" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="N392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="N392" s="1" t="n">
+      <c r="O392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -18536,6 +19715,9 @@
         <v>0.00237</v>
       </c>
       <c r="N393" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="O393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -18579,9 +19761,12 @@
         <v>0.05943</v>
       </c>
       <c r="M394" s="1" t="n">
+        <v>0.05947</v>
+      </c>
+      <c r="N394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="N394" s="1" t="n">
+      <c r="O394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -18625,9 +19810,12 @@
         <v>0.0405</v>
       </c>
       <c r="M395" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="N395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="N395" s="1" t="n">
+      <c r="O395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -18671,9 +19859,12 @@
         <v>0.09231</v>
       </c>
       <c r="M396" s="1" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="N396" s="1" t="n">
         <v>0.09272</v>
       </c>
-      <c r="N396" s="1" t="n">
+      <c r="O396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -18717,9 +19908,12 @@
         <v>0.152</v>
       </c>
       <c r="M397" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="N397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="N397" s="1" t="n">
+      <c r="O397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -18766,6 +19960,9 @@
         <v>0.929</v>
       </c>
       <c r="N398" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="O398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -18809,9 +20006,12 @@
         <v>0.05255</v>
       </c>
       <c r="M399" s="1" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="N399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="N399" s="1" t="n">
+      <c r="O399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -18855,9 +20055,12 @@
         <v>2.521</v>
       </c>
       <c r="M400" s="1" t="n">
+        <v>2.518</v>
+      </c>
+      <c r="N400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="N400" s="1" t="n">
+      <c r="O400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -18901,10 +20104,13 @@
         <v>0.01794</v>
       </c>
       <c r="M401" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="N401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="N401" s="1" t="n">
-        <v>0.01788</v>
+      <c r="O401" s="1" t="n">
+        <v>0.01785</v>
       </c>
     </row>
     <row r="402">
@@ -18947,9 +20153,12 @@
         <v>0.08044</v>
       </c>
       <c r="M402" s="1" t="n">
+        <v>0.08049000000000001</v>
+      </c>
+      <c r="N402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="N402" s="1" t="n">
+      <c r="O402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -18993,9 +20202,12 @@
         <v>1.2486</v>
       </c>
       <c r="M403" s="1" t="n">
+        <v>1.2494</v>
+      </c>
+      <c r="N403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="N403" s="1" t="n">
+      <c r="O403" s="1" t="n">
         <v>1.2455</v>
       </c>
     </row>
@@ -19039,10 +20251,13 @@
         <v>0.00715</v>
       </c>
       <c r="M404" s="1" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="N404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="N404" s="1" t="n">
-        <v>0.00715</v>
+      <c r="O404" s="1" t="n">
+        <v>0.00714</v>
       </c>
     </row>
     <row r="405">
@@ -19085,9 +20300,12 @@
         <v>0.4973</v>
       </c>
       <c r="M405" s="1" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5012</v>
       </c>
       <c r="N405" s="1" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="O405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -19131,9 +20349,12 @@
         <v>0.01153</v>
       </c>
       <c r="M406" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="N406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="N406" s="1" t="n">
+      <c r="O406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -19177,9 +20398,12 @@
         <v>0.04614</v>
       </c>
       <c r="M407" s="1" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="N407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="N407" s="1" t="n">
+      <c r="O407" s="1" t="n">
         <v>0.04612</v>
       </c>
     </row>
@@ -19223,9 +20447,12 @@
         <v>0.03947</v>
       </c>
       <c r="M408" s="1" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="N408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="N408" s="1" t="n">
+      <c r="O408" s="1" t="n">
         <v>0.0394</v>
       </c>
     </row>
@@ -19269,9 +20496,12 @@
         <v>0.05241</v>
       </c>
       <c r="M409" s="1" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="N409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="N409" s="1" t="n">
+      <c r="O409" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -19315,10 +20545,13 @@
         <v>0.01239</v>
       </c>
       <c r="M410" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="N410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="N410" s="1" t="n">
-        <v>0.01237</v>
+      <c r="O410" s="1" t="n">
+        <v>0.01235</v>
       </c>
     </row>
     <row r="411">
@@ -19361,9 +20594,12 @@
         <v>0.06382</v>
       </c>
       <c r="M411" s="1" t="n">
+        <v>0.06376</v>
+      </c>
+      <c r="N411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="N411" s="1" t="n">
+      <c r="O411" s="1" t="n">
         <v>0.06347</v>
       </c>
     </row>
@@ -19407,9 +20643,12 @@
         <v>0.04154</v>
       </c>
       <c r="M412" s="1" t="n">
+        <v>0.04144</v>
+      </c>
+      <c r="N412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="N412" s="1" t="n">
+      <c r="O412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -19453,9 +20692,12 @@
         <v>1.124</v>
       </c>
       <c r="M413" s="1" t="n">
-        <v>1.124</v>
+        <v>1.126</v>
       </c>
       <c r="N413" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="O413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -19499,9 +20741,12 @@
         <v>0.2629</v>
       </c>
       <c r="M414" s="1" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="N414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="N414" s="1" t="n">
+      <c r="O414" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -19545,9 +20790,12 @@
         <v>0.001224</v>
       </c>
       <c r="M415" s="1" t="n">
+        <v>0.001221</v>
+      </c>
+      <c r="N415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="N415" s="1" t="n">
+      <c r="O415" s="1" t="n">
         <v>0.00122</v>
       </c>
     </row>
@@ -19591,9 +20839,12 @@
         <v>0.03191</v>
       </c>
       <c r="M416" s="1" t="n">
+        <v>0.03195</v>
+      </c>
+      <c r="N416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="N416" s="1" t="n">
+      <c r="O416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -19637,9 +20888,12 @@
         <v>0.01469</v>
       </c>
       <c r="M417" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="N417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="N417" s="1" t="n">
+      <c r="O417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -19683,9 +20937,12 @@
         <v>0.1488</v>
       </c>
       <c r="M418" s="1" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="N418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="N418" s="1" t="n">
+      <c r="O418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -19729,9 +20986,12 @@
         <v>0.04952</v>
       </c>
       <c r="M419" s="1" t="n">
-        <v>0.04952</v>
+        <v>0.04968</v>
       </c>
       <c r="N419" s="1" t="n">
+        <v>0.04968</v>
+      </c>
+      <c r="O419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -19775,9 +21035,12 @@
         <v>66.90000000000001</v>
       </c>
       <c r="M420" s="1" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="N420" s="1" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="N420" s="1" t="n">
+      <c r="O420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -19824,6 +21087,9 @@
         <v>0.879</v>
       </c>
       <c r="N421" s="1" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="O421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -19867,10 +21133,13 @@
         <v>0.012567</v>
       </c>
       <c r="M422" s="1" t="n">
+        <v>0.012549</v>
+      </c>
+      <c r="N422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="N422" s="1" t="n">
-        <v>0.012567</v>
+      <c r="O422" s="1" t="n">
+        <v>0.012549</v>
       </c>
     </row>
     <row r="423">
@@ -19913,9 +21182,12 @@
         <v>0.01598</v>
       </c>
       <c r="M423" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="N423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="N423" s="1" t="n">
+      <c r="O423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -19959,9 +21231,12 @@
         <v>0.27023</v>
       </c>
       <c r="M424" s="1" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="N424" s="1" t="n">
         <v>0.27102</v>
       </c>
-      <c r="N424" s="1" t="n">
+      <c r="O424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -20005,9 +21280,12 @@
         <v>0.6004</v>
       </c>
       <c r="M425" s="1" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="N425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="N425" s="1" t="n">
+      <c r="O425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -20051,10 +21329,13 @@
         <v>0.005571</v>
       </c>
       <c r="M426" s="1" t="n">
+        <v>0.005555</v>
+      </c>
+      <c r="N426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="N426" s="1" t="n">
-        <v>0.005557</v>
+      <c r="O426" s="1" t="n">
+        <v>0.005555</v>
       </c>
     </row>
     <row r="427">
@@ -20097,9 +21378,12 @@
         <v>0.04927</v>
       </c>
       <c r="M427" s="1" t="n">
-        <v>0.04927</v>
+        <v>0.0496</v>
       </c>
       <c r="N427" s="1" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="O427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -20143,9 +21427,12 @@
         <v>0.1272</v>
       </c>
       <c r="M428" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="N428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="N428" s="1" t="n">
+      <c r="O428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -20189,9 +21476,12 @@
         <v>0.003188</v>
       </c>
       <c r="M429" s="1" t="n">
+        <v>0.003188</v>
+      </c>
+      <c r="N429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="N429" s="1" t="n">
+      <c r="O429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -20235,9 +21525,12 @@
         <v>0.0365</v>
       </c>
       <c r="M430" s="1" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="N430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="N430" s="1" t="n">
+      <c r="O430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -20281,10 +21574,13 @@
         <v>0.3982</v>
       </c>
       <c r="M431" s="1" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="N431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="N431" s="1" t="n">
-        <v>0.3982</v>
+      <c r="O431" s="1" t="n">
+        <v>0.3981</v>
       </c>
     </row>
     <row r="432">
@@ -20327,9 +21623,12 @@
         <v>0.004504</v>
       </c>
       <c r="M432" s="1" t="n">
+        <v>0.004505</v>
+      </c>
+      <c r="N432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="N432" s="1" t="n">
+      <c r="O432" s="1" t="n">
         <v>0.0045</v>
       </c>
     </row>
@@ -20373,9 +21672,12 @@
         <v>0.098</v>
       </c>
       <c r="M433" s="1" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0983</v>
       </c>
       <c r="N433" s="1" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="O433" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -20419,9 +21721,12 @@
         <v>0.01243</v>
       </c>
       <c r="M434" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="N434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="N434" s="1" t="n">
+      <c r="O434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -20465,9 +21770,12 @@
         <v>1.984</v>
       </c>
       <c r="M435" s="1" t="n">
+        <v>1.982</v>
+      </c>
+      <c r="N435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="N435" s="1" t="n">
+      <c r="O435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -20511,10 +21819,13 @@
         <v>0.001825</v>
       </c>
       <c r="M436" s="1" t="n">
+        <v>0.001798</v>
+      </c>
+      <c r="N436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="N436" s="1" t="n">
-        <v>0.001813</v>
+      <c r="O436" s="1" t="n">
+        <v>0.001798</v>
       </c>
     </row>
     <row r="437">
@@ -20557,9 +21868,12 @@
         <v>0.4425</v>
       </c>
       <c r="M437" s="1" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="N437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="N437" s="1" t="n">
+      <c r="O437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -20603,9 +21917,12 @@
         <v>0.00535</v>
       </c>
       <c r="M438" s="1" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="N438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="N438" s="1" t="n">
+      <c r="O438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -20649,9 +21966,12 @@
         <v>0.1038</v>
       </c>
       <c r="M439" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="N439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="N439" s="1" t="n">
+      <c r="O439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -20695,9 +22015,12 @@
         <v>0.0344</v>
       </c>
       <c r="M440" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="N440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="N440" s="1" t="n">
+      <c r="O440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -20741,9 +22064,12 @@
         <v>0.08214</v>
       </c>
       <c r="M441" s="1" t="n">
+        <v>0.08209</v>
+      </c>
+      <c r="N441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="N441" s="1" t="n">
+      <c r="O441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -20787,9 +22113,12 @@
         <v>1.303</v>
       </c>
       <c r="M442" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="N442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="N442" s="1" t="n">
+      <c r="O442" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -20833,9 +22162,12 @@
         <v>0.07549</v>
       </c>
       <c r="M443" s="1" t="n">
+        <v>0.07555000000000001</v>
+      </c>
+      <c r="N443" s="1" t="n">
         <v>0.07581</v>
       </c>
-      <c r="N443" s="1" t="n">
+      <c r="O443" s="1" t="n">
         <v>0.07549</v>
       </c>
     </row>
@@ -20879,9 +22211,12 @@
         <v>0.07697</v>
       </c>
       <c r="M444" s="1" t="n">
+        <v>0.07692</v>
+      </c>
+      <c r="N444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="N444" s="1" t="n">
+      <c r="O444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -20925,10 +22260,13 @@
         <v>0.04366</v>
       </c>
       <c r="M445" s="1" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="N445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="N445" s="1" t="n">
-        <v>0.04357</v>
+      <c r="O445" s="1" t="n">
+        <v>0.04356</v>
       </c>
     </row>
     <row r="446">
@@ -20971,10 +22309,13 @@
         <v>0.02142</v>
       </c>
       <c r="M446" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="N446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="N446" s="1" t="n">
-        <v>0.02142</v>
+      <c r="O446" s="1" t="n">
+        <v>0.02141</v>
       </c>
     </row>
     <row r="447">
@@ -21017,9 +22358,12 @@
         <v>0.2806</v>
       </c>
       <c r="M447" s="1" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="N447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="N447" s="1" t="n">
+      <c r="O447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -21063,9 +22407,12 @@
         <v>0.03123</v>
       </c>
       <c r="M448" s="1" t="n">
+        <v>0.03119</v>
+      </c>
+      <c r="N448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="N448" s="1" t="n">
+      <c r="O448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -21109,9 +22456,12 @@
         <v>0.00647</v>
       </c>
       <c r="M449" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="N449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="N449" s="1" t="n">
+      <c r="O449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -21155,9 +22505,12 @@
         <v>0.023086</v>
       </c>
       <c r="M450" s="1" t="n">
+        <v>0.023008</v>
+      </c>
+      <c r="N450" s="1" t="n">
         <v>0.023086</v>
       </c>
-      <c r="N450" s="1" t="n">
+      <c r="O450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -21201,9 +22554,12 @@
         <v>0.04239</v>
       </c>
       <c r="M451" s="1" t="n">
+        <v>0.04235</v>
+      </c>
+      <c r="N451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="N451" s="1" t="n">
+      <c r="O451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -21247,9 +22603,12 @@
         <v>0.07246</v>
       </c>
       <c r="M452" s="1" t="n">
+        <v>0.07216</v>
+      </c>
+      <c r="N452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="N452" s="1" t="n">
+      <c r="O452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -21293,10 +22652,13 @@
         <v>0.0005927</v>
       </c>
       <c r="M453" s="1" t="n">
+        <v>0.0005908</v>
+      </c>
+      <c r="N453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="N453" s="1" t="n">
-        <v>0.0005925</v>
+      <c r="O453" s="1" t="n">
+        <v>0.0005908</v>
       </c>
     </row>
     <row r="454">
@@ -21339,9 +22701,12 @@
         <v>0.306</v>
       </c>
       <c r="M454" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="N454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="N454" s="1" t="n">
+      <c r="O454" s="1" t="n">
         <v>0.306</v>
       </c>
     </row>
@@ -21385,9 +22750,12 @@
         <v>0.004292</v>
       </c>
       <c r="M455" s="1" t="n">
+        <v>0.004293</v>
+      </c>
+      <c r="N455" s="1" t="n">
         <v>0.004324</v>
       </c>
-      <c r="N455" s="1" t="n">
+      <c r="O455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -21431,9 +22799,12 @@
         <v>0.183</v>
       </c>
       <c r="M456" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="N456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="N456" s="1" t="n">
+      <c r="O456" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -21477,9 +22848,12 @@
         <v>0.04278</v>
       </c>
       <c r="M457" s="1" t="n">
+        <v>0.04276</v>
+      </c>
+      <c r="N457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="N457" s="1" t="n">
+      <c r="O457" s="1" t="n">
         <v>0.04268</v>
       </c>
     </row>
@@ -21523,9 +22897,12 @@
         <v>0.1461</v>
       </c>
       <c r="M458" s="1" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="N458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="N458" s="1" t="n">
+      <c r="O458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -21569,9 +22946,12 @@
         <v>0.008635</v>
       </c>
       <c r="M459" s="1" t="n">
-        <v>0.008635</v>
+        <v>0.008665000000000001</v>
       </c>
       <c r="N459" s="1" t="n">
+        <v>0.008665000000000001</v>
+      </c>
+      <c r="O459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -21615,9 +22995,12 @@
         <v>0.007357</v>
       </c>
       <c r="M460" s="1" t="n">
+        <v>0.007385</v>
+      </c>
+      <c r="N460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="N460" s="1" t="n">
+      <c r="O460" s="1" t="n">
         <v>0.007357</v>
       </c>
     </row>
@@ -21661,9 +23044,12 @@
         <v>0.0001729</v>
       </c>
       <c r="M461" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="N461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="N461" s="1" t="n">
+      <c r="O461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -21707,9 +23093,12 @@
         <v>0.02304</v>
       </c>
       <c r="M462" s="1" t="n">
+        <v>0.02313</v>
+      </c>
+      <c r="N462" s="1" t="n">
         <v>0.02321</v>
       </c>
-      <c r="N462" s="1" t="n">
+      <c r="O462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -21753,9 +23142,12 @@
         <v>0.03746</v>
       </c>
       <c r="M463" s="1" t="n">
+        <v>0.03751</v>
+      </c>
+      <c r="N463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="N463" s="1" t="n">
+      <c r="O463" s="1" t="n">
         <v>0.03685</v>
       </c>
     </row>
@@ -21799,9 +23191,12 @@
         <v>0.3013</v>
       </c>
       <c r="M464" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="N464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="N464" s="1" t="n">
+      <c r="O464" s="1" t="n">
         <v>0.3013</v>
       </c>
     </row>
@@ -21845,9 +23240,12 @@
         <v>0.03921</v>
       </c>
       <c r="M465" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="N465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="N465" s="1" t="n">
+      <c r="O465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -21891,9 +23289,12 @@
         <v>2.672</v>
       </c>
       <c r="M466" s="1" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="N466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="N466" s="1" t="n">
+      <c r="O466" s="1" t="n">
         <v>2.667</v>
       </c>
     </row>
@@ -21937,9 +23338,12 @@
         <v>0.03402</v>
       </c>
       <c r="M467" s="1" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="N467" s="1" t="n">
         <v>0.03436</v>
       </c>
-      <c r="N467" s="1" t="n">
+      <c r="O467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -21983,9 +23387,12 @@
         <v>0.1767</v>
       </c>
       <c r="M468" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="N468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="N468" s="1" t="n">
+      <c r="O468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -22029,9 +23436,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="M469" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="N469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="N469" s="1" t="n">
+      <c r="O469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -22075,9 +23485,12 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="M470" s="1" t="n">
+        <v>0.06752</v>
+      </c>
+      <c r="N470" s="1" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="N470" s="1" t="n">
+      <c r="O470" s="1" t="n">
         <v>0.06716999999999999</v>
       </c>
     </row>
@@ -22121,9 +23534,12 @@
         <v>0.04005</v>
       </c>
       <c r="M471" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="N471" s="1" t="n">
+      <c r="O471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -22167,9 +23583,12 @@
         <v>0.2478</v>
       </c>
       <c r="M472" s="1" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="N472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="N472" s="1" t="n">
+      <c r="O472" s="1" t="n">
         <v>0.2472</v>
       </c>
     </row>
@@ -22213,9 +23632,12 @@
         <v>0.016367</v>
       </c>
       <c r="M473" s="1" t="n">
+        <v>0.016379</v>
+      </c>
+      <c r="N473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="N473" s="1" t="n">
+      <c r="O473" s="1" t="n">
         <v>0.016367</v>
       </c>
     </row>
@@ -22259,9 +23681,12 @@
         <v>0.1158</v>
       </c>
       <c r="M474" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="N474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="N474" s="1" t="n">
+      <c r="O474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -22305,9 +23730,12 @@
         <v>0.04299</v>
       </c>
       <c r="M475" s="1" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="N475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="N475" s="1" t="n">
+      <c r="O475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -22351,9 +23779,12 @@
         <v>0.2074</v>
       </c>
       <c r="M476" s="1" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="N476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="N476" s="1" t="n">
+      <c r="O476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -22397,9 +23828,12 @@
         <v>0.006833</v>
       </c>
       <c r="M477" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+      <c r="N477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="N477" s="1" t="n">
+      <c r="O477" s="1" t="n">
         <v>0.006796</v>
       </c>
     </row>
@@ -22443,10 +23877,13 @@
         <v>0.01784</v>
       </c>
       <c r="M478" s="1" t="n">
+        <v>0.01782</v>
+      </c>
+      <c r="N478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="N478" s="1" t="n">
-        <v>0.01784</v>
+      <c r="O478" s="1" t="n">
+        <v>0.01782</v>
       </c>
     </row>
     <row r="479">
@@ -22489,9 +23926,12 @@
         <v>0.04688</v>
       </c>
       <c r="M479" s="1" t="n">
+        <v>0.04688</v>
+      </c>
+      <c r="N479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="N479" s="1" t="n">
+      <c r="O479" s="1" t="n">
         <v>0.04683</v>
       </c>
     </row>
@@ -22535,9 +23975,12 @@
         <v>0.2618</v>
       </c>
       <c r="M480" s="1" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="N480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N480" s="1" t="n">
+      <c r="O480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -22581,10 +24024,13 @@
         <v>0.0123</v>
       </c>
       <c r="M481" s="1" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="N481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="N481" s="1" t="n">
-        <v>0.01229</v>
+      <c r="O481" s="1" t="n">
+        <v>0.01227</v>
       </c>
     </row>
     <row r="482">
@@ -22627,9 +24073,12 @@
         <v>0.004097</v>
       </c>
       <c r="M482" s="1" t="n">
+        <v>0.004111</v>
+      </c>
+      <c r="N482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="N482" s="1" t="n">
+      <c r="O482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -22673,9 +24122,12 @@
         <v>0.123</v>
       </c>
       <c r="M483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="N483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="N483" s="1" t="n">
+      <c r="O483" s="1" t="n">
         <v>0.1229</v>
       </c>
     </row>
@@ -22719,9 +24171,12 @@
         <v>0.02201</v>
       </c>
       <c r="M484" s="1" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="N484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="N484" s="1" t="n">
+      <c r="O484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -22765,9 +24220,12 @@
         <v>0.04514</v>
       </c>
       <c r="M485" s="1" t="n">
+        <v>0.04542</v>
+      </c>
+      <c r="N485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="N485" s="1" t="n">
+      <c r="O485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -22811,9 +24269,12 @@
         <v>0.1738</v>
       </c>
       <c r="M486" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="N486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="N486" s="1" t="n">
+      <c r="O486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -22857,9 +24318,12 @@
         <v>0.2729</v>
       </c>
       <c r="M487" s="1" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="N487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="N487" s="1" t="n">
+      <c r="O487" s="1" t="n">
         <v>0.2726</v>
       </c>
     </row>
@@ -22903,9 +24367,12 @@
         <v>0.0463</v>
       </c>
       <c r="M488" s="1" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="N488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="N488" s="1" t="n">
+      <c r="O488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -22949,9 +24416,12 @@
         <v>0.0002149</v>
       </c>
       <c r="M489" s="1" t="n">
+        <v>0.0002151</v>
+      </c>
+      <c r="N489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="N489" s="1" t="n">
+      <c r="O489" s="1" t="n">
         <v>0.0002149</v>
       </c>
     </row>
@@ -22995,9 +24465,12 @@
         <v>1.779</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>1.779</v>
+        <v>1.78</v>
       </c>
       <c r="N490" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -23041,9 +24514,12 @@
         <v>16.087</v>
       </c>
       <c r="M491" s="1" t="n">
+        <v>16.064</v>
+      </c>
+      <c r="N491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="N491" s="1" t="n">
+      <c r="O491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -23087,9 +24563,12 @@
         <v>0.06676</v>
       </c>
       <c r="M492" s="1" t="n">
+        <v>0.06676</v>
+      </c>
+      <c r="N492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="N492" s="1" t="n">
+      <c r="O492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -23133,9 +24612,12 @@
         <v>0.06756</v>
       </c>
       <c r="M493" s="1" t="n">
+        <v>0.06754</v>
+      </c>
+      <c r="N493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="N493" s="1" t="n">
+      <c r="O493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -23179,9 +24661,12 @@
         <v>0.009446</v>
       </c>
       <c r="M494" s="1" t="n">
+        <v>0.009424</v>
+      </c>
+      <c r="N494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="N494" s="1" t="n">
+      <c r="O494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -23225,10 +24710,13 @@
         <v>0.005829</v>
       </c>
       <c r="M495" s="1" t="n">
+        <v>0.005809</v>
+      </c>
+      <c r="N495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="N495" s="1" t="n">
-        <v>0.005829</v>
+      <c r="O495" s="1" t="n">
+        <v>0.005809</v>
       </c>
     </row>
     <row r="496">
@@ -23271,9 +24759,12 @@
         <v>0.009889999999999999</v>
       </c>
       <c r="M496" s="1" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="N496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="N496" s="1" t="n">
+      <c r="O496" s="1" t="n">
         <v>0.00987</v>
       </c>
     </row>
@@ -23317,9 +24808,12 @@
         <v>0.0449</v>
       </c>
       <c r="M497" s="1" t="n">
-        <v>0.0449</v>
+        <v>0.0455</v>
       </c>
       <c r="N497" s="1" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="O497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -23363,9 +24857,12 @@
         <v>0.006374</v>
       </c>
       <c r="M498" s="1" t="n">
+        <v>0.006376</v>
+      </c>
+      <c r="N498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="N498" s="1" t="n">
+      <c r="O498" s="1" t="n">
         <v>0.006374</v>
       </c>
     </row>
@@ -23409,9 +24906,12 @@
         <v>0.01047</v>
       </c>
       <c r="M499" s="1" t="n">
+        <v>0.01046</v>
+      </c>
+      <c r="N499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="N499" s="1" t="n">
+      <c r="O499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -23455,9 +24955,12 @@
         <v>0.5097</v>
       </c>
       <c r="M500" s="1" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="N500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="N500" s="1" t="n">
+      <c r="O500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -23501,9 +25004,12 @@
         <v>0.03205</v>
       </c>
       <c r="M501" s="1" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="N501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="N501" s="1" t="n">
+      <c r="O501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -23547,9 +25053,12 @@
         <v>0.4436</v>
       </c>
       <c r="M502" s="1" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="N502" s="1" t="n">
         <v>0.4436</v>
       </c>
-      <c r="N502" s="1" t="n">
+      <c r="O502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -23593,9 +25102,12 @@
         <v>0.999342</v>
       </c>
       <c r="M503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="N503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="N503" s="1" t="n">
+      <c r="O503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -23639,10 +25151,13 @@
         <v>0.03509</v>
       </c>
       <c r="M504" s="1" t="n">
+        <v>0.03501</v>
+      </c>
+      <c r="N504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="N504" s="1" t="n">
-        <v>0.03509</v>
+      <c r="O504" s="1" t="n">
+        <v>0.03501</v>
       </c>
     </row>
     <row r="505">
@@ -23685,9 +25200,12 @@
         <v>0.004962</v>
       </c>
       <c r="M505" s="1" t="n">
+        <v>0.004951</v>
+      </c>
+      <c r="N505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="N505" s="1" t="n">
+      <c r="O505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -23731,9 +25249,12 @@
         <v>0.01397</v>
       </c>
       <c r="M506" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="N506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="N506" s="1" t="n">
+      <c r="O506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -23777,9 +25298,12 @@
         <v>0.003477</v>
       </c>
       <c r="M507" s="1" t="n">
+        <v>0.003475</v>
+      </c>
+      <c r="N507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="N507" s="1" t="n">
+      <c r="O507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -23823,9 +25347,12 @@
         <v>1.42</v>
       </c>
       <c r="M508" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="N508" s="1" t="n">
+      <c r="O508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -23869,9 +25396,12 @@
         <v>0.005087</v>
       </c>
       <c r="M509" s="1" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="N509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="N509" s="1" t="n">
+      <c r="O509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -23915,9 +25445,12 @@
         <v>0.01577</v>
       </c>
       <c r="M510" s="1" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="N510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="N510" s="1" t="n">
+      <c r="O510" s="1" t="n">
         <v>0.01571</v>
       </c>
     </row>
@@ -23961,9 +25494,12 @@
         <v>0.08252</v>
       </c>
       <c r="M511" s="1" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="N511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="N511" s="1" t="n">
+      <c r="O511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -24007,9 +25543,12 @@
         <v>0.007101</v>
       </c>
       <c r="M512" s="1" t="n">
+        <v>0.007098</v>
+      </c>
+      <c r="N512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="N512" s="1" t="n">
+      <c r="O512" s="1" t="n">
         <v>0.007093</v>
       </c>
     </row>
@@ -24056,6 +25595,9 @@
         <v>0.01495</v>
       </c>
       <c r="N513" s="1" t="n">
+        <v>0.01495</v>
+      </c>
+      <c r="O513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -24099,9 +25641,12 @@
         <v>0.04754</v>
       </c>
       <c r="M514" s="1" t="n">
+        <v>0.04748</v>
+      </c>
+      <c r="N514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="N514" s="1" t="n">
+      <c r="O514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -24145,9 +25690,12 @@
         <v>0.01827</v>
       </c>
       <c r="M515" s="1" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="N515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="N515" s="1" t="n">
+      <c r="O515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -24191,10 +25739,13 @@
         <v>0.0005792</v>
       </c>
       <c r="M516" s="1" t="n">
+        <v>0.000579</v>
+      </c>
+      <c r="N516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="N516" s="1" t="n">
-        <v>0.0005792</v>
+      <c r="O516" s="1" t="n">
+        <v>0.000579</v>
       </c>
     </row>
     <row r="517">
@@ -24237,9 +25788,12 @@
         <v>0.07872</v>
       </c>
       <c r="M517" s="1" t="n">
+        <v>0.07865</v>
+      </c>
+      <c r="N517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="N517" s="1" t="n">
+      <c r="O517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -24283,9 +25837,12 @@
         <v>0.006387</v>
       </c>
       <c r="M518" s="1" t="n">
+        <v>0.006386</v>
+      </c>
+      <c r="N518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="N518" s="1" t="n">
+      <c r="O518" s="1" t="n">
         <v>0.006373</v>
       </c>
     </row>
@@ -24329,9 +25886,12 @@
         <v>0.05791</v>
       </c>
       <c r="M519" s="1" t="n">
+        <v>0.05791</v>
+      </c>
+      <c r="N519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="N519" s="1" t="n">
+      <c r="O519" s="1" t="n">
         <v>0.05784</v>
       </c>
     </row>
@@ -24375,9 +25935,12 @@
         <v>0.1053</v>
       </c>
       <c r="M520" s="1" t="n">
+        <v>0.10485</v>
+      </c>
+      <c r="N520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="N520" s="1" t="n">
+      <c r="O520" s="1" t="n">
         <v>0.10469</v>
       </c>
     </row>
@@ -24421,9 +25984,12 @@
         <v>0.01798</v>
       </c>
       <c r="M521" s="1" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="N521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="N521" s="1" t="n">
+      <c r="O521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -24467,9 +26033,12 @@
         <v>0.01652</v>
       </c>
       <c r="M522" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="N522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="N522" s="1" t="n">
+      <c r="O522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -24513,9 +26082,12 @@
         <v>0.01089</v>
       </c>
       <c r="M523" s="1" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="N523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="N523" s="1" t="n">
+      <c r="O523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -24559,9 +26131,12 @@
         <v>0.007108</v>
       </c>
       <c r="M524" s="1" t="n">
+        <v>0.007116</v>
+      </c>
+      <c r="N524" s="1" t="n">
         <v>0.007158</v>
       </c>
-      <c r="N524" s="1" t="n">
+      <c r="O524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -24605,10 +26180,13 @@
         <v>0.005908</v>
       </c>
       <c r="M525" s="1" t="n">
+        <v>0.005885</v>
+      </c>
+      <c r="N525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="N525" s="1" t="n">
-        <v>0.005889</v>
+      <c r="O525" s="1" t="n">
+        <v>0.005885</v>
       </c>
     </row>
     <row r="526">
@@ -24651,9 +26229,12 @@
         <v>0.001443</v>
       </c>
       <c r="M526" s="1" t="n">
+        <v>0.001446</v>
+      </c>
+      <c r="N526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="N526" s="1" t="n">
+      <c r="O526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -24697,9 +26278,12 @@
         <v>0.374</v>
       </c>
       <c r="M527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="N527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="N527" s="1" t="n">
+      <c r="O527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -24743,9 +26327,12 @@
         <v>0.00521</v>
       </c>
       <c r="M528" s="1" t="n">
-        <v>0.00521</v>
+        <v>0.005219</v>
       </c>
       <c r="N528" s="1" t="n">
+        <v>0.005219</v>
+      </c>
+      <c r="O528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -24789,9 +26376,12 @@
         <v>2.96</v>
       </c>
       <c r="M529" s="1" t="n">
-        <v>2.96</v>
+        <v>2.961</v>
       </c>
       <c r="N529" s="1" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="O529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -24835,9 +26425,12 @@
         <v>0.1565</v>
       </c>
       <c r="M530" s="1" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="N530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="N530" s="1" t="n">
+      <c r="O530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -24884,6 +26477,9 @@
         <v>2544</v>
       </c>
       <c r="N531" s="1" t="n">
+        <v>2544</v>
+      </c>
+      <c r="O531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -24927,9 +26523,12 @@
         <v>0.0393</v>
       </c>
       <c r="M532" s="1" t="n">
+        <v>0.03923</v>
+      </c>
+      <c r="N532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="N532" s="1" t="n">
+      <c r="O532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -24973,9 +26572,12 @@
         <v>0.02165</v>
       </c>
       <c r="M533" s="1" t="n">
+        <v>0.02162</v>
+      </c>
+      <c r="N533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="N533" s="1" t="n">
+      <c r="O533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -25019,9 +26621,12 @@
         <v>0.07374</v>
       </c>
       <c r="M534" s="1" t="n">
+        <v>0.07367</v>
+      </c>
+      <c r="N534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="N534" s="1" t="n">
+      <c r="O534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -25065,9 +26670,12 @@
         <v>0.008029</v>
       </c>
       <c r="M535" s="1" t="n">
+        <v>0.008014</v>
+      </c>
+      <c r="N535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="N535" s="1" t="n">
+      <c r="O535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -25111,9 +26719,12 @@
         <v>0.05021</v>
       </c>
       <c r="M536" s="1" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="N536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="N536" s="1" t="n">
+      <c r="O536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -25157,9 +26768,12 @@
         <v>0.00404</v>
       </c>
       <c r="M537" s="1" t="n">
+        <v>0.00404</v>
+      </c>
+      <c r="N537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="N537" s="1" t="n">
+      <c r="O537" s="1" t="n">
         <v>0.00404</v>
       </c>
     </row>
@@ -25203,9 +26817,12 @@
         <v>0.08296000000000001</v>
       </c>
       <c r="M538" s="1" t="n">
+        <v>0.08296000000000001</v>
+      </c>
+      <c r="N538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="N538" s="1" t="n">
+      <c r="O538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -25249,9 +26866,12 @@
         <v>0.02496</v>
       </c>
       <c r="M539" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="N539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="N539" s="1" t="n">
+      <c r="O539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -25295,9 +26915,12 @@
         <v>0.08433</v>
       </c>
       <c r="M540" s="1" t="n">
+        <v>0.08433</v>
+      </c>
+      <c r="N540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="N540" s="1" t="n">
+      <c r="O540" s="1" t="n">
         <v>0.08433</v>
       </c>
     </row>
@@ -25341,9 +26964,12 @@
         <v>0.0189</v>
       </c>
       <c r="M541" s="1" t="n">
+        <v>0.01891</v>
+      </c>
+      <c r="N541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="N541" s="1" t="n">
+      <c r="O541" s="1" t="n">
         <v>0.0189</v>
       </c>
     </row>
@@ -25387,10 +27013,13 @@
         <v>0.0169</v>
       </c>
       <c r="M542" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="N542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="N542" s="1" t="n">
-        <v>0.0169</v>
+      <c r="O542" s="1" t="n">
+        <v>0.01689</v>
       </c>
     </row>
     <row r="543">
@@ -25436,6 +27065,9 @@
         <v>0.105</v>
       </c>
       <c r="N543" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R543"/>
+  <dimension ref="A1:S543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -435,8 +435,9 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,10 +523,15 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>price_04:00</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -583,9 +589,12 @@
         <v>70690.2</v>
       </c>
       <c r="Q2" s="1" t="n">
+        <v>70664.10000000001</v>
+      </c>
+      <c r="R2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="S2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -641,9 +650,12 @@
         <v>2077.45</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>2076.25</v>
+      </c>
+      <c r="R3" s="1" t="n">
         <v>2077.45</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="S3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -699,9 +711,12 @@
         <v>86.98</v>
       </c>
       <c r="Q4" s="1" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="R4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="S4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -757,9 +772,12 @@
         <v>4.002</v>
       </c>
       <c r="Q5" s="1" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="R5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="S5" s="1" t="n">
         <v>3.991</v>
       </c>
     </row>
@@ -815,9 +833,12 @@
         <v>0.09471</v>
       </c>
       <c r="Q6" s="1" t="n">
+        <v>0.09472999999999999</v>
+      </c>
+      <c r="R6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -873,9 +894,12 @@
         <v>1.3895</v>
       </c>
       <c r="Q7" s="1" t="n">
+        <v>1.3894</v>
+      </c>
+      <c r="R7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="S7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -931,9 +955,12 @@
         <v>22.497</v>
       </c>
       <c r="Q8" s="1" t="n">
+        <v>22.421</v>
+      </c>
+      <c r="R8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="S8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -989,9 +1016,12 @@
         <v>0.002026</v>
       </c>
       <c r="Q9" s="1" t="n">
+        <v>0.002061</v>
+      </c>
+      <c r="R9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="S9" s="1" t="n">
         <v>0.001972</v>
       </c>
     </row>
@@ -1047,9 +1077,12 @@
         <v>0.009991999999999999</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>0.009877</v>
+      </c>
+      <c r="R10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="S10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1105,9 +1138,12 @@
         <v>0.14433</v>
       </c>
       <c r="Q11" s="1" t="n">
+        <v>0.14388</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="S11" s="1" t="n">
         <v>0.13838</v>
       </c>
     </row>
@@ -1163,9 +1199,12 @@
         <v>0.011403</v>
       </c>
       <c r="Q12" s="1" t="n">
+        <v>0.011421</v>
+      </c>
+      <c r="R12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="S12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -1221,9 +1260,12 @@
         <v>38.157</v>
       </c>
       <c r="Q13" s="1" t="n">
+        <v>38.051</v>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="S13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1279,9 +1321,12 @@
         <v>653.76</v>
       </c>
       <c r="Q14" s="1" t="n">
+        <v>653.58</v>
+      </c>
+      <c r="R14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="S14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1337,9 +1382,12 @@
         <v>210.04</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>210.04</v>
+        <v>210.26</v>
       </c>
       <c r="R15" s="1" t="n">
+        <v>210.26</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1395,9 +1443,12 @@
         <v>0.0033226</v>
       </c>
       <c r="Q16" s="1" t="n">
+        <v>0.003319</v>
+      </c>
+      <c r="R16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="S16" s="1" t="n">
         <v>0.0033182</v>
       </c>
     </row>
@@ -1453,9 +1504,12 @@
         <v>238.41</v>
       </c>
       <c r="Q17" s="1" t="n">
+        <v>237.76</v>
+      </c>
+      <c r="R17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="S17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1511,10 +1565,13 @@
         <v>0.9881</v>
       </c>
       <c r="Q18" s="1" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="R18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="R18" s="1" t="n">
-        <v>0.987</v>
+      <c r="S18" s="1" t="n">
+        <v>0.9865</v>
       </c>
     </row>
     <row r="19">
@@ -1569,9 +1626,12 @@
         <v>1.0264</v>
       </c>
       <c r="Q19" s="1" t="n">
+        <v>1.0271</v>
+      </c>
+      <c r="R19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="S19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1627,9 +1687,12 @@
         <v>0.2594</v>
       </c>
       <c r="Q20" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="R20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="S20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1685,9 +1748,12 @@
         <v>0.59271</v>
       </c>
       <c r="Q21" s="1" t="n">
+        <v>0.5984699999999999</v>
+      </c>
+      <c r="R21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="S21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -1743,9 +1809,12 @@
         <v>9.032999999999999</v>
       </c>
       <c r="Q22" s="1" t="n">
+        <v>9.021000000000001</v>
+      </c>
+      <c r="R22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="S22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1801,9 +1870,12 @@
         <v>0.02399</v>
       </c>
       <c r="Q23" s="1" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="R23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="S23" s="1" t="n">
         <v>0.02397</v>
       </c>
     </row>
@@ -1859,9 +1931,12 @@
         <v>9.565</v>
       </c>
       <c r="Q24" s="1" t="n">
+        <v>9.568</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="S24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1917,9 +1992,12 @@
         <v>1.24</v>
       </c>
       <c r="Q25" s="1" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="R25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="S25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1975,9 +2053,12 @@
         <v>0.07242</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.07242</v>
+        <v>0.07253</v>
       </c>
       <c r="R26" s="1" t="n">
+        <v>0.07253</v>
+      </c>
+      <c r="S26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2033,10 +2114,13 @@
         <v>1.416</v>
       </c>
       <c r="Q27" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="R27" s="1" t="n">
-        <v>1.416</v>
+      <c r="S27" s="1" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="28">
@@ -2091,9 +2175,12 @@
         <v>1.305</v>
       </c>
       <c r="Q28" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="R28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="S28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2149,9 +2236,12 @@
         <v>463.55</v>
       </c>
       <c r="Q29" s="1" t="n">
+        <v>463.52</v>
+      </c>
+      <c r="R29" s="1" t="n">
         <v>463.55</v>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="S29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2207,9 +2297,12 @@
         <v>1.2972</v>
       </c>
       <c r="Q30" s="1" t="n">
+        <v>1.2972</v>
+      </c>
+      <c r="R30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="S30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2268,6 +2361,9 @@
         <v>5025.5</v>
       </c>
       <c r="R31" s="1" t="n">
+        <v>5025.5</v>
+      </c>
+      <c r="S31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -2323,9 +2419,12 @@
         <v>0.881</v>
       </c>
       <c r="Q32" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="R32" s="1" t="n">
+      <c r="S32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2381,9 +2480,12 @@
         <v>0.001975</v>
       </c>
       <c r="Q33" s="1" t="n">
+        <v>0.001972</v>
+      </c>
+      <c r="R33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="S33" s="1" t="n">
         <v>0.001969</v>
       </c>
     </row>
@@ -2439,9 +2541,12 @@
         <v>0.17141</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>0.17264</v>
+        <v>0.17272</v>
       </c>
       <c r="R34" s="1" t="n">
+        <v>0.17272</v>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2497,9 +2602,12 @@
         <v>0.29677</v>
       </c>
       <c r="Q35" s="1" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="R35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="S35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -2555,9 +2663,12 @@
         <v>1.783</v>
       </c>
       <c r="Q36" s="1" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="R36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="S36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -2613,10 +2724,13 @@
         <v>110.38</v>
       </c>
       <c r="Q37" s="1" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="R37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="R37" s="1" t="n">
-        <v>110.23</v>
+      <c r="S37" s="1" t="n">
+        <v>110.18</v>
       </c>
     </row>
     <row r="38">
@@ -2671,9 +2785,12 @@
         <v>0.21964</v>
       </c>
       <c r="Q38" s="1" t="n">
+        <v>0.21983</v>
+      </c>
+      <c r="R38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="S38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -2729,10 +2846,13 @@
         <v>0.1069</v>
       </c>
       <c r="Q39" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="R39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="R39" s="1" t="n">
-        <v>0.1068</v>
+      <c r="S39" s="1" t="n">
+        <v>0.1067</v>
       </c>
     </row>
     <row r="40">
@@ -2787,9 +2907,12 @@
         <v>0.37377</v>
       </c>
       <c r="Q40" s="1" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="R40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="S40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2845,9 +2968,12 @@
         <v>54.66</v>
       </c>
       <c r="Q41" s="1" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="R41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="S41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2903,10 +3029,13 @@
         <v>0.0010645</v>
       </c>
       <c r="Q42" s="1" t="n">
+        <v>0.0010558</v>
+      </c>
+      <c r="R42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="R42" s="1" t="n">
-        <v>0.0010643</v>
+      <c r="S42" s="1" t="n">
+        <v>0.0010558</v>
       </c>
     </row>
     <row r="43">
@@ -2961,9 +3090,12 @@
         <v>6.478</v>
       </c>
       <c r="Q43" s="1" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="R43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="R43" s="1" t="n">
+      <c r="S43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3019,10 +3151,13 @@
         <v>0.6276</v>
       </c>
       <c r="Q44" s="1" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="R44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="R44" s="1" t="n">
-        <v>0.6276</v>
+      <c r="S44" s="1" t="n">
+        <v>0.6263</v>
       </c>
     </row>
     <row r="45">
@@ -3077,10 +3212,13 @@
         <v>0.3528</v>
       </c>
       <c r="Q45" s="1" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="R45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="R45" s="1" t="n">
-        <v>0.3528</v>
+      <c r="S45" s="1" t="n">
+        <v>0.3519</v>
       </c>
     </row>
     <row r="46">
@@ -3135,9 +3273,12 @@
         <v>0.03321</v>
       </c>
       <c r="Q46" s="1" t="n">
+        <v>0.03308</v>
+      </c>
+      <c r="R46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="S46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3193,10 +3334,13 @@
         <v>0.07126</v>
       </c>
       <c r="Q47" s="1" t="n">
+        <v>0.07076</v>
+      </c>
+      <c r="R47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="R47" s="1" t="n">
-        <v>0.0712</v>
+      <c r="S47" s="1" t="n">
+        <v>0.07076</v>
       </c>
     </row>
     <row r="48">
@@ -3251,9 +3395,12 @@
         <v>0.7096</v>
       </c>
       <c r="Q48" s="1" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="R48" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="S48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3309,10 +3456,13 @@
         <v>0.004326</v>
       </c>
       <c r="Q49" s="1" t="n">
+        <v>0.004268</v>
+      </c>
+      <c r="R49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="R49" s="1" t="n">
-        <v>0.004326</v>
+      <c r="S49" s="1" t="n">
+        <v>0.004268</v>
       </c>
     </row>
     <row r="50">
@@ -3367,10 +3517,13 @@
         <v>0.1035</v>
       </c>
       <c r="Q50" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="R50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="R50" s="1" t="n">
-        <v>0.1035</v>
+      <c r="S50" s="1" t="n">
+        <v>0.1034</v>
       </c>
     </row>
     <row r="51">
@@ -3425,9 +3578,12 @@
         <v>0.04024</v>
       </c>
       <c r="Q51" s="1" t="n">
+        <v>0.04034</v>
+      </c>
+      <c r="R51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="S51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -3483,10 +3639,13 @@
         <v>0.1647</v>
       </c>
       <c r="Q52" s="1" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="R52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="R52" s="1" t="n">
-        <v>0.1646</v>
+      <c r="S52" s="1" t="n">
+        <v>0.1645</v>
       </c>
     </row>
     <row r="53">
@@ -3541,9 +3700,12 @@
         <v>0.02067</v>
       </c>
       <c r="Q53" s="1" t="n">
+        <v>0.02062</v>
+      </c>
+      <c r="R53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="R53" s="1" t="n">
+      <c r="S53" s="1" t="n">
         <v>0.02002</v>
       </c>
     </row>
@@ -3599,9 +3761,12 @@
         <v>0.00719</v>
       </c>
       <c r="Q54" s="1" t="n">
+        <v>0.007184</v>
+      </c>
+      <c r="R54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="S54" s="1" t="n">
         <v>0.007182</v>
       </c>
     </row>
@@ -3657,10 +3822,13 @@
         <v>3.913</v>
       </c>
       <c r="Q55" s="1" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="R55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="R55" s="1" t="n">
-        <v>3.911</v>
+      <c r="S55" s="1" t="n">
+        <v>3.909</v>
       </c>
     </row>
     <row r="56">
@@ -3715,9 +3883,12 @@
         <v>0.017032</v>
       </c>
       <c r="Q56" s="1" t="n">
+        <v>0.017019</v>
+      </c>
+      <c r="R56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="R56" s="1" t="n">
+      <c r="S56" s="1" t="n">
         <v>0.016965</v>
       </c>
     </row>
@@ -3773,10 +3944,13 @@
         <v>0.1089</v>
       </c>
       <c r="Q57" s="1" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="R57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="R57" s="1" t="n">
-        <v>0.1088</v>
+      <c r="S57" s="1" t="n">
+        <v>0.1081</v>
       </c>
     </row>
     <row r="58">
@@ -3831,9 +4005,12 @@
         <v>2.65</v>
       </c>
       <c r="Q58" s="1" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="R58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="R58" s="1" t="n">
+      <c r="S58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -3889,10 +4066,13 @@
         <v>0.1587</v>
       </c>
       <c r="Q59" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="R59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="R59" s="1" t="n">
-        <v>0.1587</v>
+      <c r="S59" s="1" t="n">
+        <v>0.1584</v>
       </c>
     </row>
     <row r="60">
@@ -3947,10 +4127,13 @@
         <v>0.005879</v>
       </c>
       <c r="Q60" s="1" t="n">
+        <v>0.005862</v>
+      </c>
+      <c r="R60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="R60" s="1" t="n">
-        <v>0.005874</v>
+      <c r="S60" s="1" t="n">
+        <v>0.005862</v>
       </c>
     </row>
     <row r="61">
@@ -4005,10 +4188,13 @@
         <v>0.09186999999999999</v>
       </c>
       <c r="Q61" s="1" t="n">
+        <v>0.09161</v>
+      </c>
+      <c r="R61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="R61" s="1" t="n">
-        <v>0.09186</v>
+      <c r="S61" s="1" t="n">
+        <v>0.09161</v>
       </c>
     </row>
     <row r="62">
@@ -4063,9 +4249,12 @@
         <v>0.9125</v>
       </c>
       <c r="Q62" s="1" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="R62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="R62" s="1" t="n">
+      <c r="S62" s="1" t="n">
         <v>0.9112</v>
       </c>
     </row>
@@ -4121,9 +4310,12 @@
         <v>0.781</v>
       </c>
       <c r="Q63" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="R63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="R63" s="1" t="n">
+      <c r="S63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -4179,9 +4371,12 @@
         <v>0.04652</v>
       </c>
       <c r="Q64" s="1" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="R64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="R64" s="1" t="n">
+      <c r="S64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -4237,9 +4432,12 @@
         <v>355.13</v>
       </c>
       <c r="Q65" s="1" t="n">
+        <v>354.57</v>
+      </c>
+      <c r="R65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="R65" s="1" t="n">
+      <c r="S65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -4295,9 +4493,12 @@
         <v>0.12439</v>
       </c>
       <c r="Q66" s="1" t="n">
+        <v>0.12518</v>
+      </c>
+      <c r="R66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="R66" s="1" t="n">
+      <c r="S66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -4353,9 +4554,12 @@
         <v>0.2258</v>
       </c>
       <c r="Q67" s="1" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="R67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="R67" s="1" t="n">
+      <c r="S67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -4411,9 +4615,12 @@
         <v>0.00339</v>
       </c>
       <c r="Q68" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="R68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="R68" s="1" t="n">
+      <c r="S68" s="1" t="n">
         <v>0.00338</v>
       </c>
     </row>
@@ -4469,9 +4676,12 @@
         <v>0.1745</v>
       </c>
       <c r="Q69" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="R69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="R69" s="1" t="n">
+      <c r="S69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -4527,10 +4737,13 @@
         <v>0.16385</v>
       </c>
       <c r="Q70" s="1" t="n">
+        <v>0.16361</v>
+      </c>
+      <c r="R70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="R70" s="1" t="n">
-        <v>0.16374</v>
+      <c r="S70" s="1" t="n">
+        <v>0.16361</v>
       </c>
     </row>
     <row r="71">
@@ -4585,9 +4798,12 @@
         <v>0.3566</v>
       </c>
       <c r="Q71" s="1" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="R71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="R71" s="1" t="n">
+      <c r="S71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -4643,9 +4859,12 @@
         <v>0.7077</v>
       </c>
       <c r="Q72" s="1" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="R72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="R72" s="1" t="n">
+      <c r="S72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -4701,9 +4920,12 @@
         <v>0.00865</v>
       </c>
       <c r="Q73" s="1" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="R73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="R73" s="1" t="n">
+      <c r="S73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -4759,9 +4981,12 @@
         <v>0.005986</v>
       </c>
       <c r="Q74" s="1" t="n">
+        <v>0.005977</v>
+      </c>
+      <c r="R74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="R74" s="1" t="n">
+      <c r="S74" s="1" t="n">
         <v>0.005967</v>
       </c>
     </row>
@@ -4817,9 +5042,12 @@
         <v>0.229</v>
       </c>
       <c r="Q75" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="R75" s="1" t="n">
         <v>0.229</v>
       </c>
-      <c r="R75" s="1" t="n">
+      <c r="S75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -4875,9 +5103,12 @@
         <v>0.3257</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>0.3265</v>
+        <v>0.3278</v>
       </c>
       <c r="R76" s="1" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="S76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -4933,9 +5164,12 @@
         <v>0.1003</v>
       </c>
       <c r="Q77" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="R77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="R77" s="1" t="n">
+      <c r="S77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -4991,10 +5225,13 @@
         <v>0.1226</v>
       </c>
       <c r="Q78" s="1" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="R78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="R78" s="1" t="n">
-        <v>0.1225</v>
+      <c r="S78" s="1" t="n">
+        <v>0.1223</v>
       </c>
     </row>
     <row r="79">
@@ -5049,9 +5286,12 @@
         <v>0.07373</v>
       </c>
       <c r="Q79" s="1" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="R79" s="1" t="n">
         <v>0.07373</v>
       </c>
-      <c r="R79" s="1" t="n">
+      <c r="S79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -5107,9 +5347,12 @@
         <v>0.04676</v>
       </c>
       <c r="Q80" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="R80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="R80" s="1" t="n">
+      <c r="S80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -5165,9 +5408,12 @@
         <v>0.000233</v>
       </c>
       <c r="Q81" s="1" t="n">
+        <v>0.000233</v>
+      </c>
+      <c r="R81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="R81" s="1" t="n">
+      <c r="S81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -5223,10 +5469,13 @@
         <v>8.215999999999999</v>
       </c>
       <c r="Q82" s="1" t="n">
+        <v>8.204000000000001</v>
+      </c>
+      <c r="R82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="R82" s="1" t="n">
-        <v>8.206</v>
+      <c r="S82" s="1" t="n">
+        <v>8.204000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5281,9 +5530,12 @@
         <v>0.0005787</v>
       </c>
       <c r="Q83" s="1" t="n">
+        <v>0.0005774</v>
+      </c>
+      <c r="R83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="R83" s="1" t="n">
+      <c r="S83" s="1" t="n">
         <v>0.0005756</v>
       </c>
     </row>
@@ -5339,9 +5591,12 @@
         <v>0.4471</v>
       </c>
       <c r="Q84" s="1" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="R84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="R84" s="1" t="n">
+      <c r="S84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -5397,9 +5652,12 @@
         <v>0.06265</v>
       </c>
       <c r="Q85" s="1" t="n">
+        <v>0.06267</v>
+      </c>
+      <c r="R85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="R85" s="1" t="n">
+      <c r="S85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -5455,10 +5713,13 @@
         <v>0.05432</v>
       </c>
       <c r="Q86" s="1" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="R86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="R86" s="1" t="n">
-        <v>0.05424</v>
+      <c r="S86" s="1" t="n">
+        <v>0.0542</v>
       </c>
     </row>
     <row r="87">
@@ -5513,9 +5774,12 @@
         <v>0.003346</v>
       </c>
       <c r="Q87" s="1" t="n">
+        <v>0.003349</v>
+      </c>
+      <c r="R87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="R87" s="1" t="n">
+      <c r="S87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -5571,9 +5835,12 @@
         <v>0.05037</v>
       </c>
       <c r="Q88" s="1" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="R88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="R88" s="1" t="n">
+      <c r="S88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -5629,9 +5896,12 @@
         <v>0.03108</v>
       </c>
       <c r="Q89" s="1" t="n">
+        <v>0.03123</v>
+      </c>
+      <c r="R89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="R89" s="1" t="n">
+      <c r="S89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -5687,10 +5957,13 @@
         <v>0.346</v>
       </c>
       <c r="Q90" s="1" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="R90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="R90" s="1" t="n">
-        <v>0.346</v>
+      <c r="S90" s="1" t="n">
+        <v>0.3453</v>
       </c>
     </row>
     <row r="91">
@@ -5745,9 +6018,12 @@
         <v>0.07739</v>
       </c>
       <c r="Q91" s="1" t="n">
+        <v>0.07776</v>
+      </c>
+      <c r="R91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="R91" s="1" t="n">
+      <c r="S91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -5803,9 +6079,12 @@
         <v>0.361</v>
       </c>
       <c r="Q92" s="1" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="R92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="R92" s="1" t="n">
+      <c r="S92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -5861,9 +6140,12 @@
         <v>1.9722</v>
       </c>
       <c r="Q93" s="1" t="n">
+        <v>1.9762</v>
+      </c>
+      <c r="R93" s="1" t="n">
         <v>1.9809</v>
       </c>
-      <c r="R93" s="1" t="n">
+      <c r="S93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -5919,10 +6201,13 @@
         <v>0.2586</v>
       </c>
       <c r="Q94" s="1" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="R94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="R94" s="1" t="n">
-        <v>0.2583</v>
+      <c r="S94" s="1" t="n">
+        <v>0.2581</v>
       </c>
     </row>
     <row r="95">
@@ -5977,9 +6262,12 @@
         <v>0.04574</v>
       </c>
       <c r="Q95" s="1" t="n">
+        <v>0.04547</v>
+      </c>
+      <c r="R95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="R95" s="1" t="n">
+      <c r="S95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -6035,9 +6323,12 @@
         <v>0.006101</v>
       </c>
       <c r="Q96" s="1" t="n">
+        <v>0.006146</v>
+      </c>
+      <c r="R96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="R96" s="1" t="n">
+      <c r="S96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -6093,10 +6384,13 @@
         <v>0.001724</v>
       </c>
       <c r="Q97" s="1" t="n">
+        <v>0.001716</v>
+      </c>
+      <c r="R97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="R97" s="1" t="n">
-        <v>0.001723</v>
+      <c r="S97" s="1" t="n">
+        <v>0.001716</v>
       </c>
     </row>
     <row r="98">
@@ -6151,10 +6445,13 @@
         <v>5.198</v>
       </c>
       <c r="Q98" s="1" t="n">
+        <v>5.179</v>
+      </c>
+      <c r="R98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="R98" s="1" t="n">
-        <v>5.188</v>
+      <c r="S98" s="1" t="n">
+        <v>5.179</v>
       </c>
     </row>
     <row r="99">
@@ -6209,9 +6506,12 @@
         <v>0.01514</v>
       </c>
       <c r="Q99" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="R99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="R99" s="1" t="n">
+      <c r="S99" s="1" t="n">
         <v>0.01508</v>
       </c>
     </row>
@@ -6267,9 +6567,12 @@
         <v>0.5531</v>
       </c>
       <c r="Q100" s="1" t="n">
+        <v>0.5527</v>
+      </c>
+      <c r="R100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="R100" s="1" t="n">
+      <c r="S100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -6325,10 +6628,13 @@
         <v>0.09</v>
       </c>
       <c r="Q101" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="R101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="R101" s="1" t="n">
-        <v>0.09</v>
+      <c r="S101" s="1" t="n">
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6689,13 @@
         <v>32.4</v>
       </c>
       <c r="Q102" s="1" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="R102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="R102" s="1" t="n">
-        <v>32.36</v>
+      <c r="S102" s="1" t="n">
+        <v>32.34</v>
       </c>
     </row>
     <row r="103">
@@ -6441,9 +6750,12 @@
         <v>0.03188</v>
       </c>
       <c r="Q103" s="1" t="n">
+        <v>0.03192</v>
+      </c>
+      <c r="R103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="R103" s="1" t="n">
+      <c r="S103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -6499,9 +6811,12 @@
         <v>0.06572</v>
       </c>
       <c r="Q104" s="1" t="n">
+        <v>0.06564</v>
+      </c>
+      <c r="R104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="R104" s="1" t="n">
+      <c r="S104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -6557,9 +6872,12 @@
         <v>1.3034</v>
       </c>
       <c r="Q105" s="1" t="n">
+        <v>1.3012</v>
+      </c>
+      <c r="R105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="R105" s="1" t="n">
+      <c r="S105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -6615,9 +6933,12 @@
         <v>0.1204</v>
       </c>
       <c r="Q106" s="1" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="R106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="R106" s="1" t="n">
+      <c r="S106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -6673,9 +6994,12 @@
         <v>0.12</v>
       </c>
       <c r="Q107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="R107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="R107" s="1" t="n">
+      <c r="S107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -6731,9 +7055,12 @@
         <v>0.09596</v>
       </c>
       <c r="Q108" s="1" t="n">
+        <v>0.09586</v>
+      </c>
+      <c r="R108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="R108" s="1" t="n">
+      <c r="S108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -6789,9 +7116,12 @@
         <v>0.13863</v>
       </c>
       <c r="Q109" s="1" t="n">
+        <v>0.14032</v>
+      </c>
+      <c r="R109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="R109" s="1" t="n">
+      <c r="S109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -6847,9 +7177,12 @@
         <v>5.565</v>
       </c>
       <c r="Q110" s="1" t="n">
+        <v>5.569</v>
+      </c>
+      <c r="R110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="R110" s="1" t="n">
+      <c r="S110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -6905,9 +7238,12 @@
         <v>1.099</v>
       </c>
       <c r="Q111" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="R111" s="1" t="n">
+      <c r="S111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -6963,10 +7299,13 @@
         <v>0.028821</v>
       </c>
       <c r="Q112" s="1" t="n">
+        <v>0.028817</v>
+      </c>
+      <c r="R112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="R112" s="1" t="n">
-        <v>0.028821</v>
+      <c r="S112" s="1" t="n">
+        <v>0.028817</v>
       </c>
     </row>
     <row r="113">
@@ -7021,10 +7360,13 @@
         <v>1.868</v>
       </c>
       <c r="Q113" s="1" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="R113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="R113" s="1" t="n">
-        <v>1.868</v>
+      <c r="S113" s="1" t="n">
+        <v>1.867</v>
       </c>
     </row>
     <row r="114">
@@ -7079,9 +7421,12 @@
         <v>0.05875</v>
       </c>
       <c r="Q114" s="1" t="n">
+        <v>0.05871</v>
+      </c>
+      <c r="R114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="R114" s="1" t="n">
+      <c r="S114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -7137,9 +7482,12 @@
         <v>0.12859</v>
       </c>
       <c r="Q115" s="1" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="R115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="R115" s="1" t="n">
+      <c r="S115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -7195,9 +7543,12 @@
         <v>1.1066</v>
       </c>
       <c r="Q116" s="1" t="n">
+        <v>1.1039</v>
+      </c>
+      <c r="R116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="R116" s="1" t="n">
+      <c r="S116" s="1" t="n">
         <v>1.1039</v>
       </c>
     </row>
@@ -7253,10 +7604,13 @@
         <v>0.1515</v>
       </c>
       <c r="Q117" s="1" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="R117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="R117" s="1" t="n">
-        <v>0.1515</v>
+      <c r="S117" s="1" t="n">
+        <v>0.1491</v>
       </c>
     </row>
     <row r="118">
@@ -7311,9 +7665,12 @@
         <v>0.1583</v>
       </c>
       <c r="Q118" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="R118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="R118" s="1" t="n">
+      <c r="S118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -7369,9 +7726,12 @@
         <v>0.04721</v>
       </c>
       <c r="Q119" s="1" t="n">
+        <v>0.04724</v>
+      </c>
+      <c r="R119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="R119" s="1" t="n">
+      <c r="S119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -7427,10 +7787,13 @@
         <v>3.018</v>
       </c>
       <c r="Q120" s="1" t="n">
+        <v>3.014</v>
+      </c>
+      <c r="R120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="R120" s="1" t="n">
-        <v>3.016</v>
+      <c r="S120" s="1" t="n">
+        <v>3.014</v>
       </c>
     </row>
     <row r="121">
@@ -7485,9 +7848,12 @@
         <v>0.2972</v>
       </c>
       <c r="Q121" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="R121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="R121" s="1" t="n">
+      <c r="S121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -7543,10 +7909,13 @@
         <v>0.5793</v>
       </c>
       <c r="Q122" s="1" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="R122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="R122" s="1" t="n">
-        <v>0.5792</v>
+      <c r="S122" s="1" t="n">
+        <v>0.5783</v>
       </c>
     </row>
     <row r="123">
@@ -7601,9 +7970,12 @@
         <v>0.01254</v>
       </c>
       <c r="Q123" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="R123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="R123" s="1" t="n">
+      <c r="S123" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -7659,9 +8031,12 @@
         <v>0.1575</v>
       </c>
       <c r="Q124" s="1" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="R124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="R124" s="1" t="n">
+      <c r="S124" s="1" t="n">
         <v>0.1574</v>
       </c>
     </row>
@@ -7717,9 +8092,12 @@
         <v>0.001783</v>
       </c>
       <c r="Q125" s="1" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="R125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="R125" s="1" t="n">
+      <c r="S125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -7775,9 +8153,12 @@
         <v>0.0004842</v>
       </c>
       <c r="Q126" s="1" t="n">
+        <v>0.0004835</v>
+      </c>
+      <c r="R126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="R126" s="1" t="n">
+      <c r="S126" s="1" t="n">
         <v>0.0004831</v>
       </c>
     </row>
@@ -7833,10 +8214,13 @@
         <v>0.02935</v>
       </c>
       <c r="Q127" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="R127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="R127" s="1" t="n">
-        <v>0.02934</v>
+      <c r="S127" s="1" t="n">
+        <v>0.0293</v>
       </c>
     </row>
     <row r="128">
@@ -7891,10 +8275,13 @@
         <v>0.04125</v>
       </c>
       <c r="Q128" s="1" t="n">
+        <v>0.04117</v>
+      </c>
+      <c r="R128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="R128" s="1" t="n">
-        <v>0.04119</v>
+      <c r="S128" s="1" t="n">
+        <v>0.04117</v>
       </c>
     </row>
     <row r="129">
@@ -7949,9 +8336,12 @@
         <v>0.04868</v>
       </c>
       <c r="Q129" s="1" t="n">
-        <v>0.04887</v>
+        <v>0.04889</v>
       </c>
       <c r="R129" s="1" t="n">
+        <v>0.04889</v>
+      </c>
+      <c r="S129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -8007,9 +8397,12 @@
         <v>1.22e-05</v>
       </c>
       <c r="Q130" s="1" t="n">
+        <v>1.23e-05</v>
+      </c>
+      <c r="R130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="R130" s="1" t="n">
+      <c r="S130" s="1" t="n">
         <v>1.22e-05</v>
       </c>
     </row>
@@ -8065,9 +8458,12 @@
         <v>6.9e-06</v>
       </c>
       <c r="Q131" s="1" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="R131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="R131" s="1" t="n">
+      <c r="S131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -8123,10 +8519,13 @@
         <v>0.00699</v>
       </c>
       <c r="Q132" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="R132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="R132" s="1" t="n">
-        <v>0.00699</v>
+      <c r="S132" s="1" t="n">
+        <v>0.00698</v>
       </c>
     </row>
     <row r="133">
@@ -8181,10 +8580,13 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="Q133" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="R133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="R133" s="1" t="n">
-        <v>0.09660000000000001</v>
+      <c r="S133" s="1" t="n">
+        <v>0.0965</v>
       </c>
     </row>
     <row r="134">
@@ -8239,9 +8641,12 @@
         <v>0.0004106</v>
       </c>
       <c r="Q134" s="1" t="n">
+        <v>0.0004094</v>
+      </c>
+      <c r="R134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="R134" s="1" t="n">
+      <c r="S134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -8297,9 +8702,12 @@
         <v>0.08195</v>
       </c>
       <c r="Q135" s="1" t="n">
+        <v>0.08209</v>
+      </c>
+      <c r="R135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="R135" s="1" t="n">
+      <c r="S135" s="1" t="n">
         <v>0.08195</v>
       </c>
     </row>
@@ -8355,9 +8763,12 @@
         <v>0.007875999999999999</v>
       </c>
       <c r="Q136" s="1" t="n">
+        <v>0.007858</v>
+      </c>
+      <c r="R136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="R136" s="1" t="n">
+      <c r="S136" s="1" t="n">
         <v>0.007851</v>
       </c>
     </row>
@@ -8413,10 +8824,13 @@
         <v>0.0008207000000000001</v>
       </c>
       <c r="Q137" s="1" t="n">
+        <v>0.0008158</v>
+      </c>
+      <c r="R137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="R137" s="1" t="n">
-        <v>0.000816</v>
+      <c r="S137" s="1" t="n">
+        <v>0.0008158</v>
       </c>
     </row>
     <row r="138">
@@ -8471,10 +8885,13 @@
         <v>0.1469</v>
       </c>
       <c r="Q138" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="R138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="R138" s="1" t="n">
-        <v>0.1468</v>
+      <c r="S138" s="1" t="n">
+        <v>0.1465</v>
       </c>
     </row>
     <row r="139">
@@ -8529,10 +8946,13 @@
         <v>0.006693</v>
       </c>
       <c r="Q139" s="1" t="n">
+        <v>0.006682</v>
+      </c>
+      <c r="R139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="R139" s="1" t="n">
-        <v>0.006689</v>
+      <c r="S139" s="1" t="n">
+        <v>0.006682</v>
       </c>
     </row>
     <row r="140">
@@ -8587,9 +9007,12 @@
         <v>0.01386</v>
       </c>
       <c r="Q140" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="R140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="R140" s="1" t="n">
+      <c r="S140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -8645,9 +9068,12 @@
         <v>0.09718</v>
       </c>
       <c r="Q141" s="1" t="n">
+        <v>0.09722</v>
+      </c>
+      <c r="R141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="R141" s="1" t="n">
+      <c r="S141" s="1" t="n">
         <v>0.09718</v>
       </c>
     </row>
@@ -8703,9 +9129,12 @@
         <v>0.05417</v>
       </c>
       <c r="Q142" s="1" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="R142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="R142" s="1" t="n">
+      <c r="S142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -8761,10 +9190,13 @@
         <v>0.3223</v>
       </c>
       <c r="Q143" s="1" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="R143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="R143" s="1" t="n">
-        <v>0.3222</v>
+      <c r="S143" s="1" t="n">
+        <v>0.3221</v>
       </c>
     </row>
     <row r="144">
@@ -8819,9 +9251,12 @@
         <v>0.0257</v>
       </c>
       <c r="Q144" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="R144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="R144" s="1" t="n">
+      <c r="S144" s="1" t="n">
         <v>0.02564</v>
       </c>
     </row>
@@ -8877,10 +9312,13 @@
         <v>0.2367</v>
       </c>
       <c r="Q145" s="1" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="R145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="R145" s="1" t="n">
-        <v>0.2367</v>
+      <c r="S145" s="1" t="n">
+        <v>0.2362</v>
       </c>
     </row>
     <row r="146">
@@ -8935,9 +9373,12 @@
         <v>0.00702</v>
       </c>
       <c r="Q146" s="1" t="n">
+        <v>0.006992</v>
+      </c>
+      <c r="R146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="R146" s="1" t="n">
+      <c r="S146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -8993,10 +9434,13 @@
         <v>0.08656999999999999</v>
       </c>
       <c r="Q147" s="1" t="n">
+        <v>0.08597</v>
+      </c>
+      <c r="R147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="R147" s="1" t="n">
-        <v>0.08637</v>
+      <c r="S147" s="1" t="n">
+        <v>0.08597</v>
       </c>
     </row>
     <row r="148">
@@ -9051,9 +9495,12 @@
         <v>0.05202</v>
       </c>
       <c r="Q148" s="1" t="n">
+        <v>0.05233</v>
+      </c>
+      <c r="R148" s="1" t="n">
         <v>0.05284</v>
       </c>
-      <c r="R148" s="1" t="n">
+      <c r="S148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -9109,9 +9556,12 @@
         <v>0.02398</v>
       </c>
       <c r="Q149" s="1" t="n">
-        <v>0.02398</v>
+        <v>0.02399</v>
       </c>
       <c r="R149" s="1" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="S149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -9167,9 +9617,12 @@
         <v>0.08567</v>
       </c>
       <c r="Q150" s="1" t="n">
+        <v>0.08584</v>
+      </c>
+      <c r="R150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="R150" s="1" t="n">
+      <c r="S150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -9225,9 +9678,12 @@
         <v>0.0232</v>
       </c>
       <c r="Q151" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="R151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="R151" s="1" t="n">
+      <c r="S151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -9283,9 +9739,12 @@
         <v>0.02541</v>
       </c>
       <c r="Q152" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="R152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="R152" s="1" t="n">
+      <c r="S152" s="1" t="n">
         <v>0.02534</v>
       </c>
     </row>
@@ -9341,9 +9800,12 @@
         <v>0.0002131</v>
       </c>
       <c r="Q153" s="1" t="n">
+        <v>0.0002141</v>
+      </c>
+      <c r="R153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="R153" s="1" t="n">
+      <c r="S153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -9399,10 +9861,13 @@
         <v>0.438</v>
       </c>
       <c r="Q154" s="1" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="R154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="R154" s="1" t="n">
-        <v>0.4376</v>
+      <c r="S154" s="1" t="n">
+        <v>0.4371</v>
       </c>
     </row>
     <row r="155">
@@ -9457,9 +9922,12 @@
         <v>0.06759</v>
       </c>
       <c r="Q155" s="1" t="n">
+        <v>0.06775</v>
+      </c>
+      <c r="R155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="R155" s="1" t="n">
+      <c r="S155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -9515,9 +9983,12 @@
         <v>0.1276</v>
       </c>
       <c r="Q156" s="1" t="n">
+        <v>0.12763</v>
+      </c>
+      <c r="R156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="R156" s="1" t="n">
+      <c r="S156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -9573,9 +10044,12 @@
         <v>0.4839</v>
       </c>
       <c r="Q157" s="1" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="R157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="R157" s="1" t="n">
+      <c r="S157" s="1" t="n">
         <v>0.4838</v>
       </c>
     </row>
@@ -9631,9 +10105,12 @@
         <v>0.4517</v>
       </c>
       <c r="Q158" s="1" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="R158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="R158" s="1" t="n">
+      <c r="S158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -9689,10 +10166,13 @@
         <v>0.007456</v>
       </c>
       <c r="Q159" s="1" t="n">
+        <v>0.007427</v>
+      </c>
+      <c r="R159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="R159" s="1" t="n">
-        <v>0.007456</v>
+      <c r="S159" s="1" t="n">
+        <v>0.007427</v>
       </c>
     </row>
     <row r="160">
@@ -9747,9 +10227,12 @@
         <v>0.004658</v>
       </c>
       <c r="Q160" s="1" t="n">
+        <v>0.004652</v>
+      </c>
+      <c r="R160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="R160" s="1" t="n">
+      <c r="S160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -9805,10 +10288,13 @@
         <v>0.004294</v>
       </c>
       <c r="Q161" s="1" t="n">
+        <v>0.004283</v>
+      </c>
+      <c r="R161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="R161" s="1" t="n">
-        <v>0.00429</v>
+      <c r="S161" s="1" t="n">
+        <v>0.004283</v>
       </c>
     </row>
     <row r="162">
@@ -9863,10 +10349,13 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="Q162" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="R162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="R162" s="1" t="n">
-        <v>0.0956</v>
+      <c r="S162" s="1" t="n">
+        <v>0.0955</v>
       </c>
     </row>
     <row r="163">
@@ -9921,9 +10410,12 @@
         <v>0.2855</v>
       </c>
       <c r="Q163" s="1" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="R163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="R163" s="1" t="n">
+      <c r="S163" s="1" t="n">
         <v>0.285</v>
       </c>
     </row>
@@ -9979,9 +10471,12 @@
         <v>0.1145</v>
       </c>
       <c r="Q164" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="R164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="R164" s="1" t="n">
+      <c r="S164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -10037,10 +10532,13 @@
         <v>0.1754</v>
       </c>
       <c r="Q165" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="R165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="R165" s="1" t="n">
-        <v>0.1753</v>
+      <c r="S165" s="1" t="n">
+        <v>0.1751</v>
       </c>
     </row>
     <row r="166">
@@ -10095,10 +10593,13 @@
         <v>0.01009</v>
       </c>
       <c r="Q166" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="R166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="R166" s="1" t="n">
-        <v>0.01006</v>
+      <c r="S166" s="1" t="n">
+        <v>0.01005</v>
       </c>
     </row>
     <row r="167">
@@ -10153,10 +10654,13 @@
         <v>1.823</v>
       </c>
       <c r="Q167" s="1" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="R167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="R167" s="1" t="n">
-        <v>1.823</v>
+      <c r="S167" s="1" t="n">
+        <v>1.818</v>
       </c>
     </row>
     <row r="168">
@@ -10211,9 +10715,12 @@
         <v>1.346</v>
       </c>
       <c r="Q168" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="R168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="R168" s="1" t="n">
+      <c r="S168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -10269,10 +10776,13 @@
         <v>0.007305</v>
       </c>
       <c r="Q169" s="1" t="n">
+        <v>0.007295</v>
+      </c>
+      <c r="R169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="R169" s="1" t="n">
-        <v>0.007296</v>
+      <c r="S169" s="1" t="n">
+        <v>0.007295</v>
       </c>
     </row>
     <row r="170">
@@ -10327,9 +10837,12 @@
         <v>0.0116</v>
       </c>
       <c r="Q170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="R170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="R170" s="1" t="n">
+      <c r="S170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -10385,10 +10898,13 @@
         <v>0.005794</v>
       </c>
       <c r="Q171" s="1" t="n">
+        <v>0.005772</v>
+      </c>
+      <c r="R171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="R171" s="1" t="n">
-        <v>0.00578</v>
+      <c r="S171" s="1" t="n">
+        <v>0.005772</v>
       </c>
     </row>
     <row r="172">
@@ -10443,9 +10959,12 @@
         <v>0.14898</v>
       </c>
       <c r="Q172" s="1" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="R172" s="1" t="n">
         <v>0.14898</v>
       </c>
-      <c r="R172" s="1" t="n">
+      <c r="S172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -10501,9 +11020,12 @@
         <v>4.886</v>
       </c>
       <c r="Q173" s="1" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="R173" s="1" t="n">
         <v>4.909</v>
       </c>
-      <c r="R173" s="1" t="n">
+      <c r="S173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -10559,10 +11081,13 @@
         <v>0.07822</v>
       </c>
       <c r="Q174" s="1" t="n">
+        <v>0.07808</v>
+      </c>
+      <c r="R174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="R174" s="1" t="n">
-        <v>0.07819</v>
+      <c r="S174" s="1" t="n">
+        <v>0.07808</v>
       </c>
     </row>
     <row r="175">
@@ -10617,9 +11142,12 @@
         <v>0.007421</v>
       </c>
       <c r="Q175" s="1" t="n">
+        <v>0.007418</v>
+      </c>
+      <c r="R175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="R175" s="1" t="n">
+      <c r="S175" s="1" t="n">
         <v>0.007407</v>
       </c>
     </row>
@@ -10675,9 +11203,12 @@
         <v>0.2</v>
       </c>
       <c r="Q176" s="1" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="R176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="R176" s="1" t="n">
+      <c r="S176" s="1" t="n">
         <v>0.1997</v>
       </c>
     </row>
@@ -10733,9 +11264,12 @@
         <v>0.05185</v>
       </c>
       <c r="Q177" s="1" t="n">
+        <v>0.05176</v>
+      </c>
+      <c r="R177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="R177" s="1" t="n">
+      <c r="S177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -10791,9 +11325,12 @@
         <v>0.05473</v>
       </c>
       <c r="Q178" s="1" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="R178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="R178" s="1" t="n">
+      <c r="S178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -10849,9 +11386,12 @@
         <v>0.02324</v>
       </c>
       <c r="Q179" s="1" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="R179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="R179" s="1" t="n">
+      <c r="S179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -10907,10 +11447,13 @@
         <v>0.6951000000000001</v>
       </c>
       <c r="Q180" s="1" t="n">
+        <v>0.6936</v>
+      </c>
+      <c r="R180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="R180" s="1" t="n">
-        <v>0.6938</v>
+      <c r="S180" s="1" t="n">
+        <v>0.6936</v>
       </c>
     </row>
     <row r="181">
@@ -10965,9 +11508,12 @@
         <v>0.0003745</v>
       </c>
       <c r="Q181" s="1" t="n">
+        <v>0.0003725</v>
+      </c>
+      <c r="R181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="R181" s="1" t="n">
+      <c r="S181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -11023,9 +11569,12 @@
         <v>0.01257</v>
       </c>
       <c r="Q182" s="1" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="R182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="R182" s="1" t="n">
+      <c r="S182" s="1" t="n">
         <v>0.01255</v>
       </c>
     </row>
@@ -11081,9 +11630,12 @@
         <v>4.228</v>
       </c>
       <c r="Q183" s="1" t="n">
+        <v>4.224</v>
+      </c>
+      <c r="R183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="R183" s="1" t="n">
+      <c r="S183" s="1" t="n">
         <v>4.22</v>
       </c>
     </row>
@@ -11139,10 +11691,13 @@
         <v>0.2359</v>
       </c>
       <c r="Q184" s="1" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="R184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="R184" s="1" t="n">
-        <v>0.2354</v>
+      <c r="S184" s="1" t="n">
+        <v>0.2351</v>
       </c>
     </row>
     <row r="185">
@@ -11197,9 +11752,12 @@
         <v>0.03684</v>
       </c>
       <c r="Q185" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="R185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="R185" s="1" t="n">
+      <c r="S185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -11255,9 +11813,12 @@
         <v>0.11557</v>
       </c>
       <c r="Q186" s="1" t="n">
+        <v>0.11564</v>
+      </c>
+      <c r="R186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="R186" s="1" t="n">
+      <c r="S186" s="1" t="n">
         <v>0.11557</v>
       </c>
     </row>
@@ -11313,9 +11874,12 @@
         <v>0.009169999999999999</v>
       </c>
       <c r="Q187" s="1" t="n">
+        <v>0.009084999999999999</v>
+      </c>
+      <c r="R187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="R187" s="1" t="n">
+      <c r="S187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -11371,10 +11935,13 @@
         <v>0.0973</v>
       </c>
       <c r="Q188" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="R188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="R188" s="1" t="n">
-        <v>0.09719999999999999</v>
+      <c r="S188" s="1" t="n">
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -11429,10 +11996,13 @@
         <v>0.02749</v>
       </c>
       <c r="Q189" s="1" t="n">
+        <v>0.02742</v>
+      </c>
+      <c r="R189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="R189" s="1" t="n">
-        <v>0.02749</v>
+      <c r="S189" s="1" t="n">
+        <v>0.02742</v>
       </c>
     </row>
     <row r="190">
@@ -11487,9 +12057,12 @@
         <v>0.008659999999999999</v>
       </c>
       <c r="Q190" s="1" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="R190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="R190" s="1" t="n">
+      <c r="S190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -11545,9 +12118,12 @@
         <v>0.001951</v>
       </c>
       <c r="Q191" s="1" t="n">
+        <v>0.001951</v>
+      </c>
+      <c r="R191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="R191" s="1" t="n">
+      <c r="S191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -11603,9 +12179,12 @@
         <v>0.1003</v>
       </c>
       <c r="Q192" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="R192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="R192" s="1" t="n">
+      <c r="S192" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -11661,9 +12240,12 @@
         <v>0.02312</v>
       </c>
       <c r="Q193" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="R193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="R193" s="1" t="n">
+      <c r="S193" s="1" t="n">
         <v>0.02312</v>
       </c>
     </row>
@@ -11719,9 +12301,12 @@
         <v>0.01343</v>
       </c>
       <c r="Q194" s="1" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="R194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="R194" s="1" t="n">
+      <c r="S194" s="1" t="n">
         <v>0.01342</v>
       </c>
     </row>
@@ -11777,10 +12362,13 @@
         <v>0.02083</v>
       </c>
       <c r="Q195" s="1" t="n">
+        <v>0.02078</v>
+      </c>
+      <c r="R195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="R195" s="1" t="n">
-        <v>0.02079</v>
+      <c r="S195" s="1" t="n">
+        <v>0.02078</v>
       </c>
     </row>
     <row r="196">
@@ -11835,9 +12423,12 @@
         <v>0.17643</v>
       </c>
       <c r="Q196" s="1" t="n">
-        <v>0.17643</v>
+        <v>0.17659</v>
       </c>
       <c r="R196" s="1" t="n">
+        <v>0.17659</v>
+      </c>
+      <c r="S196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -11893,9 +12484,12 @@
         <v>0.00734</v>
       </c>
       <c r="Q197" s="1" t="n">
+        <v>0.007366</v>
+      </c>
+      <c r="R197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="R197" s="1" t="n">
+      <c r="S197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -11951,9 +12545,12 @@
         <v>0.01908</v>
       </c>
       <c r="Q198" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="R198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="R198" s="1" t="n">
+      <c r="S198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -12009,9 +12606,12 @@
         <v>0.01657</v>
       </c>
       <c r="Q199" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="R199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="R199" s="1" t="n">
+      <c r="S199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -12067,9 +12667,12 @@
         <v>0.2977</v>
       </c>
       <c r="Q200" s="1" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="R200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="R200" s="1" t="n">
+      <c r="S200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -12125,9 +12728,12 @@
         <v>0.006224</v>
       </c>
       <c r="Q201" s="1" t="n">
+        <v>0.006208</v>
+      </c>
+      <c r="R201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="R201" s="1" t="n">
+      <c r="S201" s="1" t="n">
         <v>0.006205</v>
       </c>
     </row>
@@ -12183,10 +12789,13 @@
         <v>0.0004411</v>
       </c>
       <c r="Q202" s="1" t="n">
+        <v>0.0004404</v>
+      </c>
+      <c r="R202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="R202" s="1" t="n">
-        <v>0.0004411</v>
+      <c r="S202" s="1" t="n">
+        <v>0.0004404</v>
       </c>
     </row>
     <row r="203">
@@ -12241,9 +12850,12 @@
         <v>0.007276</v>
       </c>
       <c r="Q203" s="1" t="n">
+        <v>0.007272</v>
+      </c>
+      <c r="R203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="R203" s="1" t="n">
+      <c r="S203" s="1" t="n">
         <v>0.007251</v>
       </c>
     </row>
@@ -12299,9 +12911,12 @@
         <v>0.1309</v>
       </c>
       <c r="Q204" s="1" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="R204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="R204" s="1" t="n">
+      <c r="S204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -12357,9 +12972,12 @@
         <v>0.01415</v>
       </c>
       <c r="Q205" s="1" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="R205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="R205" s="1" t="n">
+      <c r="S205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -12415,9 +13033,12 @@
         <v>0.003565</v>
       </c>
       <c r="Q206" s="1" t="n">
+        <v>0.003566</v>
+      </c>
+      <c r="R206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="R206" s="1" t="n">
+      <c r="S206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -12473,10 +13094,13 @@
         <v>0.05937</v>
       </c>
       <c r="Q207" s="1" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="R207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="R207" s="1" t="n">
-        <v>0.05937</v>
+      <c r="S207" s="1" t="n">
+        <v>0.05933</v>
       </c>
     </row>
     <row r="208">
@@ -12531,9 +13155,12 @@
         <v>15.46</v>
       </c>
       <c r="Q208" s="1" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="R208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="R208" s="1" t="n">
+      <c r="S208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -12589,9 +13216,12 @@
         <v>5192.1</v>
       </c>
       <c r="Q209" s="1" t="n">
-        <v>5193.5</v>
+        <v>5194.1</v>
       </c>
       <c r="R209" s="1" t="n">
+        <v>5194.1</v>
+      </c>
+      <c r="S209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -12647,9 +13277,12 @@
         <v>0.12027</v>
       </c>
       <c r="Q210" s="1" t="n">
+        <v>0.12005</v>
+      </c>
+      <c r="R210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="R210" s="1" t="n">
+      <c r="S210" s="1" t="n">
         <v>0.11955</v>
       </c>
     </row>
@@ -12705,9 +13338,12 @@
         <v>0.1817</v>
       </c>
       <c r="Q211" s="1" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="R211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="R211" s="1" t="n">
+      <c r="S211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -12763,9 +13399,12 @@
         <v>0.0306</v>
       </c>
       <c r="Q212" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="R212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="R212" s="1" t="n">
+      <c r="S212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -12821,9 +13460,12 @@
         <v>1.3979</v>
       </c>
       <c r="Q213" s="1" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="R213" s="1" t="n">
         <v>1.3979</v>
       </c>
-      <c r="R213" s="1" t="n">
+      <c r="S213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -12879,9 +13521,12 @@
         <v>0.05641</v>
       </c>
       <c r="Q214" s="1" t="n">
+        <v>0.05649</v>
+      </c>
+      <c r="R214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="R214" s="1" t="n">
+      <c r="S214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -12937,9 +13582,12 @@
         <v>0.04437</v>
       </c>
       <c r="Q215" s="1" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="R215" s="1" t="n">
         <v>0.04437</v>
       </c>
-      <c r="R215" s="1" t="n">
+      <c r="S215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -12995,9 +13643,12 @@
         <v>0.15109</v>
       </c>
       <c r="Q216" s="1" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="R216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="R216" s="1" t="n">
+      <c r="S216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -13053,9 +13704,12 @@
         <v>0.073</v>
       </c>
       <c r="Q217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="R217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="R217" s="1" t="n">
+      <c r="S217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -13111,9 +13765,12 @@
         <v>0.00268</v>
       </c>
       <c r="Q218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="R218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="R218" s="1" t="n">
+      <c r="S218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -13169,10 +13826,13 @@
         <v>0.01703</v>
       </c>
       <c r="Q219" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="R219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="R219" s="1" t="n">
-        <v>0.01703</v>
+      <c r="S219" s="1" t="n">
+        <v>0.01698</v>
       </c>
     </row>
     <row r="220">
@@ -13227,9 +13887,12 @@
         <v>0.05512</v>
       </c>
       <c r="Q220" s="1" t="n">
+        <v>0.05507</v>
+      </c>
+      <c r="R220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="R220" s="1" t="n">
+      <c r="S220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -13285,10 +13948,13 @@
         <v>0.02187</v>
       </c>
       <c r="Q221" s="1" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="R221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="R221" s="1" t="n">
-        <v>0.02182</v>
+      <c r="S221" s="1" t="n">
+        <v>0.02179</v>
       </c>
     </row>
     <row r="222">
@@ -13343,10 +14009,13 @@
         <v>0.00937</v>
       </c>
       <c r="Q222" s="1" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="R222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="R222" s="1" t="n">
-        <v>0.009339999999999999</v>
+      <c r="S222" s="1" t="n">
+        <v>0.009299999999999999</v>
       </c>
     </row>
     <row r="223">
@@ -13401,9 +14070,12 @@
         <v>0.0164</v>
       </c>
       <c r="Q223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="R223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="R223" s="1" t="n">
+      <c r="S223" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -13459,9 +14131,12 @@
         <v>0.03833</v>
       </c>
       <c r="Q224" s="1" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="R224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="R224" s="1" t="n">
+      <c r="S224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -13517,10 +14192,13 @@
         <v>0.001523</v>
       </c>
       <c r="Q225" s="1" t="n">
+        <v>0.00152</v>
+      </c>
+      <c r="R225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="R225" s="1" t="n">
-        <v>0.001522</v>
+      <c r="S225" s="1" t="n">
+        <v>0.00152</v>
       </c>
     </row>
     <row r="226">
@@ -13575,9 +14253,12 @@
         <v>27.11</v>
       </c>
       <c r="Q226" s="1" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="R226" s="1" t="n">
         <v>27.2</v>
       </c>
-      <c r="R226" s="1" t="n">
+      <c r="S226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -13633,9 +14314,12 @@
         <v>0.07043000000000001</v>
       </c>
       <c r="Q227" s="1" t="n">
+        <v>0.07044</v>
+      </c>
+      <c r="R227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="R227" s="1" t="n">
+      <c r="S227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -13691,9 +14375,12 @@
         <v>0.313</v>
       </c>
       <c r="Q228" s="1" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="R228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="R228" s="1" t="n">
+      <c r="S228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -13749,9 +14436,12 @@
         <v>18.39</v>
       </c>
       <c r="Q229" s="1" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="R229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="R229" s="1" t="n">
+      <c r="S229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -13807,10 +14497,13 @@
         <v>0.01925</v>
       </c>
       <c r="Q230" s="1" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="R230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="R230" s="1" t="n">
-        <v>0.01921</v>
+      <c r="S230" s="1" t="n">
+        <v>0.01918</v>
       </c>
     </row>
     <row r="231">
@@ -13865,9 +14558,12 @@
         <v>0.01218</v>
       </c>
       <c r="Q231" s="1" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="R231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="R231" s="1" t="n">
+      <c r="S231" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -13923,9 +14619,12 @@
         <v>0.2276</v>
       </c>
       <c r="Q232" s="1" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="R232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="R232" s="1" t="n">
+      <c r="S232" s="1" t="n">
         <v>0.2274</v>
       </c>
     </row>
@@ -13981,10 +14680,13 @@
         <v>0.07091</v>
       </c>
       <c r="Q233" s="1" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="R233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="R233" s="1" t="n">
-        <v>0.07087</v>
+      <c r="S233" s="1" t="n">
+        <v>0.07074</v>
       </c>
     </row>
     <row r="234">
@@ -14039,9 +14741,12 @@
         <v>0.1705</v>
       </c>
       <c r="Q234" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="R234" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="R234" s="1" t="n">
+      <c r="S234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -14097,9 +14802,12 @@
         <v>0.025</v>
       </c>
       <c r="Q235" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="R235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="R235" s="1" t="n">
+      <c r="S235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -14155,10 +14863,13 @@
         <v>0.02995</v>
       </c>
       <c r="Q236" s="1" t="n">
+        <v>0.02993</v>
+      </c>
+      <c r="R236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="R236" s="1" t="n">
-        <v>0.02995</v>
+      <c r="S236" s="1" t="n">
+        <v>0.02993</v>
       </c>
     </row>
     <row r="237">
@@ -14213,9 +14924,12 @@
         <v>2.006</v>
       </c>
       <c r="Q237" s="1" t="n">
-        <v>2.006</v>
+        <v>2.008</v>
       </c>
       <c r="R237" s="1" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="S237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -14271,9 +14985,12 @@
         <v>0.4214</v>
       </c>
       <c r="Q238" s="1" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="R238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="R238" s="1" t="n">
+      <c r="S238" s="1" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -14329,9 +15046,12 @@
         <v>0.03354</v>
       </c>
       <c r="Q239" s="1" t="n">
+        <v>0.03352</v>
+      </c>
+      <c r="R239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="R239" s="1" t="n">
+      <c r="S239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -14387,9 +15107,12 @@
         <v>0.03401</v>
       </c>
       <c r="Q240" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="R240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="R240" s="1" t="n">
+      <c r="S240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -14445,9 +15168,12 @@
         <v>0.0007507</v>
       </c>
       <c r="Q241" s="1" t="n">
+        <v>0.0007515999999999999</v>
+      </c>
+      <c r="R241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="R241" s="1" t="n">
+      <c r="S241" s="1" t="n">
         <v>0.0007489</v>
       </c>
     </row>
@@ -14503,9 +15229,12 @@
         <v>0.1832</v>
       </c>
       <c r="Q242" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="R242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="R242" s="1" t="n">
+      <c r="S242" s="1" t="n">
         <v>0.1828</v>
       </c>
     </row>
@@ -14561,9 +15290,12 @@
         <v>0.014755</v>
       </c>
       <c r="Q243" s="1" t="n">
+        <v>0.014757</v>
+      </c>
+      <c r="R243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="R243" s="1" t="n">
+      <c r="S243" s="1" t="n">
         <v>0.014735</v>
       </c>
     </row>
@@ -14619,9 +15351,12 @@
         <v>3.01e-05</v>
       </c>
       <c r="Q244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="R244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="R244" s="1" t="n">
+      <c r="S244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -14677,10 +15412,13 @@
         <v>0.0352</v>
       </c>
       <c r="Q245" s="1" t="n">
+        <v>0.03505</v>
+      </c>
+      <c r="R245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="R245" s="1" t="n">
-        <v>0.03514</v>
+      <c r="S245" s="1" t="n">
+        <v>0.03505</v>
       </c>
     </row>
     <row r="246">
@@ -14735,10 +15473,13 @@
         <v>0.08037999999999999</v>
       </c>
       <c r="Q246" s="1" t="n">
+        <v>0.08025</v>
+      </c>
+      <c r="R246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="R246" s="1" t="n">
-        <v>0.08033999999999999</v>
+      <c r="S246" s="1" t="n">
+        <v>0.08025</v>
       </c>
     </row>
     <row r="247">
@@ -14793,9 +15534,12 @@
         <v>0.007229</v>
       </c>
       <c r="Q247" s="1" t="n">
+        <v>0.007259</v>
+      </c>
+      <c r="R247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="R247" s="1" t="n">
+      <c r="S247" s="1" t="n">
         <v>0.007229</v>
       </c>
     </row>
@@ -14851,9 +15595,12 @@
         <v>0.09452000000000001</v>
       </c>
       <c r="Q248" s="1" t="n">
+        <v>0.09442</v>
+      </c>
+      <c r="R248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="R248" s="1" t="n">
+      <c r="S248" s="1" t="n">
         <v>0.09438000000000001</v>
       </c>
     </row>
@@ -14909,9 +15656,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="Q249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="R249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="R249" s="1" t="n">
+      <c r="S249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -14967,10 +15717,13 @@
         <v>0.03483</v>
       </c>
       <c r="Q250" s="1" t="n">
+        <v>0.03472</v>
+      </c>
+      <c r="R250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="R250" s="1" t="n">
-        <v>0.0348</v>
+      <c r="S250" s="1" t="n">
+        <v>0.03472</v>
       </c>
     </row>
     <row r="251">
@@ -15025,10 +15778,13 @@
         <v>0.03916</v>
       </c>
       <c r="Q251" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="R251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="R251" s="1" t="n">
-        <v>0.03916</v>
+      <c r="S251" s="1" t="n">
+        <v>0.03915</v>
       </c>
     </row>
     <row r="252">
@@ -15083,10 +15839,13 @@
         <v>0.089</v>
       </c>
       <c r="Q252" s="1" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="R252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="R252" s="1" t="n">
-        <v>0.089</v>
+      <c r="S252" s="1" t="n">
+        <v>0.0888</v>
       </c>
     </row>
     <row r="253">
@@ -15141,9 +15900,12 @@
         <v>4.083</v>
       </c>
       <c r="Q253" s="1" t="n">
+        <v>4.075</v>
+      </c>
+      <c r="R253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="R253" s="1" t="n">
+      <c r="S253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -15199,9 +15961,12 @@
         <v>0.1877</v>
       </c>
       <c r="Q254" s="1" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="R254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="R254" s="1" t="n">
+      <c r="S254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -15257,9 +16022,12 @@
         <v>0.07185</v>
       </c>
       <c r="Q255" s="1" t="n">
+        <v>0.07187</v>
+      </c>
+      <c r="R255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="R255" s="1" t="n">
+      <c r="S255" s="1" t="n">
         <v>0.07185</v>
       </c>
     </row>
@@ -15315,9 +16083,12 @@
         <v>0.01825</v>
       </c>
       <c r="Q256" s="1" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="R256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="R256" s="1" t="n">
+      <c r="S256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -15373,9 +16144,12 @@
         <v>5.942</v>
       </c>
       <c r="Q257" s="1" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="R257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="R257" s="1" t="n">
+      <c r="S257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -15431,9 +16205,12 @@
         <v>0.2618</v>
       </c>
       <c r="Q258" s="1" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="R258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="R258" s="1" t="n">
+      <c r="S258" s="1" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -15489,10 +16266,13 @@
         <v>0.1357</v>
       </c>
       <c r="Q259" s="1" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="R259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="R259" s="1" t="n">
-        <v>0.1356</v>
+      <c r="S259" s="1" t="n">
+        <v>0.1355</v>
       </c>
     </row>
     <row r="260">
@@ -15547,9 +16327,12 @@
         <v>0.30655</v>
       </c>
       <c r="Q260" s="1" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="R260" s="1" t="n">
         <v>0.30784</v>
       </c>
-      <c r="R260" s="1" t="n">
+      <c r="S260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -15605,9 +16388,12 @@
         <v>0.09927999999999999</v>
       </c>
       <c r="Q261" s="1" t="n">
+        <v>0.09915</v>
+      </c>
+      <c r="R261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="R261" s="1" t="n">
+      <c r="S261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -15663,9 +16449,12 @@
         <v>0.5389</v>
       </c>
       <c r="Q262" s="1" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="R262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="R262" s="1" t="n">
+      <c r="S262" s="1" t="n">
         <v>0.538</v>
       </c>
     </row>
@@ -15721,10 +16510,13 @@
         <v>0.2903</v>
       </c>
       <c r="Q263" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="R263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="R263" s="1" t="n">
-        <v>0.2903</v>
+      <c r="S263" s="1" t="n">
+        <v>0.289</v>
       </c>
     </row>
     <row r="264">
@@ -15779,9 +16571,12 @@
         <v>0.983</v>
       </c>
       <c r="Q264" s="1" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R264" s="1" t="n">
         <v>0.983</v>
       </c>
-      <c r="R264" s="1" t="n">
+      <c r="S264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -15837,10 +16632,13 @@
         <v>0.5407999999999999</v>
       </c>
       <c r="Q265" s="1" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="R265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="R265" s="1" t="n">
-        <v>0.5394</v>
+      <c r="S265" s="1" t="n">
+        <v>0.539</v>
       </c>
     </row>
     <row r="266">
@@ -15895,10 +16693,13 @@
         <v>0.07356</v>
       </c>
       <c r="Q266" s="1" t="n">
+        <v>0.07351000000000001</v>
+      </c>
+      <c r="R266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="R266" s="1" t="n">
-        <v>0.07355</v>
+      <c r="S266" s="1" t="n">
+        <v>0.07351000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -15953,9 +16754,12 @@
         <v>0.02167</v>
       </c>
       <c r="Q267" s="1" t="n">
+        <v>0.02153</v>
+      </c>
+      <c r="R267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="R267" s="1" t="n">
+      <c r="S267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -16011,9 +16815,12 @@
         <v>0.01611</v>
       </c>
       <c r="Q268" s="1" t="n">
+        <v>0.01609</v>
+      </c>
+      <c r="R268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="R268" s="1" t="n">
+      <c r="S268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -16069,9 +16876,12 @@
         <v>0.0038</v>
       </c>
       <c r="Q269" s="1" t="n">
+        <v>0.003791</v>
+      </c>
+      <c r="R269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="R269" s="1" t="n">
+      <c r="S269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -16127,10 +16937,13 @@
         <v>0.00763</v>
       </c>
       <c r="Q270" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="R270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="R270" s="1" t="n">
-        <v>0.00761</v>
+      <c r="S270" s="1" t="n">
+        <v>0.0076</v>
       </c>
     </row>
     <row r="271">
@@ -16185,9 +16998,12 @@
         <v>0.05509</v>
       </c>
       <c r="Q271" s="1" t="n">
+        <v>0.05497</v>
+      </c>
+      <c r="R271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="R271" s="1" t="n">
+      <c r="S271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -16243,10 +17059,13 @@
         <v>2.273</v>
       </c>
       <c r="Q272" s="1" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="R272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="R272" s="1" t="n">
-        <v>2.271</v>
+      <c r="S272" s="1" t="n">
+        <v>2.268</v>
       </c>
     </row>
     <row r="273">
@@ -16301,9 +17120,12 @@
         <v>0.05494</v>
       </c>
       <c r="Q273" s="1" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="R273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="R273" s="1" t="n">
+      <c r="S273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -16359,9 +17181,12 @@
         <v>0.02324</v>
       </c>
       <c r="Q274" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="R274" s="1" t="n">
         <v>0.02336</v>
       </c>
-      <c r="R274" s="1" t="n">
+      <c r="S274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -16417,9 +17242,12 @@
         <v>1.176</v>
       </c>
       <c r="Q275" s="1" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="R275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="R275" s="1" t="n">
+      <c r="S275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -16475,9 +17303,12 @@
         <v>0.2715</v>
       </c>
       <c r="Q276" s="1" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="R276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="R276" s="1" t="n">
+      <c r="S276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -16533,10 +17364,13 @@
         <v>0.931</v>
       </c>
       <c r="Q277" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="R277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="R277" s="1" t="n">
-        <v>0.929</v>
+      <c r="S277" s="1" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="278">
@@ -16591,9 +17425,12 @@
         <v>0.6236</v>
       </c>
       <c r="Q278" s="1" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="R278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="R278" s="1" t="n">
+      <c r="S278" s="1" t="n">
         <v>0.6221</v>
       </c>
     </row>
@@ -16649,10 +17486,13 @@
         <v>0.001343</v>
       </c>
       <c r="Q279" s="1" t="n">
+        <v>0.001336</v>
+      </c>
+      <c r="R279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="R279" s="1" t="n">
-        <v>0.001341</v>
+      <c r="S279" s="1" t="n">
+        <v>0.001336</v>
       </c>
     </row>
     <row r="280">
@@ -16707,9 +17547,12 @@
         <v>0.005601</v>
       </c>
       <c r="Q280" s="1" t="n">
+        <v>0.005599</v>
+      </c>
+      <c r="R280" s="1" t="n">
         <v>0.005601</v>
       </c>
-      <c r="R280" s="1" t="n">
+      <c r="S280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -16765,9 +17608,12 @@
         <v>1.52</v>
       </c>
       <c r="Q281" s="1" t="n">
+        <v>1.517</v>
+      </c>
+      <c r="R281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="R281" s="1" t="n">
+      <c r="S281" s="1" t="n">
         <v>1.516</v>
       </c>
     </row>
@@ -16823,9 +17669,12 @@
         <v>28.34</v>
       </c>
       <c r="Q282" s="1" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="R282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="R282" s="1" t="n">
+      <c r="S282" s="1" t="n">
         <v>28.26</v>
       </c>
     </row>
@@ -16881,10 +17730,13 @@
         <v>0.12846</v>
       </c>
       <c r="Q283" s="1" t="n">
+        <v>0.12828</v>
+      </c>
+      <c r="R283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="R283" s="1" t="n">
-        <v>0.12839</v>
+      <c r="S283" s="1" t="n">
+        <v>0.12828</v>
       </c>
     </row>
     <row r="284">
@@ -16939,10 +17791,13 @@
         <v>0.01109</v>
       </c>
       <c r="Q284" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="R284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="R284" s="1" t="n">
-        <v>0.01108</v>
+      <c r="S284" s="1" t="n">
+        <v>0.01106</v>
       </c>
     </row>
     <row r="285">
@@ -16997,9 +17852,12 @@
         <v>6.549</v>
       </c>
       <c r="Q285" s="1" t="n">
+        <v>6.538</v>
+      </c>
+      <c r="R285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="R285" s="1" t="n">
+      <c r="S285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -17055,9 +17913,12 @@
         <v>0.01842</v>
       </c>
       <c r="Q286" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="R286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="R286" s="1" t="n">
+      <c r="S286" s="1" t="n">
         <v>0.01838</v>
       </c>
     </row>
@@ -17113,10 +17974,13 @@
         <v>0.008348</v>
       </c>
       <c r="Q287" s="1" t="n">
+        <v>0.008336</v>
+      </c>
+      <c r="R287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="R287" s="1" t="n">
-        <v>0.008348</v>
+      <c r="S287" s="1" t="n">
+        <v>0.008336</v>
       </c>
     </row>
     <row r="288">
@@ -17171,9 +18035,12 @@
         <v>0.3803</v>
       </c>
       <c r="Q288" s="1" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="R288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="R288" s="1" t="n">
+      <c r="S288" s="1" t="n">
         <v>0.3803</v>
       </c>
     </row>
@@ -17229,10 +18096,13 @@
         <v>0.009882999999999999</v>
       </c>
       <c r="Q289" s="1" t="n">
+        <v>0.009868</v>
+      </c>
+      <c r="R289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="R289" s="1" t="n">
-        <v>0.009882999999999999</v>
+      <c r="S289" s="1" t="n">
+        <v>0.009868</v>
       </c>
     </row>
     <row r="290">
@@ -17287,9 +18157,12 @@
         <v>0.02593</v>
       </c>
       <c r="Q290" s="1" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="R290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="R290" s="1" t="n">
+      <c r="S290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -17345,9 +18218,12 @@
         <v>0.095</v>
       </c>
       <c r="Q291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="R291" s="1" t="n">
+      <c r="S291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -17403,9 +18279,12 @@
         <v>0.28764</v>
       </c>
       <c r="Q292" s="1" t="n">
-        <v>0.28764</v>
+        <v>0.28799</v>
       </c>
       <c r="R292" s="1" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="S292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -17461,9 +18340,12 @@
         <v>0.01536</v>
       </c>
       <c r="Q293" s="1" t="n">
+        <v>0.01534</v>
+      </c>
+      <c r="R293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="R293" s="1" t="n">
+      <c r="S293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -17519,10 +18401,13 @@
         <v>0.00341</v>
       </c>
       <c r="Q294" s="1" t="n">
+        <v>0.003395</v>
+      </c>
+      <c r="R294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="R294" s="1" t="n">
-        <v>0.00341</v>
+      <c r="S294" s="1" t="n">
+        <v>0.003395</v>
       </c>
     </row>
     <row r="295">
@@ -17577,10 +18462,13 @@
         <v>0.042856</v>
       </c>
       <c r="Q295" s="1" t="n">
+        <v>0.042232</v>
+      </c>
+      <c r="R295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="R295" s="1" t="n">
-        <v>0.042629</v>
+      <c r="S295" s="1" t="n">
+        <v>0.042232</v>
       </c>
     </row>
     <row r="296">
@@ -17635,9 +18523,12 @@
         <v>0.02894</v>
       </c>
       <c r="Q296" s="1" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="R296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="R296" s="1" t="n">
+      <c r="S296" s="1" t="n">
         <v>0.02894</v>
       </c>
     </row>
@@ -17693,9 +18584,12 @@
         <v>0.03791</v>
       </c>
       <c r="Q297" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="R297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="R297" s="1" t="n">
+      <c r="S297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -17751,9 +18645,12 @@
         <v>0.08298999999999999</v>
       </c>
       <c r="Q298" s="1" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="R298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="R298" s="1" t="n">
+      <c r="S298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -17809,9 +18706,12 @@
         <v>0.00765</v>
       </c>
       <c r="Q299" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="R299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="R299" s="1" t="n">
+      <c r="S299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -17867,10 +18767,13 @@
         <v>0.01509</v>
       </c>
       <c r="Q300" s="1" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="R300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="R300" s="1" t="n">
-        <v>0.01505</v>
+      <c r="S300" s="1" t="n">
+        <v>0.01502</v>
       </c>
     </row>
     <row r="301">
@@ -17925,9 +18828,12 @@
         <v>0.1403</v>
       </c>
       <c r="Q301" s="1" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="R301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="R301" s="1" t="n">
+      <c r="S301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -17983,9 +18889,12 @@
         <v>0.0006288</v>
       </c>
       <c r="Q302" s="1" t="n">
+        <v>0.000626</v>
+      </c>
+      <c r="R302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="R302" s="1" t="n">
+      <c r="S302" s="1" t="n">
         <v>0.0006229</v>
       </c>
     </row>
@@ -18041,9 +18950,12 @@
         <v>0.06234</v>
       </c>
       <c r="Q303" s="1" t="n">
+        <v>0.06227</v>
+      </c>
+      <c r="R303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="R303" s="1" t="n">
+      <c r="S303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -18099,10 +19011,13 @@
         <v>0.0001624</v>
       </c>
       <c r="Q304" s="1" t="n">
+        <v>0.0001623</v>
+      </c>
+      <c r="R304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="R304" s="1" t="n">
-        <v>0.0001624</v>
+      <c r="S304" s="1" t="n">
+        <v>0.0001623</v>
       </c>
     </row>
     <row r="305">
@@ -18157,9 +19072,12 @@
         <v>0.06081</v>
       </c>
       <c r="Q305" s="1" t="n">
+        <v>0.06096</v>
+      </c>
+      <c r="R305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="R305" s="1" t="n">
+      <c r="S305" s="1" t="n">
         <v>0.06076</v>
       </c>
     </row>
@@ -18215,9 +19133,12 @@
         <v>0.022482</v>
       </c>
       <c r="Q306" s="1" t="n">
+        <v>0.022396</v>
+      </c>
+      <c r="R306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="R306" s="1" t="n">
+      <c r="S306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -18273,9 +19194,12 @@
         <v>0.02361</v>
       </c>
       <c r="Q307" s="1" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="R307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="R307" s="1" t="n">
+      <c r="S307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -18331,9 +19255,12 @@
         <v>0.000411</v>
       </c>
       <c r="Q308" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="R308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="R308" s="1" t="n">
+      <c r="S308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -18389,9 +19316,12 @@
         <v>0.0898</v>
       </c>
       <c r="Q309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="R309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="R309" s="1" t="n">
+      <c r="S309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -18447,9 +19377,12 @@
         <v>0.3664</v>
       </c>
       <c r="Q310" s="1" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="R310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="R310" s="1" t="n">
+      <c r="S310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -18505,9 +19438,12 @@
         <v>0.0354</v>
       </c>
       <c r="Q311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="R311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="R311" s="1" t="n">
+      <c r="S311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -18563,10 +19499,13 @@
         <v>0.0244</v>
       </c>
       <c r="Q312" s="1" t="n">
+        <v>0.02426</v>
+      </c>
+      <c r="R312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="R312" s="1" t="n">
-        <v>0.0244</v>
+      <c r="S312" s="1" t="n">
+        <v>0.02426</v>
       </c>
     </row>
     <row r="313">
@@ -18621,10 +19560,13 @@
         <v>0.04106</v>
       </c>
       <c r="Q313" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="R313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="R313" s="1" t="n">
-        <v>0.04106</v>
+      <c r="S313" s="1" t="n">
+        <v>0.041</v>
       </c>
     </row>
     <row r="314">
@@ -18679,10 +19621,13 @@
         <v>3.964</v>
       </c>
       <c r="Q314" s="1" t="n">
+        <v>3.944</v>
+      </c>
+      <c r="R314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="R314" s="1" t="n">
-        <v>3.964</v>
+      <c r="S314" s="1" t="n">
+        <v>3.944</v>
       </c>
     </row>
     <row r="315">
@@ -18737,10 +19682,13 @@
         <v>0.1596</v>
       </c>
       <c r="Q315" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="R315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="R315" s="1" t="n">
-        <v>0.1594</v>
+      <c r="S315" s="1" t="n">
+        <v>0.159</v>
       </c>
     </row>
     <row r="316">
@@ -18795,9 +19743,12 @@
         <v>0.09016</v>
       </c>
       <c r="Q316" s="1" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="R316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="R316" s="1" t="n">
+      <c r="S316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -18853,9 +19804,12 @@
         <v>0.06796000000000001</v>
       </c>
       <c r="Q317" s="1" t="n">
+        <v>0.06809</v>
+      </c>
+      <c r="R317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="R317" s="1" t="n">
+      <c r="S317" s="1" t="n">
         <v>0.06791999999999999</v>
       </c>
     </row>
@@ -18911,9 +19865,12 @@
         <v>0.012421</v>
       </c>
       <c r="Q318" s="1" t="n">
+        <v>0.012432</v>
+      </c>
+      <c r="R318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="R318" s="1" t="n">
+      <c r="S318" s="1" t="n">
         <v>0.012414</v>
       </c>
     </row>
@@ -18969,10 +19926,13 @@
         <v>0.001133</v>
       </c>
       <c r="Q319" s="1" t="n">
+        <v>0.001132</v>
+      </c>
+      <c r="R319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="R319" s="1" t="n">
-        <v>0.001133</v>
+      <c r="S319" s="1" t="n">
+        <v>0.001132</v>
       </c>
     </row>
     <row r="320">
@@ -19027,9 +19987,12 @@
         <v>0.063</v>
       </c>
       <c r="Q320" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="R320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="R320" s="1" t="n">
+      <c r="S320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -19085,9 +20048,12 @@
         <v>0.00524</v>
       </c>
       <c r="Q321" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="R321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="R321" s="1" t="n">
+      <c r="S321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -19143,9 +20109,12 @@
         <v>0.1117</v>
       </c>
       <c r="Q322" s="1" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="R322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="R322" s="1" t="n">
+      <c r="S322" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
@@ -19201,9 +20170,12 @@
         <v>0.04376</v>
       </c>
       <c r="Q323" s="1" t="n">
-        <v>0.04376</v>
+        <v>0.04392</v>
       </c>
       <c r="R323" s="1" t="n">
+        <v>0.04392</v>
+      </c>
+      <c r="S323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -19259,9 +20231,12 @@
         <v>0.01786</v>
       </c>
       <c r="Q324" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="R324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="R324" s="1" t="n">
+      <c r="S324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -19317,9 +20292,12 @@
         <v>0.005638</v>
       </c>
       <c r="Q325" s="1" t="n">
+        <v>0.00564</v>
+      </c>
+      <c r="R325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="R325" s="1" t="n">
+      <c r="S325" s="1" t="n">
         <v>0.005638</v>
       </c>
     </row>
@@ -19375,10 +20353,13 @@
         <v>0.001757</v>
       </c>
       <c r="Q326" s="1" t="n">
+        <v>0.001756</v>
+      </c>
+      <c r="R326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="R326" s="1" t="n">
-        <v>0.001757</v>
+      <c r="S326" s="1" t="n">
+        <v>0.001756</v>
       </c>
     </row>
     <row r="327">
@@ -19433,10 +20414,13 @@
         <v>0.04022</v>
       </c>
       <c r="Q327" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="R327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="R327" s="1" t="n">
-        <v>0.04022</v>
+      <c r="S327" s="1" t="n">
+        <v>0.04011</v>
       </c>
     </row>
     <row r="328">
@@ -19491,9 +20475,12 @@
         <v>0.053699</v>
       </c>
       <c r="Q328" s="1" t="n">
+        <v>0.053684</v>
+      </c>
+      <c r="R328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="R328" s="1" t="n">
+      <c r="S328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -19549,9 +20536,12 @@
         <v>0.2782</v>
       </c>
       <c r="Q329" s="1" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="R329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="R329" s="1" t="n">
+      <c r="S329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -19607,9 +20597,12 @@
         <v>0.1591</v>
       </c>
       <c r="Q330" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="R330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="R330" s="1" t="n">
+      <c r="S330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -19665,9 +20658,12 @@
         <v>0.05366</v>
       </c>
       <c r="Q331" s="1" t="n">
+        <v>0.05355</v>
+      </c>
+      <c r="R331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="R331" s="1" t="n">
+      <c r="S331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -19723,9 +20719,12 @@
         <v>0.3607</v>
       </c>
       <c r="Q332" s="1" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="R332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="R332" s="1" t="n">
+      <c r="S332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -19781,9 +20780,12 @@
         <v>0.03054</v>
       </c>
       <c r="Q333" s="1" t="n">
-        <v>0.03054</v>
+        <v>0.03055</v>
       </c>
       <c r="R333" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="S333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -19839,9 +20841,12 @@
         <v>0.01767</v>
       </c>
       <c r="Q334" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="R334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="R334" s="1" t="n">
+      <c r="S334" s="1" t="n">
         <v>0.01751</v>
       </c>
     </row>
@@ -19897,9 +20902,12 @@
         <v>0.058</v>
       </c>
       <c r="Q335" s="1" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="R335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="R335" s="1" t="n">
+      <c r="S335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -19955,9 +20963,12 @@
         <v>0.09045</v>
       </c>
       <c r="Q336" s="1" t="n">
+        <v>0.09054</v>
+      </c>
+      <c r="R336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="R336" s="1" t="n">
+      <c r="S336" s="1" t="n">
         <v>0.09045</v>
       </c>
     </row>
@@ -20013,9 +21024,12 @@
         <v>0.1803</v>
       </c>
       <c r="Q337" s="1" t="n">
+        <v>0.18046</v>
+      </c>
+      <c r="R337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="R337" s="1" t="n">
+      <c r="S337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -20071,10 +21085,13 @@
         <v>0.02089</v>
       </c>
       <c r="Q338" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="R338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="R338" s="1" t="n">
-        <v>0.02089</v>
+      <c r="S338" s="1" t="n">
+        <v>0.02081</v>
       </c>
     </row>
     <row r="339">
@@ -20129,9 +21146,12 @@
         <v>0.1319</v>
       </c>
       <c r="Q339" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="R339" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="R339" s="1" t="n">
+      <c r="S339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -20187,9 +21207,12 @@
         <v>0.007952000000000001</v>
       </c>
       <c r="Q340" s="1" t="n">
+        <v>0.007946999999999999</v>
+      </c>
+      <c r="R340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="R340" s="1" t="n">
+      <c r="S340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -20245,9 +21268,12 @@
         <v>4.415</v>
       </c>
       <c r="Q341" s="1" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="R341" s="1" t="n">
+      <c r="S341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -20303,9 +21329,12 @@
         <v>0.1891</v>
       </c>
       <c r="Q342" s="1" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="R342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="R342" s="1" t="n">
+      <c r="S342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -20361,9 +21390,12 @@
         <v>0.08311</v>
       </c>
       <c r="Q343" s="1" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="R343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="R343" s="1" t="n">
+      <c r="S343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -20419,10 +21451,13 @@
         <v>0.1823</v>
       </c>
       <c r="Q344" s="1" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="R344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="R344" s="1" t="n">
-        <v>0.1817</v>
+      <c r="S344" s="1" t="n">
+        <v>0.1813</v>
       </c>
     </row>
     <row r="345">
@@ -20477,10 +21512,13 @@
         <v>0.003242</v>
       </c>
       <c r="Q345" s="1" t="n">
+        <v>0.003237</v>
+      </c>
+      <c r="R345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="R345" s="1" t="n">
-        <v>0.00324</v>
+      <c r="S345" s="1" t="n">
+        <v>0.003237</v>
       </c>
     </row>
     <row r="346">
@@ -20535,9 +21573,12 @@
         <v>0.09111</v>
       </c>
       <c r="Q346" s="1" t="n">
+        <v>0.09098000000000001</v>
+      </c>
+      <c r="R346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="R346" s="1" t="n">
+      <c r="S346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -20593,10 +21634,13 @@
         <v>2.245</v>
       </c>
       <c r="Q347" s="1" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="R347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="R347" s="1" t="n">
-        <v>2.243</v>
+      <c r="S347" s="1" t="n">
+        <v>2.242</v>
       </c>
     </row>
     <row r="348">
@@ -20651,9 +21695,12 @@
         <v>0.303</v>
       </c>
       <c r="Q348" s="1" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="R348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="R348" s="1" t="n">
+      <c r="S348" s="1" t="n">
         <v>0.3027</v>
       </c>
     </row>
@@ -20709,9 +21756,12 @@
         <v>0.02945</v>
       </c>
       <c r="Q349" s="1" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="R349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="R349" s="1" t="n">
+      <c r="S349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -20767,9 +21817,12 @@
         <v>0.1276</v>
       </c>
       <c r="Q350" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="R350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="R350" s="1" t="n">
+      <c r="S350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -20825,10 +21878,13 @@
         <v>0.06655999999999999</v>
       </c>
       <c r="Q351" s="1" t="n">
+        <v>0.06644</v>
+      </c>
+      <c r="R351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="R351" s="1" t="n">
-        <v>0.06651</v>
+      <c r="S351" s="1" t="n">
+        <v>0.06644</v>
       </c>
     </row>
     <row r="352">
@@ -20883,10 +21939,13 @@
         <v>0.06244</v>
       </c>
       <c r="Q352" s="1" t="n">
+        <v>0.06234</v>
+      </c>
+      <c r="R352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="R352" s="1" t="n">
-        <v>0.06236</v>
+      <c r="S352" s="1" t="n">
+        <v>0.06234</v>
       </c>
     </row>
     <row r="353">
@@ -20941,10 +22000,13 @@
         <v>0.06337</v>
       </c>
       <c r="Q353" s="1" t="n">
+        <v>0.06315999999999999</v>
+      </c>
+      <c r="R353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="R353" s="1" t="n">
-        <v>0.06329</v>
+      <c r="S353" s="1" t="n">
+        <v>0.06315999999999999</v>
       </c>
     </row>
     <row r="354">
@@ -20999,9 +22061,12 @@
         <v>0.10393</v>
       </c>
       <c r="Q354" s="1" t="n">
+        <v>0.10407</v>
+      </c>
+      <c r="R354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="R354" s="1" t="n">
+      <c r="S354" s="1" t="n">
         <v>0.10393</v>
       </c>
     </row>
@@ -21057,9 +22122,12 @@
         <v>0.0901</v>
       </c>
       <c r="Q355" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="R355" s="1" t="n">
+      <c r="S355" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -21115,10 +22183,13 @@
         <v>0.06958</v>
       </c>
       <c r="Q356" s="1" t="n">
+        <v>0.06938999999999999</v>
+      </c>
+      <c r="R356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="R356" s="1" t="n">
-        <v>0.06958</v>
+      <c r="S356" s="1" t="n">
+        <v>0.06938999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -21173,10 +22244,13 @@
         <v>0.4526</v>
       </c>
       <c r="Q357" s="1" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="R357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="R357" s="1" t="n">
-        <v>0.4518</v>
+      <c r="S357" s="1" t="n">
+        <v>0.4509</v>
       </c>
     </row>
     <row r="358">
@@ -21231,9 +22305,12 @@
         <v>0.03483</v>
       </c>
       <c r="Q358" s="1" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="R358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="R358" s="1" t="n">
+      <c r="S358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -21289,10 +22366,13 @@
         <v>0.01463</v>
       </c>
       <c r="Q359" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="R359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="R359" s="1" t="n">
-        <v>0.01463</v>
+      <c r="S359" s="1" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="360">
@@ -21347,9 +22427,12 @@
         <v>0.13325</v>
       </c>
       <c r="Q360" s="1" t="n">
+        <v>0.13327</v>
+      </c>
+      <c r="R360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="R360" s="1" t="n">
+      <c r="S360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -21405,9 +22488,12 @@
         <v>0.0005886</v>
       </c>
       <c r="Q361" s="1" t="n">
+        <v>0.0005888999999999999</v>
+      </c>
+      <c r="R361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="R361" s="1" t="n">
+      <c r="S361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -21463,9 +22549,12 @@
         <v>0.03863</v>
       </c>
       <c r="Q362" s="1" t="n">
+        <v>0.03856</v>
+      </c>
+      <c r="R362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="R362" s="1" t="n">
+      <c r="S362" s="1" t="n">
         <v>0.03855</v>
       </c>
     </row>
@@ -21521,9 +22610,12 @@
         <v>3.223</v>
       </c>
       <c r="Q363" s="1" t="n">
+        <v>3.217</v>
+      </c>
+      <c r="R363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="R363" s="1" t="n">
+      <c r="S363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -21579,10 +22671,13 @@
         <v>0.1636</v>
       </c>
       <c r="Q364" s="1" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="R364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="R364" s="1" t="n">
-        <v>0.1635</v>
+      <c r="S364" s="1" t="n">
+        <v>0.1632</v>
       </c>
     </row>
     <row r="365">
@@ -21637,9 +22732,12 @@
         <v>0.1136</v>
       </c>
       <c r="Q365" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="R365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="R365" s="1" t="n">
+      <c r="S365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -21695,10 +22793,13 @@
         <v>0.0006375</v>
       </c>
       <c r="Q366" s="1" t="n">
+        <v>0.0006363</v>
+      </c>
+      <c r="R366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="R366" s="1" t="n">
-        <v>0.0006375</v>
+      <c r="S366" s="1" t="n">
+        <v>0.0006363</v>
       </c>
     </row>
     <row r="367">
@@ -21753,9 +22854,12 @@
         <v>0.05939</v>
       </c>
       <c r="Q367" s="1" t="n">
+        <v>0.05943</v>
+      </c>
+      <c r="R367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="R367" s="1" t="n">
+      <c r="S367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -21811,10 +22915,13 @@
         <v>0.08162999999999999</v>
       </c>
       <c r="Q368" s="1" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="R368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="R368" s="1" t="n">
-        <v>0.08162999999999999</v>
+      <c r="S368" s="1" t="n">
+        <v>0.08160000000000001</v>
       </c>
     </row>
     <row r="369">
@@ -21869,10 +22976,13 @@
         <v>0.03939</v>
       </c>
       <c r="Q369" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="R369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="R369" s="1" t="n">
-        <v>0.03931</v>
+      <c r="S369" s="1" t="n">
+        <v>0.0393</v>
       </c>
     </row>
     <row r="370">
@@ -21927,9 +23037,12 @@
         <v>3.689</v>
       </c>
       <c r="Q370" s="1" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="R370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="R370" s="1" t="n">
+      <c r="S370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -21985,10 +23098,13 @@
         <v>0.1209</v>
       </c>
       <c r="Q371" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="R371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="R371" s="1" t="n">
-        <v>0.1208</v>
+      <c r="S371" s="1" t="n">
+        <v>0.1206</v>
       </c>
     </row>
     <row r="372">
@@ -22043,9 +23159,12 @@
         <v>0.01478</v>
       </c>
       <c r="Q372" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="R372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="R372" s="1" t="n">
+      <c r="S372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -22101,9 +23220,12 @@
         <v>0.022</v>
       </c>
       <c r="Q373" s="1" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="R373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="R373" s="1" t="n">
+      <c r="S373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -22159,9 +23281,12 @@
         <v>1.8612</v>
       </c>
       <c r="Q374" s="1" t="n">
+        <v>1.8573</v>
+      </c>
+      <c r="R374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="R374" s="1" t="n">
+      <c r="S374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -22217,10 +23342,13 @@
         <v>0.02087</v>
       </c>
       <c r="Q375" s="1" t="n">
+        <v>0.02082</v>
+      </c>
+      <c r="R375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="R375" s="1" t="n">
-        <v>0.02087</v>
+      <c r="S375" s="1" t="n">
+        <v>0.02082</v>
       </c>
     </row>
     <row r="376">
@@ -22275,9 +23403,12 @@
         <v>1.303</v>
       </c>
       <c r="Q376" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="R376" s="1" t="n">
+      <c r="S376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -22333,10 +23464,13 @@
         <v>0.2826</v>
       </c>
       <c r="Q377" s="1" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="R377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="R377" s="1" t="n">
-        <v>0.2826</v>
+      <c r="S377" s="1" t="n">
+        <v>0.282</v>
       </c>
     </row>
     <row r="378">
@@ -22391,9 +23525,12 @@
         <v>0.01562</v>
       </c>
       <c r="Q378" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="R378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="R378" s="1" t="n">
+      <c r="S378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -22449,9 +23586,12 @@
         <v>1.5325</v>
       </c>
       <c r="Q379" s="1" t="n">
+        <v>1.5302</v>
+      </c>
+      <c r="R379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="R379" s="1" t="n">
+      <c r="S379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -22507,10 +23647,13 @@
         <v>6.905e-05</v>
       </c>
       <c r="Q380" s="1" t="n">
+        <v>6.887e-05</v>
+      </c>
+      <c r="R380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="R380" s="1" t="n">
-        <v>6.896e-05</v>
+      <c r="S380" s="1" t="n">
+        <v>6.887e-05</v>
       </c>
     </row>
     <row r="381">
@@ -22565,10 +23708,13 @@
         <v>2.548</v>
       </c>
       <c r="Q381" s="1" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="R381" s="1" t="n">
-        <v>2.545</v>
+      <c r="S381" s="1" t="n">
+        <v>2.544</v>
       </c>
     </row>
     <row r="382">
@@ -22623,10 +23769,13 @@
         <v>0.0669</v>
       </c>
       <c r="Q382" s="1" t="n">
+        <v>0.06680999999999999</v>
+      </c>
+      <c r="R382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="R382" s="1" t="n">
-        <v>0.06683</v>
+      <c r="S382" s="1" t="n">
+        <v>0.06680999999999999</v>
       </c>
     </row>
     <row r="383">
@@ -22681,10 +23830,13 @@
         <v>0.01744</v>
       </c>
       <c r="Q383" s="1" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="R383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="R383" s="1" t="n">
-        <v>0.01713</v>
+      <c r="S383" s="1" t="n">
+        <v>0.01695</v>
       </c>
     </row>
     <row r="384">
@@ -22739,9 +23891,12 @@
         <v>0.05153</v>
       </c>
       <c r="Q384" s="1" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="R384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="R384" s="1" t="n">
+      <c r="S384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -22797,9 +23952,12 @@
         <v>7.571</v>
       </c>
       <c r="Q385" s="1" t="n">
+        <v>7.559</v>
+      </c>
+      <c r="R385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="R385" s="1" t="n">
+      <c r="S385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -22855,9 +24013,12 @@
         <v>0.003278</v>
       </c>
       <c r="Q386" s="1" t="n">
+        <v>0.003273</v>
+      </c>
+      <c r="R386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="R386" s="1" t="n">
+      <c r="S386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -22913,10 +24074,13 @@
         <v>0.0003802</v>
       </c>
       <c r="Q387" s="1" t="n">
+        <v>0.0003797</v>
+      </c>
+      <c r="R387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="R387" s="1" t="n">
-        <v>0.0003801</v>
+      <c r="S387" s="1" t="n">
+        <v>0.0003797</v>
       </c>
     </row>
     <row r="388">
@@ -22971,10 +24135,13 @@
         <v>0.00945</v>
       </c>
       <c r="Q388" s="1" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="R388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="R388" s="1" t="n">
-        <v>0.00945</v>
+      <c r="S388" s="1" t="n">
+        <v>0.00942</v>
       </c>
     </row>
     <row r="389">
@@ -23029,9 +24196,12 @@
         <v>0.2897</v>
       </c>
       <c r="Q389" s="1" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="R389" s="1" t="n">
         <v>0.2904</v>
       </c>
-      <c r="R389" s="1" t="n">
+      <c r="S389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -23087,9 +24257,12 @@
         <v>0.0253</v>
       </c>
       <c r="Q390" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="R390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="R390" s="1" t="n">
+      <c r="S390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -23145,9 +24318,12 @@
         <v>2.845</v>
       </c>
       <c r="Q391" s="1" t="n">
-        <v>2.845</v>
+        <v>2.859</v>
       </c>
       <c r="R391" s="1" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="S391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -23203,9 +24379,12 @@
         <v>0.0135</v>
       </c>
       <c r="Q392" s="1" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="R392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="R392" s="1" t="n">
+      <c r="S392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -23261,9 +24440,12 @@
         <v>0.00237</v>
       </c>
       <c r="Q393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="R393" s="1" t="n">
         <v>0.00237</v>
       </c>
-      <c r="R393" s="1" t="n">
+      <c r="S393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -23319,9 +24501,12 @@
         <v>0.05935</v>
       </c>
       <c r="Q394" s="1" t="n">
+        <v>0.05925</v>
+      </c>
+      <c r="R394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="R394" s="1" t="n">
+      <c r="S394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -23377,9 +24562,12 @@
         <v>0.0404</v>
       </c>
       <c r="Q395" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="R395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="R395" s="1" t="n">
+      <c r="S395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -23435,9 +24623,12 @@
         <v>0.09273000000000001</v>
       </c>
       <c r="Q396" s="1" t="n">
-        <v>0.09273000000000001</v>
+        <v>0.09275</v>
       </c>
       <c r="R396" s="1" t="n">
+        <v>0.09275</v>
+      </c>
+      <c r="S396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -23493,9 +24684,12 @@
         <v>0.1516</v>
       </c>
       <c r="Q397" s="1" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="R397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="R397" s="1" t="n">
+      <c r="S397" s="1" t="n">
         <v>0.1515</v>
       </c>
     </row>
@@ -23551,9 +24745,12 @@
         <v>0.931</v>
       </c>
       <c r="Q398" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="R398" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="R398" s="1" t="n">
+      <c r="S398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -23609,9 +24806,12 @@
         <v>0.05239</v>
       </c>
       <c r="Q399" s="1" t="n">
+        <v>0.05233</v>
+      </c>
+      <c r="R399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="R399" s="1" t="n">
+      <c r="S399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -23667,10 +24867,13 @@
         <v>2.514</v>
       </c>
       <c r="Q400" s="1" t="n">
+        <v>2.508</v>
+      </c>
+      <c r="R400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="R400" s="1" t="n">
-        <v>2.512</v>
+      <c r="S400" s="1" t="n">
+        <v>2.508</v>
       </c>
     </row>
     <row r="401">
@@ -23725,10 +24928,13 @@
         <v>0.0178</v>
       </c>
       <c r="Q401" s="1" t="n">
+        <v>0.01772</v>
+      </c>
+      <c r="R401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="R401" s="1" t="n">
-        <v>0.0178</v>
+      <c r="S401" s="1" t="n">
+        <v>0.01772</v>
       </c>
     </row>
     <row r="402">
@@ -23783,9 +24989,12 @@
         <v>0.07973</v>
       </c>
       <c r="Q402" s="1" t="n">
+        <v>0.07979</v>
+      </c>
+      <c r="R402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="R402" s="1" t="n">
+      <c r="S402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -23841,9 +25050,12 @@
         <v>1.2496</v>
       </c>
       <c r="Q403" s="1" t="n">
+        <v>1.2474</v>
+      </c>
+      <c r="R403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="R403" s="1" t="n">
+      <c r="S403" s="1" t="n">
         <v>1.2455</v>
       </c>
     </row>
@@ -23899,10 +25111,13 @@
         <v>0.00711</v>
       </c>
       <c r="Q404" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="R404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="R404" s="1" t="n">
-        <v>0.00711</v>
+      <c r="S404" s="1" t="n">
+        <v>0.0071</v>
       </c>
     </row>
     <row r="405">
@@ -23957,9 +25172,12 @@
         <v>0.502</v>
       </c>
       <c r="Q405" s="1" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="R405" s="1" t="n">
         <v>0.5041</v>
       </c>
-      <c r="R405" s="1" t="n">
+      <c r="S405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -24015,10 +25233,13 @@
         <v>0.01144</v>
       </c>
       <c r="Q406" s="1" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="R406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="R406" s="1" t="n">
-        <v>0.01144</v>
+      <c r="S406" s="1" t="n">
+        <v>0.01142</v>
       </c>
     </row>
     <row r="407">
@@ -24073,10 +25294,13 @@
         <v>0.04602</v>
       </c>
       <c r="Q407" s="1" t="n">
+        <v>0.04592</v>
+      </c>
+      <c r="R407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="R407" s="1" t="n">
-        <v>0.04596</v>
+      <c r="S407" s="1" t="n">
+        <v>0.04592</v>
       </c>
     </row>
     <row r="408">
@@ -24131,9 +25355,12 @@
         <v>0.03936</v>
       </c>
       <c r="Q408" s="1" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="R408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="R408" s="1" t="n">
+      <c r="S408" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -24189,10 +25416,13 @@
         <v>0.0523</v>
       </c>
       <c r="Q409" s="1" t="n">
+        <v>0.05216</v>
+      </c>
+      <c r="R409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="R409" s="1" t="n">
-        <v>0.05226</v>
+      <c r="S409" s="1" t="n">
+        <v>0.05216</v>
       </c>
     </row>
     <row r="410">
@@ -24247,9 +25477,12 @@
         <v>0.01227</v>
       </c>
       <c r="Q410" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="R410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="R410" s="1" t="n">
+      <c r="S410" s="1" t="n">
         <v>0.01227</v>
       </c>
     </row>
@@ -24305,9 +25538,12 @@
         <v>0.06342</v>
       </c>
       <c r="Q411" s="1" t="n">
+        <v>0.06342</v>
+      </c>
+      <c r="R411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="R411" s="1" t="n">
+      <c r="S411" s="1" t="n">
         <v>0.06342</v>
       </c>
     </row>
@@ -24363,9 +25599,12 @@
         <v>0.04136</v>
       </c>
       <c r="Q412" s="1" t="n">
+        <v>0.04136</v>
+      </c>
+      <c r="R412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="R412" s="1" t="n">
+      <c r="S412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -24421,9 +25660,12 @@
         <v>1.112</v>
       </c>
       <c r="Q413" s="1" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="R413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="R413" s="1" t="n">
+      <c r="S413" s="1" t="n">
         <v>1.112</v>
       </c>
     </row>
@@ -24479,10 +25721,13 @@
         <v>0.2626</v>
       </c>
       <c r="Q414" s="1" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="R414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="R414" s="1" t="n">
-        <v>0.2624</v>
+      <c r="S414" s="1" t="n">
+        <v>0.2617</v>
       </c>
     </row>
     <row r="415">
@@ -24537,9 +25782,12 @@
         <v>0.001218</v>
       </c>
       <c r="Q415" s="1" t="n">
+        <v>0.001219</v>
+      </c>
+      <c r="R415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="R415" s="1" t="n">
+      <c r="S415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -24595,9 +25843,12 @@
         <v>0.03203</v>
       </c>
       <c r="Q416" s="1" t="n">
+        <v>0.03195</v>
+      </c>
+      <c r="R416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="R416" s="1" t="n">
+      <c r="S416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -24653,9 +25904,12 @@
         <v>0.0146</v>
       </c>
       <c r="Q417" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="R417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="R417" s="1" t="n">
+      <c r="S417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -24711,10 +25965,13 @@
         <v>0.148</v>
       </c>
       <c r="Q418" s="1" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="R418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="R418" s="1" t="n">
-        <v>0.1479</v>
+      <c r="S418" s="1" t="n">
+        <v>0.1478</v>
       </c>
     </row>
     <row r="419">
@@ -24769,9 +26026,12 @@
         <v>0.04914</v>
       </c>
       <c r="Q419" s="1" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="R419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="R419" s="1" t="n">
+      <c r="S419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -24827,9 +26087,12 @@
         <v>66.5</v>
       </c>
       <c r="Q420" s="1" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="R420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="R420" s="1" t="n">
+      <c r="S420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -24885,10 +26148,13 @@
         <v>0.876</v>
       </c>
       <c r="Q421" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="R421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="R421" s="1" t="n">
-        <v>0.875</v>
+      <c r="S421" s="1" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="422">
@@ -24943,9 +26209,12 @@
         <v>0.01239</v>
       </c>
       <c r="Q422" s="1" t="n">
+        <v>0.012508</v>
+      </c>
+      <c r="R422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="R422" s="1" t="n">
+      <c r="S422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -25001,9 +26270,12 @@
         <v>0.01596</v>
       </c>
       <c r="Q423" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="R423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="R423" s="1" t="n">
+      <c r="S423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -25059,9 +26331,12 @@
         <v>0.27462</v>
       </c>
       <c r="Q424" s="1" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="R424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="R424" s="1" t="n">
+      <c r="S424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -25117,9 +26392,12 @@
         <v>0.6009</v>
       </c>
       <c r="Q425" s="1" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="R425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="R425" s="1" t="n">
+      <c r="S425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -25175,10 +26453,13 @@
         <v>0.005501</v>
       </c>
       <c r="Q426" s="1" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="R426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="R426" s="1" t="n">
-        <v>0.005501</v>
+      <c r="S426" s="1" t="n">
+        <v>0.0055</v>
       </c>
     </row>
     <row r="427">
@@ -25233,9 +26514,12 @@
         <v>0.04957</v>
       </c>
       <c r="Q427" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="R427" s="1" t="n">
         <v>0.04962</v>
       </c>
-      <c r="R427" s="1" t="n">
+      <c r="S427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -25291,9 +26575,12 @@
         <v>0.1258</v>
       </c>
       <c r="Q428" s="1" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="R428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="R428" s="1" t="n">
+      <c r="S428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -25349,9 +26636,12 @@
         <v>0.003198</v>
       </c>
       <c r="Q429" s="1" t="n">
+        <v>0.003196</v>
+      </c>
+      <c r="R429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="R429" s="1" t="n">
+      <c r="S429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -25407,10 +26697,13 @@
         <v>0.03641</v>
       </c>
       <c r="Q430" s="1" t="n">
+        <v>0.03637</v>
+      </c>
+      <c r="R430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="R430" s="1" t="n">
-        <v>0.03641</v>
+      <c r="S430" s="1" t="n">
+        <v>0.03637</v>
       </c>
     </row>
     <row r="431">
@@ -25465,10 +26758,13 @@
         <v>0.3952</v>
       </c>
       <c r="Q431" s="1" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="R431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="R431" s="1" t="n">
-        <v>0.3952</v>
+      <c r="S431" s="1" t="n">
+        <v>0.3935</v>
       </c>
     </row>
     <row r="432">
@@ -25523,10 +26819,13 @@
         <v>0.00448</v>
       </c>
       <c r="Q432" s="1" t="n">
+        <v>0.004478</v>
+      </c>
+      <c r="R432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="R432" s="1" t="n">
-        <v>0.00448</v>
+      <c r="S432" s="1" t="n">
+        <v>0.004478</v>
       </c>
     </row>
     <row r="433">
@@ -25581,9 +26880,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="Q433" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="R433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="R433" s="1" t="n">
+      <c r="S433" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -25639,10 +26941,13 @@
         <v>0.01239</v>
       </c>
       <c r="Q434" s="1" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="R434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="R434" s="1" t="n">
-        <v>0.01237</v>
+      <c r="S434" s="1" t="n">
+        <v>0.01236</v>
       </c>
     </row>
     <row r="435">
@@ -25697,9 +27002,12 @@
         <v>1.985</v>
       </c>
       <c r="Q435" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="R435" s="1" t="n">
+      <c r="S435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -25755,10 +27063,13 @@
         <v>0.001777</v>
       </c>
       <c r="Q436" s="1" t="n">
+        <v>0.001774</v>
+      </c>
+      <c r="R436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="R436" s="1" t="n">
-        <v>0.001777</v>
+      <c r="S436" s="1" t="n">
+        <v>0.001774</v>
       </c>
     </row>
     <row r="437">
@@ -25813,9 +27124,12 @@
         <v>0.4424</v>
       </c>
       <c r="Q437" s="1" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="R437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="R437" s="1" t="n">
+      <c r="S437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -25871,9 +27185,12 @@
         <v>0.00534</v>
       </c>
       <c r="Q438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="R438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="R438" s="1" t="n">
+      <c r="S438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -25929,9 +27246,12 @@
         <v>0.1036</v>
       </c>
       <c r="Q439" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="R439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="R439" s="1" t="n">
+      <c r="S439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -25987,9 +27307,12 @@
         <v>0.03399</v>
       </c>
       <c r="Q440" s="1" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="R440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="R440" s="1" t="n">
+      <c r="S440" s="1" t="n">
         <v>0.03399</v>
       </c>
     </row>
@@ -26045,10 +27368,13 @@
         <v>0.08212999999999999</v>
       </c>
       <c r="Q441" s="1" t="n">
+        <v>0.08193</v>
+      </c>
+      <c r="R441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="R441" s="1" t="n">
-        <v>0.08201</v>
+      <c r="S441" s="1" t="n">
+        <v>0.08193</v>
       </c>
     </row>
     <row r="442">
@@ -26103,10 +27429,13 @@
         <v>1.306</v>
       </c>
       <c r="Q442" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="R442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="R442" s="1" t="n">
-        <v>1.302</v>
+      <c r="S442" s="1" t="n">
+        <v>1.301</v>
       </c>
     </row>
     <row r="443">
@@ -26161,10 +27490,13 @@
         <v>0.07543999999999999</v>
       </c>
       <c r="Q443" s="1" t="n">
+        <v>0.07521</v>
+      </c>
+      <c r="R443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="R443" s="1" t="n">
-        <v>0.07543999999999999</v>
+      <c r="S443" s="1" t="n">
+        <v>0.07521</v>
       </c>
     </row>
     <row r="444">
@@ -26219,9 +27551,12 @@
         <v>0.07638</v>
       </c>
       <c r="Q444" s="1" t="n">
+        <v>0.07641000000000001</v>
+      </c>
+      <c r="R444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="R444" s="1" t="n">
+      <c r="S444" s="1" t="n">
         <v>0.07638</v>
       </c>
     </row>
@@ -26277,9 +27612,12 @@
         <v>0.04335</v>
       </c>
       <c r="Q445" s="1" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="R445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="R445" s="1" t="n">
+      <c r="S445" s="1" t="n">
         <v>0.0433</v>
       </c>
     </row>
@@ -26335,9 +27673,12 @@
         <v>0.02144</v>
       </c>
       <c r="Q446" s="1" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="R446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="R446" s="1" t="n">
+      <c r="S446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -26393,9 +27734,12 @@
         <v>0.2803</v>
       </c>
       <c r="Q447" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="R447" s="1" t="n">
+      <c r="S447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -26451,10 +27795,13 @@
         <v>0.03097</v>
       </c>
       <c r="Q448" s="1" t="n">
+        <v>0.03069</v>
+      </c>
+      <c r="R448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="R448" s="1" t="n">
-        <v>0.03097</v>
+      <c r="S448" s="1" t="n">
+        <v>0.03069</v>
       </c>
     </row>
     <row r="449">
@@ -26509,9 +27856,12 @@
         <v>0.00647</v>
       </c>
       <c r="Q449" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="R449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="R449" s="1" t="n">
+      <c r="S449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -26567,9 +27917,12 @@
         <v>0.023057</v>
       </c>
       <c r="Q450" s="1" t="n">
+        <v>0.023002</v>
+      </c>
+      <c r="R450" s="1" t="n">
         <v>0.023086</v>
       </c>
-      <c r="R450" s="1" t="n">
+      <c r="S450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -26625,9 +27978,12 @@
         <v>0.04236</v>
       </c>
       <c r="Q451" s="1" t="n">
+        <v>0.04247</v>
+      </c>
+      <c r="R451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="R451" s="1" t="n">
+      <c r="S451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -26683,9 +28039,12 @@
         <v>0.07239</v>
       </c>
       <c r="Q452" s="1" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="R452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="R452" s="1" t="n">
+      <c r="S452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -26741,9 +28100,12 @@
         <v>0.0005910000000000001</v>
       </c>
       <c r="Q453" s="1" t="n">
+        <v>0.0005907</v>
+      </c>
+      <c r="R453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="R453" s="1" t="n">
+      <c r="S453" s="1" t="n">
         <v>0.0005904</v>
       </c>
     </row>
@@ -26799,10 +28161,13 @@
         <v>0.305</v>
       </c>
       <c r="Q454" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="R454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="R454" s="1" t="n">
-        <v>0.305</v>
+      <c r="S454" s="1" t="n">
+        <v>0.304</v>
       </c>
     </row>
     <row r="455">
@@ -26857,9 +28222,12 @@
         <v>0.004277</v>
       </c>
       <c r="Q455" s="1" t="n">
+        <v>0.004268</v>
+      </c>
+      <c r="R455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="R455" s="1" t="n">
+      <c r="S455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -26915,9 +28283,12 @@
         <v>0.1824</v>
       </c>
       <c r="Q456" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="R456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="R456" s="1" t="n">
+      <c r="S456" s="1" t="n">
         <v>0.1821</v>
       </c>
     </row>
@@ -26973,9 +28344,12 @@
         <v>0.04275</v>
       </c>
       <c r="Q457" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="R457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="R457" s="1" t="n">
+      <c r="S457" s="1" t="n">
         <v>0.04267</v>
       </c>
     </row>
@@ -27031,10 +28405,13 @@
         <v>0.1462</v>
       </c>
       <c r="Q458" s="1" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="R458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="R458" s="1" t="n">
-        <v>0.1459</v>
+      <c r="S458" s="1" t="n">
+        <v>0.1457</v>
       </c>
     </row>
     <row r="459">
@@ -27089,9 +28466,12 @@
         <v>0.008626</v>
       </c>
       <c r="Q459" s="1" t="n">
+        <v>0.008621999999999999</v>
+      </c>
+      <c r="R459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="R459" s="1" t="n">
+      <c r="S459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -27147,9 +28527,12 @@
         <v>0.007414</v>
       </c>
       <c r="Q460" s="1" t="n">
+        <v>0.007394</v>
+      </c>
+      <c r="R460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="R460" s="1" t="n">
+      <c r="S460" s="1" t="n">
         <v>0.007357</v>
       </c>
     </row>
@@ -27205,9 +28588,12 @@
         <v>0.0001735</v>
       </c>
       <c r="Q461" s="1" t="n">
+        <v>0.0001734</v>
+      </c>
+      <c r="R461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="R461" s="1" t="n">
+      <c r="S461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -27263,9 +28649,12 @@
         <v>0.02337</v>
       </c>
       <c r="Q462" s="1" t="n">
-        <v>0.02337</v>
+        <v>0.02374</v>
       </c>
       <c r="R462" s="1" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="S462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -27321,9 +28710,12 @@
         <v>0.03694</v>
       </c>
       <c r="Q463" s="1" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="R463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="R463" s="1" t="n">
+      <c r="S463" s="1" t="n">
         <v>0.03685</v>
       </c>
     </row>
@@ -27379,10 +28771,13 @@
         <v>0.3017</v>
       </c>
       <c r="Q464" s="1" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="R464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="R464" s="1" t="n">
-        <v>0.3012</v>
+      <c r="S464" s="1" t="n">
+        <v>0.3011</v>
       </c>
     </row>
     <row r="465">
@@ -27437,9 +28832,12 @@
         <v>0.03896</v>
       </c>
       <c r="Q465" s="1" t="n">
+        <v>0.03898</v>
+      </c>
+      <c r="R465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="R465" s="1" t="n">
+      <c r="S465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -27495,10 +28893,13 @@
         <v>2.67</v>
       </c>
       <c r="Q466" s="1" t="n">
+        <v>2.661</v>
+      </c>
+      <c r="R466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="R466" s="1" t="n">
-        <v>2.662</v>
+      <c r="S466" s="1" t="n">
+        <v>2.661</v>
       </c>
     </row>
     <row r="467">
@@ -27553,9 +28954,12 @@
         <v>0.03438</v>
       </c>
       <c r="Q467" s="1" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="R467" s="1" t="n">
         <v>0.03438</v>
       </c>
-      <c r="R467" s="1" t="n">
+      <c r="S467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -27611,9 +29015,12 @@
         <v>0.1761</v>
       </c>
       <c r="Q468" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="R468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="R468" s="1" t="n">
+      <c r="S468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -27669,9 +29076,12 @@
         <v>0.0965</v>
       </c>
       <c r="Q469" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="R469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="R469" s="1" t="n">
+      <c r="S469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -27727,10 +29137,13 @@
         <v>0.06713</v>
       </c>
       <c r="Q470" s="1" t="n">
+        <v>0.06696000000000001</v>
+      </c>
+      <c r="R470" s="1" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="R470" s="1" t="n">
-        <v>0.06708</v>
+      <c r="S470" s="1" t="n">
+        <v>0.06696000000000001</v>
       </c>
     </row>
     <row r="471">
@@ -27785,9 +29198,12 @@
         <v>0.03988</v>
       </c>
       <c r="Q471" s="1" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="R471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="R471" s="1" t="n">
+      <c r="S471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -27843,9 +29259,12 @@
         <v>0.247</v>
       </c>
       <c r="Q472" s="1" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="R472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="R472" s="1" t="n">
+      <c r="S472" s="1" t="n">
         <v>0.2466</v>
       </c>
     </row>
@@ -27901,10 +29320,13 @@
         <v>0.016346</v>
       </c>
       <c r="Q473" s="1" t="n">
+        <v>0.016316</v>
+      </c>
+      <c r="R473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="R473" s="1" t="n">
-        <v>0.016346</v>
+      <c r="S473" s="1" t="n">
+        <v>0.016316</v>
       </c>
     </row>
     <row r="474">
@@ -27959,9 +29381,12 @@
         <v>0.1156</v>
       </c>
       <c r="Q474" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="R474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="R474" s="1" t="n">
+      <c r="S474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -28017,9 +29442,12 @@
         <v>0.04277</v>
       </c>
       <c r="Q475" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="R475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="R475" s="1" t="n">
+      <c r="S475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -28075,9 +29503,12 @@
         <v>0.2071</v>
       </c>
       <c r="Q476" s="1" t="n">
+        <v>0.2069</v>
+      </c>
+      <c r="R476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="R476" s="1" t="n">
+      <c r="S476" s="1" t="n">
         <v>0.2066</v>
       </c>
     </row>
@@ -28133,10 +29564,13 @@
         <v>0.0068</v>
       </c>
       <c r="Q477" s="1" t="n">
+        <v>0.006776</v>
+      </c>
+      <c r="R477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="R477" s="1" t="n">
-        <v>0.006789</v>
+      <c r="S477" s="1" t="n">
+        <v>0.006776</v>
       </c>
     </row>
     <row r="478">
@@ -28191,10 +29625,13 @@
         <v>0.01781</v>
       </c>
       <c r="Q478" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="R478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="R478" s="1" t="n">
-        <v>0.01781</v>
+      <c r="S478" s="1" t="n">
+        <v>0.01776</v>
       </c>
     </row>
     <row r="479">
@@ -28249,10 +29686,13 @@
         <v>0.04673</v>
       </c>
       <c r="Q479" s="1" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="R479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="R479" s="1" t="n">
-        <v>0.04672</v>
+      <c r="S479" s="1" t="n">
+        <v>0.04665</v>
       </c>
     </row>
     <row r="480">
@@ -28307,9 +29747,12 @@
         <v>0.26029</v>
       </c>
       <c r="Q480" s="1" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="R480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="R480" s="1" t="n">
+      <c r="S480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -28365,9 +29808,12 @@
         <v>0.01222</v>
       </c>
       <c r="Q481" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="R481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="R481" s="1" t="n">
+      <c r="S481" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>
@@ -28423,9 +29869,12 @@
         <v>0.004085</v>
       </c>
       <c r="Q482" s="1" t="n">
+        <v>0.004079</v>
+      </c>
+      <c r="R482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="R482" s="1" t="n">
+      <c r="S482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -28481,9 +29930,12 @@
         <v>0.1229</v>
       </c>
       <c r="Q483" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="R483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="R483" s="1" t="n">
+      <c r="S483" s="1" t="n">
         <v>0.1229</v>
       </c>
     </row>
@@ -28539,9 +29991,12 @@
         <v>0.02217</v>
       </c>
       <c r="Q484" s="1" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="R484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="R484" s="1" t="n">
+      <c r="S484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -28597,9 +30052,12 @@
         <v>0.04517</v>
       </c>
       <c r="Q485" s="1" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="R485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="R485" s="1" t="n">
+      <c r="S485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -28655,9 +30113,12 @@
         <v>0.1735</v>
       </c>
       <c r="Q486" s="1" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="R486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="R486" s="1" t="n">
+      <c r="S486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -28713,9 +30174,12 @@
         <v>0.2728</v>
       </c>
       <c r="Q487" s="1" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="R487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="R487" s="1" t="n">
+      <c r="S487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -28771,10 +30235,13 @@
         <v>0.04609</v>
       </c>
       <c r="Q488" s="1" t="n">
+        <v>0.04599</v>
+      </c>
+      <c r="R488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="R488" s="1" t="n">
-        <v>0.04604</v>
+      <c r="S488" s="1" t="n">
+        <v>0.04599</v>
       </c>
     </row>
     <row r="489">
@@ -28829,9 +30296,12 @@
         <v>0.0002146</v>
       </c>
       <c r="Q489" s="1" t="n">
+        <v>0.0002145</v>
+      </c>
+      <c r="R489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="R489" s="1" t="n">
+      <c r="S489" s="1" t="n">
         <v>0.0002144</v>
       </c>
     </row>
@@ -28887,9 +30357,12 @@
         <v>1.78</v>
       </c>
       <c r="Q490" s="1" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="R490" s="1" t="n">
         <v>1.78</v>
       </c>
-      <c r="R490" s="1" t="n">
+      <c r="S490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -28945,9 +30418,12 @@
         <v>16.044</v>
       </c>
       <c r="Q491" s="1" t="n">
+        <v>16.021</v>
+      </c>
+      <c r="R491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="R491" s="1" t="n">
+      <c r="S491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -29003,9 +30479,12 @@
         <v>0.06671000000000001</v>
       </c>
       <c r="Q492" s="1" t="n">
+        <v>0.06655999999999999</v>
+      </c>
+      <c r="R492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="R492" s="1" t="n">
+      <c r="S492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -29061,9 +30540,12 @@
         <v>0.06734</v>
       </c>
       <c r="Q493" s="1" t="n">
+        <v>0.06734</v>
+      </c>
+      <c r="R493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="R493" s="1" t="n">
+      <c r="S493" s="1" t="n">
         <v>0.06728000000000001</v>
       </c>
     </row>
@@ -29119,9 +30601,12 @@
         <v>0.009427</v>
       </c>
       <c r="Q494" s="1" t="n">
+        <v>0.009443</v>
+      </c>
+      <c r="R494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="R494" s="1" t="n">
+      <c r="S494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -29177,10 +30662,13 @@
         <v>0.005885</v>
       </c>
       <c r="Q495" s="1" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="R495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="R495" s="1" t="n">
-        <v>0.005809</v>
+      <c r="S495" s="1" t="n">
+        <v>0.0058</v>
       </c>
     </row>
     <row r="496">
@@ -29235,9 +30723,12 @@
         <v>0.00988</v>
       </c>
       <c r="Q496" s="1" t="n">
+        <v>0.00987</v>
+      </c>
+      <c r="R496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="R496" s="1" t="n">
+      <c r="S496" s="1" t="n">
         <v>0.009849999999999999</v>
       </c>
     </row>
@@ -29293,9 +30784,12 @@
         <v>0.04613</v>
       </c>
       <c r="Q497" s="1" t="n">
+        <v>0.04604</v>
+      </c>
+      <c r="R497" s="1" t="n">
         <v>0.04613</v>
       </c>
-      <c r="R497" s="1" t="n">
+      <c r="S497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -29351,9 +30845,12 @@
         <v>0.006366</v>
       </c>
       <c r="Q498" s="1" t="n">
+        <v>0.006353</v>
+      </c>
+      <c r="R498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="R498" s="1" t="n">
+      <c r="S498" s="1" t="n">
         <v>0.006353</v>
       </c>
     </row>
@@ -29409,10 +30906,13 @@
         <v>0.01038</v>
       </c>
       <c r="Q499" s="1" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="R499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="R499" s="1" t="n">
-        <v>0.01038</v>
+      <c r="S499" s="1" t="n">
+        <v>0.01035</v>
       </c>
     </row>
     <row r="500">
@@ -29467,10 +30967,13 @@
         <v>0.511</v>
       </c>
       <c r="Q500" s="1" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="R500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="R500" s="1" t="n">
-        <v>0.5075</v>
+      <c r="S500" s="1" t="n">
+        <v>0.5067</v>
       </c>
     </row>
     <row r="501">
@@ -29525,9 +31028,12 @@
         <v>0.03201</v>
       </c>
       <c r="Q501" s="1" t="n">
+        <v>0.03206</v>
+      </c>
+      <c r="R501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="R501" s="1" t="n">
+      <c r="S501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -29583,9 +31089,12 @@
         <v>0.4433</v>
       </c>
       <c r="Q502" s="1" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="R502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="R502" s="1" t="n">
+      <c r="S502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -29641,9 +31150,12 @@
         <v>0.999341</v>
       </c>
       <c r="Q503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="R503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="R503" s="1" t="n">
+      <c r="S503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -29699,9 +31211,12 @@
         <v>0.03513</v>
       </c>
       <c r="Q504" s="1" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="R504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="R504" s="1" t="n">
+      <c r="S504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -29757,9 +31272,12 @@
         <v>0.004943</v>
       </c>
       <c r="Q505" s="1" t="n">
+        <v>0.004922</v>
+      </c>
+      <c r="R505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="R505" s="1" t="n">
+      <c r="S505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -29815,10 +31333,13 @@
         <v>0.0139</v>
       </c>
       <c r="Q506" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="R506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="R506" s="1" t="n">
-        <v>0.01388</v>
+      <c r="S506" s="1" t="n">
+        <v>0.01386</v>
       </c>
     </row>
     <row r="507">
@@ -29873,9 +31394,12 @@
         <v>0.003478</v>
       </c>
       <c r="Q507" s="1" t="n">
+        <v>0.003474</v>
+      </c>
+      <c r="R507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="R507" s="1" t="n">
+      <c r="S507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -29931,9 +31455,12 @@
         <v>1.414</v>
       </c>
       <c r="Q508" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="R508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="R508" s="1" t="n">
+      <c r="S508" s="1" t="n">
         <v>1.413</v>
       </c>
     </row>
@@ -29989,10 +31516,13 @@
         <v>0.005074</v>
       </c>
       <c r="Q509" s="1" t="n">
+        <v>0.005063</v>
+      </c>
+      <c r="R509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="R509" s="1" t="n">
-        <v>0.005067</v>
+      <c r="S509" s="1" t="n">
+        <v>0.005063</v>
       </c>
     </row>
     <row r="510">
@@ -30047,10 +31577,13 @@
         <v>0.01568</v>
       </c>
       <c r="Q510" s="1" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="R510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="R510" s="1" t="n">
-        <v>0.01568</v>
+      <c r="S510" s="1" t="n">
+        <v>0.01565</v>
       </c>
     </row>
     <row r="511">
@@ -30105,9 +31638,12 @@
         <v>0.08227</v>
       </c>
       <c r="Q511" s="1" t="n">
+        <v>0.08225</v>
+      </c>
+      <c r="R511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="R511" s="1" t="n">
+      <c r="S511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -30163,10 +31699,13 @@
         <v>0.007092</v>
       </c>
       <c r="Q512" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="R512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="R512" s="1" t="n">
-        <v>0.007089</v>
+      <c r="S512" s="1" t="n">
+        <v>0.00708</v>
       </c>
     </row>
     <row r="513">
@@ -30221,9 +31760,12 @@
         <v>0.01484</v>
       </c>
       <c r="Q513" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="R513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="R513" s="1" t="n">
+      <c r="S513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -30279,9 +31821,12 @@
         <v>0.04745</v>
       </c>
       <c r="Q514" s="1" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="R514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="R514" s="1" t="n">
+      <c r="S514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -30337,10 +31882,13 @@
         <v>0.01808</v>
       </c>
       <c r="Q515" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="R515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="R515" s="1" t="n">
-        <v>0.01808</v>
+      <c r="S515" s="1" t="n">
+        <v>0.01804</v>
       </c>
     </row>
     <row r="516">
@@ -30395,9 +31943,12 @@
         <v>0.0005795</v>
       </c>
       <c r="Q516" s="1" t="n">
+        <v>0.0005791</v>
+      </c>
+      <c r="R516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="R516" s="1" t="n">
+      <c r="S516" s="1" t="n">
         <v>0.0005782</v>
       </c>
     </row>
@@ -30453,9 +32004,12 @@
         <v>0.07853</v>
       </c>
       <c r="Q517" s="1" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="R517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="R517" s="1" t="n">
+      <c r="S517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -30511,10 +32065,13 @@
         <v>0.006374</v>
       </c>
       <c r="Q518" s="1" t="n">
+        <v>0.006369</v>
+      </c>
+      <c r="R518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="R518" s="1" t="n">
-        <v>0.006373</v>
+      <c r="S518" s="1" t="n">
+        <v>0.006369</v>
       </c>
     </row>
     <row r="519">
@@ -30569,9 +32126,12 @@
         <v>0.05776</v>
       </c>
       <c r="Q519" s="1" t="n">
+        <v>0.05767</v>
+      </c>
+      <c r="R519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="R519" s="1" t="n">
+      <c r="S519" s="1" t="n">
         <v>0.05765</v>
       </c>
     </row>
@@ -30627,10 +32187,13 @@
         <v>0.10448</v>
       </c>
       <c r="Q520" s="1" t="n">
+        <v>0.10413</v>
+      </c>
+      <c r="R520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="R520" s="1" t="n">
-        <v>0.10448</v>
+      <c r="S520" s="1" t="n">
+        <v>0.10413</v>
       </c>
     </row>
     <row r="521">
@@ -30685,10 +32248,13 @@
         <v>0.01792</v>
       </c>
       <c r="Q521" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="R521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="R521" s="1" t="n">
-        <v>0.01787</v>
+      <c r="S521" s="1" t="n">
+        <v>0.01786</v>
       </c>
     </row>
     <row r="522">
@@ -30743,10 +32309,13 @@
         <v>0.01636</v>
       </c>
       <c r="Q522" s="1" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="R522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="R522" s="1" t="n">
-        <v>0.01635</v>
+      <c r="S522" s="1" t="n">
+        <v>0.01618</v>
       </c>
     </row>
     <row r="523">
@@ -30801,9 +32370,12 @@
         <v>0.01079</v>
       </c>
       <c r="Q523" s="1" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="R523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="R523" s="1" t="n">
+      <c r="S523" s="1" t="n">
         <v>0.01079</v>
       </c>
     </row>
@@ -30859,9 +32431,12 @@
         <v>0.007244</v>
       </c>
       <c r="Q524" s="1" t="n">
+        <v>0.007133</v>
+      </c>
+      <c r="R524" s="1" t="n">
         <v>0.007244</v>
       </c>
-      <c r="R524" s="1" t="n">
+      <c r="S524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -30917,10 +32492,13 @@
         <v>0.005828</v>
       </c>
       <c r="Q525" s="1" t="n">
+        <v>0.005827</v>
+      </c>
+      <c r="R525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="R525" s="1" t="n">
-        <v>0.005828</v>
+      <c r="S525" s="1" t="n">
+        <v>0.005827</v>
       </c>
     </row>
     <row r="526">
@@ -30975,9 +32553,12 @@
         <v>0.001437</v>
       </c>
       <c r="Q526" s="1" t="n">
+        <v>0.001438</v>
+      </c>
+      <c r="R526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="R526" s="1" t="n">
+      <c r="S526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -31033,9 +32614,12 @@
         <v>0.373</v>
       </c>
       <c r="Q527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="R527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="R527" s="1" t="n">
+      <c r="S527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -31091,9 +32675,12 @@
         <v>0.005323</v>
       </c>
       <c r="Q528" s="1" t="n">
+        <v>0.005247</v>
+      </c>
+      <c r="R528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="R528" s="1" t="n">
+      <c r="S528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -31149,9 +32736,12 @@
         <v>2.952</v>
       </c>
       <c r="Q529" s="1" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="R529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="R529" s="1" t="n">
+      <c r="S529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -31207,9 +32797,12 @@
         <v>0.1545</v>
       </c>
       <c r="Q530" s="1" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="R530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="R530" s="1" t="n">
+      <c r="S530" s="1" t="n">
         <v>0.1545</v>
       </c>
     </row>
@@ -31265,9 +32858,12 @@
         <v>2559</v>
       </c>
       <c r="Q531" s="1" t="n">
-        <v>2561</v>
+        <v>2579</v>
       </c>
       <c r="R531" s="1" t="n">
+        <v>2579</v>
+      </c>
+      <c r="S531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -31323,10 +32919,13 @@
         <v>0.03909</v>
       </c>
       <c r="Q532" s="1" t="n">
+        <v>0.03903</v>
+      </c>
+      <c r="R532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="R532" s="1" t="n">
-        <v>0.03905</v>
+      <c r="S532" s="1" t="n">
+        <v>0.03903</v>
       </c>
     </row>
     <row r="533">
@@ -31381,9 +32980,12 @@
         <v>0.02156</v>
       </c>
       <c r="Q533" s="1" t="n">
+        <v>0.02162</v>
+      </c>
+      <c r="R533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="R533" s="1" t="n">
+      <c r="S533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -31439,9 +33041,12 @@
         <v>0.07335999999999999</v>
       </c>
       <c r="Q534" s="1" t="n">
+        <v>0.07325</v>
+      </c>
+      <c r="R534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="R534" s="1" t="n">
+      <c r="S534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -31497,9 +33102,12 @@
         <v>0.007837999999999999</v>
       </c>
       <c r="Q535" s="1" t="n">
+        <v>0.007823</v>
+      </c>
+      <c r="R535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="R535" s="1" t="n">
+      <c r="S535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -31555,10 +33163,13 @@
         <v>0.05009</v>
       </c>
       <c r="Q536" s="1" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="R536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="R536" s="1" t="n">
-        <v>0.05002</v>
+      <c r="S536" s="1" t="n">
+        <v>0.04995</v>
       </c>
     </row>
     <row r="537">
@@ -31613,10 +33224,13 @@
         <v>0.00402</v>
       </c>
       <c r="Q537" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="R537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="R537" s="1" t="n">
-        <v>0.00402</v>
+      <c r="S537" s="1" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="538">
@@ -31671,9 +33285,12 @@
         <v>0.08289000000000001</v>
       </c>
       <c r="Q538" s="1" t="n">
+        <v>0.08284</v>
+      </c>
+      <c r="R538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="R538" s="1" t="n">
+      <c r="S538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -31729,10 +33346,13 @@
         <v>0.02483</v>
       </c>
       <c r="Q539" s="1" t="n">
+        <v>0.02479</v>
+      </c>
+      <c r="R539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="R539" s="1" t="n">
-        <v>0.02483</v>
+      <c r="S539" s="1" t="n">
+        <v>0.02479</v>
       </c>
     </row>
     <row r="540">
@@ -31787,9 +33407,12 @@
         <v>0.08424</v>
       </c>
       <c r="Q540" s="1" t="n">
+        <v>0.08432000000000001</v>
+      </c>
+      <c r="R540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="R540" s="1" t="n">
+      <c r="S540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -31845,9 +33468,12 @@
         <v>0.01883</v>
       </c>
       <c r="Q541" s="1" t="n">
+        <v>0.01883</v>
+      </c>
+      <c r="R541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="R541" s="1" t="n">
+      <c r="S541" s="1" t="n">
         <v>0.01882</v>
       </c>
     </row>
@@ -31903,10 +33529,13 @@
         <v>0.01687</v>
       </c>
       <c r="Q542" s="1" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="R542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="R542" s="1" t="n">
-        <v>0.01685</v>
+      <c r="S542" s="1" t="n">
+        <v>0.01679</v>
       </c>
     </row>
     <row r="543">
@@ -31961,10 +33590,13 @@
         <v>0.1047</v>
       </c>
       <c r="Q543" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="R543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="R543" s="1" t="n">
-        <v>0.1047</v>
+      <c r="S543" s="1" t="n">
+        <v>0.1044</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S543"/>
+  <dimension ref="A1:T543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -436,8 +436,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,10 +529,15 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>price_04:15</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -592,9 +598,12 @@
         <v>70664.10000000001</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>70651.39999999999</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -653,9 +662,12 @@
         <v>2076.25</v>
       </c>
       <c r="R3" s="1" t="n">
+        <v>2076.93</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>2077.45</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="T3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -714,9 +726,12 @@
         <v>86.95999999999999</v>
       </c>
       <c r="R4" s="1" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="S4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -775,9 +790,12 @@
         <v>4.018</v>
       </c>
       <c r="R5" s="1" t="n">
+        <v>3.995</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="T5" s="1" t="n">
         <v>3.991</v>
       </c>
     </row>
@@ -836,9 +854,12 @@
         <v>0.09472999999999999</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>0.09462</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="T6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -897,9 +918,12 @@
         <v>1.3894</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>1.3883</v>
+      </c>
+      <c r="S7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="T7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -958,10 +982,13 @@
         <v>22.421</v>
       </c>
       <c r="R8" s="1" t="n">
+        <v>21.772</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="S8" s="1" t="n">
-        <v>22.204</v>
+      <c r="T8" s="1" t="n">
+        <v>21.772</v>
       </c>
     </row>
     <row r="9">
@@ -1019,9 +1046,12 @@
         <v>0.002061</v>
       </c>
       <c r="R9" s="1" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="T9" s="1" t="n">
         <v>0.001972</v>
       </c>
     </row>
@@ -1080,9 +1110,12 @@
         <v>0.009877</v>
       </c>
       <c r="R10" s="1" t="n">
+        <v>0.010026</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="S10" s="1" t="n">
+      <c r="T10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1141,9 +1174,12 @@
         <v>0.14388</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>0.14059</v>
+      </c>
+      <c r="S11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="S11" s="1" t="n">
+      <c r="T11" s="1" t="n">
         <v>0.13838</v>
       </c>
     </row>
@@ -1202,10 +1238,13 @@
         <v>0.011421</v>
       </c>
       <c r="R12" s="1" t="n">
+        <v>0.011225</v>
+      </c>
+      <c r="S12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="S12" s="1" t="n">
-        <v>0.011355</v>
+      <c r="T12" s="1" t="n">
+        <v>0.011225</v>
       </c>
     </row>
     <row r="13">
@@ -1263,9 +1302,12 @@
         <v>38.051</v>
       </c>
       <c r="R13" s="1" t="n">
+        <v>37.947</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="S13" s="1" t="n">
+      <c r="T13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1324,9 +1366,12 @@
         <v>653.58</v>
       </c>
       <c r="R14" s="1" t="n">
+        <v>653.34</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="S14" s="1" t="n">
+      <c r="T14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1385,9 +1430,12 @@
         <v>210.26</v>
       </c>
       <c r="R15" s="1" t="n">
+        <v>209.95</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>210.26</v>
       </c>
-      <c r="S15" s="1" t="n">
+      <c r="T15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1446,10 +1494,13 @@
         <v>0.003319</v>
       </c>
       <c r="R16" s="1" t="n">
+        <v>0.0033084</v>
+      </c>
+      <c r="S16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="S16" s="1" t="n">
-        <v>0.0033182</v>
+      <c r="T16" s="1" t="n">
+        <v>0.0033084</v>
       </c>
     </row>
     <row r="17">
@@ -1507,9 +1558,12 @@
         <v>237.76</v>
       </c>
       <c r="R17" s="1" t="n">
+        <v>238.12</v>
+      </c>
+      <c r="S17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="S17" s="1" t="n">
+      <c r="T17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1568,10 +1622,13 @@
         <v>0.9865</v>
       </c>
       <c r="R18" s="1" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="S18" s="1" t="n">
-        <v>0.9865</v>
+      <c r="T18" s="1" t="n">
+        <v>0.9861</v>
       </c>
     </row>
     <row r="19">
@@ -1629,9 +1686,12 @@
         <v>1.0271</v>
       </c>
       <c r="R19" s="1" t="n">
+        <v>1.0306</v>
+      </c>
+      <c r="S19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="S19" s="1" t="n">
+      <c r="T19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1690,9 +1750,12 @@
         <v>0.2589</v>
       </c>
       <c r="R20" s="1" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="S20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="S20" s="1" t="n">
+      <c r="T20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1751,9 +1814,12 @@
         <v>0.5984699999999999</v>
       </c>
       <c r="R21" s="1" t="n">
+        <v>0.59256</v>
+      </c>
+      <c r="S21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="S21" s="1" t="n">
+      <c r="T21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -1812,9 +1878,12 @@
         <v>9.021000000000001</v>
       </c>
       <c r="R22" s="1" t="n">
+        <v>9.022</v>
+      </c>
+      <c r="S22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="S22" s="1" t="n">
+      <c r="T22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1873,10 +1942,13 @@
         <v>0.02404</v>
       </c>
       <c r="R23" s="1" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="S23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="S23" s="1" t="n">
-        <v>0.02397</v>
+      <c r="T23" s="1" t="n">
+        <v>0.02387</v>
       </c>
     </row>
     <row r="24">
@@ -1934,9 +2006,12 @@
         <v>9.568</v>
       </c>
       <c r="R24" s="1" t="n">
+        <v>9.568</v>
+      </c>
+      <c r="S24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="S24" s="1" t="n">
+      <c r="T24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1995,9 +2070,12 @@
         <v>1.239</v>
       </c>
       <c r="R25" s="1" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="S25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="S25" s="1" t="n">
+      <c r="T25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -2056,9 +2134,12 @@
         <v>0.07253</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.07253</v>
+        <v>0.073</v>
       </c>
       <c r="S26" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="T26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2117,10 +2198,13 @@
         <v>1.41</v>
       </c>
       <c r="R27" s="1" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="S27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="S27" s="1" t="n">
-        <v>1.41</v>
+      <c r="T27" s="1" t="n">
+        <v>1.405</v>
       </c>
     </row>
     <row r="28">
@@ -2178,9 +2262,12 @@
         <v>1.304</v>
       </c>
       <c r="R28" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="S28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="S28" s="1" t="n">
+      <c r="T28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2239,9 +2326,12 @@
         <v>463.52</v>
       </c>
       <c r="R29" s="1" t="n">
+        <v>462.54</v>
+      </c>
+      <c r="S29" s="1" t="n">
         <v>463.55</v>
       </c>
-      <c r="S29" s="1" t="n">
+      <c r="T29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2300,9 +2390,12 @@
         <v>1.2972</v>
       </c>
       <c r="R30" s="1" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="S30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="S30" s="1" t="n">
+      <c r="T30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2361,9 +2454,12 @@
         <v>5025.5</v>
       </c>
       <c r="R31" s="1" t="n">
+        <v>5021.56</v>
+      </c>
+      <c r="S31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="S31" s="1" t="n">
+      <c r="T31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -2422,9 +2518,12 @@
         <v>0.88</v>
       </c>
       <c r="R32" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="S32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="S32" s="1" t="n">
+      <c r="T32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2483,9 +2582,12 @@
         <v>0.001972</v>
       </c>
       <c r="R33" s="1" t="n">
+        <v>0.00197</v>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="S33" s="1" t="n">
+      <c r="T33" s="1" t="n">
         <v>0.001969</v>
       </c>
     </row>
@@ -2544,9 +2646,12 @@
         <v>0.17272</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.17272</v>
+        <v>0.17284</v>
       </c>
       <c r="S34" s="1" t="n">
+        <v>0.17284</v>
+      </c>
+      <c r="T34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2605,9 +2710,12 @@
         <v>0.29699</v>
       </c>
       <c r="R35" s="1" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="S35" s="1" t="n">
+      <c r="T35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -2666,9 +2774,12 @@
         <v>1.779</v>
       </c>
       <c r="R36" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="S36" s="1" t="n">
+      <c r="T36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -2727,10 +2838,13 @@
         <v>110.18</v>
       </c>
       <c r="R37" s="1" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="S37" s="1" t="n">
-        <v>110.18</v>
+      <c r="T37" s="1" t="n">
+        <v>110.17</v>
       </c>
     </row>
     <row r="38">
@@ -2788,9 +2902,12 @@
         <v>0.21983</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>0.21973</v>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="S38" s="1" t="n">
+      <c r="T38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -2849,9 +2966,12 @@
         <v>0.1067</v>
       </c>
       <c r="R39" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="S39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="S39" s="1" t="n">
+      <c r="T39" s="1" t="n">
         <v>0.1067</v>
       </c>
     </row>
@@ -2910,9 +3030,12 @@
         <v>0.37394</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="S40" s="1" t="n">
+      <c r="T40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2971,9 +3094,12 @@
         <v>54.62</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="S41" s="1" t="n">
+      <c r="T41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3032,10 +3158,13 @@
         <v>0.0010558</v>
       </c>
       <c r="R42" s="1" t="n">
+        <v>0.001053</v>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="S42" s="1" t="n">
-        <v>0.0010558</v>
+      <c r="T42" s="1" t="n">
+        <v>0.001053</v>
       </c>
     </row>
     <row r="43">
@@ -3093,9 +3222,12 @@
         <v>6.473</v>
       </c>
       <c r="R43" s="1" t="n">
+        <v>6.459</v>
+      </c>
+      <c r="S43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="S43" s="1" t="n">
+      <c r="T43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3154,10 +3286,13 @@
         <v>0.6263</v>
       </c>
       <c r="R44" s="1" t="n">
+        <v>0.6222</v>
+      </c>
+      <c r="S44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="S44" s="1" t="n">
-        <v>0.6263</v>
+      <c r="T44" s="1" t="n">
+        <v>0.6222</v>
       </c>
     </row>
     <row r="45">
@@ -3215,10 +3350,13 @@
         <v>0.3519</v>
       </c>
       <c r="R45" s="1" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="S45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="S45" s="1" t="n">
-        <v>0.3519</v>
+      <c r="T45" s="1" t="n">
+        <v>0.3516</v>
       </c>
     </row>
     <row r="46">
@@ -3276,9 +3414,12 @@
         <v>0.03308</v>
       </c>
       <c r="R46" s="1" t="n">
+        <v>0.03288</v>
+      </c>
+      <c r="S46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="S46" s="1" t="n">
+      <c r="T46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3337,10 +3478,13 @@
         <v>0.07076</v>
       </c>
       <c r="R47" s="1" t="n">
+        <v>0.06952999999999999</v>
+      </c>
+      <c r="S47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="S47" s="1" t="n">
-        <v>0.07076</v>
+      <c r="T47" s="1" t="n">
+        <v>0.06952999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3398,9 +3542,12 @@
         <v>0.7096</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>0.7097</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="S48" s="1" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="T48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3459,10 +3606,13 @@
         <v>0.004268</v>
       </c>
       <c r="R49" s="1" t="n">
+        <v>0.004241</v>
+      </c>
+      <c r="S49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="S49" s="1" t="n">
-        <v>0.004268</v>
+      <c r="T49" s="1" t="n">
+        <v>0.004241</v>
       </c>
     </row>
     <row r="50">
@@ -3520,10 +3670,13 @@
         <v>0.1034</v>
       </c>
       <c r="R50" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="S50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="S50" s="1" t="n">
-        <v>0.1034</v>
+      <c r="T50" s="1" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="51">
@@ -3581,9 +3734,12 @@
         <v>0.04034</v>
       </c>
       <c r="R51" s="1" t="n">
+        <v>0.04023</v>
+      </c>
+      <c r="S51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="S51" s="1" t="n">
+      <c r="T51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -3642,9 +3798,12 @@
         <v>0.1645</v>
       </c>
       <c r="R52" s="1" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="S52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="S52" s="1" t="n">
+      <c r="T52" s="1" t="n">
         <v>0.1645</v>
       </c>
     </row>
@@ -3703,9 +3862,12 @@
         <v>0.02062</v>
       </c>
       <c r="R53" s="1" t="n">
+        <v>0.02003</v>
+      </c>
+      <c r="S53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="S53" s="1" t="n">
+      <c r="T53" s="1" t="n">
         <v>0.02002</v>
       </c>
     </row>
@@ -3764,10 +3926,13 @@
         <v>0.007184</v>
       </c>
       <c r="R54" s="1" t="n">
+        <v>0.007175</v>
+      </c>
+      <c r="S54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="S54" s="1" t="n">
-        <v>0.007182</v>
+      <c r="T54" s="1" t="n">
+        <v>0.007175</v>
       </c>
     </row>
     <row r="55">
@@ -3825,9 +3990,12 @@
         <v>3.909</v>
       </c>
       <c r="R55" s="1" t="n">
+        <v>3.915</v>
+      </c>
+      <c r="S55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="S55" s="1" t="n">
+      <c r="T55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -3886,10 +4054,13 @@
         <v>0.017019</v>
       </c>
       <c r="R56" s="1" t="n">
+        <v>0.016935</v>
+      </c>
+      <c r="S56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="S56" s="1" t="n">
-        <v>0.016965</v>
+      <c r="T56" s="1" t="n">
+        <v>0.016935</v>
       </c>
     </row>
     <row r="57">
@@ -3947,10 +4118,13 @@
         <v>0.1081</v>
       </c>
       <c r="R57" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="S57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="S57" s="1" t="n">
-        <v>0.1081</v>
+      <c r="T57" s="1" t="n">
+        <v>0.1075</v>
       </c>
     </row>
     <row r="58">
@@ -4008,9 +4182,12 @@
         <v>2.649</v>
       </c>
       <c r="R58" s="1" t="n">
+        <v>2.648</v>
+      </c>
+      <c r="S58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="S58" s="1" t="n">
+      <c r="T58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -4069,9 +4246,12 @@
         <v>0.1584</v>
       </c>
       <c r="R59" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="S59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="S59" s="1" t="n">
+      <c r="T59" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -4130,10 +4310,13 @@
         <v>0.005862</v>
       </c>
       <c r="R60" s="1" t="n">
+        <v>0.005834</v>
+      </c>
+      <c r="S60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="S60" s="1" t="n">
-        <v>0.005862</v>
+      <c r="T60" s="1" t="n">
+        <v>0.005834</v>
       </c>
     </row>
     <row r="61">
@@ -4191,10 +4374,13 @@
         <v>0.09161</v>
       </c>
       <c r="R61" s="1" t="n">
+        <v>0.09145</v>
+      </c>
+      <c r="S61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="S61" s="1" t="n">
-        <v>0.09161</v>
+      <c r="T61" s="1" t="n">
+        <v>0.09145</v>
       </c>
     </row>
     <row r="62">
@@ -4252,10 +4438,13 @@
         <v>0.9114</v>
       </c>
       <c r="R62" s="1" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="S62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="S62" s="1" t="n">
-        <v>0.9112</v>
+      <c r="T62" s="1" t="n">
+        <v>0.9103</v>
       </c>
     </row>
     <row r="63">
@@ -4313,9 +4502,12 @@
         <v>0.779</v>
       </c>
       <c r="R63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="S63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="S63" s="1" t="n">
+      <c r="T63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -4374,9 +4566,12 @@
         <v>0.04658</v>
       </c>
       <c r="R64" s="1" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="S64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="S64" s="1" t="n">
+      <c r="T64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -4435,9 +4630,12 @@
         <v>354.57</v>
       </c>
       <c r="R65" s="1" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="S65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="S65" s="1" t="n">
+      <c r="T65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -4496,9 +4694,12 @@
         <v>0.12518</v>
       </c>
       <c r="R66" s="1" t="n">
+        <v>0.12462</v>
+      </c>
+      <c r="S66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="S66" s="1" t="n">
+      <c r="T66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -4557,9 +4758,12 @@
         <v>0.2266</v>
       </c>
       <c r="R67" s="1" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="S67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="S67" s="1" t="n">
+      <c r="T67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -4618,10 +4822,13 @@
         <v>0.00339</v>
       </c>
       <c r="R68" s="1" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="S68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="S68" s="1" t="n">
-        <v>0.00338</v>
+      <c r="T68" s="1" t="n">
+        <v>0.00337</v>
       </c>
     </row>
     <row r="69">
@@ -4679,9 +4886,12 @@
         <v>0.1738</v>
       </c>
       <c r="R69" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="S69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="S69" s="1" t="n">
+      <c r="T69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -4740,9 +4950,12 @@
         <v>0.16361</v>
       </c>
       <c r="R70" s="1" t="n">
+        <v>0.16361</v>
+      </c>
+      <c r="S70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="S70" s="1" t="n">
+      <c r="T70" s="1" t="n">
         <v>0.16361</v>
       </c>
     </row>
@@ -4801,9 +5014,12 @@
         <v>0.354</v>
       </c>
       <c r="R71" s="1" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="S71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="S71" s="1" t="n">
+      <c r="T71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -4862,9 +5078,12 @@
         <v>0.707</v>
       </c>
       <c r="R72" s="1" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="S72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="S72" s="1" t="n">
+      <c r="T72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -4923,10 +5142,13 @@
         <v>0.00859</v>
       </c>
       <c r="R73" s="1" t="n">
+        <v>0.008569999999999999</v>
+      </c>
+      <c r="S73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="S73" s="1" t="n">
-        <v>0.00859</v>
+      <c r="T73" s="1" t="n">
+        <v>0.008569999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -4984,10 +5206,13 @@
         <v>0.005977</v>
       </c>
       <c r="R74" s="1" t="n">
+        <v>0.005964</v>
+      </c>
+      <c r="S74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="S74" s="1" t="n">
-        <v>0.005967</v>
+      <c r="T74" s="1" t="n">
+        <v>0.005964</v>
       </c>
     </row>
     <row r="75">
@@ -5048,6 +5273,9 @@
         <v>0.229</v>
       </c>
       <c r="S75" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="T75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -5106,9 +5334,12 @@
         <v>0.3278</v>
       </c>
       <c r="R76" s="1" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="S76" s="1" t="n">
         <v>0.3278</v>
       </c>
-      <c r="S76" s="1" t="n">
+      <c r="T76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -5167,10 +5398,13 @@
         <v>0.1001</v>
       </c>
       <c r="R77" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="S77" s="1" t="n">
-        <v>0.1001</v>
+      <c r="T77" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="78">
@@ -5228,9 +5462,12 @@
         <v>0.1223</v>
       </c>
       <c r="R78" s="1" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="S78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="S78" s="1" t="n">
+      <c r="T78" s="1" t="n">
         <v>0.1223</v>
       </c>
     </row>
@@ -5289,9 +5526,12 @@
         <v>0.0733</v>
       </c>
       <c r="R79" s="1" t="n">
-        <v>0.07373</v>
+        <v>0.07378999999999999</v>
       </c>
       <c r="S79" s="1" t="n">
+        <v>0.07378999999999999</v>
+      </c>
+      <c r="T79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -5350,10 +5590,13 @@
         <v>0.04667</v>
       </c>
       <c r="R80" s="1" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="S80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="S80" s="1" t="n">
-        <v>0.04655</v>
+      <c r="T80" s="1" t="n">
+        <v>0.0464</v>
       </c>
     </row>
     <row r="81">
@@ -5411,10 +5654,13 @@
         <v>0.000233</v>
       </c>
       <c r="R81" s="1" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="S81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="S81" s="1" t="n">
-        <v>0.000231</v>
+      <c r="T81" s="1" t="n">
+        <v>0.00023</v>
       </c>
     </row>
     <row r="82">
@@ -5472,10 +5718,13 @@
         <v>8.204000000000001</v>
       </c>
       <c r="R82" s="1" t="n">
+        <v>8.194000000000001</v>
+      </c>
+      <c r="S82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="S82" s="1" t="n">
-        <v>8.204000000000001</v>
+      <c r="T82" s="1" t="n">
+        <v>8.194000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5533,9 +5782,12 @@
         <v>0.0005774</v>
       </c>
       <c r="R83" s="1" t="n">
+        <v>0.0005792</v>
+      </c>
+      <c r="S83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="S83" s="1" t="n">
+      <c r="T83" s="1" t="n">
         <v>0.0005756</v>
       </c>
     </row>
@@ -5594,9 +5846,12 @@
         <v>0.4453</v>
       </c>
       <c r="R84" s="1" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="S84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="S84" s="1" t="n">
+      <c r="T84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -5655,9 +5910,12 @@
         <v>0.06267</v>
       </c>
       <c r="R85" s="1" t="n">
+        <v>0.06253</v>
+      </c>
+      <c r="S85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="S85" s="1" t="n">
+      <c r="T85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -5716,10 +5974,13 @@
         <v>0.0542</v>
       </c>
       <c r="R86" s="1" t="n">
+        <v>0.05403</v>
+      </c>
+      <c r="S86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="S86" s="1" t="n">
-        <v>0.0542</v>
+      <c r="T86" s="1" t="n">
+        <v>0.05403</v>
       </c>
     </row>
     <row r="87">
@@ -5777,9 +6038,12 @@
         <v>0.003349</v>
       </c>
       <c r="R87" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="S87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="S87" s="1" t="n">
+      <c r="T87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -5838,9 +6102,12 @@
         <v>0.05035</v>
       </c>
       <c r="R88" s="1" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="S88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="S88" s="1" t="n">
+      <c r="T88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -5899,9 +6166,12 @@
         <v>0.03123</v>
       </c>
       <c r="R89" s="1" t="n">
-        <v>0.0313</v>
+        <v>0.03145</v>
       </c>
       <c r="S89" s="1" t="n">
+        <v>0.03145</v>
+      </c>
+      <c r="T89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -5960,10 +6230,13 @@
         <v>0.3453</v>
       </c>
       <c r="R90" s="1" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="S90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="S90" s="1" t="n">
-        <v>0.3453</v>
+      <c r="T90" s="1" t="n">
+        <v>0.3445</v>
       </c>
     </row>
     <row r="91">
@@ -6021,9 +6294,12 @@
         <v>0.07776</v>
       </c>
       <c r="R91" s="1" t="n">
+        <v>0.07562000000000001</v>
+      </c>
+      <c r="S91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="S91" s="1" t="n">
+      <c r="T91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -6082,9 +6358,12 @@
         <v>0.3569</v>
       </c>
       <c r="R92" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="S92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="S92" s="1" t="n">
+      <c r="T92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -6143,9 +6422,12 @@
         <v>1.9762</v>
       </c>
       <c r="R93" s="1" t="n">
+        <v>1.9726</v>
+      </c>
+      <c r="S93" s="1" t="n">
         <v>1.9809</v>
       </c>
-      <c r="S93" s="1" t="n">
+      <c r="T93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -6204,9 +6486,12 @@
         <v>0.2581</v>
       </c>
       <c r="R94" s="1" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="S94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="S94" s="1" t="n">
+      <c r="T94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -6265,10 +6550,13 @@
         <v>0.04547</v>
       </c>
       <c r="R95" s="1" t="n">
+        <v>0.04483</v>
+      </c>
+      <c r="S95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="S95" s="1" t="n">
-        <v>0.045</v>
+      <c r="T95" s="1" t="n">
+        <v>0.04483</v>
       </c>
     </row>
     <row r="96">
@@ -6326,9 +6614,12 @@
         <v>0.006146</v>
       </c>
       <c r="R96" s="1" t="n">
+        <v>0.00611</v>
+      </c>
+      <c r="S96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="S96" s="1" t="n">
+      <c r="T96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -6387,10 +6678,13 @@
         <v>0.001716</v>
       </c>
       <c r="R97" s="1" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="S97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="S97" s="1" t="n">
-        <v>0.001716</v>
+      <c r="T97" s="1" t="n">
+        <v>0.00171</v>
       </c>
     </row>
     <row r="98">
@@ -6448,9 +6742,12 @@
         <v>5.179</v>
       </c>
       <c r="R98" s="1" t="n">
+        <v>5.198</v>
+      </c>
+      <c r="S98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="S98" s="1" t="n">
+      <c r="T98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -6509,9 +6806,12 @@
         <v>0.01511</v>
       </c>
       <c r="R99" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="S99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="S99" s="1" t="n">
+      <c r="T99" s="1" t="n">
         <v>0.01508</v>
       </c>
     </row>
@@ -6570,9 +6870,12 @@
         <v>0.5527</v>
       </c>
       <c r="R100" s="1" t="n">
+        <v>0.5516</v>
+      </c>
+      <c r="S100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="S100" s="1" t="n">
+      <c r="T100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -6631,10 +6934,13 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="R101" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="S101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="S101" s="1" t="n">
-        <v>0.08989999999999999</v>
+      <c r="T101" s="1" t="n">
+        <v>0.0898</v>
       </c>
     </row>
     <row r="102">
@@ -6692,10 +6998,13 @@
         <v>32.34</v>
       </c>
       <c r="R102" s="1" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="S102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="S102" s="1" t="n">
-        <v>32.34</v>
+      <c r="T102" s="1" t="n">
+        <v>32.29</v>
       </c>
     </row>
     <row r="103">
@@ -6753,9 +7062,12 @@
         <v>0.03192</v>
       </c>
       <c r="R103" s="1" t="n">
+        <v>0.03162</v>
+      </c>
+      <c r="S103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="S103" s="1" t="n">
+      <c r="T103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -6814,9 +7126,12 @@
         <v>0.06564</v>
       </c>
       <c r="R104" s="1" t="n">
+        <v>0.06564</v>
+      </c>
+      <c r="S104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="S104" s="1" t="n">
+      <c r="T104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -6875,9 +7190,12 @@
         <v>1.3012</v>
       </c>
       <c r="R105" s="1" t="n">
+        <v>1.3005</v>
+      </c>
+      <c r="S105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="S105" s="1" t="n">
+      <c r="T105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -6936,9 +7254,12 @@
         <v>0.1208</v>
       </c>
       <c r="R106" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="S106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="S106" s="1" t="n">
+      <c r="T106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -6997,9 +7318,12 @@
         <v>0.119</v>
       </c>
       <c r="R107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="S107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="S107" s="1" t="n">
+      <c r="T107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -7058,10 +7382,13 @@
         <v>0.09586</v>
       </c>
       <c r="R108" s="1" t="n">
+        <v>0.09576</v>
+      </c>
+      <c r="S108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="S108" s="1" t="n">
-        <v>0.09579</v>
+      <c r="T108" s="1" t="n">
+        <v>0.09576</v>
       </c>
     </row>
     <row r="109">
@@ -7119,9 +7446,12 @@
         <v>0.14032</v>
       </c>
       <c r="R109" s="1" t="n">
+        <v>0.13884</v>
+      </c>
+      <c r="S109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="S109" s="1" t="n">
+      <c r="T109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -7180,9 +7510,12 @@
         <v>5.569</v>
       </c>
       <c r="R110" s="1" t="n">
+        <v>5.556</v>
+      </c>
+      <c r="S110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="S110" s="1" t="n">
+      <c r="T110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -7241,9 +7574,12 @@
         <v>1.1</v>
       </c>
       <c r="R111" s="1" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="S111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="S111" s="1" t="n">
+      <c r="T111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -7302,10 +7638,13 @@
         <v>0.028817</v>
       </c>
       <c r="R112" s="1" t="n">
+        <v>0.028774</v>
+      </c>
+      <c r="S112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="S112" s="1" t="n">
-        <v>0.028817</v>
+      <c r="T112" s="1" t="n">
+        <v>0.028774</v>
       </c>
     </row>
     <row r="113">
@@ -7363,10 +7702,13 @@
         <v>1.867</v>
       </c>
       <c r="R113" s="1" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="S113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="S113" s="1" t="n">
-        <v>1.867</v>
+      <c r="T113" s="1" t="n">
+        <v>1.865</v>
       </c>
     </row>
     <row r="114">
@@ -7424,9 +7766,12 @@
         <v>0.05871</v>
       </c>
       <c r="R114" s="1" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="S114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="S114" s="1" t="n">
+      <c r="T114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -7485,9 +7830,12 @@
         <v>0.12825</v>
       </c>
       <c r="R115" s="1" t="n">
+        <v>0.12738</v>
+      </c>
+      <c r="S115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="S115" s="1" t="n">
+      <c r="T115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -7546,9 +7894,12 @@
         <v>1.1039</v>
       </c>
       <c r="R116" s="1" t="n">
+        <v>1.1066</v>
+      </c>
+      <c r="S116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="S116" s="1" t="n">
+      <c r="T116" s="1" t="n">
         <v>1.1039</v>
       </c>
     </row>
@@ -7607,10 +7958,13 @@
         <v>0.1491</v>
       </c>
       <c r="R117" s="1" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="S117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="S117" s="1" t="n">
-        <v>0.1491</v>
+      <c r="T117" s="1" t="n">
+        <v>0.1485</v>
       </c>
     </row>
     <row r="118">
@@ -7668,9 +8022,12 @@
         <v>0.1582</v>
       </c>
       <c r="R118" s="1" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="S118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="S118" s="1" t="n">
+      <c r="T118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -7729,9 +8086,12 @@
         <v>0.04724</v>
       </c>
       <c r="R119" s="1" t="n">
+        <v>0.04661</v>
+      </c>
+      <c r="S119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="S119" s="1" t="n">
+      <c r="T119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -7790,10 +8150,13 @@
         <v>3.014</v>
       </c>
       <c r="R120" s="1" t="n">
+        <v>3.006</v>
+      </c>
+      <c r="S120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="S120" s="1" t="n">
-        <v>3.014</v>
+      <c r="T120" s="1" t="n">
+        <v>3.006</v>
       </c>
     </row>
     <row r="121">
@@ -7851,9 +8214,12 @@
         <v>0.2971</v>
       </c>
       <c r="R121" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="S121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="S121" s="1" t="n">
+      <c r="T121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -7912,10 +8278,13 @@
         <v>0.5783</v>
       </c>
       <c r="R122" s="1" t="n">
+        <v>0.5772</v>
+      </c>
+      <c r="S122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="S122" s="1" t="n">
-        <v>0.5783</v>
+      <c r="T122" s="1" t="n">
+        <v>0.5772</v>
       </c>
     </row>
     <row r="123">
@@ -7973,9 +8342,12 @@
         <v>0.01254</v>
       </c>
       <c r="R123" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="S123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="S123" s="1" t="n">
+      <c r="T123" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -8034,10 +8406,13 @@
         <v>0.1574</v>
       </c>
       <c r="R124" s="1" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="S124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="S124" s="1" t="n">
-        <v>0.1574</v>
+      <c r="T124" s="1" t="n">
+        <v>0.1571</v>
       </c>
     </row>
     <row r="125">
@@ -8095,9 +8470,12 @@
         <v>0.00178</v>
       </c>
       <c r="R125" s="1" t="n">
+        <v>0.001781</v>
+      </c>
+      <c r="S125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="S125" s="1" t="n">
+      <c r="T125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -8156,10 +8534,13 @@
         <v>0.0004835</v>
       </c>
       <c r="R126" s="1" t="n">
+        <v>0.0004824</v>
+      </c>
+      <c r="S126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="S126" s="1" t="n">
-        <v>0.0004831</v>
+      <c r="T126" s="1" t="n">
+        <v>0.0004824</v>
       </c>
     </row>
     <row r="127">
@@ -8217,10 +8598,13 @@
         <v>0.0293</v>
       </c>
       <c r="R127" s="1" t="n">
+        <v>0.02926</v>
+      </c>
+      <c r="S127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="S127" s="1" t="n">
-        <v>0.0293</v>
+      <c r="T127" s="1" t="n">
+        <v>0.02926</v>
       </c>
     </row>
     <row r="128">
@@ -8278,9 +8662,12 @@
         <v>0.04117</v>
       </c>
       <c r="R128" s="1" t="n">
+        <v>0.04117</v>
+      </c>
+      <c r="S128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="S128" s="1" t="n">
+      <c r="T128" s="1" t="n">
         <v>0.04117</v>
       </c>
     </row>
@@ -8339,9 +8726,12 @@
         <v>0.04889</v>
       </c>
       <c r="R129" s="1" t="n">
-        <v>0.04889</v>
+        <v>0.04918</v>
       </c>
       <c r="S129" s="1" t="n">
+        <v>0.04918</v>
+      </c>
+      <c r="T129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -8400,10 +8790,13 @@
         <v>1.23e-05</v>
       </c>
       <c r="R130" s="1" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="S130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="S130" s="1" t="n">
-        <v>1.22e-05</v>
+      <c r="T130" s="1" t="n">
+        <v>1.21e-05</v>
       </c>
     </row>
     <row r="131">
@@ -8461,9 +8854,12 @@
         <v>7e-06</v>
       </c>
       <c r="R131" s="1" t="n">
-        <v>7.2e-06</v>
+        <v>7.4e-06</v>
       </c>
       <c r="S131" s="1" t="n">
+        <v>7.4e-06</v>
+      </c>
+      <c r="T131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -8522,9 +8918,12 @@
         <v>0.00698</v>
       </c>
       <c r="R132" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="S132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="S132" s="1" t="n">
+      <c r="T132" s="1" t="n">
         <v>0.00698</v>
       </c>
     </row>
@@ -8583,10 +8982,13 @@
         <v>0.0965</v>
       </c>
       <c r="R133" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="S133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="S133" s="1" t="n">
-        <v>0.0965</v>
+      <c r="T133" s="1" t="n">
+        <v>0.0961</v>
       </c>
     </row>
     <row r="134">
@@ -8644,9 +9046,12 @@
         <v>0.0004094</v>
       </c>
       <c r="R134" s="1" t="n">
+        <v>0.0004092</v>
+      </c>
+      <c r="S134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="S134" s="1" t="n">
+      <c r="T134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -8705,10 +9110,13 @@
         <v>0.08209</v>
       </c>
       <c r="R135" s="1" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="S135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="S135" s="1" t="n">
-        <v>0.08195</v>
+      <c r="T135" s="1" t="n">
+        <v>0.0818</v>
       </c>
     </row>
     <row r="136">
@@ -8766,10 +9174,13 @@
         <v>0.007858</v>
       </c>
       <c r="R136" s="1" t="n">
+        <v>0.007816999999999999</v>
+      </c>
+      <c r="S136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="S136" s="1" t="n">
-        <v>0.007851</v>
+      <c r="T136" s="1" t="n">
+        <v>0.007816999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -8827,10 +9238,13 @@
         <v>0.0008158</v>
       </c>
       <c r="R137" s="1" t="n">
+        <v>0.0008104</v>
+      </c>
+      <c r="S137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="S137" s="1" t="n">
-        <v>0.0008158</v>
+      <c r="T137" s="1" t="n">
+        <v>0.0008104</v>
       </c>
     </row>
     <row r="138">
@@ -8888,10 +9302,13 @@
         <v>0.1465</v>
       </c>
       <c r="R138" s="1" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="S138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="S138" s="1" t="n">
-        <v>0.1465</v>
+      <c r="T138" s="1" t="n">
+        <v>0.1463</v>
       </c>
     </row>
     <row r="139">
@@ -8949,10 +9366,13 @@
         <v>0.006682</v>
       </c>
       <c r="R139" s="1" t="n">
+        <v>0.006679</v>
+      </c>
+      <c r="S139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="S139" s="1" t="n">
-        <v>0.006682</v>
+      <c r="T139" s="1" t="n">
+        <v>0.006679</v>
       </c>
     </row>
     <row r="140">
@@ -9010,9 +9430,12 @@
         <v>0.01384</v>
       </c>
       <c r="R140" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="S140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="S140" s="1" t="n">
+      <c r="T140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -9071,10 +9494,13 @@
         <v>0.09722</v>
       </c>
       <c r="R141" s="1" t="n">
+        <v>0.09676999999999999</v>
+      </c>
+      <c r="S141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="S141" s="1" t="n">
-        <v>0.09718</v>
+      <c r="T141" s="1" t="n">
+        <v>0.09676999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -9132,9 +9558,12 @@
         <v>0.0541</v>
       </c>
       <c r="R142" s="1" t="n">
+        <v>0.05409</v>
+      </c>
+      <c r="S142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="S142" s="1" t="n">
+      <c r="T142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -9193,10 +9622,13 @@
         <v>0.3221</v>
       </c>
       <c r="R143" s="1" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="S143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="S143" s="1" t="n">
-        <v>0.3221</v>
+      <c r="T143" s="1" t="n">
+        <v>0.322</v>
       </c>
     </row>
     <row r="144">
@@ -9254,10 +9686,13 @@
         <v>0.0257</v>
       </c>
       <c r="R144" s="1" t="n">
+        <v>0.02563</v>
+      </c>
+      <c r="S144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="S144" s="1" t="n">
-        <v>0.02564</v>
+      <c r="T144" s="1" t="n">
+        <v>0.02563</v>
       </c>
     </row>
     <row r="145">
@@ -9315,10 +9750,13 @@
         <v>0.2362</v>
       </c>
       <c r="R145" s="1" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="S145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="S145" s="1" t="n">
-        <v>0.2362</v>
+      <c r="T145" s="1" t="n">
+        <v>0.2354</v>
       </c>
     </row>
     <row r="146">
@@ -9376,9 +9814,12 @@
         <v>0.006992</v>
       </c>
       <c r="R146" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="S146" s="1" t="n">
+      <c r="T146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -9437,9 +9878,12 @@
         <v>0.08597</v>
       </c>
       <c r="R147" s="1" t="n">
+        <v>0.08641</v>
+      </c>
+      <c r="S147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="S147" s="1" t="n">
+      <c r="T147" s="1" t="n">
         <v>0.08597</v>
       </c>
     </row>
@@ -9498,9 +9942,12 @@
         <v>0.05233</v>
       </c>
       <c r="R148" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S148" s="1" t="n">
         <v>0.05284</v>
       </c>
-      <c r="S148" s="1" t="n">
+      <c r="T148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -9559,9 +10006,12 @@
         <v>0.02399</v>
       </c>
       <c r="R149" s="1" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="S149" s="1" t="n">
         <v>0.02399</v>
       </c>
-      <c r="S149" s="1" t="n">
+      <c r="T149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -9620,9 +10070,12 @@
         <v>0.08584</v>
       </c>
       <c r="R150" s="1" t="n">
+        <v>0.08634</v>
+      </c>
+      <c r="S150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="S150" s="1" t="n">
+      <c r="T150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -9681,9 +10134,12 @@
         <v>0.02332</v>
       </c>
       <c r="R151" s="1" t="n">
+        <v>0.02343</v>
+      </c>
+      <c r="S151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="S151" s="1" t="n">
+      <c r="T151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -9742,10 +10198,13 @@
         <v>0.0254</v>
       </c>
       <c r="R152" s="1" t="n">
+        <v>0.02531</v>
+      </c>
+      <c r="S152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="S152" s="1" t="n">
-        <v>0.02534</v>
+      <c r="T152" s="1" t="n">
+        <v>0.02531</v>
       </c>
     </row>
     <row r="153">
@@ -9803,9 +10262,12 @@
         <v>0.0002141</v>
       </c>
       <c r="R153" s="1" t="n">
+        <v>0.0002125</v>
+      </c>
+      <c r="S153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="S153" s="1" t="n">
+      <c r="T153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -9864,10 +10326,13 @@
         <v>0.4371</v>
       </c>
       <c r="R154" s="1" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="S154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="S154" s="1" t="n">
-        <v>0.4371</v>
+      <c r="T154" s="1" t="n">
+        <v>0.437</v>
       </c>
     </row>
     <row r="155">
@@ -9925,9 +10390,12 @@
         <v>0.06775</v>
       </c>
       <c r="R155" s="1" t="n">
+        <v>0.06766</v>
+      </c>
+      <c r="S155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="S155" s="1" t="n">
+      <c r="T155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -9986,9 +10454,12 @@
         <v>0.12763</v>
       </c>
       <c r="R156" s="1" t="n">
+        <v>0.12908</v>
+      </c>
+      <c r="S156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="S156" s="1" t="n">
+      <c r="T156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -10047,10 +10518,13 @@
         <v>0.4838</v>
       </c>
       <c r="R157" s="1" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="S157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="S157" s="1" t="n">
-        <v>0.4838</v>
+      <c r="T157" s="1" t="n">
+        <v>0.4828</v>
       </c>
     </row>
     <row r="158">
@@ -10108,9 +10582,12 @@
         <v>0.4502</v>
       </c>
       <c r="R158" s="1" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="S158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="S158" s="1" t="n">
+      <c r="T158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -10169,10 +10646,13 @@
         <v>0.007427</v>
       </c>
       <c r="R159" s="1" t="n">
+        <v>0.007422</v>
+      </c>
+      <c r="S159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="S159" s="1" t="n">
-        <v>0.007427</v>
+      <c r="T159" s="1" t="n">
+        <v>0.007422</v>
       </c>
     </row>
     <row r="160">
@@ -10230,9 +10710,12 @@
         <v>0.004652</v>
       </c>
       <c r="R160" s="1" t="n">
+        <v>0.004651</v>
+      </c>
+      <c r="S160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="S160" s="1" t="n">
+      <c r="T160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -10291,10 +10774,13 @@
         <v>0.004283</v>
       </c>
       <c r="R161" s="1" t="n">
+        <v>0.004278</v>
+      </c>
+      <c r="S161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="S161" s="1" t="n">
-        <v>0.004283</v>
+      <c r="T161" s="1" t="n">
+        <v>0.004278</v>
       </c>
     </row>
     <row r="162">
@@ -10352,10 +10838,13 @@
         <v>0.0955</v>
       </c>
       <c r="R162" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="S162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="S162" s="1" t="n">
-        <v>0.0955</v>
+      <c r="T162" s="1" t="n">
+        <v>0.0954</v>
       </c>
     </row>
     <row r="163">
@@ -10413,10 +10902,13 @@
         <v>0.2851</v>
       </c>
       <c r="R163" s="1" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="S163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="S163" s="1" t="n">
-        <v>0.285</v>
+      <c r="T163" s="1" t="n">
+        <v>0.2843</v>
       </c>
     </row>
     <row r="164">
@@ -10474,10 +10966,13 @@
         <v>0.114</v>
       </c>
       <c r="R164" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="S164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="S164" s="1" t="n">
-        <v>0.1139</v>
+      <c r="T164" s="1" t="n">
+        <v>0.1135</v>
       </c>
     </row>
     <row r="165">
@@ -10535,10 +11030,13 @@
         <v>0.1751</v>
       </c>
       <c r="R165" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="S165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="S165" s="1" t="n">
-        <v>0.1751</v>
+      <c r="T165" s="1" t="n">
+        <v>0.1748</v>
       </c>
     </row>
     <row r="166">
@@ -10596,9 +11094,12 @@
         <v>0.01005</v>
       </c>
       <c r="R166" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="S166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="S166" s="1" t="n">
+      <c r="T166" s="1" t="n">
         <v>0.01005</v>
       </c>
     </row>
@@ -10657,10 +11158,13 @@
         <v>1.818</v>
       </c>
       <c r="R167" s="1" t="n">
+        <v>1.817</v>
+      </c>
+      <c r="S167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="S167" s="1" t="n">
-        <v>1.818</v>
+      <c r="T167" s="1" t="n">
+        <v>1.817</v>
       </c>
     </row>
     <row r="168">
@@ -10718,9 +11222,12 @@
         <v>1.346</v>
       </c>
       <c r="R168" s="1" t="n">
+        <v>1.347</v>
+      </c>
+      <c r="S168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="S168" s="1" t="n">
+      <c r="T168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -10779,10 +11286,13 @@
         <v>0.007295</v>
       </c>
       <c r="R169" s="1" t="n">
+        <v>0.007286</v>
+      </c>
+      <c r="S169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="S169" s="1" t="n">
-        <v>0.007295</v>
+      <c r="T169" s="1" t="n">
+        <v>0.007286</v>
       </c>
     </row>
     <row r="170">
@@ -10840,9 +11350,12 @@
         <v>0.0116</v>
       </c>
       <c r="R170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="S170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="S170" s="1" t="n">
+      <c r="T170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -10901,10 +11414,13 @@
         <v>0.005772</v>
       </c>
       <c r="R171" s="1" t="n">
+        <v>0.005766</v>
+      </c>
+      <c r="S171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="S171" s="1" t="n">
-        <v>0.005772</v>
+      <c r="T171" s="1" t="n">
+        <v>0.005766</v>
       </c>
     </row>
     <row r="172">
@@ -10962,9 +11478,12 @@
         <v>0.14888</v>
       </c>
       <c r="R172" s="1" t="n">
-        <v>0.14898</v>
+        <v>0.14905</v>
       </c>
       <c r="S172" s="1" t="n">
+        <v>0.14905</v>
+      </c>
+      <c r="T172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -11023,9 +11542,12 @@
         <v>4.885</v>
       </c>
       <c r="R173" s="1" t="n">
-        <v>4.909</v>
+        <v>4.917</v>
       </c>
       <c r="S173" s="1" t="n">
+        <v>4.917</v>
+      </c>
+      <c r="T173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -11084,10 +11606,13 @@
         <v>0.07808</v>
       </c>
       <c r="R174" s="1" t="n">
+        <v>0.07792</v>
+      </c>
+      <c r="S174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="S174" s="1" t="n">
-        <v>0.07808</v>
+      <c r="T174" s="1" t="n">
+        <v>0.07792</v>
       </c>
     </row>
     <row r="175">
@@ -11145,10 +11670,13 @@
         <v>0.007418</v>
       </c>
       <c r="R175" s="1" t="n">
+        <v>0.007405</v>
+      </c>
+      <c r="S175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="S175" s="1" t="n">
-        <v>0.007407</v>
+      <c r="T175" s="1" t="n">
+        <v>0.007405</v>
       </c>
     </row>
     <row r="176">
@@ -11206,10 +11734,13 @@
         <v>0.1999</v>
       </c>
       <c r="R176" s="1" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="S176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="S176" s="1" t="n">
-        <v>0.1997</v>
+      <c r="T176" s="1" t="n">
+        <v>0.1988</v>
       </c>
     </row>
     <row r="177">
@@ -11267,10 +11798,13 @@
         <v>0.05176</v>
       </c>
       <c r="R177" s="1" t="n">
+        <v>0.05171</v>
+      </c>
+      <c r="S177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="S177" s="1" t="n">
-        <v>0.05175</v>
+      <c r="T177" s="1" t="n">
+        <v>0.05171</v>
       </c>
     </row>
     <row r="178">
@@ -11328,9 +11862,12 @@
         <v>0.0546</v>
       </c>
       <c r="R178" s="1" t="n">
+        <v>0.05457</v>
+      </c>
+      <c r="S178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="S178" s="1" t="n">
+      <c r="T178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -11389,9 +11926,12 @@
         <v>0.02321</v>
       </c>
       <c r="R179" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="S179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="S179" s="1" t="n">
+      <c r="T179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -11450,9 +11990,12 @@
         <v>0.6936</v>
       </c>
       <c r="R180" s="1" t="n">
+        <v>0.6971000000000001</v>
+      </c>
+      <c r="S180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="S180" s="1" t="n">
+      <c r="T180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -11511,9 +12054,12 @@
         <v>0.0003725</v>
       </c>
       <c r="R181" s="1" t="n">
+        <v>0.0003722</v>
+      </c>
+      <c r="S181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="S181" s="1" t="n">
+      <c r="T181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -11572,10 +12118,13 @@
         <v>0.01255</v>
       </c>
       <c r="R182" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="S182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="S182" s="1" t="n">
-        <v>0.01255</v>
+      <c r="T182" s="1" t="n">
+        <v>0.01254</v>
       </c>
     </row>
     <row r="183">
@@ -11633,10 +12182,13 @@
         <v>4.224</v>
       </c>
       <c r="R183" s="1" t="n">
+        <v>4.182</v>
+      </c>
+      <c r="S183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="S183" s="1" t="n">
-        <v>4.22</v>
+      <c r="T183" s="1" t="n">
+        <v>4.182</v>
       </c>
     </row>
     <row r="184">
@@ -11694,10 +12246,13 @@
         <v>0.2351</v>
       </c>
       <c r="R184" s="1" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="S184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="S184" s="1" t="n">
-        <v>0.2351</v>
+      <c r="T184" s="1" t="n">
+        <v>0.2337</v>
       </c>
     </row>
     <row r="185">
@@ -11755,9 +12310,12 @@
         <v>0.0372</v>
       </c>
       <c r="R185" s="1" t="n">
+        <v>0.03709</v>
+      </c>
+      <c r="S185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="S185" s="1" t="n">
+      <c r="T185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -11816,9 +12374,12 @@
         <v>0.11564</v>
       </c>
       <c r="R186" s="1" t="n">
+        <v>0.11572</v>
+      </c>
+      <c r="S186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="S186" s="1" t="n">
+      <c r="T186" s="1" t="n">
         <v>0.11557</v>
       </c>
     </row>
@@ -11877,9 +12438,12 @@
         <v>0.009084999999999999</v>
       </c>
       <c r="R187" s="1" t="n">
+        <v>0.009119</v>
+      </c>
+      <c r="S187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="S187" s="1" t="n">
+      <c r="T187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -11938,10 +12502,13 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="R188" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="S188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="S188" s="1" t="n">
-        <v>0.09710000000000001</v>
+      <c r="T188" s="1" t="n">
+        <v>0.0968</v>
       </c>
     </row>
     <row r="189">
@@ -11999,10 +12566,13 @@
         <v>0.02742</v>
       </c>
       <c r="R189" s="1" t="n">
+        <v>0.02737</v>
+      </c>
+      <c r="S189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="S189" s="1" t="n">
-        <v>0.02742</v>
+      <c r="T189" s="1" t="n">
+        <v>0.02737</v>
       </c>
     </row>
     <row r="190">
@@ -12060,9 +12630,12 @@
         <v>0.008670000000000001</v>
       </c>
       <c r="R190" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="S190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="S190" s="1" t="n">
+      <c r="T190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -12121,9 +12694,12 @@
         <v>0.001951</v>
       </c>
       <c r="R191" s="1" t="n">
+        <v>0.001949</v>
+      </c>
+      <c r="S191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="S191" s="1" t="n">
+      <c r="T191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -12182,9 +12758,12 @@
         <v>0.1001</v>
       </c>
       <c r="R192" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="S192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="S192" s="1" t="n">
+      <c r="T192" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -12243,9 +12822,12 @@
         <v>0.02324</v>
       </c>
       <c r="R193" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="S193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="S193" s="1" t="n">
+      <c r="T193" s="1" t="n">
         <v>0.02312</v>
       </c>
     </row>
@@ -12304,10 +12886,13 @@
         <v>0.01342</v>
       </c>
       <c r="R194" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="S194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="S194" s="1" t="n">
-        <v>0.01342</v>
+      <c r="T194" s="1" t="n">
+        <v>0.01341</v>
       </c>
     </row>
     <row r="195">
@@ -12365,9 +12950,12 @@
         <v>0.02078</v>
       </c>
       <c r="R195" s="1" t="n">
+        <v>0.02078</v>
+      </c>
+      <c r="S195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="S195" s="1" t="n">
+      <c r="T195" s="1" t="n">
         <v>0.02078</v>
       </c>
     </row>
@@ -12426,9 +13014,12 @@
         <v>0.17659</v>
       </c>
       <c r="R196" s="1" t="n">
+        <v>0.17573</v>
+      </c>
+      <c r="S196" s="1" t="n">
         <v>0.17659</v>
       </c>
-      <c r="S196" s="1" t="n">
+      <c r="T196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -12487,9 +13078,12 @@
         <v>0.007366</v>
       </c>
       <c r="R197" s="1" t="n">
+        <v>0.007343</v>
+      </c>
+      <c r="S197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="S197" s="1" t="n">
+      <c r="T197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -12548,10 +13142,13 @@
         <v>0.01904</v>
       </c>
       <c r="R198" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="S198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="S198" s="1" t="n">
-        <v>0.01904</v>
+      <c r="T198" s="1" t="n">
+        <v>0.019</v>
       </c>
     </row>
     <row r="199">
@@ -12609,9 +13206,12 @@
         <v>0.01647</v>
       </c>
       <c r="R199" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="S199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="S199" s="1" t="n">
+      <c r="T199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -12670,9 +13270,12 @@
         <v>0.2979</v>
       </c>
       <c r="R200" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="S200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="S200" s="1" t="n">
+      <c r="T200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -12731,10 +13334,13 @@
         <v>0.006208</v>
       </c>
       <c r="R201" s="1" t="n">
+        <v>0.006203</v>
+      </c>
+      <c r="S201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="S201" s="1" t="n">
-        <v>0.006205</v>
+      <c r="T201" s="1" t="n">
+        <v>0.006203</v>
       </c>
     </row>
     <row r="202">
@@ -12792,10 +13398,13 @@
         <v>0.0004404</v>
       </c>
       <c r="R202" s="1" t="n">
+        <v>0.0004393</v>
+      </c>
+      <c r="S202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="S202" s="1" t="n">
-        <v>0.0004404</v>
+      <c r="T202" s="1" t="n">
+        <v>0.0004393</v>
       </c>
     </row>
     <row r="203">
@@ -12853,10 +13462,13 @@
         <v>0.007272</v>
       </c>
       <c r="R203" s="1" t="n">
+        <v>0.007245</v>
+      </c>
+      <c r="S203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="S203" s="1" t="n">
-        <v>0.007251</v>
+      <c r="T203" s="1" t="n">
+        <v>0.007245</v>
       </c>
     </row>
     <row r="204">
@@ -12914,9 +13526,12 @@
         <v>0.1308</v>
       </c>
       <c r="R204" s="1" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="S204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="S204" s="1" t="n">
+      <c r="T204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -12975,9 +13590,12 @@
         <v>0.01412</v>
       </c>
       <c r="R205" s="1" t="n">
+        <v>0.01416</v>
+      </c>
+      <c r="S205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="S205" s="1" t="n">
+      <c r="T205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -13036,9 +13654,12 @@
         <v>0.003566</v>
       </c>
       <c r="R206" s="1" t="n">
+        <v>0.00357</v>
+      </c>
+      <c r="S206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="S206" s="1" t="n">
+      <c r="T206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -13097,10 +13718,13 @@
         <v>0.05933</v>
       </c>
       <c r="R207" s="1" t="n">
+        <v>0.05924</v>
+      </c>
+      <c r="S207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="S207" s="1" t="n">
-        <v>0.05933</v>
+      <c r="T207" s="1" t="n">
+        <v>0.05924</v>
       </c>
     </row>
     <row r="208">
@@ -13158,9 +13782,12 @@
         <v>15.45</v>
       </c>
       <c r="R208" s="1" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="S208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="S208" s="1" t="n">
+      <c r="T208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -13219,9 +13846,12 @@
         <v>5194.1</v>
       </c>
       <c r="R209" s="1" t="n">
+        <v>5193.6</v>
+      </c>
+      <c r="S209" s="1" t="n">
         <v>5194.1</v>
       </c>
-      <c r="S209" s="1" t="n">
+      <c r="T209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -13280,9 +13910,12 @@
         <v>0.12005</v>
       </c>
       <c r="R210" s="1" t="n">
+        <v>0.11991</v>
+      </c>
+      <c r="S210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="S210" s="1" t="n">
+      <c r="T210" s="1" t="n">
         <v>0.11955</v>
       </c>
     </row>
@@ -13341,9 +13974,12 @@
         <v>0.1811</v>
       </c>
       <c r="R211" s="1" t="n">
+        <v>0.1808</v>
+      </c>
+      <c r="S211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="S211" s="1" t="n">
+      <c r="T211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -13402,9 +14038,12 @@
         <v>0.0303</v>
       </c>
       <c r="R212" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="S212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="S212" s="1" t="n">
+      <c r="T212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -13463,9 +14102,12 @@
         <v>1.3965</v>
       </c>
       <c r="R213" s="1" t="n">
+        <v>1.3966</v>
+      </c>
+      <c r="S213" s="1" t="n">
         <v>1.3979</v>
       </c>
-      <c r="S213" s="1" t="n">
+      <c r="T213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -13524,9 +14166,12 @@
         <v>0.05649</v>
       </c>
       <c r="R214" s="1" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="S214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="S214" s="1" t="n">
+      <c r="T214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -13585,9 +14230,12 @@
         <v>0.04415</v>
       </c>
       <c r="R215" s="1" t="n">
-        <v>0.04437</v>
+        <v>0.04447</v>
       </c>
       <c r="S215" s="1" t="n">
+        <v>0.04447</v>
+      </c>
+      <c r="T215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -13646,9 +14294,12 @@
         <v>0.15079</v>
       </c>
       <c r="R216" s="1" t="n">
+        <v>0.15053</v>
+      </c>
+      <c r="S216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="S216" s="1" t="n">
+      <c r="T216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -13710,6 +14361,9 @@
         <v>0.074</v>
       </c>
       <c r="S217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="T217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -13768,9 +14422,12 @@
         <v>0.00267</v>
       </c>
       <c r="R218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="S218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="S218" s="1" t="n">
+      <c r="T218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -13829,10 +14486,13 @@
         <v>0.01698</v>
       </c>
       <c r="R219" s="1" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="S219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="S219" s="1" t="n">
-        <v>0.01698</v>
+      <c r="T219" s="1" t="n">
+        <v>0.01696</v>
       </c>
     </row>
     <row r="220">
@@ -13890,10 +14550,13 @@
         <v>0.05507</v>
       </c>
       <c r="R220" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="S220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="S220" s="1" t="n">
-        <v>0.05507</v>
+      <c r="T220" s="1" t="n">
+        <v>0.05504</v>
       </c>
     </row>
     <row r="221">
@@ -13951,9 +14614,12 @@
         <v>0.02179</v>
       </c>
       <c r="R221" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="S221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="S221" s="1" t="n">
+      <c r="T221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -14012,10 +14678,13 @@
         <v>0.009299999999999999</v>
       </c>
       <c r="R222" s="1" t="n">
+        <v>0.00924</v>
+      </c>
+      <c r="S222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="S222" s="1" t="n">
-        <v>0.009299999999999999</v>
+      <c r="T222" s="1" t="n">
+        <v>0.00924</v>
       </c>
     </row>
     <row r="223">
@@ -14073,10 +14742,13 @@
         <v>0.0164</v>
       </c>
       <c r="R223" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="S223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="S223" s="1" t="n">
-        <v>0.0164</v>
+      <c r="T223" s="1" t="n">
+        <v>0.0163</v>
       </c>
     </row>
     <row r="224">
@@ -14134,9 +14806,12 @@
         <v>0.03825</v>
       </c>
       <c r="R224" s="1" t="n">
+        <v>0.03836</v>
+      </c>
+      <c r="S224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="S224" s="1" t="n">
+      <c r="T224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -14195,10 +14870,13 @@
         <v>0.00152</v>
       </c>
       <c r="R225" s="1" t="n">
+        <v>0.001513</v>
+      </c>
+      <c r="S225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="S225" s="1" t="n">
-        <v>0.00152</v>
+      <c r="T225" s="1" t="n">
+        <v>0.001513</v>
       </c>
     </row>
     <row r="226">
@@ -14256,9 +14934,12 @@
         <v>27.17</v>
       </c>
       <c r="R226" s="1" t="n">
-        <v>27.2</v>
+        <v>27.25</v>
       </c>
       <c r="S226" s="1" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="T226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -14317,10 +14998,13 @@
         <v>0.07044</v>
       </c>
       <c r="R227" s="1" t="n">
+        <v>0.07009</v>
+      </c>
+      <c r="S227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="S227" s="1" t="n">
-        <v>0.07015</v>
+      <c r="T227" s="1" t="n">
+        <v>0.07009</v>
       </c>
     </row>
     <row r="228">
@@ -14378,9 +15062,12 @@
         <v>0.3121</v>
       </c>
       <c r="R228" s="1" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="S228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="S228" s="1" t="n">
+      <c r="T228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -14439,9 +15126,12 @@
         <v>18.34</v>
       </c>
       <c r="R229" s="1" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="S229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="S229" s="1" t="n">
+      <c r="T229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -14500,10 +15190,13 @@
         <v>0.01918</v>
       </c>
       <c r="R230" s="1" t="n">
+        <v>0.01914</v>
+      </c>
+      <c r="S230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="S230" s="1" t="n">
-        <v>0.01918</v>
+      <c r="T230" s="1" t="n">
+        <v>0.01914</v>
       </c>
     </row>
     <row r="231">
@@ -14561,10 +15254,13 @@
         <v>0.01217</v>
       </c>
       <c r="R231" s="1" t="n">
+        <v>0.01214</v>
+      </c>
+      <c r="S231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="S231" s="1" t="n">
-        <v>0.01216</v>
+      <c r="T231" s="1" t="n">
+        <v>0.01214</v>
       </c>
     </row>
     <row r="232">
@@ -14622,10 +15318,13 @@
         <v>0.2274</v>
       </c>
       <c r="R232" s="1" t="n">
+        <v>0.2271</v>
+      </c>
+      <c r="S232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="S232" s="1" t="n">
-        <v>0.2274</v>
+      <c r="T232" s="1" t="n">
+        <v>0.2271</v>
       </c>
     </row>
     <row r="233">
@@ -14683,10 +15382,13 @@
         <v>0.07074</v>
       </c>
       <c r="R233" s="1" t="n">
+        <v>0.07073</v>
+      </c>
+      <c r="S233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="S233" s="1" t="n">
-        <v>0.07074</v>
+      <c r="T233" s="1" t="n">
+        <v>0.07073</v>
       </c>
     </row>
     <row r="234">
@@ -14744,9 +15446,12 @@
         <v>0.1703</v>
       </c>
       <c r="R234" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="S234" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="S234" s="1" t="n">
+      <c r="T234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -14805,9 +15510,12 @@
         <v>0.025</v>
       </c>
       <c r="R235" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="S235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="S235" s="1" t="n">
+      <c r="T235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -14866,9 +15574,12 @@
         <v>0.02993</v>
       </c>
       <c r="R236" s="1" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="S236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="S236" s="1" t="n">
+      <c r="T236" s="1" t="n">
         <v>0.02993</v>
       </c>
     </row>
@@ -14927,9 +15638,12 @@
         <v>2.008</v>
       </c>
       <c r="R237" s="1" t="n">
-        <v>2.008</v>
+        <v>2.016</v>
       </c>
       <c r="S237" s="1" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="T237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -14988,9 +15702,12 @@
         <v>0.4214</v>
       </c>
       <c r="R238" s="1" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="S238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="S238" s="1" t="n">
+      <c r="T238" s="1" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -15049,10 +15766,13 @@
         <v>0.03352</v>
       </c>
       <c r="R239" s="1" t="n">
+        <v>0.03315</v>
+      </c>
+      <c r="S239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="S239" s="1" t="n">
-        <v>0.03328</v>
+      <c r="T239" s="1" t="n">
+        <v>0.03315</v>
       </c>
     </row>
     <row r="240">
@@ -15110,9 +15830,12 @@
         <v>0.034</v>
       </c>
       <c r="R240" s="1" t="n">
+        <v>0.03393</v>
+      </c>
+      <c r="S240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="S240" s="1" t="n">
+      <c r="T240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -15171,9 +15894,12 @@
         <v>0.0007515999999999999</v>
       </c>
       <c r="R241" s="1" t="n">
+        <v>0.000751</v>
+      </c>
+      <c r="S241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="S241" s="1" t="n">
+      <c r="T241" s="1" t="n">
         <v>0.0007489</v>
       </c>
     </row>
@@ -15232,10 +15958,13 @@
         <v>0.183</v>
       </c>
       <c r="R242" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="S242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="S242" s="1" t="n">
-        <v>0.1828</v>
+      <c r="T242" s="1" t="n">
+        <v>0.1823</v>
       </c>
     </row>
     <row r="243">
@@ -15293,10 +16022,13 @@
         <v>0.014757</v>
       </c>
       <c r="R243" s="1" t="n">
+        <v>0.014721</v>
+      </c>
+      <c r="S243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="S243" s="1" t="n">
-        <v>0.014735</v>
+      <c r="T243" s="1" t="n">
+        <v>0.014721</v>
       </c>
     </row>
     <row r="244">
@@ -15354,9 +16086,12 @@
         <v>3.01e-05</v>
       </c>
       <c r="R244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="S244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="S244" s="1" t="n">
+      <c r="T244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -15415,10 +16150,13 @@
         <v>0.03505</v>
       </c>
       <c r="R245" s="1" t="n">
+        <v>0.03502</v>
+      </c>
+      <c r="S245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="S245" s="1" t="n">
-        <v>0.03505</v>
+      <c r="T245" s="1" t="n">
+        <v>0.03502</v>
       </c>
     </row>
     <row r="246">
@@ -15476,10 +16214,13 @@
         <v>0.08025</v>
       </c>
       <c r="R246" s="1" t="n">
+        <v>0.08018</v>
+      </c>
+      <c r="S246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="S246" s="1" t="n">
-        <v>0.08025</v>
+      <c r="T246" s="1" t="n">
+        <v>0.08018</v>
       </c>
     </row>
     <row r="247">
@@ -15537,9 +16278,12 @@
         <v>0.007259</v>
       </c>
       <c r="R247" s="1" t="n">
+        <v>0.007281</v>
+      </c>
+      <c r="S247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="S247" s="1" t="n">
+      <c r="T247" s="1" t="n">
         <v>0.007229</v>
       </c>
     </row>
@@ -15598,10 +16342,13 @@
         <v>0.09442</v>
       </c>
       <c r="R248" s="1" t="n">
+        <v>0.09372</v>
+      </c>
+      <c r="S248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="S248" s="1" t="n">
-        <v>0.09438000000000001</v>
+      <c r="T248" s="1" t="n">
+        <v>0.09372</v>
       </c>
     </row>
     <row r="249">
@@ -15659,9 +16406,12 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="R249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="S249" s="1" t="n">
+      <c r="T249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -15720,10 +16470,13 @@
         <v>0.03472</v>
       </c>
       <c r="R250" s="1" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="S250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="S250" s="1" t="n">
-        <v>0.03472</v>
+      <c r="T250" s="1" t="n">
+        <v>0.03469</v>
       </c>
     </row>
     <row r="251">
@@ -15781,9 +16534,12 @@
         <v>0.03915</v>
       </c>
       <c r="R251" s="1" t="n">
+        <v>0.03916</v>
+      </c>
+      <c r="S251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="S251" s="1" t="n">
+      <c r="T251" s="1" t="n">
         <v>0.03915</v>
       </c>
     </row>
@@ -15842,10 +16598,13 @@
         <v>0.0888</v>
       </c>
       <c r="R252" s="1" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="S252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="S252" s="1" t="n">
-        <v>0.0888</v>
+      <c r="T252" s="1" t="n">
+        <v>0.0876</v>
       </c>
     </row>
     <row r="253">
@@ -15903,9 +16662,12 @@
         <v>4.075</v>
       </c>
       <c r="R253" s="1" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="S253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="S253" s="1" t="n">
+      <c r="T253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -15964,9 +16726,12 @@
         <v>0.1873</v>
       </c>
       <c r="R254" s="1" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="S254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="S254" s="1" t="n">
+      <c r="T254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -16025,10 +16790,13 @@
         <v>0.07187</v>
       </c>
       <c r="R255" s="1" t="n">
+        <v>0.07174</v>
+      </c>
+      <c r="S255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="S255" s="1" t="n">
-        <v>0.07185</v>
+      <c r="T255" s="1" t="n">
+        <v>0.07174</v>
       </c>
     </row>
     <row r="256">
@@ -16086,9 +16854,12 @@
         <v>0.01825</v>
       </c>
       <c r="R256" s="1" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="S256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="S256" s="1" t="n">
+      <c r="T256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -16147,9 +16918,12 @@
         <v>5.933</v>
       </c>
       <c r="R257" s="1" t="n">
+        <v>5.934</v>
+      </c>
+      <c r="S257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="S257" s="1" t="n">
+      <c r="T257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -16208,10 +16982,13 @@
         <v>0.2619</v>
       </c>
       <c r="R258" s="1" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="S258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="S258" s="1" t="n">
-        <v>0.261</v>
+      <c r="T258" s="1" t="n">
+        <v>0.2599</v>
       </c>
     </row>
     <row r="259">
@@ -16269,10 +17046,13 @@
         <v>0.1355</v>
       </c>
       <c r="R259" s="1" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="S259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="S259" s="1" t="n">
-        <v>0.1355</v>
+      <c r="T259" s="1" t="n">
+        <v>0.1352</v>
       </c>
     </row>
     <row r="260">
@@ -16330,9 +17110,12 @@
         <v>0.30654</v>
       </c>
       <c r="R260" s="1" t="n">
-        <v>0.30784</v>
+        <v>0.30794</v>
       </c>
       <c r="S260" s="1" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="T260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -16391,9 +17174,12 @@
         <v>0.09915</v>
       </c>
       <c r="R261" s="1" t="n">
+        <v>0.09875</v>
+      </c>
+      <c r="S261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="S261" s="1" t="n">
+      <c r="T261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -16452,9 +17238,12 @@
         <v>0.5383</v>
       </c>
       <c r="R262" s="1" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="S262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="S262" s="1" t="n">
+      <c r="T262" s="1" t="n">
         <v>0.538</v>
       </c>
     </row>
@@ -16513,10 +17302,13 @@
         <v>0.289</v>
       </c>
       <c r="R263" s="1" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="S263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="S263" s="1" t="n">
-        <v>0.289</v>
+      <c r="T263" s="1" t="n">
+        <v>0.2885</v>
       </c>
     </row>
     <row r="264">
@@ -16574,9 +17366,12 @@
         <v>0.97</v>
       </c>
       <c r="R264" s="1" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="S264" s="1" t="n">
         <v>0.983</v>
       </c>
-      <c r="S264" s="1" t="n">
+      <c r="T264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -16635,10 +17430,13 @@
         <v>0.539</v>
       </c>
       <c r="R265" s="1" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="S265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="S265" s="1" t="n">
-        <v>0.539</v>
+      <c r="T265" s="1" t="n">
+        <v>0.5367</v>
       </c>
     </row>
     <row r="266">
@@ -16696,10 +17494,13 @@
         <v>0.07351000000000001</v>
       </c>
       <c r="R266" s="1" t="n">
+        <v>0.07341</v>
+      </c>
+      <c r="S266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="S266" s="1" t="n">
-        <v>0.07351000000000001</v>
+      <c r="T266" s="1" t="n">
+        <v>0.07341</v>
       </c>
     </row>
     <row r="267">
@@ -16757,9 +17558,12 @@
         <v>0.02153</v>
       </c>
       <c r="R267" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="S267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="S267" s="1" t="n">
+      <c r="T267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -16818,10 +17622,13 @@
         <v>0.01609</v>
       </c>
       <c r="R268" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="S268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="S268" s="1" t="n">
-        <v>0.01606</v>
+      <c r="T268" s="1" t="n">
+        <v>0.01603</v>
       </c>
     </row>
     <row r="269">
@@ -16879,9 +17686,12 @@
         <v>0.003791</v>
       </c>
       <c r="R269" s="1" t="n">
+        <v>0.003795</v>
+      </c>
+      <c r="S269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="S269" s="1" t="n">
+      <c r="T269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -16940,10 +17750,13 @@
         <v>0.0076</v>
       </c>
       <c r="R270" s="1" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="S270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="S270" s="1" t="n">
-        <v>0.0076</v>
+      <c r="T270" s="1" t="n">
+        <v>0.00757</v>
       </c>
     </row>
     <row r="271">
@@ -17001,10 +17814,13 @@
         <v>0.05497</v>
       </c>
       <c r="R271" s="1" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="S271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="S271" s="1" t="n">
-        <v>0.05495</v>
+      <c r="T271" s="1" t="n">
+        <v>0.0547</v>
       </c>
     </row>
     <row r="272">
@@ -17062,10 +17878,13 @@
         <v>2.268</v>
       </c>
       <c r="R272" s="1" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="S272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="S272" s="1" t="n">
-        <v>2.268</v>
+      <c r="T272" s="1" t="n">
+        <v>2.267</v>
       </c>
     </row>
     <row r="273">
@@ -17123,9 +17942,12 @@
         <v>0.05492</v>
       </c>
       <c r="R273" s="1" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="S273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="S273" s="1" t="n">
+      <c r="T273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -17184,9 +18006,12 @@
         <v>0.0233</v>
       </c>
       <c r="R274" s="1" t="n">
+        <v>0.02328</v>
+      </c>
+      <c r="S274" s="1" t="n">
         <v>0.02336</v>
       </c>
-      <c r="S274" s="1" t="n">
+      <c r="T274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -17245,9 +18070,12 @@
         <v>1.175</v>
       </c>
       <c r="R275" s="1" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="S275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="S275" s="1" t="n">
+      <c r="T275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -17306,9 +18134,12 @@
         <v>0.2708</v>
       </c>
       <c r="R276" s="1" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="S276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="S276" s="1" t="n">
+      <c r="T276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -17367,10 +18198,13 @@
         <v>0.928</v>
       </c>
       <c r="R277" s="1" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="S277" s="1" t="n">
-        <v>0.928</v>
+      <c r="T277" s="1" t="n">
+        <v>0.923</v>
       </c>
     </row>
     <row r="278">
@@ -17428,9 +18262,12 @@
         <v>0.6237</v>
       </c>
       <c r="R278" s="1" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="S278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="S278" s="1" t="n">
+      <c r="T278" s="1" t="n">
         <v>0.6221</v>
       </c>
     </row>
@@ -17489,10 +18326,13 @@
         <v>0.001336</v>
       </c>
       <c r="R279" s="1" t="n">
+        <v>0.001331</v>
+      </c>
+      <c r="S279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="S279" s="1" t="n">
-        <v>0.001336</v>
+      <c r="T279" s="1" t="n">
+        <v>0.001331</v>
       </c>
     </row>
     <row r="280">
@@ -17550,9 +18390,12 @@
         <v>0.005599</v>
       </c>
       <c r="R280" s="1" t="n">
+        <v>0.005591</v>
+      </c>
+      <c r="S280" s="1" t="n">
         <v>0.005601</v>
       </c>
-      <c r="S280" s="1" t="n">
+      <c r="T280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -17611,10 +18454,13 @@
         <v>1.517</v>
       </c>
       <c r="R281" s="1" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="S281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="S281" s="1" t="n">
-        <v>1.516</v>
+      <c r="T281" s="1" t="n">
+        <v>1.515</v>
       </c>
     </row>
     <row r="282">
@@ -17672,10 +18518,13 @@
         <v>28.29</v>
       </c>
       <c r="R282" s="1" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="S282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="S282" s="1" t="n">
-        <v>28.26</v>
+      <c r="T282" s="1" t="n">
+        <v>28.25</v>
       </c>
     </row>
     <row r="283">
@@ -17733,10 +18582,13 @@
         <v>0.12828</v>
       </c>
       <c r="R283" s="1" t="n">
+        <v>0.12788</v>
+      </c>
+      <c r="S283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="S283" s="1" t="n">
-        <v>0.12828</v>
+      <c r="T283" s="1" t="n">
+        <v>0.12788</v>
       </c>
     </row>
     <row r="284">
@@ -17794,10 +18646,13 @@
         <v>0.01106</v>
       </c>
       <c r="R284" s="1" t="n">
+        <v>0.01103</v>
+      </c>
+      <c r="S284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="S284" s="1" t="n">
-        <v>0.01106</v>
+      <c r="T284" s="1" t="n">
+        <v>0.01103</v>
       </c>
     </row>
     <row r="285">
@@ -17855,9 +18710,12 @@
         <v>6.538</v>
       </c>
       <c r="R285" s="1" t="n">
+        <v>6.533</v>
+      </c>
+      <c r="S285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="S285" s="1" t="n">
+      <c r="T285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -17916,10 +18774,13 @@
         <v>0.01841</v>
       </c>
       <c r="R286" s="1" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="S286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="S286" s="1" t="n">
-        <v>0.01838</v>
+      <c r="T286" s="1" t="n">
+        <v>0.01831</v>
       </c>
     </row>
     <row r="287">
@@ -17977,10 +18838,13 @@
         <v>0.008336</v>
       </c>
       <c r="R287" s="1" t="n">
+        <v>0.008312999999999999</v>
+      </c>
+      <c r="S287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="S287" s="1" t="n">
-        <v>0.008336</v>
+      <c r="T287" s="1" t="n">
+        <v>0.008312999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -18038,9 +18902,12 @@
         <v>0.3812</v>
       </c>
       <c r="R288" s="1" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="S288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="S288" s="1" t="n">
+      <c r="T288" s="1" t="n">
         <v>0.3803</v>
       </c>
     </row>
@@ -18099,10 +18966,13 @@
         <v>0.009868</v>
       </c>
       <c r="R289" s="1" t="n">
+        <v>0.009771</v>
+      </c>
+      <c r="S289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="S289" s="1" t="n">
-        <v>0.009868</v>
+      <c r="T289" s="1" t="n">
+        <v>0.009771</v>
       </c>
     </row>
     <row r="290">
@@ -18160,9 +19030,12 @@
         <v>0.02591</v>
       </c>
       <c r="R290" s="1" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="S290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="S290" s="1" t="n">
+      <c r="T290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -18221,9 +19094,12 @@
         <v>0.095</v>
       </c>
       <c r="R291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="S291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="S291" s="1" t="n">
+      <c r="T291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -18282,9 +19158,12 @@
         <v>0.28799</v>
       </c>
       <c r="R292" s="1" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="S292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="S292" s="1" t="n">
+      <c r="T292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -18343,9 +19222,12 @@
         <v>0.01534</v>
       </c>
       <c r="R293" s="1" t="n">
+        <v>0.01534</v>
+      </c>
+      <c r="S293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="S293" s="1" t="n">
+      <c r="T293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -18404,10 +19286,13 @@
         <v>0.003395</v>
       </c>
       <c r="R294" s="1" t="n">
+        <v>0.003381</v>
+      </c>
+      <c r="S294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="S294" s="1" t="n">
-        <v>0.003395</v>
+      <c r="T294" s="1" t="n">
+        <v>0.003381</v>
       </c>
     </row>
     <row r="295">
@@ -18465,9 +19350,12 @@
         <v>0.042232</v>
       </c>
       <c r="R295" s="1" t="n">
+        <v>0.042519</v>
+      </c>
+      <c r="S295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="S295" s="1" t="n">
+      <c r="T295" s="1" t="n">
         <v>0.042232</v>
       </c>
     </row>
@@ -18526,9 +19414,12 @@
         <v>0.02946</v>
       </c>
       <c r="R296" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="S296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="S296" s="1" t="n">
+      <c r="T296" s="1" t="n">
         <v>0.02894</v>
       </c>
     </row>
@@ -18587,9 +19478,12 @@
         <v>0.03787</v>
       </c>
       <c r="R297" s="1" t="n">
+        <v>0.03823</v>
+      </c>
+      <c r="S297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="S297" s="1" t="n">
+      <c r="T297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -18648,9 +19542,12 @@
         <v>0.0832</v>
       </c>
       <c r="R298" s="1" t="n">
+        <v>0.08373</v>
+      </c>
+      <c r="S298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="S298" s="1" t="n">
+      <c r="T298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -18709,9 +19606,12 @@
         <v>0.00763</v>
       </c>
       <c r="R299" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="S299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="S299" s="1" t="n">
+      <c r="T299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -18770,10 +19670,13 @@
         <v>0.01502</v>
       </c>
       <c r="R300" s="1" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="S300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="S300" s="1" t="n">
-        <v>0.01502</v>
+      <c r="T300" s="1" t="n">
+        <v>0.01498</v>
       </c>
     </row>
     <row r="301">
@@ -18831,9 +19734,12 @@
         <v>0.1402</v>
       </c>
       <c r="R301" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="S301" s="1" t="n">
+      <c r="T301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -18892,10 +19798,13 @@
         <v>0.000626</v>
       </c>
       <c r="R302" s="1" t="n">
+        <v>0.0006217</v>
+      </c>
+      <c r="S302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="S302" s="1" t="n">
-        <v>0.0006229</v>
+      <c r="T302" s="1" t="n">
+        <v>0.0006217</v>
       </c>
     </row>
     <row r="303">
@@ -18953,9 +19862,12 @@
         <v>0.06227</v>
       </c>
       <c r="R303" s="1" t="n">
+        <v>0.06212</v>
+      </c>
+      <c r="S303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="S303" s="1" t="n">
+      <c r="T303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -19014,9 +19926,12 @@
         <v>0.0001623</v>
       </c>
       <c r="R304" s="1" t="n">
+        <v>0.0001624</v>
+      </c>
+      <c r="S304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="S304" s="1" t="n">
+      <c r="T304" s="1" t="n">
         <v>0.0001623</v>
       </c>
     </row>
@@ -19075,9 +19990,12 @@
         <v>0.06096</v>
       </c>
       <c r="R305" s="1" t="n">
+        <v>0.06104</v>
+      </c>
+      <c r="S305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="S305" s="1" t="n">
+      <c r="T305" s="1" t="n">
         <v>0.06076</v>
       </c>
     </row>
@@ -19136,9 +20054,12 @@
         <v>0.022396</v>
       </c>
       <c r="R306" s="1" t="n">
+        <v>0.022283</v>
+      </c>
+      <c r="S306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="S306" s="1" t="n">
+      <c r="T306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -19197,10 +20118,13 @@
         <v>0.02373</v>
       </c>
       <c r="R307" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="S307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="S307" s="1" t="n">
-        <v>0.02332</v>
+      <c r="T307" s="1" t="n">
+        <v>0.02331</v>
       </c>
     </row>
     <row r="308">
@@ -19258,9 +20182,12 @@
         <v>0.00041</v>
       </c>
       <c r="R308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="S308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="S308" s="1" t="n">
+      <c r="T308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -19319,10 +20246,13 @@
         <v>0.0898</v>
       </c>
       <c r="R309" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="S309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="S309" s="1" t="n">
-        <v>0.0897</v>
+      <c r="T309" s="1" t="n">
+        <v>0.0896</v>
       </c>
     </row>
     <row r="310">
@@ -19380,9 +20310,12 @@
         <v>0.3688</v>
       </c>
       <c r="R310" s="1" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="S310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="S310" s="1" t="n">
+      <c r="T310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -19441,9 +20374,12 @@
         <v>0.0354</v>
       </c>
       <c r="R311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="S311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="S311" s="1" t="n">
+      <c r="T311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -19502,10 +20438,13 @@
         <v>0.02426</v>
       </c>
       <c r="R312" s="1" t="n">
+        <v>0.02423</v>
+      </c>
+      <c r="S312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="S312" s="1" t="n">
-        <v>0.02426</v>
+      <c r="T312" s="1" t="n">
+        <v>0.02423</v>
       </c>
     </row>
     <row r="313">
@@ -19563,10 +20502,13 @@
         <v>0.041</v>
       </c>
       <c r="R313" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="S313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="S313" s="1" t="n">
-        <v>0.041</v>
+      <c r="T313" s="1" t="n">
+        <v>0.0409</v>
       </c>
     </row>
     <row r="314">
@@ -19624,10 +20566,13 @@
         <v>3.944</v>
       </c>
       <c r="R314" s="1" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="S314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="S314" s="1" t="n">
-        <v>3.944</v>
+      <c r="T314" s="1" t="n">
+        <v>3.933</v>
       </c>
     </row>
     <row r="315">
@@ -19685,10 +20630,13 @@
         <v>0.159</v>
       </c>
       <c r="R315" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="S315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="S315" s="1" t="n">
-        <v>0.159</v>
+      <c r="T315" s="1" t="n">
+        <v>0.1589</v>
       </c>
     </row>
     <row r="316">
@@ -19746,9 +20694,12 @@
         <v>0.08977</v>
       </c>
       <c r="R316" s="1" t="n">
+        <v>0.09092</v>
+      </c>
+      <c r="S316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="S316" s="1" t="n">
+      <c r="T316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -19807,9 +20758,12 @@
         <v>0.06809</v>
       </c>
       <c r="R317" s="1" t="n">
+        <v>0.06809</v>
+      </c>
+      <c r="S317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="S317" s="1" t="n">
+      <c r="T317" s="1" t="n">
         <v>0.06791999999999999</v>
       </c>
     </row>
@@ -19868,10 +20822,13 @@
         <v>0.012432</v>
       </c>
       <c r="R318" s="1" t="n">
+        <v>0.012382</v>
+      </c>
+      <c r="S318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="S318" s="1" t="n">
-        <v>0.012414</v>
+      <c r="T318" s="1" t="n">
+        <v>0.012382</v>
       </c>
     </row>
     <row r="319">
@@ -19929,10 +20886,13 @@
         <v>0.001132</v>
       </c>
       <c r="R319" s="1" t="n">
+        <v>0.001131</v>
+      </c>
+      <c r="S319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="S319" s="1" t="n">
-        <v>0.001132</v>
+      <c r="T319" s="1" t="n">
+        <v>0.001131</v>
       </c>
     </row>
     <row r="320">
@@ -19990,9 +20950,12 @@
         <v>0.0629</v>
       </c>
       <c r="R320" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="S320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="S320" s="1" t="n">
+      <c r="T320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -20051,9 +21014,12 @@
         <v>0.00524</v>
       </c>
       <c r="R321" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="S321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="S321" s="1" t="n">
+      <c r="T321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -20112,10 +21078,13 @@
         <v>0.1113</v>
       </c>
       <c r="R322" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="S322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="S322" s="1" t="n">
-        <v>0.1113</v>
+      <c r="T322" s="1" t="n">
+        <v>0.111</v>
       </c>
     </row>
     <row r="323">
@@ -20173,9 +21142,12 @@
         <v>0.04392</v>
       </c>
       <c r="R323" s="1" t="n">
-        <v>0.04392</v>
+        <v>0.04413</v>
       </c>
       <c r="S323" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="T323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -20234,9 +21206,12 @@
         <v>0.01787</v>
       </c>
       <c r="R324" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="S324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="S324" s="1" t="n">
+      <c r="T324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -20295,10 +21270,13 @@
         <v>0.00564</v>
       </c>
       <c r="R325" s="1" t="n">
+        <v>0.005633</v>
+      </c>
+      <c r="S325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="S325" s="1" t="n">
-        <v>0.005638</v>
+      <c r="T325" s="1" t="n">
+        <v>0.005633</v>
       </c>
     </row>
     <row r="326">
@@ -20356,10 +21334,13 @@
         <v>0.001756</v>
       </c>
       <c r="R326" s="1" t="n">
+        <v>0.001751</v>
+      </c>
+      <c r="S326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="S326" s="1" t="n">
-        <v>0.001756</v>
+      <c r="T326" s="1" t="n">
+        <v>0.001751</v>
       </c>
     </row>
     <row r="327">
@@ -20417,9 +21398,12 @@
         <v>0.04011</v>
       </c>
       <c r="R327" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="S327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="S327" s="1" t="n">
+      <c r="T327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -20478,9 +21462,12 @@
         <v>0.053684</v>
       </c>
       <c r="R328" s="1" t="n">
+        <v>0.05353</v>
+      </c>
+      <c r="S328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="S328" s="1" t="n">
+      <c r="T328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -20539,10 +21526,13 @@
         <v>0.2779</v>
       </c>
       <c r="R329" s="1" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="S329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="S329" s="1" t="n">
-        <v>0.2779</v>
+      <c r="T329" s="1" t="n">
+        <v>0.2771</v>
       </c>
     </row>
     <row r="330">
@@ -20600,10 +21590,13 @@
         <v>0.1588</v>
       </c>
       <c r="R330" s="1" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="S330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="S330" s="1" t="n">
-        <v>0.1587</v>
+      <c r="T330" s="1" t="n">
+        <v>0.1586</v>
       </c>
     </row>
     <row r="331">
@@ -20661,9 +21654,12 @@
         <v>0.05355</v>
       </c>
       <c r="R331" s="1" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="S331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="S331" s="1" t="n">
+      <c r="T331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -20722,9 +21718,12 @@
         <v>0.3605</v>
       </c>
       <c r="R332" s="1" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="S332" s="1" t="n">
+      <c r="T332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -20783,9 +21782,12 @@
         <v>0.03055</v>
       </c>
       <c r="R333" s="1" t="n">
-        <v>0.03055</v>
+        <v>0.0306</v>
       </c>
       <c r="S333" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="T333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -20844,9 +21846,12 @@
         <v>0.01756</v>
       </c>
       <c r="R334" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="S334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="S334" s="1" t="n">
+      <c r="T334" s="1" t="n">
         <v>0.01751</v>
       </c>
     </row>
@@ -20905,9 +21910,12 @@
         <v>0.0578</v>
       </c>
       <c r="R335" s="1" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="S335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="S335" s="1" t="n">
+      <c r="T335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -20966,10 +21974,13 @@
         <v>0.09054</v>
       </c>
       <c r="R336" s="1" t="n">
+        <v>0.09031</v>
+      </c>
+      <c r="S336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="S336" s="1" t="n">
-        <v>0.09045</v>
+      <c r="T336" s="1" t="n">
+        <v>0.09031</v>
       </c>
     </row>
     <row r="337">
@@ -21027,9 +22038,12 @@
         <v>0.18046</v>
       </c>
       <c r="R337" s="1" t="n">
+        <v>0.18019</v>
+      </c>
+      <c r="S337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="S337" s="1" t="n">
+      <c r="T337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -21088,10 +22102,13 @@
         <v>0.02081</v>
       </c>
       <c r="R338" s="1" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="S338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="S338" s="1" t="n">
-        <v>0.02081</v>
+      <c r="T338" s="1" t="n">
+        <v>0.02074</v>
       </c>
     </row>
     <row r="339">
@@ -21149,9 +22166,12 @@
         <v>0.1317</v>
       </c>
       <c r="R339" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="S339" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="S339" s="1" t="n">
+      <c r="T339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -21210,9 +22230,12 @@
         <v>0.007946999999999999</v>
       </c>
       <c r="R340" s="1" t="n">
+        <v>0.007957000000000001</v>
+      </c>
+      <c r="S340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="S340" s="1" t="n">
+      <c r="T340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -21271,9 +22294,12 @@
         <v>4.4</v>
       </c>
       <c r="R341" s="1" t="n">
+        <v>4.393</v>
+      </c>
+      <c r="S341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="S341" s="1" t="n">
+      <c r="T341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -21332,9 +22358,12 @@
         <v>0.18926</v>
       </c>
       <c r="R342" s="1" t="n">
+        <v>0.19012</v>
+      </c>
+      <c r="S342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="S342" s="1" t="n">
+      <c r="T342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -21393,9 +22422,12 @@
         <v>0.08309</v>
       </c>
       <c r="R343" s="1" t="n">
+        <v>0.08291</v>
+      </c>
+      <c r="S343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="S343" s="1" t="n">
+      <c r="T343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -21454,9 +22486,12 @@
         <v>0.1813</v>
       </c>
       <c r="R344" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="S344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="S344" s="1" t="n">
+      <c r="T344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -21515,10 +22550,13 @@
         <v>0.003237</v>
       </c>
       <c r="R345" s="1" t="n">
+        <v>0.003222</v>
+      </c>
+      <c r="S345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="S345" s="1" t="n">
-        <v>0.003237</v>
+      <c r="T345" s="1" t="n">
+        <v>0.003222</v>
       </c>
     </row>
     <row r="346">
@@ -21576,9 +22614,12 @@
         <v>0.09098000000000001</v>
       </c>
       <c r="R346" s="1" t="n">
+        <v>0.09134</v>
+      </c>
+      <c r="S346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="S346" s="1" t="n">
+      <c r="T346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -21637,10 +22678,13 @@
         <v>2.242</v>
       </c>
       <c r="R347" s="1" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="S347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="S347" s="1" t="n">
-        <v>2.242</v>
+      <c r="T347" s="1" t="n">
+        <v>2.235</v>
       </c>
     </row>
     <row r="348">
@@ -21698,9 +22742,12 @@
         <v>0.3033</v>
       </c>
       <c r="R348" s="1" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="S348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="S348" s="1" t="n">
+      <c r="T348" s="1" t="n">
         <v>0.3027</v>
       </c>
     </row>
@@ -21759,9 +22806,12 @@
         <v>0.02946</v>
       </c>
       <c r="R349" s="1" t="n">
+        <v>0.02954</v>
+      </c>
+      <c r="S349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="S349" s="1" t="n">
+      <c r="T349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -21820,9 +22870,12 @@
         <v>0.1276</v>
       </c>
       <c r="R350" s="1" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="S350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="S350" s="1" t="n">
+      <c r="T350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -21881,10 +22934,13 @@
         <v>0.06644</v>
       </c>
       <c r="R351" s="1" t="n">
+        <v>0.06612999999999999</v>
+      </c>
+      <c r="S351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="S351" s="1" t="n">
-        <v>0.06644</v>
+      <c r="T351" s="1" t="n">
+        <v>0.06612999999999999</v>
       </c>
     </row>
     <row r="352">
@@ -21942,10 +22998,13 @@
         <v>0.06234</v>
       </c>
       <c r="R352" s="1" t="n">
+        <v>0.06227</v>
+      </c>
+      <c r="S352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="S352" s="1" t="n">
-        <v>0.06234</v>
+      <c r="T352" s="1" t="n">
+        <v>0.06227</v>
       </c>
     </row>
     <row r="353">
@@ -22003,10 +23062,13 @@
         <v>0.06315999999999999</v>
       </c>
       <c r="R353" s="1" t="n">
+        <v>0.06283</v>
+      </c>
+      <c r="S353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="S353" s="1" t="n">
-        <v>0.06315999999999999</v>
+      <c r="T353" s="1" t="n">
+        <v>0.06283</v>
       </c>
     </row>
     <row r="354">
@@ -22064,9 +23126,12 @@
         <v>0.10407</v>
       </c>
       <c r="R354" s="1" t="n">
+        <v>0.10457</v>
+      </c>
+      <c r="S354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="S354" s="1" t="n">
+      <c r="T354" s="1" t="n">
         <v>0.10393</v>
       </c>
     </row>
@@ -22125,10 +23190,13 @@
         <v>0.09</v>
       </c>
       <c r="R355" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="S355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="S355" s="1" t="n">
-        <v>0.09</v>
+      <c r="T355" s="1" t="n">
+        <v>0.0898</v>
       </c>
     </row>
     <row r="356">
@@ -22186,10 +23254,13 @@
         <v>0.06938999999999999</v>
       </c>
       <c r="R356" s="1" t="n">
+        <v>0.06915</v>
+      </c>
+      <c r="S356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="S356" s="1" t="n">
-        <v>0.06938999999999999</v>
+      <c r="T356" s="1" t="n">
+        <v>0.06915</v>
       </c>
     </row>
     <row r="357">
@@ -22247,10 +23318,13 @@
         <v>0.4509</v>
       </c>
       <c r="R357" s="1" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="S357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="S357" s="1" t="n">
-        <v>0.4509</v>
+      <c r="T357" s="1" t="n">
+        <v>0.4505</v>
       </c>
     </row>
     <row r="358">
@@ -22308,10 +23382,13 @@
         <v>0.03469</v>
       </c>
       <c r="R358" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="S358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="S358" s="1" t="n">
-        <v>0.03467</v>
+      <c r="T358" s="1" t="n">
+        <v>0.03442</v>
       </c>
     </row>
     <row r="359">
@@ -22369,9 +23446,12 @@
         <v>0.0146</v>
       </c>
       <c r="R359" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="S359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="S359" s="1" t="n">
+      <c r="T359" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -22430,9 +23510,12 @@
         <v>0.13327</v>
       </c>
       <c r="R360" s="1" t="n">
+        <v>0.13301</v>
+      </c>
+      <c r="S360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="S360" s="1" t="n">
+      <c r="T360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -22491,9 +23574,12 @@
         <v>0.0005888999999999999</v>
       </c>
       <c r="R361" s="1" t="n">
+        <v>0.0005865</v>
+      </c>
+      <c r="S361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="S361" s="1" t="n">
+      <c r="T361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -22552,9 +23638,12 @@
         <v>0.03856</v>
       </c>
       <c r="R362" s="1" t="n">
+        <v>0.03864</v>
+      </c>
+      <c r="S362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="S362" s="1" t="n">
+      <c r="T362" s="1" t="n">
         <v>0.03855</v>
       </c>
     </row>
@@ -22613,9 +23702,12 @@
         <v>3.217</v>
       </c>
       <c r="R363" s="1" t="n">
+        <v>3.222</v>
+      </c>
+      <c r="S363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="S363" s="1" t="n">
+      <c r="T363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -22674,9 +23766,12 @@
         <v>0.1632</v>
       </c>
       <c r="R364" s="1" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="S364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="S364" s="1" t="n">
+      <c r="T364" s="1" t="n">
         <v>0.1632</v>
       </c>
     </row>
@@ -22735,10 +23830,13 @@
         <v>0.1131</v>
       </c>
       <c r="R365" s="1" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="S365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="S365" s="1" t="n">
-        <v>0.1129</v>
+      <c r="T365" s="1" t="n">
+        <v>0.1128</v>
       </c>
     </row>
     <row r="366">
@@ -22796,10 +23894,13 @@
         <v>0.0006363</v>
       </c>
       <c r="R366" s="1" t="n">
+        <v>0.0006349</v>
+      </c>
+      <c r="S366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="S366" s="1" t="n">
-        <v>0.0006363</v>
+      <c r="T366" s="1" t="n">
+        <v>0.0006349</v>
       </c>
     </row>
     <row r="367">
@@ -22857,9 +23958,12 @@
         <v>0.05943</v>
       </c>
       <c r="R367" s="1" t="n">
+        <v>0.05956</v>
+      </c>
+      <c r="S367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="S367" s="1" t="n">
+      <c r="T367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -22918,10 +24022,13 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="R368" s="1" t="n">
+        <v>0.08135000000000001</v>
+      </c>
+      <c r="S368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="S368" s="1" t="n">
-        <v>0.08160000000000001</v>
+      <c r="T368" s="1" t="n">
+        <v>0.08135000000000001</v>
       </c>
     </row>
     <row r="369">
@@ -22979,9 +24086,12 @@
         <v>0.0393</v>
       </c>
       <c r="R369" s="1" t="n">
+        <v>0.03934</v>
+      </c>
+      <c r="S369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="S369" s="1" t="n">
+      <c r="T369" s="1" t="n">
         <v>0.0393</v>
       </c>
     </row>
@@ -23040,9 +24150,12 @@
         <v>3.691</v>
       </c>
       <c r="R370" s="1" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="S370" s="1" t="n">
+      <c r="T370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -23101,9 +24214,12 @@
         <v>0.1206</v>
       </c>
       <c r="R371" s="1" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="S371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="S371" s="1" t="n">
+      <c r="T371" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -23162,9 +24278,12 @@
         <v>0.01471</v>
       </c>
       <c r="R372" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="S372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="S372" s="1" t="n">
+      <c r="T372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -23223,9 +24342,12 @@
         <v>0.02199</v>
       </c>
       <c r="R373" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="S373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="S373" s="1" t="n">
+      <c r="T373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -23284,9 +24406,12 @@
         <v>1.8573</v>
       </c>
       <c r="R374" s="1" t="n">
+        <v>1.8617</v>
+      </c>
+      <c r="S374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="S374" s="1" t="n">
+      <c r="T374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -23345,10 +24470,13 @@
         <v>0.02082</v>
       </c>
       <c r="R375" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="S375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="S375" s="1" t="n">
-        <v>0.02082</v>
+      <c r="T375" s="1" t="n">
+        <v>0.02081</v>
       </c>
     </row>
     <row r="376">
@@ -23406,9 +24534,12 @@
         <v>1.3</v>
       </c>
       <c r="R376" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="S376" s="1" t="n">
+      <c r="T376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -23467,10 +24598,13 @@
         <v>0.282</v>
       </c>
       <c r="R377" s="1" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="S377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="S377" s="1" t="n">
-        <v>0.282</v>
+      <c r="T377" s="1" t="n">
+        <v>0.2819</v>
       </c>
     </row>
     <row r="378">
@@ -23528,9 +24662,12 @@
         <v>0.01556</v>
       </c>
       <c r="R378" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="S378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="S378" s="1" t="n">
+      <c r="T378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -23589,9 +24726,12 @@
         <v>1.5302</v>
       </c>
       <c r="R379" s="1" t="n">
+        <v>1.5281</v>
+      </c>
+      <c r="S379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="S379" s="1" t="n">
+      <c r="T379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -23650,10 +24790,13 @@
         <v>6.887e-05</v>
       </c>
       <c r="R380" s="1" t="n">
+        <v>6.871e-05</v>
+      </c>
+      <c r="S380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="S380" s="1" t="n">
-        <v>6.887e-05</v>
+      <c r="T380" s="1" t="n">
+        <v>6.871e-05</v>
       </c>
     </row>
     <row r="381">
@@ -23711,10 +24854,13 @@
         <v>2.544</v>
       </c>
       <c r="R381" s="1" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="S381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="S381" s="1" t="n">
-        <v>2.544</v>
+      <c r="T381" s="1" t="n">
+        <v>2.536</v>
       </c>
     </row>
     <row r="382">
@@ -23772,10 +24918,13 @@
         <v>0.06680999999999999</v>
       </c>
       <c r="R382" s="1" t="n">
+        <v>0.06661</v>
+      </c>
+      <c r="S382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="S382" s="1" t="n">
-        <v>0.06680999999999999</v>
+      <c r="T382" s="1" t="n">
+        <v>0.06661</v>
       </c>
     </row>
     <row r="383">
@@ -23833,10 +24982,13 @@
         <v>0.01695</v>
       </c>
       <c r="R383" s="1" t="n">
+        <v>0.01683</v>
+      </c>
+      <c r="S383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="S383" s="1" t="n">
-        <v>0.01695</v>
+      <c r="T383" s="1" t="n">
+        <v>0.01683</v>
       </c>
     </row>
     <row r="384">
@@ -23894,9 +25046,12 @@
         <v>0.05155</v>
       </c>
       <c r="R384" s="1" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="S384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="S384" s="1" t="n">
+      <c r="T384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -23955,9 +25110,12 @@
         <v>7.559</v>
       </c>
       <c r="R385" s="1" t="n">
+        <v>7.566</v>
+      </c>
+      <c r="S385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="S385" s="1" t="n">
+      <c r="T385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -24016,10 +25174,13 @@
         <v>0.003273</v>
       </c>
       <c r="R386" s="1" t="n">
+        <v>0.003258</v>
+      </c>
+      <c r="S386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="S386" s="1" t="n">
-        <v>0.00327</v>
+      <c r="T386" s="1" t="n">
+        <v>0.003258</v>
       </c>
     </row>
     <row r="387">
@@ -24077,10 +25238,13 @@
         <v>0.0003797</v>
       </c>
       <c r="R387" s="1" t="n">
+        <v>0.0003793</v>
+      </c>
+      <c r="S387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="S387" s="1" t="n">
-        <v>0.0003797</v>
+      <c r="T387" s="1" t="n">
+        <v>0.0003793</v>
       </c>
     </row>
     <row r="388">
@@ -24138,9 +25302,12 @@
         <v>0.00942</v>
       </c>
       <c r="R388" s="1" t="n">
+        <v>0.009469999999999999</v>
+      </c>
+      <c r="S388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="S388" s="1" t="n">
+      <c r="T388" s="1" t="n">
         <v>0.00942</v>
       </c>
     </row>
@@ -24199,9 +25366,12 @@
         <v>0.2893</v>
       </c>
       <c r="R389" s="1" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="S389" s="1" t="n">
         <v>0.2904</v>
       </c>
-      <c r="S389" s="1" t="n">
+      <c r="T389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -24260,9 +25430,12 @@
         <v>0.0251</v>
       </c>
       <c r="R390" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="S390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="S390" s="1" t="n">
+      <c r="T390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -24321,9 +25494,12 @@
         <v>2.859</v>
       </c>
       <c r="R391" s="1" t="n">
+        <v>2.843</v>
+      </c>
+      <c r="S391" s="1" t="n">
         <v>2.859</v>
       </c>
-      <c r="S391" s="1" t="n">
+      <c r="T391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -24382,9 +25558,12 @@
         <v>0.01348</v>
       </c>
       <c r="R392" s="1" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="S392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="S392" s="1" t="n">
+      <c r="T392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -24443,9 +25622,12 @@
         <v>0.00236</v>
       </c>
       <c r="R393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="S393" s="1" t="n">
         <v>0.00237</v>
       </c>
-      <c r="S393" s="1" t="n">
+      <c r="T393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -24504,9 +25686,12 @@
         <v>0.05925</v>
       </c>
       <c r="R394" s="1" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="S394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="S394" s="1" t="n">
+      <c r="T394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -24565,9 +25750,12 @@
         <v>0.0402</v>
       </c>
       <c r="R395" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="S395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="S395" s="1" t="n">
+      <c r="T395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -24626,9 +25814,12 @@
         <v>0.09275</v>
       </c>
       <c r="R396" s="1" t="n">
-        <v>0.09275</v>
+        <v>0.09288</v>
       </c>
       <c r="S396" s="1" t="n">
+        <v>0.09288</v>
+      </c>
+      <c r="T396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -24687,10 +25878,13 @@
         <v>0.1515</v>
       </c>
       <c r="R397" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="S397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="S397" s="1" t="n">
-        <v>0.1515</v>
+      <c r="T397" s="1" t="n">
+        <v>0.1512</v>
       </c>
     </row>
     <row r="398">
@@ -24748,9 +25942,12 @@
         <v>0.929</v>
       </c>
       <c r="R398" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="S398" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="S398" s="1" t="n">
+      <c r="T398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -24809,10 +26006,13 @@
         <v>0.05233</v>
       </c>
       <c r="R399" s="1" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="S399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="S399" s="1" t="n">
-        <v>0.05215</v>
+      <c r="T399" s="1" t="n">
+        <v>0.05213</v>
       </c>
     </row>
     <row r="400">
@@ -24870,10 +26070,13 @@
         <v>2.508</v>
       </c>
       <c r="R400" s="1" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="S400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="S400" s="1" t="n">
-        <v>2.508</v>
+      <c r="T400" s="1" t="n">
+        <v>2.504</v>
       </c>
     </row>
     <row r="401">
@@ -24931,9 +26134,12 @@
         <v>0.01772</v>
       </c>
       <c r="R401" s="1" t="n">
+        <v>0.01774</v>
+      </c>
+      <c r="S401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="S401" s="1" t="n">
+      <c r="T401" s="1" t="n">
         <v>0.01772</v>
       </c>
     </row>
@@ -24992,9 +26198,12 @@
         <v>0.07979</v>
       </c>
       <c r="R402" s="1" t="n">
+        <v>0.07982</v>
+      </c>
+      <c r="S402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="S402" s="1" t="n">
+      <c r="T402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -25053,10 +26262,13 @@
         <v>1.2474</v>
       </c>
       <c r="R403" s="1" t="n">
+        <v>1.2451</v>
+      </c>
+      <c r="S403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="S403" s="1" t="n">
-        <v>1.2455</v>
+      <c r="T403" s="1" t="n">
+        <v>1.2451</v>
       </c>
     </row>
     <row r="404">
@@ -25114,10 +26326,13 @@
         <v>0.0071</v>
       </c>
       <c r="R404" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="S404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="S404" s="1" t="n">
-        <v>0.0071</v>
+      <c r="T404" s="1" t="n">
+        <v>0.00708</v>
       </c>
     </row>
     <row r="405">
@@ -25175,9 +26390,12 @@
         <v>0.5019</v>
       </c>
       <c r="R405" s="1" t="n">
+        <v>0.5023</v>
+      </c>
+      <c r="S405" s="1" t="n">
         <v>0.5041</v>
       </c>
-      <c r="S405" s="1" t="n">
+      <c r="T405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -25236,9 +26454,12 @@
         <v>0.01142</v>
       </c>
       <c r="R406" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="S406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="S406" s="1" t="n">
+      <c r="T406" s="1" t="n">
         <v>0.01142</v>
       </c>
     </row>
@@ -25297,10 +26518,13 @@
         <v>0.04592</v>
       </c>
       <c r="R407" s="1" t="n">
+        <v>0.04584</v>
+      </c>
+      <c r="S407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="S407" s="1" t="n">
-        <v>0.04592</v>
+      <c r="T407" s="1" t="n">
+        <v>0.04584</v>
       </c>
     </row>
     <row r="408">
@@ -25358,10 +26582,13 @@
         <v>0.03936</v>
       </c>
       <c r="R408" s="1" t="n">
+        <v>0.03922</v>
+      </c>
+      <c r="S408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="S408" s="1" t="n">
-        <v>0.03927</v>
+      <c r="T408" s="1" t="n">
+        <v>0.03922</v>
       </c>
     </row>
     <row r="409">
@@ -25419,10 +26646,13 @@
         <v>0.05216</v>
       </c>
       <c r="R409" s="1" t="n">
+        <v>0.05211</v>
+      </c>
+      <c r="S409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="S409" s="1" t="n">
-        <v>0.05216</v>
+      <c r="T409" s="1" t="n">
+        <v>0.05211</v>
       </c>
     </row>
     <row r="410">
@@ -25480,9 +26710,12 @@
         <v>0.01229</v>
       </c>
       <c r="R410" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="S410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="S410" s="1" t="n">
+      <c r="T410" s="1" t="n">
         <v>0.01227</v>
       </c>
     </row>
@@ -25541,10 +26774,13 @@
         <v>0.06342</v>
       </c>
       <c r="R411" s="1" t="n">
+        <v>0.06333999999999999</v>
+      </c>
+      <c r="S411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="S411" s="1" t="n">
-        <v>0.06342</v>
+      <c r="T411" s="1" t="n">
+        <v>0.06333999999999999</v>
       </c>
     </row>
     <row r="412">
@@ -25602,10 +26838,13 @@
         <v>0.04136</v>
       </c>
       <c r="R412" s="1" t="n">
+        <v>0.04114</v>
+      </c>
+      <c r="S412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="S412" s="1" t="n">
-        <v>0.04126</v>
+      <c r="T412" s="1" t="n">
+        <v>0.04114</v>
       </c>
     </row>
     <row r="413">
@@ -25663,10 +26902,13 @@
         <v>1.114</v>
       </c>
       <c r="R413" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="S413" s="1" t="n">
-        <v>1.112</v>
+      <c r="T413" s="1" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="414">
@@ -25724,10 +26966,13 @@
         <v>0.2617</v>
       </c>
       <c r="R414" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="S414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="S414" s="1" t="n">
-        <v>0.2617</v>
+      <c r="T414" s="1" t="n">
+        <v>0.2614</v>
       </c>
     </row>
     <row r="415">
@@ -25785,9 +27030,12 @@
         <v>0.001219</v>
       </c>
       <c r="R415" s="1" t="n">
+        <v>0.001226</v>
+      </c>
+      <c r="S415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="S415" s="1" t="n">
+      <c r="T415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -25846,9 +27094,12 @@
         <v>0.03195</v>
       </c>
       <c r="R416" s="1" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="S416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="S416" s="1" t="n">
+      <c r="T416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -25907,10 +27158,13 @@
         <v>0.0146</v>
       </c>
       <c r="R417" s="1" t="n">
+        <v>0.01452</v>
+      </c>
+      <c r="S417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="S417" s="1" t="n">
-        <v>0.01454</v>
+      <c r="T417" s="1" t="n">
+        <v>0.01452</v>
       </c>
     </row>
     <row r="418">
@@ -25968,9 +27222,12 @@
         <v>0.1478</v>
       </c>
       <c r="R418" s="1" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="S418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="S418" s="1" t="n">
+      <c r="T418" s="1" t="n">
         <v>0.1478</v>
       </c>
     </row>
@@ -26029,9 +27286,12 @@
         <v>0.04904</v>
       </c>
       <c r="R419" s="1" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="S419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="S419" s="1" t="n">
+      <c r="T419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -26090,9 +27350,12 @@
         <v>66.52</v>
       </c>
       <c r="R420" s="1" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="S420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="S420" s="1" t="n">
+      <c r="T420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -26151,9 +27414,12 @@
         <v>0.874</v>
       </c>
       <c r="R421" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="S421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="S421" s="1" t="n">
+      <c r="T421" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -26212,9 +27478,12 @@
         <v>0.012508</v>
       </c>
       <c r="R422" s="1" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="S422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="S422" s="1" t="n">
+      <c r="T422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -26273,10 +27542,13 @@
         <v>0.01596</v>
       </c>
       <c r="R423" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="S423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="S423" s="1" t="n">
-        <v>0.01594</v>
+      <c r="T423" s="1" t="n">
+        <v>0.01592</v>
       </c>
     </row>
     <row r="424">
@@ -26334,9 +27606,12 @@
         <v>0.27364</v>
       </c>
       <c r="R424" s="1" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="S424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="S424" s="1" t="n">
+      <c r="T424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -26395,9 +27670,12 @@
         <v>0.5997</v>
       </c>
       <c r="R425" s="1" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="S425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="S425" s="1" t="n">
+      <c r="T425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -26456,10 +27734,13 @@
         <v>0.0055</v>
       </c>
       <c r="R426" s="1" t="n">
+        <v>0.005493</v>
+      </c>
+      <c r="S426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="S426" s="1" t="n">
-        <v>0.0055</v>
+      <c r="T426" s="1" t="n">
+        <v>0.005493</v>
       </c>
     </row>
     <row r="427">
@@ -26517,9 +27798,12 @@
         <v>0.04943</v>
       </c>
       <c r="R427" s="1" t="n">
-        <v>0.04962</v>
+        <v>0.04978</v>
       </c>
       <c r="S427" s="1" t="n">
+        <v>0.04978</v>
+      </c>
+      <c r="T427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -26578,10 +27862,13 @@
         <v>0.1256</v>
       </c>
       <c r="R428" s="1" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="S428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="S428" s="1" t="n">
-        <v>0.1254</v>
+      <c r="T428" s="1" t="n">
+        <v>0.1249</v>
       </c>
     </row>
     <row r="429">
@@ -26639,9 +27926,12 @@
         <v>0.003196</v>
       </c>
       <c r="R429" s="1" t="n">
+        <v>0.003194</v>
+      </c>
+      <c r="S429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="S429" s="1" t="n">
+      <c r="T429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -26700,10 +27990,13 @@
         <v>0.03637</v>
       </c>
       <c r="R430" s="1" t="n">
+        <v>0.03636</v>
+      </c>
+      <c r="S430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="S430" s="1" t="n">
-        <v>0.03637</v>
+      <c r="T430" s="1" t="n">
+        <v>0.03636</v>
       </c>
     </row>
     <row r="431">
@@ -26761,10 +28054,13 @@
         <v>0.3935</v>
       </c>
       <c r="R431" s="1" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="S431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="S431" s="1" t="n">
-        <v>0.3935</v>
+      <c r="T431" s="1" t="n">
+        <v>0.3918</v>
       </c>
     </row>
     <row r="432">
@@ -26822,10 +28118,13 @@
         <v>0.004478</v>
       </c>
       <c r="R432" s="1" t="n">
+        <v>0.004471</v>
+      </c>
+      <c r="S432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="S432" s="1" t="n">
-        <v>0.004478</v>
+      <c r="T432" s="1" t="n">
+        <v>0.004471</v>
       </c>
     </row>
     <row r="433">
@@ -26883,10 +28182,13 @@
         <v>0.0979</v>
       </c>
       <c r="R433" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="S433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="S433" s="1" t="n">
-        <v>0.09760000000000001</v>
+      <c r="T433" s="1" t="n">
+        <v>0.0973</v>
       </c>
     </row>
     <row r="434">
@@ -26944,10 +28246,13 @@
         <v>0.01236</v>
       </c>
       <c r="R434" s="1" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="S434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="S434" s="1" t="n">
-        <v>0.01236</v>
+      <c r="T434" s="1" t="n">
+        <v>0.01234</v>
       </c>
     </row>
     <row r="435">
@@ -27005,9 +28310,12 @@
         <v>1.98</v>
       </c>
       <c r="R435" s="1" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="S435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="S435" s="1" t="n">
+      <c r="T435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -27066,9 +28374,12 @@
         <v>0.001774</v>
       </c>
       <c r="R436" s="1" t="n">
+        <v>0.001775</v>
+      </c>
+      <c r="S436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="S436" s="1" t="n">
+      <c r="T436" s="1" t="n">
         <v>0.001774</v>
       </c>
     </row>
@@ -27127,9 +28438,12 @@
         <v>0.4421</v>
       </c>
       <c r="R437" s="1" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="S437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="S437" s="1" t="n">
+      <c r="T437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -27188,10 +28502,13 @@
         <v>0.00534</v>
       </c>
       <c r="R438" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="S438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="S438" s="1" t="n">
-        <v>0.00534</v>
+      <c r="T438" s="1" t="n">
+        <v>0.00533</v>
       </c>
     </row>
     <row r="439">
@@ -27249,10 +28566,13 @@
         <v>0.1034</v>
       </c>
       <c r="R439" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="S439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="S439" s="1" t="n">
-        <v>0.1033</v>
+      <c r="T439" s="1" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="440">
@@ -27310,10 +28630,13 @@
         <v>0.03404</v>
       </c>
       <c r="R440" s="1" t="n">
+        <v>0.03387</v>
+      </c>
+      <c r="S440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="S440" s="1" t="n">
-        <v>0.03399</v>
+      <c r="T440" s="1" t="n">
+        <v>0.03387</v>
       </c>
     </row>
     <row r="441">
@@ -27371,10 +28694,13 @@
         <v>0.08193</v>
       </c>
       <c r="R441" s="1" t="n">
+        <v>0.08184</v>
+      </c>
+      <c r="S441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="S441" s="1" t="n">
-        <v>0.08193</v>
+      <c r="T441" s="1" t="n">
+        <v>0.08184</v>
       </c>
     </row>
     <row r="442">
@@ -27432,9 +28758,12 @@
         <v>1.301</v>
       </c>
       <c r="R442" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="S442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="S442" s="1" t="n">
+      <c r="T442" s="1" t="n">
         <v>1.301</v>
       </c>
     </row>
@@ -27493,10 +28822,13 @@
         <v>0.07521</v>
       </c>
       <c r="R443" s="1" t="n">
+        <v>0.07507</v>
+      </c>
+      <c r="S443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="S443" s="1" t="n">
-        <v>0.07521</v>
+      <c r="T443" s="1" t="n">
+        <v>0.07507</v>
       </c>
     </row>
     <row r="444">
@@ -27554,10 +28886,13 @@
         <v>0.07641000000000001</v>
       </c>
       <c r="R444" s="1" t="n">
+        <v>0.07628</v>
+      </c>
+      <c r="S444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="S444" s="1" t="n">
-        <v>0.07638</v>
+      <c r="T444" s="1" t="n">
+        <v>0.07628</v>
       </c>
     </row>
     <row r="445">
@@ -27615,10 +28950,13 @@
         <v>0.0433</v>
       </c>
       <c r="R445" s="1" t="n">
+        <v>0.04316</v>
+      </c>
+      <c r="S445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="S445" s="1" t="n">
-        <v>0.0433</v>
+      <c r="T445" s="1" t="n">
+        <v>0.04316</v>
       </c>
     </row>
     <row r="446">
@@ -27676,9 +29014,12 @@
         <v>0.02137</v>
       </c>
       <c r="R446" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="S446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="S446" s="1" t="n">
+      <c r="T446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -27737,9 +29078,12 @@
         <v>0.28</v>
       </c>
       <c r="R447" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="S447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="S447" s="1" t="n">
+      <c r="T447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -27798,9 +29142,12 @@
         <v>0.03069</v>
       </c>
       <c r="R448" s="1" t="n">
+        <v>0.03073</v>
+      </c>
+      <c r="S448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="S448" s="1" t="n">
+      <c r="T448" s="1" t="n">
         <v>0.03069</v>
       </c>
     </row>
@@ -27859,9 +29206,12 @@
         <v>0.00645</v>
       </c>
       <c r="R449" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="S449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="S449" s="1" t="n">
+      <c r="T449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -27920,9 +29270,12 @@
         <v>0.023002</v>
       </c>
       <c r="R450" s="1" t="n">
-        <v>0.023086</v>
+        <v>0.02312</v>
       </c>
       <c r="S450" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="T450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -27981,9 +29334,12 @@
         <v>0.04247</v>
       </c>
       <c r="R451" s="1" t="n">
+        <v>0.04226</v>
+      </c>
+      <c r="S451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="S451" s="1" t="n">
+      <c r="T451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -28042,9 +29398,12 @@
         <v>0.07226</v>
       </c>
       <c r="R452" s="1" t="n">
+        <v>0.07217999999999999</v>
+      </c>
+      <c r="S452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="S452" s="1" t="n">
+      <c r="T452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -28103,9 +29462,12 @@
         <v>0.0005907</v>
       </c>
       <c r="R453" s="1" t="n">
+        <v>0.0005922</v>
+      </c>
+      <c r="S453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="S453" s="1" t="n">
+      <c r="T453" s="1" t="n">
         <v>0.0005904</v>
       </c>
     </row>
@@ -28164,9 +29526,12 @@
         <v>0.304</v>
       </c>
       <c r="R454" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="S454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="S454" s="1" t="n">
+      <c r="T454" s="1" t="n">
         <v>0.304</v>
       </c>
     </row>
@@ -28225,9 +29590,12 @@
         <v>0.004268</v>
       </c>
       <c r="R455" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+      <c r="S455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="S455" s="1" t="n">
+      <c r="T455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -28286,10 +29654,13 @@
         <v>0.1821</v>
       </c>
       <c r="R456" s="1" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="S456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="S456" s="1" t="n">
-        <v>0.1821</v>
+      <c r="T456" s="1" t="n">
+        <v>0.1819</v>
       </c>
     </row>
     <row r="457">
@@ -28347,10 +29718,13 @@
         <v>0.0427</v>
       </c>
       <c r="R457" s="1" t="n">
+        <v>0.04254</v>
+      </c>
+      <c r="S457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="S457" s="1" t="n">
-        <v>0.04267</v>
+      <c r="T457" s="1" t="n">
+        <v>0.04254</v>
       </c>
     </row>
     <row r="458">
@@ -28408,10 +29782,13 @@
         <v>0.1457</v>
       </c>
       <c r="R458" s="1" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="S458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="S458" s="1" t="n">
-        <v>0.1457</v>
+      <c r="T458" s="1" t="n">
+        <v>0.1452</v>
       </c>
     </row>
     <row r="459">
@@ -28469,9 +29846,12 @@
         <v>0.008621999999999999</v>
       </c>
       <c r="R459" s="1" t="n">
+        <v>0.008574</v>
+      </c>
+      <c r="S459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="S459" s="1" t="n">
+      <c r="T459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -28530,10 +29910,13 @@
         <v>0.007394</v>
       </c>
       <c r="R460" s="1" t="n">
+        <v>0.007353</v>
+      </c>
+      <c r="S460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="S460" s="1" t="n">
-        <v>0.007357</v>
+      <c r="T460" s="1" t="n">
+        <v>0.007353</v>
       </c>
     </row>
     <row r="461">
@@ -28591,9 +29974,12 @@
         <v>0.0001734</v>
       </c>
       <c r="R461" s="1" t="n">
+        <v>0.0001729</v>
+      </c>
+      <c r="S461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="S461" s="1" t="n">
+      <c r="T461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -28652,9 +30038,12 @@
         <v>0.02374</v>
       </c>
       <c r="R462" s="1" t="n">
-        <v>0.02374</v>
+        <v>0.02585</v>
       </c>
       <c r="S462" s="1" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="T462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -28713,10 +30102,13 @@
         <v>0.03692</v>
       </c>
       <c r="R463" s="1" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="S463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="S463" s="1" t="n">
-        <v>0.03685</v>
+      <c r="T463" s="1" t="n">
+        <v>0.03667</v>
       </c>
     </row>
     <row r="464">
@@ -28774,10 +30166,13 @@
         <v>0.3011</v>
       </c>
       <c r="R464" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="S464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="S464" s="1" t="n">
-        <v>0.3011</v>
+      <c r="T464" s="1" t="n">
+        <v>0.3003</v>
       </c>
     </row>
     <row r="465">
@@ -28835,9 +30230,12 @@
         <v>0.03898</v>
       </c>
       <c r="R465" s="1" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="S465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="S465" s="1" t="n">
+      <c r="T465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -28896,9 +30294,12 @@
         <v>2.661</v>
       </c>
       <c r="R466" s="1" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="S466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="S466" s="1" t="n">
+      <c r="T466" s="1" t="n">
         <v>2.661</v>
       </c>
     </row>
@@ -28957,9 +30358,12 @@
         <v>0.03417</v>
       </c>
       <c r="R467" s="1" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="S467" s="1" t="n">
         <v>0.03438</v>
       </c>
-      <c r="S467" s="1" t="n">
+      <c r="T467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -29018,9 +30422,12 @@
         <v>0.1762</v>
       </c>
       <c r="R468" s="1" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="S468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="S468" s="1" t="n">
+      <c r="T468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -29079,9 +30486,12 @@
         <v>0.0961</v>
       </c>
       <c r="R469" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="S469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="S469" s="1" t="n">
+      <c r="T469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -29140,9 +30550,12 @@
         <v>0.06696000000000001</v>
       </c>
       <c r="R470" s="1" t="n">
+        <v>0.06722</v>
+      </c>
+      <c r="S470" s="1" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="S470" s="1" t="n">
+      <c r="T470" s="1" t="n">
         <v>0.06696000000000001</v>
       </c>
     </row>
@@ -29201,10 +30614,13 @@
         <v>0.0398</v>
       </c>
       <c r="R471" s="1" t="n">
+        <v>0.03972</v>
+      </c>
+      <c r="S471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="S471" s="1" t="n">
-        <v>0.03978</v>
+      <c r="T471" s="1" t="n">
+        <v>0.03972</v>
       </c>
     </row>
     <row r="472">
@@ -29262,10 +30678,13 @@
         <v>0.2466</v>
       </c>
       <c r="R472" s="1" t="n">
+        <v>0.2464</v>
+      </c>
+      <c r="S472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="S472" s="1" t="n">
-        <v>0.2466</v>
+      <c r="T472" s="1" t="n">
+        <v>0.2464</v>
       </c>
     </row>
     <row r="473">
@@ -29323,10 +30742,13 @@
         <v>0.016316</v>
       </c>
       <c r="R473" s="1" t="n">
+        <v>0.016269</v>
+      </c>
+      <c r="S473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="S473" s="1" t="n">
-        <v>0.016316</v>
+      <c r="T473" s="1" t="n">
+        <v>0.016269</v>
       </c>
     </row>
     <row r="474">
@@ -29384,10 +30806,13 @@
         <v>0.1152</v>
       </c>
       <c r="R474" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="S474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="S474" s="1" t="n">
-        <v>0.1148</v>
+      <c r="T474" s="1" t="n">
+        <v>0.1147</v>
       </c>
     </row>
     <row r="475">
@@ -29445,10 +30870,13 @@
         <v>0.0427</v>
       </c>
       <c r="R475" s="1" t="n">
+        <v>0.04258</v>
+      </c>
+      <c r="S475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="S475" s="1" t="n">
-        <v>0.04264</v>
+      <c r="T475" s="1" t="n">
+        <v>0.04258</v>
       </c>
     </row>
     <row r="476">
@@ -29506,10 +30934,13 @@
         <v>0.2069</v>
       </c>
       <c r="R476" s="1" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="S476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="S476" s="1" t="n">
-        <v>0.2066</v>
+      <c r="T476" s="1" t="n">
+        <v>0.2065</v>
       </c>
     </row>
     <row r="477">
@@ -29567,10 +30998,13 @@
         <v>0.006776</v>
       </c>
       <c r="R477" s="1" t="n">
+        <v>0.006763</v>
+      </c>
+      <c r="S477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="S477" s="1" t="n">
-        <v>0.006776</v>
+      <c r="T477" s="1" t="n">
+        <v>0.006763</v>
       </c>
     </row>
     <row r="478">
@@ -29628,9 +31062,12 @@
         <v>0.01776</v>
       </c>
       <c r="R478" s="1" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="S478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="S478" s="1" t="n">
+      <c r="T478" s="1" t="n">
         <v>0.01776</v>
       </c>
     </row>
@@ -29689,10 +31126,13 @@
         <v>0.04665</v>
       </c>
       <c r="R479" s="1" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="S479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="S479" s="1" t="n">
-        <v>0.04665</v>
+      <c r="T479" s="1" t="n">
+        <v>0.0465</v>
       </c>
     </row>
     <row r="480">
@@ -29750,9 +31190,12 @@
         <v>0.25972</v>
       </c>
       <c r="R480" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="S480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="S480" s="1" t="n">
+      <c r="T480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -29811,10 +31254,13 @@
         <v>0.01218</v>
       </c>
       <c r="R481" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="S481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="S481" s="1" t="n">
-        <v>0.01218</v>
+      <c r="T481" s="1" t="n">
+        <v>0.01216</v>
       </c>
     </row>
     <row r="482">
@@ -29872,9 +31318,12 @@
         <v>0.004079</v>
       </c>
       <c r="R482" s="1" t="n">
+        <v>0.004073</v>
+      </c>
+      <c r="S482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="S482" s="1" t="n">
+      <c r="T482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -29933,10 +31382,13 @@
         <v>0.1229</v>
       </c>
       <c r="R483" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="S483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="S483" s="1" t="n">
-        <v>0.1229</v>
+      <c r="T483" s="1" t="n">
+        <v>0.1226</v>
       </c>
     </row>
     <row r="484">
@@ -29994,9 +31446,12 @@
         <v>0.02216</v>
       </c>
       <c r="R484" s="1" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="S484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="S484" s="1" t="n">
+      <c r="T484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -30055,9 +31510,12 @@
         <v>0.04515</v>
       </c>
       <c r="R485" s="1" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="S485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="S485" s="1" t="n">
+      <c r="T485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -30116,10 +31574,13 @@
         <v>0.1731</v>
       </c>
       <c r="R486" s="1" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="S486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="S486" s="1" t="n">
-        <v>0.1731</v>
+      <c r="T486" s="1" t="n">
+        <v>0.1727</v>
       </c>
     </row>
     <row r="487">
@@ -30177,9 +31638,12 @@
         <v>0.2726</v>
       </c>
       <c r="R487" s="1" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="S487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="S487" s="1" t="n">
+      <c r="T487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -30238,10 +31702,13 @@
         <v>0.04599</v>
       </c>
       <c r="R488" s="1" t="n">
+        <v>0.04581</v>
+      </c>
+      <c r="S488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="S488" s="1" t="n">
-        <v>0.04599</v>
+      <c r="T488" s="1" t="n">
+        <v>0.04581</v>
       </c>
     </row>
     <row r="489">
@@ -30299,10 +31766,13 @@
         <v>0.0002145</v>
       </c>
       <c r="R489" s="1" t="n">
+        <v>0.0002139</v>
+      </c>
+      <c r="S489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="S489" s="1" t="n">
-        <v>0.0002144</v>
+      <c r="T489" s="1" t="n">
+        <v>0.0002139</v>
       </c>
     </row>
     <row r="490">
@@ -30360,9 +31830,12 @@
         <v>1.777</v>
       </c>
       <c r="R490" s="1" t="n">
-        <v>1.78</v>
+        <v>1.782</v>
       </c>
       <c r="S490" s="1" t="n">
+        <v>1.782</v>
+      </c>
+      <c r="T490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -30421,9 +31894,12 @@
         <v>16.021</v>
       </c>
       <c r="R491" s="1" t="n">
+        <v>16.002</v>
+      </c>
+      <c r="S491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="S491" s="1" t="n">
+      <c r="T491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -30482,10 +31958,13 @@
         <v>0.06655999999999999</v>
       </c>
       <c r="R492" s="1" t="n">
+        <v>0.06645</v>
+      </c>
+      <c r="S492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="S492" s="1" t="n">
-        <v>0.06648</v>
+      <c r="T492" s="1" t="n">
+        <v>0.06645</v>
       </c>
     </row>
     <row r="493">
@@ -30543,10 +32022,13 @@
         <v>0.06734</v>
       </c>
       <c r="R493" s="1" t="n">
+        <v>0.06709</v>
+      </c>
+      <c r="S493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="S493" s="1" t="n">
-        <v>0.06728000000000001</v>
+      <c r="T493" s="1" t="n">
+        <v>0.06709</v>
       </c>
     </row>
     <row r="494">
@@ -30604,9 +32086,12 @@
         <v>0.009443</v>
       </c>
       <c r="R494" s="1" t="n">
+        <v>0.009389</v>
+      </c>
+      <c r="S494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="S494" s="1" t="n">
+      <c r="T494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -30665,9 +32150,12 @@
         <v>0.0058</v>
       </c>
       <c r="R495" s="1" t="n">
+        <v>0.005814</v>
+      </c>
+      <c r="S495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="S495" s="1" t="n">
+      <c r="T495" s="1" t="n">
         <v>0.0058</v>
       </c>
     </row>
@@ -30726,10 +32214,13 @@
         <v>0.00987</v>
       </c>
       <c r="R496" s="1" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="S496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="S496" s="1" t="n">
-        <v>0.009849999999999999</v>
+      <c r="T496" s="1" t="n">
+        <v>0.00984</v>
       </c>
     </row>
     <row r="497">
@@ -30787,9 +32278,12 @@
         <v>0.04604</v>
       </c>
       <c r="R497" s="1" t="n">
-        <v>0.04613</v>
+        <v>0.04638</v>
       </c>
       <c r="S497" s="1" t="n">
+        <v>0.04638</v>
+      </c>
+      <c r="T497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -30848,10 +32342,13 @@
         <v>0.006353</v>
       </c>
       <c r="R498" s="1" t="n">
+        <v>0.006344</v>
+      </c>
+      <c r="S498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="S498" s="1" t="n">
-        <v>0.006353</v>
+      <c r="T498" s="1" t="n">
+        <v>0.006344</v>
       </c>
     </row>
     <row r="499">
@@ -30909,10 +32406,13 @@
         <v>0.01035</v>
       </c>
       <c r="R499" s="1" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="S499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="S499" s="1" t="n">
-        <v>0.01035</v>
+      <c r="T499" s="1" t="n">
+        <v>0.01032</v>
       </c>
     </row>
     <row r="500">
@@ -30970,9 +32470,12 @@
         <v>0.5067</v>
       </c>
       <c r="R500" s="1" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="S500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="S500" s="1" t="n">
+      <c r="T500" s="1" t="n">
         <v>0.5067</v>
       </c>
     </row>
@@ -31031,9 +32534,12 @@
         <v>0.03206</v>
       </c>
       <c r="R501" s="1" t="n">
-        <v>0.03212</v>
+        <v>0.03213</v>
       </c>
       <c r="S501" s="1" t="n">
+        <v>0.03213</v>
+      </c>
+      <c r="T501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -31092,9 +32598,12 @@
         <v>0.4404</v>
       </c>
       <c r="R502" s="1" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="S502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="S502" s="1" t="n">
+      <c r="T502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -31153,9 +32662,12 @@
         <v>0.999341</v>
       </c>
       <c r="R503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="S503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="S503" s="1" t="n">
+      <c r="T503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -31214,9 +32726,12 @@
         <v>0.03517</v>
       </c>
       <c r="R504" s="1" t="n">
+        <v>0.03523</v>
+      </c>
+      <c r="S504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="S504" s="1" t="n">
+      <c r="T504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -31275,9 +32790,12 @@
         <v>0.004922</v>
       </c>
       <c r="R505" s="1" t="n">
+        <v>0.004918</v>
+      </c>
+      <c r="S505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="S505" s="1" t="n">
+      <c r="T505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -31336,10 +32854,13 @@
         <v>0.01386</v>
       </c>
       <c r="R506" s="1" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="S506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="S506" s="1" t="n">
-        <v>0.01386</v>
+      <c r="T506" s="1" t="n">
+        <v>0.01381</v>
       </c>
     </row>
     <row r="507">
@@ -31397,9 +32918,12 @@
         <v>0.003474</v>
       </c>
       <c r="R507" s="1" t="n">
+        <v>0.003469</v>
+      </c>
+      <c r="S507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="S507" s="1" t="n">
+      <c r="T507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -31458,10 +32982,13 @@
         <v>1.413</v>
       </c>
       <c r="R508" s="1" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="S508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="S508" s="1" t="n">
-        <v>1.413</v>
+      <c r="T508" s="1" t="n">
+        <v>1.411</v>
       </c>
     </row>
     <row r="509">
@@ -31519,10 +33046,13 @@
         <v>0.005063</v>
       </c>
       <c r="R509" s="1" t="n">
+        <v>0.005056</v>
+      </c>
+      <c r="S509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="S509" s="1" t="n">
-        <v>0.005063</v>
+      <c r="T509" s="1" t="n">
+        <v>0.005056</v>
       </c>
     </row>
     <row r="510">
@@ -31580,10 +33110,13 @@
         <v>0.01565</v>
       </c>
       <c r="R510" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="S510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="S510" s="1" t="n">
-        <v>0.01565</v>
+      <c r="T510" s="1" t="n">
+        <v>0.0156</v>
       </c>
     </row>
     <row r="511">
@@ -31641,10 +33174,13 @@
         <v>0.08225</v>
       </c>
       <c r="R511" s="1" t="n">
+        <v>0.08123</v>
+      </c>
+      <c r="S511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="S511" s="1" t="n">
-        <v>0.08212999999999999</v>
+      <c r="T511" s="1" t="n">
+        <v>0.08123</v>
       </c>
     </row>
     <row r="512">
@@ -31702,10 +33238,13 @@
         <v>0.00708</v>
       </c>
       <c r="R512" s="1" t="n">
+        <v>0.007071</v>
+      </c>
+      <c r="S512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="S512" s="1" t="n">
-        <v>0.00708</v>
+      <c r="T512" s="1" t="n">
+        <v>0.007071</v>
       </c>
     </row>
     <row r="513">
@@ -31763,9 +33302,12 @@
         <v>0.01483</v>
       </c>
       <c r="R513" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="S513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="S513" s="1" t="n">
+      <c r="T513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -31824,9 +33366,12 @@
         <v>0.04734</v>
       </c>
       <c r="R514" s="1" t="n">
+        <v>0.04727</v>
+      </c>
+      <c r="S514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="S514" s="1" t="n">
+      <c r="T514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -31885,10 +33430,13 @@
         <v>0.01804</v>
       </c>
       <c r="R515" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="S515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="S515" s="1" t="n">
-        <v>0.01804</v>
+      <c r="T515" s="1" t="n">
+        <v>0.01797</v>
       </c>
     </row>
     <row r="516">
@@ -31946,10 +33494,13 @@
         <v>0.0005791</v>
       </c>
       <c r="R516" s="1" t="n">
+        <v>0.000578</v>
+      </c>
+      <c r="S516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="S516" s="1" t="n">
-        <v>0.0005782</v>
+      <c r="T516" s="1" t="n">
+        <v>0.000578</v>
       </c>
     </row>
     <row r="517">
@@ -32007,9 +33558,12 @@
         <v>0.07836</v>
       </c>
       <c r="R517" s="1" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="S517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="S517" s="1" t="n">
+      <c r="T517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -32068,10 +33622,13 @@
         <v>0.006369</v>
       </c>
       <c r="R518" s="1" t="n">
+        <v>0.006356</v>
+      </c>
+      <c r="S518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="S518" s="1" t="n">
-        <v>0.006369</v>
+      <c r="T518" s="1" t="n">
+        <v>0.006356</v>
       </c>
     </row>
     <row r="519">
@@ -32129,10 +33686,13 @@
         <v>0.05767</v>
       </c>
       <c r="R519" s="1" t="n">
+        <v>0.05759</v>
+      </c>
+      <c r="S519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="S519" s="1" t="n">
-        <v>0.05765</v>
+      <c r="T519" s="1" t="n">
+        <v>0.05759</v>
       </c>
     </row>
     <row r="520">
@@ -32190,10 +33750,13 @@
         <v>0.10413</v>
       </c>
       <c r="R520" s="1" t="n">
+        <v>0.10366</v>
+      </c>
+      <c r="S520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="S520" s="1" t="n">
-        <v>0.10413</v>
+      <c r="T520" s="1" t="n">
+        <v>0.10366</v>
       </c>
     </row>
     <row r="521">
@@ -32251,9 +33814,12 @@
         <v>0.01786</v>
       </c>
       <c r="R521" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="S521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="S521" s="1" t="n">
+      <c r="T521" s="1" t="n">
         <v>0.01786</v>
       </c>
     </row>
@@ -32312,10 +33878,13 @@
         <v>0.01618</v>
       </c>
       <c r="R522" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="S522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="S522" s="1" t="n">
-        <v>0.01618</v>
+      <c r="T522" s="1" t="n">
+        <v>0.01602</v>
       </c>
     </row>
     <row r="523">
@@ -32373,9 +33942,12 @@
         <v>0.01079</v>
       </c>
       <c r="R523" s="1" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="S523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="S523" s="1" t="n">
+      <c r="T523" s="1" t="n">
         <v>0.01079</v>
       </c>
     </row>
@@ -32434,9 +34006,12 @@
         <v>0.007133</v>
       </c>
       <c r="R524" s="1" t="n">
-        <v>0.007244</v>
+        <v>0.007318</v>
       </c>
       <c r="S524" s="1" t="n">
+        <v>0.007318</v>
+      </c>
+      <c r="T524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -32495,10 +34070,13 @@
         <v>0.005827</v>
       </c>
       <c r="R525" s="1" t="n">
+        <v>0.005816</v>
+      </c>
+      <c r="S525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="S525" s="1" t="n">
-        <v>0.005827</v>
+      <c r="T525" s="1" t="n">
+        <v>0.005816</v>
       </c>
     </row>
     <row r="526">
@@ -32556,9 +34134,12 @@
         <v>0.001438</v>
       </c>
       <c r="R526" s="1" t="n">
+        <v>0.001448</v>
+      </c>
+      <c r="S526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="S526" s="1" t="n">
+      <c r="T526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -32617,9 +34198,12 @@
         <v>0.373</v>
       </c>
       <c r="R527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="S527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="S527" s="1" t="n">
+      <c r="T527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -32678,9 +34262,12 @@
         <v>0.005247</v>
       </c>
       <c r="R528" s="1" t="n">
+        <v>0.005237</v>
+      </c>
+      <c r="S528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="S528" s="1" t="n">
+      <c r="T528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -32739,9 +34326,12 @@
         <v>2.951</v>
       </c>
       <c r="R529" s="1" t="n">
+        <v>2.947</v>
+      </c>
+      <c r="S529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="S529" s="1" t="n">
+      <c r="T529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -32800,10 +34390,13 @@
         <v>0.1545</v>
       </c>
       <c r="R530" s="1" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="S530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="S530" s="1" t="n">
-        <v>0.1545</v>
+      <c r="T530" s="1" t="n">
+        <v>0.1529</v>
       </c>
     </row>
     <row r="531">
@@ -32861,9 +34454,12 @@
         <v>2579</v>
       </c>
       <c r="R531" s="1" t="n">
+        <v>2567</v>
+      </c>
+      <c r="S531" s="1" t="n">
         <v>2579</v>
       </c>
-      <c r="S531" s="1" t="n">
+      <c r="T531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -32922,10 +34518,13 @@
         <v>0.03903</v>
       </c>
       <c r="R532" s="1" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="S532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="S532" s="1" t="n">
-        <v>0.03903</v>
+      <c r="T532" s="1" t="n">
+        <v>0.03897</v>
       </c>
     </row>
     <row r="533">
@@ -32983,9 +34582,12 @@
         <v>0.02162</v>
       </c>
       <c r="R533" s="1" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="S533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="S533" s="1" t="n">
+      <c r="T533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -33044,9 +34646,12 @@
         <v>0.07325</v>
       </c>
       <c r="R534" s="1" t="n">
+        <v>0.07321</v>
+      </c>
+      <c r="S534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="S534" s="1" t="n">
+      <c r="T534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -33105,9 +34710,12 @@
         <v>0.007823</v>
       </c>
       <c r="R535" s="1" t="n">
+        <v>0.007852</v>
+      </c>
+      <c r="S535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="S535" s="1" t="n">
+      <c r="T535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -33166,10 +34774,13 @@
         <v>0.04995</v>
       </c>
       <c r="R536" s="1" t="n">
+        <v>0.04994</v>
+      </c>
+      <c r="S536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="S536" s="1" t="n">
-        <v>0.04995</v>
+      <c r="T536" s="1" t="n">
+        <v>0.04994</v>
       </c>
     </row>
     <row r="537">
@@ -33227,10 +34838,13 @@
         <v>0.004</v>
       </c>
       <c r="R537" s="1" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="S537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="S537" s="1" t="n">
-        <v>0.004</v>
+      <c r="T537" s="1" t="n">
+        <v>0.00397</v>
       </c>
     </row>
     <row r="538">
@@ -33288,10 +34902,13 @@
         <v>0.08284</v>
       </c>
       <c r="R538" s="1" t="n">
+        <v>0.08266999999999999</v>
+      </c>
+      <c r="S538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="S538" s="1" t="n">
-        <v>0.08284</v>
+      <c r="T538" s="1" t="n">
+        <v>0.08266999999999999</v>
       </c>
     </row>
     <row r="539">
@@ -33349,9 +34966,12 @@
         <v>0.02479</v>
       </c>
       <c r="R539" s="1" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="S539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="S539" s="1" t="n">
+      <c r="T539" s="1" t="n">
         <v>0.02479</v>
       </c>
     </row>
@@ -33410,9 +35030,12 @@
         <v>0.08432000000000001</v>
       </c>
       <c r="R540" s="1" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="S540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="S540" s="1" t="n">
+      <c r="T540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -33471,9 +35094,12 @@
         <v>0.01883</v>
       </c>
       <c r="R541" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="S541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="S541" s="1" t="n">
+      <c r="T541" s="1" t="n">
         <v>0.01882</v>
       </c>
     </row>
@@ -33532,9 +35158,12 @@
         <v>0.01679</v>
       </c>
       <c r="R542" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="S542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="S542" s="1" t="n">
+      <c r="T542" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -33593,9 +35222,12 @@
         <v>0.1044</v>
       </c>
       <c r="R543" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="S543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="S543" s="1" t="n">
+      <c r="T543" s="1" t="n">
         <v>0.1044</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T543"/>
+  <dimension ref="A1:U543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,9 @@
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,10 +535,15 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>price_04:30</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -601,9 +607,12 @@
         <v>70651.39999999999</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>70693.10000000001</v>
+        <v>70696.3</v>
       </c>
       <c r="T2" s="1" t="n">
+        <v>70696.3</v>
+      </c>
+      <c r="U2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -665,9 +674,12 @@
         <v>2076.93</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>2077.45</v>
+        <v>2078.18</v>
       </c>
       <c r="T3" s="1" t="n">
+        <v>2078.18</v>
+      </c>
+      <c r="U3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -729,9 +741,12 @@
         <v>86.84999999999999</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="U4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -793,9 +808,12 @@
         <v>3.995</v>
       </c>
       <c r="S5" s="1" t="n">
+        <v>4.001</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="U5" s="1" t="n">
         <v>3.991</v>
       </c>
     </row>
@@ -857,9 +875,12 @@
         <v>0.09462</v>
       </c>
       <c r="S6" s="1" t="n">
+        <v>0.09465999999999999</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="U6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -921,9 +942,12 @@
         <v>1.3883</v>
       </c>
       <c r="S7" s="1" t="n">
+        <v>1.3905</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="T7" s="1" t="n">
+      <c r="U7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -985,9 +1009,12 @@
         <v>21.772</v>
       </c>
       <c r="S8" s="1" t="n">
+        <v>21.906</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="T8" s="1" t="n">
+      <c r="U8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1049,9 +1076,12 @@
         <v>0.002019</v>
       </c>
       <c r="S9" s="1" t="n">
+        <v>0.001995</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="U9" s="1" t="n">
         <v>0.001972</v>
       </c>
     </row>
@@ -1113,9 +1143,12 @@
         <v>0.010026</v>
       </c>
       <c r="S10" s="1" t="n">
+        <v>0.009995</v>
+      </c>
+      <c r="T10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="T10" s="1" t="n">
+      <c r="U10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1177,10 +1210,13 @@
         <v>0.14059</v>
       </c>
       <c r="S11" s="1" t="n">
+        <v>0.13631</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="T11" s="1" t="n">
-        <v>0.13838</v>
+      <c r="U11" s="1" t="n">
+        <v>0.13631</v>
       </c>
     </row>
     <row r="12">
@@ -1241,9 +1277,12 @@
         <v>0.011225</v>
       </c>
       <c r="S12" s="1" t="n">
+        <v>0.011229</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="U12" s="1" t="n">
         <v>0.011225</v>
       </c>
     </row>
@@ -1305,9 +1344,12 @@
         <v>37.947</v>
       </c>
       <c r="S13" s="1" t="n">
+        <v>37.907</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="T13" s="1" t="n">
+      <c r="U13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1369,9 +1411,12 @@
         <v>653.34</v>
       </c>
       <c r="S14" s="1" t="n">
+        <v>653.27</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="T14" s="1" t="n">
+      <c r="U14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1433,9 +1478,12 @@
         <v>209.95</v>
       </c>
       <c r="S15" s="1" t="n">
+        <v>209.77</v>
+      </c>
+      <c r="T15" s="1" t="n">
         <v>210.26</v>
       </c>
-      <c r="T15" s="1" t="n">
+      <c r="U15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1497,9 +1545,12 @@
         <v>0.0033084</v>
       </c>
       <c r="S16" s="1" t="n">
+        <v>0.0033105</v>
+      </c>
+      <c r="T16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="T16" s="1" t="n">
+      <c r="U16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1561,9 +1612,12 @@
         <v>238.12</v>
       </c>
       <c r="S17" s="1" t="n">
+        <v>239.33</v>
+      </c>
+      <c r="T17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="T17" s="1" t="n">
+      <c r="U17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1625,10 +1679,13 @@
         <v>0.9861</v>
       </c>
       <c r="S18" s="1" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="T18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="T18" s="1" t="n">
-        <v>0.9861</v>
+      <c r="U18" s="1" t="n">
+        <v>0.9858</v>
       </c>
     </row>
     <row r="19">
@@ -1689,10 +1746,13 @@
         <v>1.0306</v>
       </c>
       <c r="S19" s="1" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="T19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="T19" s="1" t="n">
-        <v>1.0184</v>
+      <c r="U19" s="1" t="n">
+        <v>0.9972</v>
       </c>
     </row>
     <row r="20">
@@ -1753,9 +1813,12 @@
         <v>0.259</v>
       </c>
       <c r="S20" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="T20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="T20" s="1" t="n">
+      <c r="U20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1817,9 +1880,12 @@
         <v>0.59256</v>
       </c>
       <c r="S21" s="1" t="n">
+        <v>0.60123</v>
+      </c>
+      <c r="T21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="T21" s="1" t="n">
+      <c r="U21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -1881,9 +1947,12 @@
         <v>9.022</v>
       </c>
       <c r="S22" s="1" t="n">
+        <v>9.029</v>
+      </c>
+      <c r="T22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="T22" s="1" t="n">
+      <c r="U22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1945,10 +2014,13 @@
         <v>0.02387</v>
       </c>
       <c r="S23" s="1" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="T23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="T23" s="1" t="n">
-        <v>0.02387</v>
+      <c r="U23" s="1" t="n">
+        <v>0.02384</v>
       </c>
     </row>
     <row r="24">
@@ -2009,9 +2081,12 @@
         <v>9.568</v>
       </c>
       <c r="S24" s="1" t="n">
+        <v>9.563000000000001</v>
+      </c>
+      <c r="T24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="T24" s="1" t="n">
+      <c r="U24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2073,9 +2148,12 @@
         <v>1.226</v>
       </c>
       <c r="S25" s="1" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="T25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="T25" s="1" t="n">
+      <c r="U25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -2137,9 +2215,12 @@
         <v>0.073</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.073</v>
+        <v>0.07317</v>
       </c>
       <c r="T26" s="1" t="n">
+        <v>0.07317</v>
+      </c>
+      <c r="U26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2201,9 +2282,12 @@
         <v>1.405</v>
       </c>
       <c r="S27" s="1" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="T27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="T27" s="1" t="n">
+      <c r="U27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2265,9 +2349,12 @@
         <v>1.304</v>
       </c>
       <c r="S28" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="T28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="T28" s="1" t="n">
+      <c r="U28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2329,9 +2416,12 @@
         <v>462.54</v>
       </c>
       <c r="S29" s="1" t="n">
+        <v>462.92</v>
+      </c>
+      <c r="T29" s="1" t="n">
         <v>463.55</v>
       </c>
-      <c r="T29" s="1" t="n">
+      <c r="U29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2393,9 +2483,12 @@
         <v>1.293</v>
       </c>
       <c r="S30" s="1" t="n">
+        <v>1.2939</v>
+      </c>
+      <c r="T30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="T30" s="1" t="n">
+      <c r="U30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2457,9 +2550,12 @@
         <v>5021.56</v>
       </c>
       <c r="S31" s="1" t="n">
+        <v>5021.55</v>
+      </c>
+      <c r="T31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="T31" s="1" t="n">
+      <c r="U31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -2521,9 +2617,12 @@
         <v>0.877</v>
       </c>
       <c r="S32" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="T32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="T32" s="1" t="n">
+      <c r="U32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2585,10 +2684,13 @@
         <v>0.00197</v>
       </c>
       <c r="S33" s="1" t="n">
+        <v>0.001966</v>
+      </c>
+      <c r="T33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="T33" s="1" t="n">
-        <v>0.001969</v>
+      <c r="U33" s="1" t="n">
+        <v>0.001966</v>
       </c>
     </row>
     <row r="34">
@@ -2649,9 +2751,12 @@
         <v>0.17284</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.17284</v>
+        <v>0.17416</v>
       </c>
       <c r="T34" s="1" t="n">
+        <v>0.17416</v>
+      </c>
+      <c r="U34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2713,9 +2818,12 @@
         <v>0.29674</v>
       </c>
       <c r="S35" s="1" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="T35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="T35" s="1" t="n">
+      <c r="U35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -2777,9 +2885,12 @@
         <v>1.78</v>
       </c>
       <c r="S36" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="T36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="T36" s="1" t="n">
+      <c r="U36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -2841,9 +2952,12 @@
         <v>110.17</v>
       </c>
       <c r="S37" s="1" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="T37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="T37" s="1" t="n">
+      <c r="U37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -2905,9 +3019,12 @@
         <v>0.21973</v>
       </c>
       <c r="S38" s="1" t="n">
+        <v>0.2209</v>
+      </c>
+      <c r="T38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="T38" s="1" t="n">
+      <c r="U38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -2969,10 +3086,13 @@
         <v>0.1067</v>
       </c>
       <c r="S39" s="1" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="T39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="T39" s="1" t="n">
-        <v>0.1067</v>
+      <c r="U39" s="1" t="n">
+        <v>0.1066</v>
       </c>
     </row>
     <row r="40">
@@ -3033,9 +3153,12 @@
         <v>0.37239</v>
       </c>
       <c r="S40" s="1" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="T40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="T40" s="1" t="n">
+      <c r="U40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -3097,9 +3220,12 @@
         <v>54.52</v>
       </c>
       <c r="S41" s="1" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="T41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="T41" s="1" t="n">
+      <c r="U41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3161,9 +3287,12 @@
         <v>0.001053</v>
       </c>
       <c r="S42" s="1" t="n">
+        <v>0.0010538</v>
+      </c>
+      <c r="T42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="T42" s="1" t="n">
+      <c r="U42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -3225,9 +3354,12 @@
         <v>6.459</v>
       </c>
       <c r="S43" s="1" t="n">
+        <v>6.465</v>
+      </c>
+      <c r="T43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="T43" s="1" t="n">
+      <c r="U43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3289,10 +3421,13 @@
         <v>0.6222</v>
       </c>
       <c r="S44" s="1" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="T44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="T44" s="1" t="n">
-        <v>0.6222</v>
+      <c r="U44" s="1" t="n">
+        <v>0.6213</v>
       </c>
     </row>
     <row r="45">
@@ -3353,10 +3488,13 @@
         <v>0.3516</v>
       </c>
       <c r="S45" s="1" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="T45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="T45" s="1" t="n">
-        <v>0.3516</v>
+      <c r="U45" s="1" t="n">
+        <v>0.3512</v>
       </c>
     </row>
     <row r="46">
@@ -3417,9 +3555,12 @@
         <v>0.03288</v>
       </c>
       <c r="S46" s="1" t="n">
+        <v>0.03282</v>
+      </c>
+      <c r="T46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="T46" s="1" t="n">
+      <c r="U46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3481,10 +3622,13 @@
         <v>0.06952999999999999</v>
       </c>
       <c r="S47" s="1" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="T47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="T47" s="1" t="n">
-        <v>0.06952999999999999</v>
+      <c r="U47" s="1" t="n">
+        <v>0.06920999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3545,9 +3689,12 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="S48" s="1" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="T48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="T48" s="1" t="n">
+      <c r="U48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3609,10 +3756,13 @@
         <v>0.004241</v>
       </c>
       <c r="S49" s="1" t="n">
+        <v>0.004224</v>
+      </c>
+      <c r="T49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="T49" s="1" t="n">
-        <v>0.004241</v>
+      <c r="U49" s="1" t="n">
+        <v>0.004224</v>
       </c>
     </row>
     <row r="50">
@@ -3673,10 +3823,13 @@
         <v>0.1032</v>
       </c>
       <c r="S50" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="T50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="T50" s="1" t="n">
-        <v>0.1032</v>
+      <c r="U50" s="1" t="n">
+        <v>0.1031</v>
       </c>
     </row>
     <row r="51">
@@ -3737,10 +3890,13 @@
         <v>0.04023</v>
       </c>
       <c r="S51" s="1" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="T51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="T51" s="1" t="n">
-        <v>0.04023</v>
+      <c r="U51" s="1" t="n">
+        <v>0.04021</v>
       </c>
     </row>
     <row r="52">
@@ -3801,9 +3957,12 @@
         <v>0.1645</v>
       </c>
       <c r="S52" s="1" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="T52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="T52" s="1" t="n">
+      <c r="U52" s="1" t="n">
         <v>0.1645</v>
       </c>
     </row>
@@ -3865,10 +4024,13 @@
         <v>0.02003</v>
       </c>
       <c r="S53" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="T53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="T53" s="1" t="n">
-        <v>0.02002</v>
+      <c r="U53" s="1" t="n">
+        <v>0.01925</v>
       </c>
     </row>
     <row r="54">
@@ -3929,10 +4091,13 @@
         <v>0.007175</v>
       </c>
       <c r="S54" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="T54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="T54" s="1" t="n">
-        <v>0.007175</v>
+      <c r="U54" s="1" t="n">
+        <v>0.00717</v>
       </c>
     </row>
     <row r="55">
@@ -3993,9 +4158,12 @@
         <v>3.915</v>
       </c>
       <c r="S55" s="1" t="n">
+        <v>3.918</v>
+      </c>
+      <c r="T55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="T55" s="1" t="n">
+      <c r="U55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -4057,10 +4225,13 @@
         <v>0.016935</v>
       </c>
       <c r="S56" s="1" t="n">
+        <v>0.016808</v>
+      </c>
+      <c r="T56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="T56" s="1" t="n">
-        <v>0.016935</v>
+      <c r="U56" s="1" t="n">
+        <v>0.016808</v>
       </c>
     </row>
     <row r="57">
@@ -4121,9 +4292,12 @@
         <v>0.1075</v>
       </c>
       <c r="S57" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="T57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="T57" s="1" t="n">
+      <c r="U57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -4185,10 +4359,13 @@
         <v>2.648</v>
       </c>
       <c r="S58" s="1" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="T58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="T58" s="1" t="n">
-        <v>2.643</v>
+      <c r="U58" s="1" t="n">
+        <v>2.639</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4426,13 @@
         <v>0.1584</v>
       </c>
       <c r="S59" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="T59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="T59" s="1" t="n">
-        <v>0.1584</v>
+      <c r="U59" s="1" t="n">
+        <v>0.1582</v>
       </c>
     </row>
     <row r="60">
@@ -4313,9 +4493,12 @@
         <v>0.005834</v>
       </c>
       <c r="S60" s="1" t="n">
+        <v>0.005839</v>
+      </c>
+      <c r="T60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="T60" s="1" t="n">
+      <c r="U60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -4377,10 +4560,13 @@
         <v>0.09145</v>
       </c>
       <c r="S61" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="T61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="T61" s="1" t="n">
-        <v>0.09145</v>
+      <c r="U61" s="1" t="n">
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4441,10 +4627,13 @@
         <v>0.9103</v>
       </c>
       <c r="S62" s="1" t="n">
+        <v>0.9101</v>
+      </c>
+      <c r="T62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="T62" s="1" t="n">
-        <v>0.9103</v>
+      <c r="U62" s="1" t="n">
+        <v>0.9101</v>
       </c>
     </row>
     <row r="63">
@@ -4505,9 +4694,12 @@
         <v>0.778</v>
       </c>
       <c r="S63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="T63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="T63" s="1" t="n">
+      <c r="U63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -4569,9 +4761,12 @@
         <v>0.04617</v>
       </c>
       <c r="S64" s="1" t="n">
+        <v>0.04603</v>
+      </c>
+      <c r="T64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="T64" s="1" t="n">
+      <c r="U64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -4633,9 +4828,12 @@
         <v>354.67</v>
       </c>
       <c r="S65" s="1" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="T65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="T65" s="1" t="n">
+      <c r="U65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -4697,9 +4895,12 @@
         <v>0.12462</v>
       </c>
       <c r="S66" s="1" t="n">
+        <v>0.12486</v>
+      </c>
+      <c r="T66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="T66" s="1" t="n">
+      <c r="U66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -4761,9 +4962,12 @@
         <v>0.2291</v>
       </c>
       <c r="S67" s="1" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="T67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="T67" s="1" t="n">
+      <c r="U67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -4825,9 +5029,12 @@
         <v>0.00337</v>
       </c>
       <c r="S68" s="1" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="T68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="T68" s="1" t="n">
+      <c r="U68" s="1" t="n">
         <v>0.00337</v>
       </c>
     </row>
@@ -4889,9 +5096,12 @@
         <v>0.1737</v>
       </c>
       <c r="S69" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="T69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="T69" s="1" t="n">
+      <c r="U69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -4953,10 +5163,13 @@
         <v>0.16361</v>
       </c>
       <c r="S70" s="1" t="n">
+        <v>0.16358</v>
+      </c>
+      <c r="T70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="T70" s="1" t="n">
-        <v>0.16361</v>
+      <c r="U70" s="1" t="n">
+        <v>0.16358</v>
       </c>
     </row>
     <row r="71">
@@ -5017,9 +5230,12 @@
         <v>0.3523</v>
       </c>
       <c r="S71" s="1" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="T71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="T71" s="1" t="n">
+      <c r="U71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -5081,9 +5297,12 @@
         <v>0.7069</v>
       </c>
       <c r="S72" s="1" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="T72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="T72" s="1" t="n">
+      <c r="U72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -5145,9 +5364,12 @@
         <v>0.008569999999999999</v>
       </c>
       <c r="S73" s="1" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="T73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="T73" s="1" t="n">
+      <c r="U73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -5209,10 +5431,13 @@
         <v>0.005964</v>
       </c>
       <c r="S74" s="1" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="T74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="T74" s="1" t="n">
-        <v>0.005964</v>
+      <c r="U74" s="1" t="n">
+        <v>0.005958</v>
       </c>
     </row>
     <row r="75">
@@ -5276,6 +5501,9 @@
         <v>0.229</v>
       </c>
       <c r="T75" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="U75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -5337,9 +5565,12 @@
         <v>0.3244</v>
       </c>
       <c r="S76" s="1" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="T76" s="1" t="n">
         <v>0.3278</v>
       </c>
-      <c r="T76" s="1" t="n">
+      <c r="U76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -5401,10 +5632,13 @@
         <v>0.1</v>
       </c>
       <c r="S77" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="T77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="T77" s="1" t="n">
-        <v>0.1</v>
+      <c r="U77" s="1" t="n">
+        <v>0.0999</v>
       </c>
     </row>
     <row r="78">
@@ -5465,10 +5699,13 @@
         <v>0.1223</v>
       </c>
       <c r="S78" s="1" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="T78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="T78" s="1" t="n">
-        <v>0.1223</v>
+      <c r="U78" s="1" t="n">
+        <v>0.1222</v>
       </c>
     </row>
     <row r="79">
@@ -5529,9 +5766,12 @@
         <v>0.07378999999999999</v>
       </c>
       <c r="S79" s="1" t="n">
-        <v>0.07378999999999999</v>
+        <v>0.07459</v>
       </c>
       <c r="T79" s="1" t="n">
+        <v>0.07459</v>
+      </c>
+      <c r="U79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -5593,10 +5833,13 @@
         <v>0.0464</v>
       </c>
       <c r="S80" s="1" t="n">
+        <v>0.04634</v>
+      </c>
+      <c r="T80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="T80" s="1" t="n">
-        <v>0.0464</v>
+      <c r="U80" s="1" t="n">
+        <v>0.04634</v>
       </c>
     </row>
     <row r="81">
@@ -5657,10 +5900,13 @@
         <v>0.00023</v>
       </c>
       <c r="S81" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="T81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="T81" s="1" t="n">
-        <v>0.00023</v>
+      <c r="U81" s="1" t="n">
+        <v>0.000228</v>
       </c>
     </row>
     <row r="82">
@@ -5721,9 +5967,12 @@
         <v>8.194000000000001</v>
       </c>
       <c r="S82" s="1" t="n">
+        <v>8.196999999999999</v>
+      </c>
+      <c r="T82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="T82" s="1" t="n">
+      <c r="U82" s="1" t="n">
         <v>8.194000000000001</v>
       </c>
     </row>
@@ -5785,10 +6034,13 @@
         <v>0.0005792</v>
       </c>
       <c r="S83" s="1" t="n">
+        <v>0.0005713</v>
+      </c>
+      <c r="T83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="T83" s="1" t="n">
-        <v>0.0005756</v>
+      <c r="U83" s="1" t="n">
+        <v>0.0005713</v>
       </c>
     </row>
     <row r="84">
@@ -5849,9 +6101,12 @@
         <v>0.4475</v>
       </c>
       <c r="S84" s="1" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="T84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="T84" s="1" t="n">
+      <c r="U84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -5913,10 +6168,13 @@
         <v>0.06253</v>
       </c>
       <c r="S85" s="1" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="T85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="T85" s="1" t="n">
-        <v>0.06235</v>
+      <c r="U85" s="1" t="n">
+        <v>0.0623</v>
       </c>
     </row>
     <row r="86">
@@ -5977,9 +6235,12 @@
         <v>0.05403</v>
       </c>
       <c r="S86" s="1" t="n">
+        <v>0.05409</v>
+      </c>
+      <c r="T86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="T86" s="1" t="n">
+      <c r="U86" s="1" t="n">
         <v>0.05403</v>
       </c>
     </row>
@@ -6041,9 +6302,12 @@
         <v>0.00333</v>
       </c>
       <c r="S87" s="1" t="n">
+        <v>0.003352</v>
+      </c>
+      <c r="T87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="T87" s="1" t="n">
+      <c r="U87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -6105,9 +6369,12 @@
         <v>0.05049</v>
       </c>
       <c r="S88" s="1" t="n">
+        <v>0.05034</v>
+      </c>
+      <c r="T88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="T88" s="1" t="n">
+      <c r="U88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -6169,9 +6436,12 @@
         <v>0.03145</v>
       </c>
       <c r="S89" s="1" t="n">
-        <v>0.03145</v>
+        <v>0.03164</v>
       </c>
       <c r="T89" s="1" t="n">
+        <v>0.03164</v>
+      </c>
+      <c r="U89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -6233,10 +6503,13 @@
         <v>0.3445</v>
       </c>
       <c r="S90" s="1" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="T90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="T90" s="1" t="n">
-        <v>0.3445</v>
+      <c r="U90" s="1" t="n">
+        <v>0.3442</v>
       </c>
     </row>
     <row r="91">
@@ -6297,9 +6570,12 @@
         <v>0.07562000000000001</v>
       </c>
       <c r="S91" s="1" t="n">
+        <v>0.07342</v>
+      </c>
+      <c r="T91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="T91" s="1" t="n">
+      <c r="U91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -6361,9 +6637,12 @@
         <v>0.359</v>
       </c>
       <c r="S92" s="1" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="T92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="T92" s="1" t="n">
+      <c r="U92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -6425,9 +6704,12 @@
         <v>1.9726</v>
       </c>
       <c r="S93" s="1" t="n">
+        <v>1.9769</v>
+      </c>
+      <c r="T93" s="1" t="n">
         <v>1.9809</v>
       </c>
-      <c r="T93" s="1" t="n">
+      <c r="U93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -6489,9 +6771,12 @@
         <v>0.2581</v>
       </c>
       <c r="S94" s="1" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="T94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="T94" s="1" t="n">
+      <c r="U94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -6553,9 +6838,12 @@
         <v>0.04483</v>
       </c>
       <c r="S95" s="1" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="T95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="T95" s="1" t="n">
+      <c r="U95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -6617,9 +6905,12 @@
         <v>0.00611</v>
       </c>
       <c r="S96" s="1" t="n">
+        <v>0.006133</v>
+      </c>
+      <c r="T96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="T96" s="1" t="n">
+      <c r="U96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -6681,10 +6972,13 @@
         <v>0.00171</v>
       </c>
       <c r="S97" s="1" t="n">
+        <v>0.001706</v>
+      </c>
+      <c r="T97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="T97" s="1" t="n">
-        <v>0.00171</v>
+      <c r="U97" s="1" t="n">
+        <v>0.001706</v>
       </c>
     </row>
     <row r="98">
@@ -6745,9 +7039,12 @@
         <v>5.198</v>
       </c>
       <c r="S98" s="1" t="n">
+        <v>5.224</v>
+      </c>
+      <c r="T98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="T98" s="1" t="n">
+      <c r="U98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -6809,10 +7106,13 @@
         <v>0.01514</v>
       </c>
       <c r="S99" s="1" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="T99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="T99" s="1" t="n">
-        <v>0.01508</v>
+      <c r="U99" s="1" t="n">
+        <v>0.01503</v>
       </c>
     </row>
     <row r="100">
@@ -6873,10 +7173,13 @@
         <v>0.5516</v>
       </c>
       <c r="S100" s="1" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="T100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="T100" s="1" t="n">
-        <v>0.5508999999999999</v>
+      <c r="U100" s="1" t="n">
+        <v>0.5508</v>
       </c>
     </row>
     <row r="101">
@@ -6937,10 +7240,13 @@
         <v>0.0898</v>
       </c>
       <c r="S101" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="T101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="T101" s="1" t="n">
-        <v>0.0898</v>
+      <c r="U101" s="1" t="n">
+        <v>0.0897</v>
       </c>
     </row>
     <row r="102">
@@ -7001,9 +7307,12 @@
         <v>32.29</v>
       </c>
       <c r="S102" s="1" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="T102" s="1" t="n">
+      <c r="U102" s="1" t="n">
         <v>32.29</v>
       </c>
     </row>
@@ -7065,9 +7374,12 @@
         <v>0.03162</v>
       </c>
       <c r="S103" s="1" t="n">
+        <v>0.03214</v>
+      </c>
+      <c r="T103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="T103" s="1" t="n">
+      <c r="U103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -7129,10 +7441,13 @@
         <v>0.06564</v>
       </c>
       <c r="S104" s="1" t="n">
+        <v>0.06559</v>
+      </c>
+      <c r="T104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="T104" s="1" t="n">
-        <v>0.06561</v>
+      <c r="U104" s="1" t="n">
+        <v>0.06559</v>
       </c>
     </row>
     <row r="105">
@@ -7193,9 +7508,12 @@
         <v>1.3005</v>
       </c>
       <c r="S105" s="1" t="n">
+        <v>1.3001</v>
+      </c>
+      <c r="T105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="T105" s="1" t="n">
+      <c r="U105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -7257,9 +7575,12 @@
         <v>0.1203</v>
       </c>
       <c r="S106" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="T106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="T106" s="1" t="n">
+      <c r="U106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -7321,9 +7642,12 @@
         <v>0.119</v>
       </c>
       <c r="S107" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="T107" s="1" t="n">
+      <c r="U107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -7385,10 +7709,13 @@
         <v>0.09576</v>
       </c>
       <c r="S108" s="1" t="n">
+        <v>0.09572</v>
+      </c>
+      <c r="T108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="T108" s="1" t="n">
-        <v>0.09576</v>
+      <c r="U108" s="1" t="n">
+        <v>0.09572</v>
       </c>
     </row>
     <row r="109">
@@ -7449,9 +7776,12 @@
         <v>0.13884</v>
       </c>
       <c r="S109" s="1" t="n">
+        <v>0.13824</v>
+      </c>
+      <c r="T109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="T109" s="1" t="n">
+      <c r="U109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -7513,9 +7843,12 @@
         <v>5.556</v>
       </c>
       <c r="S110" s="1" t="n">
+        <v>5.553</v>
+      </c>
+      <c r="T110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="T110" s="1" t="n">
+      <c r="U110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -7577,9 +7910,12 @@
         <v>1.098</v>
       </c>
       <c r="S111" s="1" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="T111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="T111" s="1" t="n">
+      <c r="U111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -7641,10 +7977,13 @@
         <v>0.028774</v>
       </c>
       <c r="S112" s="1" t="n">
+        <v>0.028743</v>
+      </c>
+      <c r="T112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="T112" s="1" t="n">
-        <v>0.028774</v>
+      <c r="U112" s="1" t="n">
+        <v>0.028743</v>
       </c>
     </row>
     <row r="113">
@@ -7705,10 +8044,13 @@
         <v>1.865</v>
       </c>
       <c r="S113" s="1" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="T113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="T113" s="1" t="n">
-        <v>1.865</v>
+      <c r="U113" s="1" t="n">
+        <v>1.862</v>
       </c>
     </row>
     <row r="114">
@@ -7769,9 +8111,12 @@
         <v>0.05889</v>
       </c>
       <c r="S114" s="1" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="T114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="T114" s="1" t="n">
+      <c r="U114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -7833,9 +8178,12 @@
         <v>0.12738</v>
       </c>
       <c r="S115" s="1" t="n">
+        <v>0.12805</v>
+      </c>
+      <c r="T115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="T115" s="1" t="n">
+      <c r="U115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -7897,10 +8245,13 @@
         <v>1.1066</v>
       </c>
       <c r="S116" s="1" t="n">
+        <v>1.1018</v>
+      </c>
+      <c r="T116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="T116" s="1" t="n">
-        <v>1.1039</v>
+      <c r="U116" s="1" t="n">
+        <v>1.1018</v>
       </c>
     </row>
     <row r="117">
@@ -7961,10 +8312,13 @@
         <v>0.1485</v>
       </c>
       <c r="S117" s="1" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="T117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="T117" s="1" t="n">
-        <v>0.1485</v>
+      <c r="U117" s="1" t="n">
+        <v>0.1484</v>
       </c>
     </row>
     <row r="118">
@@ -8025,9 +8379,12 @@
         <v>0.1586</v>
       </c>
       <c r="S118" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="T118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="T118" s="1" t="n">
+      <c r="U118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -8089,9 +8446,12 @@
         <v>0.04661</v>
       </c>
       <c r="S119" s="1" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="T119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="T119" s="1" t="n">
+      <c r="U119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -8153,9 +8513,12 @@
         <v>3.006</v>
       </c>
       <c r="S120" s="1" t="n">
+        <v>3.006</v>
+      </c>
+      <c r="T120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="T120" s="1" t="n">
+      <c r="U120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -8217,9 +8580,12 @@
         <v>0.2971</v>
       </c>
       <c r="S121" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="T121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="T121" s="1" t="n">
+      <c r="U121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -8281,10 +8647,13 @@
         <v>0.5772</v>
       </c>
       <c r="S122" s="1" t="n">
+        <v>0.5770999999999999</v>
+      </c>
+      <c r="T122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="T122" s="1" t="n">
-        <v>0.5772</v>
+      <c r="U122" s="1" t="n">
+        <v>0.5770999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -8345,10 +8714,13 @@
         <v>0.01254</v>
       </c>
       <c r="S123" s="1" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="T123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="T123" s="1" t="n">
-        <v>0.01254</v>
+      <c r="U123" s="1" t="n">
+        <v>0.01253</v>
       </c>
     </row>
     <row r="124">
@@ -8409,10 +8781,13 @@
         <v>0.1571</v>
       </c>
       <c r="S124" s="1" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="T124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="T124" s="1" t="n">
-        <v>0.1571</v>
+      <c r="U124" s="1" t="n">
+        <v>0.1569</v>
       </c>
     </row>
     <row r="125">
@@ -8473,9 +8848,12 @@
         <v>0.001781</v>
       </c>
       <c r="S125" s="1" t="n">
+        <v>0.001781</v>
+      </c>
+      <c r="T125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="T125" s="1" t="n">
+      <c r="U125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -8537,9 +8915,12 @@
         <v>0.0004824</v>
       </c>
       <c r="S126" s="1" t="n">
+        <v>0.0004825</v>
+      </c>
+      <c r="T126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="T126" s="1" t="n">
+      <c r="U126" s="1" t="n">
         <v>0.0004824</v>
       </c>
     </row>
@@ -8601,10 +8982,13 @@
         <v>0.02926</v>
       </c>
       <c r="S127" s="1" t="n">
+        <v>0.02924</v>
+      </c>
+      <c r="T127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="T127" s="1" t="n">
-        <v>0.02926</v>
+      <c r="U127" s="1" t="n">
+        <v>0.02924</v>
       </c>
     </row>
     <row r="128">
@@ -8665,10 +9049,13 @@
         <v>0.04117</v>
       </c>
       <c r="S128" s="1" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="T128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="T128" s="1" t="n">
-        <v>0.04117</v>
+      <c r="U128" s="1" t="n">
+        <v>0.04116</v>
       </c>
     </row>
     <row r="129">
@@ -8729,9 +9116,12 @@
         <v>0.04918</v>
       </c>
       <c r="S129" s="1" t="n">
-        <v>0.04918</v>
+        <v>0.04935</v>
       </c>
       <c r="T129" s="1" t="n">
+        <v>0.04935</v>
+      </c>
+      <c r="U129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -8793,9 +9183,12 @@
         <v>1.21e-05</v>
       </c>
       <c r="S130" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="T130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="T130" s="1" t="n">
+      <c r="U130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -8857,9 +9250,12 @@
         <v>7.4e-06</v>
       </c>
       <c r="S131" s="1" t="n">
-        <v>7.4e-06</v>
+        <v>7.5e-06</v>
       </c>
       <c r="T131" s="1" t="n">
+        <v>7.5e-06</v>
+      </c>
+      <c r="U131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -8921,10 +9317,13 @@
         <v>0.00698</v>
       </c>
       <c r="S132" s="1" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="T132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="T132" s="1" t="n">
-        <v>0.00698</v>
+      <c r="U132" s="1" t="n">
+        <v>0.00697</v>
       </c>
     </row>
     <row r="133">
@@ -8985,9 +9384,12 @@
         <v>0.0961</v>
       </c>
       <c r="S133" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="T133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="T133" s="1" t="n">
+      <c r="U133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -9049,9 +9451,12 @@
         <v>0.0004092</v>
       </c>
       <c r="S134" s="1" t="n">
+        <v>0.0004087</v>
+      </c>
+      <c r="T134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="T134" s="1" t="n">
+      <c r="U134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -9113,10 +9518,13 @@
         <v>0.0818</v>
       </c>
       <c r="S135" s="1" t="n">
+        <v>0.08148</v>
+      </c>
+      <c r="T135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="T135" s="1" t="n">
-        <v>0.0818</v>
+      <c r="U135" s="1" t="n">
+        <v>0.08148</v>
       </c>
     </row>
     <row r="136">
@@ -9177,10 +9585,13 @@
         <v>0.007816999999999999</v>
       </c>
       <c r="S136" s="1" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="T136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="T136" s="1" t="n">
-        <v>0.007816999999999999</v>
+      <c r="U136" s="1" t="n">
+        <v>0.0078</v>
       </c>
     </row>
     <row r="137">
@@ -9241,10 +9652,13 @@
         <v>0.0008104</v>
       </c>
       <c r="S137" s="1" t="n">
+        <v>0.0008066</v>
+      </c>
+      <c r="T137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="T137" s="1" t="n">
-        <v>0.0008104</v>
+      <c r="U137" s="1" t="n">
+        <v>0.0008066</v>
       </c>
     </row>
     <row r="138">
@@ -9305,10 +9719,13 @@
         <v>0.1463</v>
       </c>
       <c r="S138" s="1" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="T138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="T138" s="1" t="n">
-        <v>0.1463</v>
+      <c r="U138" s="1" t="n">
+        <v>0.1453</v>
       </c>
     </row>
     <row r="139">
@@ -9369,10 +9786,13 @@
         <v>0.006679</v>
       </c>
       <c r="S139" s="1" t="n">
+        <v>0.006677</v>
+      </c>
+      <c r="T139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="T139" s="1" t="n">
-        <v>0.006679</v>
+      <c r="U139" s="1" t="n">
+        <v>0.006677</v>
       </c>
     </row>
     <row r="140">
@@ -9433,10 +9853,13 @@
         <v>0.01382</v>
       </c>
       <c r="S140" s="1" t="n">
+        <v>0.01377</v>
+      </c>
+      <c r="T140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="T140" s="1" t="n">
-        <v>0.01381</v>
+      <c r="U140" s="1" t="n">
+        <v>0.01377</v>
       </c>
     </row>
     <row r="141">
@@ -9497,10 +9920,13 @@
         <v>0.09676999999999999</v>
       </c>
       <c r="S141" s="1" t="n">
+        <v>0.09667000000000001</v>
+      </c>
+      <c r="T141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="T141" s="1" t="n">
-        <v>0.09676999999999999</v>
+      <c r="U141" s="1" t="n">
+        <v>0.09667000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9561,9 +9987,12 @@
         <v>0.05409</v>
       </c>
       <c r="S142" s="1" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="T142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="T142" s="1" t="n">
+      <c r="U142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -9625,10 +10054,13 @@
         <v>0.322</v>
       </c>
       <c r="S143" s="1" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="T143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="T143" s="1" t="n">
-        <v>0.322</v>
+      <c r="U143" s="1" t="n">
+        <v>0.3219</v>
       </c>
     </row>
     <row r="144">
@@ -9689,10 +10121,13 @@
         <v>0.02563</v>
       </c>
       <c r="S144" s="1" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="T144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="T144" s="1" t="n">
-        <v>0.02563</v>
+      <c r="U144" s="1" t="n">
+        <v>0.02558</v>
       </c>
     </row>
     <row r="145">
@@ -9753,10 +10188,13 @@
         <v>0.2354</v>
       </c>
       <c r="S145" s="1" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="T145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="T145" s="1" t="n">
-        <v>0.2354</v>
+      <c r="U145" s="1" t="n">
+        <v>0.2352</v>
       </c>
     </row>
     <row r="146">
@@ -9817,9 +10255,12 @@
         <v>0.007</v>
       </c>
       <c r="S146" s="1" t="n">
+        <v>0.006992</v>
+      </c>
+      <c r="T146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="T146" s="1" t="n">
+      <c r="U146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -9881,9 +10322,12 @@
         <v>0.08641</v>
       </c>
       <c r="S147" s="1" t="n">
+        <v>0.08644</v>
+      </c>
+      <c r="T147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="T147" s="1" t="n">
+      <c r="U147" s="1" t="n">
         <v>0.08597</v>
       </c>
     </row>
@@ -9945,9 +10389,12 @@
         <v>0.052</v>
       </c>
       <c r="S148" s="1" t="n">
+        <v>0.05216</v>
+      </c>
+      <c r="T148" s="1" t="n">
         <v>0.05284</v>
       </c>
-      <c r="T148" s="1" t="n">
+      <c r="U148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -10009,9 +10456,12 @@
         <v>0.02396</v>
       </c>
       <c r="S149" s="1" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="T149" s="1" t="n">
         <v>0.02399</v>
       </c>
-      <c r="T149" s="1" t="n">
+      <c r="U149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -10073,9 +10523,12 @@
         <v>0.08634</v>
       </c>
       <c r="S150" s="1" t="n">
+        <v>0.08618000000000001</v>
+      </c>
+      <c r="T150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="T150" s="1" t="n">
+      <c r="U150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -10137,9 +10590,12 @@
         <v>0.02343</v>
       </c>
       <c r="S151" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="T151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="T151" s="1" t="n">
+      <c r="U151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -10201,10 +10657,13 @@
         <v>0.02531</v>
       </c>
       <c r="S152" s="1" t="n">
+        <v>0.02528</v>
+      </c>
+      <c r="T152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="T152" s="1" t="n">
-        <v>0.02531</v>
+      <c r="U152" s="1" t="n">
+        <v>0.02528</v>
       </c>
     </row>
     <row r="153">
@@ -10265,9 +10724,12 @@
         <v>0.0002125</v>
       </c>
       <c r="S153" s="1" t="n">
+        <v>0.0002109</v>
+      </c>
+      <c r="T153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="T153" s="1" t="n">
+      <c r="U153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -10329,9 +10791,12 @@
         <v>0.437</v>
       </c>
       <c r="S154" s="1" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="T154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="T154" s="1" t="n">
+      <c r="U154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -10393,9 +10858,12 @@
         <v>0.06766</v>
       </c>
       <c r="S155" s="1" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="T155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="T155" s="1" t="n">
+      <c r="U155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -10457,9 +10925,12 @@
         <v>0.12908</v>
       </c>
       <c r="S156" s="1" t="n">
-        <v>0.12938</v>
+        <v>0.12939</v>
       </c>
       <c r="T156" s="1" t="n">
+        <v>0.12939</v>
+      </c>
+      <c r="U156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -10521,10 +10992,13 @@
         <v>0.4828</v>
       </c>
       <c r="S157" s="1" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="T157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="T157" s="1" t="n">
-        <v>0.4828</v>
+      <c r="U157" s="1" t="n">
+        <v>0.4826</v>
       </c>
     </row>
     <row r="158">
@@ -10585,9 +11059,12 @@
         <v>0.4503</v>
       </c>
       <c r="S158" s="1" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="T158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="T158" s="1" t="n">
+      <c r="U158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -10649,10 +11126,13 @@
         <v>0.007422</v>
       </c>
       <c r="S159" s="1" t="n">
+        <v>0.007417</v>
+      </c>
+      <c r="T159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="T159" s="1" t="n">
-        <v>0.007422</v>
+      <c r="U159" s="1" t="n">
+        <v>0.007417</v>
       </c>
     </row>
     <row r="160">
@@ -10713,9 +11193,12 @@
         <v>0.004651</v>
       </c>
       <c r="S160" s="1" t="n">
+        <v>0.004656</v>
+      </c>
+      <c r="T160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="T160" s="1" t="n">
+      <c r="U160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -10777,10 +11260,13 @@
         <v>0.004278</v>
       </c>
       <c r="S161" s="1" t="n">
+        <v>0.004276</v>
+      </c>
+      <c r="T161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="T161" s="1" t="n">
-        <v>0.004278</v>
+      <c r="U161" s="1" t="n">
+        <v>0.004276</v>
       </c>
     </row>
     <row r="162">
@@ -10841,9 +11327,12 @@
         <v>0.0954</v>
       </c>
       <c r="S162" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="T162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="T162" s="1" t="n">
+      <c r="U162" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -10905,9 +11394,12 @@
         <v>0.2843</v>
       </c>
       <c r="S163" s="1" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="T163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="T163" s="1" t="n">
+      <c r="U163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -10969,9 +11461,12 @@
         <v>0.1135</v>
       </c>
       <c r="S164" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="T164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="T164" s="1" t="n">
+      <c r="U164" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -11033,9 +11528,12 @@
         <v>0.1748</v>
       </c>
       <c r="S165" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="T165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="T165" s="1" t="n">
+      <c r="U165" s="1" t="n">
         <v>0.1748</v>
       </c>
     </row>
@@ -11097,10 +11595,13 @@
         <v>0.01005</v>
       </c>
       <c r="S166" s="1" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="T166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="T166" s="1" t="n">
-        <v>0.01005</v>
+      <c r="U166" s="1" t="n">
+        <v>0.01004</v>
       </c>
     </row>
     <row r="167">
@@ -11161,10 +11662,13 @@
         <v>1.817</v>
       </c>
       <c r="S167" s="1" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="T167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="T167" s="1" t="n">
-        <v>1.817</v>
+      <c r="U167" s="1" t="n">
+        <v>1.814</v>
       </c>
     </row>
     <row r="168">
@@ -11225,9 +11729,12 @@
         <v>1.347</v>
       </c>
       <c r="S168" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="T168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="T168" s="1" t="n">
+      <c r="U168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -11289,10 +11796,13 @@
         <v>0.007286</v>
       </c>
       <c r="S169" s="1" t="n">
+        <v>0.007284</v>
+      </c>
+      <c r="T169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="T169" s="1" t="n">
-        <v>0.007286</v>
+      <c r="U169" s="1" t="n">
+        <v>0.007284</v>
       </c>
     </row>
     <row r="170">
@@ -11353,9 +11863,12 @@
         <v>0.0115</v>
       </c>
       <c r="S170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="T170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="T170" s="1" t="n">
+      <c r="U170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -11417,10 +11930,13 @@
         <v>0.005766</v>
       </c>
       <c r="S171" s="1" t="n">
+        <v>0.00576</v>
+      </c>
+      <c r="T171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="T171" s="1" t="n">
-        <v>0.005766</v>
+      <c r="U171" s="1" t="n">
+        <v>0.00576</v>
       </c>
     </row>
     <row r="172">
@@ -11481,9 +11997,12 @@
         <v>0.14905</v>
       </c>
       <c r="S172" s="1" t="n">
+        <v>0.14867</v>
+      </c>
+      <c r="T172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="T172" s="1" t="n">
+      <c r="U172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -11545,9 +12064,12 @@
         <v>4.917</v>
       </c>
       <c r="S173" s="1" t="n">
+        <v>4.892</v>
+      </c>
+      <c r="T173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="T173" s="1" t="n">
+      <c r="U173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -11609,10 +12131,13 @@
         <v>0.07792</v>
       </c>
       <c r="S174" s="1" t="n">
+        <v>0.07789</v>
+      </c>
+      <c r="T174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="T174" s="1" t="n">
-        <v>0.07792</v>
+      <c r="U174" s="1" t="n">
+        <v>0.07789</v>
       </c>
     </row>
     <row r="175">
@@ -11673,10 +12198,13 @@
         <v>0.007405</v>
       </c>
       <c r="S175" s="1" t="n">
+        <v>0.007403</v>
+      </c>
+      <c r="T175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="T175" s="1" t="n">
-        <v>0.007405</v>
+      <c r="U175" s="1" t="n">
+        <v>0.007403</v>
       </c>
     </row>
     <row r="176">
@@ -11737,10 +12265,13 @@
         <v>0.1988</v>
       </c>
       <c r="S176" s="1" t="n">
+        <v>0.1985</v>
+      </c>
+      <c r="T176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="T176" s="1" t="n">
-        <v>0.1988</v>
+      <c r="U176" s="1" t="n">
+        <v>0.1985</v>
       </c>
     </row>
     <row r="177">
@@ -11801,9 +12332,12 @@
         <v>0.05171</v>
       </c>
       <c r="S177" s="1" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="T177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="T177" s="1" t="n">
+      <c r="U177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -11865,10 +12399,13 @@
         <v>0.05457</v>
       </c>
       <c r="S178" s="1" t="n">
+        <v>0.05447</v>
+      </c>
+      <c r="T178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="T178" s="1" t="n">
-        <v>0.05455</v>
+      <c r="U178" s="1" t="n">
+        <v>0.05447</v>
       </c>
     </row>
     <row r="179">
@@ -11929,9 +12466,12 @@
         <v>0.02327</v>
       </c>
       <c r="S179" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="T179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="T179" s="1" t="n">
+      <c r="U179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -11993,9 +12533,12 @@
         <v>0.6971000000000001</v>
       </c>
       <c r="S180" s="1" t="n">
+        <v>0.6971000000000001</v>
+      </c>
+      <c r="T180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="T180" s="1" t="n">
+      <c r="U180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -12057,9 +12600,12 @@
         <v>0.0003722</v>
       </c>
       <c r="S181" s="1" t="n">
+        <v>0.0003741</v>
+      </c>
+      <c r="T181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="T181" s="1" t="n">
+      <c r="U181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -12121,9 +12667,12 @@
         <v>0.01254</v>
       </c>
       <c r="S182" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="T182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="T182" s="1" t="n">
+      <c r="U182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -12185,9 +12734,12 @@
         <v>4.182</v>
       </c>
       <c r="S183" s="1" t="n">
+        <v>4.223</v>
+      </c>
+      <c r="T183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="T183" s="1" t="n">
+      <c r="U183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -12249,10 +12801,13 @@
         <v>0.2337</v>
       </c>
       <c r="S184" s="1" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="T184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="T184" s="1" t="n">
-        <v>0.2337</v>
+      <c r="U184" s="1" t="n">
+        <v>0.2335</v>
       </c>
     </row>
     <row r="185">
@@ -12313,9 +12868,12 @@
         <v>0.03709</v>
       </c>
       <c r="S185" s="1" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="T185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="T185" s="1" t="n">
+      <c r="U185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -12377,10 +12935,13 @@
         <v>0.11572</v>
       </c>
       <c r="S186" s="1" t="n">
+        <v>0.11555</v>
+      </c>
+      <c r="T186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="T186" s="1" t="n">
-        <v>0.11557</v>
+      <c r="U186" s="1" t="n">
+        <v>0.11555</v>
       </c>
     </row>
     <row r="187">
@@ -12441,9 +13002,12 @@
         <v>0.009119</v>
       </c>
       <c r="S187" s="1" t="n">
+        <v>0.009124999999999999</v>
+      </c>
+      <c r="T187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="T187" s="1" t="n">
+      <c r="U187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -12505,9 +13069,12 @@
         <v>0.0968</v>
       </c>
       <c r="S188" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="T188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="T188" s="1" t="n">
+      <c r="U188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -12569,10 +13136,13 @@
         <v>0.02737</v>
       </c>
       <c r="S189" s="1" t="n">
+        <v>0.02731</v>
+      </c>
+      <c r="T189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="T189" s="1" t="n">
-        <v>0.02737</v>
+      <c r="U189" s="1" t="n">
+        <v>0.02731</v>
       </c>
     </row>
     <row r="190">
@@ -12633,9 +13203,12 @@
         <v>0.00868</v>
       </c>
       <c r="S190" s="1" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="T190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="T190" s="1" t="n">
+      <c r="U190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -12697,9 +13270,12 @@
         <v>0.001949</v>
       </c>
       <c r="S191" s="1" t="n">
+        <v>0.001951</v>
+      </c>
+      <c r="T191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="T191" s="1" t="n">
+      <c r="U191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -12761,10 +13337,13 @@
         <v>0.1001</v>
       </c>
       <c r="S192" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="T192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="T192" s="1" t="n">
-        <v>0.1001</v>
+      <c r="U192" s="1" t="n">
+        <v>0.09959999999999999</v>
       </c>
     </row>
     <row r="193">
@@ -12825,10 +13404,13 @@
         <v>0.02322</v>
       </c>
       <c r="S193" s="1" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="T193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="T193" s="1" t="n">
-        <v>0.02312</v>
+      <c r="U193" s="1" t="n">
+        <v>0.0231</v>
       </c>
     </row>
     <row r="194">
@@ -12889,9 +13471,12 @@
         <v>0.01341</v>
       </c>
       <c r="S194" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="T194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="T194" s="1" t="n">
+      <c r="U194" s="1" t="n">
         <v>0.01341</v>
       </c>
     </row>
@@ -12953,10 +13538,13 @@
         <v>0.02078</v>
       </c>
       <c r="S195" s="1" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="T195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="T195" s="1" t="n">
-        <v>0.02078</v>
+      <c r="U195" s="1" t="n">
+        <v>0.02076</v>
       </c>
     </row>
     <row r="196">
@@ -13017,9 +13605,12 @@
         <v>0.17573</v>
       </c>
       <c r="S196" s="1" t="n">
+        <v>0.17498</v>
+      </c>
+      <c r="T196" s="1" t="n">
         <v>0.17659</v>
       </c>
-      <c r="T196" s="1" t="n">
+      <c r="U196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -13081,9 +13672,12 @@
         <v>0.007343</v>
       </c>
       <c r="S197" s="1" t="n">
+        <v>0.007396</v>
+      </c>
+      <c r="T197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="T197" s="1" t="n">
+      <c r="U197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -13145,9 +13739,12 @@
         <v>0.019</v>
       </c>
       <c r="S198" s="1" t="n">
+        <v>0.01902</v>
+      </c>
+      <c r="T198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="T198" s="1" t="n">
+      <c r="U198" s="1" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -13209,9 +13806,12 @@
         <v>0.0164</v>
       </c>
       <c r="S199" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="T199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="T199" s="1" t="n">
+      <c r="U199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -13273,9 +13873,12 @@
         <v>0.2971</v>
       </c>
       <c r="S200" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="T200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="T200" s="1" t="n">
+      <c r="U200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -13337,9 +13940,12 @@
         <v>0.006203</v>
       </c>
       <c r="S201" s="1" t="n">
+        <v>0.006209</v>
+      </c>
+      <c r="T201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="T201" s="1" t="n">
+      <c r="U201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -13401,10 +14007,13 @@
         <v>0.0004393</v>
       </c>
       <c r="S202" s="1" t="n">
+        <v>0.0004386</v>
+      </c>
+      <c r="T202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="T202" s="1" t="n">
-        <v>0.0004393</v>
+      <c r="U202" s="1" t="n">
+        <v>0.0004386</v>
       </c>
     </row>
     <row r="203">
@@ -13465,9 +14074,12 @@
         <v>0.007245</v>
       </c>
       <c r="S203" s="1" t="n">
+        <v>0.007252</v>
+      </c>
+      <c r="T203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="T203" s="1" t="n">
+      <c r="U203" s="1" t="n">
         <v>0.007245</v>
       </c>
     </row>
@@ -13529,9 +14141,12 @@
         <v>0.1308</v>
       </c>
       <c r="S204" s="1" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="T204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="T204" s="1" t="n">
+      <c r="U204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -13593,9 +14208,12 @@
         <v>0.01416</v>
       </c>
       <c r="S205" s="1" t="n">
+        <v>0.01416</v>
+      </c>
+      <c r="T205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="T205" s="1" t="n">
+      <c r="U205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -13657,9 +14275,12 @@
         <v>0.00357</v>
       </c>
       <c r="S206" s="1" t="n">
+        <v>0.003576</v>
+      </c>
+      <c r="T206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="T206" s="1" t="n">
+      <c r="U206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -13721,10 +14342,13 @@
         <v>0.05924</v>
       </c>
       <c r="S207" s="1" t="n">
+        <v>0.05914</v>
+      </c>
+      <c r="T207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="T207" s="1" t="n">
-        <v>0.05924</v>
+      <c r="U207" s="1" t="n">
+        <v>0.05914</v>
       </c>
     </row>
     <row r="208">
@@ -13785,9 +14409,12 @@
         <v>15.46</v>
       </c>
       <c r="S208" s="1" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="T208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="T208" s="1" t="n">
+      <c r="U208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -13849,9 +14476,12 @@
         <v>5193.6</v>
       </c>
       <c r="S209" s="1" t="n">
-        <v>5194.1</v>
+        <v>5194.4</v>
       </c>
       <c r="T209" s="1" t="n">
+        <v>5194.4</v>
+      </c>
+      <c r="U209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -13913,9 +14543,12 @@
         <v>0.11991</v>
       </c>
       <c r="S210" s="1" t="n">
+        <v>0.12002</v>
+      </c>
+      <c r="T210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="T210" s="1" t="n">
+      <c r="U210" s="1" t="n">
         <v>0.11955</v>
       </c>
     </row>
@@ -13977,9 +14610,12 @@
         <v>0.1808</v>
       </c>
       <c r="S211" s="1" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="T211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="T211" s="1" t="n">
+      <c r="U211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -14041,9 +14677,12 @@
         <v>0.0303</v>
       </c>
       <c r="S212" s="1" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="T212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="T212" s="1" t="n">
+      <c r="U212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -14105,9 +14744,12 @@
         <v>1.3966</v>
       </c>
       <c r="S213" s="1" t="n">
+        <v>1.3966</v>
+      </c>
+      <c r="T213" s="1" t="n">
         <v>1.3979</v>
       </c>
-      <c r="T213" s="1" t="n">
+      <c r="U213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -14169,9 +14811,12 @@
         <v>0.05653</v>
       </c>
       <c r="S214" s="1" t="n">
+        <v>0.05654</v>
+      </c>
+      <c r="T214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="T214" s="1" t="n">
+      <c r="U214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -14233,9 +14878,12 @@
         <v>0.04447</v>
       </c>
       <c r="S215" s="1" t="n">
+        <v>0.04426</v>
+      </c>
+      <c r="T215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="T215" s="1" t="n">
+      <c r="U215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -14297,9 +14945,12 @@
         <v>0.15053</v>
       </c>
       <c r="S216" s="1" t="n">
+        <v>0.15068</v>
+      </c>
+      <c r="T216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="T216" s="1" t="n">
+      <c r="U216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -14364,6 +15015,9 @@
         <v>0.074</v>
       </c>
       <c r="T217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="U217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -14425,9 +15079,12 @@
         <v>0.00267</v>
       </c>
       <c r="S218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="T218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="T218" s="1" t="n">
+      <c r="U218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -14489,9 +15146,12 @@
         <v>0.01696</v>
       </c>
       <c r="S219" s="1" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="T219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="T219" s="1" t="n">
+      <c r="U219" s="1" t="n">
         <v>0.01696</v>
       </c>
     </row>
@@ -14553,9 +15213,12 @@
         <v>0.05504</v>
       </c>
       <c r="S220" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="T220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="T220" s="1" t="n">
+      <c r="U220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -14617,9 +15280,12 @@
         <v>0.02187</v>
       </c>
       <c r="S221" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="T221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="T221" s="1" t="n">
+      <c r="U221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -14681,10 +15347,13 @@
         <v>0.00924</v>
       </c>
       <c r="S222" s="1" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="T222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="T222" s="1" t="n">
-        <v>0.00924</v>
+      <c r="U222" s="1" t="n">
+        <v>0.00923</v>
       </c>
     </row>
     <row r="223">
@@ -14745,9 +15414,12 @@
         <v>0.0163</v>
       </c>
       <c r="S223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="T223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="T223" s="1" t="n">
+      <c r="U223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -14809,9 +15481,12 @@
         <v>0.03836</v>
       </c>
       <c r="S224" s="1" t="n">
-        <v>0.03841</v>
+        <v>0.03843</v>
       </c>
       <c r="T224" s="1" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="U224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -14873,9 +15548,12 @@
         <v>0.001513</v>
       </c>
       <c r="S225" s="1" t="n">
+        <v>0.001514</v>
+      </c>
+      <c r="T225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="T225" s="1" t="n">
+      <c r="U225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -14937,9 +15615,12 @@
         <v>27.25</v>
       </c>
       <c r="S226" s="1" t="n">
-        <v>27.25</v>
+        <v>27.31</v>
       </c>
       <c r="T226" s="1" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="U226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -15001,10 +15682,13 @@
         <v>0.07009</v>
       </c>
       <c r="S227" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="T227" s="1" t="n">
-        <v>0.07009</v>
+      <c r="U227" s="1" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="228">
@@ -15065,9 +15749,12 @@
         <v>0.3113</v>
       </c>
       <c r="S228" s="1" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="T228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="T228" s="1" t="n">
+      <c r="U228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -15129,9 +15816,12 @@
         <v>18.37</v>
       </c>
       <c r="S229" s="1" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="T229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="T229" s="1" t="n">
+      <c r="U229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -15193,9 +15883,12 @@
         <v>0.01914</v>
       </c>
       <c r="S230" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="T230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="T230" s="1" t="n">
+      <c r="U230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -15257,9 +15950,12 @@
         <v>0.01214</v>
       </c>
       <c r="S231" s="1" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="T231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="T231" s="1" t="n">
+      <c r="U231" s="1" t="n">
         <v>0.01214</v>
       </c>
     </row>
@@ -15321,10 +16017,13 @@
         <v>0.2271</v>
       </c>
       <c r="S232" s="1" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="T232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="T232" s="1" t="n">
-        <v>0.2271</v>
+      <c r="U232" s="1" t="n">
+        <v>0.2269</v>
       </c>
     </row>
     <row r="233">
@@ -15385,9 +16084,12 @@
         <v>0.07073</v>
       </c>
       <c r="S233" s="1" t="n">
+        <v>0.07074999999999999</v>
+      </c>
+      <c r="T233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="T233" s="1" t="n">
+      <c r="U233" s="1" t="n">
         <v>0.07073</v>
       </c>
     </row>
@@ -15449,9 +16151,12 @@
         <v>0.1703</v>
       </c>
       <c r="S234" s="1" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="T234" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="T234" s="1" t="n">
+      <c r="U234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -15513,9 +16218,12 @@
         <v>0.025</v>
       </c>
       <c r="S235" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="T235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="T235" s="1" t="n">
+      <c r="U235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -15577,9 +16285,12 @@
         <v>0.03001</v>
       </c>
       <c r="S236" s="1" t="n">
+        <v>0.02998</v>
+      </c>
+      <c r="T236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="T236" s="1" t="n">
+      <c r="U236" s="1" t="n">
         <v>0.02993</v>
       </c>
     </row>
@@ -15641,9 +16352,12 @@
         <v>2.016</v>
       </c>
       <c r="S237" s="1" t="n">
-        <v>2.016</v>
+        <v>2.029</v>
       </c>
       <c r="T237" s="1" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="U237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -15705,9 +16419,12 @@
         <v>0.4235</v>
       </c>
       <c r="S238" s="1" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="T238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="T238" s="1" t="n">
+      <c r="U238" s="1" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -15769,9 +16486,12 @@
         <v>0.03315</v>
       </c>
       <c r="S239" s="1" t="n">
+        <v>0.03316</v>
+      </c>
+      <c r="T239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="T239" s="1" t="n">
+      <c r="U239" s="1" t="n">
         <v>0.03315</v>
       </c>
     </row>
@@ -15833,9 +16553,12 @@
         <v>0.03393</v>
       </c>
       <c r="S240" s="1" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="T240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="T240" s="1" t="n">
+      <c r="U240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -15897,9 +16620,12 @@
         <v>0.000751</v>
       </c>
       <c r="S241" s="1" t="n">
+        <v>0.000749</v>
+      </c>
+      <c r="T241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="T241" s="1" t="n">
+      <c r="U241" s="1" t="n">
         <v>0.0007489</v>
       </c>
     </row>
@@ -15961,9 +16687,12 @@
         <v>0.1823</v>
       </c>
       <c r="S242" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="T242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="T242" s="1" t="n">
+      <c r="U242" s="1" t="n">
         <v>0.1823</v>
       </c>
     </row>
@@ -16025,10 +16754,13 @@
         <v>0.014721</v>
       </c>
       <c r="S243" s="1" t="n">
+        <v>0.014706</v>
+      </c>
+      <c r="T243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="T243" s="1" t="n">
-        <v>0.014721</v>
+      <c r="U243" s="1" t="n">
+        <v>0.014706</v>
       </c>
     </row>
     <row r="244">
@@ -16089,10 +16821,13 @@
         <v>3.01e-05</v>
       </c>
       <c r="S244" s="1" t="n">
+        <v>2.99e-05</v>
+      </c>
+      <c r="T244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="T244" s="1" t="n">
-        <v>3.01e-05</v>
+      <c r="U244" s="1" t="n">
+        <v>2.99e-05</v>
       </c>
     </row>
     <row r="245">
@@ -16153,9 +16888,12 @@
         <v>0.03502</v>
       </c>
       <c r="S245" s="1" t="n">
+        <v>0.03508</v>
+      </c>
+      <c r="T245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="T245" s="1" t="n">
+      <c r="U245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -16217,9 +16955,12 @@
         <v>0.08018</v>
       </c>
       <c r="S246" s="1" t="n">
+        <v>0.08026</v>
+      </c>
+      <c r="T246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="T246" s="1" t="n">
+      <c r="U246" s="1" t="n">
         <v>0.08018</v>
       </c>
     </row>
@@ -16281,10 +17022,13 @@
         <v>0.007281</v>
       </c>
       <c r="S247" s="1" t="n">
+        <v>0.007172</v>
+      </c>
+      <c r="T247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="T247" s="1" t="n">
-        <v>0.007229</v>
+      <c r="U247" s="1" t="n">
+        <v>0.007172</v>
       </c>
     </row>
     <row r="248">
@@ -16345,10 +17089,13 @@
         <v>0.09372</v>
       </c>
       <c r="S248" s="1" t="n">
+        <v>0.09239</v>
+      </c>
+      <c r="T248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="T248" s="1" t="n">
-        <v>0.09372</v>
+      <c r="U248" s="1" t="n">
+        <v>0.09239</v>
       </c>
     </row>
     <row r="249">
@@ -16409,9 +17156,12 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="S249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="T249" s="1" t="n">
+      <c r="U249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -16473,9 +17223,12 @@
         <v>0.03469</v>
       </c>
       <c r="S250" s="1" t="n">
+        <v>0.03471</v>
+      </c>
+      <c r="T250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="T250" s="1" t="n">
+      <c r="U250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -16537,10 +17290,13 @@
         <v>0.03916</v>
       </c>
       <c r="S251" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="T251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="T251" s="1" t="n">
-        <v>0.03915</v>
+      <c r="U251" s="1" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="252">
@@ -16601,9 +17357,12 @@
         <v>0.0876</v>
       </c>
       <c r="S252" s="1" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="T252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="T252" s="1" t="n">
+      <c r="U252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -16665,9 +17424,12 @@
         <v>4.072</v>
       </c>
       <c r="S253" s="1" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="T253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="T253" s="1" t="n">
+      <c r="U253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -16729,9 +17491,12 @@
         <v>0.1866</v>
       </c>
       <c r="S254" s="1" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="T254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="T254" s="1" t="n">
+      <c r="U254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -16793,9 +17558,12 @@
         <v>0.07174</v>
       </c>
       <c r="S255" s="1" t="n">
+        <v>0.07174</v>
+      </c>
+      <c r="T255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="T255" s="1" t="n">
+      <c r="U255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -16857,9 +17625,12 @@
         <v>0.01825</v>
       </c>
       <c r="S256" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="T256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="T256" s="1" t="n">
+      <c r="U256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -16921,9 +17692,12 @@
         <v>5.934</v>
       </c>
       <c r="S257" s="1" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="T257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="T257" s="1" t="n">
+      <c r="U257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -16985,9 +17759,12 @@
         <v>0.2599</v>
       </c>
       <c r="S258" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="T258" s="1" t="n">
+      <c r="U258" s="1" t="n">
         <v>0.2599</v>
       </c>
     </row>
@@ -17049,9 +17826,12 @@
         <v>0.1352</v>
       </c>
       <c r="S259" s="1" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="T259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="T259" s="1" t="n">
+      <c r="U259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -17113,9 +17893,12 @@
         <v>0.30794</v>
       </c>
       <c r="S260" s="1" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="T260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="T260" s="1" t="n">
+      <c r="U260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -17177,9 +17960,12 @@
         <v>0.09875</v>
       </c>
       <c r="S261" s="1" t="n">
+        <v>0.09871000000000001</v>
+      </c>
+      <c r="T261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="T261" s="1" t="n">
+      <c r="U261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -17241,10 +18027,13 @@
         <v>0.5382</v>
       </c>
       <c r="S262" s="1" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="T262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="T262" s="1" t="n">
-        <v>0.538</v>
+      <c r="U262" s="1" t="n">
+        <v>0.5377999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -17305,10 +18094,13 @@
         <v>0.2885</v>
       </c>
       <c r="S263" s="1" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="T263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="T263" s="1" t="n">
-        <v>0.2885</v>
+      <c r="U263" s="1" t="n">
+        <v>0.2877</v>
       </c>
     </row>
     <row r="264">
@@ -17369,9 +18161,12 @@
         <v>0.961</v>
       </c>
       <c r="S264" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="T264" s="1" t="n">
         <v>0.983</v>
       </c>
-      <c r="T264" s="1" t="n">
+      <c r="U264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -17433,9 +18228,12 @@
         <v>0.5367</v>
       </c>
       <c r="S265" s="1" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="T265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="T265" s="1" t="n">
+      <c r="U265" s="1" t="n">
         <v>0.5367</v>
       </c>
     </row>
@@ -17497,9 +18295,12 @@
         <v>0.07341</v>
       </c>
       <c r="S266" s="1" t="n">
+        <v>0.07341</v>
+      </c>
+      <c r="T266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="T266" s="1" t="n">
+      <c r="U266" s="1" t="n">
         <v>0.07341</v>
       </c>
     </row>
@@ -17561,9 +18362,12 @@
         <v>0.02144</v>
       </c>
       <c r="S267" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="T267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="T267" s="1" t="n">
+      <c r="U267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -17625,9 +18429,12 @@
         <v>0.01603</v>
       </c>
       <c r="S268" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="T268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="T268" s="1" t="n">
+      <c r="U268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -17689,9 +18496,12 @@
         <v>0.003795</v>
       </c>
       <c r="S269" s="1" t="n">
+        <v>0.003787</v>
+      </c>
+      <c r="T269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="T269" s="1" t="n">
+      <c r="U269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -17753,10 +18563,13 @@
         <v>0.00757</v>
       </c>
       <c r="S270" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="T270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="T270" s="1" t="n">
-        <v>0.00757</v>
+      <c r="U270" s="1" t="n">
+        <v>0.00754</v>
       </c>
     </row>
     <row r="271">
@@ -17817,9 +18630,12 @@
         <v>0.0547</v>
       </c>
       <c r="S271" s="1" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="T271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="T271" s="1" t="n">
+      <c r="U271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -17881,9 +18697,12 @@
         <v>2.267</v>
       </c>
       <c r="S272" s="1" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="T272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="T272" s="1" t="n">
+      <c r="U272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -17945,9 +18764,12 @@
         <v>0.05483</v>
       </c>
       <c r="S273" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="T273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="T273" s="1" t="n">
+      <c r="U273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -18009,9 +18831,12 @@
         <v>0.02328</v>
       </c>
       <c r="S274" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="T274" s="1" t="n">
         <v>0.02336</v>
       </c>
-      <c r="T274" s="1" t="n">
+      <c r="U274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -18073,9 +18898,12 @@
         <v>1.172</v>
       </c>
       <c r="S275" s="1" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="T275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="T275" s="1" t="n">
+      <c r="U275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -18137,9 +18965,12 @@
         <v>0.2718</v>
       </c>
       <c r="S276" s="1" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="T276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="T276" s="1" t="n">
+      <c r="U276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -18201,10 +19032,13 @@
         <v>0.923</v>
       </c>
       <c r="S277" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="T277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="T277" s="1" t="n">
-        <v>0.923</v>
+      <c r="U277" s="1" t="n">
+        <v>0.919</v>
       </c>
     </row>
     <row r="278">
@@ -18265,10 +19099,13 @@
         <v>0.6237</v>
       </c>
       <c r="S278" s="1" t="n">
+        <v>0.6218</v>
+      </c>
+      <c r="T278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="T278" s="1" t="n">
-        <v>0.6221</v>
+      <c r="U278" s="1" t="n">
+        <v>0.6218</v>
       </c>
     </row>
     <row r="279">
@@ -18329,10 +19166,13 @@
         <v>0.001331</v>
       </c>
       <c r="S279" s="1" t="n">
+        <v>0.001326</v>
+      </c>
+      <c r="T279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="T279" s="1" t="n">
-        <v>0.001331</v>
+      <c r="U279" s="1" t="n">
+        <v>0.001326</v>
       </c>
     </row>
     <row r="280">
@@ -18396,6 +19236,9 @@
         <v>0.005601</v>
       </c>
       <c r="T280" s="1" t="n">
+        <v>0.005601</v>
+      </c>
+      <c r="U280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -18457,9 +19300,12 @@
         <v>1.515</v>
       </c>
       <c r="S281" s="1" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="T281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="T281" s="1" t="n">
+      <c r="U281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -18521,9 +19367,12 @@
         <v>28.25</v>
       </c>
       <c r="S282" s="1" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="T282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="T282" s="1" t="n">
+      <c r="U282" s="1" t="n">
         <v>28.25</v>
       </c>
     </row>
@@ -18585,9 +19434,12 @@
         <v>0.12788</v>
       </c>
       <c r="S283" s="1" t="n">
+        <v>0.12797</v>
+      </c>
+      <c r="T283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="T283" s="1" t="n">
+      <c r="U283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -18649,10 +19501,13 @@
         <v>0.01103</v>
       </c>
       <c r="S284" s="1" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="T284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="T284" s="1" t="n">
-        <v>0.01103</v>
+      <c r="U284" s="1" t="n">
+        <v>0.01102</v>
       </c>
     </row>
     <row r="285">
@@ -18713,9 +19568,12 @@
         <v>6.533</v>
       </c>
       <c r="S285" s="1" t="n">
+        <v>6.529</v>
+      </c>
+      <c r="T285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="T285" s="1" t="n">
+      <c r="U285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -18777,9 +19635,12 @@
         <v>0.01831</v>
       </c>
       <c r="S286" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="T286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="T286" s="1" t="n">
+      <c r="U286" s="1" t="n">
         <v>0.01831</v>
       </c>
     </row>
@@ -18841,9 +19702,12 @@
         <v>0.008312999999999999</v>
       </c>
       <c r="S287" s="1" t="n">
+        <v>0.008331</v>
+      </c>
+      <c r="T287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="T287" s="1" t="n">
+      <c r="U287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -18905,9 +19769,12 @@
         <v>0.3817</v>
       </c>
       <c r="S288" s="1" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="T288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="T288" s="1" t="n">
+      <c r="U288" s="1" t="n">
         <v>0.3803</v>
       </c>
     </row>
@@ -18969,10 +19836,13 @@
         <v>0.009771</v>
       </c>
       <c r="S289" s="1" t="n">
+        <v>0.00974</v>
+      </c>
+      <c r="T289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="T289" s="1" t="n">
-        <v>0.009771</v>
+      <c r="U289" s="1" t="n">
+        <v>0.00974</v>
       </c>
     </row>
     <row r="290">
@@ -19033,9 +19903,12 @@
         <v>0.02585</v>
       </c>
       <c r="S290" s="1" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="T290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="T290" s="1" t="n">
+      <c r="U290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -19097,9 +19970,12 @@
         <v>0.096</v>
       </c>
       <c r="S291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="T291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="T291" s="1" t="n">
+      <c r="U291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -19161,9 +20037,12 @@
         <v>0.28748</v>
       </c>
       <c r="S292" s="1" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="T292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="T292" s="1" t="n">
+      <c r="U292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -19225,10 +20104,13 @@
         <v>0.01534</v>
       </c>
       <c r="S293" s="1" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="T293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="T293" s="1" t="n">
-        <v>0.01533</v>
+      <c r="U293" s="1" t="n">
+        <v>0.01528</v>
       </c>
     </row>
     <row r="294">
@@ -19289,9 +20171,12 @@
         <v>0.003381</v>
       </c>
       <c r="S294" s="1" t="n">
+        <v>0.003385</v>
+      </c>
+      <c r="T294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="T294" s="1" t="n">
+      <c r="U294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -19353,9 +20238,12 @@
         <v>0.042519</v>
       </c>
       <c r="S295" s="1" t="n">
+        <v>0.042439</v>
+      </c>
+      <c r="T295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="T295" s="1" t="n">
+      <c r="U295" s="1" t="n">
         <v>0.042232</v>
       </c>
     </row>
@@ -19417,9 +20305,12 @@
         <v>0.02965</v>
       </c>
       <c r="S296" s="1" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="T296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="T296" s="1" t="n">
+      <c r="U296" s="1" t="n">
         <v>0.02894</v>
       </c>
     </row>
@@ -19481,9 +20372,12 @@
         <v>0.03823</v>
       </c>
       <c r="S297" s="1" t="n">
+        <v>0.03797</v>
+      </c>
+      <c r="T297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="T297" s="1" t="n">
+      <c r="U297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -19545,9 +20439,12 @@
         <v>0.08373</v>
       </c>
       <c r="S298" s="1" t="n">
+        <v>0.08304</v>
+      </c>
+      <c r="T298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="T298" s="1" t="n">
+      <c r="U298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -19609,10 +20506,13 @@
         <v>0.00762</v>
       </c>
       <c r="S299" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="T299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="T299" s="1" t="n">
-        <v>0.00761</v>
+      <c r="U299" s="1" t="n">
+        <v>0.0076</v>
       </c>
     </row>
     <row r="300">
@@ -19673,10 +20573,13 @@
         <v>0.01498</v>
       </c>
       <c r="S300" s="1" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="T300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="T300" s="1" t="n">
-        <v>0.01498</v>
+      <c r="U300" s="1" t="n">
+        <v>0.01496</v>
       </c>
     </row>
     <row r="301">
@@ -19737,9 +20640,12 @@
         <v>0.14</v>
       </c>
       <c r="S301" s="1" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="T301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="T301" s="1" t="n">
+      <c r="U301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -19801,9 +20707,12 @@
         <v>0.0006217</v>
       </c>
       <c r="S302" s="1" t="n">
+        <v>0.0006255</v>
+      </c>
+      <c r="T302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="T302" s="1" t="n">
+      <c r="U302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -19865,10 +20774,13 @@
         <v>0.06212</v>
       </c>
       <c r="S303" s="1" t="n">
+        <v>0.06207</v>
+      </c>
+      <c r="T303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="T303" s="1" t="n">
-        <v>0.0621</v>
+      <c r="U303" s="1" t="n">
+        <v>0.06207</v>
       </c>
     </row>
     <row r="304">
@@ -19929,10 +20841,13 @@
         <v>0.0001624</v>
       </c>
       <c r="S304" s="1" t="n">
+        <v>0.000162</v>
+      </c>
+      <c r="T304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="T304" s="1" t="n">
-        <v>0.0001623</v>
+      <c r="U304" s="1" t="n">
+        <v>0.000162</v>
       </c>
     </row>
     <row r="305">
@@ -19993,10 +20908,13 @@
         <v>0.06104</v>
       </c>
       <c r="S305" s="1" t="n">
+        <v>0.06071</v>
+      </c>
+      <c r="T305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="T305" s="1" t="n">
-        <v>0.06076</v>
+      <c r="U305" s="1" t="n">
+        <v>0.06071</v>
       </c>
     </row>
     <row r="306">
@@ -20057,9 +20975,12 @@
         <v>0.022283</v>
       </c>
       <c r="S306" s="1" t="n">
+        <v>0.022341</v>
+      </c>
+      <c r="T306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="T306" s="1" t="n">
+      <c r="U306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -20121,10 +21042,13 @@
         <v>0.02331</v>
       </c>
       <c r="S307" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="T307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="T307" s="1" t="n">
-        <v>0.02331</v>
+      <c r="U307" s="1" t="n">
+        <v>0.02278</v>
       </c>
     </row>
     <row r="308">
@@ -20185,9 +21109,12 @@
         <v>0.000411</v>
       </c>
       <c r="S308" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="T308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="T308" s="1" t="n">
+      <c r="U308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -20249,9 +21176,12 @@
         <v>0.0896</v>
       </c>
       <c r="S309" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="T309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="T309" s="1" t="n">
+      <c r="U309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -20313,9 +21243,12 @@
         <v>0.371</v>
       </c>
       <c r="S310" s="1" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="T310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="T310" s="1" t="n">
+      <c r="U310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -20377,9 +21310,12 @@
         <v>0.0354</v>
       </c>
       <c r="S311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="T311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="T311" s="1" t="n">
+      <c r="U311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -20441,10 +21377,13 @@
         <v>0.02423</v>
       </c>
       <c r="S312" s="1" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="T312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="T312" s="1" t="n">
-        <v>0.02423</v>
+      <c r="U312" s="1" t="n">
+        <v>0.02415</v>
       </c>
     </row>
     <row r="313">
@@ -20505,10 +21444,13 @@
         <v>0.0409</v>
       </c>
       <c r="S313" s="1" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="T313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="T313" s="1" t="n">
-        <v>0.0409</v>
+      <c r="U313" s="1" t="n">
+        <v>0.04087</v>
       </c>
     </row>
     <row r="314">
@@ -20569,10 +21511,13 @@
         <v>3.933</v>
       </c>
       <c r="S314" s="1" t="n">
+        <v>3.932</v>
+      </c>
+      <c r="T314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="T314" s="1" t="n">
-        <v>3.933</v>
+      <c r="U314" s="1" t="n">
+        <v>3.932</v>
       </c>
     </row>
     <row r="315">
@@ -20633,9 +21578,12 @@
         <v>0.1589</v>
       </c>
       <c r="S315" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="T315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="T315" s="1" t="n">
+      <c r="U315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -20697,9 +21645,12 @@
         <v>0.09092</v>
       </c>
       <c r="S316" s="1" t="n">
+        <v>0.09191000000000001</v>
+      </c>
+      <c r="T316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="T316" s="1" t="n">
+      <c r="U316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -20761,9 +21712,12 @@
         <v>0.06809</v>
       </c>
       <c r="S317" s="1" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="T317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="T317" s="1" t="n">
+      <c r="U317" s="1" t="n">
         <v>0.06791999999999999</v>
       </c>
     </row>
@@ -20825,9 +21779,12 @@
         <v>0.012382</v>
       </c>
       <c r="S318" s="1" t="n">
+        <v>0.012449</v>
+      </c>
+      <c r="T318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="T318" s="1" t="n">
+      <c r="U318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -20889,10 +21846,13 @@
         <v>0.001131</v>
       </c>
       <c r="S319" s="1" t="n">
+        <v>0.00113</v>
+      </c>
+      <c r="T319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="T319" s="1" t="n">
-        <v>0.001131</v>
+      <c r="U319" s="1" t="n">
+        <v>0.00113</v>
       </c>
     </row>
     <row r="320">
@@ -20953,9 +21913,12 @@
         <v>0.0629</v>
       </c>
       <c r="S320" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="T320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="T320" s="1" t="n">
+      <c r="U320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -21017,9 +21980,12 @@
         <v>0.00524</v>
       </c>
       <c r="S321" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="T321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="T321" s="1" t="n">
+      <c r="U321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -21081,9 +22047,12 @@
         <v>0.111</v>
       </c>
       <c r="S322" s="1" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="T322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="T322" s="1" t="n">
+      <c r="U322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -21145,9 +22114,12 @@
         <v>0.04413</v>
       </c>
       <c r="S323" s="1" t="n">
+        <v>0.04397</v>
+      </c>
+      <c r="T323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="T323" s="1" t="n">
+      <c r="U323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -21209,9 +22181,12 @@
         <v>0.01784</v>
       </c>
       <c r="S324" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="T324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="T324" s="1" t="n">
+      <c r="U324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -21273,9 +22248,12 @@
         <v>0.005633</v>
       </c>
       <c r="S325" s="1" t="n">
+        <v>0.005635</v>
+      </c>
+      <c r="T325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="T325" s="1" t="n">
+      <c r="U325" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -21337,9 +22315,12 @@
         <v>0.001751</v>
       </c>
       <c r="S326" s="1" t="n">
+        <v>0.001753</v>
+      </c>
+      <c r="T326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="T326" s="1" t="n">
+      <c r="U326" s="1" t="n">
         <v>0.001751</v>
       </c>
     </row>
@@ -21401,9 +22382,12 @@
         <v>0.04016</v>
       </c>
       <c r="S327" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="T327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="T327" s="1" t="n">
+      <c r="U327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -21465,9 +22449,12 @@
         <v>0.05353</v>
       </c>
       <c r="S328" s="1" t="n">
+        <v>0.053525</v>
+      </c>
+      <c r="T328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="T328" s="1" t="n">
+      <c r="U328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -21529,9 +22516,12 @@
         <v>0.2771</v>
       </c>
       <c r="S329" s="1" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="T329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="T329" s="1" t="n">
+      <c r="U329" s="1" t="n">
         <v>0.2771</v>
       </c>
     </row>
@@ -21593,10 +22583,13 @@
         <v>0.1586</v>
       </c>
       <c r="S330" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="T330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="T330" s="1" t="n">
-        <v>0.1586</v>
+      <c r="U330" s="1" t="n">
+        <v>0.1585</v>
       </c>
     </row>
     <row r="331">
@@ -21657,9 +22650,12 @@
         <v>0.05349</v>
       </c>
       <c r="S331" s="1" t="n">
+        <v>0.05352</v>
+      </c>
+      <c r="T331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="T331" s="1" t="n">
+      <c r="U331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -21721,9 +22717,12 @@
         <v>0.3604</v>
       </c>
       <c r="S332" s="1" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="T332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="T332" s="1" t="n">
+      <c r="U332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -21788,6 +22787,9 @@
         <v>0.0306</v>
       </c>
       <c r="T333" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="U333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -21849,9 +22851,12 @@
         <v>0.01783</v>
       </c>
       <c r="S334" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="T334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="T334" s="1" t="n">
+      <c r="U334" s="1" t="n">
         <v>0.01751</v>
       </c>
     </row>
@@ -21913,9 +22918,12 @@
         <v>0.0577</v>
       </c>
       <c r="S335" s="1" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="T335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="T335" s="1" t="n">
+      <c r="U335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -21977,10 +22985,13 @@
         <v>0.09031</v>
       </c>
       <c r="S336" s="1" t="n">
+        <v>0.09025</v>
+      </c>
+      <c r="T336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="T336" s="1" t="n">
-        <v>0.09031</v>
+      <c r="U336" s="1" t="n">
+        <v>0.09025</v>
       </c>
     </row>
     <row r="337">
@@ -22041,9 +23052,12 @@
         <v>0.18019</v>
       </c>
       <c r="S337" s="1" t="n">
+        <v>0.18058</v>
+      </c>
+      <c r="T337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="T337" s="1" t="n">
+      <c r="U337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -22105,9 +23119,12 @@
         <v>0.02074</v>
       </c>
       <c r="S338" s="1" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="T338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="T338" s="1" t="n">
+      <c r="U338" s="1" t="n">
         <v>0.02074</v>
       </c>
     </row>
@@ -22169,9 +23186,12 @@
         <v>0.1317</v>
       </c>
       <c r="S339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="T339" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="T339" s="1" t="n">
+      <c r="U339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -22233,9 +23253,12 @@
         <v>0.007957000000000001</v>
       </c>
       <c r="S340" s="1" t="n">
+        <v>0.007963</v>
+      </c>
+      <c r="T340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="T340" s="1" t="n">
+      <c r="U340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -22297,9 +23320,12 @@
         <v>4.393</v>
       </c>
       <c r="S341" s="1" t="n">
+        <v>4.394</v>
+      </c>
+      <c r="T341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="T341" s="1" t="n">
+      <c r="U341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -22361,9 +23387,12 @@
         <v>0.19012</v>
       </c>
       <c r="S342" s="1" t="n">
+        <v>0.18979</v>
+      </c>
+      <c r="T342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="T342" s="1" t="n">
+      <c r="U342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -22425,9 +23454,12 @@
         <v>0.08291</v>
       </c>
       <c r="S343" s="1" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="T343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="T343" s="1" t="n">
+      <c r="U343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -22489,9 +23521,12 @@
         <v>0.1816</v>
       </c>
       <c r="S344" s="1" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="T344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="T344" s="1" t="n">
+      <c r="U344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -22553,9 +23588,12 @@
         <v>0.003222</v>
       </c>
       <c r="S345" s="1" t="n">
+        <v>0.003223</v>
+      </c>
+      <c r="T345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="T345" s="1" t="n">
+      <c r="U345" s="1" t="n">
         <v>0.003222</v>
       </c>
     </row>
@@ -22617,9 +23655,12 @@
         <v>0.09134</v>
       </c>
       <c r="S346" s="1" t="n">
+        <v>0.09107</v>
+      </c>
+      <c r="T346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="T346" s="1" t="n">
+      <c r="U346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -22681,9 +23722,12 @@
         <v>2.235</v>
       </c>
       <c r="S347" s="1" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="T347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="T347" s="1" t="n">
+      <c r="U347" s="1" t="n">
         <v>2.235</v>
       </c>
     </row>
@@ -22745,9 +23789,12 @@
         <v>0.3031</v>
       </c>
       <c r="S348" s="1" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="T348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="T348" s="1" t="n">
+      <c r="U348" s="1" t="n">
         <v>0.3027</v>
       </c>
     </row>
@@ -22809,9 +23856,12 @@
         <v>0.02954</v>
       </c>
       <c r="S349" s="1" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="T349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="T349" s="1" t="n">
+      <c r="U349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -22873,9 +23923,12 @@
         <v>0.1275</v>
       </c>
       <c r="S350" s="1" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="T350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="T350" s="1" t="n">
+      <c r="U350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -22937,10 +23990,13 @@
         <v>0.06612999999999999</v>
       </c>
       <c r="S351" s="1" t="n">
+        <v>0.06607</v>
+      </c>
+      <c r="T351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="T351" s="1" t="n">
-        <v>0.06612999999999999</v>
+      <c r="U351" s="1" t="n">
+        <v>0.06607</v>
       </c>
     </row>
     <row r="352">
@@ -23001,10 +24057,13 @@
         <v>0.06227</v>
       </c>
       <c r="S352" s="1" t="n">
+        <v>0.06225</v>
+      </c>
+      <c r="T352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="T352" s="1" t="n">
-        <v>0.06227</v>
+      <c r="U352" s="1" t="n">
+        <v>0.06225</v>
       </c>
     </row>
     <row r="353">
@@ -23065,10 +24124,13 @@
         <v>0.06283</v>
       </c>
       <c r="S353" s="1" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="T353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="T353" s="1" t="n">
-        <v>0.06283</v>
+      <c r="U353" s="1" t="n">
+        <v>0.06270000000000001</v>
       </c>
     </row>
     <row r="354">
@@ -23129,9 +24191,12 @@
         <v>0.10457</v>
       </c>
       <c r="S354" s="1" t="n">
+        <v>0.10502</v>
+      </c>
+      <c r="T354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="T354" s="1" t="n">
+      <c r="U354" s="1" t="n">
         <v>0.10393</v>
       </c>
     </row>
@@ -23193,9 +24258,12 @@
         <v>0.0898</v>
       </c>
       <c r="S355" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="T355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="T355" s="1" t="n">
+      <c r="U355" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -23257,10 +24325,13 @@
         <v>0.06915</v>
       </c>
       <c r="S356" s="1" t="n">
+        <v>0.06905</v>
+      </c>
+      <c r="T356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="T356" s="1" t="n">
-        <v>0.06915</v>
+      <c r="U356" s="1" t="n">
+        <v>0.06905</v>
       </c>
     </row>
     <row r="357">
@@ -23321,10 +24392,13 @@
         <v>0.4505</v>
       </c>
       <c r="S357" s="1" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="T357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="T357" s="1" t="n">
-        <v>0.4505</v>
+      <c r="U357" s="1" t="n">
+        <v>0.4504</v>
       </c>
     </row>
     <row r="358">
@@ -23385,10 +24459,13 @@
         <v>0.03442</v>
       </c>
       <c r="S358" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="T358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="T358" s="1" t="n">
-        <v>0.03442</v>
+      <c r="U358" s="1" t="n">
+        <v>0.03441</v>
       </c>
     </row>
     <row r="359">
@@ -23449,10 +24526,13 @@
         <v>0.0146</v>
       </c>
       <c r="S359" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="T359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="T359" s="1" t="n">
-        <v>0.0146</v>
+      <c r="U359" s="1" t="n">
+        <v>0.01454</v>
       </c>
     </row>
     <row r="360">
@@ -23513,9 +24593,12 @@
         <v>0.13301</v>
       </c>
       <c r="S360" s="1" t="n">
+        <v>0.13328</v>
+      </c>
+      <c r="T360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="T360" s="1" t="n">
+      <c r="U360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -23577,9 +24660,12 @@
         <v>0.0005865</v>
       </c>
       <c r="S361" s="1" t="n">
+        <v>0.0005855</v>
+      </c>
+      <c r="T361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="T361" s="1" t="n">
+      <c r="U361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -23641,10 +24727,13 @@
         <v>0.03864</v>
       </c>
       <c r="S362" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="T362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="T362" s="1" t="n">
-        <v>0.03855</v>
+      <c r="U362" s="1" t="n">
+        <v>0.03824</v>
       </c>
     </row>
     <row r="363">
@@ -23705,9 +24794,12 @@
         <v>3.222</v>
       </c>
       <c r="S363" s="1" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="T363" s="1" t="n">
+      <c r="U363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -23769,9 +24861,12 @@
         <v>0.1632</v>
       </c>
       <c r="S364" s="1" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="T364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="T364" s="1" t="n">
+      <c r="U364" s="1" t="n">
         <v>0.1632</v>
       </c>
     </row>
@@ -23833,9 +24928,12 @@
         <v>0.1128</v>
       </c>
       <c r="S365" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="T365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="T365" s="1" t="n">
+      <c r="U365" s="1" t="n">
         <v>0.1128</v>
       </c>
     </row>
@@ -23897,10 +24995,13 @@
         <v>0.0006349</v>
       </c>
       <c r="S366" s="1" t="n">
+        <v>0.000634</v>
+      </c>
+      <c r="T366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="T366" s="1" t="n">
-        <v>0.0006349</v>
+      <c r="U366" s="1" t="n">
+        <v>0.000634</v>
       </c>
     </row>
     <row r="367">
@@ -23961,9 +25062,12 @@
         <v>0.05956</v>
       </c>
       <c r="S367" s="1" t="n">
+        <v>0.05941</v>
+      </c>
+      <c r="T367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="T367" s="1" t="n">
+      <c r="U367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -24025,10 +25129,13 @@
         <v>0.08135000000000001</v>
       </c>
       <c r="S368" s="1" t="n">
+        <v>0.08122</v>
+      </c>
+      <c r="T368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="T368" s="1" t="n">
-        <v>0.08135000000000001</v>
+      <c r="U368" s="1" t="n">
+        <v>0.08122</v>
       </c>
     </row>
     <row r="369">
@@ -24089,10 +25196,13 @@
         <v>0.03934</v>
       </c>
       <c r="S369" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="T369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="T369" s="1" t="n">
-        <v>0.0393</v>
+      <c r="U369" s="1" t="n">
+        <v>0.03927</v>
       </c>
     </row>
     <row r="370">
@@ -24153,9 +25263,12 @@
         <v>3.7</v>
       </c>
       <c r="S370" s="1" t="n">
+        <v>3.686</v>
+      </c>
+      <c r="T370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="T370" s="1" t="n">
+      <c r="U370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -24217,9 +25330,12 @@
         <v>0.1208</v>
       </c>
       <c r="S371" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="T371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="T371" s="1" t="n">
+      <c r="U371" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -24281,10 +25397,13 @@
         <v>0.01472</v>
       </c>
       <c r="S372" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="T372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="T372" s="1" t="n">
-        <v>0.01471</v>
+      <c r="U372" s="1" t="n">
+        <v>0.01467</v>
       </c>
     </row>
     <row r="373">
@@ -24345,9 +25464,12 @@
         <v>0.022</v>
       </c>
       <c r="S373" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="T373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="T373" s="1" t="n">
+      <c r="U373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -24412,6 +25534,9 @@
         <v>1.8671</v>
       </c>
       <c r="T374" s="1" t="n">
+        <v>1.8671</v>
+      </c>
+      <c r="U374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -24473,9 +25598,12 @@
         <v>0.02081</v>
       </c>
       <c r="S375" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="T375" s="1" t="n">
+      <c r="U375" s="1" t="n">
         <v>0.02081</v>
       </c>
     </row>
@@ -24537,9 +25665,12 @@
         <v>1.308</v>
       </c>
       <c r="S376" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="T376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="T376" s="1" t="n">
+      <c r="U376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -24601,9 +25732,12 @@
         <v>0.2819</v>
       </c>
       <c r="S377" s="1" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="T377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="T377" s="1" t="n">
+      <c r="U377" s="1" t="n">
         <v>0.2819</v>
       </c>
     </row>
@@ -24665,9 +25799,12 @@
         <v>0.01553</v>
       </c>
       <c r="S378" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="T378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="T378" s="1" t="n">
+      <c r="U378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -24729,9 +25866,12 @@
         <v>1.5281</v>
       </c>
       <c r="S379" s="1" t="n">
+        <v>1.5292</v>
+      </c>
+      <c r="T379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="T379" s="1" t="n">
+      <c r="U379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -24793,9 +25933,12 @@
         <v>6.871e-05</v>
       </c>
       <c r="S380" s="1" t="n">
+        <v>6.873e-05</v>
+      </c>
+      <c r="T380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="T380" s="1" t="n">
+      <c r="U380" s="1" t="n">
         <v>6.871e-05</v>
       </c>
     </row>
@@ -24857,9 +26000,12 @@
         <v>2.536</v>
       </c>
       <c r="S381" s="1" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="T381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="T381" s="1" t="n">
+      <c r="U381" s="1" t="n">
         <v>2.536</v>
       </c>
     </row>
@@ -24921,10 +26067,13 @@
         <v>0.06661</v>
       </c>
       <c r="S382" s="1" t="n">
+        <v>0.06646000000000001</v>
+      </c>
+      <c r="T382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="T382" s="1" t="n">
-        <v>0.06661</v>
+      <c r="U382" s="1" t="n">
+        <v>0.06646000000000001</v>
       </c>
     </row>
     <row r="383">
@@ -24985,10 +26134,13 @@
         <v>0.01683</v>
       </c>
       <c r="S383" s="1" t="n">
+        <v>0.01662</v>
+      </c>
+      <c r="T383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="T383" s="1" t="n">
-        <v>0.01683</v>
+      <c r="U383" s="1" t="n">
+        <v>0.01662</v>
       </c>
     </row>
     <row r="384">
@@ -25049,9 +26201,12 @@
         <v>0.05177</v>
       </c>
       <c r="S384" s="1" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="T384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="T384" s="1" t="n">
+      <c r="U384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -25113,9 +26268,12 @@
         <v>7.566</v>
       </c>
       <c r="S385" s="1" t="n">
+        <v>7.568</v>
+      </c>
+      <c r="T385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="T385" s="1" t="n">
+      <c r="U385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -25177,9 +26335,12 @@
         <v>0.003258</v>
       </c>
       <c r="S386" s="1" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="T386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="T386" s="1" t="n">
+      <c r="U386" s="1" t="n">
         <v>0.003258</v>
       </c>
     </row>
@@ -25241,9 +26402,12 @@
         <v>0.0003793</v>
       </c>
       <c r="S387" s="1" t="n">
+        <v>0.0003793</v>
+      </c>
+      <c r="T387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="T387" s="1" t="n">
+      <c r="U387" s="1" t="n">
         <v>0.0003793</v>
       </c>
     </row>
@@ -25305,9 +26469,12 @@
         <v>0.009469999999999999</v>
       </c>
       <c r="S388" s="1" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="T388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="T388" s="1" t="n">
+      <c r="U388" s="1" t="n">
         <v>0.00942</v>
       </c>
     </row>
@@ -25369,9 +26536,12 @@
         <v>0.2892</v>
       </c>
       <c r="S389" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="T389" s="1" t="n">
         <v>0.2904</v>
       </c>
-      <c r="T389" s="1" t="n">
+      <c r="U389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -25433,9 +26603,12 @@
         <v>0.0252</v>
       </c>
       <c r="S390" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="T390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="T390" s="1" t="n">
+      <c r="U390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -25497,9 +26670,12 @@
         <v>2.843</v>
       </c>
       <c r="S391" s="1" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="T391" s="1" t="n">
         <v>2.859</v>
       </c>
-      <c r="T391" s="1" t="n">
+      <c r="U391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -25561,9 +26737,12 @@
         <v>0.01344</v>
       </c>
       <c r="S392" s="1" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="T392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="T392" s="1" t="n">
+      <c r="U392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -25625,9 +26804,12 @@
         <v>0.00236</v>
       </c>
       <c r="S393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="T393" s="1" t="n">
         <v>0.00237</v>
       </c>
-      <c r="T393" s="1" t="n">
+      <c r="U393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -25689,9 +26871,12 @@
         <v>0.05926</v>
       </c>
       <c r="S394" s="1" t="n">
+        <v>0.05928</v>
+      </c>
+      <c r="T394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="T394" s="1" t="n">
+      <c r="U394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -25753,9 +26938,12 @@
         <v>0.0402</v>
       </c>
       <c r="S395" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="T395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="T395" s="1" t="n">
+      <c r="U395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -25817,9 +27005,12 @@
         <v>0.09288</v>
       </c>
       <c r="S396" s="1" t="n">
-        <v>0.09288</v>
+        <v>0.09291000000000001</v>
       </c>
       <c r="T396" s="1" t="n">
+        <v>0.09291000000000001</v>
+      </c>
+      <c r="U396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -25881,9 +27072,12 @@
         <v>0.1512</v>
       </c>
       <c r="S397" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="T397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="T397" s="1" t="n">
+      <c r="U397" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -25945,9 +27139,12 @@
         <v>0.927</v>
       </c>
       <c r="S398" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="T398" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="T398" s="1" t="n">
+      <c r="U398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -26009,9 +27206,12 @@
         <v>0.05213</v>
       </c>
       <c r="S399" s="1" t="n">
+        <v>0.05218</v>
+      </c>
+      <c r="T399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="T399" s="1" t="n">
+      <c r="U399" s="1" t="n">
         <v>0.05213</v>
       </c>
     </row>
@@ -26073,9 +27273,12 @@
         <v>2.504</v>
       </c>
       <c r="S400" s="1" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="T400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="T400" s="1" t="n">
+      <c r="U400" s="1" t="n">
         <v>2.504</v>
       </c>
     </row>
@@ -26137,10 +27340,13 @@
         <v>0.01774</v>
       </c>
       <c r="S401" s="1" t="n">
+        <v>0.01769</v>
+      </c>
+      <c r="T401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="T401" s="1" t="n">
-        <v>0.01772</v>
+      <c r="U401" s="1" t="n">
+        <v>0.01769</v>
       </c>
     </row>
     <row r="402">
@@ -26201,9 +27407,12 @@
         <v>0.07982</v>
       </c>
       <c r="S402" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="T402" s="1" t="n">
+      <c r="U402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -26265,9 +27474,12 @@
         <v>1.2451</v>
       </c>
       <c r="S403" s="1" t="n">
+        <v>1.2468</v>
+      </c>
+      <c r="T403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="T403" s="1" t="n">
+      <c r="U403" s="1" t="n">
         <v>1.2451</v>
       </c>
     </row>
@@ -26329,9 +27541,12 @@
         <v>0.00708</v>
       </c>
       <c r="S404" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="T404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="T404" s="1" t="n">
+      <c r="U404" s="1" t="n">
         <v>0.00708</v>
       </c>
     </row>
@@ -26393,9 +27608,12 @@
         <v>0.5023</v>
       </c>
       <c r="S405" s="1" t="n">
-        <v>0.5041</v>
+        <v>0.5049</v>
       </c>
       <c r="T405" s="1" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="U405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -26457,9 +27675,12 @@
         <v>0.01145</v>
       </c>
       <c r="S406" s="1" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="T406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="T406" s="1" t="n">
+      <c r="U406" s="1" t="n">
         <v>0.01142</v>
       </c>
     </row>
@@ -26521,10 +27742,13 @@
         <v>0.04584</v>
       </c>
       <c r="S407" s="1" t="n">
+        <v>0.04583</v>
+      </c>
+      <c r="T407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="T407" s="1" t="n">
-        <v>0.04584</v>
+      <c r="U407" s="1" t="n">
+        <v>0.04583</v>
       </c>
     </row>
     <row r="408">
@@ -26585,9 +27809,12 @@
         <v>0.03922</v>
       </c>
       <c r="S408" s="1" t="n">
+        <v>0.03922</v>
+      </c>
+      <c r="T408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="T408" s="1" t="n">
+      <c r="U408" s="1" t="n">
         <v>0.03922</v>
       </c>
     </row>
@@ -26649,10 +27876,13 @@
         <v>0.05211</v>
       </c>
       <c r="S409" s="1" t="n">
+        <v>0.05209</v>
+      </c>
+      <c r="T409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="T409" s="1" t="n">
-        <v>0.05211</v>
+      <c r="U409" s="1" t="n">
+        <v>0.05209</v>
       </c>
     </row>
     <row r="410">
@@ -26713,10 +27943,13 @@
         <v>0.01228</v>
       </c>
       <c r="S410" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="T410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="T410" s="1" t="n">
-        <v>0.01227</v>
+      <c r="U410" s="1" t="n">
+        <v>0.01222</v>
       </c>
     </row>
     <row r="411">
@@ -26777,10 +28010,13 @@
         <v>0.06333999999999999</v>
       </c>
       <c r="S411" s="1" t="n">
+        <v>0.06333</v>
+      </c>
+      <c r="T411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="T411" s="1" t="n">
-        <v>0.06333999999999999</v>
+      <c r="U411" s="1" t="n">
+        <v>0.06333</v>
       </c>
     </row>
     <row r="412">
@@ -26841,9 +28077,12 @@
         <v>0.04114</v>
       </c>
       <c r="S412" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="T412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="T412" s="1" t="n">
+      <c r="U412" s="1" t="n">
         <v>0.04114</v>
       </c>
     </row>
@@ -26905,9 +28144,12 @@
         <v>1.11</v>
       </c>
       <c r="S413" s="1" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="T413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="T413" s="1" t="n">
+      <c r="U413" s="1" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -26969,9 +28211,12 @@
         <v>0.2614</v>
       </c>
       <c r="S414" s="1" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="T414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="T414" s="1" t="n">
+      <c r="U414" s="1" t="n">
         <v>0.2614</v>
       </c>
     </row>
@@ -27033,9 +28278,12 @@
         <v>0.001226</v>
       </c>
       <c r="S415" s="1" t="n">
+        <v>0.001221</v>
+      </c>
+      <c r="T415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="T415" s="1" t="n">
+      <c r="U415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -27097,9 +28345,12 @@
         <v>0.03191</v>
       </c>
       <c r="S416" s="1" t="n">
+        <v>0.03194</v>
+      </c>
+      <c r="T416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="T416" s="1" t="n">
+      <c r="U416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -27161,10 +28412,13 @@
         <v>0.01452</v>
       </c>
       <c r="S417" s="1" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="T417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="T417" s="1" t="n">
-        <v>0.01452</v>
+      <c r="U417" s="1" t="n">
+        <v>0.01451</v>
       </c>
     </row>
     <row r="418">
@@ -27225,9 +28479,12 @@
         <v>0.1479</v>
       </c>
       <c r="S418" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="T418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="T418" s="1" t="n">
+      <c r="U418" s="1" t="n">
         <v>0.1478</v>
       </c>
     </row>
@@ -27289,9 +28546,12 @@
         <v>0.04882</v>
       </c>
       <c r="S419" s="1" t="n">
+        <v>0.04872</v>
+      </c>
+      <c r="T419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="T419" s="1" t="n">
+      <c r="U419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -27353,9 +28613,12 @@
         <v>66.56</v>
       </c>
       <c r="S420" s="1" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="T420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="T420" s="1" t="n">
+      <c r="U420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -27417,9 +28680,12 @@
         <v>0.876</v>
       </c>
       <c r="S421" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="T421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="T421" s="1" t="n">
+      <c r="U421" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -27481,9 +28747,12 @@
         <v>0.01242</v>
       </c>
       <c r="S422" s="1" t="n">
+        <v>0.012461</v>
+      </c>
+      <c r="T422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="T422" s="1" t="n">
+      <c r="U422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -27545,9 +28814,12 @@
         <v>0.01592</v>
       </c>
       <c r="S423" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="T423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="T423" s="1" t="n">
+      <c r="U423" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -27609,9 +28881,12 @@
         <v>0.27375</v>
       </c>
       <c r="S424" s="1" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="T424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="T424" s="1" t="n">
+      <c r="U424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -27673,10 +28948,13 @@
         <v>0.599</v>
       </c>
       <c r="S425" s="1" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="T425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="T425" s="1" t="n">
-        <v>0.599</v>
+      <c r="U425" s="1" t="n">
+        <v>0.5984</v>
       </c>
     </row>
     <row r="426">
@@ -27737,9 +29015,12 @@
         <v>0.005493</v>
       </c>
       <c r="S426" s="1" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="T426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="T426" s="1" t="n">
+      <c r="U426" s="1" t="n">
         <v>0.005493</v>
       </c>
     </row>
@@ -27801,9 +29082,12 @@
         <v>0.04978</v>
       </c>
       <c r="S427" s="1" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="T427" s="1" t="n">
         <v>0.04978</v>
       </c>
-      <c r="T427" s="1" t="n">
+      <c r="U427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -27865,9 +29149,12 @@
         <v>0.1249</v>
       </c>
       <c r="S428" s="1" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="T428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="T428" s="1" t="n">
+      <c r="U428" s="1" t="n">
         <v>0.1249</v>
       </c>
     </row>
@@ -27929,9 +29216,12 @@
         <v>0.003194</v>
       </c>
       <c r="S429" s="1" t="n">
+        <v>0.003185</v>
+      </c>
+      <c r="T429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="T429" s="1" t="n">
+      <c r="U429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -27993,10 +29283,13 @@
         <v>0.03636</v>
       </c>
       <c r="S430" s="1" t="n">
+        <v>0.03629</v>
+      </c>
+      <c r="T430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="T430" s="1" t="n">
-        <v>0.03636</v>
+      <c r="U430" s="1" t="n">
+        <v>0.03629</v>
       </c>
     </row>
     <row r="431">
@@ -28057,10 +29350,13 @@
         <v>0.3918</v>
       </c>
       <c r="S431" s="1" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="T431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="T431" s="1" t="n">
-        <v>0.3918</v>
+      <c r="U431" s="1" t="n">
+        <v>0.3914</v>
       </c>
     </row>
     <row r="432">
@@ -28121,10 +29417,13 @@
         <v>0.004471</v>
       </c>
       <c r="S432" s="1" t="n">
+        <v>0.004446</v>
+      </c>
+      <c r="T432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="T432" s="1" t="n">
-        <v>0.004471</v>
+      <c r="U432" s="1" t="n">
+        <v>0.004446</v>
       </c>
     </row>
     <row r="433">
@@ -28185,10 +29484,13 @@
         <v>0.0973</v>
       </c>
       <c r="S433" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="T433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="T433" s="1" t="n">
-        <v>0.0973</v>
+      <c r="U433" s="1" t="n">
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="434">
@@ -28249,9 +29551,12 @@
         <v>0.01234</v>
       </c>
       <c r="S434" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="T434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="T434" s="1" t="n">
+      <c r="U434" s="1" t="n">
         <v>0.01234</v>
       </c>
     </row>
@@ -28313,9 +29618,12 @@
         <v>1.985</v>
       </c>
       <c r="S435" s="1" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="T435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="T435" s="1" t="n">
+      <c r="U435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -28377,10 +29685,13 @@
         <v>0.001775</v>
       </c>
       <c r="S436" s="1" t="n">
+        <v>0.001772</v>
+      </c>
+      <c r="T436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="T436" s="1" t="n">
-        <v>0.001774</v>
+      <c r="U436" s="1" t="n">
+        <v>0.001772</v>
       </c>
     </row>
     <row r="437">
@@ -28441,9 +29752,12 @@
         <v>0.4421</v>
       </c>
       <c r="S437" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="T437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="T437" s="1" t="n">
+      <c r="U437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -28505,9 +29819,12 @@
         <v>0.00533</v>
       </c>
       <c r="S438" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="T438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="T438" s="1" t="n">
+      <c r="U438" s="1" t="n">
         <v>0.00533</v>
       </c>
     </row>
@@ -28569,9 +29886,12 @@
         <v>0.1032</v>
       </c>
       <c r="S439" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="T439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="T439" s="1" t="n">
+      <c r="U439" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -28633,10 +29953,13 @@
         <v>0.03387</v>
       </c>
       <c r="S440" s="1" t="n">
+        <v>0.03361</v>
+      </c>
+      <c r="T440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="T440" s="1" t="n">
-        <v>0.03387</v>
+      <c r="U440" s="1" t="n">
+        <v>0.03361</v>
       </c>
     </row>
     <row r="441">
@@ -28697,10 +30020,13 @@
         <v>0.08184</v>
       </c>
       <c r="S441" s="1" t="n">
+        <v>0.08179</v>
+      </c>
+      <c r="T441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="T441" s="1" t="n">
-        <v>0.08184</v>
+      <c r="U441" s="1" t="n">
+        <v>0.08179</v>
       </c>
     </row>
     <row r="442">
@@ -28761,9 +30087,12 @@
         <v>1.301</v>
       </c>
       <c r="S442" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="T442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="T442" s="1" t="n">
+      <c r="U442" s="1" t="n">
         <v>1.301</v>
       </c>
     </row>
@@ -28825,10 +30154,13 @@
         <v>0.07507</v>
       </c>
       <c r="S443" s="1" t="n">
+        <v>0.07491</v>
+      </c>
+      <c r="T443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="T443" s="1" t="n">
-        <v>0.07507</v>
+      <c r="U443" s="1" t="n">
+        <v>0.07491</v>
       </c>
     </row>
     <row r="444">
@@ -28889,10 +30221,13 @@
         <v>0.07628</v>
       </c>
       <c r="S444" s="1" t="n">
+        <v>0.07616000000000001</v>
+      </c>
+      <c r="T444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="T444" s="1" t="n">
-        <v>0.07628</v>
+      <c r="U444" s="1" t="n">
+        <v>0.07616000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -28953,10 +30288,13 @@
         <v>0.04316</v>
       </c>
       <c r="S445" s="1" t="n">
+        <v>0.04302</v>
+      </c>
+      <c r="T445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="T445" s="1" t="n">
-        <v>0.04316</v>
+      <c r="U445" s="1" t="n">
+        <v>0.04302</v>
       </c>
     </row>
     <row r="446">
@@ -29017,9 +30355,12 @@
         <v>0.02138</v>
       </c>
       <c r="S446" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="T446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="T446" s="1" t="n">
+      <c r="U446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -29081,10 +30422,13 @@
         <v>0.2795</v>
       </c>
       <c r="S447" s="1" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="T447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="T447" s="1" t="n">
-        <v>0.2795</v>
+      <c r="U447" s="1" t="n">
+        <v>0.2791</v>
       </c>
     </row>
     <row r="448">
@@ -29145,9 +30489,12 @@
         <v>0.03073</v>
       </c>
       <c r="S448" s="1" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="T448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="T448" s="1" t="n">
+      <c r="U448" s="1" t="n">
         <v>0.03069</v>
       </c>
     </row>
@@ -29209,9 +30556,12 @@
         <v>0.00645</v>
       </c>
       <c r="S449" s="1" t="n">
+        <v>0.00642</v>
+      </c>
+      <c r="T449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="T449" s="1" t="n">
+      <c r="U449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -29273,9 +30623,12 @@
         <v>0.02312</v>
       </c>
       <c r="S450" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="T450" s="1" t="n">
         <v>0.02312</v>
       </c>
-      <c r="T450" s="1" t="n">
+      <c r="U450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -29337,9 +30690,12 @@
         <v>0.04226</v>
       </c>
       <c r="S451" s="1" t="n">
+        <v>0.04225</v>
+      </c>
+      <c r="T451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="T451" s="1" t="n">
+      <c r="U451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -29401,10 +30757,13 @@
         <v>0.07217999999999999</v>
       </c>
       <c r="S452" s="1" t="n">
+        <v>0.07204000000000001</v>
+      </c>
+      <c r="T452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="T452" s="1" t="n">
-        <v>0.07205</v>
+      <c r="U452" s="1" t="n">
+        <v>0.07204000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -29465,9 +30824,12 @@
         <v>0.0005922</v>
       </c>
       <c r="S453" s="1" t="n">
+        <v>0.0005911</v>
+      </c>
+      <c r="T453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="T453" s="1" t="n">
+      <c r="U453" s="1" t="n">
         <v>0.0005904</v>
       </c>
     </row>
@@ -29529,9 +30891,12 @@
         <v>0.304</v>
       </c>
       <c r="S454" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="T454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="T454" s="1" t="n">
+      <c r="U454" s="1" t="n">
         <v>0.304</v>
       </c>
     </row>
@@ -29593,9 +30958,12 @@
         <v>0.004294</v>
       </c>
       <c r="S455" s="1" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="T455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="T455" s="1" t="n">
+      <c r="U455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -29657,10 +31025,13 @@
         <v>0.1819</v>
       </c>
       <c r="S456" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="T456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="T456" s="1" t="n">
-        <v>0.1819</v>
+      <c r="U456" s="1" t="n">
+        <v>0.1817</v>
       </c>
     </row>
     <row r="457">
@@ -29721,9 +31092,12 @@
         <v>0.04254</v>
       </c>
       <c r="S457" s="1" t="n">
+        <v>0.04256</v>
+      </c>
+      <c r="T457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="T457" s="1" t="n">
+      <c r="U457" s="1" t="n">
         <v>0.04254</v>
       </c>
     </row>
@@ -29785,9 +31159,12 @@
         <v>0.1452</v>
       </c>
       <c r="S458" s="1" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="T458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="T458" s="1" t="n">
+      <c r="U458" s="1" t="n">
         <v>0.1452</v>
       </c>
     </row>
@@ -29849,9 +31226,12 @@
         <v>0.008574</v>
       </c>
       <c r="S459" s="1" t="n">
+        <v>0.008577</v>
+      </c>
+      <c r="T459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="T459" s="1" t="n">
+      <c r="U459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -29913,9 +31293,12 @@
         <v>0.007353</v>
       </c>
       <c r="S460" s="1" t="n">
+        <v>0.007364</v>
+      </c>
+      <c r="T460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="T460" s="1" t="n">
+      <c r="U460" s="1" t="n">
         <v>0.007353</v>
       </c>
     </row>
@@ -29977,9 +31360,12 @@
         <v>0.0001729</v>
       </c>
       <c r="S461" s="1" t="n">
+        <v>0.0001731</v>
+      </c>
+      <c r="T461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="T461" s="1" t="n">
+      <c r="U461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -30041,9 +31427,12 @@
         <v>0.02585</v>
       </c>
       <c r="S462" s="1" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="T462" s="1" t="n">
         <v>0.02585</v>
       </c>
-      <c r="T462" s="1" t="n">
+      <c r="U462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -30105,10 +31494,13 @@
         <v>0.03667</v>
       </c>
       <c r="S463" s="1" t="n">
+        <v>0.03656</v>
+      </c>
+      <c r="T463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="T463" s="1" t="n">
-        <v>0.03667</v>
+      <c r="U463" s="1" t="n">
+        <v>0.03656</v>
       </c>
     </row>
     <row r="464">
@@ -30169,9 +31561,12 @@
         <v>0.3003</v>
       </c>
       <c r="S464" s="1" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="T464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="T464" s="1" t="n">
+      <c r="U464" s="1" t="n">
         <v>0.3003</v>
       </c>
     </row>
@@ -30233,10 +31628,13 @@
         <v>0.03899</v>
       </c>
       <c r="S465" s="1" t="n">
+        <v>0.03889</v>
+      </c>
+      <c r="T465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="T465" s="1" t="n">
-        <v>0.03892</v>
+      <c r="U465" s="1" t="n">
+        <v>0.03889</v>
       </c>
     </row>
     <row r="466">
@@ -30297,10 +31695,13 @@
         <v>2.662</v>
       </c>
       <c r="S466" s="1" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="T466" s="1" t="n">
-        <v>2.661</v>
+      <c r="U466" s="1" t="n">
+        <v>2.66</v>
       </c>
     </row>
     <row r="467">
@@ -30361,9 +31762,12 @@
         <v>0.0343</v>
       </c>
       <c r="S467" s="1" t="n">
+        <v>0.03429</v>
+      </c>
+      <c r="T467" s="1" t="n">
         <v>0.03438</v>
       </c>
-      <c r="T467" s="1" t="n">
+      <c r="U467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -30425,9 +31829,12 @@
         <v>0.1759</v>
       </c>
       <c r="S468" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="T468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="T468" s="1" t="n">
+      <c r="U468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -30489,9 +31896,12 @@
         <v>0.0958</v>
       </c>
       <c r="S469" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="T469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="T469" s="1" t="n">
+      <c r="U469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -30553,9 +31963,12 @@
         <v>0.06722</v>
       </c>
       <c r="S470" s="1" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.06771000000000001</v>
       </c>
       <c r="T470" s="1" t="n">
+        <v>0.06771000000000001</v>
+      </c>
+      <c r="U470" s="1" t="n">
         <v>0.06696000000000001</v>
       </c>
     </row>
@@ -30617,10 +32030,13 @@
         <v>0.03972</v>
       </c>
       <c r="S471" s="1" t="n">
+        <v>0.03969</v>
+      </c>
+      <c r="T471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="T471" s="1" t="n">
-        <v>0.03972</v>
+      <c r="U471" s="1" t="n">
+        <v>0.03969</v>
       </c>
     </row>
     <row r="472">
@@ -30681,10 +32097,13 @@
         <v>0.2464</v>
       </c>
       <c r="S472" s="1" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="T472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="T472" s="1" t="n">
-        <v>0.2464</v>
+      <c r="U472" s="1" t="n">
+        <v>0.2457</v>
       </c>
     </row>
     <row r="473">
@@ -30745,10 +32164,13 @@
         <v>0.016269</v>
       </c>
       <c r="S473" s="1" t="n">
+        <v>0.016238</v>
+      </c>
+      <c r="T473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="T473" s="1" t="n">
-        <v>0.016269</v>
+      <c r="U473" s="1" t="n">
+        <v>0.016238</v>
       </c>
     </row>
     <row r="474">
@@ -30809,10 +32231,13 @@
         <v>0.1147</v>
       </c>
       <c r="S474" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="T474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="T474" s="1" t="n">
-        <v>0.1147</v>
+      <c r="U474" s="1" t="n">
+        <v>0.1146</v>
       </c>
     </row>
     <row r="475">
@@ -30873,9 +32298,12 @@
         <v>0.04258</v>
       </c>
       <c r="S475" s="1" t="n">
+        <v>0.04265</v>
+      </c>
+      <c r="T475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="T475" s="1" t="n">
+      <c r="U475" s="1" t="n">
         <v>0.04258</v>
       </c>
     </row>
@@ -30937,10 +32365,13 @@
         <v>0.2065</v>
       </c>
       <c r="S476" s="1" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="T476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="T476" s="1" t="n">
-        <v>0.2065</v>
+      <c r="U476" s="1" t="n">
+        <v>0.2062</v>
       </c>
     </row>
     <row r="477">
@@ -31001,9 +32432,12 @@
         <v>0.006763</v>
       </c>
       <c r="S477" s="1" t="n">
+        <v>0.006781</v>
+      </c>
+      <c r="T477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="T477" s="1" t="n">
+      <c r="U477" s="1" t="n">
         <v>0.006763</v>
       </c>
     </row>
@@ -31065,9 +32499,12 @@
         <v>0.0178</v>
       </c>
       <c r="S478" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="T478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="T478" s="1" t="n">
+      <c r="U478" s="1" t="n">
         <v>0.01776</v>
       </c>
     </row>
@@ -31129,10 +32566,13 @@
         <v>0.0465</v>
       </c>
       <c r="S479" s="1" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="T479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="T479" s="1" t="n">
-        <v>0.0465</v>
+      <c r="U479" s="1" t="n">
+        <v>0.04647</v>
       </c>
     </row>
     <row r="480">
@@ -31193,9 +32633,12 @@
         <v>0.2596</v>
       </c>
       <c r="S480" s="1" t="n">
+        <v>0.25967</v>
+      </c>
+      <c r="T480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="T480" s="1" t="n">
+      <c r="U480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -31257,10 +32700,13 @@
         <v>0.01216</v>
       </c>
       <c r="S481" s="1" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="T481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="T481" s="1" t="n">
-        <v>0.01216</v>
+      <c r="U481" s="1" t="n">
+        <v>0.01209</v>
       </c>
     </row>
     <row r="482">
@@ -31321,9 +32767,12 @@
         <v>0.004073</v>
       </c>
       <c r="S482" s="1" t="n">
+        <v>0.004066</v>
+      </c>
+      <c r="T482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="T482" s="1" t="n">
+      <c r="U482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -31385,9 +32834,12 @@
         <v>0.1226</v>
       </c>
       <c r="S483" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="T483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="T483" s="1" t="n">
+      <c r="U483" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -31449,9 +32901,12 @@
         <v>0.02185</v>
       </c>
       <c r="S484" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="T484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="T484" s="1" t="n">
+      <c r="U484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -31513,9 +32968,12 @@
         <v>0.0452</v>
       </c>
       <c r="S485" s="1" t="n">
+        <v>0.04526</v>
+      </c>
+      <c r="T485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="T485" s="1" t="n">
+      <c r="U485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -31577,10 +33035,13 @@
         <v>0.1727</v>
       </c>
       <c r="S486" s="1" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="T486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="T486" s="1" t="n">
-        <v>0.1727</v>
+      <c r="U486" s="1" t="n">
+        <v>0.1726</v>
       </c>
     </row>
     <row r="487">
@@ -31641,9 +33102,12 @@
         <v>0.2731</v>
       </c>
       <c r="S487" s="1" t="n">
-        <v>0.2735</v>
+        <v>0.2741</v>
       </c>
       <c r="T487" s="1" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="U487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -31705,10 +33169,13 @@
         <v>0.04581</v>
       </c>
       <c r="S488" s="1" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="T488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="T488" s="1" t="n">
-        <v>0.04581</v>
+      <c r="U488" s="1" t="n">
+        <v>0.04578</v>
       </c>
     </row>
     <row r="489">
@@ -31769,9 +33236,12 @@
         <v>0.0002139</v>
       </c>
       <c r="S489" s="1" t="n">
+        <v>0.0002139</v>
+      </c>
+      <c r="T489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="T489" s="1" t="n">
+      <c r="U489" s="1" t="n">
         <v>0.0002139</v>
       </c>
     </row>
@@ -31833,9 +33303,12 @@
         <v>1.782</v>
       </c>
       <c r="S490" s="1" t="n">
-        <v>1.782</v>
+        <v>1.783</v>
       </c>
       <c r="T490" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="U490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -31897,10 +33370,13 @@
         <v>16.002</v>
       </c>
       <c r="S491" s="1" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="T491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="T491" s="1" t="n">
-        <v>15.996</v>
+      <c r="U491" s="1" t="n">
+        <v>15.99</v>
       </c>
     </row>
     <row r="492">
@@ -31961,10 +33437,13 @@
         <v>0.06645</v>
       </c>
       <c r="S492" s="1" t="n">
+        <v>0.06637</v>
+      </c>
+      <c r="T492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="T492" s="1" t="n">
-        <v>0.06645</v>
+      <c r="U492" s="1" t="n">
+        <v>0.06637</v>
       </c>
     </row>
     <row r="493">
@@ -32025,9 +33504,12 @@
         <v>0.06709</v>
       </c>
       <c r="S493" s="1" t="n">
+        <v>0.06714000000000001</v>
+      </c>
+      <c r="T493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="T493" s="1" t="n">
+      <c r="U493" s="1" t="n">
         <v>0.06709</v>
       </c>
     </row>
@@ -32089,9 +33571,12 @@
         <v>0.009389</v>
       </c>
       <c r="S494" s="1" t="n">
+        <v>0.009405</v>
+      </c>
+      <c r="T494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="T494" s="1" t="n">
+      <c r="U494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -32153,10 +33638,13 @@
         <v>0.005814</v>
       </c>
       <c r="S495" s="1" t="n">
+        <v>0.005788</v>
+      </c>
+      <c r="T495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="T495" s="1" t="n">
-        <v>0.0058</v>
+      <c r="U495" s="1" t="n">
+        <v>0.005788</v>
       </c>
     </row>
     <row r="496">
@@ -32217,9 +33705,12 @@
         <v>0.00984</v>
       </c>
       <c r="S496" s="1" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="T496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="T496" s="1" t="n">
+      <c r="U496" s="1" t="n">
         <v>0.00984</v>
       </c>
     </row>
@@ -32281,9 +33772,12 @@
         <v>0.04638</v>
       </c>
       <c r="S497" s="1" t="n">
-        <v>0.04638</v>
+        <v>0.04665</v>
       </c>
       <c r="T497" s="1" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="U497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -32345,10 +33839,13 @@
         <v>0.006344</v>
       </c>
       <c r="S498" s="1" t="n">
+        <v>0.006338</v>
+      </c>
+      <c r="T498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="T498" s="1" t="n">
-        <v>0.006344</v>
+      <c r="U498" s="1" t="n">
+        <v>0.006338</v>
       </c>
     </row>
     <row r="499">
@@ -32409,9 +33906,12 @@
         <v>0.01032</v>
       </c>
       <c r="S499" s="1" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="T499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="T499" s="1" t="n">
+      <c r="U499" s="1" t="n">
         <v>0.01032</v>
       </c>
     </row>
@@ -32473,9 +33973,12 @@
         <v>0.5073</v>
       </c>
       <c r="S500" s="1" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="T500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="T500" s="1" t="n">
+      <c r="U500" s="1" t="n">
         <v>0.5067</v>
       </c>
     </row>
@@ -32537,9 +34040,12 @@
         <v>0.03213</v>
       </c>
       <c r="S501" s="1" t="n">
+        <v>0.03211</v>
+      </c>
+      <c r="T501" s="1" t="n">
         <v>0.03213</v>
       </c>
-      <c r="T501" s="1" t="n">
+      <c r="U501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -32601,9 +34107,12 @@
         <v>0.4383</v>
       </c>
       <c r="S502" s="1" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="T502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="T502" s="1" t="n">
+      <c r="U502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -32665,9 +34174,12 @@
         <v>0.999342</v>
       </c>
       <c r="S503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="T503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="T503" s="1" t="n">
+      <c r="U503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -32729,9 +34241,12 @@
         <v>0.03523</v>
       </c>
       <c r="S504" s="1" t="n">
+        <v>0.03516</v>
+      </c>
+      <c r="T504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="T504" s="1" t="n">
+      <c r="U504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -32793,9 +34308,12 @@
         <v>0.004918</v>
       </c>
       <c r="S505" s="1" t="n">
+        <v>0.004916</v>
+      </c>
+      <c r="T505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="T505" s="1" t="n">
+      <c r="U505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -32857,10 +34375,13 @@
         <v>0.01381</v>
       </c>
       <c r="S506" s="1" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="T506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="T506" s="1" t="n">
-        <v>0.01381</v>
+      <c r="U506" s="1" t="n">
+        <v>0.0138</v>
       </c>
     </row>
     <row r="507">
@@ -32921,9 +34442,12 @@
         <v>0.003469</v>
       </c>
       <c r="S507" s="1" t="n">
+        <v>0.00348</v>
+      </c>
+      <c r="T507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="T507" s="1" t="n">
+      <c r="U507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -32985,9 +34509,12 @@
         <v>1.411</v>
       </c>
       <c r="S508" s="1" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="T508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="T508" s="1" t="n">
+      <c r="U508" s="1" t="n">
         <v>1.411</v>
       </c>
     </row>
@@ -33049,9 +34576,12 @@
         <v>0.005056</v>
       </c>
       <c r="S509" s="1" t="n">
+        <v>0.005059</v>
+      </c>
+      <c r="T509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="T509" s="1" t="n">
+      <c r="U509" s="1" t="n">
         <v>0.005056</v>
       </c>
     </row>
@@ -33113,9 +34643,12 @@
         <v>0.0156</v>
       </c>
       <c r="S510" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="T510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="T510" s="1" t="n">
+      <c r="U510" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -33177,10 +34710,13 @@
         <v>0.08123</v>
       </c>
       <c r="S511" s="1" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="T511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="T511" s="1" t="n">
-        <v>0.08123</v>
+      <c r="U511" s="1" t="n">
+        <v>0.08119</v>
       </c>
     </row>
     <row r="512">
@@ -33241,10 +34777,13 @@
         <v>0.007071</v>
       </c>
       <c r="S512" s="1" t="n">
+        <v>0.007067</v>
+      </c>
+      <c r="T512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="T512" s="1" t="n">
-        <v>0.007071</v>
+      <c r="U512" s="1" t="n">
+        <v>0.007067</v>
       </c>
     </row>
     <row r="513">
@@ -33305,9 +34844,12 @@
         <v>0.01477</v>
       </c>
       <c r="S513" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="T513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="T513" s="1" t="n">
+      <c r="U513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -33369,10 +34911,13 @@
         <v>0.04727</v>
       </c>
       <c r="S514" s="1" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="T514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="T514" s="1" t="n">
-        <v>0.04721</v>
+      <c r="U514" s="1" t="n">
+        <v>0.04719</v>
       </c>
     </row>
     <row r="515">
@@ -33433,10 +34978,13 @@
         <v>0.01797</v>
       </c>
       <c r="S515" s="1" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="T515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="T515" s="1" t="n">
-        <v>0.01797</v>
+      <c r="U515" s="1" t="n">
+        <v>0.01796</v>
       </c>
     </row>
     <row r="516">
@@ -33497,9 +35045,12 @@
         <v>0.000578</v>
       </c>
       <c r="S516" s="1" t="n">
+        <v>0.0005783</v>
+      </c>
+      <c r="T516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="T516" s="1" t="n">
+      <c r="U516" s="1" t="n">
         <v>0.000578</v>
       </c>
     </row>
@@ -33561,10 +35112,13 @@
         <v>0.07836</v>
       </c>
       <c r="S517" s="1" t="n">
+        <v>0.07817</v>
+      </c>
+      <c r="T517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="T517" s="1" t="n">
-        <v>0.07829</v>
+      <c r="U517" s="1" t="n">
+        <v>0.07817</v>
       </c>
     </row>
     <row r="518">
@@ -33625,10 +35179,13 @@
         <v>0.006356</v>
       </c>
       <c r="S518" s="1" t="n">
+        <v>0.00635</v>
+      </c>
+      <c r="T518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="T518" s="1" t="n">
-        <v>0.006356</v>
+      <c r="U518" s="1" t="n">
+        <v>0.00635</v>
       </c>
     </row>
     <row r="519">
@@ -33689,10 +35246,13 @@
         <v>0.05759</v>
       </c>
       <c r="S519" s="1" t="n">
+        <v>0.05746</v>
+      </c>
+      <c r="T519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="T519" s="1" t="n">
-        <v>0.05759</v>
+      <c r="U519" s="1" t="n">
+        <v>0.05746</v>
       </c>
     </row>
     <row r="520">
@@ -33753,10 +35313,13 @@
         <v>0.10366</v>
       </c>
       <c r="S520" s="1" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="T520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="T520" s="1" t="n">
-        <v>0.10366</v>
+      <c r="U520" s="1" t="n">
+        <v>0.10341</v>
       </c>
     </row>
     <row r="521">
@@ -33817,10 +35380,13 @@
         <v>0.01787</v>
       </c>
       <c r="S521" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="T521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="T521" s="1" t="n">
-        <v>0.01786</v>
+      <c r="U521" s="1" t="n">
+        <v>0.01785</v>
       </c>
     </row>
     <row r="522">
@@ -33881,9 +35447,12 @@
         <v>0.01602</v>
       </c>
       <c r="S522" s="1" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="T522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="T522" s="1" t="n">
+      <c r="U522" s="1" t="n">
         <v>0.01602</v>
       </c>
     </row>
@@ -33945,10 +35514,13 @@
         <v>0.01079</v>
       </c>
       <c r="S523" s="1" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="T523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="T523" s="1" t="n">
-        <v>0.01079</v>
+      <c r="U523" s="1" t="n">
+        <v>0.01077</v>
       </c>
     </row>
     <row r="524">
@@ -34009,9 +35581,12 @@
         <v>0.007318</v>
       </c>
       <c r="S524" s="1" t="n">
+        <v>0.007307</v>
+      </c>
+      <c r="T524" s="1" t="n">
         <v>0.007318</v>
       </c>
-      <c r="T524" s="1" t="n">
+      <c r="U524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -34073,10 +35648,13 @@
         <v>0.005816</v>
       </c>
       <c r="S525" s="1" t="n">
+        <v>0.00581</v>
+      </c>
+      <c r="T525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="T525" s="1" t="n">
-        <v>0.005816</v>
+      <c r="U525" s="1" t="n">
+        <v>0.00581</v>
       </c>
     </row>
     <row r="526">
@@ -34137,9 +35715,12 @@
         <v>0.001448</v>
       </c>
       <c r="S526" s="1" t="n">
+        <v>0.001443</v>
+      </c>
+      <c r="T526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="T526" s="1" t="n">
+      <c r="U526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -34204,6 +35785,9 @@
         <v>0.374</v>
       </c>
       <c r="T527" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="U527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -34265,9 +35849,12 @@
         <v>0.005237</v>
       </c>
       <c r="S528" s="1" t="n">
+        <v>0.005219</v>
+      </c>
+      <c r="T528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="T528" s="1" t="n">
+      <c r="U528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -34329,9 +35916,12 @@
         <v>2.947</v>
       </c>
       <c r="S529" s="1" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="T529" s="1" t="n">
+      <c r="U529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -34393,10 +35983,13 @@
         <v>0.1529</v>
       </c>
       <c r="S530" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="T530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="T530" s="1" t="n">
-        <v>0.1529</v>
+      <c r="U530" s="1" t="n">
+        <v>0.1526</v>
       </c>
     </row>
     <row r="531">
@@ -34457,9 +36050,12 @@
         <v>2567</v>
       </c>
       <c r="S531" s="1" t="n">
+        <v>2570</v>
+      </c>
+      <c r="T531" s="1" t="n">
         <v>2579</v>
       </c>
-      <c r="T531" s="1" t="n">
+      <c r="U531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -34521,10 +36117,13 @@
         <v>0.03897</v>
       </c>
       <c r="S532" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="T532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="T532" s="1" t="n">
-        <v>0.03897</v>
+      <c r="U532" s="1" t="n">
+        <v>0.03893</v>
       </c>
     </row>
     <row r="533">
@@ -34585,9 +36184,12 @@
         <v>0.02172</v>
       </c>
       <c r="S533" s="1" t="n">
+        <v>0.02176</v>
+      </c>
+      <c r="T533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="T533" s="1" t="n">
+      <c r="U533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -34649,9 +36251,12 @@
         <v>0.07321</v>
       </c>
       <c r="S534" s="1" t="n">
+        <v>0.07296</v>
+      </c>
+      <c r="T534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="T534" s="1" t="n">
+      <c r="U534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -34713,9 +36318,12 @@
         <v>0.007852</v>
       </c>
       <c r="S535" s="1" t="n">
+        <v>0.007844</v>
+      </c>
+      <c r="T535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="T535" s="1" t="n">
+      <c r="U535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -34777,10 +36385,13 @@
         <v>0.04994</v>
       </c>
       <c r="S536" s="1" t="n">
+        <v>0.04985</v>
+      </c>
+      <c r="T536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="T536" s="1" t="n">
-        <v>0.04994</v>
+      <c r="U536" s="1" t="n">
+        <v>0.04985</v>
       </c>
     </row>
     <row r="537">
@@ -34841,9 +36452,12 @@
         <v>0.00397</v>
       </c>
       <c r="S537" s="1" t="n">
+        <v>0.00398</v>
+      </c>
+      <c r="T537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="T537" s="1" t="n">
+      <c r="U537" s="1" t="n">
         <v>0.00397</v>
       </c>
     </row>
@@ -34905,10 +36519,13 @@
         <v>0.08266999999999999</v>
       </c>
       <c r="S538" s="1" t="n">
+        <v>0.08252</v>
+      </c>
+      <c r="T538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="T538" s="1" t="n">
-        <v>0.08266999999999999</v>
+      <c r="U538" s="1" t="n">
+        <v>0.08252</v>
       </c>
     </row>
     <row r="539">
@@ -34969,10 +36586,13 @@
         <v>0.0248</v>
       </c>
       <c r="S539" s="1" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="T539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="T539" s="1" t="n">
-        <v>0.02479</v>
+      <c r="U539" s="1" t="n">
+        <v>0.02477</v>
       </c>
     </row>
     <row r="540">
@@ -35033,9 +36653,12 @@
         <v>0.08419</v>
       </c>
       <c r="S540" s="1" t="n">
+        <v>0.08431</v>
+      </c>
+      <c r="T540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="T540" s="1" t="n">
+      <c r="U540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -35097,10 +36720,13 @@
         <v>0.01885</v>
       </c>
       <c r="S541" s="1" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="T541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="T541" s="1" t="n">
-        <v>0.01882</v>
+      <c r="U541" s="1" t="n">
+        <v>0.0188</v>
       </c>
     </row>
     <row r="542">
@@ -35161,9 +36787,12 @@
         <v>0.0168</v>
       </c>
       <c r="S542" s="1" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="T542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="T542" s="1" t="n">
+      <c r="U542" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -35225,9 +36854,12 @@
         <v>0.1045</v>
       </c>
       <c r="S543" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="T543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="T543" s="1" t="n">
+      <c r="U543" s="1" t="n">
         <v>0.1044</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U543"/>
+  <dimension ref="A1:V543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -438,8 +438,9 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,10 +541,15 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>price_04:45</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -610,9 +616,12 @@
         <v>70696.3</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>70696.3</v>
+        <v>70796.5</v>
       </c>
       <c r="U2" s="1" t="n">
+        <v>70796.5</v>
+      </c>
+      <c r="V2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -677,9 +686,12 @@
         <v>2078.18</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>2078.18</v>
+        <v>2083.29</v>
       </c>
       <c r="U3" s="1" t="n">
+        <v>2083.29</v>
+      </c>
+      <c r="V3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -744,9 +756,12 @@
         <v>86.84999999999999</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>87.01000000000001</v>
+        <v>87.05</v>
       </c>
       <c r="U4" s="1" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="V4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -811,9 +826,12 @@
         <v>4.001</v>
       </c>
       <c r="T5" s="1" t="n">
+        <v>3.994</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="V5" s="1" t="n">
         <v>3.991</v>
       </c>
     </row>
@@ -878,9 +896,12 @@
         <v>0.09465999999999999</v>
       </c>
       <c r="T6" s="1" t="n">
+        <v>0.09483</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -945,9 +966,12 @@
         <v>1.3905</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>1.3924</v>
+        <v>1.3929</v>
       </c>
       <c r="U7" s="1" t="n">
+        <v>1.3929</v>
+      </c>
+      <c r="V7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -1012,9 +1036,12 @@
         <v>21.906</v>
       </c>
       <c r="T8" s="1" t="n">
+        <v>21.944</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="U8" s="1" t="n">
+      <c r="V8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1079,10 +1106,13 @@
         <v>0.001995</v>
       </c>
       <c r="T9" s="1" t="n">
+        <v>0.001951</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="U9" s="1" t="n">
-        <v>0.001972</v>
+      <c r="V9" s="1" t="n">
+        <v>0.001951</v>
       </c>
     </row>
     <row r="10">
@@ -1146,9 +1176,12 @@
         <v>0.009995</v>
       </c>
       <c r="T10" s="1" t="n">
+        <v>0.009974</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1213,9 +1246,12 @@
         <v>0.13631</v>
       </c>
       <c r="T11" s="1" t="n">
+        <v>0.15083</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.13631</v>
       </c>
     </row>
@@ -1280,9 +1316,12 @@
         <v>0.011229</v>
       </c>
       <c r="T12" s="1" t="n">
+        <v>0.011307</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="U12" s="1" t="n">
+      <c r="V12" s="1" t="n">
         <v>0.011225</v>
       </c>
     </row>
@@ -1347,10 +1386,13 @@
         <v>37.907</v>
       </c>
       <c r="T13" s="1" t="n">
+        <v>37.748</v>
+      </c>
+      <c r="U13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="U13" s="1" t="n">
-        <v>37.812</v>
+      <c r="V13" s="1" t="n">
+        <v>37.748</v>
       </c>
     </row>
     <row r="14">
@@ -1414,9 +1456,12 @@
         <v>653.27</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>654.02</v>
+        <v>654.13</v>
       </c>
       <c r="U14" s="1" t="n">
+        <v>654.13</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1481,9 +1526,12 @@
         <v>209.77</v>
       </c>
       <c r="T15" s="1" t="n">
+        <v>209.96</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <v>210.26</v>
       </c>
-      <c r="U15" s="1" t="n">
+      <c r="V15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1548,9 +1596,12 @@
         <v>0.0033105</v>
       </c>
       <c r="T16" s="1" t="n">
+        <v>0.0033231</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="U16" s="1" t="n">
+      <c r="V16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1615,9 +1666,12 @@
         <v>239.33</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>239.55</v>
+        <v>240.32</v>
       </c>
       <c r="U17" s="1" t="n">
+        <v>240.32</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1682,9 +1736,12 @@
         <v>0.9858</v>
       </c>
       <c r="T18" s="1" t="n">
+        <v>0.9878</v>
+      </c>
+      <c r="U18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="U18" s="1" t="n">
+      <c r="V18" s="1" t="n">
         <v>0.9858</v>
       </c>
     </row>
@@ -1749,9 +1806,12 @@
         <v>0.9972</v>
       </c>
       <c r="T19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="U19" s="1" t="n">
+      <c r="V19" s="1" t="n">
         <v>0.9972</v>
       </c>
     </row>
@@ -1816,9 +1876,12 @@
         <v>0.2589</v>
       </c>
       <c r="T20" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="U20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="U20" s="1" t="n">
+      <c r="V20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1883,9 +1946,12 @@
         <v>0.60123</v>
       </c>
       <c r="T21" s="1" t="n">
+        <v>0.59321</v>
+      </c>
+      <c r="U21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="U21" s="1" t="n">
+      <c r="V21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -1950,9 +2016,12 @@
         <v>9.029</v>
       </c>
       <c r="T22" s="1" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="U22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="U22" s="1" t="n">
+      <c r="V22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -2017,10 +2086,13 @@
         <v>0.02384</v>
       </c>
       <c r="T23" s="1" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="U23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="U23" s="1" t="n">
-        <v>0.02384</v>
+      <c r="V23" s="1" t="n">
+        <v>0.02367</v>
       </c>
     </row>
     <row r="24">
@@ -2084,9 +2156,12 @@
         <v>9.563000000000001</v>
       </c>
       <c r="T24" s="1" t="n">
+        <v>9.593</v>
+      </c>
+      <c r="U24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="U24" s="1" t="n">
+      <c r="V24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2151,9 +2226,12 @@
         <v>1.222</v>
       </c>
       <c r="T25" s="1" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="U25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="U25" s="1" t="n">
+      <c r="V25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -2218,9 +2296,12 @@
         <v>0.07317</v>
       </c>
       <c r="T26" s="1" t="n">
+        <v>0.07269</v>
+      </c>
+      <c r="U26" s="1" t="n">
         <v>0.07317</v>
       </c>
-      <c r="U26" s="1" t="n">
+      <c r="V26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2285,9 +2366,12 @@
         <v>1.407</v>
       </c>
       <c r="T27" s="1" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="U27" s="1" t="n">
+      <c r="V27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2352,9 +2436,12 @@
         <v>1.303</v>
       </c>
       <c r="T28" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="U28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="U28" s="1" t="n">
+      <c r="V28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2419,9 +2506,12 @@
         <v>462.92</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>463.55</v>
+        <v>464.27</v>
       </c>
       <c r="U29" s="1" t="n">
+        <v>464.27</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2486,9 +2576,12 @@
         <v>1.2939</v>
       </c>
       <c r="T30" s="1" t="n">
+        <v>1.2937</v>
+      </c>
+      <c r="U30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="U30" s="1" t="n">
+      <c r="V30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2553,10 +2646,13 @@
         <v>5021.55</v>
       </c>
       <c r="T31" s="1" t="n">
+        <v>5019.42</v>
+      </c>
+      <c r="U31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="U31" s="1" t="n">
-        <v>5021.33</v>
+      <c r="V31" s="1" t="n">
+        <v>5019.42</v>
       </c>
     </row>
     <row r="32">
@@ -2620,9 +2716,12 @@
         <v>0.874</v>
       </c>
       <c r="T32" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="U32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="U32" s="1" t="n">
+      <c r="V32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2687,9 +2786,12 @@
         <v>0.001966</v>
       </c>
       <c r="T33" s="1" t="n">
+        <v>0.001972</v>
+      </c>
+      <c r="U33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="U33" s="1" t="n">
+      <c r="V33" s="1" t="n">
         <v>0.001966</v>
       </c>
     </row>
@@ -2754,9 +2856,12 @@
         <v>0.17416</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.17416</v>
+        <v>0.17484</v>
       </c>
       <c r="U34" s="1" t="n">
+        <v>0.17484</v>
+      </c>
+      <c r="V34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2821,9 +2926,12 @@
         <v>0.29676</v>
       </c>
       <c r="T35" s="1" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="U35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="U35" s="1" t="n">
+      <c r="V35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -2891,6 +2999,9 @@
         <v>1.795</v>
       </c>
       <c r="U36" s="1" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="V36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -2955,9 +3066,12 @@
         <v>110.2</v>
       </c>
       <c r="T37" s="1" t="n">
+        <v>110.49</v>
+      </c>
+      <c r="U37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="U37" s="1" t="n">
+      <c r="V37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -3022,9 +3136,12 @@
         <v>0.2209</v>
       </c>
       <c r="T38" s="1" t="n">
+        <v>0.22043</v>
+      </c>
+      <c r="U38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="U38" s="1" t="n">
+      <c r="V38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -3089,9 +3206,12 @@
         <v>0.1066</v>
       </c>
       <c r="T39" s="1" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="U39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="U39" s="1" t="n">
+      <c r="V39" s="1" t="n">
         <v>0.1066</v>
       </c>
     </row>
@@ -3156,9 +3276,12 @@
         <v>0.37283</v>
       </c>
       <c r="T40" s="1" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="U40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="U40" s="1" t="n">
+      <c r="V40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -3223,9 +3346,12 @@
         <v>54.5</v>
       </c>
       <c r="T41" s="1" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="U41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="U41" s="1" t="n">
+      <c r="V41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3290,9 +3416,12 @@
         <v>0.0010538</v>
       </c>
       <c r="T42" s="1" t="n">
+        <v>0.001058</v>
+      </c>
+      <c r="U42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="U42" s="1" t="n">
+      <c r="V42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -3357,9 +3486,12 @@
         <v>6.465</v>
       </c>
       <c r="T43" s="1" t="n">
+        <v>6.519</v>
+      </c>
+      <c r="U43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="U43" s="1" t="n">
+      <c r="V43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3424,9 +3556,12 @@
         <v>0.6213</v>
       </c>
       <c r="T44" s="1" t="n">
+        <v>0.6259</v>
+      </c>
+      <c r="U44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="U44" s="1" t="n">
+      <c r="V44" s="1" t="n">
         <v>0.6213</v>
       </c>
     </row>
@@ -3491,9 +3626,12 @@
         <v>0.3512</v>
       </c>
       <c r="T45" s="1" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="U45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="U45" s="1" t="n">
+      <c r="V45" s="1" t="n">
         <v>0.3512</v>
       </c>
     </row>
@@ -3558,9 +3696,12 @@
         <v>0.03282</v>
       </c>
       <c r="T46" s="1" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="U46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="U46" s="1" t="n">
+      <c r="V46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3625,9 +3766,12 @@
         <v>0.06920999999999999</v>
       </c>
       <c r="T47" s="1" t="n">
+        <v>0.06927999999999999</v>
+      </c>
+      <c r="U47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="U47" s="1" t="n">
+      <c r="V47" s="1" t="n">
         <v>0.06920999999999999</v>
       </c>
     </row>
@@ -3692,9 +3836,12 @@
         <v>0.7086</v>
       </c>
       <c r="T48" s="1" t="n">
+        <v>0.7065</v>
+      </c>
+      <c r="U48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="U48" s="1" t="n">
+      <c r="V48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3759,9 +3906,12 @@
         <v>0.004224</v>
       </c>
       <c r="T49" s="1" t="n">
+        <v>0.004267</v>
+      </c>
+      <c r="U49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="U49" s="1" t="n">
+      <c r="V49" s="1" t="n">
         <v>0.004224</v>
       </c>
     </row>
@@ -3826,9 +3976,12 @@
         <v>0.1031</v>
       </c>
       <c r="T50" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="U50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="U50" s="1" t="n">
+      <c r="V50" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -3893,9 +4046,12 @@
         <v>0.04021</v>
       </c>
       <c r="T51" s="1" t="n">
+        <v>0.04033</v>
+      </c>
+      <c r="U51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="U51" s="1" t="n">
+      <c r="V51" s="1" t="n">
         <v>0.04021</v>
       </c>
     </row>
@@ -3960,9 +4116,12 @@
         <v>0.1645</v>
       </c>
       <c r="T52" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="U52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="U52" s="1" t="n">
+      <c r="V52" s="1" t="n">
         <v>0.1645</v>
       </c>
     </row>
@@ -4027,10 +4186,13 @@
         <v>0.01925</v>
       </c>
       <c r="T53" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="U53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="U53" s="1" t="n">
-        <v>0.01925</v>
+      <c r="V53" s="1" t="n">
+        <v>0.01922</v>
       </c>
     </row>
     <row r="54">
@@ -4094,9 +4256,12 @@
         <v>0.00717</v>
       </c>
       <c r="T54" s="1" t="n">
+        <v>0.007188</v>
+      </c>
+      <c r="U54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="U54" s="1" t="n">
+      <c r="V54" s="1" t="n">
         <v>0.00717</v>
       </c>
     </row>
@@ -4161,9 +4326,12 @@
         <v>3.918</v>
       </c>
       <c r="T55" s="1" t="n">
+        <v>3.926</v>
+      </c>
+      <c r="U55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="U55" s="1" t="n">
+      <c r="V55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -4228,9 +4396,12 @@
         <v>0.016808</v>
       </c>
       <c r="T56" s="1" t="n">
+        <v>0.016874</v>
+      </c>
+      <c r="U56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="U56" s="1" t="n">
+      <c r="V56" s="1" t="n">
         <v>0.016808</v>
       </c>
     </row>
@@ -4295,9 +4466,12 @@
         <v>0.108</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="U57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="U57" s="1" t="n">
+      <c r="V57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -4362,9 +4536,12 @@
         <v>2.639</v>
       </c>
       <c r="T58" s="1" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="U58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="U58" s="1" t="n">
+      <c r="V58" s="1" t="n">
         <v>2.639</v>
       </c>
     </row>
@@ -4429,9 +4606,12 @@
         <v>0.1582</v>
       </c>
       <c r="T59" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="U59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="U59" s="1" t="n">
+      <c r="V59" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -4496,9 +4676,12 @@
         <v>0.005839</v>
       </c>
       <c r="T60" s="1" t="n">
+        <v>0.005845</v>
+      </c>
+      <c r="U60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="U60" s="1" t="n">
+      <c r="V60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -4563,9 +4746,12 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="T61" s="1" t="n">
+        <v>0.09182</v>
+      </c>
+      <c r="U61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="U61" s="1" t="n">
+      <c r="V61" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -4630,9 +4816,12 @@
         <v>0.9101</v>
       </c>
       <c r="T62" s="1" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="U62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="U62" s="1" t="n">
+      <c r="V62" s="1" t="n">
         <v>0.9101</v>
       </c>
     </row>
@@ -4697,9 +4886,12 @@
         <v>0.778</v>
       </c>
       <c r="T63" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="U63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="U63" s="1" t="n">
+      <c r="V63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -4764,9 +4956,12 @@
         <v>0.04603</v>
       </c>
       <c r="T64" s="1" t="n">
+        <v>0.04595</v>
+      </c>
+      <c r="U64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="U64" s="1" t="n">
+      <c r="V64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -4831,9 +5026,12 @@
         <v>355.15</v>
       </c>
       <c r="T65" s="1" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="U65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="U65" s="1" t="n">
+      <c r="V65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -4898,9 +5096,12 @@
         <v>0.12486</v>
       </c>
       <c r="T66" s="1" t="n">
+        <v>0.12519</v>
+      </c>
+      <c r="U66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="U66" s="1" t="n">
+      <c r="V66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -4965,9 +5166,12 @@
         <v>0.2294</v>
       </c>
       <c r="T67" s="1" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="U67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="U67" s="1" t="n">
+      <c r="V67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -5032,9 +5236,12 @@
         <v>0.00337</v>
       </c>
       <c r="T68" s="1" t="n">
+        <v>0.00338</v>
+      </c>
+      <c r="U68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="U68" s="1" t="n">
+      <c r="V68" s="1" t="n">
         <v>0.00337</v>
       </c>
     </row>
@@ -5099,9 +5306,12 @@
         <v>0.1746</v>
       </c>
       <c r="T69" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="U69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="U69" s="1" t="n">
+      <c r="V69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -5166,9 +5376,12 @@
         <v>0.16358</v>
       </c>
       <c r="T70" s="1" t="n">
+        <v>0.16409</v>
+      </c>
+      <c r="U70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="U70" s="1" t="n">
+      <c r="V70" s="1" t="n">
         <v>0.16358</v>
       </c>
     </row>
@@ -5233,9 +5446,12 @@
         <v>0.3552</v>
       </c>
       <c r="T71" s="1" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="U71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="U71" s="1" t="n">
+      <c r="V71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -5300,9 +5516,12 @@
         <v>0.707</v>
       </c>
       <c r="T72" s="1" t="n">
+        <v>0.7099</v>
+      </c>
+      <c r="U72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="U72" s="1" t="n">
+      <c r="V72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -5367,9 +5586,12 @@
         <v>0.00859</v>
       </c>
       <c r="T73" s="1" t="n">
+        <v>0.008630000000000001</v>
+      </c>
+      <c r="U73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="U73" s="1" t="n">
+      <c r="V73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -5434,9 +5656,12 @@
         <v>0.005958</v>
       </c>
       <c r="T74" s="1" t="n">
+        <v>0.005976</v>
+      </c>
+      <c r="U74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="U74" s="1" t="n">
+      <c r="V74" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -5504,6 +5729,9 @@
         <v>0.229</v>
       </c>
       <c r="U75" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="V75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -5568,9 +5796,12 @@
         <v>0.324</v>
       </c>
       <c r="T76" s="1" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="U76" s="1" t="n">
         <v>0.3278</v>
       </c>
-      <c r="U76" s="1" t="n">
+      <c r="V76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -5635,9 +5866,12 @@
         <v>0.0999</v>
       </c>
       <c r="T77" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="U77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="U77" s="1" t="n">
+      <c r="V77" s="1" t="n">
         <v>0.0999</v>
       </c>
     </row>
@@ -5702,9 +5936,12 @@
         <v>0.1222</v>
       </c>
       <c r="T78" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="U78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="U78" s="1" t="n">
+      <c r="V78" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -5769,9 +6006,12 @@
         <v>0.07459</v>
       </c>
       <c r="T79" s="1" t="n">
-        <v>0.07459</v>
+        <v>0.07549</v>
       </c>
       <c r="U79" s="1" t="n">
+        <v>0.07549</v>
+      </c>
+      <c r="V79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -5836,10 +6076,13 @@
         <v>0.04634</v>
       </c>
       <c r="T80" s="1" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="U80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="U80" s="1" t="n">
-        <v>0.04634</v>
+      <c r="V80" s="1" t="n">
+        <v>0.04628</v>
       </c>
     </row>
     <row r="81">
@@ -5903,9 +6146,12 @@
         <v>0.000228</v>
       </c>
       <c r="T81" s="1" t="n">
+        <v>0.000232</v>
+      </c>
+      <c r="U81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="U81" s="1" t="n">
+      <c r="V81" s="1" t="n">
         <v>0.000228</v>
       </c>
     </row>
@@ -5970,9 +6216,12 @@
         <v>8.196999999999999</v>
       </c>
       <c r="T82" s="1" t="n">
+        <v>8.212</v>
+      </c>
+      <c r="U82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="U82" s="1" t="n">
+      <c r="V82" s="1" t="n">
         <v>8.194000000000001</v>
       </c>
     </row>
@@ -6037,9 +6286,12 @@
         <v>0.0005713</v>
       </c>
       <c r="T83" s="1" t="n">
+        <v>0.0005761</v>
+      </c>
+      <c r="U83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="U83" s="1" t="n">
+      <c r="V83" s="1" t="n">
         <v>0.0005713</v>
       </c>
     </row>
@@ -6104,9 +6356,12 @@
         <v>0.4474</v>
       </c>
       <c r="T84" s="1" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="U84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="U84" s="1" t="n">
+      <c r="V84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6171,9 +6426,12 @@
         <v>0.0623</v>
       </c>
       <c r="T85" s="1" t="n">
+        <v>0.06241</v>
+      </c>
+      <c r="U85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="U85" s="1" t="n">
+      <c r="V85" s="1" t="n">
         <v>0.0623</v>
       </c>
     </row>
@@ -6238,9 +6496,12 @@
         <v>0.05409</v>
       </c>
       <c r="T86" s="1" t="n">
+        <v>0.05425</v>
+      </c>
+      <c r="U86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="U86" s="1" t="n">
+      <c r="V86" s="1" t="n">
         <v>0.05403</v>
       </c>
     </row>
@@ -6305,9 +6566,12 @@
         <v>0.003352</v>
       </c>
       <c r="T87" s="1" t="n">
+        <v>0.003355</v>
+      </c>
+      <c r="U87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="U87" s="1" t="n">
+      <c r="V87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -6372,9 +6636,12 @@
         <v>0.05034</v>
       </c>
       <c r="T88" s="1" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="U88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="U88" s="1" t="n">
+      <c r="V88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -6439,9 +6706,12 @@
         <v>0.03164</v>
       </c>
       <c r="T89" s="1" t="n">
-        <v>0.03164</v>
+        <v>0.03192</v>
       </c>
       <c r="U89" s="1" t="n">
+        <v>0.03192</v>
+      </c>
+      <c r="V89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -6506,9 +6776,12 @@
         <v>0.3442</v>
       </c>
       <c r="T90" s="1" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="U90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="U90" s="1" t="n">
+      <c r="V90" s="1" t="n">
         <v>0.3442</v>
       </c>
     </row>
@@ -6573,9 +6846,12 @@
         <v>0.07342</v>
       </c>
       <c r="T91" s="1" t="n">
+        <v>0.07452</v>
+      </c>
+      <c r="U91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="U91" s="1" t="n">
+      <c r="V91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -6640,9 +6916,12 @@
         <v>0.3607</v>
       </c>
       <c r="T92" s="1" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="U92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="U92" s="1" t="n">
+      <c r="V92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -6707,9 +6986,12 @@
         <v>1.9769</v>
       </c>
       <c r="T93" s="1" t="n">
+        <v>1.9759</v>
+      </c>
+      <c r="U93" s="1" t="n">
         <v>1.9809</v>
       </c>
-      <c r="U93" s="1" t="n">
+      <c r="V93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -6774,9 +7056,12 @@
         <v>0.2583</v>
       </c>
       <c r="T94" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="U94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="U94" s="1" t="n">
+      <c r="V94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -6841,9 +7126,12 @@
         <v>0.0452</v>
       </c>
       <c r="T95" s="1" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="U95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="U95" s="1" t="n">
+      <c r="V95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -6908,9 +7196,12 @@
         <v>0.006133</v>
       </c>
       <c r="T96" s="1" t="n">
+        <v>0.006202</v>
+      </c>
+      <c r="U96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="U96" s="1" t="n">
+      <c r="V96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -6975,9 +7266,12 @@
         <v>0.001706</v>
       </c>
       <c r="T97" s="1" t="n">
+        <v>0.001707</v>
+      </c>
+      <c r="U97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="U97" s="1" t="n">
+      <c r="V97" s="1" t="n">
         <v>0.001706</v>
       </c>
     </row>
@@ -7042,9 +7336,12 @@
         <v>5.224</v>
       </c>
       <c r="T98" s="1" t="n">
+        <v>5.215</v>
+      </c>
+      <c r="U98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="U98" s="1" t="n">
+      <c r="V98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -7109,9 +7406,12 @@
         <v>0.01503</v>
       </c>
       <c r="T99" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="U99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="U99" s="1" t="n">
+      <c r="V99" s="1" t="n">
         <v>0.01503</v>
       </c>
     </row>
@@ -7176,9 +7476,12 @@
         <v>0.5508</v>
       </c>
       <c r="T100" s="1" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="U100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="U100" s="1" t="n">
+      <c r="V100" s="1" t="n">
         <v>0.5508</v>
       </c>
     </row>
@@ -7243,9 +7546,12 @@
         <v>0.0897</v>
       </c>
       <c r="T101" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="U101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="U101" s="1" t="n">
+      <c r="V101" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -7310,9 +7616,12 @@
         <v>32.3</v>
       </c>
       <c r="T102" s="1" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="U102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="U102" s="1" t="n">
+      <c r="V102" s="1" t="n">
         <v>32.29</v>
       </c>
     </row>
@@ -7377,9 +7686,12 @@
         <v>0.03214</v>
       </c>
       <c r="T103" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="U103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="U103" s="1" t="n">
+      <c r="V103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -7444,9 +7756,12 @@
         <v>0.06559</v>
       </c>
       <c r="T104" s="1" t="n">
+        <v>0.06571</v>
+      </c>
+      <c r="U104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="U104" s="1" t="n">
+      <c r="V104" s="1" t="n">
         <v>0.06559</v>
       </c>
     </row>
@@ -7511,9 +7826,12 @@
         <v>1.3001</v>
       </c>
       <c r="T105" s="1" t="n">
+        <v>1.3024</v>
+      </c>
+      <c r="U105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="U105" s="1" t="n">
+      <c r="V105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -7578,9 +7896,12 @@
         <v>0.1204</v>
       </c>
       <c r="T106" s="1" t="n">
+        <v>0.1201</v>
+      </c>
+      <c r="U106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="U106" s="1" t="n">
+      <c r="V106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -7645,9 +7966,12 @@
         <v>0.12</v>
       </c>
       <c r="T107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="U107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="U107" s="1" t="n">
+      <c r="V107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -7712,9 +8036,12 @@
         <v>0.09572</v>
       </c>
       <c r="T108" s="1" t="n">
+        <v>0.09574000000000001</v>
+      </c>
+      <c r="U108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="U108" s="1" t="n">
+      <c r="V108" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -7779,9 +8106,12 @@
         <v>0.13824</v>
       </c>
       <c r="T109" s="1" t="n">
+        <v>0.13981</v>
+      </c>
+      <c r="U109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="U109" s="1" t="n">
+      <c r="V109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -7846,9 +8176,12 @@
         <v>5.553</v>
       </c>
       <c r="T110" s="1" t="n">
+        <v>5.569</v>
+      </c>
+      <c r="U110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="U110" s="1" t="n">
+      <c r="V110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -7913,9 +8246,12 @@
         <v>1.097</v>
       </c>
       <c r="T111" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="U111" s="1" t="n">
+      <c r="V111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -7980,9 +8316,12 @@
         <v>0.028743</v>
       </c>
       <c r="T112" s="1" t="n">
+        <v>0.02881</v>
+      </c>
+      <c r="U112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="U112" s="1" t="n">
+      <c r="V112" s="1" t="n">
         <v>0.028743</v>
       </c>
     </row>
@@ -8047,9 +8386,12 @@
         <v>1.862</v>
       </c>
       <c r="T113" s="1" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="U113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="U113" s="1" t="n">
+      <c r="V113" s="1" t="n">
         <v>1.862</v>
       </c>
     </row>
@@ -8114,9 +8456,12 @@
         <v>0.05903</v>
       </c>
       <c r="T114" s="1" t="n">
+        <v>0.05912</v>
+      </c>
+      <c r="U114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="U114" s="1" t="n">
+      <c r="V114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -8181,9 +8526,12 @@
         <v>0.12805</v>
       </c>
       <c r="T115" s="1" t="n">
+        <v>0.12769</v>
+      </c>
+      <c r="U115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="U115" s="1" t="n">
+      <c r="V115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -8248,10 +8596,13 @@
         <v>1.1018</v>
       </c>
       <c r="T116" s="1" t="n">
+        <v>1.0959</v>
+      </c>
+      <c r="U116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="U116" s="1" t="n">
-        <v>1.1018</v>
+      <c r="V116" s="1" t="n">
+        <v>1.0959</v>
       </c>
     </row>
     <row r="117">
@@ -8315,9 +8666,12 @@
         <v>0.1484</v>
       </c>
       <c r="T117" s="1" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="U117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="U117" s="1" t="n">
+      <c r="V117" s="1" t="n">
         <v>0.1484</v>
       </c>
     </row>
@@ -8382,9 +8736,12 @@
         <v>0.1582</v>
       </c>
       <c r="T118" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="U118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="U118" s="1" t="n">
+      <c r="V118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -8449,9 +8806,12 @@
         <v>0.04668</v>
       </c>
       <c r="T119" s="1" t="n">
+        <v>0.04685</v>
+      </c>
+      <c r="U119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="U119" s="1" t="n">
+      <c r="V119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -8516,9 +8876,12 @@
         <v>3.006</v>
       </c>
       <c r="T120" s="1" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="U120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="U120" s="1" t="n">
+      <c r="V120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -8583,9 +8946,12 @@
         <v>0.297</v>
       </c>
       <c r="T121" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="U121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="U121" s="1" t="n">
+      <c r="V121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -8650,9 +9016,12 @@
         <v>0.5770999999999999</v>
       </c>
       <c r="T122" s="1" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="U122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="U122" s="1" t="n">
+      <c r="V122" s="1" t="n">
         <v>0.5770999999999999</v>
       </c>
     </row>
@@ -8717,10 +9086,13 @@
         <v>0.01253</v>
       </c>
       <c r="T123" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="U123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="U123" s="1" t="n">
-        <v>0.01253</v>
+      <c r="V123" s="1" t="n">
+        <v>0.01251</v>
       </c>
     </row>
     <row r="124">
@@ -8784,9 +9156,12 @@
         <v>0.1569</v>
       </c>
       <c r="T124" s="1" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="U124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="U124" s="1" t="n">
+      <c r="V124" s="1" t="n">
         <v>0.1569</v>
       </c>
     </row>
@@ -8854,6 +9229,9 @@
         <v>0.001786</v>
       </c>
       <c r="U125" s="1" t="n">
+        <v>0.001786</v>
+      </c>
+      <c r="V125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -8918,9 +9296,12 @@
         <v>0.0004825</v>
       </c>
       <c r="T126" s="1" t="n">
+        <v>0.0004844</v>
+      </c>
+      <c r="U126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="U126" s="1" t="n">
+      <c r="V126" s="1" t="n">
         <v>0.0004824</v>
       </c>
     </row>
@@ -8985,9 +9366,12 @@
         <v>0.02924</v>
       </c>
       <c r="T127" s="1" t="n">
+        <v>0.02932</v>
+      </c>
+      <c r="U127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="U127" s="1" t="n">
+      <c r="V127" s="1" t="n">
         <v>0.02924</v>
       </c>
     </row>
@@ -9052,9 +9436,12 @@
         <v>0.04116</v>
       </c>
       <c r="T128" s="1" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="U128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="U128" s="1" t="n">
+      <c r="V128" s="1" t="n">
         <v>0.04116</v>
       </c>
     </row>
@@ -9119,9 +9506,12 @@
         <v>0.04935</v>
       </c>
       <c r="T129" s="1" t="n">
+        <v>0.04906</v>
+      </c>
+      <c r="U129" s="1" t="n">
         <v>0.04935</v>
       </c>
-      <c r="U129" s="1" t="n">
+      <c r="V129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -9186,9 +9576,12 @@
         <v>1.22e-05</v>
       </c>
       <c r="T130" s="1" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="U130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="U130" s="1" t="n">
+      <c r="V130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -9253,9 +9646,12 @@
         <v>7.5e-06</v>
       </c>
       <c r="T131" s="1" t="n">
+        <v>7.3e-06</v>
+      </c>
+      <c r="U131" s="1" t="n">
         <v>7.5e-06</v>
       </c>
-      <c r="U131" s="1" t="n">
+      <c r="V131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -9320,9 +9716,12 @@
         <v>0.00697</v>
       </c>
       <c r="T132" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="U132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="U132" s="1" t="n">
+      <c r="V132" s="1" t="n">
         <v>0.00697</v>
       </c>
     </row>
@@ -9387,9 +9786,12 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="T133" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="U133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="U133" s="1" t="n">
+      <c r="V133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -9454,9 +9856,12 @@
         <v>0.0004087</v>
       </c>
       <c r="T134" s="1" t="n">
+        <v>0.0004107</v>
+      </c>
+      <c r="U134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="U134" s="1" t="n">
+      <c r="V134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -9521,9 +9926,12 @@
         <v>0.08148</v>
       </c>
       <c r="T135" s="1" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="U135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="U135" s="1" t="n">
+      <c r="V135" s="1" t="n">
         <v>0.08148</v>
       </c>
     </row>
@@ -9588,9 +9996,12 @@
         <v>0.0078</v>
       </c>
       <c r="T136" s="1" t="n">
+        <v>0.007844</v>
+      </c>
+      <c r="U136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="U136" s="1" t="n">
+      <c r="V136" s="1" t="n">
         <v>0.0078</v>
       </c>
     </row>
@@ -9655,9 +10066,12 @@
         <v>0.0008066</v>
       </c>
       <c r="T137" s="1" t="n">
+        <v>0.0008079</v>
+      </c>
+      <c r="U137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="U137" s="1" t="n">
+      <c r="V137" s="1" t="n">
         <v>0.0008066</v>
       </c>
     </row>
@@ -9722,9 +10136,12 @@
         <v>0.1453</v>
       </c>
       <c r="T138" s="1" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="U138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="U138" s="1" t="n">
+      <c r="V138" s="1" t="n">
         <v>0.1453</v>
       </c>
     </row>
@@ -9789,9 +10206,12 @@
         <v>0.006677</v>
       </c>
       <c r="T139" s="1" t="n">
+        <v>0.006679</v>
+      </c>
+      <c r="U139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="U139" s="1" t="n">
+      <c r="V139" s="1" t="n">
         <v>0.006677</v>
       </c>
     </row>
@@ -9856,9 +10276,12 @@
         <v>0.01377</v>
       </c>
       <c r="T140" s="1" t="n">
+        <v>0.01378</v>
+      </c>
+      <c r="U140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="U140" s="1" t="n">
+      <c r="V140" s="1" t="n">
         <v>0.01377</v>
       </c>
     </row>
@@ -9923,9 +10346,12 @@
         <v>0.09667000000000001</v>
       </c>
       <c r="T141" s="1" t="n">
+        <v>0.09668</v>
+      </c>
+      <c r="U141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="U141" s="1" t="n">
+      <c r="V141" s="1" t="n">
         <v>0.09667000000000001</v>
       </c>
     </row>
@@ -9990,9 +10416,12 @@
         <v>0.05408</v>
       </c>
       <c r="T142" s="1" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="U142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="U142" s="1" t="n">
+      <c r="V142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -10057,9 +10486,12 @@
         <v>0.3219</v>
       </c>
       <c r="T143" s="1" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="U143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="U143" s="1" t="n">
+      <c r="V143" s="1" t="n">
         <v>0.3219</v>
       </c>
     </row>
@@ -10124,10 +10556,13 @@
         <v>0.02558</v>
       </c>
       <c r="T144" s="1" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="U144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="U144" s="1" t="n">
-        <v>0.02558</v>
+      <c r="V144" s="1" t="n">
+        <v>0.02557</v>
       </c>
     </row>
     <row r="145">
@@ -10191,9 +10626,12 @@
         <v>0.2352</v>
       </c>
       <c r="T145" s="1" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="U145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="U145" s="1" t="n">
+      <c r="V145" s="1" t="n">
         <v>0.2352</v>
       </c>
     </row>
@@ -10258,9 +10696,12 @@
         <v>0.006992</v>
       </c>
       <c r="T146" s="1" t="n">
+        <v>0.007053</v>
+      </c>
+      <c r="U146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="U146" s="1" t="n">
+      <c r="V146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -10325,9 +10766,12 @@
         <v>0.08644</v>
       </c>
       <c r="T147" s="1" t="n">
+        <v>0.08667999999999999</v>
+      </c>
+      <c r="U147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="U147" s="1" t="n">
+      <c r="V147" s="1" t="n">
         <v>0.08597</v>
       </c>
     </row>
@@ -10392,9 +10836,12 @@
         <v>0.05216</v>
       </c>
       <c r="T148" s="1" t="n">
+        <v>0.05224</v>
+      </c>
+      <c r="U148" s="1" t="n">
         <v>0.05284</v>
       </c>
-      <c r="U148" s="1" t="n">
+      <c r="V148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -10459,9 +10906,12 @@
         <v>0.02395</v>
       </c>
       <c r="T149" s="1" t="n">
+        <v>0.02392</v>
+      </c>
+      <c r="U149" s="1" t="n">
         <v>0.02399</v>
       </c>
-      <c r="U149" s="1" t="n">
+      <c r="V149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -10526,9 +10976,12 @@
         <v>0.08618000000000001</v>
       </c>
       <c r="T150" s="1" t="n">
+        <v>0.08653</v>
+      </c>
+      <c r="U150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="U150" s="1" t="n">
+      <c r="V150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -10593,9 +11046,12 @@
         <v>0.02322</v>
       </c>
       <c r="T151" s="1" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="U151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="U151" s="1" t="n">
+      <c r="V151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -10660,10 +11116,13 @@
         <v>0.02528</v>
       </c>
       <c r="T152" s="1" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="U152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="U152" s="1" t="n">
-        <v>0.02528</v>
+      <c r="V152" s="1" t="n">
+        <v>0.02524</v>
       </c>
     </row>
     <row r="153">
@@ -10727,9 +11186,12 @@
         <v>0.0002109</v>
       </c>
       <c r="T153" s="1" t="n">
+        <v>0.0002118</v>
+      </c>
+      <c r="U153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="U153" s="1" t="n">
+      <c r="V153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -10794,9 +11256,12 @@
         <v>0.4389</v>
       </c>
       <c r="T154" s="1" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="U154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="U154" s="1" t="n">
+      <c r="V154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -10861,9 +11326,12 @@
         <v>0.06784999999999999</v>
       </c>
       <c r="T155" s="1" t="n">
+        <v>0.06796000000000001</v>
+      </c>
+      <c r="U155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="U155" s="1" t="n">
+      <c r="V155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -10928,9 +11396,12 @@
         <v>0.12939</v>
       </c>
       <c r="T156" s="1" t="n">
-        <v>0.12939</v>
+        <v>0.13403</v>
       </c>
       <c r="U156" s="1" t="n">
+        <v>0.13403</v>
+      </c>
+      <c r="V156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -10995,10 +11466,13 @@
         <v>0.4826</v>
       </c>
       <c r="T157" s="1" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="U157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="U157" s="1" t="n">
-        <v>0.4826</v>
+      <c r="V157" s="1" t="n">
+        <v>0.4823</v>
       </c>
     </row>
     <row r="158">
@@ -11062,9 +11536,12 @@
         <v>0.451</v>
       </c>
       <c r="T158" s="1" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="U158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="U158" s="1" t="n">
+      <c r="V158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -11129,9 +11606,12 @@
         <v>0.007417</v>
       </c>
       <c r="T159" s="1" t="n">
+        <v>0.007433</v>
+      </c>
+      <c r="U159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="U159" s="1" t="n">
+      <c r="V159" s="1" t="n">
         <v>0.007417</v>
       </c>
     </row>
@@ -11196,9 +11676,12 @@
         <v>0.004656</v>
       </c>
       <c r="T160" s="1" t="n">
+        <v>0.004657</v>
+      </c>
+      <c r="U160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="U160" s="1" t="n">
+      <c r="V160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -11263,9 +11746,12 @@
         <v>0.004276</v>
       </c>
       <c r="T161" s="1" t="n">
+        <v>0.004291</v>
+      </c>
+      <c r="U161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="U161" s="1" t="n">
+      <c r="V161" s="1" t="n">
         <v>0.004276</v>
       </c>
     </row>
@@ -11330,9 +11816,12 @@
         <v>0.0954</v>
       </c>
       <c r="T162" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="U162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="U162" s="1" t="n">
+      <c r="V162" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -11397,9 +11886,12 @@
         <v>0.2843</v>
       </c>
       <c r="T163" s="1" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="U163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="U163" s="1" t="n">
+      <c r="V163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -11464,9 +11956,12 @@
         <v>0.1137</v>
       </c>
       <c r="T164" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="U164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="U164" s="1" t="n">
+      <c r="V164" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -11531,9 +12026,12 @@
         <v>0.1748</v>
       </c>
       <c r="T165" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="U165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="U165" s="1" t="n">
+      <c r="V165" s="1" t="n">
         <v>0.1748</v>
       </c>
     </row>
@@ -11598,9 +12096,12 @@
         <v>0.01004</v>
       </c>
       <c r="T166" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="U166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="U166" s="1" t="n">
+      <c r="V166" s="1" t="n">
         <v>0.01004</v>
       </c>
     </row>
@@ -11665,9 +12166,12 @@
         <v>1.814</v>
       </c>
       <c r="T167" s="1" t="n">
+        <v>1.819</v>
+      </c>
+      <c r="U167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="U167" s="1" t="n">
+      <c r="V167" s="1" t="n">
         <v>1.814</v>
       </c>
     </row>
@@ -11732,9 +12236,12 @@
         <v>1.346</v>
       </c>
       <c r="T168" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="U168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="U168" s="1" t="n">
+      <c r="V168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -11799,9 +12306,12 @@
         <v>0.007284</v>
       </c>
       <c r="T169" s="1" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="U169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="U169" s="1" t="n">
+      <c r="V169" s="1" t="n">
         <v>0.007284</v>
       </c>
     </row>
@@ -11866,9 +12376,12 @@
         <v>0.0116</v>
       </c>
       <c r="T170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="U170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="U170" s="1" t="n">
+      <c r="V170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -11933,9 +12446,12 @@
         <v>0.00576</v>
       </c>
       <c r="T171" s="1" t="n">
+        <v>0.005778</v>
+      </c>
+      <c r="U171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="U171" s="1" t="n">
+      <c r="V171" s="1" t="n">
         <v>0.00576</v>
       </c>
     </row>
@@ -12000,9 +12516,12 @@
         <v>0.14867</v>
       </c>
       <c r="T172" s="1" t="n">
+        <v>0.14854</v>
+      </c>
+      <c r="U172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="U172" s="1" t="n">
+      <c r="V172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -12067,9 +12586,12 @@
         <v>4.892</v>
       </c>
       <c r="T173" s="1" t="n">
+        <v>4.877</v>
+      </c>
+      <c r="U173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="U173" s="1" t="n">
+      <c r="V173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -12134,9 +12656,12 @@
         <v>0.07789</v>
       </c>
       <c r="T174" s="1" t="n">
+        <v>0.07790999999999999</v>
+      </c>
+      <c r="U174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="U174" s="1" t="n">
+      <c r="V174" s="1" t="n">
         <v>0.07789</v>
       </c>
     </row>
@@ -12201,9 +12726,12 @@
         <v>0.007403</v>
       </c>
       <c r="T175" s="1" t="n">
+        <v>0.007417</v>
+      </c>
+      <c r="U175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="U175" s="1" t="n">
+      <c r="V175" s="1" t="n">
         <v>0.007403</v>
       </c>
     </row>
@@ -12268,9 +12796,12 @@
         <v>0.1985</v>
       </c>
       <c r="T176" s="1" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="U176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="U176" s="1" t="n">
+      <c r="V176" s="1" t="n">
         <v>0.1985</v>
       </c>
     </row>
@@ -12335,9 +12866,12 @@
         <v>0.05172</v>
       </c>
       <c r="T177" s="1" t="n">
+        <v>0.05186</v>
+      </c>
+      <c r="U177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="U177" s="1" t="n">
+      <c r="V177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -12402,9 +12936,12 @@
         <v>0.05447</v>
       </c>
       <c r="T178" s="1" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="U178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="U178" s="1" t="n">
+      <c r="V178" s="1" t="n">
         <v>0.05447</v>
       </c>
     </row>
@@ -12469,9 +13006,12 @@
         <v>0.02336</v>
       </c>
       <c r="T179" s="1" t="n">
-        <v>0.02338</v>
+        <v>0.02341</v>
       </c>
       <c r="U179" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="V179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -12536,9 +13076,12 @@
         <v>0.6971000000000001</v>
       </c>
       <c r="T180" s="1" t="n">
+        <v>0.6971000000000001</v>
+      </c>
+      <c r="U180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="U180" s="1" t="n">
+      <c r="V180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -12603,9 +13146,12 @@
         <v>0.0003741</v>
       </c>
       <c r="T181" s="1" t="n">
+        <v>0.0003754</v>
+      </c>
+      <c r="U181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="U181" s="1" t="n">
+      <c r="V181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -12670,9 +13216,12 @@
         <v>0.01257</v>
       </c>
       <c r="T182" s="1" t="n">
+        <v>0.01264</v>
+      </c>
+      <c r="U182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="U182" s="1" t="n">
+      <c r="V182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -12737,9 +13286,12 @@
         <v>4.223</v>
       </c>
       <c r="T183" s="1" t="n">
+        <v>4.238</v>
+      </c>
+      <c r="U183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="U183" s="1" t="n">
+      <c r="V183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -12804,9 +13356,12 @@
         <v>0.2335</v>
       </c>
       <c r="T184" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="U184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="U184" s="1" t="n">
+      <c r="V184" s="1" t="n">
         <v>0.2335</v>
       </c>
     </row>
@@ -12871,9 +13426,12 @@
         <v>0.03708</v>
       </c>
       <c r="T185" s="1" t="n">
+        <v>0.03709</v>
+      </c>
+      <c r="U185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="U185" s="1" t="n">
+      <c r="V185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -12938,10 +13496,13 @@
         <v>0.11555</v>
       </c>
       <c r="T186" s="1" t="n">
+        <v>0.11543</v>
+      </c>
+      <c r="U186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="U186" s="1" t="n">
-        <v>0.11555</v>
+      <c r="V186" s="1" t="n">
+        <v>0.11543</v>
       </c>
     </row>
     <row r="187">
@@ -13005,9 +13566,12 @@
         <v>0.009124999999999999</v>
       </c>
       <c r="T187" s="1" t="n">
+        <v>0.009168000000000001</v>
+      </c>
+      <c r="U187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="U187" s="1" t="n">
+      <c r="V187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -13072,9 +13636,12 @@
         <v>0.0969</v>
       </c>
       <c r="T188" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="U188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="U188" s="1" t="n">
+      <c r="V188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -13139,10 +13706,13 @@
         <v>0.02731</v>
       </c>
       <c r="T189" s="1" t="n">
+        <v>0.02727</v>
+      </c>
+      <c r="U189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="U189" s="1" t="n">
-        <v>0.02731</v>
+      <c r="V189" s="1" t="n">
+        <v>0.02727</v>
       </c>
     </row>
     <row r="190">
@@ -13206,9 +13776,12 @@
         <v>0.00864</v>
       </c>
       <c r="T190" s="1" t="n">
+        <v>0.008659999999999999</v>
+      </c>
+      <c r="U190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="U190" s="1" t="n">
+      <c r="V190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -13273,9 +13846,12 @@
         <v>0.001951</v>
       </c>
       <c r="T191" s="1" t="n">
+        <v>0.001958</v>
+      </c>
+      <c r="U191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="U191" s="1" t="n">
+      <c r="V191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -13340,9 +13916,12 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="T192" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="U192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="U192" s="1" t="n">
+      <c r="V192" s="1" t="n">
         <v>0.09959999999999999</v>
       </c>
     </row>
@@ -13407,9 +13986,12 @@
         <v>0.0231</v>
       </c>
       <c r="T193" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="U193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="U193" s="1" t="n">
+      <c r="V193" s="1" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -13474,9 +14056,12 @@
         <v>0.01341</v>
       </c>
       <c r="T194" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="U194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="U194" s="1" t="n">
+      <c r="V194" s="1" t="n">
         <v>0.01341</v>
       </c>
     </row>
@@ -13541,9 +14126,12 @@
         <v>0.02076</v>
       </c>
       <c r="T195" s="1" t="n">
+        <v>0.02082</v>
+      </c>
+      <c r="U195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="U195" s="1" t="n">
+      <c r="V195" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -13608,9 +14196,12 @@
         <v>0.17498</v>
       </c>
       <c r="T196" s="1" t="n">
+        <v>0.17448</v>
+      </c>
+      <c r="U196" s="1" t="n">
         <v>0.17659</v>
       </c>
-      <c r="U196" s="1" t="n">
+      <c r="V196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -13675,9 +14266,12 @@
         <v>0.007396</v>
       </c>
       <c r="T197" s="1" t="n">
+        <v>0.007349</v>
+      </c>
+      <c r="U197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="U197" s="1" t="n">
+      <c r="V197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -13742,9 +14336,12 @@
         <v>0.01902</v>
       </c>
       <c r="T198" s="1" t="n">
+        <v>0.01902</v>
+      </c>
+      <c r="U198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="U198" s="1" t="n">
+      <c r="V198" s="1" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -13809,9 +14406,12 @@
         <v>0.01629</v>
       </c>
       <c r="T199" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="U199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="U199" s="1" t="n">
+      <c r="V199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -13876,9 +14476,12 @@
         <v>0.2971</v>
       </c>
       <c r="T200" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="U200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="U200" s="1" t="n">
+      <c r="V200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -13943,9 +14546,12 @@
         <v>0.006209</v>
       </c>
       <c r="T201" s="1" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="U201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="U201" s="1" t="n">
+      <c r="V201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -14010,9 +14616,12 @@
         <v>0.0004386</v>
       </c>
       <c r="T202" s="1" t="n">
+        <v>0.0004399</v>
+      </c>
+      <c r="U202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="U202" s="1" t="n">
+      <c r="V202" s="1" t="n">
         <v>0.0004386</v>
       </c>
     </row>
@@ -14077,9 +14686,12 @@
         <v>0.007252</v>
       </c>
       <c r="T203" s="1" t="n">
+        <v>0.007275</v>
+      </c>
+      <c r="U203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="U203" s="1" t="n">
+      <c r="V203" s="1" t="n">
         <v>0.007245</v>
       </c>
     </row>
@@ -14144,9 +14756,12 @@
         <v>0.1307</v>
       </c>
       <c r="T204" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="U204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="U204" s="1" t="n">
+      <c r="V204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -14211,9 +14826,12 @@
         <v>0.01416</v>
       </c>
       <c r="T205" s="1" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="U205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="U205" s="1" t="n">
+      <c r="V205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -14278,9 +14896,12 @@
         <v>0.003576</v>
       </c>
       <c r="T206" s="1" t="n">
+        <v>0.003571</v>
+      </c>
+      <c r="U206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="U206" s="1" t="n">
+      <c r="V206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -14345,9 +14966,12 @@
         <v>0.05914</v>
       </c>
       <c r="T207" s="1" t="n">
+        <v>0.05952</v>
+      </c>
+      <c r="U207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="U207" s="1" t="n">
+      <c r="V207" s="1" t="n">
         <v>0.05914</v>
       </c>
     </row>
@@ -14412,9 +15036,12 @@
         <v>15.43</v>
       </c>
       <c r="T208" s="1" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="U208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="U208" s="1" t="n">
+      <c r="V208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -14479,9 +15106,12 @@
         <v>5194.4</v>
       </c>
       <c r="T209" s="1" t="n">
+        <v>5192.3</v>
+      </c>
+      <c r="U209" s="1" t="n">
         <v>5194.4</v>
       </c>
-      <c r="U209" s="1" t="n">
+      <c r="V209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -14546,10 +15176,13 @@
         <v>0.12002</v>
       </c>
       <c r="T210" s="1" t="n">
+        <v>0.11941</v>
+      </c>
+      <c r="U210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="U210" s="1" t="n">
-        <v>0.11955</v>
+      <c r="V210" s="1" t="n">
+        <v>0.11941</v>
       </c>
     </row>
     <row r="211">
@@ -14613,9 +15246,12 @@
         <v>0.1815</v>
       </c>
       <c r="T211" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="U211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="U211" s="1" t="n">
+      <c r="V211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -14680,9 +15316,12 @@
         <v>0.0302</v>
       </c>
       <c r="T212" s="1" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="U212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="U212" s="1" t="n">
+      <c r="V212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -14747,9 +15386,12 @@
         <v>1.3966</v>
       </c>
       <c r="T213" s="1" t="n">
-        <v>1.3979</v>
+        <v>1.3995</v>
       </c>
       <c r="U213" s="1" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="V213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -14814,9 +15456,12 @@
         <v>0.05654</v>
       </c>
       <c r="T214" s="1" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="U214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="U214" s="1" t="n">
+      <c r="V214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -14881,9 +15526,12 @@
         <v>0.04426</v>
       </c>
       <c r="T215" s="1" t="n">
+        <v>0.04399</v>
+      </c>
+      <c r="U215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="U215" s="1" t="n">
+      <c r="V215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -14948,9 +15596,12 @@
         <v>0.15068</v>
       </c>
       <c r="T216" s="1" t="n">
+        <v>0.15096</v>
+      </c>
+      <c r="U216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="U216" s="1" t="n">
+      <c r="V216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -15015,9 +15666,12 @@
         <v>0.074</v>
       </c>
       <c r="T217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="U217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="U217" s="1" t="n">
+      <c r="V217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -15082,9 +15736,12 @@
         <v>0.00267</v>
       </c>
       <c r="T218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="U218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="U218" s="1" t="n">
+      <c r="V218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -15149,9 +15806,12 @@
         <v>0.01699</v>
       </c>
       <c r="T219" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="U219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="U219" s="1" t="n">
+      <c r="V219" s="1" t="n">
         <v>0.01696</v>
       </c>
     </row>
@@ -15216,9 +15876,12 @@
         <v>0.05504</v>
       </c>
       <c r="T220" s="1" t="n">
+        <v>0.05519</v>
+      </c>
+      <c r="U220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="U220" s="1" t="n">
+      <c r="V220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -15283,9 +15946,12 @@
         <v>0.02186</v>
       </c>
       <c r="T221" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="U221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="U221" s="1" t="n">
+      <c r="V221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -15350,9 +16016,12 @@
         <v>0.00923</v>
       </c>
       <c r="T222" s="1" t="n">
+        <v>0.00928</v>
+      </c>
+      <c r="U222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="U222" s="1" t="n">
+      <c r="V222" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -15417,9 +16086,12 @@
         <v>0.0164</v>
       </c>
       <c r="T223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="U223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="U223" s="1" t="n">
+      <c r="V223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -15484,9 +16156,12 @@
         <v>0.03843</v>
       </c>
       <c r="T224" s="1" t="n">
-        <v>0.03843</v>
+        <v>0.03846</v>
       </c>
       <c r="U224" s="1" t="n">
+        <v>0.03846</v>
+      </c>
+      <c r="V224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -15551,9 +16226,12 @@
         <v>0.001514</v>
       </c>
       <c r="T225" s="1" t="n">
+        <v>0.001517</v>
+      </c>
+      <c r="U225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="U225" s="1" t="n">
+      <c r="V225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -15618,9 +16296,12 @@
         <v>27.31</v>
       </c>
       <c r="T226" s="1" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="U226" s="1" t="n">
         <v>27.31</v>
       </c>
-      <c r="U226" s="1" t="n">
+      <c r="V226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -15685,9 +16366,12 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="T227" s="1" t="n">
+        <v>0.07018000000000001</v>
+      </c>
+      <c r="U227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="U227" s="1" t="n">
+      <c r="V227" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -15752,9 +16436,12 @@
         <v>0.3113</v>
       </c>
       <c r="T228" s="1" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="U228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="U228" s="1" t="n">
+      <c r="V228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -15819,9 +16506,12 @@
         <v>18.36</v>
       </c>
       <c r="T229" s="1" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="U229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="U229" s="1" t="n">
+      <c r="V229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -15886,9 +16576,12 @@
         <v>0.01915</v>
       </c>
       <c r="T230" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="U230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="U230" s="1" t="n">
+      <c r="V230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -15953,9 +16646,12 @@
         <v>0.01215</v>
       </c>
       <c r="T231" s="1" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="U231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="U231" s="1" t="n">
+      <c r="V231" s="1" t="n">
         <v>0.01214</v>
       </c>
     </row>
@@ -16020,9 +16716,12 @@
         <v>0.2269</v>
       </c>
       <c r="T232" s="1" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="U232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="U232" s="1" t="n">
+      <c r="V232" s="1" t="n">
         <v>0.2269</v>
       </c>
     </row>
@@ -16087,9 +16786,12 @@
         <v>0.07074999999999999</v>
       </c>
       <c r="T233" s="1" t="n">
+        <v>0.07081999999999999</v>
+      </c>
+      <c r="U233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="U233" s="1" t="n">
+      <c r="V233" s="1" t="n">
         <v>0.07073</v>
       </c>
     </row>
@@ -16154,9 +16856,12 @@
         <v>0.1705</v>
       </c>
       <c r="T234" s="1" t="n">
-        <v>0.1706</v>
+        <v>0.1709</v>
       </c>
       <c r="U234" s="1" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -16221,9 +16926,12 @@
         <v>0.0251</v>
       </c>
       <c r="T235" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="U235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="U235" s="1" t="n">
+      <c r="V235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -16288,9 +16996,12 @@
         <v>0.02998</v>
       </c>
       <c r="T236" s="1" t="n">
+        <v>0.02999</v>
+      </c>
+      <c r="U236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="U236" s="1" t="n">
+      <c r="V236" s="1" t="n">
         <v>0.02993</v>
       </c>
     </row>
@@ -16355,9 +17066,12 @@
         <v>2.029</v>
       </c>
       <c r="T237" s="1" t="n">
-        <v>2.029</v>
+        <v>2.039</v>
       </c>
       <c r="U237" s="1" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="V237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -16422,10 +17136,13 @@
         <v>0.4213</v>
       </c>
       <c r="T238" s="1" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="U238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="U238" s="1" t="n">
-        <v>0.42</v>
+      <c r="V238" s="1" t="n">
+        <v>0.4198</v>
       </c>
     </row>
     <row r="239">
@@ -16489,10 +17206,13 @@
         <v>0.03316</v>
       </c>
       <c r="T239" s="1" t="n">
+        <v>0.03308</v>
+      </c>
+      <c r="U239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="U239" s="1" t="n">
-        <v>0.03315</v>
+      <c r="V239" s="1" t="n">
+        <v>0.03308</v>
       </c>
     </row>
     <row r="240">
@@ -16556,9 +17276,12 @@
         <v>0.0339</v>
       </c>
       <c r="T240" s="1" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="U240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="U240" s="1" t="n">
+      <c r="V240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -16623,10 +17346,13 @@
         <v>0.000749</v>
       </c>
       <c r="T241" s="1" t="n">
+        <v>0.0007463</v>
+      </c>
+      <c r="U241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="U241" s="1" t="n">
-        <v>0.0007489</v>
+      <c r="V241" s="1" t="n">
+        <v>0.0007463</v>
       </c>
     </row>
     <row r="242">
@@ -16690,10 +17416,13 @@
         <v>0.1823</v>
       </c>
       <c r="T242" s="1" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="U242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="U242" s="1" t="n">
-        <v>0.1823</v>
+      <c r="V242" s="1" t="n">
+        <v>0.1822</v>
       </c>
     </row>
     <row r="243">
@@ -16757,9 +17486,12 @@
         <v>0.014706</v>
       </c>
       <c r="T243" s="1" t="n">
+        <v>0.014728</v>
+      </c>
+      <c r="U243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="U243" s="1" t="n">
+      <c r="V243" s="1" t="n">
         <v>0.014706</v>
       </c>
     </row>
@@ -16824,9 +17556,12 @@
         <v>2.99e-05</v>
       </c>
       <c r="T244" s="1" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="U244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="U244" s="1" t="n">
+      <c r="V244" s="1" t="n">
         <v>2.99e-05</v>
       </c>
     </row>
@@ -16891,9 +17626,12 @@
         <v>0.03508</v>
       </c>
       <c r="T245" s="1" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="U245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="U245" s="1" t="n">
+      <c r="V245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -16958,9 +17696,12 @@
         <v>0.08026</v>
       </c>
       <c r="T246" s="1" t="n">
+        <v>0.08036</v>
+      </c>
+      <c r="U246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="U246" s="1" t="n">
+      <c r="V246" s="1" t="n">
         <v>0.08018</v>
       </c>
     </row>
@@ -17025,10 +17766,13 @@
         <v>0.007172</v>
       </c>
       <c r="T247" s="1" t="n">
+        <v>0.007129</v>
+      </c>
+      <c r="U247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="U247" s="1" t="n">
-        <v>0.007172</v>
+      <c r="V247" s="1" t="n">
+        <v>0.007129</v>
       </c>
     </row>
     <row r="248">
@@ -17092,9 +17836,12 @@
         <v>0.09239</v>
       </c>
       <c r="T248" s="1" t="n">
+        <v>0.09317</v>
+      </c>
+      <c r="U248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="U248" s="1" t="n">
+      <c r="V248" s="1" t="n">
         <v>0.09239</v>
       </c>
     </row>
@@ -17162,6 +17909,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="U249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -17226,9 +17976,12 @@
         <v>0.03471</v>
       </c>
       <c r="T250" s="1" t="n">
+        <v>0.03481</v>
+      </c>
+      <c r="U250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="U250" s="1" t="n">
+      <c r="V250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -17293,10 +18046,13 @@
         <v>0.039</v>
       </c>
       <c r="T251" s="1" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="U251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="U251" s="1" t="n">
-        <v>0.039</v>
+      <c r="V251" s="1" t="n">
+        <v>0.03896</v>
       </c>
     </row>
     <row r="252">
@@ -17360,9 +18116,12 @@
         <v>0.0877</v>
       </c>
       <c r="T252" s="1" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="U252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="U252" s="1" t="n">
+      <c r="V252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -17427,9 +18186,12 @@
         <v>4.067</v>
       </c>
       <c r="T253" s="1" t="n">
+        <v>4.081</v>
+      </c>
+      <c r="U253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="U253" s="1" t="n">
+      <c r="V253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -17494,9 +18256,12 @@
         <v>0.1867</v>
       </c>
       <c r="T254" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="U254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="U254" s="1" t="n">
+      <c r="V254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -17561,9 +18326,12 @@
         <v>0.07174</v>
       </c>
       <c r="T255" s="1" t="n">
+        <v>0.07192999999999999</v>
+      </c>
+      <c r="U255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="U255" s="1" t="n">
+      <c r="V255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -17628,9 +18396,12 @@
         <v>0.01823</v>
       </c>
       <c r="T256" s="1" t="n">
-        <v>0.01835</v>
+        <v>0.01845</v>
       </c>
       <c r="U256" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="V256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -17695,9 +18466,12 @@
         <v>5.933</v>
       </c>
       <c r="T257" s="1" t="n">
+        <v>5.947</v>
+      </c>
+      <c r="U257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="U257" s="1" t="n">
+      <c r="V257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -17762,10 +18536,13 @@
         <v>0.26</v>
       </c>
       <c r="T258" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="U258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="U258" s="1" t="n">
-        <v>0.2599</v>
+      <c r="V258" s="1" t="n">
+        <v>0.2596</v>
       </c>
     </row>
     <row r="259">
@@ -17829,9 +18606,12 @@
         <v>0.1353</v>
       </c>
       <c r="T259" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="U259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="U259" s="1" t="n">
+      <c r="V259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -17896,9 +18676,12 @@
         <v>0.30792</v>
       </c>
       <c r="T260" s="1" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="U260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="U260" s="1" t="n">
+      <c r="V260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -17963,9 +18746,12 @@
         <v>0.09871000000000001</v>
       </c>
       <c r="T261" s="1" t="n">
+        <v>0.09876</v>
+      </c>
+      <c r="U261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="U261" s="1" t="n">
+      <c r="V261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -18030,9 +18816,12 @@
         <v>0.5377999999999999</v>
       </c>
       <c r="T262" s="1" t="n">
+        <v>0.5396</v>
+      </c>
+      <c r="U262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="U262" s="1" t="n">
+      <c r="V262" s="1" t="n">
         <v>0.5377999999999999</v>
       </c>
     </row>
@@ -18097,9 +18886,12 @@
         <v>0.2877</v>
       </c>
       <c r="T263" s="1" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="U263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="U263" s="1" t="n">
+      <c r="V263" s="1" t="n">
         <v>0.2877</v>
       </c>
     </row>
@@ -18164,9 +18956,12 @@
         <v>0.974</v>
       </c>
       <c r="T264" s="1" t="n">
-        <v>0.983</v>
+        <v>0.989</v>
       </c>
       <c r="U264" s="1" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="V264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -18231,9 +19026,12 @@
         <v>0.5371</v>
       </c>
       <c r="T265" s="1" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="U265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="U265" s="1" t="n">
+      <c r="V265" s="1" t="n">
         <v>0.5367</v>
       </c>
     </row>
@@ -18298,9 +19096,12 @@
         <v>0.07341</v>
       </c>
       <c r="T266" s="1" t="n">
+        <v>0.07346999999999999</v>
+      </c>
+      <c r="U266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="U266" s="1" t="n">
+      <c r="V266" s="1" t="n">
         <v>0.07341</v>
       </c>
     </row>
@@ -18365,9 +19166,12 @@
         <v>0.02142</v>
       </c>
       <c r="T267" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="U267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="U267" s="1" t="n">
+      <c r="V267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -18432,9 +19236,12 @@
         <v>0.01603</v>
       </c>
       <c r="T268" s="1" t="n">
+        <v>0.01605</v>
+      </c>
+      <c r="U268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="U268" s="1" t="n">
+      <c r="V268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -18499,9 +19306,12 @@
         <v>0.003787</v>
       </c>
       <c r="T269" s="1" t="n">
+        <v>0.003781</v>
+      </c>
+      <c r="U269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="U269" s="1" t="n">
+      <c r="V269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -18566,9 +19376,12 @@
         <v>0.00754</v>
       </c>
       <c r="T270" s="1" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="U270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="U270" s="1" t="n">
+      <c r="V270" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -18633,9 +19446,12 @@
         <v>0.05481</v>
       </c>
       <c r="T271" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="U271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="U271" s="1" t="n">
+      <c r="V271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -18700,9 +19516,12 @@
         <v>2.273</v>
       </c>
       <c r="T272" s="1" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="U272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="U272" s="1" t="n">
+      <c r="V272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -18767,9 +19586,12 @@
         <v>0.05474</v>
       </c>
       <c r="T273" s="1" t="n">
+        <v>0.05484</v>
+      </c>
+      <c r="U273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="U273" s="1" t="n">
+      <c r="V273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -18834,9 +19656,12 @@
         <v>0.02326</v>
       </c>
       <c r="T274" s="1" t="n">
-        <v>0.02336</v>
+        <v>0.02349</v>
       </c>
       <c r="U274" s="1" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="V274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -18901,9 +19726,12 @@
         <v>1.172</v>
       </c>
       <c r="T275" s="1" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="U275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="U275" s="1" t="n">
+      <c r="V275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -18968,9 +19796,12 @@
         <v>0.2713</v>
       </c>
       <c r="T276" s="1" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="U276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="U276" s="1" t="n">
+      <c r="V276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -19035,9 +19866,12 @@
         <v>0.919</v>
       </c>
       <c r="T277" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="U277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="U277" s="1" t="n">
+      <c r="V277" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -19102,9 +19936,12 @@
         <v>0.6218</v>
       </c>
       <c r="T278" s="1" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="U278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="U278" s="1" t="n">
+      <c r="V278" s="1" t="n">
         <v>0.6218</v>
       </c>
     </row>
@@ -19169,9 +20006,12 @@
         <v>0.001326</v>
       </c>
       <c r="T279" s="1" t="n">
+        <v>0.001329</v>
+      </c>
+      <c r="U279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="U279" s="1" t="n">
+      <c r="V279" s="1" t="n">
         <v>0.001326</v>
       </c>
     </row>
@@ -19236,9 +20076,12 @@
         <v>0.005601</v>
       </c>
       <c r="T280" s="1" t="n">
-        <v>0.005601</v>
+        <v>0.005613</v>
       </c>
       <c r="U280" s="1" t="n">
+        <v>0.005613</v>
+      </c>
+      <c r="V280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -19303,9 +20146,12 @@
         <v>1.516</v>
       </c>
       <c r="T281" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="U281" s="1" t="n">
+      <c r="V281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -19370,9 +20216,12 @@
         <v>28.27</v>
       </c>
       <c r="T282" s="1" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="U282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="U282" s="1" t="n">
+      <c r="V282" s="1" t="n">
         <v>28.25</v>
       </c>
     </row>
@@ -19437,9 +20286,12 @@
         <v>0.12797</v>
       </c>
       <c r="T283" s="1" t="n">
+        <v>0.12814</v>
+      </c>
+      <c r="U283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="U283" s="1" t="n">
+      <c r="V283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -19504,9 +20356,12 @@
         <v>0.01102</v>
       </c>
       <c r="T284" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="U284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="U284" s="1" t="n">
+      <c r="V284" s="1" t="n">
         <v>0.01102</v>
       </c>
     </row>
@@ -19571,9 +20426,12 @@
         <v>6.529</v>
       </c>
       <c r="T285" s="1" t="n">
+        <v>6.554</v>
+      </c>
+      <c r="U285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="U285" s="1" t="n">
+      <c r="V285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -19638,9 +20496,12 @@
         <v>0.01833</v>
       </c>
       <c r="T286" s="1" t="n">
+        <v>0.01834</v>
+      </c>
+      <c r="U286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="U286" s="1" t="n">
+      <c r="V286" s="1" t="n">
         <v>0.01831</v>
       </c>
     </row>
@@ -19705,9 +20566,12 @@
         <v>0.008331</v>
       </c>
       <c r="T287" s="1" t="n">
+        <v>0.008343</v>
+      </c>
+      <c r="U287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="U287" s="1" t="n">
+      <c r="V287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -19772,10 +20636,13 @@
         <v>0.3807</v>
       </c>
       <c r="T288" s="1" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="U288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="U288" s="1" t="n">
-        <v>0.3803</v>
+      <c r="V288" s="1" t="n">
+        <v>0.3791</v>
       </c>
     </row>
     <row r="289">
@@ -19839,9 +20706,12 @@
         <v>0.00974</v>
       </c>
       <c r="T289" s="1" t="n">
+        <v>0.009797999999999999</v>
+      </c>
+      <c r="U289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="U289" s="1" t="n">
+      <c r="V289" s="1" t="n">
         <v>0.00974</v>
       </c>
     </row>
@@ -19906,9 +20776,12 @@
         <v>0.02589</v>
       </c>
       <c r="T290" s="1" t="n">
+        <v>0.02597</v>
+      </c>
+      <c r="U290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="U290" s="1" t="n">
+      <c r="V290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -19973,10 +20846,13 @@
         <v>0.095</v>
       </c>
       <c r="T291" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="U291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="U291" s="1" t="n">
-        <v>0.095</v>
+      <c r="V291" s="1" t="n">
+        <v>0.094</v>
       </c>
     </row>
     <row r="292">
@@ -20040,9 +20916,12 @@
         <v>0.28682</v>
       </c>
       <c r="T292" s="1" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="U292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="U292" s="1" t="n">
+      <c r="V292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -20107,9 +20986,12 @@
         <v>0.01528</v>
       </c>
       <c r="T293" s="1" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="U293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="U293" s="1" t="n">
+      <c r="V293" s="1" t="n">
         <v>0.01528</v>
       </c>
     </row>
@@ -20174,9 +21056,12 @@
         <v>0.003385</v>
       </c>
       <c r="T294" s="1" t="n">
+        <v>0.003399</v>
+      </c>
+      <c r="U294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="U294" s="1" t="n">
+      <c r="V294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -20241,9 +21126,12 @@
         <v>0.042439</v>
       </c>
       <c r="T295" s="1" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="U295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="U295" s="1" t="n">
+      <c r="V295" s="1" t="n">
         <v>0.042232</v>
       </c>
     </row>
@@ -20308,9 +21196,12 @@
         <v>0.0294</v>
       </c>
       <c r="T296" s="1" t="n">
+        <v>0.02897</v>
+      </c>
+      <c r="U296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="U296" s="1" t="n">
+      <c r="V296" s="1" t="n">
         <v>0.02894</v>
       </c>
     </row>
@@ -20375,9 +21266,12 @@
         <v>0.03797</v>
       </c>
       <c r="T297" s="1" t="n">
+        <v>0.03799</v>
+      </c>
+      <c r="U297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="U297" s="1" t="n">
+      <c r="V297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -20442,9 +21336,12 @@
         <v>0.08304</v>
       </c>
       <c r="T298" s="1" t="n">
+        <v>0.08282</v>
+      </c>
+      <c r="U298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="U298" s="1" t="n">
+      <c r="V298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -20509,9 +21406,12 @@
         <v>0.0076</v>
       </c>
       <c r="T299" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="U299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="U299" s="1" t="n">
+      <c r="V299" s="1" t="n">
         <v>0.0076</v>
       </c>
     </row>
@@ -20576,9 +21476,12 @@
         <v>0.01496</v>
       </c>
       <c r="T300" s="1" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="U300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="U300" s="1" t="n">
+      <c r="V300" s="1" t="n">
         <v>0.01496</v>
       </c>
     </row>
@@ -20643,9 +21546,12 @@
         <v>0.1403</v>
       </c>
       <c r="T301" s="1" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="U301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="U301" s="1" t="n">
+      <c r="V301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -20710,9 +21616,12 @@
         <v>0.0006255</v>
       </c>
       <c r="T302" s="1" t="n">
+        <v>0.0006269</v>
+      </c>
+      <c r="U302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="U302" s="1" t="n">
+      <c r="V302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -20777,9 +21686,12 @@
         <v>0.06207</v>
       </c>
       <c r="T303" s="1" t="n">
+        <v>0.06231</v>
+      </c>
+      <c r="U303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="U303" s="1" t="n">
+      <c r="V303" s="1" t="n">
         <v>0.06207</v>
       </c>
     </row>
@@ -20844,9 +21756,12 @@
         <v>0.000162</v>
       </c>
       <c r="T304" s="1" t="n">
+        <v>0.0001623</v>
+      </c>
+      <c r="U304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="U304" s="1" t="n">
+      <c r="V304" s="1" t="n">
         <v>0.000162</v>
       </c>
     </row>
@@ -20911,9 +21826,12 @@
         <v>0.06071</v>
       </c>
       <c r="T305" s="1" t="n">
+        <v>0.06098</v>
+      </c>
+      <c r="U305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="U305" s="1" t="n">
+      <c r="V305" s="1" t="n">
         <v>0.06071</v>
       </c>
     </row>
@@ -20978,9 +21896,12 @@
         <v>0.022341</v>
       </c>
       <c r="T306" s="1" t="n">
+        <v>0.02232</v>
+      </c>
+      <c r="U306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="U306" s="1" t="n">
+      <c r="V306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -21045,9 +21966,12 @@
         <v>0.02278</v>
       </c>
       <c r="T307" s="1" t="n">
+        <v>0.02297</v>
+      </c>
+      <c r="U307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="U307" s="1" t="n">
+      <c r="V307" s="1" t="n">
         <v>0.02278</v>
       </c>
     </row>
@@ -21112,9 +22036,12 @@
         <v>0.00041</v>
       </c>
       <c r="T308" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="U308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="U308" s="1" t="n">
+      <c r="V308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -21179,9 +22106,12 @@
         <v>0.0897</v>
       </c>
       <c r="T309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="U309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="U309" s="1" t="n">
+      <c r="V309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -21246,9 +22176,12 @@
         <v>0.3704</v>
       </c>
       <c r="T310" s="1" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="U310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="U310" s="1" t="n">
+      <c r="V310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -21313,9 +22246,12 @@
         <v>0.0354</v>
       </c>
       <c r="T311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="U311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="U311" s="1" t="n">
+      <c r="V311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -21380,9 +22316,12 @@
         <v>0.02415</v>
       </c>
       <c r="T312" s="1" t="n">
+        <v>0.02426</v>
+      </c>
+      <c r="U312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="U312" s="1" t="n">
+      <c r="V312" s="1" t="n">
         <v>0.02415</v>
       </c>
     </row>
@@ -21447,9 +22386,12 @@
         <v>0.04087</v>
       </c>
       <c r="T313" s="1" t="n">
+        <v>0.04094</v>
+      </c>
+      <c r="U313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="U313" s="1" t="n">
+      <c r="V313" s="1" t="n">
         <v>0.04087</v>
       </c>
     </row>
@@ -21514,9 +22456,12 @@
         <v>3.932</v>
       </c>
       <c r="T314" s="1" t="n">
+        <v>3.937</v>
+      </c>
+      <c r="U314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="U314" s="1" t="n">
+      <c r="V314" s="1" t="n">
         <v>3.932</v>
       </c>
     </row>
@@ -21581,9 +22526,12 @@
         <v>0.159</v>
       </c>
       <c r="T315" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="U315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="U315" s="1" t="n">
+      <c r="V315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -21648,9 +22596,12 @@
         <v>0.09191000000000001</v>
       </c>
       <c r="T316" s="1" t="n">
+        <v>0.09067</v>
+      </c>
+      <c r="U316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="U316" s="1" t="n">
+      <c r="V316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -21715,9 +22666,12 @@
         <v>0.06806</v>
       </c>
       <c r="T317" s="1" t="n">
+        <v>0.06808</v>
+      </c>
+      <c r="U317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="U317" s="1" t="n">
+      <c r="V317" s="1" t="n">
         <v>0.06791999999999999</v>
       </c>
     </row>
@@ -21782,9 +22736,12 @@
         <v>0.012449</v>
       </c>
       <c r="T318" s="1" t="n">
+        <v>0.012463</v>
+      </c>
+      <c r="U318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="U318" s="1" t="n">
+      <c r="V318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -21849,9 +22806,12 @@
         <v>0.00113</v>
       </c>
       <c r="T319" s="1" t="n">
+        <v>0.001133</v>
+      </c>
+      <c r="U319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="U319" s="1" t="n">
+      <c r="V319" s="1" t="n">
         <v>0.00113</v>
       </c>
     </row>
@@ -21916,9 +22876,12 @@
         <v>0.0629</v>
       </c>
       <c r="T320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="U320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="U320" s="1" t="n">
+      <c r="V320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -21983,9 +22946,12 @@
         <v>0.00524</v>
       </c>
       <c r="T321" s="1" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="U321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="U321" s="1" t="n">
+      <c r="V321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -22050,9 +23016,12 @@
         <v>0.1111</v>
       </c>
       <c r="T322" s="1" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="U322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="U322" s="1" t="n">
+      <c r="V322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -22117,9 +23086,12 @@
         <v>0.04397</v>
       </c>
       <c r="T323" s="1" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="U323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="U323" s="1" t="n">
+      <c r="V323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -22184,9 +23156,12 @@
         <v>0.01781</v>
       </c>
       <c r="T324" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="U324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="U324" s="1" t="n">
+      <c r="V324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -22251,9 +23226,12 @@
         <v>0.005635</v>
       </c>
       <c r="T325" s="1" t="n">
+        <v>0.005656</v>
+      </c>
+      <c r="U325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="U325" s="1" t="n">
+      <c r="V325" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -22318,9 +23296,12 @@
         <v>0.001753</v>
       </c>
       <c r="T326" s="1" t="n">
+        <v>0.00176</v>
+      </c>
+      <c r="U326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="U326" s="1" t="n">
+      <c r="V326" s="1" t="n">
         <v>0.001751</v>
       </c>
     </row>
@@ -22385,9 +23366,12 @@
         <v>0.04011</v>
       </c>
       <c r="T327" s="1" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="U327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="U327" s="1" t="n">
+      <c r="V327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -22452,9 +23436,12 @@
         <v>0.053525</v>
       </c>
       <c r="T328" s="1" t="n">
+        <v>0.053583</v>
+      </c>
+      <c r="U328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="U328" s="1" t="n">
+      <c r="V328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -22519,9 +23506,12 @@
         <v>0.2773</v>
       </c>
       <c r="T329" s="1" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="U329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="U329" s="1" t="n">
+      <c r="V329" s="1" t="n">
         <v>0.2771</v>
       </c>
     </row>
@@ -22586,9 +23576,12 @@
         <v>0.1585</v>
       </c>
       <c r="T330" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="U330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="U330" s="1" t="n">
+      <c r="V330" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -22653,9 +23646,12 @@
         <v>0.05352</v>
       </c>
       <c r="T331" s="1" t="n">
+        <v>0.05365</v>
+      </c>
+      <c r="U331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="U331" s="1" t="n">
+      <c r="V331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -22723,6 +23719,9 @@
         <v>0.3624</v>
       </c>
       <c r="U332" s="1" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="V332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -22787,9 +23786,12 @@
         <v>0.0306</v>
       </c>
       <c r="T333" s="1" t="n">
-        <v>0.0306</v>
+        <v>0.03063</v>
       </c>
       <c r="U333" s="1" t="n">
+        <v>0.03063</v>
+      </c>
+      <c r="V333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -22854,9 +23856,12 @@
         <v>0.01779</v>
       </c>
       <c r="T334" s="1" t="n">
+        <v>0.01774</v>
+      </c>
+      <c r="U334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="U334" s="1" t="n">
+      <c r="V334" s="1" t="n">
         <v>0.01751</v>
       </c>
     </row>
@@ -22921,9 +23926,12 @@
         <v>0.0576</v>
       </c>
       <c r="T335" s="1" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="U335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="U335" s="1" t="n">
+      <c r="V335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -22988,10 +23996,13 @@
         <v>0.09025</v>
       </c>
       <c r="T336" s="1" t="n">
+        <v>0.09023</v>
+      </c>
+      <c r="U336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="U336" s="1" t="n">
-        <v>0.09025</v>
+      <c r="V336" s="1" t="n">
+        <v>0.09023</v>
       </c>
     </row>
     <row r="337">
@@ -23055,9 +24066,12 @@
         <v>0.18058</v>
       </c>
       <c r="T337" s="1" t="n">
+        <v>0.18091</v>
+      </c>
+      <c r="U337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="U337" s="1" t="n">
+      <c r="V337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -23122,9 +24136,12 @@
         <v>0.02075</v>
       </c>
       <c r="T338" s="1" t="n">
+        <v>0.02084</v>
+      </c>
+      <c r="U338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="U338" s="1" t="n">
+      <c r="V338" s="1" t="n">
         <v>0.02074</v>
       </c>
     </row>
@@ -23192,6 +24209,9 @@
         <v>0.1319</v>
       </c>
       <c r="U339" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="V339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -23256,9 +24276,12 @@
         <v>0.007963</v>
       </c>
       <c r="T340" s="1" t="n">
+        <v>0.007971000000000001</v>
+      </c>
+      <c r="U340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="U340" s="1" t="n">
+      <c r="V340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -23323,9 +24346,12 @@
         <v>4.394</v>
       </c>
       <c r="T341" s="1" t="n">
+        <v>4.416</v>
+      </c>
+      <c r="U341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="U341" s="1" t="n">
+      <c r="V341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -23390,9 +24416,12 @@
         <v>0.18979</v>
       </c>
       <c r="T342" s="1" t="n">
+        <v>0.19001</v>
+      </c>
+      <c r="U342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="U342" s="1" t="n">
+      <c r="V342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -23457,9 +24486,12 @@
         <v>0.08316</v>
       </c>
       <c r="T343" s="1" t="n">
+        <v>0.08318</v>
+      </c>
+      <c r="U343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="U343" s="1" t="n">
+      <c r="V343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -23524,9 +24556,12 @@
         <v>0.1818</v>
       </c>
       <c r="T344" s="1" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="U344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="U344" s="1" t="n">
+      <c r="V344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -23591,9 +24626,12 @@
         <v>0.003223</v>
       </c>
       <c r="T345" s="1" t="n">
+        <v>0.003231</v>
+      </c>
+      <c r="U345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="U345" s="1" t="n">
+      <c r="V345" s="1" t="n">
         <v>0.003222</v>
       </c>
     </row>
@@ -23658,9 +24696,12 @@
         <v>0.09107</v>
       </c>
       <c r="T346" s="1" t="n">
+        <v>0.09137000000000001</v>
+      </c>
+      <c r="U346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="U346" s="1" t="n">
+      <c r="V346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -23725,9 +24766,12 @@
         <v>2.236</v>
       </c>
       <c r="T347" s="1" t="n">
+        <v>2.243</v>
+      </c>
+      <c r="U347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="U347" s="1" t="n">
+      <c r="V347" s="1" t="n">
         <v>2.235</v>
       </c>
     </row>
@@ -23792,9 +24836,12 @@
         <v>0.3036</v>
       </c>
       <c r="T348" s="1" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="U348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="U348" s="1" t="n">
+      <c r="V348" s="1" t="n">
         <v>0.3027</v>
       </c>
     </row>
@@ -23859,9 +24906,12 @@
         <v>0.0296</v>
       </c>
       <c r="T349" s="1" t="n">
+        <v>0.02987</v>
+      </c>
+      <c r="U349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="U349" s="1" t="n">
+      <c r="V349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -23926,9 +24976,12 @@
         <v>0.1277</v>
       </c>
       <c r="T350" s="1" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="U350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="U350" s="1" t="n">
+      <c r="V350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -23993,10 +25046,13 @@
         <v>0.06607</v>
       </c>
       <c r="T351" s="1" t="n">
+        <v>0.06591</v>
+      </c>
+      <c r="U351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="U351" s="1" t="n">
-        <v>0.06607</v>
+      <c r="V351" s="1" t="n">
+        <v>0.06591</v>
       </c>
     </row>
     <row r="352">
@@ -24060,10 +25116,13 @@
         <v>0.06225</v>
       </c>
       <c r="T352" s="1" t="n">
+        <v>0.06224</v>
+      </c>
+      <c r="U352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="U352" s="1" t="n">
-        <v>0.06225</v>
+      <c r="V352" s="1" t="n">
+        <v>0.06224</v>
       </c>
     </row>
     <row r="353">
@@ -24127,9 +25186,12 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="T353" s="1" t="n">
+        <v>0.06288000000000001</v>
+      </c>
+      <c r="U353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="U353" s="1" t="n">
+      <c r="V353" s="1" t="n">
         <v>0.06270000000000001</v>
       </c>
     </row>
@@ -24194,9 +25256,12 @@
         <v>0.10502</v>
       </c>
       <c r="T354" s="1" t="n">
+        <v>0.10498</v>
+      </c>
+      <c r="U354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="U354" s="1" t="n">
+      <c r="V354" s="1" t="n">
         <v>0.10393</v>
       </c>
     </row>
@@ -24261,9 +25326,12 @@
         <v>0.0898</v>
       </c>
       <c r="T355" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="U355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="U355" s="1" t="n">
+      <c r="V355" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -24328,9 +25396,12 @@
         <v>0.06905</v>
       </c>
       <c r="T356" s="1" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="U356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="U356" s="1" t="n">
+      <c r="V356" s="1" t="n">
         <v>0.06905</v>
       </c>
     </row>
@@ -24395,9 +25466,12 @@
         <v>0.4504</v>
       </c>
       <c r="T357" s="1" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="U357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="U357" s="1" t="n">
+      <c r="V357" s="1" t="n">
         <v>0.4504</v>
       </c>
     </row>
@@ -24462,9 +25536,12 @@
         <v>0.03441</v>
       </c>
       <c r="T358" s="1" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="U358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="U358" s="1" t="n">
+      <c r="V358" s="1" t="n">
         <v>0.03441</v>
       </c>
     </row>
@@ -24529,9 +25606,12 @@
         <v>0.01454</v>
       </c>
       <c r="T359" s="1" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="U359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="U359" s="1" t="n">
+      <c r="V359" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -24596,9 +25676,12 @@
         <v>0.13328</v>
       </c>
       <c r="T360" s="1" t="n">
+        <v>0.13341</v>
+      </c>
+      <c r="U360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="U360" s="1" t="n">
+      <c r="V360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -24663,9 +25746,12 @@
         <v>0.0005855</v>
       </c>
       <c r="T361" s="1" t="n">
+        <v>0.0005862</v>
+      </c>
+      <c r="U361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="U361" s="1" t="n">
+      <c r="V361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -24730,9 +25816,12 @@
         <v>0.03824</v>
       </c>
       <c r="T362" s="1" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="U362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="U362" s="1" t="n">
+      <c r="V362" s="1" t="n">
         <v>0.03824</v>
       </c>
     </row>
@@ -24797,9 +25886,12 @@
         <v>3.22</v>
       </c>
       <c r="T363" s="1" t="n">
+        <v>3.229</v>
+      </c>
+      <c r="U363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="U363" s="1" t="n">
+      <c r="V363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -24864,9 +25956,12 @@
         <v>0.1634</v>
       </c>
       <c r="T364" s="1" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="U364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="U364" s="1" t="n">
+      <c r="V364" s="1" t="n">
         <v>0.1632</v>
       </c>
     </row>
@@ -24931,9 +26026,12 @@
         <v>0.1129</v>
       </c>
       <c r="T365" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="U365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="U365" s="1" t="n">
+      <c r="V365" s="1" t="n">
         <v>0.1128</v>
       </c>
     </row>
@@ -24998,9 +26096,12 @@
         <v>0.000634</v>
       </c>
       <c r="T366" s="1" t="n">
+        <v>0.0006361</v>
+      </c>
+      <c r="U366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="U366" s="1" t="n">
+      <c r="V366" s="1" t="n">
         <v>0.000634</v>
       </c>
     </row>
@@ -25065,9 +26166,12 @@
         <v>0.05941</v>
       </c>
       <c r="T367" s="1" t="n">
+        <v>0.05982</v>
+      </c>
+      <c r="U367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="U367" s="1" t="n">
+      <c r="V367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -25132,10 +26236,13 @@
         <v>0.08122</v>
       </c>
       <c r="T368" s="1" t="n">
+        <v>0.08111</v>
+      </c>
+      <c r="U368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="U368" s="1" t="n">
-        <v>0.08122</v>
+      <c r="V368" s="1" t="n">
+        <v>0.08111</v>
       </c>
     </row>
     <row r="369">
@@ -25199,9 +26306,12 @@
         <v>0.03927</v>
       </c>
       <c r="T369" s="1" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="U369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="U369" s="1" t="n">
+      <c r="V369" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -25266,9 +26376,12 @@
         <v>3.686</v>
       </c>
       <c r="T370" s="1" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="U370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="U370" s="1" t="n">
+      <c r="V370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -25333,9 +26446,12 @@
         <v>0.1206</v>
       </c>
       <c r="T371" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="U371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="U371" s="1" t="n">
+      <c r="V371" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -25400,9 +26516,12 @@
         <v>0.01467</v>
       </c>
       <c r="T372" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="U372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="U372" s="1" t="n">
+      <c r="V372" s="1" t="n">
         <v>0.01467</v>
       </c>
     </row>
@@ -25467,9 +26586,12 @@
         <v>0.02198</v>
       </c>
       <c r="T373" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="U373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="U373" s="1" t="n">
+      <c r="V373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -25534,9 +26656,12 @@
         <v>1.8671</v>
       </c>
       <c r="T374" s="1" t="n">
-        <v>1.8671</v>
+        <v>1.8723</v>
       </c>
       <c r="U374" s="1" t="n">
+        <v>1.8723</v>
+      </c>
+      <c r="V374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -25601,9 +26726,12 @@
         <v>0.02083</v>
       </c>
       <c r="T375" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="U375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="U375" s="1" t="n">
+      <c r="V375" s="1" t="n">
         <v>0.02081</v>
       </c>
     </row>
@@ -25668,9 +26796,12 @@
         <v>1.301</v>
       </c>
       <c r="T376" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="U376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="U376" s="1" t="n">
+      <c r="V376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -25735,9 +26866,12 @@
         <v>0.2824</v>
       </c>
       <c r="T377" s="1" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="U377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="U377" s="1" t="n">
+      <c r="V377" s="1" t="n">
         <v>0.2819</v>
       </c>
     </row>
@@ -25802,9 +26936,12 @@
         <v>0.01553</v>
       </c>
       <c r="T378" s="1" t="n">
+        <v>0.01558</v>
+      </c>
+      <c r="U378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="U378" s="1" t="n">
+      <c r="V378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -25869,9 +27006,12 @@
         <v>1.5292</v>
       </c>
       <c r="T379" s="1" t="n">
+        <v>1.5302</v>
+      </c>
+      <c r="U379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="U379" s="1" t="n">
+      <c r="V379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -25936,9 +27076,12 @@
         <v>6.873e-05</v>
       </c>
       <c r="T380" s="1" t="n">
+        <v>6.886e-05</v>
+      </c>
+      <c r="U380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="U380" s="1" t="n">
+      <c r="V380" s="1" t="n">
         <v>6.871e-05</v>
       </c>
     </row>
@@ -26003,9 +27146,12 @@
         <v>2.539</v>
       </c>
       <c r="T381" s="1" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="U381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="U381" s="1" t="n">
+      <c r="V381" s="1" t="n">
         <v>2.536</v>
       </c>
     </row>
@@ -26070,9 +27216,12 @@
         <v>0.06646000000000001</v>
       </c>
       <c r="T382" s="1" t="n">
+        <v>0.06655999999999999</v>
+      </c>
+      <c r="U382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="U382" s="1" t="n">
+      <c r="V382" s="1" t="n">
         <v>0.06646000000000001</v>
       </c>
     </row>
@@ -26137,9 +27286,12 @@
         <v>0.01662</v>
       </c>
       <c r="T383" s="1" t="n">
+        <v>0.01664</v>
+      </c>
+      <c r="U383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="U383" s="1" t="n">
+      <c r="V383" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -26204,9 +27356,12 @@
         <v>0.05152</v>
       </c>
       <c r="T384" s="1" t="n">
+        <v>0.05171</v>
+      </c>
+      <c r="U384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="U384" s="1" t="n">
+      <c r="V384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -26271,9 +27426,12 @@
         <v>7.568</v>
       </c>
       <c r="T385" s="1" t="n">
-        <v>7.591</v>
+        <v>7.597</v>
       </c>
       <c r="U385" s="1" t="n">
+        <v>7.597</v>
+      </c>
+      <c r="V385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -26338,9 +27496,12 @@
         <v>0.00327</v>
       </c>
       <c r="T386" s="1" t="n">
+        <v>0.003267</v>
+      </c>
+      <c r="U386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="U386" s="1" t="n">
+      <c r="V386" s="1" t="n">
         <v>0.003258</v>
       </c>
     </row>
@@ -26405,9 +27566,12 @@
         <v>0.0003793</v>
       </c>
       <c r="T387" s="1" t="n">
+        <v>0.0003796</v>
+      </c>
+      <c r="U387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="U387" s="1" t="n">
+      <c r="V387" s="1" t="n">
         <v>0.0003793</v>
       </c>
     </row>
@@ -26472,9 +27636,12 @@
         <v>0.009520000000000001</v>
       </c>
       <c r="T388" s="1" t="n">
+        <v>0.009560000000000001</v>
+      </c>
+      <c r="U388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="U388" s="1" t="n">
+      <c r="V388" s="1" t="n">
         <v>0.00942</v>
       </c>
     </row>
@@ -26539,9 +27706,12 @@
         <v>0.289</v>
       </c>
       <c r="T389" s="1" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="U389" s="1" t="n">
         <v>0.2904</v>
       </c>
-      <c r="U389" s="1" t="n">
+      <c r="V389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -26606,9 +27776,12 @@
         <v>0.0251</v>
       </c>
       <c r="T390" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="U390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="U390" s="1" t="n">
+      <c r="V390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -26673,9 +27846,12 @@
         <v>2.844</v>
       </c>
       <c r="T391" s="1" t="n">
+        <v>2.836</v>
+      </c>
+      <c r="U391" s="1" t="n">
         <v>2.859</v>
       </c>
-      <c r="U391" s="1" t="n">
+      <c r="V391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -26740,9 +27916,12 @@
         <v>0.01348</v>
       </c>
       <c r="T392" s="1" t="n">
+        <v>0.01346</v>
+      </c>
+      <c r="U392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="U392" s="1" t="n">
+      <c r="V392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -26807,9 +27986,12 @@
         <v>0.00236</v>
       </c>
       <c r="T393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="U393" s="1" t="n">
         <v>0.00237</v>
       </c>
-      <c r="U393" s="1" t="n">
+      <c r="V393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -26874,9 +28056,12 @@
         <v>0.05928</v>
       </c>
       <c r="T394" s="1" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="U394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="U394" s="1" t="n">
+      <c r="V394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -26941,10 +28126,13 @@
         <v>0.0402</v>
       </c>
       <c r="T395" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="U395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="U395" s="1" t="n">
-        <v>0.0402</v>
+      <c r="V395" s="1" t="n">
+        <v>0.0401</v>
       </c>
     </row>
     <row r="396">
@@ -27008,9 +28196,12 @@
         <v>0.09291000000000001</v>
       </c>
       <c r="T396" s="1" t="n">
-        <v>0.09291000000000001</v>
+        <v>0.09447</v>
       </c>
       <c r="U396" s="1" t="n">
+        <v>0.09447</v>
+      </c>
+      <c r="V396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -27075,9 +28266,12 @@
         <v>0.1512</v>
       </c>
       <c r="T397" s="1" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="U397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="U397" s="1" t="n">
+      <c r="V397" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -27145,6 +28339,9 @@
         <v>0.931</v>
       </c>
       <c r="U398" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="V398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -27209,9 +28406,12 @@
         <v>0.05218</v>
       </c>
       <c r="T399" s="1" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="U399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="U399" s="1" t="n">
+      <c r="V399" s="1" t="n">
         <v>0.05213</v>
       </c>
     </row>
@@ -27276,9 +28476,12 @@
         <v>2.504</v>
       </c>
       <c r="T400" s="1" t="n">
+        <v>2.506</v>
+      </c>
+      <c r="U400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="U400" s="1" t="n">
+      <c r="V400" s="1" t="n">
         <v>2.504</v>
       </c>
     </row>
@@ -27343,9 +28546,12 @@
         <v>0.01769</v>
       </c>
       <c r="T401" s="1" t="n">
+        <v>0.01773</v>
+      </c>
+      <c r="U401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="U401" s="1" t="n">
+      <c r="V401" s="1" t="n">
         <v>0.01769</v>
       </c>
     </row>
@@ -27410,9 +28616,12 @@
         <v>0.08</v>
       </c>
       <c r="T402" s="1" t="n">
+        <v>0.07997</v>
+      </c>
+      <c r="U402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="U402" s="1" t="n">
+      <c r="V402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -27477,9 +28686,12 @@
         <v>1.2468</v>
       </c>
       <c r="T403" s="1" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="U403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="U403" s="1" t="n">
+      <c r="V403" s="1" t="n">
         <v>1.2451</v>
       </c>
     </row>
@@ -27544,9 +28756,12 @@
         <v>0.00708</v>
       </c>
       <c r="T404" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="U404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="U404" s="1" t="n">
+      <c r="V404" s="1" t="n">
         <v>0.00708</v>
       </c>
     </row>
@@ -27611,9 +28826,12 @@
         <v>0.5049</v>
       </c>
       <c r="T405" s="1" t="n">
-        <v>0.5049</v>
+        <v>0.5065</v>
       </c>
       <c r="U405" s="1" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="V405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -27678,9 +28896,12 @@
         <v>0.01142</v>
       </c>
       <c r="T406" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="U406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="U406" s="1" t="n">
+      <c r="V406" s="1" t="n">
         <v>0.01142</v>
       </c>
     </row>
@@ -27745,9 +28966,12 @@
         <v>0.04583</v>
       </c>
       <c r="T407" s="1" t="n">
+        <v>0.04593</v>
+      </c>
+      <c r="U407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="U407" s="1" t="n">
+      <c r="V407" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -27812,9 +29036,12 @@
         <v>0.03922</v>
       </c>
       <c r="T408" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="U408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="U408" s="1" t="n">
+      <c r="V408" s="1" t="n">
         <v>0.03922</v>
       </c>
     </row>
@@ -27879,9 +29106,12 @@
         <v>0.05209</v>
       </c>
       <c r="T409" s="1" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="U409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="U409" s="1" t="n">
+      <c r="V409" s="1" t="n">
         <v>0.05209</v>
       </c>
     </row>
@@ -27946,10 +29176,13 @@
         <v>0.01222</v>
       </c>
       <c r="T410" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="U410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="U410" s="1" t="n">
-        <v>0.01222</v>
+      <c r="V410" s="1" t="n">
+        <v>0.01216</v>
       </c>
     </row>
     <row r="411">
@@ -28013,9 +29246,12 @@
         <v>0.06333</v>
       </c>
       <c r="T411" s="1" t="n">
+        <v>0.06349</v>
+      </c>
+      <c r="U411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="U411" s="1" t="n">
+      <c r="V411" s="1" t="n">
         <v>0.06333</v>
       </c>
     </row>
@@ -28080,9 +29316,12 @@
         <v>0.04123</v>
       </c>
       <c r="T412" s="1" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="U412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="U412" s="1" t="n">
+      <c r="V412" s="1" t="n">
         <v>0.04114</v>
       </c>
     </row>
@@ -28147,9 +29386,12 @@
         <v>1.111</v>
       </c>
       <c r="T413" s="1" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="U413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="U413" s="1" t="n">
+      <c r="V413" s="1" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -28214,9 +29456,12 @@
         <v>0.262</v>
       </c>
       <c r="T414" s="1" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="U414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="U414" s="1" t="n">
+      <c r="V414" s="1" t="n">
         <v>0.2614</v>
       </c>
     </row>
@@ -28281,9 +29526,12 @@
         <v>0.001221</v>
       </c>
       <c r="T415" s="1" t="n">
+        <v>0.001221</v>
+      </c>
+      <c r="U415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="U415" s="1" t="n">
+      <c r="V415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -28348,9 +29596,12 @@
         <v>0.03194</v>
       </c>
       <c r="T416" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="U416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="U416" s="1" t="n">
+      <c r="V416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -28415,9 +29666,12 @@
         <v>0.01451</v>
       </c>
       <c r="T417" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="U417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="U417" s="1" t="n">
+      <c r="V417" s="1" t="n">
         <v>0.01451</v>
       </c>
     </row>
@@ -28482,9 +29736,12 @@
         <v>0.148</v>
       </c>
       <c r="T418" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="U418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="U418" s="1" t="n">
+      <c r="V418" s="1" t="n">
         <v>0.1478</v>
       </c>
     </row>
@@ -28549,9 +29806,12 @@
         <v>0.04872</v>
       </c>
       <c r="T419" s="1" t="n">
+        <v>0.04888</v>
+      </c>
+      <c r="U419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="U419" s="1" t="n">
+      <c r="V419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -28616,9 +29876,12 @@
         <v>66.43000000000001</v>
       </c>
       <c r="T420" s="1" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="U420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="U420" s="1" t="n">
+      <c r="V420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -28683,9 +29946,12 @@
         <v>0.876</v>
       </c>
       <c r="T421" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="U421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="U421" s="1" t="n">
+      <c r="V421" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -28750,9 +30016,12 @@
         <v>0.012461</v>
       </c>
       <c r="T422" s="1" t="n">
+        <v>0.012429</v>
+      </c>
+      <c r="U422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="U422" s="1" t="n">
+      <c r="V422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -28817,9 +30086,12 @@
         <v>0.01593</v>
       </c>
       <c r="T423" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="U423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="U423" s="1" t="n">
+      <c r="V423" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -28884,9 +30156,12 @@
         <v>0.27114</v>
       </c>
       <c r="T424" s="1" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="U424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="U424" s="1" t="n">
+      <c r="V424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -28951,9 +30226,12 @@
         <v>0.5984</v>
       </c>
       <c r="T425" s="1" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="U425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="U425" s="1" t="n">
+      <c r="V425" s="1" t="n">
         <v>0.5984</v>
       </c>
     </row>
@@ -29018,9 +30296,12 @@
         <v>0.0055</v>
       </c>
       <c r="T426" s="1" t="n">
+        <v>0.005494</v>
+      </c>
+      <c r="U426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="U426" s="1" t="n">
+      <c r="V426" s="1" t="n">
         <v>0.005493</v>
       </c>
     </row>
@@ -29085,9 +30366,12 @@
         <v>0.04976</v>
       </c>
       <c r="T427" s="1" t="n">
-        <v>0.04978</v>
+        <v>0.04986</v>
       </c>
       <c r="U427" s="1" t="n">
+        <v>0.04986</v>
+      </c>
+      <c r="V427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -29152,9 +30436,12 @@
         <v>0.1251</v>
       </c>
       <c r="T428" s="1" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="U428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="U428" s="1" t="n">
+      <c r="V428" s="1" t="n">
         <v>0.1249</v>
       </c>
     </row>
@@ -29219,9 +30506,12 @@
         <v>0.003185</v>
       </c>
       <c r="T429" s="1" t="n">
+        <v>0.003186</v>
+      </c>
+      <c r="U429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="U429" s="1" t="n">
+      <c r="V429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -29286,10 +30576,13 @@
         <v>0.03629</v>
       </c>
       <c r="T430" s="1" t="n">
+        <v>0.03626</v>
+      </c>
+      <c r="U430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="U430" s="1" t="n">
-        <v>0.03629</v>
+      <c r="V430" s="1" t="n">
+        <v>0.03626</v>
       </c>
     </row>
     <row r="431">
@@ -29353,9 +30646,12 @@
         <v>0.3914</v>
       </c>
       <c r="T431" s="1" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="U431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="U431" s="1" t="n">
+      <c r="V431" s="1" t="n">
         <v>0.3914</v>
       </c>
     </row>
@@ -29420,9 +30716,12 @@
         <v>0.004446</v>
       </c>
       <c r="T432" s="1" t="n">
+        <v>0.004468</v>
+      </c>
+      <c r="U432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="U432" s="1" t="n">
+      <c r="V432" s="1" t="n">
         <v>0.004446</v>
       </c>
     </row>
@@ -29487,9 +30786,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="T433" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="U433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="U433" s="1" t="n">
+      <c r="V433" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -29554,9 +30856,12 @@
         <v>0.01235</v>
       </c>
       <c r="T434" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="U434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="U434" s="1" t="n">
+      <c r="V434" s="1" t="n">
         <v>0.01234</v>
       </c>
     </row>
@@ -29621,9 +30926,12 @@
         <v>1.984</v>
       </c>
       <c r="T435" s="1" t="n">
-        <v>1.988</v>
+        <v>2.004</v>
       </c>
       <c r="U435" s="1" t="n">
+        <v>2.004</v>
+      </c>
+      <c r="V435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -29688,10 +30996,13 @@
         <v>0.001772</v>
       </c>
       <c r="T436" s="1" t="n">
+        <v>0.001771</v>
+      </c>
+      <c r="U436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="U436" s="1" t="n">
-        <v>0.001772</v>
+      <c r="V436" s="1" t="n">
+        <v>0.001771</v>
       </c>
     </row>
     <row r="437">
@@ -29755,9 +31066,12 @@
         <v>0.4422</v>
       </c>
       <c r="T437" s="1" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="U437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="U437" s="1" t="n">
+      <c r="V437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -29822,9 +31136,12 @@
         <v>0.00533</v>
       </c>
       <c r="T438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="U438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="U438" s="1" t="n">
+      <c r="V438" s="1" t="n">
         <v>0.00533</v>
       </c>
     </row>
@@ -29889,9 +31206,12 @@
         <v>0.1032</v>
       </c>
       <c r="T439" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="U439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="U439" s="1" t="n">
+      <c r="V439" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -29956,9 +31276,12 @@
         <v>0.03361</v>
       </c>
       <c r="T440" s="1" t="n">
+        <v>0.03363</v>
+      </c>
+      <c r="U440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="U440" s="1" t="n">
+      <c r="V440" s="1" t="n">
         <v>0.03361</v>
       </c>
     </row>
@@ -30023,9 +31346,12 @@
         <v>0.08179</v>
       </c>
       <c r="T441" s="1" t="n">
+        <v>0.08196000000000001</v>
+      </c>
+      <c r="U441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="U441" s="1" t="n">
+      <c r="V441" s="1" t="n">
         <v>0.08179</v>
       </c>
     </row>
@@ -30090,10 +31416,13 @@
         <v>1.301</v>
       </c>
       <c r="T442" s="1" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="U442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="U442" s="1" t="n">
-        <v>1.301</v>
+      <c r="V442" s="1" t="n">
+        <v>1.299</v>
       </c>
     </row>
     <row r="443">
@@ -30157,9 +31486,12 @@
         <v>0.07491</v>
       </c>
       <c r="T443" s="1" t="n">
+        <v>0.07519000000000001</v>
+      </c>
+      <c r="U443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="U443" s="1" t="n">
+      <c r="V443" s="1" t="n">
         <v>0.07491</v>
       </c>
     </row>
@@ -30224,9 +31556,12 @@
         <v>0.07616000000000001</v>
       </c>
       <c r="T444" s="1" t="n">
+        <v>0.07633</v>
+      </c>
+      <c r="U444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="U444" s="1" t="n">
+      <c r="V444" s="1" t="n">
         <v>0.07616000000000001</v>
       </c>
     </row>
@@ -30291,10 +31626,13 @@
         <v>0.04302</v>
       </c>
       <c r="T445" s="1" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="U445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="U445" s="1" t="n">
-        <v>0.04302</v>
+      <c r="V445" s="1" t="n">
+        <v>0.04298</v>
       </c>
     </row>
     <row r="446">
@@ -30358,9 +31696,12 @@
         <v>0.02142</v>
       </c>
       <c r="T446" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="U446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="U446" s="1" t="n">
+      <c r="V446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -30425,10 +31766,13 @@
         <v>0.2791</v>
       </c>
       <c r="T447" s="1" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="U447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="U447" s="1" t="n">
-        <v>0.2791</v>
+      <c r="V447" s="1" t="n">
+        <v>0.2781</v>
       </c>
     </row>
     <row r="448">
@@ -30492,10 +31836,13 @@
         <v>0.0307</v>
       </c>
       <c r="T448" s="1" t="n">
+        <v>0.03065</v>
+      </c>
+      <c r="U448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="U448" s="1" t="n">
-        <v>0.03069</v>
+      <c r="V448" s="1" t="n">
+        <v>0.03065</v>
       </c>
     </row>
     <row r="449">
@@ -30559,9 +31906,12 @@
         <v>0.00642</v>
       </c>
       <c r="T449" s="1" t="n">
+        <v>0.00646</v>
+      </c>
+      <c r="U449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="U449" s="1" t="n">
+      <c r="V449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -30626,9 +31976,12 @@
         <v>0.023</v>
       </c>
       <c r="T450" s="1" t="n">
+        <v>0.022993</v>
+      </c>
+      <c r="U450" s="1" t="n">
         <v>0.02312</v>
       </c>
-      <c r="U450" s="1" t="n">
+      <c r="V450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -30693,9 +32046,12 @@
         <v>0.04225</v>
       </c>
       <c r="T451" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="U451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="U451" s="1" t="n">
+      <c r="V451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -30760,9 +32116,12 @@
         <v>0.07204000000000001</v>
       </c>
       <c r="T452" s="1" t="n">
+        <v>0.07224999999999999</v>
+      </c>
+      <c r="U452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="U452" s="1" t="n">
+      <c r="V452" s="1" t="n">
         <v>0.07204000000000001</v>
       </c>
     </row>
@@ -30827,9 +32186,12 @@
         <v>0.0005911</v>
       </c>
       <c r="T453" s="1" t="n">
+        <v>0.0005921</v>
+      </c>
+      <c r="U453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="U453" s="1" t="n">
+      <c r="V453" s="1" t="n">
         <v>0.0005904</v>
       </c>
     </row>
@@ -30894,9 +32256,12 @@
         <v>0.304</v>
       </c>
       <c r="T454" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="U454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="U454" s="1" t="n">
+      <c r="V454" s="1" t="n">
         <v>0.304</v>
       </c>
     </row>
@@ -30961,9 +32326,12 @@
         <v>0.00432</v>
       </c>
       <c r="T455" s="1" t="n">
+        <v>0.00429</v>
+      </c>
+      <c r="U455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="U455" s="1" t="n">
+      <c r="V455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -31028,9 +32396,12 @@
         <v>0.1817</v>
       </c>
       <c r="T456" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="U456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="U456" s="1" t="n">
+      <c r="V456" s="1" t="n">
         <v>0.1817</v>
       </c>
     </row>
@@ -31095,9 +32466,12 @@
         <v>0.04256</v>
       </c>
       <c r="T457" s="1" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="U457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="U457" s="1" t="n">
+      <c r="V457" s="1" t="n">
         <v>0.04254</v>
       </c>
     </row>
@@ -31162,9 +32536,12 @@
         <v>0.1452</v>
       </c>
       <c r="T458" s="1" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="U458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="U458" s="1" t="n">
+      <c r="V458" s="1" t="n">
         <v>0.1452</v>
       </c>
     </row>
@@ -31229,9 +32606,12 @@
         <v>0.008577</v>
       </c>
       <c r="T459" s="1" t="n">
+        <v>0.008588</v>
+      </c>
+      <c r="U459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="U459" s="1" t="n">
+      <c r="V459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -31296,9 +32676,12 @@
         <v>0.007364</v>
       </c>
       <c r="T460" s="1" t="n">
+        <v>0.007438</v>
+      </c>
+      <c r="U460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="U460" s="1" t="n">
+      <c r="V460" s="1" t="n">
         <v>0.007353</v>
       </c>
     </row>
@@ -31363,9 +32746,12 @@
         <v>0.0001731</v>
       </c>
       <c r="T461" s="1" t="n">
-        <v>0.0001736</v>
+        <v>0.0001749</v>
       </c>
       <c r="U461" s="1" t="n">
+        <v>0.0001749</v>
+      </c>
+      <c r="V461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -31430,9 +32816,12 @@
         <v>0.02546</v>
       </c>
       <c r="T462" s="1" t="n">
+        <v>0.02425</v>
+      </c>
+      <c r="U462" s="1" t="n">
         <v>0.02585</v>
       </c>
-      <c r="U462" s="1" t="n">
+      <c r="V462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -31497,10 +32886,13 @@
         <v>0.03656</v>
       </c>
       <c r="T463" s="1" t="n">
+        <v>0.03652</v>
+      </c>
+      <c r="U463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="U463" s="1" t="n">
-        <v>0.03656</v>
+      <c r="V463" s="1" t="n">
+        <v>0.03652</v>
       </c>
     </row>
     <row r="464">
@@ -31564,9 +32956,12 @@
         <v>0.3005</v>
       </c>
       <c r="T464" s="1" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="U464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="U464" s="1" t="n">
+      <c r="V464" s="1" t="n">
         <v>0.3003</v>
       </c>
     </row>
@@ -31631,9 +33026,12 @@
         <v>0.03889</v>
       </c>
       <c r="T465" s="1" t="n">
+        <v>0.03889</v>
+      </c>
+      <c r="U465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="U465" s="1" t="n">
+      <c r="V465" s="1" t="n">
         <v>0.03889</v>
       </c>
     </row>
@@ -31698,9 +33096,12 @@
         <v>2.66</v>
       </c>
       <c r="T466" s="1" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="U466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="U466" s="1" t="n">
+      <c r="V466" s="1" t="n">
         <v>2.66</v>
       </c>
     </row>
@@ -31765,9 +33166,12 @@
         <v>0.03429</v>
       </c>
       <c r="T467" s="1" t="n">
+        <v>0.03434</v>
+      </c>
+      <c r="U467" s="1" t="n">
         <v>0.03438</v>
       </c>
-      <c r="U467" s="1" t="n">
+      <c r="V467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -31832,9 +33236,12 @@
         <v>0.1761</v>
       </c>
       <c r="T468" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="U468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="U468" s="1" t="n">
+      <c r="V468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -31899,9 +33306,12 @@
         <v>0.0959</v>
       </c>
       <c r="T469" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="U469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="U469" s="1" t="n">
+      <c r="V469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -31966,9 +33376,12 @@
         <v>0.06771000000000001</v>
       </c>
       <c r="T470" s="1" t="n">
-        <v>0.06771000000000001</v>
+        <v>0.06815</v>
       </c>
       <c r="U470" s="1" t="n">
+        <v>0.06815</v>
+      </c>
+      <c r="V470" s="1" t="n">
         <v>0.06696000000000001</v>
       </c>
     </row>
@@ -32033,9 +33446,12 @@
         <v>0.03969</v>
       </c>
       <c r="T471" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="U471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="U471" s="1" t="n">
+      <c r="V471" s="1" t="n">
         <v>0.03969</v>
       </c>
     </row>
@@ -32100,9 +33516,12 @@
         <v>0.2457</v>
       </c>
       <c r="T472" s="1" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="U472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="U472" s="1" t="n">
+      <c r="V472" s="1" t="n">
         <v>0.2457</v>
       </c>
     </row>
@@ -32167,9 +33586,12 @@
         <v>0.016238</v>
       </c>
       <c r="T473" s="1" t="n">
+        <v>0.016239</v>
+      </c>
+      <c r="U473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="U473" s="1" t="n">
+      <c r="V473" s="1" t="n">
         <v>0.016238</v>
       </c>
     </row>
@@ -32234,9 +33656,12 @@
         <v>0.1146</v>
       </c>
       <c r="T474" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="U474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="U474" s="1" t="n">
+      <c r="V474" s="1" t="n">
         <v>0.1146</v>
       </c>
     </row>
@@ -32301,9 +33726,12 @@
         <v>0.04265</v>
       </c>
       <c r="T475" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="U475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="U475" s="1" t="n">
+      <c r="V475" s="1" t="n">
         <v>0.04258</v>
       </c>
     </row>
@@ -32368,9 +33796,12 @@
         <v>0.2062</v>
       </c>
       <c r="T476" s="1" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="U476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="U476" s="1" t="n">
+      <c r="V476" s="1" t="n">
         <v>0.2062</v>
       </c>
     </row>
@@ -32435,9 +33866,12 @@
         <v>0.006781</v>
       </c>
       <c r="T477" s="1" t="n">
+        <v>0.006817</v>
+      </c>
+      <c r="U477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="U477" s="1" t="n">
+      <c r="V477" s="1" t="n">
         <v>0.006763</v>
       </c>
     </row>
@@ -32502,9 +33936,12 @@
         <v>0.01776</v>
       </c>
       <c r="T478" s="1" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="U478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="U478" s="1" t="n">
+      <c r="V478" s="1" t="n">
         <v>0.01776</v>
       </c>
     </row>
@@ -32569,9 +34006,12 @@
         <v>0.04647</v>
       </c>
       <c r="T479" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="U479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="U479" s="1" t="n">
+      <c r="V479" s="1" t="n">
         <v>0.04647</v>
       </c>
     </row>
@@ -32636,9 +34076,12 @@
         <v>0.25967</v>
       </c>
       <c r="T480" s="1" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="U480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="U480" s="1" t="n">
+      <c r="V480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -32703,10 +34146,13 @@
         <v>0.01209</v>
       </c>
       <c r="T481" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="U481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="U481" s="1" t="n">
-        <v>0.01209</v>
+      <c r="V481" s="1" t="n">
+        <v>0.01207</v>
       </c>
     </row>
     <row r="482">
@@ -32770,10 +34216,13 @@
         <v>0.004066</v>
       </c>
       <c r="T482" s="1" t="n">
+        <v>0.004055</v>
+      </c>
+      <c r="U482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="U482" s="1" t="n">
-        <v>0.004061</v>
+      <c r="V482" s="1" t="n">
+        <v>0.004055</v>
       </c>
     </row>
     <row r="483">
@@ -32837,9 +34286,12 @@
         <v>0.1228</v>
       </c>
       <c r="T483" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="U483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="U483" s="1" t="n">
+      <c r="V483" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -32904,9 +34356,12 @@
         <v>0.02197</v>
       </c>
       <c r="T484" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="U484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="U484" s="1" t="n">
+      <c r="V484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -32971,9 +34426,12 @@
         <v>0.04526</v>
       </c>
       <c r="T485" s="1" t="n">
+        <v>0.04526</v>
+      </c>
+      <c r="U485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="U485" s="1" t="n">
+      <c r="V485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -33038,10 +34496,13 @@
         <v>0.1726</v>
       </c>
       <c r="T486" s="1" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="U486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="U486" s="1" t="n">
-        <v>0.1726</v>
+      <c r="V486" s="1" t="n">
+        <v>0.1724</v>
       </c>
     </row>
     <row r="487">
@@ -33105,9 +34566,12 @@
         <v>0.2741</v>
       </c>
       <c r="T487" s="1" t="n">
-        <v>0.2741</v>
+        <v>0.2767</v>
       </c>
       <c r="U487" s="1" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="V487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -33172,9 +34636,12 @@
         <v>0.04578</v>
       </c>
       <c r="T488" s="1" t="n">
+        <v>0.04594</v>
+      </c>
+      <c r="U488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="U488" s="1" t="n">
+      <c r="V488" s="1" t="n">
         <v>0.04578</v>
       </c>
     </row>
@@ -33239,9 +34706,12 @@
         <v>0.0002139</v>
       </c>
       <c r="T489" s="1" t="n">
+        <v>0.0002141</v>
+      </c>
+      <c r="U489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="U489" s="1" t="n">
+      <c r="V489" s="1" t="n">
         <v>0.0002139</v>
       </c>
     </row>
@@ -33309,6 +34779,9 @@
         <v>1.783</v>
       </c>
       <c r="U490" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="V490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -33373,9 +34846,12 @@
         <v>15.99</v>
       </c>
       <c r="T491" s="1" t="n">
+        <v>16.034</v>
+      </c>
+      <c r="U491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="U491" s="1" t="n">
+      <c r="V491" s="1" t="n">
         <v>15.99</v>
       </c>
     </row>
@@ -33440,9 +34916,12 @@
         <v>0.06637</v>
       </c>
       <c r="T492" s="1" t="n">
+        <v>0.06652</v>
+      </c>
+      <c r="U492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="U492" s="1" t="n">
+      <c r="V492" s="1" t="n">
         <v>0.06637</v>
       </c>
     </row>
@@ -33507,9 +34986,12 @@
         <v>0.06714000000000001</v>
       </c>
       <c r="T493" s="1" t="n">
+        <v>0.06739000000000001</v>
+      </c>
+      <c r="U493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="U493" s="1" t="n">
+      <c r="V493" s="1" t="n">
         <v>0.06709</v>
       </c>
     </row>
@@ -33574,9 +35056,12 @@
         <v>0.009405</v>
       </c>
       <c r="T494" s="1" t="n">
+        <v>0.009408</v>
+      </c>
+      <c r="U494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="U494" s="1" t="n">
+      <c r="V494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -33641,10 +35126,13 @@
         <v>0.005788</v>
       </c>
       <c r="T495" s="1" t="n">
+        <v>0.005774</v>
+      </c>
+      <c r="U495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="U495" s="1" t="n">
-        <v>0.005788</v>
+      <c r="V495" s="1" t="n">
+        <v>0.005774</v>
       </c>
     </row>
     <row r="496">
@@ -33708,10 +35196,13 @@
         <v>0.00984</v>
       </c>
       <c r="T496" s="1" t="n">
+        <v>0.009820000000000001</v>
+      </c>
+      <c r="U496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="U496" s="1" t="n">
-        <v>0.00984</v>
+      <c r="V496" s="1" t="n">
+        <v>0.009820000000000001</v>
       </c>
     </row>
     <row r="497">
@@ -33775,9 +35266,12 @@
         <v>0.04665</v>
       </c>
       <c r="T497" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="U497" s="1" t="n">
         <v>0.04665</v>
       </c>
-      <c r="U497" s="1" t="n">
+      <c r="V497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -33842,9 +35336,12 @@
         <v>0.006338</v>
       </c>
       <c r="T498" s="1" t="n">
+        <v>0.006353</v>
+      </c>
+      <c r="U498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="U498" s="1" t="n">
+      <c r="V498" s="1" t="n">
         <v>0.006338</v>
       </c>
     </row>
@@ -33909,9 +35406,12 @@
         <v>0.01034</v>
       </c>
       <c r="T499" s="1" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="U499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="U499" s="1" t="n">
+      <c r="V499" s="1" t="n">
         <v>0.01032</v>
       </c>
     </row>
@@ -33976,9 +35476,12 @@
         <v>0.5067</v>
       </c>
       <c r="T500" s="1" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="U500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="U500" s="1" t="n">
+      <c r="V500" s="1" t="n">
         <v>0.5067</v>
       </c>
     </row>
@@ -34043,9 +35546,12 @@
         <v>0.03211</v>
       </c>
       <c r="T501" s="1" t="n">
+        <v>0.03208</v>
+      </c>
+      <c r="U501" s="1" t="n">
         <v>0.03213</v>
       </c>
-      <c r="U501" s="1" t="n">
+      <c r="V501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -34110,10 +35616,13 @@
         <v>0.4359</v>
       </c>
       <c r="T502" s="1" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="U502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="U502" s="1" t="n">
-        <v>0.4356</v>
+      <c r="V502" s="1" t="n">
+        <v>0.4353</v>
       </c>
     </row>
     <row r="503">
@@ -34177,9 +35686,12 @@
         <v>0.999341</v>
       </c>
       <c r="T503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="U503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="U503" s="1" t="n">
+      <c r="V503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -34244,9 +35756,12 @@
         <v>0.03516</v>
       </c>
       <c r="T504" s="1" t="n">
+        <v>0.03535</v>
+      </c>
+      <c r="U504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="U504" s="1" t="n">
+      <c r="V504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -34311,9 +35826,12 @@
         <v>0.004916</v>
       </c>
       <c r="T505" s="1" t="n">
+        <v>0.004915</v>
+      </c>
+      <c r="U505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="U505" s="1" t="n">
+      <c r="V505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -34378,9 +35896,12 @@
         <v>0.0138</v>
       </c>
       <c r="T506" s="1" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="U506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="U506" s="1" t="n">
+      <c r="V506" s="1" t="n">
         <v>0.0138</v>
       </c>
     </row>
@@ -34445,9 +35966,12 @@
         <v>0.00348</v>
       </c>
       <c r="T507" s="1" t="n">
+        <v>0.003488</v>
+      </c>
+      <c r="U507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="U507" s="1" t="n">
+      <c r="V507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -34512,9 +36036,12 @@
         <v>1.411</v>
       </c>
       <c r="T508" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="U508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="U508" s="1" t="n">
+      <c r="V508" s="1" t="n">
         <v>1.411</v>
       </c>
     </row>
@@ -34579,9 +36106,12 @@
         <v>0.005059</v>
       </c>
       <c r="T509" s="1" t="n">
+        <v>0.005059</v>
+      </c>
+      <c r="U509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="U509" s="1" t="n">
+      <c r="V509" s="1" t="n">
         <v>0.005056</v>
       </c>
     </row>
@@ -34646,9 +36176,12 @@
         <v>0.0156</v>
       </c>
       <c r="T510" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="U510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="U510" s="1" t="n">
+      <c r="V510" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -34713,9 +36246,12 @@
         <v>0.08119</v>
       </c>
       <c r="T511" s="1" t="n">
+        <v>0.08175</v>
+      </c>
+      <c r="U511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="U511" s="1" t="n">
+      <c r="V511" s="1" t="n">
         <v>0.08119</v>
       </c>
     </row>
@@ -34780,9 +36316,12 @@
         <v>0.007067</v>
       </c>
       <c r="T512" s="1" t="n">
+        <v>0.00709</v>
+      </c>
+      <c r="U512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="U512" s="1" t="n">
+      <c r="V512" s="1" t="n">
         <v>0.007067</v>
       </c>
     </row>
@@ -34847,9 +36386,12 @@
         <v>0.01474</v>
       </c>
       <c r="T513" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="U513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="U513" s="1" t="n">
+      <c r="V513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -34914,10 +36456,13 @@
         <v>0.04719</v>
       </c>
       <c r="T514" s="1" t="n">
+        <v>0.04712</v>
+      </c>
+      <c r="U514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="U514" s="1" t="n">
-        <v>0.04719</v>
+      <c r="V514" s="1" t="n">
+        <v>0.04712</v>
       </c>
     </row>
     <row r="515">
@@ -34981,9 +36526,12 @@
         <v>0.01796</v>
       </c>
       <c r="T515" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="U515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="U515" s="1" t="n">
+      <c r="V515" s="1" t="n">
         <v>0.01796</v>
       </c>
     </row>
@@ -35048,9 +36596,12 @@
         <v>0.0005783</v>
       </c>
       <c r="T516" s="1" t="n">
+        <v>0.000579</v>
+      </c>
+      <c r="U516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="U516" s="1" t="n">
+      <c r="V516" s="1" t="n">
         <v>0.000578</v>
       </c>
     </row>
@@ -35115,9 +36666,12 @@
         <v>0.07817</v>
       </c>
       <c r="T517" s="1" t="n">
+        <v>0.07838000000000001</v>
+      </c>
+      <c r="U517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="U517" s="1" t="n">
+      <c r="V517" s="1" t="n">
         <v>0.07817</v>
       </c>
     </row>
@@ -35182,9 +36736,12 @@
         <v>0.00635</v>
       </c>
       <c r="T518" s="1" t="n">
+        <v>0.006363</v>
+      </c>
+      <c r="U518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="U518" s="1" t="n">
+      <c r="V518" s="1" t="n">
         <v>0.00635</v>
       </c>
     </row>
@@ -35249,9 +36806,12 @@
         <v>0.05746</v>
       </c>
       <c r="T519" s="1" t="n">
+        <v>0.05759</v>
+      </c>
+      <c r="U519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="U519" s="1" t="n">
+      <c r="V519" s="1" t="n">
         <v>0.05746</v>
       </c>
     </row>
@@ -35316,9 +36876,12 @@
         <v>0.10341</v>
       </c>
       <c r="T520" s="1" t="n">
+        <v>0.10376</v>
+      </c>
+      <c r="U520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="U520" s="1" t="n">
+      <c r="V520" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -35383,9 +36946,12 @@
         <v>0.01785</v>
       </c>
       <c r="T521" s="1" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="U521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="U521" s="1" t="n">
+      <c r="V521" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -35450,9 +37016,12 @@
         <v>0.0161</v>
       </c>
       <c r="T522" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="U522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="U522" s="1" t="n">
+      <c r="V522" s="1" t="n">
         <v>0.01602</v>
       </c>
     </row>
@@ -35517,9 +37086,12 @@
         <v>0.01077</v>
       </c>
       <c r="T523" s="1" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="U523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="U523" s="1" t="n">
+      <c r="V523" s="1" t="n">
         <v>0.01077</v>
       </c>
     </row>
@@ -35584,9 +37156,12 @@
         <v>0.007307</v>
       </c>
       <c r="T524" s="1" t="n">
-        <v>0.007318</v>
+        <v>0.007331</v>
       </c>
       <c r="U524" s="1" t="n">
+        <v>0.007331</v>
+      </c>
+      <c r="V524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -35651,10 +37226,13 @@
         <v>0.00581</v>
       </c>
       <c r="T525" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="U525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="U525" s="1" t="n">
-        <v>0.00581</v>
+      <c r="V525" s="1" t="n">
+        <v>0.005794</v>
       </c>
     </row>
     <row r="526">
@@ -35718,9 +37296,12 @@
         <v>0.001443</v>
       </c>
       <c r="T526" s="1" t="n">
+        <v>0.001441</v>
+      </c>
+      <c r="U526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="U526" s="1" t="n">
+      <c r="V526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -35785,9 +37366,12 @@
         <v>0.374</v>
       </c>
       <c r="T527" s="1" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="U527" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -35852,9 +37436,12 @@
         <v>0.005219</v>
       </c>
       <c r="T528" s="1" t="n">
+        <v>0.005239</v>
+      </c>
+      <c r="U528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="U528" s="1" t="n">
+      <c r="V528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -35919,9 +37506,12 @@
         <v>2.95</v>
       </c>
       <c r="T529" s="1" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="U529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="U529" s="1" t="n">
+      <c r="V529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -35986,9 +37576,12 @@
         <v>0.1526</v>
       </c>
       <c r="T530" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="U530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="U530" s="1" t="n">
+      <c r="V530" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -36053,9 +37646,12 @@
         <v>2570</v>
       </c>
       <c r="T531" s="1" t="n">
-        <v>2579</v>
+        <v>2584</v>
       </c>
       <c r="U531" s="1" t="n">
+        <v>2584</v>
+      </c>
+      <c r="V531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -36120,9 +37716,12 @@
         <v>0.03893</v>
       </c>
       <c r="T532" s="1" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="U532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="U532" s="1" t="n">
+      <c r="V532" s="1" t="n">
         <v>0.03893</v>
       </c>
     </row>
@@ -36190,6 +37789,9 @@
         <v>0.02191</v>
       </c>
       <c r="U533" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="V533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -36254,9 +37856,12 @@
         <v>0.07296</v>
       </c>
       <c r="T534" s="1" t="n">
+        <v>0.07307</v>
+      </c>
+      <c r="U534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="U534" s="1" t="n">
+      <c r="V534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -36321,9 +37926,12 @@
         <v>0.007844</v>
       </c>
       <c r="T535" s="1" t="n">
+        <v>0.007865</v>
+      </c>
+      <c r="U535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="U535" s="1" t="n">
+      <c r="V535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -36388,9 +37996,12 @@
         <v>0.04985</v>
       </c>
       <c r="T536" s="1" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="U536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="U536" s="1" t="n">
+      <c r="V536" s="1" t="n">
         <v>0.04985</v>
       </c>
     </row>
@@ -36455,9 +38066,12 @@
         <v>0.00398</v>
       </c>
       <c r="T537" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="U537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="U537" s="1" t="n">
+      <c r="V537" s="1" t="n">
         <v>0.00397</v>
       </c>
     </row>
@@ -36522,9 +38136,12 @@
         <v>0.08252</v>
       </c>
       <c r="T538" s="1" t="n">
+        <v>0.08261</v>
+      </c>
+      <c r="U538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="U538" s="1" t="n">
+      <c r="V538" s="1" t="n">
         <v>0.08252</v>
       </c>
     </row>
@@ -36589,10 +38206,13 @@
         <v>0.02477</v>
       </c>
       <c r="T539" s="1" t="n">
+        <v>0.02473</v>
+      </c>
+      <c r="U539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="U539" s="1" t="n">
-        <v>0.02477</v>
+      <c r="V539" s="1" t="n">
+        <v>0.02473</v>
       </c>
     </row>
     <row r="540">
@@ -36656,9 +38276,12 @@
         <v>0.08431</v>
       </c>
       <c r="T540" s="1" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="U540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="U540" s="1" t="n">
+      <c r="V540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -36723,9 +38346,12 @@
         <v>0.0188</v>
       </c>
       <c r="T541" s="1" t="n">
+        <v>0.01888</v>
+      </c>
+      <c r="U541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="U541" s="1" t="n">
+      <c r="V541" s="1" t="n">
         <v>0.0188</v>
       </c>
     </row>
@@ -36790,9 +38416,12 @@
         <v>0.01682</v>
       </c>
       <c r="T542" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="U542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="U542" s="1" t="n">
+      <c r="V542" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -36857,9 +38486,12 @@
         <v>0.1046</v>
       </c>
       <c r="T543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="U543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="U543" s="1" t="n">
+      <c r="V543" s="1" t="n">
         <v>0.1044</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W543"/>
+  <dimension ref="A1:X543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -440,8 +440,9 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,10 +553,15 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>price_05:15</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -628,9 +634,12 @@
         <v>70765.3</v>
       </c>
       <c r="V2" s="1" t="n">
+        <v>70627.3</v>
+      </c>
+      <c r="W2" s="1" t="n">
         <v>70796.5</v>
       </c>
-      <c r="W2" s="1" t="n">
+      <c r="X2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -701,9 +710,12 @@
         <v>2084.79</v>
       </c>
       <c r="V3" s="1" t="n">
+        <v>2081.89</v>
+      </c>
+      <c r="W3" s="1" t="n">
         <v>2084.79</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="X3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -774,9 +786,12 @@
         <v>87.03</v>
       </c>
       <c r="V4" s="1" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="W4" s="1" t="n">
         <v>87.05</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="X4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -847,9 +862,12 @@
         <v>3.967</v>
       </c>
       <c r="V5" s="1" t="n">
+        <v>3.969</v>
+      </c>
+      <c r="W5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="X5" s="1" t="n">
         <v>3.967</v>
       </c>
     </row>
@@ -920,9 +938,12 @@
         <v>0.09478</v>
       </c>
       <c r="V6" s="1" t="n">
+        <v>0.09467</v>
+      </c>
+      <c r="W6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="X6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -993,9 +1014,12 @@
         <v>1.3923</v>
       </c>
       <c r="V7" s="1" t="n">
+        <v>1.3911</v>
+      </c>
+      <c r="W7" s="1" t="n">
         <v>1.3929</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="X7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -1066,9 +1090,12 @@
         <v>21.923</v>
       </c>
       <c r="V8" s="1" t="n">
+        <v>22.193</v>
+      </c>
+      <c r="W8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="W8" s="1" t="n">
+      <c r="X8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1139,9 +1166,12 @@
         <v>0.002045</v>
       </c>
       <c r="V9" s="1" t="n">
+        <v>0.002004</v>
+      </c>
+      <c r="W9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="W9" s="1" t="n">
+      <c r="X9" s="1" t="n">
         <v>0.001951</v>
       </c>
     </row>
@@ -1212,9 +1242,12 @@
         <v>0.010015</v>
       </c>
       <c r="V10" s="1" t="n">
+        <v>0.010003</v>
+      </c>
+      <c r="W10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="W10" s="1" t="n">
+      <c r="X10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1285,9 +1318,12 @@
         <v>0.14558</v>
       </c>
       <c r="V11" s="1" t="n">
+        <v>0.14484</v>
+      </c>
+      <c r="W11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="W11" s="1" t="n">
+      <c r="X11" s="1" t="n">
         <v>0.13631</v>
       </c>
     </row>
@@ -1358,10 +1394,13 @@
         <v>0.011051</v>
       </c>
       <c r="V12" s="1" t="n">
+        <v>0.010936</v>
+      </c>
+      <c r="W12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="W12" s="1" t="n">
-        <v>0.011051</v>
+      <c r="X12" s="1" t="n">
+        <v>0.010936</v>
       </c>
     </row>
     <row r="13">
@@ -1431,9 +1470,12 @@
         <v>37.761</v>
       </c>
       <c r="V13" s="1" t="n">
+        <v>37.884</v>
+      </c>
+      <c r="W13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="W13" s="1" t="n">
+      <c r="X13" s="1" t="n">
         <v>37.748</v>
       </c>
     </row>
@@ -1504,9 +1546,12 @@
         <v>653.89</v>
       </c>
       <c r="V14" s="1" t="n">
+        <v>653.3099999999999</v>
+      </c>
+      <c r="W14" s="1" t="n">
         <v>654.13</v>
       </c>
-      <c r="W14" s="1" t="n">
+      <c r="X14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1577,9 +1622,12 @@
         <v>209.6</v>
       </c>
       <c r="V15" s="1" t="n">
+        <v>209.32</v>
+      </c>
+      <c r="W15" s="1" t="n">
         <v>210.26</v>
       </c>
-      <c r="W15" s="1" t="n">
+      <c r="X15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1650,9 +1698,12 @@
         <v>0.0033203</v>
       </c>
       <c r="V16" s="1" t="n">
+        <v>0.0033181</v>
+      </c>
+      <c r="W16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="W16" s="1" t="n">
+      <c r="X16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1723,9 +1774,12 @@
         <v>239.37</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>240.32</v>
+        <v>241.69</v>
       </c>
       <c r="W17" s="1" t="n">
+        <v>241.69</v>
+      </c>
+      <c r="X17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1796,9 +1850,12 @@
         <v>0.9876</v>
       </c>
       <c r="V18" s="1" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="W18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="W18" s="1" t="n">
+      <c r="X18" s="1" t="n">
         <v>0.9858</v>
       </c>
     </row>
@@ -1869,9 +1926,12 @@
         <v>1.0006</v>
       </c>
       <c r="V19" s="1" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="W19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="W19" s="1" t="n">
+      <c r="X19" s="1" t="n">
         <v>0.9972</v>
       </c>
     </row>
@@ -1942,9 +2002,12 @@
         <v>0.2595</v>
       </c>
       <c r="V20" s="1" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="W20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="W20" s="1" t="n">
+      <c r="X20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -2015,10 +2078,13 @@
         <v>0.59222</v>
       </c>
       <c r="V21" s="1" t="n">
+        <v>0.5868100000000001</v>
+      </c>
+      <c r="W21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="W21" s="1" t="n">
-        <v>0.59034</v>
+      <c r="X21" s="1" t="n">
+        <v>0.5868100000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2088,9 +2154,12 @@
         <v>9.036</v>
       </c>
       <c r="V22" s="1" t="n">
+        <v>9.026999999999999</v>
+      </c>
+      <c r="W22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="W22" s="1" t="n">
+      <c r="X22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -2161,9 +2230,12 @@
         <v>0.02359</v>
       </c>
       <c r="V23" s="1" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="W23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="W23" s="1" t="n">
+      <c r="X23" s="1" t="n">
         <v>0.02359</v>
       </c>
     </row>
@@ -2234,9 +2306,12 @@
         <v>9.58</v>
       </c>
       <c r="V24" s="1" t="n">
+        <v>9.574999999999999</v>
+      </c>
+      <c r="W24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="W24" s="1" t="n">
+      <c r="X24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2307,10 +2382,13 @@
         <v>1.23</v>
       </c>
       <c r="V25" s="1" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="W25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="W25" s="1" t="n">
-        <v>1.218</v>
+      <c r="X25" s="1" t="n">
+        <v>1.216</v>
       </c>
     </row>
     <row r="26">
@@ -2380,9 +2458,12 @@
         <v>0.07284</v>
       </c>
       <c r="V26" s="1" t="n">
+        <v>0.07282</v>
+      </c>
+      <c r="W26" s="1" t="n">
         <v>0.07317</v>
       </c>
-      <c r="W26" s="1" t="n">
+      <c r="X26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2453,9 +2534,12 @@
         <v>1.412</v>
       </c>
       <c r="V27" s="1" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="W27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="W27" s="1" t="n">
+      <c r="X27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2526,9 +2610,12 @@
         <v>1.306</v>
       </c>
       <c r="V28" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="W28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="W28" s="1" t="n">
+      <c r="X28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2599,9 +2686,12 @@
         <v>464.14</v>
       </c>
       <c r="V29" s="1" t="n">
+        <v>463.35</v>
+      </c>
+      <c r="W29" s="1" t="n">
         <v>464.27</v>
       </c>
-      <c r="W29" s="1" t="n">
+      <c r="X29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2672,9 +2762,12 @@
         <v>1.2889</v>
       </c>
       <c r="V30" s="1" t="n">
+        <v>1.2856</v>
+      </c>
+      <c r="W30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="W30" s="1" t="n">
+      <c r="X30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2745,9 +2838,12 @@
         <v>5019.32</v>
       </c>
       <c r="V31" s="1" t="n">
+        <v>5020.62</v>
+      </c>
+      <c r="W31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="W31" s="1" t="n">
+      <c r="X31" s="1" t="n">
         <v>5019.32</v>
       </c>
     </row>
@@ -2818,9 +2914,12 @@
         <v>0.879</v>
       </c>
       <c r="V32" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="W32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="W32" s="1" t="n">
+      <c r="X32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2891,9 +2990,12 @@
         <v>0.00197</v>
       </c>
       <c r="V33" s="1" t="n">
+        <v>0.001968</v>
+      </c>
+      <c r="W33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="W33" s="1" t="n">
+      <c r="X33" s="1" t="n">
         <v>0.001966</v>
       </c>
     </row>
@@ -2964,9 +3066,12 @@
         <v>0.17388</v>
       </c>
       <c r="V34" s="1" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="W34" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="W34" s="1" t="n">
+      <c r="X34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -3037,9 +3142,12 @@
         <v>0.29696</v>
       </c>
       <c r="V35" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="W35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="W35" s="1" t="n">
+      <c r="X35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -3110,9 +3218,12 @@
         <v>1.798</v>
       </c>
       <c r="V36" s="1" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="W36" s="1" t="n">
         <v>1.798</v>
       </c>
-      <c r="W36" s="1" t="n">
+      <c r="X36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -3183,9 +3294,12 @@
         <v>110.44</v>
       </c>
       <c r="V37" s="1" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="W37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="W37" s="1" t="n">
+      <c r="X37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -3256,9 +3370,12 @@
         <v>0.22299</v>
       </c>
       <c r="V38" s="1" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="W38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="W38" s="1" t="n">
+      <c r="X38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -3329,10 +3446,13 @@
         <v>0.1067</v>
       </c>
       <c r="V39" s="1" t="n">
+        <v>0.1063</v>
+      </c>
+      <c r="W39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="W39" s="1" t="n">
-        <v>0.1066</v>
+      <c r="X39" s="1" t="n">
+        <v>0.1063</v>
       </c>
     </row>
     <row r="40">
@@ -3402,9 +3522,12 @@
         <v>0.37226</v>
       </c>
       <c r="V40" s="1" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="W40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="W40" s="1" t="n">
+      <c r="X40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -3475,9 +3598,12 @@
         <v>54.61</v>
       </c>
       <c r="V41" s="1" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="W41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="W41" s="1" t="n">
+      <c r="X41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3548,9 +3674,12 @@
         <v>0.0010552</v>
       </c>
       <c r="V42" s="1" t="n">
+        <v>0.001054</v>
+      </c>
+      <c r="W42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="W42" s="1" t="n">
+      <c r="X42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -3621,9 +3750,12 @@
         <v>6.482</v>
       </c>
       <c r="V43" s="1" t="n">
+        <v>6.475</v>
+      </c>
+      <c r="W43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="W43" s="1" t="n">
+      <c r="X43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3694,9 +3826,12 @@
         <v>0.6264999999999999</v>
       </c>
       <c r="V44" s="1" t="n">
+        <v>0.6246</v>
+      </c>
+      <c r="W44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="W44" s="1" t="n">
+      <c r="X44" s="1" t="n">
         <v>0.6213</v>
       </c>
     </row>
@@ -3767,9 +3902,12 @@
         <v>0.3515</v>
       </c>
       <c r="V45" s="1" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="W45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="W45" s="1" t="n">
+      <c r="X45" s="1" t="n">
         <v>0.3512</v>
       </c>
     </row>
@@ -3840,9 +3978,12 @@
         <v>0.03278</v>
       </c>
       <c r="V46" s="1" t="n">
+        <v>0.03286</v>
+      </c>
+      <c r="W46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="W46" s="1" t="n">
+      <c r="X46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3913,10 +4054,13 @@
         <v>0.0687</v>
       </c>
       <c r="V47" s="1" t="n">
+        <v>0.06844</v>
+      </c>
+      <c r="W47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="W47" s="1" t="n">
-        <v>0.0687</v>
+      <c r="X47" s="1" t="n">
+        <v>0.06844</v>
       </c>
     </row>
     <row r="48">
@@ -3986,9 +4130,12 @@
         <v>0.7063</v>
       </c>
       <c r="V48" s="1" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="W48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="W48" s="1" t="n">
+      <c r="X48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -4059,9 +4206,12 @@
         <v>0.004246</v>
       </c>
       <c r="V49" s="1" t="n">
+        <v>0.004259</v>
+      </c>
+      <c r="W49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="W49" s="1" t="n">
+      <c r="X49" s="1" t="n">
         <v>0.004224</v>
       </c>
     </row>
@@ -4132,9 +4282,12 @@
         <v>0.1031</v>
       </c>
       <c r="V50" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="W50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="W50" s="1" t="n">
+      <c r="X50" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -4205,10 +4358,13 @@
         <v>0.04027</v>
       </c>
       <c r="V51" s="1" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="W51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="W51" s="1" t="n">
-        <v>0.04021</v>
+      <c r="X51" s="1" t="n">
+        <v>0.04019</v>
       </c>
     </row>
     <row r="52">
@@ -4278,10 +4434,13 @@
         <v>0.1647</v>
       </c>
       <c r="V52" s="1" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="W52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="W52" s="1" t="n">
-        <v>0.1645</v>
+      <c r="X52" s="1" t="n">
+        <v>0.1641</v>
       </c>
     </row>
     <row r="53">
@@ -4351,9 +4510,12 @@
         <v>0.01932</v>
       </c>
       <c r="V53" s="1" t="n">
+        <v>0.01953</v>
+      </c>
+      <c r="W53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="W53" s="1" t="n">
+      <c r="X53" s="1" t="n">
         <v>0.01922</v>
       </c>
     </row>
@@ -4424,10 +4586,13 @@
         <v>0.007178</v>
       </c>
       <c r="V54" s="1" t="n">
+        <v>0.007169</v>
+      </c>
+      <c r="W54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="W54" s="1" t="n">
-        <v>0.00717</v>
+      <c r="X54" s="1" t="n">
+        <v>0.007169</v>
       </c>
     </row>
     <row r="55">
@@ -4497,9 +4662,12 @@
         <v>3.923</v>
       </c>
       <c r="V55" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="W55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="W55" s="1" t="n">
+      <c r="X55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -4570,9 +4738,12 @@
         <v>0.01692</v>
       </c>
       <c r="V56" s="1" t="n">
+        <v>0.016829</v>
+      </c>
+      <c r="W56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="W56" s="1" t="n">
+      <c r="X56" s="1" t="n">
         <v>0.016808</v>
       </c>
     </row>
@@ -4643,9 +4814,12 @@
         <v>0.1082</v>
       </c>
       <c r="V57" s="1" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="W57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="W57" s="1" t="n">
+      <c r="X57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -4716,9 +4890,12 @@
         <v>2.643</v>
       </c>
       <c r="V58" s="1" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="W58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="W58" s="1" t="n">
+      <c r="X58" s="1" t="n">
         <v>2.639</v>
       </c>
     </row>
@@ -4789,10 +4966,13 @@
         <v>0.1584</v>
       </c>
       <c r="V59" s="1" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="W59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="W59" s="1" t="n">
-        <v>0.1582</v>
+      <c r="X59" s="1" t="n">
+        <v>0.1579</v>
       </c>
     </row>
     <row r="60">
@@ -4862,9 +5042,12 @@
         <v>0.005843</v>
       </c>
       <c r="V60" s="1" t="n">
+        <v>0.005836</v>
+      </c>
+      <c r="W60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="W60" s="1" t="n">
+      <c r="X60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -4935,9 +5118,12 @@
         <v>0.09171</v>
       </c>
       <c r="V61" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="W61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="W61" s="1" t="n">
+      <c r="X61" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5008,9 +5194,12 @@
         <v>0.9122</v>
       </c>
       <c r="V62" s="1" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="W62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="W62" s="1" t="n">
+      <c r="X62" s="1" t="n">
         <v>0.9101</v>
       </c>
     </row>
@@ -5081,9 +5270,12 @@
         <v>0.778</v>
       </c>
       <c r="V63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="W63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="W63" s="1" t="n">
+      <c r="X63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -5154,9 +5346,12 @@
         <v>0.04599</v>
       </c>
       <c r="V64" s="1" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="W64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="W64" s="1" t="n">
+      <c r="X64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -5227,9 +5422,12 @@
         <v>356.31</v>
       </c>
       <c r="V65" s="1" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="W65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="W65" s="1" t="n">
+      <c r="X65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -5300,9 +5498,12 @@
         <v>0.1239</v>
       </c>
       <c r="V66" s="1" t="n">
+        <v>0.12492</v>
+      </c>
+      <c r="W66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="W66" s="1" t="n">
+      <c r="X66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -5373,9 +5574,12 @@
         <v>0.2308</v>
       </c>
       <c r="V67" s="1" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="W67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="W67" s="1" t="n">
+      <c r="X67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -5446,10 +5650,13 @@
         <v>0.00337</v>
       </c>
       <c r="V68" s="1" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="W68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="W68" s="1" t="n">
-        <v>0.00337</v>
+      <c r="X68" s="1" t="n">
+        <v>0.00335</v>
       </c>
     </row>
     <row r="69">
@@ -5519,9 +5726,12 @@
         <v>0.1744</v>
       </c>
       <c r="V69" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="W69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="W69" s="1" t="n">
+      <c r="X69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -5592,9 +5802,12 @@
         <v>0.16395</v>
       </c>
       <c r="V70" s="1" t="n">
+        <v>0.16359</v>
+      </c>
+      <c r="W70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="W70" s="1" t="n">
+      <c r="X70" s="1" t="n">
         <v>0.16358</v>
       </c>
     </row>
@@ -5665,9 +5878,12 @@
         <v>0.3599</v>
       </c>
       <c r="V71" s="1" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="W71" s="1" t="n">
         <v>0.3599</v>
       </c>
-      <c r="W71" s="1" t="n">
+      <c r="X71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -5738,9 +5954,12 @@
         <v>0.7078</v>
       </c>
       <c r="V72" s="1" t="n">
+        <v>0.7071</v>
+      </c>
+      <c r="W72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="W72" s="1" t="n">
+      <c r="X72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -5811,9 +6030,12 @@
         <v>0.008580000000000001</v>
       </c>
       <c r="V73" s="1" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="W73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="W73" s="1" t="n">
+      <c r="X73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -5884,9 +6106,12 @@
         <v>0.005965</v>
       </c>
       <c r="V74" s="1" t="n">
+        <v>0.00596</v>
+      </c>
+      <c r="W74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="W74" s="1" t="n">
+      <c r="X74" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -5957,9 +6182,12 @@
         <v>0.229</v>
       </c>
       <c r="V75" s="1" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="W75" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -6030,9 +6258,12 @@
         <v>0.3287</v>
       </c>
       <c r="V76" s="1" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="W76" s="1" t="n">
         <v>0.3287</v>
       </c>
-      <c r="W76" s="1" t="n">
+      <c r="X76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -6103,9 +6334,12 @@
         <v>0.1001</v>
       </c>
       <c r="V77" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="W77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="W77" s="1" t="n">
+      <c r="X77" s="1" t="n">
         <v>0.0999</v>
       </c>
     </row>
@@ -6176,9 +6410,12 @@
         <v>0.1225</v>
       </c>
       <c r="V78" s="1" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="W78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="W78" s="1" t="n">
+      <c r="X78" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -6249,9 +6486,12 @@
         <v>0.07439</v>
       </c>
       <c r="V79" s="1" t="n">
+        <v>0.07296999999999999</v>
+      </c>
+      <c r="W79" s="1" t="n">
         <v>0.07549</v>
       </c>
-      <c r="W79" s="1" t="n">
+      <c r="X79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -6322,10 +6562,13 @@
         <v>0.04623</v>
       </c>
       <c r="V80" s="1" t="n">
+        <v>0.04605</v>
+      </c>
+      <c r="W80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="W80" s="1" t="n">
-        <v>0.04623</v>
+      <c r="X80" s="1" t="n">
+        <v>0.04605</v>
       </c>
     </row>
     <row r="81">
@@ -6395,9 +6638,12 @@
         <v>0.000231</v>
       </c>
       <c r="V81" s="1" t="n">
+        <v>0.000229</v>
+      </c>
+      <c r="W81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="W81" s="1" t="n">
+      <c r="X81" s="1" t="n">
         <v>0.000228</v>
       </c>
     </row>
@@ -6468,10 +6714,13 @@
         <v>8.206</v>
       </c>
       <c r="V82" s="1" t="n">
+        <v>8.186</v>
+      </c>
+      <c r="W82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="W82" s="1" t="n">
-        <v>8.194000000000001</v>
+      <c r="X82" s="1" t="n">
+        <v>8.186</v>
       </c>
     </row>
     <row r="83">
@@ -6541,9 +6790,12 @@
         <v>0.0005734</v>
       </c>
       <c r="V83" s="1" t="n">
+        <v>0.0005731999999999999</v>
+      </c>
+      <c r="W83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="W83" s="1" t="n">
+      <c r="X83" s="1" t="n">
         <v>0.0005713</v>
       </c>
     </row>
@@ -6614,9 +6866,12 @@
         <v>0.4439</v>
       </c>
       <c r="V84" s="1" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="W84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="W84" s="1" t="n">
+      <c r="X84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6687,9 +6942,12 @@
         <v>0.06242</v>
       </c>
       <c r="V85" s="1" t="n">
+        <v>0.06234</v>
+      </c>
+      <c r="W85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="W85" s="1" t="n">
+      <c r="X85" s="1" t="n">
         <v>0.0623</v>
       </c>
     </row>
@@ -6760,9 +7018,12 @@
         <v>0.05413</v>
       </c>
       <c r="V86" s="1" t="n">
+        <v>0.05417</v>
+      </c>
+      <c r="W86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="W86" s="1" t="n">
+      <c r="X86" s="1" t="n">
         <v>0.05403</v>
       </c>
     </row>
@@ -6833,9 +7094,12 @@
         <v>0.00336</v>
       </c>
       <c r="V87" s="1" t="n">
+        <v>0.003362</v>
+      </c>
+      <c r="W87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="W87" s="1" t="n">
+      <c r="X87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -6906,9 +7170,12 @@
         <v>0.05011</v>
       </c>
       <c r="V88" s="1" t="n">
+        <v>0.04992</v>
+      </c>
+      <c r="W88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="W88" s="1" t="n">
+      <c r="X88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -6979,9 +7246,12 @@
         <v>0.03126</v>
       </c>
       <c r="V89" s="1" t="n">
-        <v>0.03192</v>
+        <v>0.03198</v>
       </c>
       <c r="W89" s="1" t="n">
+        <v>0.03198</v>
+      </c>
+      <c r="X89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -7052,10 +7322,13 @@
         <v>0.3443</v>
       </c>
       <c r="V90" s="1" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="W90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="W90" s="1" t="n">
-        <v>0.3442</v>
+      <c r="X90" s="1" t="n">
+        <v>0.3436</v>
       </c>
     </row>
     <row r="91">
@@ -7125,9 +7398,12 @@
         <v>0.07434</v>
       </c>
       <c r="V91" s="1" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="W91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="W91" s="1" t="n">
+      <c r="X91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -7201,6 +7477,9 @@
         <v>0.361</v>
       </c>
       <c r="W92" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="X92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -7271,9 +7550,12 @@
         <v>1.9816</v>
       </c>
       <c r="V93" s="1" t="n">
+        <v>1.9759</v>
+      </c>
+      <c r="W93" s="1" t="n">
         <v>1.9816</v>
       </c>
-      <c r="W93" s="1" t="n">
+      <c r="X93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -7344,9 +7626,12 @@
         <v>0.2587</v>
       </c>
       <c r="V94" s="1" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="W94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="W94" s="1" t="n">
+      <c r="X94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -7417,9 +7702,12 @@
         <v>0.04514</v>
       </c>
       <c r="V95" s="1" t="n">
+        <v>0.04518</v>
+      </c>
+      <c r="W95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="W95" s="1" t="n">
+      <c r="X95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -7490,9 +7778,12 @@
         <v>0.006176</v>
       </c>
       <c r="V96" s="1" t="n">
+        <v>0.006287</v>
+      </c>
+      <c r="W96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="W96" s="1" t="n">
+      <c r="X96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -7563,9 +7854,12 @@
         <v>0.001708</v>
       </c>
       <c r="V97" s="1" t="n">
+        <v>0.001708</v>
+      </c>
+      <c r="W97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="W97" s="1" t="n">
+      <c r="X97" s="1" t="n">
         <v>0.001706</v>
       </c>
     </row>
@@ -7636,9 +7930,12 @@
         <v>5.198</v>
       </c>
       <c r="V98" s="1" t="n">
+        <v>5.203</v>
+      </c>
+      <c r="W98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="W98" s="1" t="n">
+      <c r="X98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -7709,9 +8006,12 @@
         <v>0.01501</v>
       </c>
       <c r="V99" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="W99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="W99" s="1" t="n">
+      <c r="X99" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -7782,9 +8082,12 @@
         <v>0.551</v>
       </c>
       <c r="V100" s="1" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="W100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="W100" s="1" t="n">
+      <c r="X100" s="1" t="n">
         <v>0.5508</v>
       </c>
     </row>
@@ -7855,9 +8158,12 @@
         <v>0.0898</v>
       </c>
       <c r="V101" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="W101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="W101" s="1" t="n">
+      <c r="X101" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -7928,10 +8234,13 @@
         <v>32.3</v>
       </c>
       <c r="V102" s="1" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="W102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="W102" s="1" t="n">
-        <v>32.29</v>
+      <c r="X102" s="1" t="n">
+        <v>32.25</v>
       </c>
     </row>
     <row r="103">
@@ -8001,9 +8310,12 @@
         <v>0.03226</v>
       </c>
       <c r="V103" s="1" t="n">
+        <v>0.03211</v>
+      </c>
+      <c r="W103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="W103" s="1" t="n">
+      <c r="X103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -8074,10 +8386,13 @@
         <v>0.06558</v>
       </c>
       <c r="V104" s="1" t="n">
+        <v>0.06548</v>
+      </c>
+      <c r="W104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="W104" s="1" t="n">
-        <v>0.06558</v>
+      <c r="X104" s="1" t="n">
+        <v>0.06548</v>
       </c>
     </row>
     <row r="105">
@@ -8147,9 +8462,12 @@
         <v>1.303</v>
       </c>
       <c r="V105" s="1" t="n">
+        <v>1.3002</v>
+      </c>
+      <c r="W105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="W105" s="1" t="n">
+      <c r="X105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -8220,9 +8538,12 @@
         <v>0.1201</v>
       </c>
       <c r="V106" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="W106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="W106" s="1" t="n">
+      <c r="X106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -8293,9 +8614,12 @@
         <v>0.119</v>
       </c>
       <c r="V107" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="W107" s="1" t="n">
+      <c r="X107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -8366,10 +8690,13 @@
         <v>0.09574000000000001</v>
       </c>
       <c r="V108" s="1" t="n">
+        <v>0.09569</v>
+      </c>
+      <c r="W108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="W108" s="1" t="n">
-        <v>0.09572</v>
+      <c r="X108" s="1" t="n">
+        <v>0.09569</v>
       </c>
     </row>
     <row r="109">
@@ -8439,9 +8766,12 @@
         <v>0.14021</v>
       </c>
       <c r="V109" s="1" t="n">
+        <v>0.13988</v>
+      </c>
+      <c r="W109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="W109" s="1" t="n">
+      <c r="X109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -8512,9 +8842,12 @@
         <v>5.56</v>
       </c>
       <c r="V110" s="1" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="W110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="W110" s="1" t="n">
+      <c r="X110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -8585,9 +8918,12 @@
         <v>1.098</v>
       </c>
       <c r="V111" s="1" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="W111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="W111" s="1" t="n">
+      <c r="X111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -8658,10 +8994,13 @@
         <v>0.028749</v>
       </c>
       <c r="V112" s="1" t="n">
+        <v>0.028712</v>
+      </c>
+      <c r="W112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="W112" s="1" t="n">
-        <v>0.028743</v>
+      <c r="X112" s="1" t="n">
+        <v>0.028712</v>
       </c>
     </row>
     <row r="113">
@@ -8731,10 +9070,13 @@
         <v>1.863</v>
       </c>
       <c r="V113" s="1" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="W113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="W113" s="1" t="n">
-        <v>1.862</v>
+      <c r="X113" s="1" t="n">
+        <v>1.859</v>
       </c>
     </row>
     <row r="114">
@@ -8804,9 +9146,12 @@
         <v>0.05924</v>
       </c>
       <c r="V114" s="1" t="n">
+        <v>0.05876</v>
+      </c>
+      <c r="W114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="W114" s="1" t="n">
+      <c r="X114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -8877,10 +9222,13 @@
         <v>0.12783</v>
       </c>
       <c r="V115" s="1" t="n">
+        <v>0.12727</v>
+      </c>
+      <c r="W115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="W115" s="1" t="n">
-        <v>0.12732</v>
+      <c r="X115" s="1" t="n">
+        <v>0.12727</v>
       </c>
     </row>
     <row r="116">
@@ -8950,10 +9298,13 @@
         <v>1.0959</v>
       </c>
       <c r="V116" s="1" t="n">
+        <v>1.0937</v>
+      </c>
+      <c r="W116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="W116" s="1" t="n">
-        <v>1.0959</v>
+      <c r="X116" s="1" t="n">
+        <v>1.0937</v>
       </c>
     </row>
     <row r="117">
@@ -9023,9 +9374,12 @@
         <v>0.1526</v>
       </c>
       <c r="V117" s="1" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="W117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="W117" s="1" t="n">
+      <c r="X117" s="1" t="n">
         <v>0.1484</v>
       </c>
     </row>
@@ -9096,10 +9450,13 @@
         <v>0.1582</v>
       </c>
       <c r="V118" s="1" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="W118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="W118" s="1" t="n">
-        <v>0.158</v>
+      <c r="X118" s="1" t="n">
+        <v>0.1572</v>
       </c>
     </row>
     <row r="119">
@@ -9169,9 +9526,12 @@
         <v>0.0472</v>
       </c>
       <c r="V119" s="1" t="n">
+        <v>0.04753</v>
+      </c>
+      <c r="W119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="W119" s="1" t="n">
+      <c r="X119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -9242,9 +9602,12 @@
         <v>3.016</v>
       </c>
       <c r="V120" s="1" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="W120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="W120" s="1" t="n">
+      <c r="X120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -9315,9 +9678,12 @@
         <v>0.2975</v>
       </c>
       <c r="V121" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="W121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="W121" s="1" t="n">
+      <c r="X121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -9388,10 +9754,13 @@
         <v>0.578</v>
       </c>
       <c r="V122" s="1" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="W122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="W122" s="1" t="n">
-        <v>0.5770999999999999</v>
+      <c r="X122" s="1" t="n">
+        <v>0.5768</v>
       </c>
     </row>
     <row r="123">
@@ -9461,10 +9830,13 @@
         <v>0.01251</v>
       </c>
       <c r="V123" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="W123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="W123" s="1" t="n">
-        <v>0.01251</v>
+      <c r="X123" s="1" t="n">
+        <v>0.01247</v>
       </c>
     </row>
     <row r="124">
@@ -9534,10 +9906,13 @@
         <v>0.1571</v>
       </c>
       <c r="V124" s="1" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="W124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="W124" s="1" t="n">
-        <v>0.1569</v>
+      <c r="X124" s="1" t="n">
+        <v>0.1566</v>
       </c>
     </row>
     <row r="125">
@@ -9610,6 +9985,9 @@
         <v>0.001786</v>
       </c>
       <c r="W125" s="1" t="n">
+        <v>0.001786</v>
+      </c>
+      <c r="X125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -9680,10 +10058,13 @@
         <v>0.0004831</v>
       </c>
       <c r="V126" s="1" t="n">
+        <v>0.0004816</v>
+      </c>
+      <c r="W126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="W126" s="1" t="n">
-        <v>0.0004824</v>
+      <c r="X126" s="1" t="n">
+        <v>0.0004816</v>
       </c>
     </row>
     <row r="127">
@@ -9753,10 +10134,13 @@
         <v>0.02926</v>
       </c>
       <c r="V127" s="1" t="n">
+        <v>0.02922</v>
+      </c>
+      <c r="W127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="W127" s="1" t="n">
-        <v>0.02924</v>
+      <c r="X127" s="1" t="n">
+        <v>0.02922</v>
       </c>
     </row>
     <row r="128">
@@ -9826,9 +10210,12 @@
         <v>0.04125</v>
       </c>
       <c r="V128" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="W128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="W128" s="1" t="n">
+      <c r="X128" s="1" t="n">
         <v>0.04116</v>
       </c>
     </row>
@@ -9899,9 +10286,12 @@
         <v>0.04913</v>
       </c>
       <c r="V129" s="1" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="W129" s="1" t="n">
         <v>0.04935</v>
       </c>
-      <c r="W129" s="1" t="n">
+      <c r="X129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -9972,9 +10362,12 @@
         <v>1.22e-05</v>
       </c>
       <c r="V130" s="1" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="W130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="W130" s="1" t="n">
+      <c r="X130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -10045,9 +10438,12 @@
         <v>7.5e-06</v>
       </c>
       <c r="V131" s="1" t="n">
+        <v>7.3e-06</v>
+      </c>
+      <c r="W131" s="1" t="n">
         <v>7.5e-06</v>
       </c>
-      <c r="W131" s="1" t="n">
+      <c r="X131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -10118,9 +10514,12 @@
         <v>0.00705</v>
       </c>
       <c r="V132" s="1" t="n">
+        <v>0.00701</v>
+      </c>
+      <c r="W132" s="1" t="n">
         <v>0.00705</v>
       </c>
-      <c r="W132" s="1" t="n">
+      <c r="X132" s="1" t="n">
         <v>0.00697</v>
       </c>
     </row>
@@ -10191,9 +10590,12 @@
         <v>0.0964</v>
       </c>
       <c r="V133" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="W133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="W133" s="1" t="n">
+      <c r="X133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -10264,9 +10666,12 @@
         <v>0.0004099</v>
       </c>
       <c r="V134" s="1" t="n">
+        <v>0.0004104</v>
+      </c>
+      <c r="W134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="W134" s="1" t="n">
+      <c r="X134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -10337,9 +10742,12 @@
         <v>0.08172</v>
       </c>
       <c r="V135" s="1" t="n">
+        <v>0.08191</v>
+      </c>
+      <c r="W135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="W135" s="1" t="n">
+      <c r="X135" s="1" t="n">
         <v>0.08148</v>
       </c>
     </row>
@@ -10410,10 +10818,13 @@
         <v>0.007757</v>
       </c>
       <c r="V136" s="1" t="n">
+        <v>0.007748</v>
+      </c>
+      <c r="W136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="W136" s="1" t="n">
-        <v>0.007757</v>
+      <c r="X136" s="1" t="n">
+        <v>0.007748</v>
       </c>
     </row>
     <row r="137">
@@ -10483,10 +10894,13 @@
         <v>0.000802</v>
       </c>
       <c r="V137" s="1" t="n">
+        <v>0.0007981</v>
+      </c>
+      <c r="W137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="W137" s="1" t="n">
-        <v>0.000802</v>
+      <c r="X137" s="1" t="n">
+        <v>0.0007981</v>
       </c>
     </row>
     <row r="138">
@@ -10556,9 +10970,12 @@
         <v>0.1453</v>
       </c>
       <c r="V138" s="1" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="W138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="W138" s="1" t="n">
+      <c r="X138" s="1" t="n">
         <v>0.1453</v>
       </c>
     </row>
@@ -10629,10 +11046,13 @@
         <v>0.00667</v>
       </c>
       <c r="V139" s="1" t="n">
+        <v>0.006661</v>
+      </c>
+      <c r="W139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="W139" s="1" t="n">
-        <v>0.00667</v>
+      <c r="X139" s="1" t="n">
+        <v>0.006661</v>
       </c>
     </row>
     <row r="140">
@@ -10702,10 +11122,13 @@
         <v>0.01374</v>
       </c>
       <c r="V140" s="1" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="W140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="W140" s="1" t="n">
-        <v>0.01374</v>
+      <c r="X140" s="1" t="n">
+        <v>0.01373</v>
       </c>
     </row>
     <row r="141">
@@ -10775,10 +11198,13 @@
         <v>0.09646</v>
       </c>
       <c r="V141" s="1" t="n">
+        <v>0.09601</v>
+      </c>
+      <c r="W141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="W141" s="1" t="n">
-        <v>0.09646</v>
+      <c r="X141" s="1" t="n">
+        <v>0.09601</v>
       </c>
     </row>
     <row r="142">
@@ -10848,9 +11274,12 @@
         <v>0.05411</v>
       </c>
       <c r="V142" s="1" t="n">
+        <v>0.05412</v>
+      </c>
+      <c r="W142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="W142" s="1" t="n">
+      <c r="X142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -10921,9 +11350,12 @@
         <v>0.3225</v>
       </c>
       <c r="V143" s="1" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="W143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="W143" s="1" t="n">
+      <c r="X143" s="1" t="n">
         <v>0.3219</v>
       </c>
     </row>
@@ -10994,10 +11426,13 @@
         <v>0.02561</v>
       </c>
       <c r="V144" s="1" t="n">
+        <v>0.02553</v>
+      </c>
+      <c r="W144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="W144" s="1" t="n">
-        <v>0.02557</v>
+      <c r="X144" s="1" t="n">
+        <v>0.02553</v>
       </c>
     </row>
     <row r="145">
@@ -11067,9 +11502,12 @@
         <v>0.2351</v>
       </c>
       <c r="V145" s="1" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="W145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="W145" s="1" t="n">
+      <c r="X145" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -11140,9 +11578,12 @@
         <v>0.007043</v>
       </c>
       <c r="V146" s="1" t="n">
+        <v>0.007037</v>
+      </c>
+      <c r="W146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="W146" s="1" t="n">
+      <c r="X146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -11213,9 +11654,12 @@
         <v>0.08641</v>
       </c>
       <c r="V147" s="1" t="n">
+        <v>0.08624999999999999</v>
+      </c>
+      <c r="W147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="W147" s="1" t="n">
+      <c r="X147" s="1" t="n">
         <v>0.08597</v>
       </c>
     </row>
@@ -11286,9 +11730,12 @@
         <v>0.05264</v>
       </c>
       <c r="V148" s="1" t="n">
-        <v>0.05284</v>
+        <v>0.05289</v>
       </c>
       <c r="W148" s="1" t="n">
+        <v>0.05289</v>
+      </c>
+      <c r="X148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -11359,9 +11806,12 @@
         <v>0.02402</v>
       </c>
       <c r="V149" s="1" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="W149" s="1" t="n">
         <v>0.02402</v>
       </c>
-      <c r="W149" s="1" t="n">
+      <c r="X149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -11432,9 +11882,12 @@
         <v>0.08631999999999999</v>
       </c>
       <c r="V150" s="1" t="n">
+        <v>0.08595</v>
+      </c>
+      <c r="W150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="W150" s="1" t="n">
+      <c r="X150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -11505,9 +11958,12 @@
         <v>0.02312</v>
       </c>
       <c r="V151" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="W151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="W151" s="1" t="n">
+      <c r="X151" s="1" t="n">
         <v>0.02312</v>
       </c>
     </row>
@@ -11578,10 +12034,13 @@
         <v>0.0252</v>
       </c>
       <c r="V152" s="1" t="n">
+        <v>0.02515</v>
+      </c>
+      <c r="W152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="W152" s="1" t="n">
-        <v>0.0252</v>
+      <c r="X152" s="1" t="n">
+        <v>0.02515</v>
       </c>
     </row>
     <row r="153">
@@ -11651,9 +12110,12 @@
         <v>0.0002123</v>
       </c>
       <c r="V153" s="1" t="n">
+        <v>0.0002109</v>
+      </c>
+      <c r="W153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="W153" s="1" t="n">
+      <c r="X153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -11724,9 +12186,12 @@
         <v>0.4411</v>
       </c>
       <c r="V154" s="1" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="W154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="W154" s="1" t="n">
+      <c r="X154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -11797,9 +12262,12 @@
         <v>0.06784</v>
       </c>
       <c r="V155" s="1" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="W155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="W155" s="1" t="n">
+      <c r="X155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -11870,9 +12338,12 @@
         <v>0.13064</v>
       </c>
       <c r="V156" s="1" t="n">
+        <v>0.13161</v>
+      </c>
+      <c r="W156" s="1" t="n">
         <v>0.13403</v>
       </c>
-      <c r="W156" s="1" t="n">
+      <c r="X156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -11943,9 +12414,12 @@
         <v>0.4831</v>
       </c>
       <c r="V157" s="1" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="W157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="W157" s="1" t="n">
+      <c r="X157" s="1" t="n">
         <v>0.4823</v>
       </c>
     </row>
@@ -12016,9 +12490,12 @@
         <v>0.4495</v>
       </c>
       <c r="V158" s="1" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="W158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="W158" s="1" t="n">
+      <c r="X158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -12089,9 +12566,12 @@
         <v>0.007431</v>
       </c>
       <c r="V159" s="1" t="n">
+        <v>0.007426</v>
+      </c>
+      <c r="W159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="W159" s="1" t="n">
+      <c r="X159" s="1" t="n">
         <v>0.007417</v>
       </c>
     </row>
@@ -12162,9 +12642,12 @@
         <v>0.004652</v>
       </c>
       <c r="V160" s="1" t="n">
+        <v>0.004649</v>
+      </c>
+      <c r="W160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="W160" s="1" t="n">
+      <c r="X160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -12235,9 +12718,12 @@
         <v>0.004287</v>
       </c>
       <c r="V161" s="1" t="n">
+        <v>0.004295</v>
+      </c>
+      <c r="W161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="W161" s="1" t="n">
+      <c r="X161" s="1" t="n">
         <v>0.004276</v>
       </c>
     </row>
@@ -12308,10 +12794,13 @@
         <v>0.0953</v>
       </c>
       <c r="V162" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="W162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="W162" s="1" t="n">
-        <v>0.0953</v>
+      <c r="X162" s="1" t="n">
+        <v>0.0951</v>
       </c>
     </row>
     <row r="163">
@@ -12381,9 +12870,12 @@
         <v>0.2844</v>
       </c>
       <c r="V163" s="1" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="W163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="W163" s="1" t="n">
+      <c r="X163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -12454,10 +12946,13 @@
         <v>0.1135</v>
       </c>
       <c r="V164" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="W164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="W164" s="1" t="n">
-        <v>0.1135</v>
+      <c r="X164" s="1" t="n">
+        <v>0.1131</v>
       </c>
     </row>
     <row r="165">
@@ -12527,10 +13022,13 @@
         <v>0.175</v>
       </c>
       <c r="V165" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="W165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="W165" s="1" t="n">
-        <v>0.1748</v>
+      <c r="X165" s="1" t="n">
+        <v>0.1747</v>
       </c>
     </row>
     <row r="166">
@@ -12600,9 +13098,12 @@
         <v>0.01007</v>
       </c>
       <c r="V166" s="1" t="n">
-        <v>0.0102</v>
+        <v>0.01055</v>
       </c>
       <c r="W166" s="1" t="n">
+        <v>0.01055</v>
+      </c>
+      <c r="X166" s="1" t="n">
         <v>0.01004</v>
       </c>
     </row>
@@ -12673,10 +13174,13 @@
         <v>1.816</v>
       </c>
       <c r="V167" s="1" t="n">
+        <v>1.813</v>
+      </c>
+      <c r="W167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="W167" s="1" t="n">
-        <v>1.814</v>
+      <c r="X167" s="1" t="n">
+        <v>1.813</v>
       </c>
     </row>
     <row r="168">
@@ -12746,9 +13250,12 @@
         <v>1.34</v>
       </c>
       <c r="V168" s="1" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="W168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="W168" s="1" t="n">
+      <c r="X168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -12819,10 +13326,13 @@
         <v>0.007299</v>
       </c>
       <c r="V169" s="1" t="n">
+        <v>0.007276</v>
+      </c>
+      <c r="W169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="W169" s="1" t="n">
-        <v>0.007284</v>
+      <c r="X169" s="1" t="n">
+        <v>0.007276</v>
       </c>
     </row>
     <row r="170">
@@ -12892,9 +13402,12 @@
         <v>0.0115</v>
       </c>
       <c r="V170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="W170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="W170" s="1" t="n">
+      <c r="X170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -12965,10 +13478,13 @@
         <v>0.005778</v>
       </c>
       <c r="V171" s="1" t="n">
+        <v>0.005751</v>
+      </c>
+      <c r="W171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="W171" s="1" t="n">
-        <v>0.00576</v>
+      <c r="X171" s="1" t="n">
+        <v>0.005751</v>
       </c>
     </row>
     <row r="172">
@@ -13038,9 +13554,12 @@
         <v>0.14879</v>
       </c>
       <c r="V172" s="1" t="n">
+        <v>0.14863</v>
+      </c>
+      <c r="W172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="W172" s="1" t="n">
+      <c r="X172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -13111,10 +13630,13 @@
         <v>4.886</v>
       </c>
       <c r="V173" s="1" t="n">
+        <v>4.868</v>
+      </c>
+      <c r="W173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="W173" s="1" t="n">
-        <v>4.871</v>
+      <c r="X173" s="1" t="n">
+        <v>4.868</v>
       </c>
     </row>
     <row r="174">
@@ -13184,10 +13706,13 @@
         <v>0.07788</v>
       </c>
       <c r="V174" s="1" t="n">
+        <v>0.07785</v>
+      </c>
+      <c r="W174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="W174" s="1" t="n">
-        <v>0.07788</v>
+      <c r="X174" s="1" t="n">
+        <v>0.07785</v>
       </c>
     </row>
     <row r="175">
@@ -13257,9 +13782,12 @@
         <v>0.007413</v>
       </c>
       <c r="V175" s="1" t="n">
+        <v>0.007404</v>
+      </c>
+      <c r="W175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="W175" s="1" t="n">
+      <c r="X175" s="1" t="n">
         <v>0.007403</v>
       </c>
     </row>
@@ -13330,10 +13858,13 @@
         <v>0.1986</v>
       </c>
       <c r="V176" s="1" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="W176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="W176" s="1" t="n">
-        <v>0.1985</v>
+      <c r="X176" s="1" t="n">
+        <v>0.1983</v>
       </c>
     </row>
     <row r="177">
@@ -13403,9 +13934,12 @@
         <v>0.05197</v>
       </c>
       <c r="V177" s="1" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="W177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="W177" s="1" t="n">
+      <c r="X177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -13476,10 +14010,13 @@
         <v>0.05455</v>
       </c>
       <c r="V178" s="1" t="n">
+        <v>0.05444</v>
+      </c>
+      <c r="W178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="W178" s="1" t="n">
-        <v>0.05447</v>
+      <c r="X178" s="1" t="n">
+        <v>0.05444</v>
       </c>
     </row>
     <row r="179">
@@ -13549,9 +14086,12 @@
         <v>0.02349</v>
       </c>
       <c r="V179" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="W179" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="W179" s="1" t="n">
+      <c r="X179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -13622,9 +14162,12 @@
         <v>0.6991000000000001</v>
       </c>
       <c r="V180" s="1" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6994</v>
       </c>
       <c r="W180" s="1" t="n">
+        <v>0.6994</v>
+      </c>
+      <c r="X180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -13695,9 +14238,12 @@
         <v>0.0003724</v>
       </c>
       <c r="V181" s="1" t="n">
+        <v>0.0003732</v>
+      </c>
+      <c r="W181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="W181" s="1" t="n">
+      <c r="X181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -13768,9 +14314,12 @@
         <v>0.01272</v>
       </c>
       <c r="V182" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="W182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="W182" s="1" t="n">
+      <c r="X182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -13841,9 +14390,12 @@
         <v>4.222</v>
       </c>
       <c r="V183" s="1" t="n">
+        <v>4.217</v>
+      </c>
+      <c r="W183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="W183" s="1" t="n">
+      <c r="X183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -13914,9 +14466,12 @@
         <v>0.2344</v>
       </c>
       <c r="V184" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="W184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="W184" s="1" t="n">
+      <c r="X184" s="1" t="n">
         <v>0.2335</v>
       </c>
     </row>
@@ -13987,9 +14542,12 @@
         <v>0.03713</v>
       </c>
       <c r="V185" s="1" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="W185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="W185" s="1" t="n">
+      <c r="X185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -14060,9 +14618,12 @@
         <v>0.11535</v>
       </c>
       <c r="V186" s="1" t="n">
+        <v>0.11568</v>
+      </c>
+      <c r="W186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="W186" s="1" t="n">
+      <c r="X186" s="1" t="n">
         <v>0.11535</v>
       </c>
     </row>
@@ -14133,9 +14694,12 @@
         <v>0.009145</v>
       </c>
       <c r="V187" s="1" t="n">
+        <v>0.009133</v>
+      </c>
+      <c r="W187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="W187" s="1" t="n">
+      <c r="X187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -14206,9 +14770,12 @@
         <v>0.097</v>
       </c>
       <c r="V188" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="W188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="W188" s="1" t="n">
+      <c r="X188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -14279,10 +14846,13 @@
         <v>0.02708</v>
       </c>
       <c r="V189" s="1" t="n">
+        <v>0.02702</v>
+      </c>
+      <c r="W189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="W189" s="1" t="n">
-        <v>0.02708</v>
+      <c r="X189" s="1" t="n">
+        <v>0.02702</v>
       </c>
     </row>
     <row r="190">
@@ -14352,9 +14922,12 @@
         <v>0.008670000000000001</v>
       </c>
       <c r="V190" s="1" t="n">
+        <v>0.008710000000000001</v>
+      </c>
+      <c r="W190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="W190" s="1" t="n">
+      <c r="X190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -14425,9 +14998,12 @@
         <v>0.001957</v>
       </c>
       <c r="V191" s="1" t="n">
+        <v>0.001957</v>
+      </c>
+      <c r="W191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="W191" s="1" t="n">
+      <c r="X191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -14498,9 +15074,12 @@
         <v>0.0998</v>
       </c>
       <c r="V192" s="1" t="n">
-        <v>0.1009</v>
+        <v>0.1019</v>
       </c>
       <c r="W192" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="X192" s="1" t="n">
         <v>0.09959999999999999</v>
       </c>
     </row>
@@ -14571,9 +15150,12 @@
         <v>0.02334</v>
       </c>
       <c r="V193" s="1" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="W193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="W193" s="1" t="n">
+      <c r="X193" s="1" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -14644,10 +15226,13 @@
         <v>0.01342</v>
       </c>
       <c r="V194" s="1" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="W194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="W194" s="1" t="n">
-        <v>0.01341</v>
+      <c r="X194" s="1" t="n">
+        <v>0.0134</v>
       </c>
     </row>
     <row r="195">
@@ -14717,10 +15302,13 @@
         <v>0.02073</v>
       </c>
       <c r="V195" s="1" t="n">
+        <v>0.02071</v>
+      </c>
+      <c r="W195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="W195" s="1" t="n">
-        <v>0.02073</v>
+      <c r="X195" s="1" t="n">
+        <v>0.02071</v>
       </c>
     </row>
     <row r="196">
@@ -14790,9 +15378,12 @@
         <v>0.17767</v>
       </c>
       <c r="V196" s="1" t="n">
+        <v>0.17655</v>
+      </c>
+      <c r="W196" s="1" t="n">
         <v>0.17767</v>
       </c>
-      <c r="W196" s="1" t="n">
+      <c r="X196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -14863,9 +15454,12 @@
         <v>0.007352</v>
       </c>
       <c r="V197" s="1" t="n">
+        <v>0.007365</v>
+      </c>
+      <c r="W197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="W197" s="1" t="n">
+      <c r="X197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -14936,10 +15530,13 @@
         <v>0.01905</v>
       </c>
       <c r="V198" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="W198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="W198" s="1" t="n">
-        <v>0.019</v>
+      <c r="X198" s="1" t="n">
+        <v>0.01896</v>
       </c>
     </row>
     <row r="199">
@@ -15009,9 +15606,12 @@
         <v>0.0163</v>
       </c>
       <c r="V199" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="W199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="W199" s="1" t="n">
+      <c r="X199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -15082,9 +15682,12 @@
         <v>0.2976</v>
       </c>
       <c r="V200" s="1" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="W200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="W200" s="1" t="n">
+      <c r="X200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -15155,9 +15758,12 @@
         <v>0.006204</v>
       </c>
       <c r="V201" s="1" t="n">
+        <v>0.006204</v>
+      </c>
+      <c r="W201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="W201" s="1" t="n">
+      <c r="X201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -15228,10 +15834,13 @@
         <v>0.0004389</v>
       </c>
       <c r="V202" s="1" t="n">
+        <v>0.0004378</v>
+      </c>
+      <c r="W202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="W202" s="1" t="n">
-        <v>0.0004386</v>
+      <c r="X202" s="1" t="n">
+        <v>0.0004378</v>
       </c>
     </row>
     <row r="203">
@@ -15301,9 +15910,12 @@
         <v>0.007282</v>
       </c>
       <c r="V203" s="1" t="n">
+        <v>0.007252</v>
+      </c>
+      <c r="W203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="W203" s="1" t="n">
+      <c r="X203" s="1" t="n">
         <v>0.007245</v>
       </c>
     </row>
@@ -15374,9 +15986,12 @@
         <v>0.1304</v>
       </c>
       <c r="V204" s="1" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="W204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="W204" s="1" t="n">
+      <c r="X204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -15447,9 +16062,12 @@
         <v>0.01414</v>
       </c>
       <c r="V205" s="1" t="n">
+        <v>0.01416</v>
+      </c>
+      <c r="W205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="W205" s="1" t="n">
+      <c r="X205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -15520,10 +16138,13 @@
         <v>0.003578</v>
       </c>
       <c r="V206" s="1" t="n">
+        <v>0.00356</v>
+      </c>
+      <c r="W206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="W206" s="1" t="n">
-        <v>0.003565</v>
+      <c r="X206" s="1" t="n">
+        <v>0.00356</v>
       </c>
     </row>
     <row r="207">
@@ -15593,10 +16214,13 @@
         <v>0.05923</v>
       </c>
       <c r="V207" s="1" t="n">
+        <v>0.05883</v>
+      </c>
+      <c r="W207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="W207" s="1" t="n">
-        <v>0.05914</v>
+      <c r="X207" s="1" t="n">
+        <v>0.05883</v>
       </c>
     </row>
     <row r="208">
@@ -15666,9 +16290,12 @@
         <v>15.49</v>
       </c>
       <c r="V208" s="1" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="W208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="W208" s="1" t="n">
+      <c r="X208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -15739,9 +16366,12 @@
         <v>5188.1</v>
       </c>
       <c r="V209" s="1" t="n">
+        <v>5183.8</v>
+      </c>
+      <c r="W209" s="1" t="n">
         <v>5194.4</v>
       </c>
-      <c r="W209" s="1" t="n">
+      <c r="X209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -15812,9 +16442,12 @@
         <v>0.11974</v>
       </c>
       <c r="V210" s="1" t="n">
+        <v>0.11992</v>
+      </c>
+      <c r="W210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="W210" s="1" t="n">
+      <c r="X210" s="1" t="n">
         <v>0.11941</v>
       </c>
     </row>
@@ -15885,9 +16518,12 @@
         <v>0.1814</v>
       </c>
       <c r="V211" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="W211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="W211" s="1" t="n">
+      <c r="X211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -15958,10 +16594,13 @@
         <v>0.0301</v>
       </c>
       <c r="V212" s="1" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="W212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="W212" s="1" t="n">
-        <v>0.0298</v>
+      <c r="X212" s="1" t="n">
+        <v>0.0297</v>
       </c>
     </row>
     <row r="213">
@@ -16031,9 +16670,12 @@
         <v>1.3997</v>
       </c>
       <c r="V213" s="1" t="n">
+        <v>1.3982</v>
+      </c>
+      <c r="W213" s="1" t="n">
         <v>1.3997</v>
       </c>
-      <c r="W213" s="1" t="n">
+      <c r="X213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -16104,9 +16746,12 @@
         <v>0.05649</v>
       </c>
       <c r="V214" s="1" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="W214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="W214" s="1" t="n">
+      <c r="X214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -16177,9 +16822,12 @@
         <v>0.04391</v>
       </c>
       <c r="V215" s="1" t="n">
+        <v>0.04389</v>
+      </c>
+      <c r="W215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="W215" s="1" t="n">
+      <c r="X215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -16250,9 +16898,12 @@
         <v>0.15088</v>
       </c>
       <c r="V216" s="1" t="n">
+        <v>0.15103</v>
+      </c>
+      <c r="W216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="W216" s="1" t="n">
+      <c r="X216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -16326,6 +16977,9 @@
         <v>0.074</v>
       </c>
       <c r="W217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="X217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -16396,9 +17050,12 @@
         <v>0.00266</v>
       </c>
       <c r="V218" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="W218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="W218" s="1" t="n">
+      <c r="X218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -16469,10 +17126,13 @@
         <v>0.01699</v>
       </c>
       <c r="V219" s="1" t="n">
+        <v>0.01693</v>
+      </c>
+      <c r="W219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="W219" s="1" t="n">
-        <v>0.01696</v>
+      <c r="X219" s="1" t="n">
+        <v>0.01693</v>
       </c>
     </row>
     <row r="220">
@@ -16542,9 +17202,12 @@
         <v>0.0552</v>
       </c>
       <c r="V220" s="1" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="W220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="W220" s="1" t="n">
+      <c r="X220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -16615,9 +17278,12 @@
         <v>0.02184</v>
       </c>
       <c r="V221" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="W221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="W221" s="1" t="n">
+      <c r="X221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -16688,9 +17354,12 @@
         <v>0.009259999999999999</v>
       </c>
       <c r="V222" s="1" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="W222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="W222" s="1" t="n">
+      <c r="X222" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -16761,9 +17430,12 @@
         <v>0.0164</v>
       </c>
       <c r="V223" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="W223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="W223" s="1" t="n">
+      <c r="X223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -16834,9 +17506,12 @@
         <v>0.03825</v>
       </c>
       <c r="V224" s="1" t="n">
+        <v>0.03811</v>
+      </c>
+      <c r="W224" s="1" t="n">
         <v>0.03846</v>
       </c>
-      <c r="W224" s="1" t="n">
+      <c r="X224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -16907,9 +17582,12 @@
         <v>0.001517</v>
       </c>
       <c r="V225" s="1" t="n">
+        <v>0.001515</v>
+      </c>
+      <c r="W225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="W225" s="1" t="n">
+      <c r="X225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -16980,9 +17658,12 @@
         <v>27.22</v>
       </c>
       <c r="V226" s="1" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="W226" s="1" t="n">
         <v>27.31</v>
       </c>
-      <c r="W226" s="1" t="n">
+      <c r="X226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -17053,9 +17734,12 @@
         <v>0.07027</v>
       </c>
       <c r="V227" s="1" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="W227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="W227" s="1" t="n">
+      <c r="X227" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -17126,9 +17810,12 @@
         <v>0.3121</v>
       </c>
       <c r="V228" s="1" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="W228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="W228" s="1" t="n">
+      <c r="X228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -17199,9 +17886,12 @@
         <v>18.39</v>
       </c>
       <c r="V229" s="1" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="W229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="W229" s="1" t="n">
+      <c r="X229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -17272,9 +17962,12 @@
         <v>0.0192</v>
       </c>
       <c r="V230" s="1" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="W230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="W230" s="1" t="n">
+      <c r="X230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -17345,10 +18038,13 @@
         <v>0.01216</v>
       </c>
       <c r="V231" s="1" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="W231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="W231" s="1" t="n">
-        <v>0.01214</v>
+      <c r="X231" s="1" t="n">
+        <v>0.01212</v>
       </c>
     </row>
     <row r="232">
@@ -17418,9 +18114,12 @@
         <v>0.2276</v>
       </c>
       <c r="V232" s="1" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="W232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="W232" s="1" t="n">
+      <c r="X232" s="1" t="n">
         <v>0.2269</v>
       </c>
     </row>
@@ -17491,9 +18190,12 @@
         <v>0.07086000000000001</v>
       </c>
       <c r="V233" s="1" t="n">
+        <v>0.07077</v>
+      </c>
+      <c r="W233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="W233" s="1" t="n">
+      <c r="X233" s="1" t="n">
         <v>0.07073</v>
       </c>
     </row>
@@ -17564,9 +18266,12 @@
         <v>0.1707</v>
       </c>
       <c r="V234" s="1" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="W234" s="1" t="n">
         <v>0.1709</v>
       </c>
-      <c r="W234" s="1" t="n">
+      <c r="X234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -17637,9 +18342,12 @@
         <v>0.025</v>
       </c>
       <c r="V235" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="W235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="W235" s="1" t="n">
+      <c r="X235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -17710,9 +18418,12 @@
         <v>0.03001</v>
       </c>
       <c r="V236" s="1" t="n">
+        <v>0.03003</v>
+      </c>
+      <c r="W236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="W236" s="1" t="n">
+      <c r="X236" s="1" t="n">
         <v>0.02993</v>
       </c>
     </row>
@@ -17783,9 +18494,12 @@
         <v>2.049</v>
       </c>
       <c r="V237" s="1" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="W237" s="1" t="n">
         <v>2.049</v>
       </c>
-      <c r="W237" s="1" t="n">
+      <c r="X237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -17856,10 +18570,13 @@
         <v>0.4187</v>
       </c>
       <c r="V238" s="1" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="W238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="W238" s="1" t="n">
-        <v>0.4187</v>
+      <c r="X238" s="1" t="n">
+        <v>0.4172</v>
       </c>
     </row>
     <row r="239">
@@ -17929,10 +18646,13 @@
         <v>0.03323</v>
       </c>
       <c r="V239" s="1" t="n">
+        <v>0.03303</v>
+      </c>
+      <c r="W239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="W239" s="1" t="n">
-        <v>0.03308</v>
+      <c r="X239" s="1" t="n">
+        <v>0.03303</v>
       </c>
     </row>
     <row r="240">
@@ -18002,9 +18722,12 @@
         <v>0.03385</v>
       </c>
       <c r="V240" s="1" t="n">
+        <v>0.03384</v>
+      </c>
+      <c r="W240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="W240" s="1" t="n">
+      <c r="X240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -18075,9 +18798,12 @@
         <v>0.0007464</v>
       </c>
       <c r="V241" s="1" t="n">
+        <v>0.0007466</v>
+      </c>
+      <c r="W241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="W241" s="1" t="n">
+      <c r="X241" s="1" t="n">
         <v>0.0007463</v>
       </c>
     </row>
@@ -18148,10 +18874,13 @@
         <v>0.1825</v>
       </c>
       <c r="V242" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="W242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="W242" s="1" t="n">
-        <v>0.1822</v>
+      <c r="X242" s="1" t="n">
+        <v>0.1816</v>
       </c>
     </row>
     <row r="243">
@@ -18221,9 +18950,12 @@
         <v>0.014718</v>
       </c>
       <c r="V243" s="1" t="n">
+        <v>0.014715</v>
+      </c>
+      <c r="W243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="W243" s="1" t="n">
+      <c r="X243" s="1" t="n">
         <v>0.014706</v>
       </c>
     </row>
@@ -18294,9 +19026,12 @@
         <v>3.01e-05</v>
       </c>
       <c r="V244" s="1" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="W244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="W244" s="1" t="n">
+      <c r="X244" s="1" t="n">
         <v>2.99e-05</v>
       </c>
     </row>
@@ -18367,9 +19102,12 @@
         <v>0.03526</v>
       </c>
       <c r="V245" s="1" t="n">
+        <v>0.03509</v>
+      </c>
+      <c r="W245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="W245" s="1" t="n">
+      <c r="X245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -18440,9 +19178,12 @@
         <v>0.08032</v>
       </c>
       <c r="V246" s="1" t="n">
+        <v>0.08019</v>
+      </c>
+      <c r="W246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="W246" s="1" t="n">
+      <c r="X246" s="1" t="n">
         <v>0.08018</v>
       </c>
     </row>
@@ -18513,10 +19254,13 @@
         <v>0.007131</v>
       </c>
       <c r="V247" s="1" t="n">
+        <v>0.00709</v>
+      </c>
+      <c r="W247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="W247" s="1" t="n">
-        <v>0.007129</v>
+      <c r="X247" s="1" t="n">
+        <v>0.00709</v>
       </c>
     </row>
     <row r="248">
@@ -18586,9 +19330,12 @@
         <v>0.09275</v>
       </c>
       <c r="V248" s="1" t="n">
+        <v>0.09371</v>
+      </c>
+      <c r="W248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="W248" s="1" t="n">
+      <c r="X248" s="1" t="n">
         <v>0.09239</v>
       </c>
     </row>
@@ -18659,9 +19406,12 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="V249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="W249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="W249" s="1" t="n">
+      <c r="X249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -18732,9 +19482,12 @@
         <v>0.03482</v>
       </c>
       <c r="V250" s="1" t="n">
+        <v>0.03474</v>
+      </c>
+      <c r="W250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="W250" s="1" t="n">
+      <c r="X250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -18805,10 +19558,13 @@
         <v>0.0388</v>
       </c>
       <c r="V251" s="1" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="W251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="W251" s="1" t="n">
-        <v>0.0388</v>
+      <c r="X251" s="1" t="n">
+        <v>0.03875</v>
       </c>
     </row>
     <row r="252">
@@ -18878,9 +19634,12 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="V252" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="W252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="W252" s="1" t="n">
+      <c r="X252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -18951,9 +19710,12 @@
         <v>4.071</v>
       </c>
       <c r="V253" s="1" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="W253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="W253" s="1" t="n">
+      <c r="X253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -19024,10 +19786,13 @@
         <v>0.1867</v>
       </c>
       <c r="V254" s="1" t="n">
+        <v>0.1865</v>
+      </c>
+      <c r="W254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="W254" s="1" t="n">
-        <v>0.1866</v>
+      <c r="X254" s="1" t="n">
+        <v>0.1865</v>
       </c>
     </row>
     <row r="255">
@@ -19097,9 +19862,12 @@
         <v>0.07183</v>
       </c>
       <c r="V255" s="1" t="n">
+        <v>0.07192999999999999</v>
+      </c>
+      <c r="W255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="W255" s="1" t="n">
+      <c r="X255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -19170,9 +19938,12 @@
         <v>0.01848</v>
       </c>
       <c r="V256" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="W256" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="W256" s="1" t="n">
+      <c r="X256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -19243,9 +20014,12 @@
         <v>5.949</v>
       </c>
       <c r="V257" s="1" t="n">
+        <v>5.938</v>
+      </c>
+      <c r="W257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="W257" s="1" t="n">
+      <c r="X257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -19316,10 +20090,13 @@
         <v>0.2596</v>
       </c>
       <c r="V258" s="1" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="W258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="W258" s="1" t="n">
-        <v>0.2596</v>
+      <c r="X258" s="1" t="n">
+        <v>0.2582</v>
       </c>
     </row>
     <row r="259">
@@ -19389,9 +20166,12 @@
         <v>0.1357</v>
       </c>
       <c r="V259" s="1" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="W259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="W259" s="1" t="n">
+      <c r="X259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -19462,9 +20242,12 @@
         <v>0.30623</v>
       </c>
       <c r="V260" s="1" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="W260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="W260" s="1" t="n">
+      <c r="X260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -19535,9 +20318,12 @@
         <v>0.09859</v>
       </c>
       <c r="V261" s="1" t="n">
+        <v>0.09872</v>
+      </c>
+      <c r="W261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="W261" s="1" t="n">
+      <c r="X261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -19608,9 +20394,12 @@
         <v>0.5395</v>
       </c>
       <c r="V262" s="1" t="n">
+        <v>0.5403</v>
+      </c>
+      <c r="W262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="W262" s="1" t="n">
+      <c r="X262" s="1" t="n">
         <v>0.5377999999999999</v>
       </c>
     </row>
@@ -19681,9 +20470,12 @@
         <v>0.2893</v>
       </c>
       <c r="V263" s="1" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="W263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="W263" s="1" t="n">
+      <c r="X263" s="1" t="n">
         <v>0.2877</v>
       </c>
     </row>
@@ -19754,9 +20546,12 @@
         <v>0.974</v>
       </c>
       <c r="V264" s="1" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="W264" s="1" t="n">
         <v>0.989</v>
       </c>
-      <c r="W264" s="1" t="n">
+      <c r="X264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -19827,10 +20622,13 @@
         <v>0.5364</v>
       </c>
       <c r="V265" s="1" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="W265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="W265" s="1" t="n">
-        <v>0.5364</v>
+      <c r="X265" s="1" t="n">
+        <v>0.5339</v>
       </c>
     </row>
     <row r="266">
@@ -19900,9 +20698,12 @@
         <v>0.07339</v>
       </c>
       <c r="V266" s="1" t="n">
+        <v>0.07359</v>
+      </c>
+      <c r="W266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="W266" s="1" t="n">
+      <c r="X266" s="1" t="n">
         <v>0.07339</v>
       </c>
     </row>
@@ -19973,10 +20774,13 @@
         <v>0.02129</v>
       </c>
       <c r="V267" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="W267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="W267" s="1" t="n">
-        <v>0.02127</v>
+      <c r="X267" s="1" t="n">
+        <v>0.02126</v>
       </c>
     </row>
     <row r="268">
@@ -20046,9 +20850,12 @@
         <v>0.01606</v>
       </c>
       <c r="V268" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="W268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="W268" s="1" t="n">
+      <c r="X268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -20119,9 +20926,12 @@
         <v>0.003787</v>
       </c>
       <c r="V269" s="1" t="n">
+        <v>0.003796</v>
+      </c>
+      <c r="W269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="W269" s="1" t="n">
+      <c r="X269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -20192,9 +21002,12 @@
         <v>0.0076</v>
       </c>
       <c r="V270" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="W270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="W270" s="1" t="n">
+      <c r="X270" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -20265,9 +21078,12 @@
         <v>0.05479</v>
       </c>
       <c r="V271" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="W271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="W271" s="1" t="n">
+      <c r="X271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -20338,9 +21154,12 @@
         <v>2.28</v>
       </c>
       <c r="V272" s="1" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="W272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="W272" s="1" t="n">
+      <c r="X272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -20411,9 +21230,12 @@
         <v>0.05476</v>
       </c>
       <c r="V273" s="1" t="n">
+        <v>0.05448</v>
+      </c>
+      <c r="W273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="W273" s="1" t="n">
+      <c r="X273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -20484,9 +21306,12 @@
         <v>0.02329</v>
       </c>
       <c r="V274" s="1" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="W274" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="W274" s="1" t="n">
+      <c r="X274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -20557,9 +21382,12 @@
         <v>1.177</v>
       </c>
       <c r="V275" s="1" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="W275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="W275" s="1" t="n">
+      <c r="X275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -20630,9 +21458,12 @@
         <v>0.2714</v>
       </c>
       <c r="V276" s="1" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="W276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="W276" s="1" t="n">
+      <c r="X276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -20703,9 +21534,12 @@
         <v>0.924</v>
       </c>
       <c r="V277" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="W277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="W277" s="1" t="n">
+      <c r="X277" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -20776,9 +21610,12 @@
         <v>0.6263</v>
       </c>
       <c r="V278" s="1" t="n">
+        <v>0.6262</v>
+      </c>
+      <c r="W278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="W278" s="1" t="n">
+      <c r="X278" s="1" t="n">
         <v>0.6218</v>
       </c>
     </row>
@@ -20849,10 +21686,13 @@
         <v>0.001328</v>
       </c>
       <c r="V279" s="1" t="n">
+        <v>0.001325</v>
+      </c>
+      <c r="W279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="W279" s="1" t="n">
-        <v>0.001326</v>
+      <c r="X279" s="1" t="n">
+        <v>0.001325</v>
       </c>
     </row>
     <row r="280">
@@ -20922,9 +21762,12 @@
         <v>0.005597</v>
       </c>
       <c r="V280" s="1" t="n">
+        <v>0.005588</v>
+      </c>
+      <c r="W280" s="1" t="n">
         <v>0.005613</v>
       </c>
-      <c r="W280" s="1" t="n">
+      <c r="X280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -20995,9 +21838,12 @@
         <v>1.522</v>
       </c>
       <c r="V281" s="1" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="W281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="W281" s="1" t="n">
+      <c r="X281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -21068,10 +21914,13 @@
         <v>28.27</v>
       </c>
       <c r="V282" s="1" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="W282" s="1" t="n">
-        <v>28.25</v>
+      <c r="X282" s="1" t="n">
+        <v>28.2</v>
       </c>
     </row>
     <row r="283">
@@ -21141,9 +21990,12 @@
         <v>0.12888</v>
       </c>
       <c r="V283" s="1" t="n">
+        <v>0.12893</v>
+      </c>
+      <c r="W283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="W283" s="1" t="n">
+      <c r="X283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -21214,10 +22066,13 @@
         <v>0.01103</v>
       </c>
       <c r="V284" s="1" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="W284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="W284" s="1" t="n">
-        <v>0.01102</v>
+      <c r="X284" s="1" t="n">
+        <v>0.01101</v>
       </c>
     </row>
     <row r="285">
@@ -21287,9 +22142,12 @@
         <v>6.548</v>
       </c>
       <c r="V285" s="1" t="n">
+        <v>6.553</v>
+      </c>
+      <c r="W285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="W285" s="1" t="n">
+      <c r="X285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -21360,10 +22218,13 @@
         <v>0.01833</v>
       </c>
       <c r="V286" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="W286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="W286" s="1" t="n">
-        <v>0.01831</v>
+      <c r="X286" s="1" t="n">
+        <v>0.0183</v>
       </c>
     </row>
     <row r="287">
@@ -21433,9 +22294,12 @@
         <v>0.008362</v>
       </c>
       <c r="V287" s="1" t="n">
+        <v>0.008363000000000001</v>
+      </c>
+      <c r="W287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="W287" s="1" t="n">
+      <c r="X287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -21506,10 +22370,13 @@
         <v>0.3774</v>
       </c>
       <c r="V288" s="1" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="W288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="W288" s="1" t="n">
-        <v>0.3774</v>
+      <c r="X288" s="1" t="n">
+        <v>0.3743</v>
       </c>
     </row>
     <row r="289">
@@ -21579,9 +22446,12 @@
         <v>0.009789000000000001</v>
       </c>
       <c r="V289" s="1" t="n">
+        <v>0.009773</v>
+      </c>
+      <c r="W289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="W289" s="1" t="n">
+      <c r="X289" s="1" t="n">
         <v>0.00974</v>
       </c>
     </row>
@@ -21652,9 +22522,12 @@
         <v>0.02592</v>
       </c>
       <c r="V290" s="1" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="W290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="W290" s="1" t="n">
+      <c r="X290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -21725,9 +22598,12 @@
         <v>0.095</v>
       </c>
       <c r="V291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="W291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="W291" s="1" t="n">
+      <c r="X291" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -21798,9 +22674,12 @@
         <v>0.28685</v>
       </c>
       <c r="V292" s="1" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="W292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="W292" s="1" t="n">
+      <c r="X292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -21871,10 +22750,13 @@
         <v>0.01525</v>
       </c>
       <c r="V293" s="1" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="W293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="W293" s="1" t="n">
-        <v>0.01525</v>
+      <c r="X293" s="1" t="n">
+        <v>0.01516</v>
       </c>
     </row>
     <row r="294">
@@ -21944,9 +22826,12 @@
         <v>0.003424</v>
       </c>
       <c r="V294" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="W294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="W294" s="1" t="n">
+      <c r="X294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -22017,9 +22902,12 @@
         <v>0.042602</v>
       </c>
       <c r="V295" s="1" t="n">
+        <v>0.042352</v>
+      </c>
+      <c r="W295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="W295" s="1" t="n">
+      <c r="X295" s="1" t="n">
         <v>0.042232</v>
       </c>
     </row>
@@ -22090,10 +22978,13 @@
         <v>0.02886</v>
       </c>
       <c r="V296" s="1" t="n">
+        <v>0.02844</v>
+      </c>
+      <c r="W296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="W296" s="1" t="n">
-        <v>0.02886</v>
+      <c r="X296" s="1" t="n">
+        <v>0.02844</v>
       </c>
     </row>
     <row r="297">
@@ -22163,9 +23054,12 @@
         <v>0.03797</v>
       </c>
       <c r="V297" s="1" t="n">
+        <v>0.03806</v>
+      </c>
+      <c r="W297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="W297" s="1" t="n">
+      <c r="X297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -22236,9 +23130,12 @@
         <v>0.08283</v>
       </c>
       <c r="V298" s="1" t="n">
+        <v>0.08271000000000001</v>
+      </c>
+      <c r="W298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="W298" s="1" t="n">
+      <c r="X298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -22309,9 +23206,12 @@
         <v>0.0076</v>
       </c>
       <c r="V299" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="W299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="W299" s="1" t="n">
+      <c r="X299" s="1" t="n">
         <v>0.0076</v>
       </c>
     </row>
@@ -22382,10 +23282,13 @@
         <v>0.01496</v>
       </c>
       <c r="V300" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="W300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="W300" s="1" t="n">
-        <v>0.01496</v>
+      <c r="X300" s="1" t="n">
+        <v>0.01489</v>
       </c>
     </row>
     <row r="301">
@@ -22455,9 +23358,12 @@
         <v>0.1405</v>
       </c>
       <c r="V301" s="1" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="W301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="W301" s="1" t="n">
+      <c r="X301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -22528,9 +23434,12 @@
         <v>0.0006228</v>
       </c>
       <c r="V302" s="1" t="n">
+        <v>0.000624</v>
+      </c>
+      <c r="W302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="W302" s="1" t="n">
+      <c r="X302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -22601,9 +23510,12 @@
         <v>0.06254</v>
       </c>
       <c r="V303" s="1" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="W303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="W303" s="1" t="n">
+      <c r="X303" s="1" t="n">
         <v>0.06207</v>
       </c>
     </row>
@@ -22674,10 +23586,13 @@
         <v>0.0001624</v>
       </c>
       <c r="V304" s="1" t="n">
+        <v>0.0001618</v>
+      </c>
+      <c r="W304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="W304" s="1" t="n">
-        <v>0.000162</v>
+      <c r="X304" s="1" t="n">
+        <v>0.0001618</v>
       </c>
     </row>
     <row r="305">
@@ -22747,10 +23662,13 @@
         <v>0.06083</v>
       </c>
       <c r="V305" s="1" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="W305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="W305" s="1" t="n">
-        <v>0.06071</v>
+      <c r="X305" s="1" t="n">
+        <v>0.0606</v>
       </c>
     </row>
     <row r="306">
@@ -22820,9 +23738,12 @@
         <v>0.022335</v>
       </c>
       <c r="V306" s="1" t="n">
+        <v>0.022281</v>
+      </c>
+      <c r="W306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="W306" s="1" t="n">
+      <c r="X306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -22893,9 +23814,12 @@
         <v>0.02308</v>
       </c>
       <c r="V307" s="1" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="W307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="W307" s="1" t="n">
+      <c r="X307" s="1" t="n">
         <v>0.02278</v>
       </c>
     </row>
@@ -22966,9 +23890,12 @@
         <v>0.000409</v>
       </c>
       <c r="V308" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="W308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="W308" s="1" t="n">
+      <c r="X308" s="1" t="n">
         <v>0.000409</v>
       </c>
     </row>
@@ -23039,9 +23966,12 @@
         <v>0.0897</v>
       </c>
       <c r="V309" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="W309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="W309" s="1" t="n">
+      <c r="X309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -23112,9 +24042,12 @@
         <v>0.3712</v>
       </c>
       <c r="V310" s="1" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="W310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="W310" s="1" t="n">
+      <c r="X310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -23185,9 +24118,12 @@
         <v>0.0353</v>
       </c>
       <c r="V311" s="1" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="W311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="W311" s="1" t="n">
+      <c r="X311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -23258,9 +24194,12 @@
         <v>0.02426</v>
       </c>
       <c r="V312" s="1" t="n">
+        <v>0.02433</v>
+      </c>
+      <c r="W312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="W312" s="1" t="n">
+      <c r="X312" s="1" t="n">
         <v>0.02415</v>
       </c>
     </row>
@@ -23331,10 +24270,13 @@
         <v>0.0409</v>
       </c>
       <c r="V313" s="1" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="W313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="W313" s="1" t="n">
-        <v>0.04087</v>
+      <c r="X313" s="1" t="n">
+        <v>0.0408</v>
       </c>
     </row>
     <row r="314">
@@ -23404,9 +24346,12 @@
         <v>3.932</v>
       </c>
       <c r="V314" s="1" t="n">
+        <v>3.932</v>
+      </c>
+      <c r="W314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="W314" s="1" t="n">
+      <c r="X314" s="1" t="n">
         <v>3.932</v>
       </c>
     </row>
@@ -23477,9 +24422,12 @@
         <v>0.1592</v>
       </c>
       <c r="V315" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="W315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="W315" s="1" t="n">
+      <c r="X315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -23550,9 +24498,12 @@
         <v>0.09016</v>
       </c>
       <c r="V316" s="1" t="n">
+        <v>0.08993</v>
+      </c>
+      <c r="W316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="W316" s="1" t="n">
+      <c r="X316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -23623,10 +24574,13 @@
         <v>0.06802999999999999</v>
       </c>
       <c r="V317" s="1" t="n">
+        <v>0.06783</v>
+      </c>
+      <c r="W317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="W317" s="1" t="n">
-        <v>0.06791999999999999</v>
+      <c r="X317" s="1" t="n">
+        <v>0.06783</v>
       </c>
     </row>
     <row r="318">
@@ -23696,9 +24650,12 @@
         <v>0.012477</v>
       </c>
       <c r="V318" s="1" t="n">
+        <v>0.012456</v>
+      </c>
+      <c r="W318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="W318" s="1" t="n">
+      <c r="X318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -23769,10 +24726,13 @@
         <v>0.00113</v>
       </c>
       <c r="V319" s="1" t="n">
+        <v>0.001129</v>
+      </c>
+      <c r="W319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="W319" s="1" t="n">
-        <v>0.00113</v>
+      <c r="X319" s="1" t="n">
+        <v>0.001129</v>
       </c>
     </row>
     <row r="320">
@@ -23842,9 +24802,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="V320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="W320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="W320" s="1" t="n">
+      <c r="X320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -23915,9 +24878,12 @@
         <v>0.00523</v>
       </c>
       <c r="V321" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="W321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="W321" s="1" t="n">
+      <c r="X321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -23988,9 +24954,12 @@
         <v>0.1113</v>
       </c>
       <c r="V322" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="W322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="W322" s="1" t="n">
+      <c r="X322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -24061,9 +25030,12 @@
         <v>0.04341</v>
       </c>
       <c r="V323" s="1" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="W323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="W323" s="1" t="n">
+      <c r="X323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -24134,9 +25106,12 @@
         <v>0.01779</v>
       </c>
       <c r="V324" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="W324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="W324" s="1" t="n">
+      <c r="X324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -24207,10 +25182,13 @@
         <v>0.005646</v>
       </c>
       <c r="V325" s="1" t="n">
+        <v>0.005628</v>
+      </c>
+      <c r="W325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="W325" s="1" t="n">
-        <v>0.005633</v>
+      <c r="X325" s="1" t="n">
+        <v>0.005628</v>
       </c>
     </row>
     <row r="326">
@@ -24280,10 +25258,13 @@
         <v>0.001757</v>
       </c>
       <c r="V326" s="1" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="W326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="W326" s="1" t="n">
-        <v>0.001751</v>
+      <c r="X326" s="1" t="n">
+        <v>0.00175</v>
       </c>
     </row>
     <row r="327">
@@ -24353,9 +25334,12 @@
         <v>0.04022</v>
       </c>
       <c r="V327" s="1" t="n">
+        <v>0.04034</v>
+      </c>
+      <c r="W327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="W327" s="1" t="n">
+      <c r="X327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -24426,9 +25410,12 @@
         <v>0.053606</v>
       </c>
       <c r="V328" s="1" t="n">
+        <v>0.053537</v>
+      </c>
+      <c r="W328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="W328" s="1" t="n">
+      <c r="X328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -24499,10 +25486,13 @@
         <v>0.2771</v>
       </c>
       <c r="V329" s="1" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="W329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="W329" s="1" t="n">
-        <v>0.2771</v>
+      <c r="X329" s="1" t="n">
+        <v>0.2769</v>
       </c>
     </row>
     <row r="330">
@@ -24572,9 +25562,12 @@
         <v>0.1587</v>
       </c>
       <c r="V330" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="W330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="W330" s="1" t="n">
+      <c r="X330" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -24645,9 +25638,12 @@
         <v>0.05369</v>
       </c>
       <c r="V331" s="1" t="n">
+        <v>0.05352</v>
+      </c>
+      <c r="W331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="W331" s="1" t="n">
+      <c r="X331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -24718,9 +25714,12 @@
         <v>0.3612</v>
       </c>
       <c r="V332" s="1" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="W332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="W332" s="1" t="n">
+      <c r="X332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -24791,9 +25790,12 @@
         <v>0.03059</v>
       </c>
       <c r="V333" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="W333" s="1" t="n">
         <v>0.03063</v>
       </c>
-      <c r="W333" s="1" t="n">
+      <c r="X333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -24864,9 +25866,12 @@
         <v>0.01729</v>
       </c>
       <c r="V334" s="1" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="W334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="W334" s="1" t="n">
+      <c r="X334" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -24937,9 +25942,12 @@
         <v>0.0578</v>
       </c>
       <c r="V335" s="1" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="W335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="W335" s="1" t="n">
+      <c r="X335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -25010,10 +26018,13 @@
         <v>0.08994000000000001</v>
       </c>
       <c r="V336" s="1" t="n">
+        <v>0.08910999999999999</v>
+      </c>
+      <c r="W336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="W336" s="1" t="n">
-        <v>0.08994000000000001</v>
+      <c r="X336" s="1" t="n">
+        <v>0.08910999999999999</v>
       </c>
     </row>
     <row r="337">
@@ -25083,9 +26094,12 @@
         <v>0.18025</v>
       </c>
       <c r="V337" s="1" t="n">
+        <v>0.17945</v>
+      </c>
+      <c r="W337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="W337" s="1" t="n">
+      <c r="X337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -25156,9 +26170,12 @@
         <v>0.02079</v>
       </c>
       <c r="V338" s="1" t="n">
+        <v>0.02078</v>
+      </c>
+      <c r="W338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="W338" s="1" t="n">
+      <c r="X338" s="1" t="n">
         <v>0.02074</v>
       </c>
     </row>
@@ -25229,9 +26246,12 @@
         <v>0.1319</v>
       </c>
       <c r="V339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="W339" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="W339" s="1" t="n">
+      <c r="X339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -25302,9 +26322,12 @@
         <v>0.007936</v>
       </c>
       <c r="V340" s="1" t="n">
+        <v>0.007908999999999999</v>
+      </c>
+      <c r="W340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="W340" s="1" t="n">
+      <c r="X340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -25375,9 +26398,12 @@
         <v>4.413</v>
       </c>
       <c r="V341" s="1" t="n">
+        <v>4.404</v>
+      </c>
+      <c r="W341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="W341" s="1" t="n">
+      <c r="X341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -25448,10 +26474,13 @@
         <v>0.18893</v>
       </c>
       <c r="V342" s="1" t="n">
+        <v>0.18732</v>
+      </c>
+      <c r="W342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="W342" s="1" t="n">
-        <v>0.18839</v>
+      <c r="X342" s="1" t="n">
+        <v>0.18732</v>
       </c>
     </row>
     <row r="343">
@@ -25521,9 +26550,12 @@
         <v>0.08312</v>
       </c>
       <c r="V343" s="1" t="n">
+        <v>0.08329</v>
+      </c>
+      <c r="W343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="W343" s="1" t="n">
+      <c r="X343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -25594,9 +26626,12 @@
         <v>0.1829</v>
       </c>
       <c r="V344" s="1" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="W344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="W344" s="1" t="n">
+      <c r="X344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -25667,10 +26702,13 @@
         <v>0.003221</v>
       </c>
       <c r="V345" s="1" t="n">
+        <v>0.003214</v>
+      </c>
+      <c r="W345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="W345" s="1" t="n">
-        <v>0.003221</v>
+      <c r="X345" s="1" t="n">
+        <v>0.003214</v>
       </c>
     </row>
     <row r="346">
@@ -25740,9 +26778,12 @@
         <v>0.09103</v>
       </c>
       <c r="V346" s="1" t="n">
+        <v>0.09093999999999999</v>
+      </c>
+      <c r="W346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="W346" s="1" t="n">
+      <c r="X346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -25813,9 +26854,12 @@
         <v>2.242</v>
       </c>
       <c r="V347" s="1" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="W347" s="1" t="n">
+      <c r="X347" s="1" t="n">
         <v>2.235</v>
       </c>
     </row>
@@ -25886,10 +26930,13 @@
         <v>0.3026</v>
       </c>
       <c r="V348" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="W348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="W348" s="1" t="n">
-        <v>0.3026</v>
+      <c r="X348" s="1" t="n">
+        <v>0.3014</v>
       </c>
     </row>
     <row r="349">
@@ -25959,9 +27006,12 @@
         <v>0.02987</v>
       </c>
       <c r="V349" s="1" t="n">
-        <v>0.02991</v>
+        <v>0.03002</v>
       </c>
       <c r="W349" s="1" t="n">
+        <v>0.03002</v>
+      </c>
+      <c r="X349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -26032,9 +27082,12 @@
         <v>0.1276</v>
       </c>
       <c r="V350" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="W350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="W350" s="1" t="n">
+      <c r="X350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -26105,10 +27158,13 @@
         <v>0.06578000000000001</v>
       </c>
       <c r="V351" s="1" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="W351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="W351" s="1" t="n">
-        <v>0.06578000000000001</v>
+      <c r="X351" s="1" t="n">
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="352">
@@ -26178,10 +27234,13 @@
         <v>0.06218</v>
       </c>
       <c r="V352" s="1" t="n">
+        <v>0.06208</v>
+      </c>
+      <c r="W352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="W352" s="1" t="n">
-        <v>0.06218</v>
+      <c r="X352" s="1" t="n">
+        <v>0.06208</v>
       </c>
     </row>
     <row r="353">
@@ -26251,9 +27310,12 @@
         <v>0.06282</v>
       </c>
       <c r="V353" s="1" t="n">
+        <v>0.06294</v>
+      </c>
+      <c r="W353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="W353" s="1" t="n">
+      <c r="X353" s="1" t="n">
         <v>0.06270000000000001</v>
       </c>
     </row>
@@ -26324,10 +27386,13 @@
         <v>0.10348</v>
       </c>
       <c r="V354" s="1" t="n">
+        <v>0.10311</v>
+      </c>
+      <c r="W354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="W354" s="1" t="n">
-        <v>0.10348</v>
+      <c r="X354" s="1" t="n">
+        <v>0.10311</v>
       </c>
     </row>
     <row r="355">
@@ -26397,10 +27462,13 @@
         <v>0.0898</v>
       </c>
       <c r="V355" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="W355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="W355" s="1" t="n">
-        <v>0.0898</v>
+      <c r="X355" s="1" t="n">
+        <v>0.0897</v>
       </c>
     </row>
     <row r="356">
@@ -26470,9 +27538,12 @@
         <v>0.06947</v>
       </c>
       <c r="V356" s="1" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="W356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="W356" s="1" t="n">
+      <c r="X356" s="1" t="n">
         <v>0.06905</v>
       </c>
     </row>
@@ -26543,9 +27614,12 @@
         <v>0.4511</v>
       </c>
       <c r="V357" s="1" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="W357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="W357" s="1" t="n">
+      <c r="X357" s="1" t="n">
         <v>0.4504</v>
       </c>
     </row>
@@ -26616,9 +27690,12 @@
         <v>0.03458</v>
       </c>
       <c r="V358" s="1" t="n">
+        <v>0.03455</v>
+      </c>
+      <c r="W358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="W358" s="1" t="n">
+      <c r="X358" s="1" t="n">
         <v>0.03441</v>
       </c>
     </row>
@@ -26689,10 +27766,13 @@
         <v>0.01451</v>
       </c>
       <c r="V359" s="1" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="W359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="W359" s="1" t="n">
-        <v>0.01451</v>
+      <c r="X359" s="1" t="n">
+        <v>0.01446</v>
       </c>
     </row>
     <row r="360">
@@ -26762,10 +27842,13 @@
         <v>0.13339</v>
       </c>
       <c r="V360" s="1" t="n">
+        <v>0.13239</v>
+      </c>
+      <c r="W360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="W360" s="1" t="n">
-        <v>0.13282</v>
+      <c r="X360" s="1" t="n">
+        <v>0.13239</v>
       </c>
     </row>
     <row r="361">
@@ -26835,9 +27918,12 @@
         <v>0.0005865</v>
       </c>
       <c r="V361" s="1" t="n">
+        <v>0.0005881</v>
+      </c>
+      <c r="W361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="W361" s="1" t="n">
+      <c r="X361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -26908,9 +27994,12 @@
         <v>0.03838</v>
       </c>
       <c r="V362" s="1" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="W362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="W362" s="1" t="n">
+      <c r="X362" s="1" t="n">
         <v>0.03824</v>
       </c>
     </row>
@@ -26981,9 +28070,12 @@
         <v>3.23</v>
       </c>
       <c r="V363" s="1" t="n">
-        <v>3.234</v>
+        <v>3.244</v>
       </c>
       <c r="W363" s="1" t="n">
+        <v>3.244</v>
+      </c>
+      <c r="X363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -27054,10 +28146,13 @@
         <v>0.1633</v>
       </c>
       <c r="V364" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="W364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="W364" s="1" t="n">
-        <v>0.1632</v>
+      <c r="X364" s="1" t="n">
+        <v>0.1627</v>
       </c>
     </row>
     <row r="365">
@@ -27127,10 +28222,13 @@
         <v>0.1129</v>
       </c>
       <c r="V365" s="1" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="W365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="W365" s="1" t="n">
-        <v>0.1128</v>
+      <c r="X365" s="1" t="n">
+        <v>0.1127</v>
       </c>
     </row>
     <row r="366">
@@ -27200,10 +28298,13 @@
         <v>0.0006353</v>
       </c>
       <c r="V366" s="1" t="n">
+        <v>0.0006339</v>
+      </c>
+      <c r="W366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="W366" s="1" t="n">
-        <v>0.000634</v>
+      <c r="X366" s="1" t="n">
+        <v>0.0006339</v>
       </c>
     </row>
     <row r="367">
@@ -27273,9 +28374,12 @@
         <v>0.05937</v>
       </c>
       <c r="V367" s="1" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="W367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="W367" s="1" t="n">
+      <c r="X367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -27346,9 +28450,12 @@
         <v>0.08112999999999999</v>
       </c>
       <c r="V368" s="1" t="n">
+        <v>0.08114</v>
+      </c>
+      <c r="W368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="W368" s="1" t="n">
+      <c r="X368" s="1" t="n">
         <v>0.08111</v>
       </c>
     </row>
@@ -27419,9 +28526,12 @@
         <v>0.03944</v>
       </c>
       <c r="V369" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="W369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="W369" s="1" t="n">
+      <c r="X369" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -27492,9 +28602,12 @@
         <v>3.706</v>
       </c>
       <c r="V370" s="1" t="n">
-        <v>3.727</v>
+        <v>3.759</v>
       </c>
       <c r="W370" s="1" t="n">
+        <v>3.759</v>
+      </c>
+      <c r="X370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -27565,10 +28678,13 @@
         <v>0.1207</v>
       </c>
       <c r="V371" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="W371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="W371" s="1" t="n">
-        <v>0.1206</v>
+      <c r="X371" s="1" t="n">
+        <v>0.1204</v>
       </c>
     </row>
     <row r="372">
@@ -27638,10 +28754,13 @@
         <v>0.01465</v>
       </c>
       <c r="V372" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="W372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="W372" s="1" t="n">
-        <v>0.01465</v>
+      <c r="X372" s="1" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="373">
@@ -27711,10 +28830,13 @@
         <v>0.02193</v>
       </c>
       <c r="V373" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="W373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="W373" s="1" t="n">
-        <v>0.02191</v>
+      <c r="X373" s="1" t="n">
+        <v>0.02187</v>
       </c>
     </row>
     <row r="374">
@@ -27784,9 +28906,12 @@
         <v>1.8728</v>
       </c>
       <c r="V374" s="1" t="n">
-        <v>1.8728</v>
+        <v>1.875</v>
       </c>
       <c r="W374" s="1" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="X374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -27857,9 +28982,12 @@
         <v>0.02082</v>
       </c>
       <c r="V375" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="W375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="W375" s="1" t="n">
+      <c r="X375" s="1" t="n">
         <v>0.02081</v>
       </c>
     </row>
@@ -27930,9 +29058,12 @@
         <v>1.312</v>
       </c>
       <c r="V376" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="W376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="W376" s="1" t="n">
+      <c r="X376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -28003,9 +29134,12 @@
         <v>0.2826</v>
       </c>
       <c r="V377" s="1" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="W377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="W377" s="1" t="n">
+      <c r="X377" s="1" t="n">
         <v>0.2819</v>
       </c>
     </row>
@@ -28076,9 +29210,12 @@
         <v>0.01557</v>
       </c>
       <c r="V378" s="1" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="W378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="W378" s="1" t="n">
+      <c r="X378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -28149,10 +29286,13 @@
         <v>1.5218</v>
       </c>
       <c r="V379" s="1" t="n">
+        <v>1.5181</v>
+      </c>
+      <c r="W379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="W379" s="1" t="n">
-        <v>1.5218</v>
+      <c r="X379" s="1" t="n">
+        <v>1.5181</v>
       </c>
     </row>
     <row r="380">
@@ -28222,10 +29362,13 @@
         <v>6.872000000000001e-05</v>
       </c>
       <c r="V380" s="1" t="n">
+        <v>6.858e-05</v>
+      </c>
+      <c r="W380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="W380" s="1" t="n">
-        <v>6.871e-05</v>
+      <c r="X380" s="1" t="n">
+        <v>6.858e-05</v>
       </c>
     </row>
     <row r="381">
@@ -28295,9 +29438,12 @@
         <v>2.541</v>
       </c>
       <c r="V381" s="1" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="W381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="W381" s="1" t="n">
+      <c r="X381" s="1" t="n">
         <v>2.536</v>
       </c>
     </row>
@@ -28368,9 +29514,12 @@
         <v>0.06661</v>
       </c>
       <c r="V382" s="1" t="n">
+        <v>0.06658</v>
+      </c>
+      <c r="W382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="W382" s="1" t="n">
+      <c r="X382" s="1" t="n">
         <v>0.06646000000000001</v>
       </c>
     </row>
@@ -28441,9 +29590,12 @@
         <v>0.01686</v>
       </c>
       <c r="V383" s="1" t="n">
+        <v>0.01662</v>
+      </c>
+      <c r="W383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="W383" s="1" t="n">
+      <c r="X383" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -28514,9 +29666,12 @@
         <v>0.05151</v>
       </c>
       <c r="V384" s="1" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="W384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="W384" s="1" t="n">
+      <c r="X384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -28587,9 +29742,12 @@
         <v>7.61</v>
       </c>
       <c r="V385" s="1" t="n">
+        <v>7.607</v>
+      </c>
+      <c r="W385" s="1" t="n">
         <v>7.61</v>
       </c>
-      <c r="W385" s="1" t="n">
+      <c r="X385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -28660,9 +29818,12 @@
         <v>0.003265</v>
       </c>
       <c r="V386" s="1" t="n">
+        <v>0.003262</v>
+      </c>
+      <c r="W386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="W386" s="1" t="n">
+      <c r="X386" s="1" t="n">
         <v>0.003258</v>
       </c>
     </row>
@@ -28733,10 +29894,13 @@
         <v>0.0003792</v>
       </c>
       <c r="V387" s="1" t="n">
+        <v>0.0003788</v>
+      </c>
+      <c r="W387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="W387" s="1" t="n">
-        <v>0.0003792</v>
+      <c r="X387" s="1" t="n">
+        <v>0.0003788</v>
       </c>
     </row>
     <row r="388">
@@ -28806,9 +29970,12 @@
         <v>0.00953</v>
       </c>
       <c r="V388" s="1" t="n">
+        <v>0.009469999999999999</v>
+      </c>
+      <c r="W388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="W388" s="1" t="n">
+      <c r="X388" s="1" t="n">
         <v>0.00942</v>
       </c>
     </row>
@@ -28879,9 +30046,12 @@
         <v>0.2899</v>
       </c>
       <c r="V389" s="1" t="n">
-        <v>0.2904</v>
+        <v>0.2917</v>
       </c>
       <c r="W389" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="X389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -28955,6 +30125,9 @@
         <v>0.0253</v>
       </c>
       <c r="W390" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="X390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -29025,9 +30198,12 @@
         <v>2.844</v>
       </c>
       <c r="V391" s="1" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="W391" s="1" t="n">
         <v>2.859</v>
       </c>
-      <c r="W391" s="1" t="n">
+      <c r="X391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -29098,9 +30274,12 @@
         <v>0.01347</v>
       </c>
       <c r="V392" s="1" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="W392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="W392" s="1" t="n">
+      <c r="X392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -29174,6 +30353,9 @@
         <v>0.00237</v>
       </c>
       <c r="W393" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="X393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -29244,9 +30426,12 @@
         <v>0.05931</v>
       </c>
       <c r="V394" s="1" t="n">
+        <v>0.05927</v>
+      </c>
+      <c r="W394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="W394" s="1" t="n">
+      <c r="X394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -29317,9 +30502,12 @@
         <v>0.04</v>
       </c>
       <c r="V395" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="W395" s="1" t="n">
+      <c r="X395" s="1" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -29390,9 +30578,12 @@
         <v>0.09411</v>
       </c>
       <c r="V396" s="1" t="n">
+        <v>0.09426</v>
+      </c>
+      <c r="W396" s="1" t="n">
         <v>0.09447</v>
       </c>
-      <c r="W396" s="1" t="n">
+      <c r="X396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -29463,9 +30654,12 @@
         <v>0.1511</v>
       </c>
       <c r="V397" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="W397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="W397" s="1" t="n">
+      <c r="X397" s="1" t="n">
         <v>0.1511</v>
       </c>
     </row>
@@ -29536,9 +30730,12 @@
         <v>0.93</v>
       </c>
       <c r="V398" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="W398" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="W398" s="1" t="n">
+      <c r="X398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -29609,10 +30806,13 @@
         <v>0.05225</v>
       </c>
       <c r="V399" s="1" t="n">
+        <v>0.05206</v>
+      </c>
+      <c r="W399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="W399" s="1" t="n">
-        <v>0.05213</v>
+      <c r="X399" s="1" t="n">
+        <v>0.05206</v>
       </c>
     </row>
     <row r="400">
@@ -29682,10 +30882,13 @@
         <v>2.502</v>
       </c>
       <c r="V400" s="1" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="W400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="W400" s="1" t="n">
-        <v>2.502</v>
+      <c r="X400" s="1" t="n">
+        <v>2.497</v>
       </c>
     </row>
     <row r="401">
@@ -29755,9 +30958,12 @@
         <v>0.01768</v>
       </c>
       <c r="V401" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+      <c r="W401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="W401" s="1" t="n">
+      <c r="X401" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -29828,9 +31034,12 @@
         <v>0.07989</v>
       </c>
       <c r="V402" s="1" t="n">
+        <v>0.08041</v>
+      </c>
+      <c r="W402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="W402" s="1" t="n">
+      <c r="X402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -29901,9 +31110,12 @@
         <v>1.2509</v>
       </c>
       <c r="V403" s="1" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="W403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="W403" s="1" t="n">
+      <c r="X403" s="1" t="n">
         <v>1.2451</v>
       </c>
     </row>
@@ -29974,9 +31186,12 @@
         <v>0.00707</v>
       </c>
       <c r="V404" s="1" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="W404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="W404" s="1" t="n">
+      <c r="X404" s="1" t="n">
         <v>0.00707</v>
       </c>
     </row>
@@ -30047,9 +31262,12 @@
         <v>0.5057</v>
       </c>
       <c r="V405" s="1" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="W405" s="1" t="n">
         <v>0.5065</v>
       </c>
-      <c r="W405" s="1" t="n">
+      <c r="X405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -30120,10 +31338,13 @@
         <v>0.01139</v>
       </c>
       <c r="V406" s="1" t="n">
+        <v>0.01138</v>
+      </c>
+      <c r="W406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="W406" s="1" t="n">
-        <v>0.01139</v>
+      <c r="X406" s="1" t="n">
+        <v>0.01138</v>
       </c>
     </row>
     <row r="407">
@@ -30193,10 +31414,13 @@
         <v>0.04588</v>
       </c>
       <c r="V407" s="1" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="W407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="W407" s="1" t="n">
-        <v>0.04583</v>
+      <c r="X407" s="1" t="n">
+        <v>0.0458</v>
       </c>
     </row>
     <row r="408">
@@ -30266,9 +31490,12 @@
         <v>0.03929</v>
       </c>
       <c r="V408" s="1" t="n">
+        <v>0.03925</v>
+      </c>
+      <c r="W408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="W408" s="1" t="n">
+      <c r="X408" s="1" t="n">
         <v>0.03922</v>
       </c>
     </row>
@@ -30339,9 +31566,12 @@
         <v>0.05219</v>
       </c>
       <c r="V409" s="1" t="n">
+        <v>0.05211</v>
+      </c>
+      <c r="W409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="W409" s="1" t="n">
+      <c r="X409" s="1" t="n">
         <v>0.05209</v>
       </c>
     </row>
@@ -30412,9 +31642,12 @@
         <v>0.01218</v>
       </c>
       <c r="V410" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="W410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="W410" s="1" t="n">
+      <c r="X410" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -30485,9 +31718,12 @@
         <v>0.06347</v>
       </c>
       <c r="V411" s="1" t="n">
+        <v>0.06342</v>
+      </c>
+      <c r="W411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="W411" s="1" t="n">
+      <c r="X411" s="1" t="n">
         <v>0.06333</v>
       </c>
     </row>
@@ -30558,9 +31794,12 @@
         <v>0.04127</v>
       </c>
       <c r="V412" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="W412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="W412" s="1" t="n">
+      <c r="X412" s="1" t="n">
         <v>0.04114</v>
       </c>
     </row>
@@ -30631,10 +31870,13 @@
         <v>1.106</v>
       </c>
       <c r="V413" s="1" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="W413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="W413" s="1" t="n">
-        <v>1.106</v>
+      <c r="X413" s="1" t="n">
+        <v>1.101</v>
       </c>
     </row>
     <row r="414">
@@ -30704,9 +31946,12 @@
         <v>0.2622</v>
       </c>
       <c r="V414" s="1" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="W414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="W414" s="1" t="n">
+      <c r="X414" s="1" t="n">
         <v>0.2614</v>
       </c>
     </row>
@@ -30777,9 +32022,12 @@
         <v>0.001219</v>
       </c>
       <c r="V415" s="1" t="n">
+        <v>0.001221</v>
+      </c>
+      <c r="W415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="W415" s="1" t="n">
+      <c r="X415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -30850,9 +32098,12 @@
         <v>0.03187</v>
       </c>
       <c r="V416" s="1" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="W416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="W416" s="1" t="n">
+      <c r="X416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -30923,9 +32174,12 @@
         <v>0.01459</v>
       </c>
       <c r="V417" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="W417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="W417" s="1" t="n">
+      <c r="X417" s="1" t="n">
         <v>0.01451</v>
       </c>
     </row>
@@ -30996,9 +32250,12 @@
         <v>0.148</v>
       </c>
       <c r="V418" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="W418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="W418" s="1" t="n">
+      <c r="X418" s="1" t="n">
         <v>0.1478</v>
       </c>
     </row>
@@ -31069,9 +32326,12 @@
         <v>0.04884</v>
       </c>
       <c r="V419" s="1" t="n">
+        <v>0.04865</v>
+      </c>
+      <c r="W419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="W419" s="1" t="n">
+      <c r="X419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -31142,9 +32402,12 @@
         <v>66.37</v>
       </c>
       <c r="V420" s="1" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="W420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="W420" s="1" t="n">
+      <c r="X420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -31215,9 +32478,12 @@
         <v>0.878</v>
       </c>
       <c r="V421" s="1" t="n">
-        <v>0.879</v>
+        <v>0.88</v>
       </c>
       <c r="W421" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="X421" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -31288,9 +32554,12 @@
         <v>0.012434</v>
       </c>
       <c r="V422" s="1" t="n">
+        <v>0.012465</v>
+      </c>
+      <c r="W422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="W422" s="1" t="n">
+      <c r="X422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -31361,9 +32630,12 @@
         <v>0.01593</v>
       </c>
       <c r="V423" s="1" t="n">
-        <v>0.01599</v>
+        <v>0.016</v>
       </c>
       <c r="W423" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="X423" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -31434,9 +32706,12 @@
         <v>0.27083</v>
       </c>
       <c r="V424" s="1" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="W424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="W424" s="1" t="n">
+      <c r="X424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -31507,10 +32782,13 @@
         <v>0.5993000000000001</v>
       </c>
       <c r="V425" s="1" t="n">
+        <v>0.5973000000000001</v>
+      </c>
+      <c r="W425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="W425" s="1" t="n">
-        <v>0.5984</v>
+      <c r="X425" s="1" t="n">
+        <v>0.5973000000000001</v>
       </c>
     </row>
     <row r="426">
@@ -31580,10 +32858,13 @@
         <v>0.005495</v>
       </c>
       <c r="V426" s="1" t="n">
+        <v>0.005468</v>
+      </c>
+      <c r="W426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="W426" s="1" t="n">
-        <v>0.005493</v>
+      <c r="X426" s="1" t="n">
+        <v>0.005468</v>
       </c>
     </row>
     <row r="427">
@@ -31653,9 +32934,12 @@
         <v>0.05022</v>
       </c>
       <c r="V427" s="1" t="n">
+        <v>0.04996</v>
+      </c>
+      <c r="W427" s="1" t="n">
         <v>0.05022</v>
       </c>
-      <c r="W427" s="1" t="n">
+      <c r="X427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -31726,9 +33010,12 @@
         <v>0.1252</v>
       </c>
       <c r="V428" s="1" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="W428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="W428" s="1" t="n">
+      <c r="X428" s="1" t="n">
         <v>0.1249</v>
       </c>
     </row>
@@ -31799,9 +33086,12 @@
         <v>0.003181</v>
       </c>
       <c r="V429" s="1" t="n">
+        <v>0.003185</v>
+      </c>
+      <c r="W429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="W429" s="1" t="n">
+      <c r="X429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -31872,10 +33162,13 @@
         <v>0.03622</v>
       </c>
       <c r="V430" s="1" t="n">
+        <v>0.03617</v>
+      </c>
+      <c r="W430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="W430" s="1" t="n">
-        <v>0.03622</v>
+      <c r="X430" s="1" t="n">
+        <v>0.03617</v>
       </c>
     </row>
     <row r="431">
@@ -31945,9 +33238,12 @@
         <v>0.3963</v>
       </c>
       <c r="V431" s="1" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="W431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="W431" s="1" t="n">
+      <c r="X431" s="1" t="n">
         <v>0.3914</v>
       </c>
     </row>
@@ -32018,9 +33314,12 @@
         <v>0.004457</v>
       </c>
       <c r="V432" s="1" t="n">
+        <v>0.004455</v>
+      </c>
+      <c r="W432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="W432" s="1" t="n">
+      <c r="X432" s="1" t="n">
         <v>0.004446</v>
       </c>
     </row>
@@ -32091,10 +33390,13 @@
         <v>0.0975</v>
       </c>
       <c r="V433" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="W433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="W433" s="1" t="n">
-        <v>0.09719999999999999</v>
+      <c r="X433" s="1" t="n">
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="434">
@@ -32164,9 +33466,12 @@
         <v>0.01239</v>
       </c>
       <c r="V434" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="W434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="W434" s="1" t="n">
+      <c r="X434" s="1" t="n">
         <v>0.01234</v>
       </c>
     </row>
@@ -32237,9 +33542,12 @@
         <v>1.98</v>
       </c>
       <c r="V435" s="1" t="n">
+        <v>1.981</v>
+      </c>
+      <c r="W435" s="1" t="n">
         <v>2.004</v>
       </c>
-      <c r="W435" s="1" t="n">
+      <c r="X435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -32310,10 +33618,13 @@
         <v>0.001767</v>
       </c>
       <c r="V436" s="1" t="n">
+        <v>0.001759</v>
+      </c>
+      <c r="W436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="W436" s="1" t="n">
-        <v>0.001767</v>
+      <c r="X436" s="1" t="n">
+        <v>0.001759</v>
       </c>
     </row>
     <row r="437">
@@ -32383,9 +33694,12 @@
         <v>0.4427</v>
       </c>
       <c r="V437" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="W437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="W437" s="1" t="n">
+      <c r="X437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -32456,9 +33770,12 @@
         <v>0.00533</v>
       </c>
       <c r="V438" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="W438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="W438" s="1" t="n">
+      <c r="X438" s="1" t="n">
         <v>0.00533</v>
       </c>
     </row>
@@ -32529,10 +33846,13 @@
         <v>0.1033</v>
       </c>
       <c r="V439" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="W439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="W439" s="1" t="n">
-        <v>0.1032</v>
+      <c r="X439" s="1" t="n">
+        <v>0.1031</v>
       </c>
     </row>
     <row r="440">
@@ -32602,10 +33922,13 @@
         <v>0.03356</v>
       </c>
       <c r="V440" s="1" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="W440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="W440" s="1" t="n">
-        <v>0.03356</v>
+      <c r="X440" s="1" t="n">
+        <v>0.03351</v>
       </c>
     </row>
     <row r="441">
@@ -32675,10 +33998,13 @@
         <v>0.08184</v>
       </c>
       <c r="V441" s="1" t="n">
+        <v>0.08173999999999999</v>
+      </c>
+      <c r="W441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="W441" s="1" t="n">
-        <v>0.08179</v>
+      <c r="X441" s="1" t="n">
+        <v>0.08173999999999999</v>
       </c>
     </row>
     <row r="442">
@@ -32748,10 +34074,13 @@
         <v>1.296</v>
       </c>
       <c r="V442" s="1" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="W442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="W442" s="1" t="n">
-        <v>1.296</v>
+      <c r="X442" s="1" t="n">
+        <v>1.293</v>
       </c>
     </row>
     <row r="443">
@@ -32821,9 +34150,12 @@
         <v>0.07514999999999999</v>
       </c>
       <c r="V443" s="1" t="n">
+        <v>0.07495</v>
+      </c>
+      <c r="W443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="W443" s="1" t="n">
+      <c r="X443" s="1" t="n">
         <v>0.07491</v>
       </c>
     </row>
@@ -32894,10 +34226,13 @@
         <v>0.07633</v>
       </c>
       <c r="V444" s="1" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="W444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="W444" s="1" t="n">
-        <v>0.07616000000000001</v>
+      <c r="X444" s="1" t="n">
+        <v>0.0761</v>
       </c>
     </row>
     <row r="445">
@@ -32967,10 +34302,13 @@
         <v>0.04299</v>
       </c>
       <c r="V445" s="1" t="n">
+        <v>0.04289</v>
+      </c>
+      <c r="W445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="W445" s="1" t="n">
-        <v>0.04298</v>
+      <c r="X445" s="1" t="n">
+        <v>0.04289</v>
       </c>
     </row>
     <row r="446">
@@ -33040,9 +34378,12 @@
         <v>0.0214</v>
       </c>
       <c r="V446" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="W446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="W446" s="1" t="n">
+      <c r="X446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -33113,9 +34454,12 @@
         <v>0.2799</v>
       </c>
       <c r="V447" s="1" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="W447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="W447" s="1" t="n">
+      <c r="X447" s="1" t="n">
         <v>0.2781</v>
       </c>
     </row>
@@ -33186,10 +34530,13 @@
         <v>0.03061</v>
       </c>
       <c r="V448" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="W448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="W448" s="1" t="n">
-        <v>0.03061</v>
+      <c r="X448" s="1" t="n">
+        <v>0.0306</v>
       </c>
     </row>
     <row r="449">
@@ -33259,9 +34606,12 @@
         <v>0.00655</v>
       </c>
       <c r="V449" s="1" t="n">
+        <v>0.00646</v>
+      </c>
+      <c r="W449" s="1" t="n">
         <v>0.00655</v>
       </c>
-      <c r="W449" s="1" t="n">
+      <c r="X449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -33332,10 +34682,13 @@
         <v>0.023004</v>
       </c>
       <c r="V450" s="1" t="n">
+        <v>0.02283</v>
+      </c>
+      <c r="W450" s="1" t="n">
         <v>0.02312</v>
       </c>
-      <c r="W450" s="1" t="n">
-        <v>0.022858</v>
+      <c r="X450" s="1" t="n">
+        <v>0.02283</v>
       </c>
     </row>
     <row r="451">
@@ -33405,9 +34758,12 @@
         <v>0.04238</v>
       </c>
       <c r="V451" s="1" t="n">
+        <v>0.04231</v>
+      </c>
+      <c r="W451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="W451" s="1" t="n">
+      <c r="X451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -33478,9 +34834,12 @@
         <v>0.07242999999999999</v>
       </c>
       <c r="V452" s="1" t="n">
+        <v>0.07214</v>
+      </c>
+      <c r="W452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="W452" s="1" t="n">
+      <c r="X452" s="1" t="n">
         <v>0.07204000000000001</v>
       </c>
     </row>
@@ -33551,10 +34910,13 @@
         <v>0.0005919</v>
       </c>
       <c r="V453" s="1" t="n">
+        <v>0.0005901</v>
+      </c>
+      <c r="W453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="W453" s="1" t="n">
-        <v>0.0005904</v>
+      <c r="X453" s="1" t="n">
+        <v>0.0005901</v>
       </c>
     </row>
     <row r="454">
@@ -33624,10 +34986,13 @@
         <v>0.304</v>
       </c>
       <c r="V454" s="1" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="W454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="W454" s="1" t="n">
-        <v>0.304</v>
+      <c r="X454" s="1" t="n">
+        <v>0.303</v>
       </c>
     </row>
     <row r="455">
@@ -33697,9 +35062,12 @@
         <v>0.004292</v>
       </c>
       <c r="V455" s="1" t="n">
+        <v>0.004287</v>
+      </c>
+      <c r="W455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="W455" s="1" t="n">
+      <c r="X455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -33770,10 +35138,13 @@
         <v>0.1816</v>
       </c>
       <c r="V456" s="1" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="W456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="W456" s="1" t="n">
-        <v>0.1816</v>
+      <c r="X456" s="1" t="n">
+        <v>0.1815</v>
       </c>
     </row>
     <row r="457">
@@ -33843,9 +35214,12 @@
         <v>0.04263</v>
       </c>
       <c r="V457" s="1" t="n">
+        <v>0.04256</v>
+      </c>
+      <c r="W457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="W457" s="1" t="n">
+      <c r="X457" s="1" t="n">
         <v>0.04254</v>
       </c>
     </row>
@@ -33916,9 +35290,12 @@
         <v>0.1448</v>
       </c>
       <c r="V458" s="1" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="W458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="W458" s="1" t="n">
+      <c r="X458" s="1" t="n">
         <v>0.1448</v>
       </c>
     </row>
@@ -33989,9 +35366,12 @@
         <v>0.008576</v>
       </c>
       <c r="V459" s="1" t="n">
+        <v>0.008616</v>
+      </c>
+      <c r="W459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="W459" s="1" t="n">
+      <c r="X459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -34062,9 +35442,12 @@
         <v>0.007446</v>
       </c>
       <c r="V460" s="1" t="n">
+        <v>0.00743</v>
+      </c>
+      <c r="W460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="W460" s="1" t="n">
+      <c r="X460" s="1" t="n">
         <v>0.007353</v>
       </c>
     </row>
@@ -34135,9 +35518,12 @@
         <v>0.0001899</v>
       </c>
       <c r="V461" s="1" t="n">
+        <v>0.0001774</v>
+      </c>
+      <c r="W461" s="1" t="n">
         <v>0.0001899</v>
       </c>
-      <c r="W461" s="1" t="n">
+      <c r="X461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -34208,9 +35594,12 @@
         <v>0.02392</v>
       </c>
       <c r="V462" s="1" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="W462" s="1" t="n">
         <v>0.02585</v>
       </c>
-      <c r="W462" s="1" t="n">
+      <c r="X462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -34281,10 +35670,13 @@
         <v>0.03658</v>
       </c>
       <c r="V463" s="1" t="n">
+        <v>0.03646</v>
+      </c>
+      <c r="W463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="W463" s="1" t="n">
-        <v>0.03652</v>
+      <c r="X463" s="1" t="n">
+        <v>0.03646</v>
       </c>
     </row>
     <row r="464">
@@ -34354,9 +35746,12 @@
         <v>0.3013</v>
       </c>
       <c r="V464" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="W464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="W464" s="1" t="n">
+      <c r="X464" s="1" t="n">
         <v>0.3003</v>
       </c>
     </row>
@@ -34427,10 +35822,13 @@
         <v>0.03887</v>
       </c>
       <c r="V465" s="1" t="n">
+        <v>0.03883</v>
+      </c>
+      <c r="W465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="W465" s="1" t="n">
-        <v>0.03887</v>
+      <c r="X465" s="1" t="n">
+        <v>0.03883</v>
       </c>
     </row>
     <row r="466">
@@ -34500,9 +35898,12 @@
         <v>2.665</v>
       </c>
       <c r="V466" s="1" t="n">
+        <v>2.666</v>
+      </c>
+      <c r="W466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="W466" s="1" t="n">
+      <c r="X466" s="1" t="n">
         <v>2.66</v>
       </c>
     </row>
@@ -34573,9 +35974,12 @@
         <v>0.0343</v>
       </c>
       <c r="V467" s="1" t="n">
-        <v>0.03438</v>
+        <v>0.03442</v>
       </c>
       <c r="W467" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="X467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -34646,9 +36050,12 @@
         <v>0.1765</v>
       </c>
       <c r="V468" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="W468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="W468" s="1" t="n">
+      <c r="X468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -34719,9 +36126,12 @@
         <v>0.0961</v>
       </c>
       <c r="V469" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="W469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="W469" s="1" t="n">
+      <c r="X469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -34792,9 +36202,12 @@
         <v>0.06838</v>
       </c>
       <c r="V470" s="1" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="W470" s="1" t="n">
         <v>0.06838</v>
       </c>
-      <c r="W470" s="1" t="n">
+      <c r="X470" s="1" t="n">
         <v>0.06696000000000001</v>
       </c>
     </row>
@@ -34865,10 +36278,13 @@
         <v>0.03967</v>
       </c>
       <c r="V471" s="1" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="W471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="W471" s="1" t="n">
-        <v>0.03967</v>
+      <c r="X471" s="1" t="n">
+        <v>0.0396</v>
       </c>
     </row>
     <row r="472">
@@ -34938,9 +36354,12 @@
         <v>0.2464</v>
       </c>
       <c r="V472" s="1" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="W472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="W472" s="1" t="n">
+      <c r="X472" s="1" t="n">
         <v>0.2457</v>
       </c>
     </row>
@@ -35011,9 +36430,12 @@
         <v>0.016273</v>
       </c>
       <c r="V473" s="1" t="n">
+        <v>0.016255</v>
+      </c>
+      <c r="W473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="W473" s="1" t="n">
+      <c r="X473" s="1" t="n">
         <v>0.016238</v>
       </c>
     </row>
@@ -35084,9 +36506,12 @@
         <v>0.1148</v>
       </c>
       <c r="V474" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="W474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="W474" s="1" t="n">
+      <c r="X474" s="1" t="n">
         <v>0.1146</v>
       </c>
     </row>
@@ -35157,9 +36582,12 @@
         <v>0.04298</v>
       </c>
       <c r="V475" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="W475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="W475" s="1" t="n">
+      <c r="X475" s="1" t="n">
         <v>0.04258</v>
       </c>
     </row>
@@ -35230,9 +36658,12 @@
         <v>0.2066</v>
       </c>
       <c r="V476" s="1" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="W476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="W476" s="1" t="n">
+      <c r="X476" s="1" t="n">
         <v>0.2062</v>
       </c>
     </row>
@@ -35303,9 +36734,12 @@
         <v>0.006791</v>
       </c>
       <c r="V477" s="1" t="n">
+        <v>0.006775</v>
+      </c>
+      <c r="W477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="W477" s="1" t="n">
+      <c r="X477" s="1" t="n">
         <v>0.006763</v>
       </c>
     </row>
@@ -35376,9 +36810,12 @@
         <v>0.01778</v>
       </c>
       <c r="V478" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="W478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="W478" s="1" t="n">
+      <c r="X478" s="1" t="n">
         <v>0.01776</v>
       </c>
     </row>
@@ -35449,9 +36886,12 @@
         <v>0.04639</v>
       </c>
       <c r="V479" s="1" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="W479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="W479" s="1" t="n">
+      <c r="X479" s="1" t="n">
         <v>0.04639</v>
       </c>
     </row>
@@ -35522,9 +36962,12 @@
         <v>0.26051</v>
       </c>
       <c r="V480" s="1" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="W480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="W480" s="1" t="n">
+      <c r="X480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -35595,10 +37038,13 @@
         <v>0.01206</v>
       </c>
       <c r="V481" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="W481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="W481" s="1" t="n">
-        <v>0.01206</v>
+      <c r="X481" s="1" t="n">
+        <v>0.01202</v>
       </c>
     </row>
     <row r="482">
@@ -35668,9 +37114,12 @@
         <v>0.004064</v>
       </c>
       <c r="V482" s="1" t="n">
+        <v>0.004063</v>
+      </c>
+      <c r="W482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="W482" s="1" t="n">
+      <c r="X482" s="1" t="n">
         <v>0.004055</v>
       </c>
     </row>
@@ -35741,10 +37190,13 @@
         <v>0.1228</v>
       </c>
       <c r="V483" s="1" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="W483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="W483" s="1" t="n">
-        <v>0.1226</v>
+      <c r="X483" s="1" t="n">
+        <v>0.1224</v>
       </c>
     </row>
     <row r="484">
@@ -35814,9 +37266,12 @@
         <v>0.022</v>
       </c>
       <c r="V484" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="W484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="W484" s="1" t="n">
+      <c r="X484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -35887,9 +37342,12 @@
         <v>0.04553</v>
       </c>
       <c r="V485" s="1" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="W485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="W485" s="1" t="n">
+      <c r="X485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -35960,10 +37418,13 @@
         <v>0.1721</v>
       </c>
       <c r="V486" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="W486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="W486" s="1" t="n">
-        <v>0.1721</v>
+      <c r="X486" s="1" t="n">
+        <v>0.1716</v>
       </c>
     </row>
     <row r="487">
@@ -36033,9 +37494,12 @@
         <v>0.2763</v>
       </c>
       <c r="V487" s="1" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="W487" s="1" t="n">
         <v>0.2767</v>
       </c>
-      <c r="W487" s="1" t="n">
+      <c r="X487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -36106,10 +37570,13 @@
         <v>0.04582</v>
       </c>
       <c r="V488" s="1" t="n">
+        <v>0.04577</v>
+      </c>
+      <c r="W488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="W488" s="1" t="n">
-        <v>0.04578</v>
+      <c r="X488" s="1" t="n">
+        <v>0.04577</v>
       </c>
     </row>
     <row r="489">
@@ -36179,9 +37646,12 @@
         <v>0.0002142</v>
       </c>
       <c r="V489" s="1" t="n">
+        <v>0.000214</v>
+      </c>
+      <c r="W489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="W489" s="1" t="n">
+      <c r="X489" s="1" t="n">
         <v>0.0002139</v>
       </c>
     </row>
@@ -36252,9 +37722,12 @@
         <v>1.778</v>
       </c>
       <c r="V490" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W490" s="1" t="n">
         <v>1.783</v>
       </c>
-      <c r="W490" s="1" t="n">
+      <c r="X490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -36325,9 +37798,12 @@
         <v>16.01</v>
       </c>
       <c r="V491" s="1" t="n">
+        <v>15.993</v>
+      </c>
+      <c r="W491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="W491" s="1" t="n">
+      <c r="X491" s="1" t="n">
         <v>15.99</v>
       </c>
     </row>
@@ -36398,9 +37874,12 @@
         <v>0.06645</v>
       </c>
       <c r="V492" s="1" t="n">
+        <v>0.06655</v>
+      </c>
+      <c r="W492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="W492" s="1" t="n">
+      <c r="X492" s="1" t="n">
         <v>0.06637</v>
       </c>
     </row>
@@ -36471,9 +37950,12 @@
         <v>0.06726</v>
       </c>
       <c r="V493" s="1" t="n">
+        <v>0.06721000000000001</v>
+      </c>
+      <c r="W493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="W493" s="1" t="n">
+      <c r="X493" s="1" t="n">
         <v>0.06709</v>
       </c>
     </row>
@@ -36544,9 +38026,12 @@
         <v>0.0094</v>
       </c>
       <c r="V494" s="1" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="W494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="W494" s="1" t="n">
+      <c r="X494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -36617,9 +38102,12 @@
         <v>0.005776</v>
       </c>
       <c r="V495" s="1" t="n">
+        <v>0.005834</v>
+      </c>
+      <c r="W495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="W495" s="1" t="n">
+      <c r="X495" s="1" t="n">
         <v>0.005774</v>
       </c>
     </row>
@@ -36690,10 +38178,13 @@
         <v>0.009809999999999999</v>
       </c>
       <c r="V496" s="1" t="n">
+        <v>0.009769999999999999</v>
+      </c>
+      <c r="W496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="W496" s="1" t="n">
-        <v>0.009809999999999999</v>
+      <c r="X496" s="1" t="n">
+        <v>0.009769999999999999</v>
       </c>
     </row>
     <row r="497">
@@ -36763,9 +38254,12 @@
         <v>0.04551</v>
       </c>
       <c r="V497" s="1" t="n">
+        <v>0.04579</v>
+      </c>
+      <c r="W497" s="1" t="n">
         <v>0.04665</v>
       </c>
-      <c r="W497" s="1" t="n">
+      <c r="X497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -36836,9 +38330,12 @@
         <v>0.006361</v>
       </c>
       <c r="V498" s="1" t="n">
+        <v>0.006346</v>
+      </c>
+      <c r="W498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="W498" s="1" t="n">
+      <c r="X498" s="1" t="n">
         <v>0.006338</v>
       </c>
     </row>
@@ -36909,10 +38406,13 @@
         <v>0.01029</v>
       </c>
       <c r="V499" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="W499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="W499" s="1" t="n">
-        <v>0.01029</v>
+      <c r="X499" s="1" t="n">
+        <v>0.01024</v>
       </c>
     </row>
     <row r="500">
@@ -36982,10 +38482,13 @@
         <v>0.5071</v>
       </c>
       <c r="V500" s="1" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="W500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="W500" s="1" t="n">
-        <v>0.5067</v>
+      <c r="X500" s="1" t="n">
+        <v>0.5061</v>
       </c>
     </row>
     <row r="501">
@@ -37055,9 +38558,12 @@
         <v>0.03209</v>
       </c>
       <c r="V501" s="1" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="W501" s="1" t="n">
         <v>0.03213</v>
       </c>
-      <c r="W501" s="1" t="n">
+      <c r="X501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -37128,9 +38634,12 @@
         <v>0.4326</v>
       </c>
       <c r="V502" s="1" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="W502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="W502" s="1" t="n">
+      <c r="X502" s="1" t="n">
         <v>0.4326</v>
       </c>
     </row>
@@ -37201,9 +38710,12 @@
         <v>0.999341</v>
       </c>
       <c r="V503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="W503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="W503" s="1" t="n">
+      <c r="X503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -37274,9 +38786,12 @@
         <v>0.03522</v>
       </c>
       <c r="V504" s="1" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="W504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="W504" s="1" t="n">
+      <c r="X504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -37347,10 +38862,13 @@
         <v>0.00491</v>
       </c>
       <c r="V505" s="1" t="n">
+        <v>0.004892</v>
+      </c>
+      <c r="W505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="W505" s="1" t="n">
-        <v>0.004893</v>
+      <c r="X505" s="1" t="n">
+        <v>0.004892</v>
       </c>
     </row>
     <row r="506">
@@ -37420,9 +38938,12 @@
         <v>0.01383</v>
       </c>
       <c r="V506" s="1" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="W506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="W506" s="1" t="n">
+      <c r="X506" s="1" t="n">
         <v>0.0138</v>
       </c>
     </row>
@@ -37493,9 +39014,12 @@
         <v>0.003477</v>
       </c>
       <c r="V507" s="1" t="n">
+        <v>0.003457</v>
+      </c>
+      <c r="W507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="W507" s="1" t="n">
+      <c r="X507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -37566,9 +39090,12 @@
         <v>1.413</v>
       </c>
       <c r="V508" s="1" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="W508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="W508" s="1" t="n">
+      <c r="X508" s="1" t="n">
         <v>1.411</v>
       </c>
     </row>
@@ -37639,9 +39166,12 @@
         <v>0.005026</v>
       </c>
       <c r="V509" s="1" t="n">
+        <v>0.005041</v>
+      </c>
+      <c r="W509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="W509" s="1" t="n">
+      <c r="X509" s="1" t="n">
         <v>0.005026</v>
       </c>
     </row>
@@ -37712,9 +39242,12 @@
         <v>0.01562</v>
       </c>
       <c r="V510" s="1" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="W510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="W510" s="1" t="n">
+      <c r="X510" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -37785,9 +39318,12 @@
         <v>0.08164</v>
       </c>
       <c r="V511" s="1" t="n">
+        <v>0.08168</v>
+      </c>
+      <c r="W511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="W511" s="1" t="n">
+      <c r="X511" s="1" t="n">
         <v>0.08119</v>
       </c>
     </row>
@@ -37858,10 +39394,13 @@
         <v>0.007082</v>
       </c>
       <c r="V512" s="1" t="n">
+        <v>0.007066</v>
+      </c>
+      <c r="W512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="W512" s="1" t="n">
-        <v>0.007067</v>
+      <c r="X512" s="1" t="n">
+        <v>0.007066</v>
       </c>
     </row>
     <row r="513">
@@ -37931,9 +39470,12 @@
         <v>0.01476</v>
       </c>
       <c r="V513" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="W513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="W513" s="1" t="n">
+      <c r="X513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -38004,10 +39546,13 @@
         <v>0.0471</v>
       </c>
       <c r="V514" s="1" t="n">
+        <v>0.04688</v>
+      </c>
+      <c r="W514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="W514" s="1" t="n">
-        <v>0.0471</v>
+      <c r="X514" s="1" t="n">
+        <v>0.04688</v>
       </c>
     </row>
     <row r="515">
@@ -38077,9 +39622,12 @@
         <v>0.01806</v>
       </c>
       <c r="V515" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="W515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="W515" s="1" t="n">
+      <c r="X515" s="1" t="n">
         <v>0.01796</v>
       </c>
     </row>
@@ -38150,9 +39698,12 @@
         <v>0.000579</v>
       </c>
       <c r="V516" s="1" t="n">
+        <v>0.0005789</v>
+      </c>
+      <c r="W516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="W516" s="1" t="n">
+      <c r="X516" s="1" t="n">
         <v>0.000578</v>
       </c>
     </row>
@@ -38223,9 +39774,12 @@
         <v>0.07825</v>
       </c>
       <c r="V517" s="1" t="n">
+        <v>0.07821</v>
+      </c>
+      <c r="W517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="W517" s="1" t="n">
+      <c r="X517" s="1" t="n">
         <v>0.07817</v>
       </c>
     </row>
@@ -38296,10 +39850,13 @@
         <v>0.006361</v>
       </c>
       <c r="V518" s="1" t="n">
+        <v>0.006348</v>
+      </c>
+      <c r="W518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="W518" s="1" t="n">
-        <v>0.00635</v>
+      <c r="X518" s="1" t="n">
+        <v>0.006348</v>
       </c>
     </row>
     <row r="519">
@@ -38369,10 +39926,13 @@
         <v>0.05752</v>
       </c>
       <c r="V519" s="1" t="n">
+        <v>0.05745</v>
+      </c>
+      <c r="W519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="W519" s="1" t="n">
-        <v>0.05746</v>
+      <c r="X519" s="1" t="n">
+        <v>0.05745</v>
       </c>
     </row>
     <row r="520">
@@ -38442,10 +40002,13 @@
         <v>0.10333</v>
       </c>
       <c r="V520" s="1" t="n">
+        <v>0.10321</v>
+      </c>
+      <c r="W520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="W520" s="1" t="n">
-        <v>0.10333</v>
+      <c r="X520" s="1" t="n">
+        <v>0.10321</v>
       </c>
     </row>
     <row r="521">
@@ -38515,9 +40078,12 @@
         <v>0.01792</v>
       </c>
       <c r="V521" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="W521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="W521" s="1" t="n">
+      <c r="X521" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -38588,9 +40154,12 @@
         <v>0.01616</v>
       </c>
       <c r="V522" s="1" t="n">
+        <v>0.01619</v>
+      </c>
+      <c r="W522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="W522" s="1" t="n">
+      <c r="X522" s="1" t="n">
         <v>0.01602</v>
       </c>
     </row>
@@ -38661,10 +40230,13 @@
         <v>0.01077</v>
       </c>
       <c r="V523" s="1" t="n">
+        <v>0.01076</v>
+      </c>
+      <c r="W523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="W523" s="1" t="n">
-        <v>0.01077</v>
+      <c r="X523" s="1" t="n">
+        <v>0.01076</v>
       </c>
     </row>
     <row r="524">
@@ -38734,9 +40306,12 @@
         <v>0.00733</v>
       </c>
       <c r="V524" s="1" t="n">
-        <v>0.007331</v>
+        <v>0.007332</v>
       </c>
       <c r="W524" s="1" t="n">
+        <v>0.007332</v>
+      </c>
+      <c r="X524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -38807,10 +40382,13 @@
         <v>0.0058</v>
       </c>
       <c r="V525" s="1" t="n">
+        <v>0.005792</v>
+      </c>
+      <c r="W525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="W525" s="1" t="n">
-        <v>0.005794</v>
+      <c r="X525" s="1" t="n">
+        <v>0.005792</v>
       </c>
     </row>
     <row r="526">
@@ -38880,9 +40458,12 @@
         <v>0.001439</v>
       </c>
       <c r="V526" s="1" t="n">
+        <v>0.001438</v>
+      </c>
+      <c r="W526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="W526" s="1" t="n">
+      <c r="X526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -38953,9 +40534,12 @@
         <v>0.375</v>
       </c>
       <c r="V527" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="W527" s="1" t="n">
         <v>0.375</v>
       </c>
-      <c r="W527" s="1" t="n">
+      <c r="X527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -39026,9 +40610,12 @@
         <v>0.005196</v>
       </c>
       <c r="V528" s="1" t="n">
+        <v>0.005245</v>
+      </c>
+      <c r="W528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="W528" s="1" t="n">
+      <c r="X528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -39099,9 +40686,12 @@
         <v>2.945</v>
       </c>
       <c r="V529" s="1" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="W529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="W529" s="1" t="n">
+      <c r="X529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -39172,10 +40762,13 @@
         <v>0.1522</v>
       </c>
       <c r="V530" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="W530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="W530" s="1" t="n">
-        <v>0.1522</v>
+      <c r="X530" s="1" t="n">
+        <v>0.1517</v>
       </c>
     </row>
     <row r="531">
@@ -39245,9 +40838,12 @@
         <v>2584</v>
       </c>
       <c r="V531" s="1" t="n">
+        <v>2575</v>
+      </c>
+      <c r="W531" s="1" t="n">
         <v>2584</v>
       </c>
-      <c r="W531" s="1" t="n">
+      <c r="X531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -39318,9 +40914,12 @@
         <v>0.039</v>
       </c>
       <c r="V532" s="1" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="W532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="W532" s="1" t="n">
+      <c r="X532" s="1" t="n">
         <v>0.03893</v>
       </c>
     </row>
@@ -39391,9 +40990,12 @@
         <v>0.0219</v>
       </c>
       <c r="V533" s="1" t="n">
-        <v>0.02191</v>
+        <v>0.02192</v>
       </c>
       <c r="W533" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="X533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -39464,9 +41066,12 @@
         <v>0.07287</v>
       </c>
       <c r="V534" s="1" t="n">
+        <v>0.07281</v>
+      </c>
+      <c r="W534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="W534" s="1" t="n">
+      <c r="X534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -39537,9 +41142,12 @@
         <v>0.007839</v>
       </c>
       <c r="V535" s="1" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="W535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="W535" s="1" t="n">
+      <c r="X535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -39610,9 +41218,12 @@
         <v>0.04999</v>
       </c>
       <c r="V536" s="1" t="n">
+        <v>0.04985</v>
+      </c>
+      <c r="W536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="W536" s="1" t="n">
+      <c r="X536" s="1" t="n">
         <v>0.04985</v>
       </c>
     </row>
@@ -39683,9 +41294,12 @@
         <v>0.00401</v>
       </c>
       <c r="V537" s="1" t="n">
+        <v>0.00401</v>
+      </c>
+      <c r="W537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="W537" s="1" t="n">
+      <c r="X537" s="1" t="n">
         <v>0.00397</v>
       </c>
     </row>
@@ -39756,9 +41370,12 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="V538" s="1" t="n">
+        <v>0.08262</v>
+      </c>
+      <c r="W538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="W538" s="1" t="n">
+      <c r="X538" s="1" t="n">
         <v>0.08252</v>
       </c>
     </row>
@@ -39829,10 +41446,13 @@
         <v>0.02476</v>
       </c>
       <c r="V539" s="1" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="W539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="W539" s="1" t="n">
-        <v>0.02473</v>
+      <c r="X539" s="1" t="n">
+        <v>0.02466</v>
       </c>
     </row>
     <row r="540">
@@ -39902,9 +41522,12 @@
         <v>0.08427999999999999</v>
       </c>
       <c r="V540" s="1" t="n">
+        <v>0.08434999999999999</v>
+      </c>
+      <c r="W540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="W540" s="1" t="n">
+      <c r="X540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -39975,9 +41598,12 @@
         <v>0.01882</v>
       </c>
       <c r="V541" s="1" t="n">
+        <v>0.01881</v>
+      </c>
+      <c r="W541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="W541" s="1" t="n">
+      <c r="X541" s="1" t="n">
         <v>0.0188</v>
       </c>
     </row>
@@ -40048,10 +41674,13 @@
         <v>0.0168</v>
       </c>
       <c r="V542" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="W542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="W542" s="1" t="n">
-        <v>0.01679</v>
+      <c r="X542" s="1" t="n">
+        <v>0.01674</v>
       </c>
     </row>
     <row r="543">
@@ -40121,9 +41750,12 @@
         <v>0.1048</v>
       </c>
       <c r="V543" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="W543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="W543" s="1" t="n">
+      <c r="X543" s="1" t="n">
         <v>0.1044</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y543"/>
+  <dimension ref="A1:Z543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -442,8 +442,9 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,10 +565,15 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>price_05:45</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -646,9 +652,12 @@
         <v>70656.10000000001</v>
       </c>
       <c r="X2" s="1" t="n">
+        <v>70721.8</v>
+      </c>
+      <c r="Y2" s="1" t="n">
         <v>70796.5</v>
       </c>
-      <c r="Y2" s="1" t="n">
+      <c r="Z2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -725,9 +734,12 @@
         <v>2082.15</v>
       </c>
       <c r="X3" s="1" t="n">
+        <v>2084.38</v>
+      </c>
+      <c r="Y3" s="1" t="n">
         <v>2084.79</v>
       </c>
-      <c r="Y3" s="1" t="n">
+      <c r="Z3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -804,9 +816,12 @@
         <v>86.93000000000001</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>87.05</v>
+        <v>87.06</v>
       </c>
       <c r="Y4" s="1" t="n">
+        <v>87.06</v>
+      </c>
+      <c r="Z4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -883,9 +898,12 @@
         <v>3.991</v>
       </c>
       <c r="X5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="Z5" s="1" t="n">
         <v>3.967</v>
       </c>
     </row>
@@ -962,9 +980,12 @@
         <v>0.09475</v>
       </c>
       <c r="X6" s="1" t="n">
+        <v>0.09481000000000001</v>
+      </c>
+      <c r="Y6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="Y6" s="1" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -1041,9 +1062,12 @@
         <v>1.3916</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>1.3929</v>
+        <v>1.3943</v>
       </c>
       <c r="Y7" s="1" t="n">
+        <v>1.3943</v>
+      </c>
+      <c r="Z7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -1120,9 +1144,12 @@
         <v>22.046</v>
       </c>
       <c r="X8" s="1" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="Y8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="Y8" s="1" t="n">
+      <c r="Z8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1199,9 +1226,12 @@
         <v>0.001987</v>
       </c>
       <c r="X9" s="1" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="Y9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="Z9" s="1" t="n">
         <v>0.001951</v>
       </c>
     </row>
@@ -1278,9 +1308,12 @@
         <v>0.009858</v>
       </c>
       <c r="X10" s="1" t="n">
+        <v>0.009830999999999999</v>
+      </c>
+      <c r="Y10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="Y10" s="1" t="n">
+      <c r="Z10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1357,9 +1390,12 @@
         <v>0.1478</v>
       </c>
       <c r="X11" s="1" t="n">
+        <v>0.15476</v>
+      </c>
+      <c r="Y11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="Y11" s="1" t="n">
+      <c r="Z11" s="1" t="n">
         <v>0.13631</v>
       </c>
     </row>
@@ -1436,9 +1472,12 @@
         <v>0.010924</v>
       </c>
       <c r="X12" s="1" t="n">
+        <v>0.011095</v>
+      </c>
+      <c r="Y12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="Y12" s="1" t="n">
+      <c r="Z12" s="1" t="n">
         <v>0.010924</v>
       </c>
     </row>
@@ -1515,9 +1554,12 @@
         <v>37.894</v>
       </c>
       <c r="X13" s="1" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="Y13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="Y13" s="1" t="n">
+      <c r="Z13" s="1" t="n">
         <v>37.748</v>
       </c>
     </row>
@@ -1594,9 +1636,12 @@
         <v>653.21</v>
       </c>
       <c r="X14" s="1" t="n">
+        <v>654.1</v>
+      </c>
+      <c r="Y14" s="1" t="n">
         <v>654.13</v>
       </c>
-      <c r="Y14" s="1" t="n">
+      <c r="Z14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1673,9 +1718,12 @@
         <v>209.69</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>210.26</v>
+        <v>210.54</v>
       </c>
       <c r="Y15" s="1" t="n">
+        <v>210.54</v>
+      </c>
+      <c r="Z15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1752,9 +1800,12 @@
         <v>0.0033217</v>
       </c>
       <c r="X16" s="1" t="n">
+        <v>0.0033262</v>
+      </c>
+      <c r="Y16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="Y16" s="1" t="n">
+      <c r="Z16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1831,9 +1882,12 @@
         <v>243.3</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>243.3</v>
+        <v>244.53</v>
       </c>
       <c r="Y17" s="1" t="n">
+        <v>244.53</v>
+      </c>
+      <c r="Z17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1910,9 +1964,12 @@
         <v>0.9879</v>
       </c>
       <c r="X18" s="1" t="n">
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="Y18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="Y18" s="1" t="n">
+      <c r="Z18" s="1" t="n">
         <v>0.9858</v>
       </c>
     </row>
@@ -1989,10 +2046,13 @@
         <v>0.9968</v>
       </c>
       <c r="X19" s="1" t="n">
+        <v>0.9887</v>
+      </c>
+      <c r="Y19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="Y19" s="1" t="n">
-        <v>0.9968</v>
+      <c r="Z19" s="1" t="n">
+        <v>0.9887</v>
       </c>
     </row>
     <row r="20">
@@ -2068,9 +2128,12 @@
         <v>0.2589</v>
       </c>
       <c r="X20" s="1" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="Y20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="Y20" s="1" t="n">
+      <c r="Z20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -2147,10 +2210,13 @@
         <v>0.58568</v>
       </c>
       <c r="X21" s="1" t="n">
+        <v>0.58548</v>
+      </c>
+      <c r="Y21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="Y21" s="1" t="n">
-        <v>0.58568</v>
+      <c r="Z21" s="1" t="n">
+        <v>0.58548</v>
       </c>
     </row>
     <row r="22">
@@ -2226,9 +2292,12 @@
         <v>9.042999999999999</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>9.042999999999999</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="Y22" s="1" t="n">
+        <v>9.066000000000001</v>
+      </c>
+      <c r="Z22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -2305,9 +2374,12 @@
         <v>0.02366</v>
       </c>
       <c r="X23" s="1" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="Y23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="Y23" s="1" t="n">
+      <c r="Z23" s="1" t="n">
         <v>0.02359</v>
       </c>
     </row>
@@ -2384,9 +2456,12 @@
         <v>9.57</v>
       </c>
       <c r="X24" s="1" t="n">
+        <v>9.581</v>
+      </c>
+      <c r="Y24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="Y24" s="1" t="n">
+      <c r="Z24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2463,9 +2538,12 @@
         <v>1.218</v>
       </c>
       <c r="X25" s="1" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="Y25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="Y25" s="1" t="n">
+      <c r="Z25" s="1" t="n">
         <v>1.216</v>
       </c>
     </row>
@@ -2542,9 +2620,12 @@
         <v>0.07215000000000001</v>
       </c>
       <c r="X26" s="1" t="n">
+        <v>0.07199</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>0.07317</v>
       </c>
-      <c r="Y26" s="1" t="n">
+      <c r="Z26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2621,9 +2702,12 @@
         <v>1.409</v>
       </c>
       <c r="X27" s="1" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="Y27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="Y27" s="1" t="n">
+      <c r="Z27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2700,9 +2784,12 @@
         <v>1.303</v>
       </c>
       <c r="X28" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="Y28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="Y28" s="1" t="n">
+      <c r="Z28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2779,9 +2866,12 @@
         <v>463.75</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>464.27</v>
+        <v>464.45</v>
       </c>
       <c r="Y29" s="1" t="n">
+        <v>464.45</v>
+      </c>
+      <c r="Z29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2858,9 +2948,12 @@
         <v>1.2906</v>
       </c>
       <c r="X30" s="1" t="n">
+        <v>1.2894</v>
+      </c>
+      <c r="Y30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="Y30" s="1" t="n">
+      <c r="Z30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2937,9 +3030,12 @@
         <v>5020.26</v>
       </c>
       <c r="X31" s="1" t="n">
+        <v>5020.52</v>
+      </c>
+      <c r="Y31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="Y31" s="1" t="n">
+      <c r="Z31" s="1" t="n">
         <v>5019.32</v>
       </c>
     </row>
@@ -3016,9 +3112,12 @@
         <v>0.877</v>
       </c>
       <c r="X32" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Y32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="Y32" s="1" t="n">
+      <c r="Z32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -3095,9 +3194,12 @@
         <v>0.001965</v>
       </c>
       <c r="X33" s="1" t="n">
+        <v>0.001966</v>
+      </c>
+      <c r="Y33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="Y33" s="1" t="n">
+      <c r="Z33" s="1" t="n">
         <v>0.001965</v>
       </c>
     </row>
@@ -3174,9 +3276,12 @@
         <v>0.1728</v>
       </c>
       <c r="X34" s="1" t="n">
+        <v>0.17411</v>
+      </c>
+      <c r="Y34" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="Y34" s="1" t="n">
+      <c r="Z34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -3253,9 +3358,12 @@
         <v>0.29703</v>
       </c>
       <c r="X35" s="1" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="Y35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="Y35" s="1" t="n">
+      <c r="Z35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -3332,9 +3440,12 @@
         <v>1.787</v>
       </c>
       <c r="X36" s="1" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="Y36" s="1" t="n">
         <v>1.798</v>
       </c>
-      <c r="Y36" s="1" t="n">
+      <c r="Z36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -3411,9 +3522,12 @@
         <v>110.24</v>
       </c>
       <c r="X37" s="1" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="Y37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="Y37" s="1" t="n">
+      <c r="Z37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -3490,9 +3604,12 @@
         <v>0.21981</v>
       </c>
       <c r="X38" s="1" t="n">
+        <v>0.22009</v>
+      </c>
+      <c r="Y38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="Y38" s="1" t="n">
+      <c r="Z38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -3569,9 +3686,12 @@
         <v>0.1065</v>
       </c>
       <c r="X39" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="Y39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="Y39" s="1" t="n">
+      <c r="Z39" s="1" t="n">
         <v>0.1063</v>
       </c>
     </row>
@@ -3648,10 +3768,13 @@
         <v>0.37049</v>
       </c>
       <c r="X40" s="1" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="Y40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="Y40" s="1" t="n">
-        <v>0.3694</v>
+      <c r="Z40" s="1" t="n">
+        <v>0.36777</v>
       </c>
     </row>
     <row r="41">
@@ -3727,9 +3850,12 @@
         <v>54.51</v>
       </c>
       <c r="X41" s="1" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="Y41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="Y41" s="1" t="n">
+      <c r="Z41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3806,9 +3932,12 @@
         <v>0.0010547</v>
       </c>
       <c r="X42" s="1" t="n">
+        <v>0.0010563</v>
+      </c>
+      <c r="Y42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="Y42" s="1" t="n">
+      <c r="Z42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -3885,9 +4014,12 @@
         <v>6.477</v>
       </c>
       <c r="X43" s="1" t="n">
+        <v>6.462</v>
+      </c>
+      <c r="Y43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="Y43" s="1" t="n">
+      <c r="Z43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3964,9 +4096,12 @@
         <v>0.6274999999999999</v>
       </c>
       <c r="X44" s="1" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="Y44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="Y44" s="1" t="n">
+      <c r="Z44" s="1" t="n">
         <v>0.6213</v>
       </c>
     </row>
@@ -4043,9 +4178,12 @@
         <v>0.3516</v>
       </c>
       <c r="X45" s="1" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="Y45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="Y45" s="1" t="n">
+      <c r="Z45" s="1" t="n">
         <v>0.3512</v>
       </c>
     </row>
@@ -4122,9 +4260,12 @@
         <v>0.033</v>
       </c>
       <c r="X46" s="1" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="Y46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="Y46" s="1" t="n">
+      <c r="Z46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -4201,10 +4342,13 @@
         <v>0.06813</v>
       </c>
       <c r="X47" s="1" t="n">
+        <v>0.06763</v>
+      </c>
+      <c r="Y47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="Y47" s="1" t="n">
-        <v>0.06813</v>
+      <c r="Z47" s="1" t="n">
+        <v>0.06763</v>
       </c>
     </row>
     <row r="48">
@@ -4280,9 +4424,12 @@
         <v>0.7087</v>
       </c>
       <c r="X48" s="1" t="n">
+        <v>0.7108</v>
+      </c>
+      <c r="Y48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="Y48" s="1" t="n">
+      <c r="Z48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -4359,9 +4506,12 @@
         <v>0.004283</v>
       </c>
       <c r="X49" s="1" t="n">
+        <v>0.004291</v>
+      </c>
+      <c r="Y49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="Y49" s="1" t="n">
+      <c r="Z49" s="1" t="n">
         <v>0.004224</v>
       </c>
     </row>
@@ -4438,9 +4588,12 @@
         <v>0.1033</v>
       </c>
       <c r="X50" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="Y50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="Y50" s="1" t="n">
+      <c r="Z50" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -4517,10 +4670,13 @@
         <v>0.04015</v>
       </c>
       <c r="X51" s="1" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="Y51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="Y51" s="1" t="n">
-        <v>0.04015</v>
+      <c r="Z51" s="1" t="n">
+        <v>0.03999</v>
       </c>
     </row>
     <row r="52">
@@ -4596,9 +4752,12 @@
         <v>0.1644</v>
       </c>
       <c r="X52" s="1" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="Y52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="Y52" s="1" t="n">
+      <c r="Z52" s="1" t="n">
         <v>0.1641</v>
       </c>
     </row>
@@ -4675,9 +4834,12 @@
         <v>0.01938</v>
       </c>
       <c r="X53" s="1" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="Y53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="Y53" s="1" t="n">
+      <c r="Z53" s="1" t="n">
         <v>0.01922</v>
       </c>
     </row>
@@ -4754,9 +4916,12 @@
         <v>0.007168</v>
       </c>
       <c r="X54" s="1" t="n">
+        <v>0.007175</v>
+      </c>
+      <c r="Y54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="Y54" s="1" t="n">
+      <c r="Z54" s="1" t="n">
         <v>0.007168</v>
       </c>
     </row>
@@ -4833,9 +4998,12 @@
         <v>3.912</v>
       </c>
       <c r="X55" s="1" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="Y55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="Y55" s="1" t="n">
+      <c r="Z55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -4912,10 +5080,13 @@
         <v>0.016778</v>
       </c>
       <c r="X56" s="1" t="n">
+        <v>0.016759</v>
+      </c>
+      <c r="Y56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="Y56" s="1" t="n">
-        <v>0.016778</v>
+      <c r="Z56" s="1" t="n">
+        <v>0.016759</v>
       </c>
     </row>
     <row r="57">
@@ -4991,9 +5162,12 @@
         <v>0.1086</v>
       </c>
       <c r="X57" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="Y57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="Y57" s="1" t="n">
+      <c r="Z57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -5070,9 +5244,12 @@
         <v>2.649</v>
       </c>
       <c r="X58" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="Y58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="Y58" s="1" t="n">
+      <c r="Z58" s="1" t="n">
         <v>2.639</v>
       </c>
     </row>
@@ -5149,9 +5326,12 @@
         <v>0.157</v>
       </c>
       <c r="X59" s="1" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="Y59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="Y59" s="1" t="n">
+      <c r="Z59" s="1" t="n">
         <v>0.157</v>
       </c>
     </row>
@@ -5228,9 +5408,12 @@
         <v>0.005837</v>
       </c>
       <c r="X60" s="1" t="n">
+        <v>0.005841</v>
+      </c>
+      <c r="Y60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="Y60" s="1" t="n">
+      <c r="Z60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -5307,9 +5490,12 @@
         <v>0.09182</v>
       </c>
       <c r="X61" s="1" t="n">
+        <v>0.09203</v>
+      </c>
+      <c r="Y61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="Y61" s="1" t="n">
+      <c r="Z61" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5386,9 +5572,12 @@
         <v>0.9114</v>
       </c>
       <c r="X62" s="1" t="n">
+        <v>0.9112</v>
+      </c>
+      <c r="Y62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="Y62" s="1" t="n">
+      <c r="Z62" s="1" t="n">
         <v>0.9101</v>
       </c>
     </row>
@@ -5465,9 +5654,12 @@
         <v>0.778</v>
       </c>
       <c r="X63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="Y63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="Y63" s="1" t="n">
+      <c r="Z63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -5544,9 +5736,12 @@
         <v>0.0458</v>
       </c>
       <c r="X64" s="1" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="Y64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="Y64" s="1" t="n">
+      <c r="Z64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -5623,9 +5818,12 @@
         <v>356.71</v>
       </c>
       <c r="X65" s="1" t="n">
+        <v>358.13</v>
+      </c>
+      <c r="Y65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="Y65" s="1" t="n">
+      <c r="Z65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -5702,9 +5900,12 @@
         <v>0.12469</v>
       </c>
       <c r="X66" s="1" t="n">
+        <v>0.12514</v>
+      </c>
+      <c r="Y66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="Y66" s="1" t="n">
+      <c r="Z66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -5781,9 +5982,12 @@
         <v>0.2294</v>
       </c>
       <c r="X67" s="1" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="Y67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="Y67" s="1" t="n">
+      <c r="Z67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -5860,9 +6064,12 @@
         <v>0.00336</v>
       </c>
       <c r="X68" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="Y68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="Y68" s="1" t="n">
+      <c r="Z68" s="1" t="n">
         <v>0.00335</v>
       </c>
     </row>
@@ -5939,9 +6146,12 @@
         <v>0.1747</v>
       </c>
       <c r="X69" s="1" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="Y69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="Y69" s="1" t="n">
+      <c r="Z69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -6018,9 +6228,12 @@
         <v>0.16365</v>
       </c>
       <c r="X70" s="1" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="Y70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="Y70" s="1" t="n">
+      <c r="Z70" s="1" t="n">
         <v>0.16358</v>
       </c>
     </row>
@@ -6097,9 +6310,12 @@
         <v>0.355</v>
       </c>
       <c r="X71" s="1" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="Y71" s="1" t="n">
         <v>0.3599</v>
       </c>
-      <c r="Y71" s="1" t="n">
+      <c r="Z71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -6176,9 +6392,12 @@
         <v>0.7068</v>
       </c>
       <c r="X72" s="1" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="Y72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="Y72" s="1" t="n">
+      <c r="Z72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -6255,9 +6474,12 @@
         <v>0.00865</v>
       </c>
       <c r="X73" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="Y73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="Y73" s="1" t="n">
+      <c r="Z73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -6334,9 +6556,12 @@
         <v>0.005969</v>
       </c>
       <c r="X74" s="1" t="n">
+        <v>0.005977</v>
+      </c>
+      <c r="Y74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="Y74" s="1" t="n">
+      <c r="Z74" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -6413,9 +6638,12 @@
         <v>0.23</v>
       </c>
       <c r="X75" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="Y75" s="1" t="n">
         <v>0.23</v>
       </c>
-      <c r="Y75" s="1" t="n">
+      <c r="Z75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -6492,9 +6720,12 @@
         <v>0.33</v>
       </c>
       <c r="X76" s="1" t="n">
-        <v>0.33</v>
+        <v>0.3342</v>
       </c>
       <c r="Y76" s="1" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="Z76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -6571,9 +6802,12 @@
         <v>0.0999</v>
       </c>
       <c r="X77" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="Y77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="Y77" s="1" t="n">
+      <c r="Z77" s="1" t="n">
         <v>0.0999</v>
       </c>
     </row>
@@ -6650,9 +6884,12 @@
         <v>0.1225</v>
       </c>
       <c r="X78" s="1" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="Y78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="Y78" s="1" t="n">
+      <c r="Z78" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -6729,9 +6966,12 @@
         <v>0.07353</v>
       </c>
       <c r="X79" s="1" t="n">
+        <v>0.07444000000000001</v>
+      </c>
+      <c r="Y79" s="1" t="n">
         <v>0.07549</v>
       </c>
-      <c r="Y79" s="1" t="n">
+      <c r="Z79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -6808,9 +7048,12 @@
         <v>0.04617</v>
       </c>
       <c r="X80" s="1" t="n">
+        <v>0.04629</v>
+      </c>
+      <c r="Y80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="Y80" s="1" t="n">
+      <c r="Z80" s="1" t="n">
         <v>0.04605</v>
       </c>
     </row>
@@ -6887,9 +7130,12 @@
         <v>0.000231</v>
       </c>
       <c r="X81" s="1" t="n">
+        <v>0.000234</v>
+      </c>
+      <c r="Y81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="Y81" s="1" t="n">
+      <c r="Z81" s="1" t="n">
         <v>0.000228</v>
       </c>
     </row>
@@ -6966,9 +7212,12 @@
         <v>8.183999999999999</v>
       </c>
       <c r="X82" s="1" t="n">
+        <v>8.207000000000001</v>
+      </c>
+      <c r="Y82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="Y82" s="1" t="n">
+      <c r="Z82" s="1" t="n">
         <v>8.183999999999999</v>
       </c>
     </row>
@@ -7045,9 +7294,12 @@
         <v>0.0005668</v>
       </c>
       <c r="X83" s="1" t="n">
+        <v>0.0005679</v>
+      </c>
+      <c r="Y83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="Y83" s="1" t="n">
+      <c r="Z83" s="1" t="n">
         <v>0.0005668</v>
       </c>
     </row>
@@ -7124,9 +7376,12 @@
         <v>0.4462</v>
       </c>
       <c r="X84" s="1" t="n">
-        <v>0.4505</v>
+        <v>0.4511</v>
       </c>
       <c r="Y84" s="1" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="Z84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -7203,9 +7458,12 @@
         <v>0.06257</v>
       </c>
       <c r="X85" s="1" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Y85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="Y85" s="1" t="n">
+      <c r="Z85" s="1" t="n">
         <v>0.0623</v>
       </c>
     </row>
@@ -7282,9 +7540,12 @@
         <v>0.05411</v>
       </c>
       <c r="X86" s="1" t="n">
+        <v>0.05421</v>
+      </c>
+      <c r="Y86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="Y86" s="1" t="n">
+      <c r="Z86" s="1" t="n">
         <v>0.05403</v>
       </c>
     </row>
@@ -7361,9 +7622,12 @@
         <v>0.003368</v>
       </c>
       <c r="X87" s="1" t="n">
+        <v>0.003349</v>
+      </c>
+      <c r="Y87" s="1" t="n">
         <v>0.003368</v>
       </c>
-      <c r="Y87" s="1" t="n">
+      <c r="Z87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -7440,9 +7704,12 @@
         <v>0.04992</v>
       </c>
       <c r="X88" s="1" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="Y88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="Y88" s="1" t="n">
+      <c r="Z88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -7519,9 +7786,12 @@
         <v>0.03178</v>
       </c>
       <c r="X89" s="1" t="n">
+        <v>0.03178</v>
+      </c>
+      <c r="Y89" s="1" t="n">
         <v>0.03198</v>
       </c>
-      <c r="Y89" s="1" t="n">
+      <c r="Z89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -7598,9 +7868,12 @@
         <v>0.3437</v>
       </c>
       <c r="X90" s="1" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="Y90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="Y90" s="1" t="n">
+      <c r="Z90" s="1" t="n">
         <v>0.3436</v>
       </c>
     </row>
@@ -7677,9 +7950,12 @@
         <v>0.07764</v>
       </c>
       <c r="X91" s="1" t="n">
+        <v>0.07826</v>
+      </c>
+      <c r="Y91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="Y91" s="1" t="n">
+      <c r="Z91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -7756,9 +8032,12 @@
         <v>0.3574</v>
       </c>
       <c r="X92" s="1" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="Y92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="Y92" s="1" t="n">
+      <c r="Z92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -7835,10 +8114,13 @@
         <v>1.9782</v>
       </c>
       <c r="X93" s="1" t="n">
+        <v>1.9564</v>
+      </c>
+      <c r="Y93" s="1" t="n">
         <v>1.9816</v>
       </c>
-      <c r="Y93" s="1" t="n">
-        <v>1.966</v>
+      <c r="Z93" s="1" t="n">
+        <v>1.9564</v>
       </c>
     </row>
     <row r="94">
@@ -7914,9 +8196,12 @@
         <v>0.2583</v>
       </c>
       <c r="X94" s="1" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="Y94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="Y94" s="1" t="n">
+      <c r="Z94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -7993,9 +8278,12 @@
         <v>0.04543</v>
       </c>
       <c r="X95" s="1" t="n">
+        <v>0.04525</v>
+      </c>
+      <c r="Y95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="Y95" s="1" t="n">
+      <c r="Z95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -8072,9 +8360,12 @@
         <v>0.006215</v>
       </c>
       <c r="X96" s="1" t="n">
+        <v>0.006119</v>
+      </c>
+      <c r="Y96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="Y96" s="1" t="n">
+      <c r="Z96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -8151,9 +8442,12 @@
         <v>0.001714</v>
       </c>
       <c r="X97" s="1" t="n">
+        <v>0.001716</v>
+      </c>
+      <c r="Y97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="Y97" s="1" t="n">
+      <c r="Z97" s="1" t="n">
         <v>0.001706</v>
       </c>
     </row>
@@ -8230,9 +8524,12 @@
         <v>5.204</v>
       </c>
       <c r="X98" s="1" t="n">
+        <v>5.256</v>
+      </c>
+      <c r="Y98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="Y98" s="1" t="n">
+      <c r="Z98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -8309,9 +8606,12 @@
         <v>0.01508</v>
       </c>
       <c r="X99" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="Y99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="Y99" s="1" t="n">
+      <c r="Z99" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -8388,10 +8688,13 @@
         <v>0.5514</v>
       </c>
       <c r="X100" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="Y100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="Y100" s="1" t="n">
-        <v>0.5508</v>
+      <c r="Z100" s="1" t="n">
+        <v>0.5501</v>
       </c>
     </row>
     <row r="101">
@@ -8467,9 +8770,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="X101" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="Y101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="Y101" s="1" t="n">
+      <c r="Z101" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -8546,9 +8852,12 @@
         <v>32.3</v>
       </c>
       <c r="X102" s="1" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="Y102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="Y102" s="1" t="n">
+      <c r="Z102" s="1" t="n">
         <v>32.25</v>
       </c>
     </row>
@@ -8625,9 +8934,12 @@
         <v>0.03179</v>
       </c>
       <c r="X103" s="1" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="Y103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="Y103" s="1" t="n">
+      <c r="Z103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -8704,9 +9016,12 @@
         <v>0.06548</v>
       </c>
       <c r="X104" s="1" t="n">
+        <v>0.06559</v>
+      </c>
+      <c r="Y104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="Y104" s="1" t="n">
+      <c r="Z104" s="1" t="n">
         <v>0.06548</v>
       </c>
     </row>
@@ -8783,9 +9098,12 @@
         <v>1.2999</v>
       </c>
       <c r="X105" s="1" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="Y105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="Y105" s="1" t="n">
+      <c r="Z105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -8862,9 +9180,12 @@
         <v>0.1189</v>
       </c>
       <c r="X106" s="1" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="Y106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="Y106" s="1" t="n">
+      <c r="Z106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -8941,9 +9262,12 @@
         <v>0.121</v>
       </c>
       <c r="X107" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Y107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="Y107" s="1" t="n">
+      <c r="Z107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -9020,9 +9344,12 @@
         <v>0.09566</v>
       </c>
       <c r="X108" s="1" t="n">
+        <v>0.09571</v>
+      </c>
+      <c r="Y108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="Y108" s="1" t="n">
+      <c r="Z108" s="1" t="n">
         <v>0.09566</v>
       </c>
     </row>
@@ -9099,9 +9426,12 @@
         <v>0.13948</v>
       </c>
       <c r="X109" s="1" t="n">
+        <v>0.13954</v>
+      </c>
+      <c r="Y109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="Y109" s="1" t="n">
+      <c r="Z109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -9178,9 +9508,12 @@
         <v>5.561</v>
       </c>
       <c r="X110" s="1" t="n">
-        <v>5.578</v>
+        <v>5.583</v>
       </c>
       <c r="Y110" s="1" t="n">
+        <v>5.583</v>
+      </c>
+      <c r="Z110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -9257,9 +9590,12 @@
         <v>1.096</v>
       </c>
       <c r="X111" s="1" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="Y111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="Y111" s="1" t="n">
+      <c r="Z111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -9336,9 +9672,12 @@
         <v>0.028741</v>
       </c>
       <c r="X112" s="1" t="n">
+        <v>0.028713</v>
+      </c>
+      <c r="Y112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="Y112" s="1" t="n">
+      <c r="Z112" s="1" t="n">
         <v>0.028712</v>
       </c>
     </row>
@@ -9415,9 +9754,12 @@
         <v>1.862</v>
       </c>
       <c r="X113" s="1" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="Y113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="Y113" s="1" t="n">
+      <c r="Z113" s="1" t="n">
         <v>1.859</v>
       </c>
     </row>
@@ -9494,9 +9836,12 @@
         <v>0.0584</v>
       </c>
       <c r="X114" s="1" t="n">
+        <v>0.05874</v>
+      </c>
+      <c r="Y114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="Y114" s="1" t="n">
+      <c r="Z114" s="1" t="n">
         <v>0.0584</v>
       </c>
     </row>
@@ -9573,10 +9918,13 @@
         <v>0.12718</v>
       </c>
       <c r="X115" s="1" t="n">
+        <v>0.12712</v>
+      </c>
+      <c r="Y115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="Y115" s="1" t="n">
-        <v>0.12718</v>
+      <c r="Z115" s="1" t="n">
+        <v>0.12712</v>
       </c>
     </row>
     <row r="116">
@@ -9652,9 +10000,12 @@
         <v>1.0951</v>
       </c>
       <c r="X116" s="1" t="n">
+        <v>1.0957</v>
+      </c>
+      <c r="Y116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="Y116" s="1" t="n">
+      <c r="Z116" s="1" t="n">
         <v>1.0937</v>
       </c>
     </row>
@@ -9731,9 +10082,12 @@
         <v>0.1543</v>
       </c>
       <c r="X117" s="1" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="Y117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="Y117" s="1" t="n">
+      <c r="Z117" s="1" t="n">
         <v>0.1484</v>
       </c>
     </row>
@@ -9810,9 +10164,12 @@
         <v>0.1575</v>
       </c>
       <c r="X118" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="Y118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="Y118" s="1" t="n">
+      <c r="Z118" s="1" t="n">
         <v>0.1572</v>
       </c>
     </row>
@@ -9889,9 +10246,12 @@
         <v>0.0478</v>
       </c>
       <c r="X119" s="1" t="n">
-        <v>0.0478</v>
+        <v>0.04783</v>
       </c>
       <c r="Y119" s="1" t="n">
+        <v>0.04783</v>
+      </c>
+      <c r="Z119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -9968,9 +10328,12 @@
         <v>3.014</v>
       </c>
       <c r="X120" s="1" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="Y120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="Y120" s="1" t="n">
+      <c r="Z120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -10047,9 +10410,12 @@
         <v>0.2972</v>
       </c>
       <c r="X121" s="1" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="Y121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="Y121" s="1" t="n">
+      <c r="Z121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -10126,9 +10492,12 @@
         <v>0.5767</v>
       </c>
       <c r="X122" s="1" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="Y122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="Y122" s="1" t="n">
+      <c r="Z122" s="1" t="n">
         <v>0.5767</v>
       </c>
     </row>
@@ -10205,9 +10574,12 @@
         <v>0.01247</v>
       </c>
       <c r="X123" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="Y123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="Y123" s="1" t="n">
+      <c r="Z123" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -10284,9 +10656,12 @@
         <v>0.1573</v>
       </c>
       <c r="X124" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="Y124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="Y124" s="1" t="n">
+      <c r="Z124" s="1" t="n">
         <v>0.1566</v>
       </c>
     </row>
@@ -10363,9 +10738,12 @@
         <v>0.001788</v>
       </c>
       <c r="X125" s="1" t="n">
-        <v>0.001788</v>
+        <v>0.00179</v>
       </c>
       <c r="Y125" s="1" t="n">
+        <v>0.00179</v>
+      </c>
+      <c r="Z125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -10442,9 +10820,12 @@
         <v>0.0004808</v>
       </c>
       <c r="X126" s="1" t="n">
+        <v>0.0004829</v>
+      </c>
+      <c r="Y126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="Y126" s="1" t="n">
+      <c r="Z126" s="1" t="n">
         <v>0.0004808</v>
       </c>
     </row>
@@ -10521,9 +10902,12 @@
         <v>0.02924</v>
       </c>
       <c r="X127" s="1" t="n">
+        <v>0.02925</v>
+      </c>
+      <c r="Y127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="Y127" s="1" t="n">
+      <c r="Z127" s="1" t="n">
         <v>0.02922</v>
       </c>
     </row>
@@ -10600,9 +10984,12 @@
         <v>0.0412</v>
       </c>
       <c r="X128" s="1" t="n">
+        <v>0.04124</v>
+      </c>
+      <c r="Y128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="Y128" s="1" t="n">
+      <c r="Z128" s="1" t="n">
         <v>0.04116</v>
       </c>
     </row>
@@ -10679,9 +11066,12 @@
         <v>0.04935</v>
       </c>
       <c r="X129" s="1" t="n">
-        <v>0.04935</v>
+        <v>0.04971</v>
       </c>
       <c r="Y129" s="1" t="n">
+        <v>0.04971</v>
+      </c>
+      <c r="Z129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -10758,9 +11148,12 @@
         <v>1.21e-05</v>
       </c>
       <c r="X130" s="1" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="Y130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="Y130" s="1" t="n">
+      <c r="Z130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -10837,9 +11230,12 @@
         <v>7.3e-06</v>
       </c>
       <c r="X131" s="1" t="n">
+        <v>7.3e-06</v>
+      </c>
+      <c r="Y131" s="1" t="n">
         <v>7.5e-06</v>
       </c>
-      <c r="Y131" s="1" t="n">
+      <c r="Z131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -10916,9 +11312,12 @@
         <v>0.007</v>
       </c>
       <c r="X132" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="Y132" s="1" t="n">
         <v>0.00705</v>
       </c>
-      <c r="Y132" s="1" t="n">
+      <c r="Z132" s="1" t="n">
         <v>0.00697</v>
       </c>
     </row>
@@ -10995,9 +11394,12 @@
         <v>0.0964</v>
       </c>
       <c r="X133" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="Y133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="Y133" s="1" t="n">
+      <c r="Z133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -11074,9 +11476,12 @@
         <v>0.0004104</v>
       </c>
       <c r="X134" s="1" t="n">
-        <v>0.0004114</v>
+        <v>0.0004116</v>
       </c>
       <c r="Y134" s="1" t="n">
+        <v>0.0004116</v>
+      </c>
+      <c r="Z134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -11153,9 +11558,12 @@
         <v>0.08193</v>
       </c>
       <c r="X135" s="1" t="n">
+        <v>0.08196000000000001</v>
+      </c>
+      <c r="Y135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="Y135" s="1" t="n">
+      <c r="Z135" s="1" t="n">
         <v>0.08148</v>
       </c>
     </row>
@@ -11232,9 +11640,12 @@
         <v>0.007786</v>
       </c>
       <c r="X136" s="1" t="n">
+        <v>0.007752</v>
+      </c>
+      <c r="Y136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="Y136" s="1" t="n">
+      <c r="Z136" s="1" t="n">
         <v>0.007748</v>
       </c>
     </row>
@@ -11311,9 +11722,12 @@
         <v>0.0007982</v>
       </c>
       <c r="X137" s="1" t="n">
+        <v>0.0007983000000000001</v>
+      </c>
+      <c r="Y137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="Y137" s="1" t="n">
+      <c r="Z137" s="1" t="n">
         <v>0.0007981</v>
       </c>
     </row>
@@ -11390,9 +11804,12 @@
         <v>0.1456</v>
       </c>
       <c r="X138" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="Y138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="Y138" s="1" t="n">
+      <c r="Z138" s="1" t="n">
         <v>0.1453</v>
       </c>
     </row>
@@ -11469,10 +11886,13 @@
         <v>0.006661</v>
       </c>
       <c r="X139" s="1" t="n">
+        <v>0.006649</v>
+      </c>
+      <c r="Y139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="Y139" s="1" t="n">
-        <v>0.006661</v>
+      <c r="Z139" s="1" t="n">
+        <v>0.006649</v>
       </c>
     </row>
     <row r="140">
@@ -11548,9 +11968,12 @@
         <v>0.01374</v>
       </c>
       <c r="X140" s="1" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="Y140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="Y140" s="1" t="n">
+      <c r="Z140" s="1" t="n">
         <v>0.01373</v>
       </c>
     </row>
@@ -11627,10 +12050,13 @@
         <v>0.09591</v>
       </c>
       <c r="X141" s="1" t="n">
+        <v>0.09583999999999999</v>
+      </c>
+      <c r="Y141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="Y141" s="1" t="n">
-        <v>0.09591</v>
+      <c r="Z141" s="1" t="n">
+        <v>0.09583999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -11706,9 +12132,12 @@
         <v>0.05416</v>
       </c>
       <c r="X142" s="1" t="n">
+        <v>0.05413</v>
+      </c>
+      <c r="Y142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="Y142" s="1" t="n">
+      <c r="Z142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -11785,9 +12214,12 @@
         <v>0.3223</v>
       </c>
       <c r="X143" s="1" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="Y143" s="1" t="n">
+      <c r="Z143" s="1" t="n">
         <v>0.3219</v>
       </c>
     </row>
@@ -11864,9 +12296,12 @@
         <v>0.02557</v>
       </c>
       <c r="X144" s="1" t="n">
+        <v>0.02559</v>
+      </c>
+      <c r="Y144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="Y144" s="1" t="n">
+      <c r="Z144" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -11943,9 +12378,12 @@
         <v>0.2368</v>
       </c>
       <c r="X145" s="1" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="Y145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="Y145" s="1" t="n">
+      <c r="Z145" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -12022,9 +12460,12 @@
         <v>0.007021</v>
       </c>
       <c r="X146" s="1" t="n">
+        <v>0.007025</v>
+      </c>
+      <c r="Y146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="Y146" s="1" t="n">
+      <c r="Z146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -12101,10 +12542,13 @@
         <v>0.08608</v>
       </c>
       <c r="X147" s="1" t="n">
+        <v>0.08579000000000001</v>
+      </c>
+      <c r="Y147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="Y147" s="1" t="n">
-        <v>0.08597</v>
+      <c r="Z147" s="1" t="n">
+        <v>0.08579000000000001</v>
       </c>
     </row>
     <row r="148">
@@ -12180,9 +12624,12 @@
         <v>0.0528</v>
       </c>
       <c r="X148" s="1" t="n">
+        <v>0.05252</v>
+      </c>
+      <c r="Y148" s="1" t="n">
         <v>0.05289</v>
       </c>
-      <c r="Y148" s="1" t="n">
+      <c r="Z148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -12259,9 +12706,12 @@
         <v>0.02391</v>
       </c>
       <c r="X149" s="1" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="Y149" s="1" t="n">
         <v>0.02402</v>
       </c>
-      <c r="Y149" s="1" t="n">
+      <c r="Z149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -12338,9 +12788,12 @@
         <v>0.08628</v>
       </c>
       <c r="X150" s="1" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="Y150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="Y150" s="1" t="n">
+      <c r="Z150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -12417,10 +12870,13 @@
         <v>0.02308</v>
       </c>
       <c r="X151" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="Y151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="Y151" s="1" t="n">
-        <v>0.02308</v>
+      <c r="Z151" s="1" t="n">
+        <v>0.02306</v>
       </c>
     </row>
     <row r="152">
@@ -12496,9 +12952,12 @@
         <v>0.02515</v>
       </c>
       <c r="X152" s="1" t="n">
+        <v>0.02519</v>
+      </c>
+      <c r="Y152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="Y152" s="1" t="n">
+      <c r="Z152" s="1" t="n">
         <v>0.02515</v>
       </c>
     </row>
@@ -12575,9 +13034,12 @@
         <v>0.000212</v>
       </c>
       <c r="X153" s="1" t="n">
+        <v>0.0002116</v>
+      </c>
+      <c r="Y153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="Y153" s="1" t="n">
+      <c r="Z153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -12654,9 +13116,12 @@
         <v>0.4422</v>
       </c>
       <c r="X154" s="1" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="Y154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="Y154" s="1" t="n">
+      <c r="Z154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -12733,9 +13198,12 @@
         <v>0.06752</v>
       </c>
       <c r="X155" s="1" t="n">
+        <v>0.06732</v>
+      </c>
+      <c r="Y155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="Y155" s="1" t="n">
+      <c r="Z155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -12812,9 +13280,12 @@
         <v>0.13384</v>
       </c>
       <c r="X156" s="1" t="n">
+        <v>0.13246</v>
+      </c>
+      <c r="Y156" s="1" t="n">
         <v>0.13403</v>
       </c>
-      <c r="Y156" s="1" t="n">
+      <c r="Z156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -12891,10 +13362,13 @@
         <v>0.4818</v>
       </c>
       <c r="X157" s="1" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="Y157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="Y157" s="1" t="n">
-        <v>0.4818</v>
+      <c r="Z157" s="1" t="n">
+        <v>0.4815</v>
       </c>
     </row>
     <row r="158">
@@ -12970,9 +13444,12 @@
         <v>0.4473</v>
       </c>
       <c r="X158" s="1" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="Y158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="Y158" s="1" t="n">
+      <c r="Z158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -13049,10 +13526,13 @@
         <v>0.007419</v>
       </c>
       <c r="X159" s="1" t="n">
+        <v>0.007406</v>
+      </c>
+      <c r="Y159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="Y159" s="1" t="n">
-        <v>0.007417</v>
+      <c r="Z159" s="1" t="n">
+        <v>0.007406</v>
       </c>
     </row>
     <row r="160">
@@ -13128,9 +13608,12 @@
         <v>0.004653</v>
       </c>
       <c r="X160" s="1" t="n">
+        <v>0.004658</v>
+      </c>
+      <c r="Y160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="Y160" s="1" t="n">
+      <c r="Z160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -13207,9 +13690,12 @@
         <v>0.004298</v>
       </c>
       <c r="X161" s="1" t="n">
+        <v>0.004303</v>
+      </c>
+      <c r="Y161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="Y161" s="1" t="n">
+      <c r="Z161" s="1" t="n">
         <v>0.004276</v>
       </c>
     </row>
@@ -13286,9 +13772,12 @@
         <v>0.0951</v>
       </c>
       <c r="X162" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="Y162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="Y162" s="1" t="n">
+      <c r="Z162" s="1" t="n">
         <v>0.0951</v>
       </c>
     </row>
@@ -13365,9 +13854,12 @@
         <v>0.2846</v>
       </c>
       <c r="X163" s="1" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="Y163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="Y163" s="1" t="n">
+      <c r="Z163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -13444,9 +13936,12 @@
         <v>0.1133</v>
       </c>
       <c r="X164" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="Y164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="Y164" s="1" t="n">
+      <c r="Z164" s="1" t="n">
         <v>0.1131</v>
       </c>
     </row>
@@ -13523,9 +14018,12 @@
         <v>0.1748</v>
       </c>
       <c r="X165" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="Y165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="Y165" s="1" t="n">
+      <c r="Z165" s="1" t="n">
         <v>0.1747</v>
       </c>
     </row>
@@ -13602,9 +14100,12 @@
         <v>0.01015</v>
       </c>
       <c r="X166" s="1" t="n">
+        <v>0.01006</v>
+      </c>
+      <c r="Y166" s="1" t="n">
         <v>0.01055</v>
       </c>
-      <c r="Y166" s="1" t="n">
+      <c r="Z166" s="1" t="n">
         <v>0.01004</v>
       </c>
     </row>
@@ -13681,9 +14182,12 @@
         <v>1.813</v>
       </c>
       <c r="X167" s="1" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="Y167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="Y167" s="1" t="n">
+      <c r="Z167" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -13760,9 +14264,12 @@
         <v>1.335</v>
       </c>
       <c r="X168" s="1" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="Y168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="Y168" s="1" t="n">
+      <c r="Z168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -13839,9 +14346,12 @@
         <v>0.007287</v>
       </c>
       <c r="X169" s="1" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="Y169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="Y169" s="1" t="n">
+      <c r="Z169" s="1" t="n">
         <v>0.007276</v>
       </c>
     </row>
@@ -13918,9 +14428,12 @@
         <v>0.0115</v>
       </c>
       <c r="X170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="Y170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="Y170" s="1" t="n">
+      <c r="Z170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -13997,9 +14510,12 @@
         <v>0.005737</v>
       </c>
       <c r="X171" s="1" t="n">
+        <v>0.005751</v>
+      </c>
+      <c r="Y171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="Y171" s="1" t="n">
+      <c r="Z171" s="1" t="n">
         <v>0.005737</v>
       </c>
     </row>
@@ -14076,9 +14592,12 @@
         <v>0.14899</v>
       </c>
       <c r="X172" s="1" t="n">
+        <v>0.14875</v>
+      </c>
+      <c r="Y172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="Y172" s="1" t="n">
+      <c r="Z172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -14155,9 +14674,12 @@
         <v>4.869</v>
       </c>
       <c r="X173" s="1" t="n">
+        <v>4.892</v>
+      </c>
+      <c r="Y173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="Y173" s="1" t="n">
+      <c r="Z173" s="1" t="n">
         <v>4.868</v>
       </c>
     </row>
@@ -14234,9 +14756,12 @@
         <v>0.07792</v>
       </c>
       <c r="X174" s="1" t="n">
+        <v>0.07795000000000001</v>
+      </c>
+      <c r="Y174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="Y174" s="1" t="n">
+      <c r="Z174" s="1" t="n">
         <v>0.07785</v>
       </c>
     </row>
@@ -14313,9 +14838,12 @@
         <v>0.007403</v>
       </c>
       <c r="X175" s="1" t="n">
+        <v>0.00742</v>
+      </c>
+      <c r="Y175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="Y175" s="1" t="n">
+      <c r="Z175" s="1" t="n">
         <v>0.007403</v>
       </c>
     </row>
@@ -14392,9 +14920,12 @@
         <v>0.1983</v>
       </c>
       <c r="X176" s="1" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="Y176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="Y176" s="1" t="n">
+      <c r="Z176" s="1" t="n">
         <v>0.1983</v>
       </c>
     </row>
@@ -14471,9 +15002,12 @@
         <v>0.05185</v>
       </c>
       <c r="X177" s="1" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="Y177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="Y177" s="1" t="n">
+      <c r="Z177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -14550,10 +15084,13 @@
         <v>0.05442</v>
       </c>
       <c r="X178" s="1" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="Y178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="Y178" s="1" t="n">
-        <v>0.05442</v>
+      <c r="Z178" s="1" t="n">
+        <v>0.0544</v>
       </c>
     </row>
     <row r="179">
@@ -14629,9 +15166,12 @@
         <v>0.02332</v>
       </c>
       <c r="X179" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="Y179" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="Y179" s="1" t="n">
+      <c r="Z179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -14708,9 +15248,12 @@
         <v>0.6973</v>
       </c>
       <c r="X180" s="1" t="n">
+        <v>0.6973</v>
+      </c>
+      <c r="Y180" s="1" t="n">
         <v>0.6994</v>
       </c>
-      <c r="Y180" s="1" t="n">
+      <c r="Z180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -14787,9 +15330,12 @@
         <v>0.0003741</v>
       </c>
       <c r="X181" s="1" t="n">
+        <v>0.0003744</v>
+      </c>
+      <c r="Y181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="Y181" s="1" t="n">
+      <c r="Z181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -14866,9 +15412,12 @@
         <v>0.01264</v>
       </c>
       <c r="X182" s="1" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="Y182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="Y182" s="1" t="n">
+      <c r="Z182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -14945,9 +15494,12 @@
         <v>4.208</v>
       </c>
       <c r="X183" s="1" t="n">
+        <v>4.192</v>
+      </c>
+      <c r="Y183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="Y183" s="1" t="n">
+      <c r="Z183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -15024,10 +15576,13 @@
         <v>0.2335</v>
       </c>
       <c r="X184" s="1" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="Y184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="Y184" s="1" t="n">
-        <v>0.2335</v>
+      <c r="Z184" s="1" t="n">
+        <v>0.2331</v>
       </c>
     </row>
     <row r="185">
@@ -15103,9 +15658,12 @@
         <v>0.03679</v>
       </c>
       <c r="X185" s="1" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="Y185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="Y185" s="1" t="n">
+      <c r="Z185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -15182,9 +15740,12 @@
         <v>0.11545</v>
       </c>
       <c r="X186" s="1" t="n">
+        <v>0.11546</v>
+      </c>
+      <c r="Y186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="Y186" s="1" t="n">
+      <c r="Z186" s="1" t="n">
         <v>0.11535</v>
       </c>
     </row>
@@ -15261,9 +15822,12 @@
         <v>0.009056</v>
       </c>
       <c r="X187" s="1" t="n">
+        <v>0.009063</v>
+      </c>
+      <c r="Y187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="Y187" s="1" t="n">
+      <c r="Z187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -15340,9 +15904,12 @@
         <v>0.0974</v>
       </c>
       <c r="X188" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="Y188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="Y188" s="1" t="n">
+      <c r="Z188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -15419,9 +15986,12 @@
         <v>0.02713</v>
       </c>
       <c r="X189" s="1" t="n">
+        <v>0.02722</v>
+      </c>
+      <c r="Y189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="Y189" s="1" t="n">
+      <c r="Z189" s="1" t="n">
         <v>0.02702</v>
       </c>
     </row>
@@ -15498,9 +16068,12 @@
         <v>0.00865</v>
       </c>
       <c r="X190" s="1" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="Y190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="Y190" s="1" t="n">
+      <c r="Z190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -15577,9 +16150,12 @@
         <v>0.001957</v>
       </c>
       <c r="X191" s="1" t="n">
-        <v>0.001961</v>
+        <v>0.001964</v>
       </c>
       <c r="Y191" s="1" t="n">
+        <v>0.001964</v>
+      </c>
+      <c r="Z191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -15656,9 +16232,12 @@
         <v>0.0998</v>
       </c>
       <c r="X192" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="Y192" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="Y192" s="1" t="n">
+      <c r="Z192" s="1" t="n">
         <v>0.09959999999999999</v>
       </c>
     </row>
@@ -15735,9 +16314,12 @@
         <v>0.0234</v>
       </c>
       <c r="X193" s="1" t="n">
+        <v>0.02338</v>
+      </c>
+      <c r="Y193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="Y193" s="1" t="n">
+      <c r="Z193" s="1" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -15814,9 +16396,12 @@
         <v>0.0134</v>
       </c>
       <c r="X194" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="Y194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="Y194" s="1" t="n">
+      <c r="Z194" s="1" t="n">
         <v>0.0134</v>
       </c>
     </row>
@@ -15893,9 +16478,12 @@
         <v>0.02071</v>
       </c>
       <c r="X195" s="1" t="n">
+        <v>0.02078</v>
+      </c>
+      <c r="Y195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="Y195" s="1" t="n">
+      <c r="Z195" s="1" t="n">
         <v>0.02071</v>
       </c>
     </row>
@@ -15972,9 +16560,12 @@
         <v>0.17687</v>
       </c>
       <c r="X196" s="1" t="n">
+        <v>0.17567</v>
+      </c>
+      <c r="Y196" s="1" t="n">
         <v>0.17767</v>
       </c>
-      <c r="Y196" s="1" t="n">
+      <c r="Z196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -16051,10 +16642,13 @@
         <v>0.007306</v>
       </c>
       <c r="X197" s="1" t="n">
+        <v>0.007264</v>
+      </c>
+      <c r="Y197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="Y197" s="1" t="n">
-        <v>0.007277</v>
+      <c r="Z197" s="1" t="n">
+        <v>0.007264</v>
       </c>
     </row>
     <row r="198">
@@ -16130,9 +16724,12 @@
         <v>0.01899</v>
       </c>
       <c r="X198" s="1" t="n">
+        <v>0.01902</v>
+      </c>
+      <c r="Y198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="Y198" s="1" t="n">
+      <c r="Z198" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -16209,9 +16806,12 @@
         <v>0.01656</v>
       </c>
       <c r="X199" s="1" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="Y199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="Y199" s="1" t="n">
+      <c r="Z199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -16288,9 +16888,12 @@
         <v>0.2974</v>
       </c>
       <c r="X200" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Y200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="Y200" s="1" t="n">
+      <c r="Z200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -16367,9 +16970,12 @@
         <v>0.006233</v>
       </c>
       <c r="X201" s="1" t="n">
+        <v>0.006236</v>
+      </c>
+      <c r="Y201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="Y201" s="1" t="n">
+      <c r="Z201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -16446,9 +17052,12 @@
         <v>0.000438</v>
       </c>
       <c r="X202" s="1" t="n">
+        <v>0.0004384</v>
+      </c>
+      <c r="Y202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="Y202" s="1" t="n">
+      <c r="Z202" s="1" t="n">
         <v>0.0004378</v>
       </c>
     </row>
@@ -16525,10 +17134,13 @@
         <v>0.007254</v>
       </c>
       <c r="X203" s="1" t="n">
+        <v>0.007241</v>
+      </c>
+      <c r="Y203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="Y203" s="1" t="n">
-        <v>0.007245</v>
+      <c r="Z203" s="1" t="n">
+        <v>0.007241</v>
       </c>
     </row>
     <row r="204">
@@ -16604,9 +17216,12 @@
         <v>0.1301</v>
       </c>
       <c r="X204" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Y204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="Y204" s="1" t="n">
+      <c r="Z204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -16683,9 +17298,12 @@
         <v>0.01419</v>
       </c>
       <c r="X205" s="1" t="n">
+        <v>0.01415</v>
+      </c>
+      <c r="Y205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="Y205" s="1" t="n">
+      <c r="Z205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -16762,10 +17380,13 @@
         <v>0.003567</v>
       </c>
       <c r="X206" s="1" t="n">
+        <v>0.003551</v>
+      </c>
+      <c r="Y206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="Y206" s="1" t="n">
-        <v>0.00356</v>
+      <c r="Z206" s="1" t="n">
+        <v>0.003551</v>
       </c>
     </row>
     <row r="207">
@@ -16841,10 +17462,13 @@
         <v>0.05887</v>
       </c>
       <c r="X207" s="1" t="n">
+        <v>0.05873</v>
+      </c>
+      <c r="Y207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="Y207" s="1" t="n">
-        <v>0.05883</v>
+      <c r="Z207" s="1" t="n">
+        <v>0.05873</v>
       </c>
     </row>
     <row r="208">
@@ -16920,9 +17544,12 @@
         <v>15.56</v>
       </c>
       <c r="X208" s="1" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="Y208" s="1" t="n">
         <v>15.56</v>
       </c>
-      <c r="Y208" s="1" t="n">
+      <c r="Z208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -16999,10 +17626,13 @@
         <v>5184.5</v>
       </c>
       <c r="X209" s="1" t="n">
+        <v>5181.4</v>
+      </c>
+      <c r="Y209" s="1" t="n">
         <v>5194.4</v>
       </c>
-      <c r="Y209" s="1" t="n">
-        <v>5183.4</v>
+      <c r="Z209" s="1" t="n">
+        <v>5181.4</v>
       </c>
     </row>
     <row r="210">
@@ -17078,9 +17708,12 @@
         <v>0.11981</v>
       </c>
       <c r="X210" s="1" t="n">
+        <v>0.11979</v>
+      </c>
+      <c r="Y210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="Y210" s="1" t="n">
+      <c r="Z210" s="1" t="n">
         <v>0.11941</v>
       </c>
     </row>
@@ -17157,10 +17790,13 @@
         <v>0.1812</v>
       </c>
       <c r="X211" s="1" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="Y211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="Y211" s="1" t="n">
-        <v>0.1802</v>
+      <c r="Z211" s="1" t="n">
+        <v>0.1801</v>
       </c>
     </row>
     <row r="212">
@@ -17236,9 +17872,12 @@
         <v>0.0298</v>
       </c>
       <c r="X212" s="1" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="Y212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="Y212" s="1" t="n">
+      <c r="Z212" s="1" t="n">
         <v>0.0297</v>
       </c>
     </row>
@@ -17315,9 +17954,12 @@
         <v>1.3975</v>
       </c>
       <c r="X213" s="1" t="n">
-        <v>1.3997</v>
+        <v>1.3999</v>
       </c>
       <c r="Y213" s="1" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="Z213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -17394,9 +18036,12 @@
         <v>0.0565</v>
       </c>
       <c r="X214" s="1" t="n">
+        <v>0.05661</v>
+      </c>
+      <c r="Y214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="Y214" s="1" t="n">
+      <c r="Z214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -17473,9 +18118,12 @@
         <v>0.0438</v>
       </c>
       <c r="X215" s="1" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="Y215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="Y215" s="1" t="n">
+      <c r="Z215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -17552,9 +18200,12 @@
         <v>0.15118</v>
       </c>
       <c r="X216" s="1" t="n">
+        <v>0.15096</v>
+      </c>
+      <c r="Y216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="Y216" s="1" t="n">
+      <c r="Z216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -17634,6 +18285,9 @@
         <v>0.074</v>
       </c>
       <c r="Y217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="Z217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -17710,9 +18364,12 @@
         <v>0.00267</v>
       </c>
       <c r="X218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="Y218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="Y218" s="1" t="n">
+      <c r="Z218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -17789,9 +18446,12 @@
         <v>0.01696</v>
       </c>
       <c r="X219" s="1" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="Y219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="Y219" s="1" t="n">
+      <c r="Z219" s="1" t="n">
         <v>0.01693</v>
       </c>
     </row>
@@ -17868,9 +18528,12 @@
         <v>0.05513</v>
       </c>
       <c r="X220" s="1" t="n">
+        <v>0.05522</v>
+      </c>
+      <c r="Y220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="Y220" s="1" t="n">
+      <c r="Z220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -17947,9 +18610,12 @@
         <v>0.02186</v>
       </c>
       <c r="X221" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="Y221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="Y221" s="1" t="n">
+      <c r="Z221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -18026,9 +18692,12 @@
         <v>0.009259999999999999</v>
       </c>
       <c r="X222" s="1" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="Y222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="Y222" s="1" t="n">
+      <c r="Z222" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -18105,9 +18774,12 @@
         <v>0.0164</v>
       </c>
       <c r="X223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="Y223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="Y223" s="1" t="n">
+      <c r="Z223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -18184,9 +18856,12 @@
         <v>0.03821</v>
       </c>
       <c r="X224" s="1" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="Y224" s="1" t="n">
         <v>0.03846</v>
       </c>
-      <c r="Y224" s="1" t="n">
+      <c r="Z224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -18263,9 +18938,12 @@
         <v>0.001517</v>
       </c>
       <c r="X225" s="1" t="n">
+        <v>0.001519</v>
+      </c>
+      <c r="Y225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="Y225" s="1" t="n">
+      <c r="Z225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -18342,9 +19020,12 @@
         <v>27.03</v>
       </c>
       <c r="X226" s="1" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="Y226" s="1" t="n">
         <v>27.31</v>
       </c>
-      <c r="Y226" s="1" t="n">
+      <c r="Z226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -18421,9 +19102,12 @@
         <v>0.07020999999999999</v>
       </c>
       <c r="X227" s="1" t="n">
+        <v>0.07006999999999999</v>
+      </c>
+      <c r="Y227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="Y227" s="1" t="n">
+      <c r="Z227" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -18500,9 +19184,12 @@
         <v>0.3112</v>
       </c>
       <c r="X228" s="1" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="Y228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="Y228" s="1" t="n">
+      <c r="Z228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -18579,9 +19266,12 @@
         <v>18.36</v>
       </c>
       <c r="X229" s="1" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="Y229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="Y229" s="1" t="n">
+      <c r="Z229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -18658,9 +19348,12 @@
         <v>0.01915</v>
       </c>
       <c r="X230" s="1" t="n">
+        <v>0.01917</v>
+      </c>
+      <c r="Y230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="Y230" s="1" t="n">
+      <c r="Z230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -18737,9 +19430,12 @@
         <v>0.01213</v>
       </c>
       <c r="X231" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="Y231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="Y231" s="1" t="n">
+      <c r="Z231" s="1" t="n">
         <v>0.01212</v>
       </c>
     </row>
@@ -18816,9 +19512,12 @@
         <v>0.2273</v>
       </c>
       <c r="X232" s="1" t="n">
+        <v>0.2277</v>
+      </c>
+      <c r="Y232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="Y232" s="1" t="n">
+      <c r="Z232" s="1" t="n">
         <v>0.2269</v>
       </c>
     </row>
@@ -18895,10 +19594,13 @@
         <v>0.07078</v>
       </c>
       <c r="X233" s="1" t="n">
+        <v>0.07068000000000001</v>
+      </c>
+      <c r="Y233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="Y233" s="1" t="n">
-        <v>0.07073</v>
+      <c r="Z233" s="1" t="n">
+        <v>0.07068000000000001</v>
       </c>
     </row>
     <row r="234">
@@ -18974,9 +19676,12 @@
         <v>0.1703</v>
       </c>
       <c r="X234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="Y234" s="1" t="n">
         <v>0.1709</v>
       </c>
-      <c r="Y234" s="1" t="n">
+      <c r="Z234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -19053,9 +19758,12 @@
         <v>0.0251</v>
       </c>
       <c r="X235" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="Y235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="Y235" s="1" t="n">
+      <c r="Z235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -19132,10 +19840,13 @@
         <v>0.03</v>
       </c>
       <c r="X236" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="Y236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="Y236" s="1" t="n">
-        <v>0.02993</v>
+      <c r="Z236" s="1" t="n">
+        <v>0.02991</v>
       </c>
     </row>
     <row r="237">
@@ -19211,9 +19922,12 @@
         <v>2.046</v>
       </c>
       <c r="X237" s="1" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="Y237" s="1" t="n">
         <v>2.049</v>
       </c>
-      <c r="Y237" s="1" t="n">
+      <c r="Z237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -19290,9 +20004,12 @@
         <v>0.4174</v>
       </c>
       <c r="X238" s="1" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="Y238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="Y238" s="1" t="n">
+      <c r="Z238" s="1" t="n">
         <v>0.4172</v>
       </c>
     </row>
@@ -19369,9 +20086,12 @@
         <v>0.03297</v>
       </c>
       <c r="X239" s="1" t="n">
+        <v>0.03301</v>
+      </c>
+      <c r="Y239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="Y239" s="1" t="n">
+      <c r="Z239" s="1" t="n">
         <v>0.03297</v>
       </c>
     </row>
@@ -19448,9 +20168,12 @@
         <v>0.03402</v>
       </c>
       <c r="X240" s="1" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="Y240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="Y240" s="1" t="n">
+      <c r="Z240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -19527,9 +20250,12 @@
         <v>0.0007452</v>
       </c>
       <c r="X241" s="1" t="n">
+        <v>0.0007483</v>
+      </c>
+      <c r="Y241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="Y241" s="1" t="n">
+      <c r="Z241" s="1" t="n">
         <v>0.0007452</v>
       </c>
     </row>
@@ -19606,9 +20332,12 @@
         <v>0.1815</v>
       </c>
       <c r="X242" s="1" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="Y242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="Y242" s="1" t="n">
+      <c r="Z242" s="1" t="n">
         <v>0.1815</v>
       </c>
     </row>
@@ -19685,10 +20414,13 @@
         <v>0.014696</v>
       </c>
       <c r="X243" s="1" t="n">
+        <v>0.014685</v>
+      </c>
+      <c r="Y243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="Y243" s="1" t="n">
-        <v>0.014696</v>
+      <c r="Z243" s="1" t="n">
+        <v>0.014685</v>
       </c>
     </row>
     <row r="244">
@@ -19764,9 +20496,12 @@
         <v>3.01e-05</v>
       </c>
       <c r="X244" s="1" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="Y244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="Y244" s="1" t="n">
+      <c r="Z244" s="1" t="n">
         <v>2.99e-05</v>
       </c>
     </row>
@@ -19843,9 +20578,12 @@
         <v>0.03513</v>
       </c>
       <c r="X245" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="Y245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="Y245" s="1" t="n">
+      <c r="Z245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -19922,10 +20660,13 @@
         <v>0.07982</v>
       </c>
       <c r="X246" s="1" t="n">
+        <v>0.07971</v>
+      </c>
+      <c r="Y246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="Y246" s="1" t="n">
-        <v>0.07982</v>
+      <c r="Z246" s="1" t="n">
+        <v>0.07971</v>
       </c>
     </row>
     <row r="247">
@@ -20001,9 +20742,12 @@
         <v>0.00707</v>
       </c>
       <c r="X247" s="1" t="n">
+        <v>0.007084</v>
+      </c>
+      <c r="Y247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="Y247" s="1" t="n">
+      <c r="Z247" s="1" t="n">
         <v>0.00707</v>
       </c>
     </row>
@@ -20080,9 +20824,12 @@
         <v>0.09372</v>
       </c>
       <c r="X248" s="1" t="n">
+        <v>0.09428</v>
+      </c>
+      <c r="Y248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="Y248" s="1" t="n">
+      <c r="Z248" s="1" t="n">
         <v>0.09239</v>
       </c>
     </row>
@@ -20159,9 +20906,12 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="X249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Y249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="Y249" s="1" t="n">
+      <c r="Z249" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
     </row>
@@ -20238,9 +20988,12 @@
         <v>0.03478</v>
       </c>
       <c r="X250" s="1" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="Y250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="Y250" s="1" t="n">
+      <c r="Z250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -20317,9 +21070,12 @@
         <v>0.03859</v>
       </c>
       <c r="X251" s="1" t="n">
+        <v>0.03868</v>
+      </c>
+      <c r="Y251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="Y251" s="1" t="n">
+      <c r="Z251" s="1" t="n">
         <v>0.03859</v>
       </c>
     </row>
@@ -20396,9 +21152,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="X252" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="Y252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="Y252" s="1" t="n">
+      <c r="Z252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -20475,9 +21234,12 @@
         <v>4.056</v>
       </c>
       <c r="X253" s="1" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="Y253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="Y253" s="1" t="n">
+      <c r="Z253" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -20554,9 +21316,12 @@
         <v>0.1865</v>
       </c>
       <c r="X254" s="1" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="Y254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="Y254" s="1" t="n">
+      <c r="Z254" s="1" t="n">
         <v>0.1865</v>
       </c>
     </row>
@@ -20633,9 +21398,12 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="X255" s="1" t="n">
+        <v>0.07196</v>
+      </c>
+      <c r="Y255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="Y255" s="1" t="n">
+      <c r="Z255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -20712,9 +21480,12 @@
         <v>0.01823</v>
       </c>
       <c r="X256" s="1" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="Y256" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="Y256" s="1" t="n">
+      <c r="Z256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -20791,9 +21562,12 @@
         <v>5.938</v>
       </c>
       <c r="X257" s="1" t="n">
+        <v>5.947</v>
+      </c>
+      <c r="Y257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="Y257" s="1" t="n">
+      <c r="Z257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -20870,9 +21644,12 @@
         <v>0.2598</v>
       </c>
       <c r="X258" s="1" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="Y258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="Y258" s="1" t="n">
+      <c r="Z258" s="1" t="n">
         <v>0.2582</v>
       </c>
     </row>
@@ -20949,9 +21726,12 @@
         <v>0.1359</v>
       </c>
       <c r="X259" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="Y259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="Y259" s="1" t="n">
+      <c r="Z259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -21028,9 +21808,12 @@
         <v>0.30723</v>
       </c>
       <c r="X260" s="1" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="Y260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="Y260" s="1" t="n">
+      <c r="Z260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -21107,9 +21890,12 @@
         <v>0.09863</v>
       </c>
       <c r="X261" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="Y261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="Y261" s="1" t="n">
+      <c r="Z261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -21186,9 +21972,12 @@
         <v>0.54</v>
       </c>
       <c r="X262" s="1" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="Y262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="Y262" s="1" t="n">
+      <c r="Z262" s="1" t="n">
         <v>0.5377999999999999</v>
       </c>
     </row>
@@ -21265,9 +22054,12 @@
         <v>0.2892</v>
       </c>
       <c r="X263" s="1" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="Y263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="Y263" s="1" t="n">
+      <c r="Z263" s="1" t="n">
         <v>0.2877</v>
       </c>
     </row>
@@ -21344,9 +22136,12 @@
         <v>0.984</v>
       </c>
       <c r="X264" s="1" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="Y264" s="1" t="n">
         <v>0.989</v>
       </c>
-      <c r="Y264" s="1" t="n">
+      <c r="Z264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -21423,9 +22218,12 @@
         <v>0.5347</v>
       </c>
       <c r="X265" s="1" t="n">
+        <v>0.5347</v>
+      </c>
+      <c r="Y265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="Y265" s="1" t="n">
+      <c r="Z265" s="1" t="n">
         <v>0.5339</v>
       </c>
     </row>
@@ -21502,9 +22300,12 @@
         <v>0.07346999999999999</v>
       </c>
       <c r="X266" s="1" t="n">
+        <v>0.07346</v>
+      </c>
+      <c r="Y266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="Y266" s="1" t="n">
+      <c r="Z266" s="1" t="n">
         <v>0.07339</v>
       </c>
     </row>
@@ -21581,9 +22382,12 @@
         <v>0.02116</v>
       </c>
       <c r="X267" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="Y267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="Y267" s="1" t="n">
+      <c r="Z267" s="1" t="n">
         <v>0.02116</v>
       </c>
     </row>
@@ -21660,9 +22464,12 @@
         <v>0.01609</v>
       </c>
       <c r="X268" s="1" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="Y268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="Y268" s="1" t="n">
+      <c r="Z268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -21739,9 +22546,12 @@
         <v>0.003794</v>
       </c>
       <c r="X269" s="1" t="n">
+        <v>0.003796</v>
+      </c>
+      <c r="Y269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="Y269" s="1" t="n">
+      <c r="Z269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -21818,9 +22628,12 @@
         <v>0.00765</v>
       </c>
       <c r="X270" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="Y270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="Y270" s="1" t="n">
+      <c r="Z270" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -21897,9 +22710,12 @@
         <v>0.05474</v>
       </c>
       <c r="X271" s="1" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="Y271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="Y271" s="1" t="n">
+      <c r="Z271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -21976,9 +22792,12 @@
         <v>2.292</v>
       </c>
       <c r="X272" s="1" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="Y272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="Y272" s="1" t="n">
+      <c r="Z272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -22055,9 +22874,12 @@
         <v>0.05445</v>
       </c>
       <c r="X273" s="1" t="n">
+        <v>0.05445</v>
+      </c>
+      <c r="Y273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="Y273" s="1" t="n">
+      <c r="Z273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -22134,9 +22956,12 @@
         <v>0.02346</v>
       </c>
       <c r="X274" s="1" t="n">
-        <v>0.02349</v>
+        <v>0.02357</v>
       </c>
       <c r="Y274" s="1" t="n">
+        <v>0.02357</v>
+      </c>
+      <c r="Z274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -22213,10 +23038,13 @@
         <v>1.172</v>
       </c>
       <c r="X275" s="1" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="Y275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="Y275" s="1" t="n">
-        <v>1.169</v>
+      <c r="Z275" s="1" t="n">
+        <v>1.168</v>
       </c>
     </row>
     <row r="276">
@@ -22292,9 +23120,12 @@
         <v>0.2714</v>
       </c>
       <c r="X276" s="1" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="Y276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="Y276" s="1" t="n">
+      <c r="Z276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -22371,9 +23202,12 @@
         <v>0.922</v>
       </c>
       <c r="X277" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="Y277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="Y277" s="1" t="n">
+      <c r="Z277" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -22450,9 +23284,12 @@
         <v>0.6254</v>
       </c>
       <c r="X278" s="1" t="n">
+        <v>0.6251</v>
+      </c>
+      <c r="Y278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="Y278" s="1" t="n">
+      <c r="Z278" s="1" t="n">
         <v>0.6218</v>
       </c>
     </row>
@@ -22529,10 +23366,13 @@
         <v>0.001324</v>
       </c>
       <c r="X279" s="1" t="n">
+        <v>0.001305</v>
+      </c>
+      <c r="Y279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="Y279" s="1" t="n">
-        <v>0.001324</v>
+      <c r="Z279" s="1" t="n">
+        <v>0.001305</v>
       </c>
     </row>
     <row r="280">
@@ -22608,9 +23448,12 @@
         <v>0.005579</v>
       </c>
       <c r="X280" s="1" t="n">
+        <v>0.005552</v>
+      </c>
+      <c r="Y280" s="1" t="n">
         <v>0.005613</v>
       </c>
-      <c r="Y280" s="1" t="n">
+      <c r="Z280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -22690,6 +23533,9 @@
         <v>1.526</v>
       </c>
       <c r="Y281" s="1" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="Z281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -22766,9 +23612,12 @@
         <v>28.24</v>
       </c>
       <c r="X282" s="1" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="Y282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="Y282" s="1" t="n">
+      <c r="Z282" s="1" t="n">
         <v>28.2</v>
       </c>
     </row>
@@ -22845,9 +23694,12 @@
         <v>0.12886</v>
       </c>
       <c r="X283" s="1" t="n">
+        <v>0.12914</v>
+      </c>
+      <c r="Y283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="Y283" s="1" t="n">
+      <c r="Z283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -22924,9 +23776,12 @@
         <v>0.011</v>
       </c>
       <c r="X284" s="1" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="Y284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="Y284" s="1" t="n">
+      <c r="Z284" s="1" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -23003,9 +23858,12 @@
         <v>6.552</v>
       </c>
       <c r="X285" s="1" t="n">
+        <v>6.568</v>
+      </c>
+      <c r="Y285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="Y285" s="1" t="n">
+      <c r="Z285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -23082,9 +23940,12 @@
         <v>0.01833</v>
       </c>
       <c r="X286" s="1" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="Y286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="Y286" s="1" t="n">
+      <c r="Z286" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -23161,9 +24022,12 @@
         <v>0.008364999999999999</v>
       </c>
       <c r="X287" s="1" t="n">
+        <v>0.008392</v>
+      </c>
+      <c r="Y287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="Y287" s="1" t="n">
+      <c r="Z287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -23240,10 +24104,13 @@
         <v>0.3745</v>
       </c>
       <c r="X288" s="1" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="Y288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="Y288" s="1" t="n">
-        <v>0.3743</v>
+      <c r="Z288" s="1" t="n">
+        <v>0.3713</v>
       </c>
     </row>
     <row r="289">
@@ -23319,10 +24186,13 @@
         <v>0.009790999999999999</v>
       </c>
       <c r="X289" s="1" t="n">
+        <v>0.009717999999999999</v>
+      </c>
+      <c r="Y289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="Y289" s="1" t="n">
-        <v>0.00974</v>
+      <c r="Z289" s="1" t="n">
+        <v>0.009717999999999999</v>
       </c>
     </row>
     <row r="290">
@@ -23398,9 +24268,12 @@
         <v>0.02587</v>
       </c>
       <c r="X290" s="1" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="Y290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="Y290" s="1" t="n">
+      <c r="Z290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -23477,9 +24350,12 @@
         <v>0.095</v>
       </c>
       <c r="X291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Y291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="Y291" s="1" t="n">
+      <c r="Z291" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -23556,9 +24432,12 @@
         <v>0.28728</v>
       </c>
       <c r="X292" s="1" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="Y292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="Y292" s="1" t="n">
+      <c r="Z292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -23635,10 +24514,13 @@
         <v>0.01517</v>
       </c>
       <c r="X293" s="1" t="n">
+        <v>0.01515</v>
+      </c>
+      <c r="Y293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="Y293" s="1" t="n">
-        <v>0.01516</v>
+      <c r="Z293" s="1" t="n">
+        <v>0.01515</v>
       </c>
     </row>
     <row r="294">
@@ -23714,9 +24596,12 @@
         <v>0.00342</v>
       </c>
       <c r="X294" s="1" t="n">
+        <v>0.003433</v>
+      </c>
+      <c r="Y294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="Y294" s="1" t="n">
+      <c r="Z294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -23793,9 +24678,12 @@
         <v>0.042061</v>
       </c>
       <c r="X295" s="1" t="n">
+        <v>0.042073</v>
+      </c>
+      <c r="Y295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="Y295" s="1" t="n">
+      <c r="Z295" s="1" t="n">
         <v>0.042061</v>
       </c>
     </row>
@@ -23872,9 +24760,12 @@
         <v>0.02845</v>
       </c>
       <c r="X296" s="1" t="n">
+        <v>0.02844</v>
+      </c>
+      <c r="Y296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="Y296" s="1" t="n">
+      <c r="Z296" s="1" t="n">
         <v>0.02844</v>
       </c>
     </row>
@@ -23951,9 +24842,12 @@
         <v>0.03785</v>
       </c>
       <c r="X297" s="1" t="n">
+        <v>0.03788</v>
+      </c>
+      <c r="Y297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="Y297" s="1" t="n">
+      <c r="Z297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -24030,9 +24924,12 @@
         <v>0.08239</v>
       </c>
       <c r="X298" s="1" t="n">
+        <v>0.08253000000000001</v>
+      </c>
+      <c r="Y298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="Y298" s="1" t="n">
+      <c r="Z298" s="1" t="n">
         <v>0.08239</v>
       </c>
     </row>
@@ -24109,9 +25006,12 @@
         <v>0.0076</v>
       </c>
       <c r="X299" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="Y299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="Y299" s="1" t="n">
+      <c r="Z299" s="1" t="n">
         <v>0.0076</v>
       </c>
     </row>
@@ -24188,9 +25088,12 @@
         <v>0.01486</v>
       </c>
       <c r="X300" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="Y300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="Y300" s="1" t="n">
+      <c r="Z300" s="1" t="n">
         <v>0.01486</v>
       </c>
     </row>
@@ -24267,9 +25170,12 @@
         <v>0.1406</v>
       </c>
       <c r="X301" s="1" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="Y301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="Y301" s="1" t="n">
+      <c r="Z301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -24346,9 +25252,12 @@
         <v>0.0006228</v>
       </c>
       <c r="X302" s="1" t="n">
+        <v>0.0006244</v>
+      </c>
+      <c r="Y302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="Y302" s="1" t="n">
+      <c r="Z302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -24425,9 +25334,12 @@
         <v>0.06214</v>
       </c>
       <c r="X303" s="1" t="n">
+        <v>0.06224</v>
+      </c>
+      <c r="Y303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="Y303" s="1" t="n">
+      <c r="Z303" s="1" t="n">
         <v>0.06207</v>
       </c>
     </row>
@@ -24504,10 +25416,13 @@
         <v>0.0001618</v>
       </c>
       <c r="X304" s="1" t="n">
+        <v>0.0001615</v>
+      </c>
+      <c r="Y304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="Y304" s="1" t="n">
-        <v>0.0001618</v>
+      <c r="Z304" s="1" t="n">
+        <v>0.0001615</v>
       </c>
     </row>
     <row r="305">
@@ -24583,9 +25498,12 @@
         <v>0.06075</v>
       </c>
       <c r="X305" s="1" t="n">
+        <v>0.06091</v>
+      </c>
+      <c r="Y305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="Y305" s="1" t="n">
+      <c r="Z305" s="1" t="n">
         <v>0.0606</v>
       </c>
     </row>
@@ -24662,9 +25580,12 @@
         <v>0.022322</v>
       </c>
       <c r="X306" s="1" t="n">
+        <v>0.022342</v>
+      </c>
+      <c r="Y306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="Y306" s="1" t="n">
+      <c r="Z306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -24741,9 +25662,12 @@
         <v>0.02281</v>
       </c>
       <c r="X307" s="1" t="n">
+        <v>0.02305</v>
+      </c>
+      <c r="Y307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="Y307" s="1" t="n">
+      <c r="Z307" s="1" t="n">
         <v>0.02278</v>
       </c>
     </row>
@@ -24820,9 +25744,12 @@
         <v>0.000409</v>
       </c>
       <c r="X308" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="Y308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="Y308" s="1" t="n">
+      <c r="Z308" s="1" t="n">
         <v>0.000409</v>
       </c>
     </row>
@@ -24902,6 +25829,9 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="Y309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="Z309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -24978,9 +25908,12 @@
         <v>0.371</v>
       </c>
       <c r="X310" s="1" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="Y310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="Y310" s="1" t="n">
+      <c r="Z310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -25057,9 +25990,12 @@
         <v>0.0354</v>
       </c>
       <c r="X311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="Y311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="Y311" s="1" t="n">
+      <c r="Z311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -25136,9 +26072,12 @@
         <v>0.02432</v>
       </c>
       <c r="X312" s="1" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="Y312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="Y312" s="1" t="n">
+      <c r="Z312" s="1" t="n">
         <v>0.02415</v>
       </c>
     </row>
@@ -25215,9 +26154,12 @@
         <v>0.04085</v>
       </c>
       <c r="X313" s="1" t="n">
+        <v>0.04081</v>
+      </c>
+      <c r="Y313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="Y313" s="1" t="n">
+      <c r="Z313" s="1" t="n">
         <v>0.0408</v>
       </c>
     </row>
@@ -25294,9 +26236,12 @@
         <v>3.935</v>
       </c>
       <c r="X314" s="1" t="n">
+        <v>3.953</v>
+      </c>
+      <c r="Y314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="Y314" s="1" t="n">
+      <c r="Z314" s="1" t="n">
         <v>3.932</v>
       </c>
     </row>
@@ -25373,9 +26318,12 @@
         <v>0.159</v>
       </c>
       <c r="X315" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="Y315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="Y315" s="1" t="n">
+      <c r="Z315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -25452,9 +26400,12 @@
         <v>0.09181</v>
       </c>
       <c r="X316" s="1" t="n">
+        <v>0.09173000000000001</v>
+      </c>
+      <c r="Y316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="Y316" s="1" t="n">
+      <c r="Z316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -25531,9 +26482,12 @@
         <v>0.06791999999999999</v>
       </c>
       <c r="X317" s="1" t="n">
+        <v>0.06791</v>
+      </c>
+      <c r="Y317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="Y317" s="1" t="n">
+      <c r="Z317" s="1" t="n">
         <v>0.06783</v>
       </c>
     </row>
@@ -25610,9 +26564,12 @@
         <v>0.012511</v>
       </c>
       <c r="X318" s="1" t="n">
+        <v>0.012563</v>
+      </c>
+      <c r="Y318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="Y318" s="1" t="n">
+      <c r="Z318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -25689,9 +26646,12 @@
         <v>0.001128</v>
       </c>
       <c r="X319" s="1" t="n">
+        <v>0.001131</v>
+      </c>
+      <c r="Y319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="Y319" s="1" t="n">
+      <c r="Z319" s="1" t="n">
         <v>0.001128</v>
       </c>
     </row>
@@ -25768,9 +26728,12 @@
         <v>0.0633</v>
       </c>
       <c r="X320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="Y320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="Y320" s="1" t="n">
+      <c r="Z320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -25847,10 +26810,13 @@
         <v>0.0052</v>
       </c>
       <c r="X321" s="1" t="n">
+        <v>0.00518</v>
+      </c>
+      <c r="Y321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="Y321" s="1" t="n">
-        <v>0.0052</v>
+      <c r="Z321" s="1" t="n">
+        <v>0.00518</v>
       </c>
     </row>
     <row r="322">
@@ -25926,9 +26892,12 @@
         <v>0.1112</v>
       </c>
       <c r="X322" s="1" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="Y322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="Y322" s="1" t="n">
+      <c r="Z322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -26005,9 +26974,12 @@
         <v>0.04323</v>
       </c>
       <c r="X323" s="1" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="Y323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="Y323" s="1" t="n">
+      <c r="Z323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -26084,9 +27056,12 @@
         <v>0.01778</v>
       </c>
       <c r="X324" s="1" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="Y324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="Y324" s="1" t="n">
+      <c r="Z324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -26163,9 +27138,12 @@
         <v>0.005636</v>
       </c>
       <c r="X325" s="1" t="n">
+        <v>0.005641</v>
+      </c>
+      <c r="Y325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="Y325" s="1" t="n">
+      <c r="Z325" s="1" t="n">
         <v>0.005628</v>
       </c>
     </row>
@@ -26242,9 +27220,12 @@
         <v>0.001733</v>
       </c>
       <c r="X326" s="1" t="n">
+        <v>0.001746</v>
+      </c>
+      <c r="Y326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="Y326" s="1" t="n">
+      <c r="Z326" s="1" t="n">
         <v>0.001733</v>
       </c>
     </row>
@@ -26321,9 +27302,12 @@
         <v>0.04032</v>
       </c>
       <c r="X327" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="Y327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="Y327" s="1" t="n">
+      <c r="Z327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -26400,9 +27384,12 @@
         <v>0.053472</v>
       </c>
       <c r="X328" s="1" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="Y328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="Y328" s="1" t="n">
+      <c r="Z328" s="1" t="n">
         <v>0.053472</v>
       </c>
     </row>
@@ -26479,10 +27466,13 @@
         <v>0.2769</v>
       </c>
       <c r="X329" s="1" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="Y329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="Y329" s="1" t="n">
-        <v>0.2769</v>
+      <c r="Z329" s="1" t="n">
+        <v>0.2768</v>
       </c>
     </row>
     <row r="330">
@@ -26558,9 +27548,12 @@
         <v>0.1587</v>
       </c>
       <c r="X330" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="Y330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="Y330" s="1" t="n">
+      <c r="Z330" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -26637,9 +27630,12 @@
         <v>0.05372</v>
       </c>
       <c r="X331" s="1" t="n">
+        <v>0.05382</v>
+      </c>
+      <c r="Y331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="Y331" s="1" t="n">
+      <c r="Z331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -26716,9 +27712,12 @@
         <v>0.3615</v>
       </c>
       <c r="X332" s="1" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="Y332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="Y332" s="1" t="n">
+      <c r="Z332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -26795,9 +27794,12 @@
         <v>0.03057</v>
       </c>
       <c r="X333" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="Y333" s="1" t="n">
         <v>0.03063</v>
       </c>
-      <c r="Y333" s="1" t="n">
+      <c r="Z333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -26874,9 +27876,12 @@
         <v>0.01741</v>
       </c>
       <c r="X334" s="1" t="n">
+        <v>0.01742</v>
+      </c>
+      <c r="Y334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="Y334" s="1" t="n">
+      <c r="Z334" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -26953,9 +27958,12 @@
         <v>0.0579</v>
       </c>
       <c r="X335" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="Y335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="Y335" s="1" t="n">
+      <c r="Z335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -27032,9 +28040,12 @@
         <v>0.08962000000000001</v>
       </c>
       <c r="X336" s="1" t="n">
+        <v>0.09012000000000001</v>
+      </c>
+      <c r="Y336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="Y336" s="1" t="n">
+      <c r="Z336" s="1" t="n">
         <v>0.08910999999999999</v>
       </c>
     </row>
@@ -27111,9 +28122,12 @@
         <v>0.17892</v>
       </c>
       <c r="X337" s="1" t="n">
+        <v>0.18015</v>
+      </c>
+      <c r="Y337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="Y337" s="1" t="n">
+      <c r="Z337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -27190,9 +28204,12 @@
         <v>0.02083</v>
       </c>
       <c r="X338" s="1" t="n">
+        <v>0.02084</v>
+      </c>
+      <c r="Y338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="Y338" s="1" t="n">
+      <c r="Z338" s="1" t="n">
         <v>0.02074</v>
       </c>
     </row>
@@ -27269,9 +28286,12 @@
         <v>0.1318</v>
       </c>
       <c r="X339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="Y339" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="Y339" s="1" t="n">
+      <c r="Z339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -27348,10 +28368,13 @@
         <v>0.007889</v>
       </c>
       <c r="X340" s="1" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="Y340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="Y340" s="1" t="n">
-        <v>0.007889</v>
+      <c r="Z340" s="1" t="n">
+        <v>0.00788</v>
       </c>
     </row>
     <row r="341">
@@ -27427,9 +28450,12 @@
         <v>4.402</v>
       </c>
       <c r="X341" s="1" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="Y341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="Y341" s="1" t="n">
+      <c r="Z341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -27506,9 +28532,12 @@
         <v>0.18789</v>
       </c>
       <c r="X342" s="1" t="n">
+        <v>0.18874</v>
+      </c>
+      <c r="Y342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="Y342" s="1" t="n">
+      <c r="Z342" s="1" t="n">
         <v>0.18732</v>
       </c>
     </row>
@@ -27585,9 +28614,12 @@
         <v>0.08323999999999999</v>
       </c>
       <c r="X343" s="1" t="n">
+        <v>0.08318</v>
+      </c>
+      <c r="Y343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="Y343" s="1" t="n">
+      <c r="Z343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -27664,9 +28696,12 @@
         <v>0.1817</v>
       </c>
       <c r="X344" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="Y344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="Y344" s="1" t="n">
+      <c r="Z344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -27743,9 +28778,12 @@
         <v>0.003214</v>
       </c>
       <c r="X345" s="1" t="n">
+        <v>0.003219</v>
+      </c>
+      <c r="Y345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="Y345" s="1" t="n">
+      <c r="Z345" s="1" t="n">
         <v>0.003214</v>
       </c>
     </row>
@@ -27822,9 +28860,12 @@
         <v>0.09117</v>
       </c>
       <c r="X346" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="Y346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="Y346" s="1" t="n">
+      <c r="Z346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -27901,9 +28942,12 @@
         <v>2.238</v>
       </c>
       <c r="X347" s="1" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="Y347" s="1" t="n">
+      <c r="Z347" s="1" t="n">
         <v>2.235</v>
       </c>
     </row>
@@ -27980,10 +29024,13 @@
         <v>0.3012</v>
       </c>
       <c r="X348" s="1" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="Y348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="Y348" s="1" t="n">
-        <v>0.3012</v>
+      <c r="Z348" s="1" t="n">
+        <v>0.3007</v>
       </c>
     </row>
     <row r="349">
@@ -28059,9 +29106,12 @@
         <v>0.02988</v>
       </c>
       <c r="X349" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="Y349" s="1" t="n">
         <v>0.03002</v>
       </c>
-      <c r="Y349" s="1" t="n">
+      <c r="Z349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -28138,9 +29188,12 @@
         <v>0.1278</v>
       </c>
       <c r="X350" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="Y350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="Y350" s="1" t="n">
+      <c r="Z350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -28217,9 +29270,12 @@
         <v>0.06559</v>
       </c>
       <c r="X351" s="1" t="n">
+        <v>0.06592000000000001</v>
+      </c>
+      <c r="Y351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="Y351" s="1" t="n">
+      <c r="Z351" s="1" t="n">
         <v>0.06559</v>
       </c>
     </row>
@@ -28296,10 +29352,13 @@
         <v>0.06203</v>
       </c>
       <c r="X352" s="1" t="n">
+        <v>0.06202</v>
+      </c>
+      <c r="Y352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="Y352" s="1" t="n">
-        <v>0.06203</v>
+      <c r="Z352" s="1" t="n">
+        <v>0.06202</v>
       </c>
     </row>
     <row r="353">
@@ -28375,9 +29434,12 @@
         <v>0.06292</v>
       </c>
       <c r="X353" s="1" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="Y353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="Y353" s="1" t="n">
+      <c r="Z353" s="1" t="n">
         <v>0.06270000000000001</v>
       </c>
     </row>
@@ -28454,10 +29516,13 @@
         <v>0.10261</v>
       </c>
       <c r="X354" s="1" t="n">
+        <v>0.10245</v>
+      </c>
+      <c r="Y354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="Y354" s="1" t="n">
-        <v>0.10261</v>
+      <c r="Z354" s="1" t="n">
+        <v>0.10245</v>
       </c>
     </row>
     <row r="355">
@@ -28533,10 +29598,13 @@
         <v>0.0898</v>
       </c>
       <c r="X355" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="Y355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="Y355" s="1" t="n">
-        <v>0.0897</v>
+      <c r="Z355" s="1" t="n">
+        <v>0.0896</v>
       </c>
     </row>
     <row r="356">
@@ -28612,9 +29680,12 @@
         <v>0.06972</v>
       </c>
       <c r="X356" s="1" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="Y356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="Y356" s="1" t="n">
+      <c r="Z356" s="1" t="n">
         <v>0.06905</v>
       </c>
     </row>
@@ -28691,9 +29762,12 @@
         <v>0.4506</v>
       </c>
       <c r="X357" s="1" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="Y357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="Y357" s="1" t="n">
+      <c r="Z357" s="1" t="n">
         <v>0.4504</v>
       </c>
     </row>
@@ -28770,9 +29844,12 @@
         <v>0.03449</v>
       </c>
       <c r="X358" s="1" t="n">
+        <v>0.03458</v>
+      </c>
+      <c r="Y358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="Y358" s="1" t="n">
+      <c r="Z358" s="1" t="n">
         <v>0.03441</v>
       </c>
     </row>
@@ -28849,9 +29926,12 @@
         <v>0.0145</v>
       </c>
       <c r="X359" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="Y359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="Y359" s="1" t="n">
+      <c r="Z359" s="1" t="n">
         <v>0.01446</v>
       </c>
     </row>
@@ -28928,9 +30008,12 @@
         <v>0.13253</v>
       </c>
       <c r="X360" s="1" t="n">
+        <v>0.13251</v>
+      </c>
+      <c r="Y360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="Y360" s="1" t="n">
+      <c r="Z360" s="1" t="n">
         <v>0.13239</v>
       </c>
     </row>
@@ -29007,9 +30090,12 @@
         <v>0.0005865999999999999</v>
       </c>
       <c r="X361" s="1" t="n">
+        <v>0.0005871</v>
+      </c>
+      <c r="Y361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="Y361" s="1" t="n">
+      <c r="Z361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -29086,10 +30172,13 @@
         <v>0.03824</v>
       </c>
       <c r="X362" s="1" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="Y362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="Y362" s="1" t="n">
-        <v>0.03824</v>
+      <c r="Z362" s="1" t="n">
+        <v>0.0382</v>
       </c>
     </row>
     <row r="363">
@@ -29165,9 +30254,12 @@
         <v>3.243</v>
       </c>
       <c r="X363" s="1" t="n">
-        <v>3.244</v>
+        <v>3.252</v>
       </c>
       <c r="Y363" s="1" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="Z363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -29244,9 +30336,12 @@
         <v>0.1631</v>
       </c>
       <c r="X364" s="1" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="Y364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="Y364" s="1" t="n">
+      <c r="Z364" s="1" t="n">
         <v>0.1627</v>
       </c>
     </row>
@@ -29323,9 +30418,12 @@
         <v>0.1127</v>
       </c>
       <c r="X365" s="1" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="Y365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="Y365" s="1" t="n">
+      <c r="Z365" s="1" t="n">
         <v>0.1127</v>
       </c>
     </row>
@@ -29402,9 +30500,12 @@
         <v>0.0006342</v>
       </c>
       <c r="X366" s="1" t="n">
+        <v>0.0006347</v>
+      </c>
+      <c r="Y366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="Y366" s="1" t="n">
+      <c r="Z366" s="1" t="n">
         <v>0.0006339</v>
       </c>
     </row>
@@ -29481,9 +30582,12 @@
         <v>0.05982</v>
       </c>
       <c r="X367" s="1" t="n">
+        <v>0.05981</v>
+      </c>
+      <c r="Y367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="Y367" s="1" t="n">
+      <c r="Z367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -29560,9 +30664,12 @@
         <v>0.08119</v>
       </c>
       <c r="X368" s="1" t="n">
+        <v>0.08124000000000001</v>
+      </c>
+      <c r="Y368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="Y368" s="1" t="n">
+      <c r="Z368" s="1" t="n">
         <v>0.08111</v>
       </c>
     </row>
@@ -29639,9 +30746,12 @@
         <v>0.03935</v>
       </c>
       <c r="X369" s="1" t="n">
+        <v>0.03972</v>
+      </c>
+      <c r="Y369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="Y369" s="1" t="n">
+      <c r="Z369" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -29718,9 +30828,12 @@
         <v>3.691</v>
       </c>
       <c r="X370" s="1" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Y370" s="1" t="n">
         <v>3.759</v>
       </c>
-      <c r="Y370" s="1" t="n">
+      <c r="Z370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -29797,9 +30910,12 @@
         <v>0.1208</v>
       </c>
       <c r="X371" s="1" t="n">
+        <v>0.1211</v>
+      </c>
+      <c r="Y371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="Y371" s="1" t="n">
+      <c r="Z371" s="1" t="n">
         <v>0.1204</v>
       </c>
     </row>
@@ -29876,9 +30992,12 @@
         <v>0.0146</v>
       </c>
       <c r="X372" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="Y372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="Y372" s="1" t="n">
+      <c r="Z372" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -29955,9 +31074,12 @@
         <v>0.02192</v>
       </c>
       <c r="X373" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="Y373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="Y373" s="1" t="n">
+      <c r="Z373" s="1" t="n">
         <v>0.02187</v>
       </c>
     </row>
@@ -30034,9 +31156,12 @@
         <v>1.8718</v>
       </c>
       <c r="X374" s="1" t="n">
+        <v>1.8689</v>
+      </c>
+      <c r="Y374" s="1" t="n">
         <v>1.875</v>
       </c>
-      <c r="Y374" s="1" t="n">
+      <c r="Z374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -30113,9 +31238,12 @@
         <v>0.02081</v>
       </c>
       <c r="X375" s="1" t="n">
+        <v>0.02084</v>
+      </c>
+      <c r="Y375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="Y375" s="1" t="n">
+      <c r="Z375" s="1" t="n">
         <v>0.02081</v>
       </c>
     </row>
@@ -30192,9 +31320,12 @@
         <v>1.302</v>
       </c>
       <c r="X376" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="Y376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="Y376" s="1" t="n">
+      <c r="Z376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -30271,9 +31402,12 @@
         <v>0.2819</v>
       </c>
       <c r="X377" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="Y377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="Y377" s="1" t="n">
+      <c r="Z377" s="1" t="n">
         <v>0.2819</v>
       </c>
     </row>
@@ -30350,9 +31484,12 @@
         <v>0.01553</v>
       </c>
       <c r="X378" s="1" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="Y378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="Y378" s="1" t="n">
+      <c r="Z378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -30429,9 +31566,12 @@
         <v>1.5215</v>
       </c>
       <c r="X379" s="1" t="n">
+        <v>1.5217</v>
+      </c>
+      <c r="Y379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="Y379" s="1" t="n">
+      <c r="Z379" s="1" t="n">
         <v>1.5181</v>
       </c>
     </row>
@@ -30508,9 +31648,12 @@
         <v>6.861e-05</v>
       </c>
       <c r="X380" s="1" t="n">
+        <v>6.874e-05</v>
+      </c>
+      <c r="Y380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="Y380" s="1" t="n">
+      <c r="Z380" s="1" t="n">
         <v>6.858e-05</v>
       </c>
     </row>
@@ -30587,9 +31730,12 @@
         <v>2.539</v>
       </c>
       <c r="X381" s="1" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="Y381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="Y381" s="1" t="n">
+      <c r="Z381" s="1" t="n">
         <v>2.536</v>
       </c>
     </row>
@@ -30666,9 +31812,12 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="X382" s="1" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="Y382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="Y382" s="1" t="n">
+      <c r="Z382" s="1" t="n">
         <v>0.06646000000000001</v>
       </c>
     </row>
@@ -30745,9 +31894,12 @@
         <v>0.01672</v>
       </c>
       <c r="X383" s="1" t="n">
+        <v>0.01665</v>
+      </c>
+      <c r="Y383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="Y383" s="1" t="n">
+      <c r="Z383" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -30824,9 +31976,12 @@
         <v>0.05126</v>
       </c>
       <c r="X384" s="1" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="Y384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="Y384" s="1" t="n">
+      <c r="Z384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -30903,9 +32058,12 @@
         <v>7.605</v>
       </c>
       <c r="X385" s="1" t="n">
-        <v>7.61</v>
+        <v>7.616</v>
       </c>
       <c r="Y385" s="1" t="n">
+        <v>7.616</v>
+      </c>
+      <c r="Z385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -30982,9 +32140,12 @@
         <v>0.003266</v>
       </c>
       <c r="X386" s="1" t="n">
+        <v>0.00326</v>
+      </c>
+      <c r="Y386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="Y386" s="1" t="n">
+      <c r="Z386" s="1" t="n">
         <v>0.003258</v>
       </c>
     </row>
@@ -31061,9 +32222,12 @@
         <v>0.0003792</v>
       </c>
       <c r="X387" s="1" t="n">
+        <v>0.0003804</v>
+      </c>
+      <c r="Y387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="Y387" s="1" t="n">
+      <c r="Z387" s="1" t="n">
         <v>0.0003788</v>
       </c>
     </row>
@@ -31140,9 +32304,12 @@
         <v>0.00954</v>
       </c>
       <c r="X388" s="1" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="Y388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="Y388" s="1" t="n">
+      <c r="Z388" s="1" t="n">
         <v>0.00942</v>
       </c>
     </row>
@@ -31219,9 +32386,12 @@
         <v>0.2906</v>
       </c>
       <c r="X389" s="1" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="Y389" s="1" t="n">
         <v>0.2917</v>
       </c>
-      <c r="Y389" s="1" t="n">
+      <c r="Z389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -31301,6 +32471,9 @@
         <v>0.0253</v>
       </c>
       <c r="Y390" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="Z390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -31377,9 +32550,12 @@
         <v>2.836</v>
       </c>
       <c r="X391" s="1" t="n">
+        <v>2.826</v>
+      </c>
+      <c r="Y391" s="1" t="n">
         <v>2.859</v>
       </c>
-      <c r="Y391" s="1" t="n">
+      <c r="Z391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -31456,9 +32632,12 @@
         <v>0.01346</v>
       </c>
       <c r="X392" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="Y392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="Y392" s="1" t="n">
+      <c r="Z392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -31538,6 +32717,9 @@
         <v>0.00237</v>
       </c>
       <c r="Y393" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="Z393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -31614,9 +32796,12 @@
         <v>0.05932</v>
       </c>
       <c r="X394" s="1" t="n">
+        <v>0.05941</v>
+      </c>
+      <c r="Y394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="Y394" s="1" t="n">
+      <c r="Z394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -31693,9 +32878,12 @@
         <v>0.0401</v>
       </c>
       <c r="X395" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="Y395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="Y395" s="1" t="n">
+      <c r="Z395" s="1" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -31772,9 +32960,12 @@
         <v>0.09404999999999999</v>
       </c>
       <c r="X396" s="1" t="n">
+        <v>0.09307</v>
+      </c>
+      <c r="Y396" s="1" t="n">
         <v>0.09447</v>
       </c>
-      <c r="Y396" s="1" t="n">
+      <c r="Z396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -31851,10 +33042,13 @@
         <v>0.1512</v>
       </c>
       <c r="X397" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="Y397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="Y397" s="1" t="n">
-        <v>0.1511</v>
+      <c r="Z397" s="1" t="n">
+        <v>0.151</v>
       </c>
     </row>
     <row r="398">
@@ -31930,9 +33124,12 @@
         <v>0.931</v>
       </c>
       <c r="X398" s="1" t="n">
-        <v>0.931</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="Y398" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="Z398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -32009,10 +33206,13 @@
         <v>0.05205</v>
       </c>
       <c r="X399" s="1" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="Y399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="Y399" s="1" t="n">
-        <v>0.05205</v>
+      <c r="Z399" s="1" t="n">
+        <v>0.05199</v>
       </c>
     </row>
     <row r="400">
@@ -32088,9 +33288,12 @@
         <v>2.501</v>
       </c>
       <c r="X400" s="1" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="Y400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="Y400" s="1" t="n">
+      <c r="Z400" s="1" t="n">
         <v>2.497</v>
       </c>
     </row>
@@ -32167,9 +33370,12 @@
         <v>0.01772</v>
       </c>
       <c r="X401" s="1" t="n">
+        <v>0.01772</v>
+      </c>
+      <c r="Y401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="Y401" s="1" t="n">
+      <c r="Z401" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -32246,9 +33452,12 @@
         <v>0.08015</v>
       </c>
       <c r="X402" s="1" t="n">
+        <v>0.08016</v>
+      </c>
+      <c r="Y402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="Y402" s="1" t="n">
+      <c r="Z402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -32325,9 +33534,12 @@
         <v>1.2513</v>
       </c>
       <c r="X403" s="1" t="n">
-        <v>1.2526</v>
+        <v>1.253</v>
       </c>
       <c r="Y403" s="1" t="n">
+        <v>1.253</v>
+      </c>
+      <c r="Z403" s="1" t="n">
         <v>1.2451</v>
       </c>
     </row>
@@ -32404,9 +33616,12 @@
         <v>0.00708</v>
       </c>
       <c r="X404" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="Y404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="Y404" s="1" t="n">
+      <c r="Z404" s="1" t="n">
         <v>0.00707</v>
       </c>
     </row>
@@ -32483,9 +33698,12 @@
         <v>0.5011</v>
       </c>
       <c r="X405" s="1" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="Y405" s="1" t="n">
         <v>0.5065</v>
       </c>
-      <c r="Y405" s="1" t="n">
+      <c r="Z405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -32562,9 +33780,12 @@
         <v>0.01141</v>
       </c>
       <c r="X406" s="1" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="Y406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="Y406" s="1" t="n">
+      <c r="Z406" s="1" t="n">
         <v>0.01138</v>
       </c>
     </row>
@@ -32641,9 +33862,12 @@
         <v>0.04581</v>
       </c>
       <c r="X407" s="1" t="n">
+        <v>0.04584</v>
+      </c>
+      <c r="Y407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="Y407" s="1" t="n">
+      <c r="Z407" s="1" t="n">
         <v>0.0458</v>
       </c>
     </row>
@@ -32720,9 +33944,12 @@
         <v>0.03921</v>
       </c>
       <c r="X408" s="1" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="Y408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="Y408" s="1" t="n">
+      <c r="Z408" s="1" t="n">
         <v>0.03921</v>
       </c>
     </row>
@@ -32799,9 +34026,12 @@
         <v>0.05211</v>
       </c>
       <c r="X409" s="1" t="n">
+        <v>0.05223</v>
+      </c>
+      <c r="Y409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="Y409" s="1" t="n">
+      <c r="Z409" s="1" t="n">
         <v>0.05209</v>
       </c>
     </row>
@@ -32878,9 +34108,12 @@
         <v>0.01227</v>
       </c>
       <c r="X410" s="1" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="Y410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="Y410" s="1" t="n">
+      <c r="Z410" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -32957,9 +34190,12 @@
         <v>0.06347999999999999</v>
       </c>
       <c r="X411" s="1" t="n">
+        <v>0.06354</v>
+      </c>
+      <c r="Y411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="Y411" s="1" t="n">
+      <c r="Z411" s="1" t="n">
         <v>0.06333</v>
       </c>
     </row>
@@ -33036,9 +34272,12 @@
         <v>0.04129</v>
       </c>
       <c r="X412" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="Y412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="Y412" s="1" t="n">
+      <c r="Z412" s="1" t="n">
         <v>0.04114</v>
       </c>
     </row>
@@ -33115,9 +34354,12 @@
         <v>1.106</v>
       </c>
       <c r="X413" s="1" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="Y413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="Y413" s="1" t="n">
+      <c r="Z413" s="1" t="n">
         <v>1.101</v>
       </c>
     </row>
@@ -33194,9 +34436,12 @@
         <v>0.262</v>
       </c>
       <c r="X414" s="1" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="Y414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="Y414" s="1" t="n">
+      <c r="Z414" s="1" t="n">
         <v>0.2614</v>
       </c>
     </row>
@@ -33273,9 +34518,12 @@
         <v>0.001225</v>
       </c>
       <c r="X415" s="1" t="n">
+        <v>0.001226</v>
+      </c>
+      <c r="Y415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="Y415" s="1" t="n">
+      <c r="Z415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -33352,9 +34600,12 @@
         <v>0.03186</v>
       </c>
       <c r="X416" s="1" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="Y416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="Y416" s="1" t="n">
+      <c r="Z416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -33431,10 +34682,13 @@
         <v>0.01449</v>
       </c>
       <c r="X417" s="1" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="Y417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="Y417" s="1" t="n">
-        <v>0.01449</v>
+      <c r="Z417" s="1" t="n">
+        <v>0.01446</v>
       </c>
     </row>
     <row r="418">
@@ -33510,9 +34764,12 @@
         <v>0.1479</v>
       </c>
       <c r="X418" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="Y418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="Y418" s="1" t="n">
+      <c r="Z418" s="1" t="n">
         <v>0.1478</v>
       </c>
     </row>
@@ -33589,9 +34846,12 @@
         <v>0.04839</v>
       </c>
       <c r="X419" s="1" t="n">
+        <v>0.04851</v>
+      </c>
+      <c r="Y419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="Y419" s="1" t="n">
+      <c r="Z419" s="1" t="n">
         <v>0.04839</v>
       </c>
     </row>
@@ -33668,9 +34928,12 @@
         <v>66.5</v>
       </c>
       <c r="X420" s="1" t="n">
+        <v>66.59</v>
+      </c>
+      <c r="Y420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="Y420" s="1" t="n">
+      <c r="Z420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -33747,9 +35010,12 @@
         <v>0.879</v>
       </c>
       <c r="X421" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="Y421" s="1" t="n">
         <v>0.88</v>
       </c>
-      <c r="Y421" s="1" t="n">
+      <c r="Z421" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -33826,9 +35092,12 @@
         <v>0.012465</v>
       </c>
       <c r="X422" s="1" t="n">
+        <v>0.012543</v>
+      </c>
+      <c r="Y422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="Y422" s="1" t="n">
+      <c r="Z422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -33905,9 +35174,12 @@
         <v>0.01604</v>
       </c>
       <c r="X423" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="Y423" s="1" t="n">
         <v>0.01604</v>
       </c>
-      <c r="Y423" s="1" t="n">
+      <c r="Z423" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -33984,9 +35256,12 @@
         <v>0.26856</v>
       </c>
       <c r="X424" s="1" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="Y424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="Y424" s="1" t="n">
+      <c r="Z424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -34063,9 +35338,12 @@
         <v>0.5975</v>
       </c>
       <c r="X425" s="1" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="Y425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="Y425" s="1" t="n">
+      <c r="Z425" s="1" t="n">
         <v>0.5973000000000001</v>
       </c>
     </row>
@@ -34142,9 +35420,12 @@
         <v>0.005453</v>
       </c>
       <c r="X426" s="1" t="n">
+        <v>0.005472</v>
+      </c>
+      <c r="Y426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="Y426" s="1" t="n">
+      <c r="Z426" s="1" t="n">
         <v>0.005453</v>
       </c>
     </row>
@@ -34221,9 +35502,12 @@
         <v>0.04972</v>
       </c>
       <c r="X427" s="1" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="Y427" s="1" t="n">
         <v>0.05022</v>
       </c>
-      <c r="Y427" s="1" t="n">
+      <c r="Z427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -34300,9 +35584,12 @@
         <v>0.125</v>
       </c>
       <c r="X428" s="1" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="Y428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="Y428" s="1" t="n">
+      <c r="Z428" s="1" t="n">
         <v>0.1249</v>
       </c>
     </row>
@@ -34379,9 +35666,12 @@
         <v>0.003188</v>
       </c>
       <c r="X429" s="1" t="n">
+        <v>0.003175</v>
+      </c>
+      <c r="Y429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="Y429" s="1" t="n">
+      <c r="Z429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -34458,10 +35748,13 @@
         <v>0.0362</v>
       </c>
       <c r="X430" s="1" t="n">
+        <v>0.03615</v>
+      </c>
+      <c r="Y430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="Y430" s="1" t="n">
-        <v>0.03617</v>
+      <c r="Z430" s="1" t="n">
+        <v>0.03615</v>
       </c>
     </row>
     <row r="431">
@@ -34537,9 +35830,12 @@
         <v>0.3929</v>
       </c>
       <c r="X431" s="1" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="Y431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="Y431" s="1" t="n">
+      <c r="Z431" s="1" t="n">
         <v>0.3914</v>
       </c>
     </row>
@@ -34616,9 +35912,12 @@
         <v>0.004456</v>
       </c>
       <c r="X432" s="1" t="n">
+        <v>0.004462</v>
+      </c>
+      <c r="Y432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="Y432" s="1" t="n">
+      <c r="Z432" s="1" t="n">
         <v>0.004446</v>
       </c>
     </row>
@@ -34695,9 +35994,12 @@
         <v>0.097</v>
       </c>
       <c r="X433" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="Y433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="Y433" s="1" t="n">
+      <c r="Z433" s="1" t="n">
         <v>0.097</v>
       </c>
     </row>
@@ -34774,9 +36076,12 @@
         <v>0.0124</v>
       </c>
       <c r="X434" s="1" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="Y434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="Y434" s="1" t="n">
+      <c r="Z434" s="1" t="n">
         <v>0.01234</v>
       </c>
     </row>
@@ -34853,9 +36158,12 @@
         <v>1.979</v>
       </c>
       <c r="X435" s="1" t="n">
+        <v>1.981</v>
+      </c>
+      <c r="Y435" s="1" t="n">
         <v>2.004</v>
       </c>
-      <c r="Y435" s="1" t="n">
+      <c r="Z435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -34932,9 +36240,12 @@
         <v>0.001757</v>
       </c>
       <c r="X436" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="Y436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="Y436" s="1" t="n">
+      <c r="Z436" s="1" t="n">
         <v>0.001757</v>
       </c>
     </row>
@@ -35011,9 +36322,12 @@
         <v>0.4423</v>
       </c>
       <c r="X437" s="1" t="n">
-        <v>0.4427</v>
+        <v>0.4428</v>
       </c>
       <c r="Y437" s="1" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="Z437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -35090,9 +36404,12 @@
         <v>0.00533</v>
       </c>
       <c r="X438" s="1" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="Y438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="Y438" s="1" t="n">
+      <c r="Z438" s="1" t="n">
         <v>0.00533</v>
       </c>
     </row>
@@ -35169,9 +36486,12 @@
         <v>0.1034</v>
       </c>
       <c r="X439" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="Y439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="Y439" s="1" t="n">
+      <c r="Z439" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -35248,9 +36568,12 @@
         <v>0.0335</v>
       </c>
       <c r="X440" s="1" t="n">
+        <v>0.03362</v>
+      </c>
+      <c r="Y440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="Y440" s="1" t="n">
+      <c r="Z440" s="1" t="n">
         <v>0.0335</v>
       </c>
     </row>
@@ -35327,10 +36650,13 @@
         <v>0.08176</v>
       </c>
       <c r="X441" s="1" t="n">
+        <v>0.08166</v>
+      </c>
+      <c r="Y441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="Y441" s="1" t="n">
-        <v>0.08173999999999999</v>
+      <c r="Z441" s="1" t="n">
+        <v>0.08166</v>
       </c>
     </row>
     <row r="442">
@@ -35406,9 +36732,12 @@
         <v>1.288</v>
       </c>
       <c r="X442" s="1" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="Y442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="Y442" s="1" t="n">
+      <c r="Z442" s="1" t="n">
         <v>1.288</v>
       </c>
     </row>
@@ -35485,9 +36814,12 @@
         <v>0.07494000000000001</v>
       </c>
       <c r="X443" s="1" t="n">
+        <v>0.07494000000000001</v>
+      </c>
+      <c r="Y443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="Y443" s="1" t="n">
+      <c r="Z443" s="1" t="n">
         <v>0.07491</v>
       </c>
     </row>
@@ -35564,9 +36896,12 @@
         <v>0.07607999999999999</v>
       </c>
       <c r="X444" s="1" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="Y444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="Y444" s="1" t="n">
+      <c r="Z444" s="1" t="n">
         <v>0.07607999999999999</v>
       </c>
     </row>
@@ -35643,9 +36978,12 @@
         <v>0.04292</v>
       </c>
       <c r="X445" s="1" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="Y445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="Y445" s="1" t="n">
+      <c r="Z445" s="1" t="n">
         <v>0.04289</v>
       </c>
     </row>
@@ -35722,10 +37060,13 @@
         <v>0.0213</v>
       </c>
       <c r="X446" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="Y446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="Y446" s="1" t="n">
-        <v>0.0213</v>
+      <c r="Z446" s="1" t="n">
+        <v>0.02129</v>
       </c>
     </row>
     <row r="447">
@@ -35801,9 +37142,12 @@
         <v>0.279</v>
       </c>
       <c r="X447" s="1" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="Y447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="Y447" s="1" t="n">
+      <c r="Z447" s="1" t="n">
         <v>0.2781</v>
       </c>
     </row>
@@ -35880,9 +37224,12 @@
         <v>0.03061</v>
       </c>
       <c r="X448" s="1" t="n">
+        <v>0.03064</v>
+      </c>
+      <c r="Y448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="Y448" s="1" t="n">
+      <c r="Z448" s="1" t="n">
         <v>0.0306</v>
       </c>
     </row>
@@ -35959,9 +37306,12 @@
         <v>0.00643</v>
       </c>
       <c r="X449" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="Y449" s="1" t="n">
         <v>0.00655</v>
       </c>
-      <c r="Y449" s="1" t="n">
+      <c r="Z449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -36038,10 +37388,13 @@
         <v>0.022841</v>
       </c>
       <c r="X450" s="1" t="n">
+        <v>0.022776</v>
+      </c>
+      <c r="Y450" s="1" t="n">
         <v>0.02312</v>
       </c>
-      <c r="Y450" s="1" t="n">
-        <v>0.02283</v>
+      <c r="Z450" s="1" t="n">
+        <v>0.022776</v>
       </c>
     </row>
     <row r="451">
@@ -36117,9 +37470,12 @@
         <v>0.04225</v>
       </c>
       <c r="X451" s="1" t="n">
+        <v>0.04226</v>
+      </c>
+      <c r="Y451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="Y451" s="1" t="n">
+      <c r="Z451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -36196,9 +37552,12 @@
         <v>0.07195</v>
       </c>
       <c r="X452" s="1" t="n">
+        <v>0.07202</v>
+      </c>
+      <c r="Y452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="Y452" s="1" t="n">
+      <c r="Z452" s="1" t="n">
         <v>0.07195</v>
       </c>
     </row>
@@ -36275,10 +37634,13 @@
         <v>0.0005899</v>
       </c>
       <c r="X453" s="1" t="n">
+        <v>0.0005891</v>
+      </c>
+      <c r="Y453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="Y453" s="1" t="n">
-        <v>0.0005899</v>
+      <c r="Z453" s="1" t="n">
+        <v>0.0005891</v>
       </c>
     </row>
     <row r="454">
@@ -36354,9 +37716,12 @@
         <v>0.304</v>
       </c>
       <c r="X454" s="1" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="Y454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="Y454" s="1" t="n">
+      <c r="Z454" s="1" t="n">
         <v>0.303</v>
       </c>
     </row>
@@ -36436,6 +37801,9 @@
         <v>0.004338</v>
       </c>
       <c r="Y455" s="1" t="n">
+        <v>0.004338</v>
+      </c>
+      <c r="Z455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -36512,9 +37880,12 @@
         <v>0.1816</v>
       </c>
       <c r="X456" s="1" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="Y456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="Y456" s="1" t="n">
+      <c r="Z456" s="1" t="n">
         <v>0.1815</v>
       </c>
     </row>
@@ -36591,9 +37962,12 @@
         <v>0.04257</v>
       </c>
       <c r="X457" s="1" t="n">
+        <v>0.04256</v>
+      </c>
+      <c r="Y457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="Y457" s="1" t="n">
+      <c r="Z457" s="1" t="n">
         <v>0.04254</v>
       </c>
     </row>
@@ -36670,10 +38044,13 @@
         <v>0.1447</v>
       </c>
       <c r="X458" s="1" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="Y458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="Y458" s="1" t="n">
-        <v>0.1447</v>
+      <c r="Z458" s="1" t="n">
+        <v>0.1434</v>
       </c>
     </row>
     <row r="459">
@@ -36749,9 +38126,12 @@
         <v>0.008628</v>
       </c>
       <c r="X459" s="1" t="n">
+        <v>0.008604000000000001</v>
+      </c>
+      <c r="Y459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="Y459" s="1" t="n">
+      <c r="Z459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -36828,9 +38208,12 @@
         <v>0.007446</v>
       </c>
       <c r="X460" s="1" t="n">
+        <v>0.007434</v>
+      </c>
+      <c r="Y460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="Y460" s="1" t="n">
+      <c r="Z460" s="1" t="n">
         <v>0.007353</v>
       </c>
     </row>
@@ -36907,9 +38290,12 @@
         <v>0.0001755</v>
       </c>
       <c r="X461" s="1" t="n">
+        <v>0.0001776</v>
+      </c>
+      <c r="Y461" s="1" t="n">
         <v>0.0001899</v>
       </c>
-      <c r="Y461" s="1" t="n">
+      <c r="Z461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -36986,9 +38372,12 @@
         <v>0.02386</v>
       </c>
       <c r="X462" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="Y462" s="1" t="n">
         <v>0.02585</v>
       </c>
-      <c r="Y462" s="1" t="n">
+      <c r="Z462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -37065,10 +38454,13 @@
         <v>0.03642</v>
       </c>
       <c r="X463" s="1" t="n">
+        <v>0.03625</v>
+      </c>
+      <c r="Y463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="Y463" s="1" t="n">
-        <v>0.03642</v>
+      <c r="Z463" s="1" t="n">
+        <v>0.03625</v>
       </c>
     </row>
     <row r="464">
@@ -37144,9 +38536,12 @@
         <v>0.3012</v>
       </c>
       <c r="X464" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="Y464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="Y464" s="1" t="n">
+      <c r="Z464" s="1" t="n">
         <v>0.3003</v>
       </c>
     </row>
@@ -37223,9 +38618,12 @@
         <v>0.03877</v>
       </c>
       <c r="X465" s="1" t="n">
+        <v>0.03892</v>
+      </c>
+      <c r="Y465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="Y465" s="1" t="n">
+      <c r="Z465" s="1" t="n">
         <v>0.03877</v>
       </c>
     </row>
@@ -37302,10 +38700,13 @@
         <v>2.661</v>
       </c>
       <c r="X466" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="Y466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="Y466" s="1" t="n">
-        <v>2.66</v>
+      <c r="Z466" s="1" t="n">
+        <v>2.656</v>
       </c>
     </row>
     <row r="467">
@@ -37381,9 +38782,12 @@
         <v>0.03454</v>
       </c>
       <c r="X467" s="1" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="Y467" s="1" t="n">
         <v>0.03454</v>
       </c>
-      <c r="Y467" s="1" t="n">
+      <c r="Z467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -37460,10 +38864,13 @@
         <v>0.1762</v>
       </c>
       <c r="X468" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="Y468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="Y468" s="1" t="n">
-        <v>0.1758</v>
+      <c r="Z468" s="1" t="n">
+        <v>0.175</v>
       </c>
     </row>
     <row r="469">
@@ -37539,9 +38946,12 @@
         <v>0.0959</v>
       </c>
       <c r="X469" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="Y469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="Y469" s="1" t="n">
+      <c r="Z469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -37618,9 +39028,12 @@
         <v>0.06753000000000001</v>
       </c>
       <c r="X470" s="1" t="n">
+        <v>0.06753000000000001</v>
+      </c>
+      <c r="Y470" s="1" t="n">
         <v>0.06838</v>
       </c>
-      <c r="Y470" s="1" t="n">
+      <c r="Z470" s="1" t="n">
         <v>0.06696000000000001</v>
       </c>
     </row>
@@ -37697,10 +39110,13 @@
         <v>0.0396</v>
       </c>
       <c r="X471" s="1" t="n">
+        <v>0.03956</v>
+      </c>
+      <c r="Y471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="Y471" s="1" t="n">
-        <v>0.0396</v>
+      <c r="Z471" s="1" t="n">
+        <v>0.03956</v>
       </c>
     </row>
     <row r="472">
@@ -37776,10 +39192,13 @@
         <v>0.2457</v>
       </c>
       <c r="X472" s="1" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="Y472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="Y472" s="1" t="n">
-        <v>0.2457</v>
+      <c r="Z472" s="1" t="n">
+        <v>0.2455</v>
       </c>
     </row>
     <row r="473">
@@ -37855,9 +39274,12 @@
         <v>0.016255</v>
       </c>
       <c r="X473" s="1" t="n">
+        <v>0.016293</v>
+      </c>
+      <c r="Y473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="Y473" s="1" t="n">
+      <c r="Z473" s="1" t="n">
         <v>0.016238</v>
       </c>
     </row>
@@ -37934,9 +39356,12 @@
         <v>0.1148</v>
       </c>
       <c r="X474" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="Y474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="Y474" s="1" t="n">
+      <c r="Z474" s="1" t="n">
         <v>0.1146</v>
       </c>
     </row>
@@ -38013,9 +39438,12 @@
         <v>0.04309</v>
       </c>
       <c r="X475" s="1" t="n">
-        <v>0.04309</v>
+        <v>0.04349</v>
       </c>
       <c r="Y475" s="1" t="n">
+        <v>0.04349</v>
+      </c>
+      <c r="Z475" s="1" t="n">
         <v>0.04258</v>
       </c>
     </row>
@@ -38092,9 +39520,12 @@
         <v>0.2067</v>
       </c>
       <c r="X476" s="1" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="Y476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="Y476" s="1" t="n">
+      <c r="Z476" s="1" t="n">
         <v>0.2062</v>
       </c>
     </row>
@@ -38171,9 +39602,12 @@
         <v>0.006791</v>
       </c>
       <c r="X477" s="1" t="n">
+        <v>0.006772</v>
+      </c>
+      <c r="Y477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="Y477" s="1" t="n">
+      <c r="Z477" s="1" t="n">
         <v>0.006763</v>
       </c>
     </row>
@@ -38250,10 +39684,13 @@
         <v>0.01776</v>
       </c>
       <c r="X478" s="1" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="Y478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="Y478" s="1" t="n">
-        <v>0.01776</v>
+      <c r="Z478" s="1" t="n">
+        <v>0.01775</v>
       </c>
     </row>
     <row r="479">
@@ -38329,9 +39766,12 @@
         <v>0.04648</v>
       </c>
       <c r="X479" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="Y479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="Y479" s="1" t="n">
+      <c r="Z479" s="1" t="n">
         <v>0.04639</v>
       </c>
     </row>
@@ -38408,9 +39848,12 @@
         <v>0.26138</v>
       </c>
       <c r="X480" s="1" t="n">
+        <v>0.26134</v>
+      </c>
+      <c r="Y480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="Y480" s="1" t="n">
+      <c r="Z480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -38487,9 +39930,12 @@
         <v>0.01201</v>
       </c>
       <c r="X481" s="1" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="Y481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="Y481" s="1" t="n">
+      <c r="Z481" s="1" t="n">
         <v>0.01201</v>
       </c>
     </row>
@@ -38566,10 +40012,13 @@
         <v>0.004071</v>
       </c>
       <c r="X482" s="1" t="n">
+        <v>0.004053</v>
+      </c>
+      <c r="Y482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="Y482" s="1" t="n">
-        <v>0.004055</v>
+      <c r="Z482" s="1" t="n">
+        <v>0.004053</v>
       </c>
     </row>
     <row r="483">
@@ -38645,9 +40094,12 @@
         <v>0.1226</v>
       </c>
       <c r="X483" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="Y483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="Y483" s="1" t="n">
+      <c r="Z483" s="1" t="n">
         <v>0.1224</v>
       </c>
     </row>
@@ -38724,9 +40176,12 @@
         <v>0.02205</v>
       </c>
       <c r="X484" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="Y484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="Y484" s="1" t="n">
+      <c r="Z484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -38803,9 +40258,12 @@
         <v>0.04557</v>
       </c>
       <c r="X485" s="1" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="Y485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="Y485" s="1" t="n">
+      <c r="Z485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -38882,9 +40340,12 @@
         <v>0.1717</v>
       </c>
       <c r="X486" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="Y486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="Y486" s="1" t="n">
+      <c r="Z486" s="1" t="n">
         <v>0.1716</v>
       </c>
     </row>
@@ -38961,9 +40422,12 @@
         <v>0.2757</v>
       </c>
       <c r="X487" s="1" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="Y487" s="1" t="n">
         <v>0.2767</v>
       </c>
-      <c r="Y487" s="1" t="n">
+      <c r="Z487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -39040,9 +40504,12 @@
         <v>0.04589</v>
       </c>
       <c r="X488" s="1" t="n">
+        <v>0.04594</v>
+      </c>
+      <c r="Y488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="Y488" s="1" t="n">
+      <c r="Z488" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -39119,9 +40586,12 @@
         <v>0.0002137</v>
       </c>
       <c r="X489" s="1" t="n">
+        <v>0.0002143</v>
+      </c>
+      <c r="Y489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="Y489" s="1" t="n">
+      <c r="Z489" s="1" t="n">
         <v>0.0002137</v>
       </c>
     </row>
@@ -39198,9 +40668,12 @@
         <v>1.778</v>
       </c>
       <c r="X490" s="1" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="Y490" s="1" t="n">
         <v>1.783</v>
       </c>
-      <c r="Y490" s="1" t="n">
+      <c r="Z490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -39277,9 +40750,12 @@
         <v>15.991</v>
       </c>
       <c r="X491" s="1" t="n">
+        <v>16.004</v>
+      </c>
+      <c r="Y491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="Y491" s="1" t="n">
+      <c r="Z491" s="1" t="n">
         <v>15.99</v>
       </c>
     </row>
@@ -39356,9 +40832,12 @@
         <v>0.06637</v>
       </c>
       <c r="X492" s="1" t="n">
+        <v>0.06641</v>
+      </c>
+      <c r="Y492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="Y492" s="1" t="n">
+      <c r="Z492" s="1" t="n">
         <v>0.06637</v>
       </c>
     </row>
@@ -39435,9 +40914,12 @@
         <v>0.0672</v>
       </c>
       <c r="X493" s="1" t="n">
+        <v>0.06747</v>
+      </c>
+      <c r="Y493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="Y493" s="1" t="n">
+      <c r="Z493" s="1" t="n">
         <v>0.06709</v>
       </c>
     </row>
@@ -39514,9 +40996,12 @@
         <v>0.009396</v>
       </c>
       <c r="X494" s="1" t="n">
+        <v>0.009396</v>
+      </c>
+      <c r="Y494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="Y494" s="1" t="n">
+      <c r="Z494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -39593,9 +41078,12 @@
         <v>0.005844</v>
       </c>
       <c r="X495" s="1" t="n">
+        <v>0.005822</v>
+      </c>
+      <c r="Y495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="Y495" s="1" t="n">
+      <c r="Z495" s="1" t="n">
         <v>0.005774</v>
       </c>
     </row>
@@ -39672,10 +41160,13 @@
         <v>0.00975</v>
       </c>
       <c r="X496" s="1" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="Y496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="Y496" s="1" t="n">
-        <v>0.00975</v>
+      <c r="Z496" s="1" t="n">
+        <v>0.009730000000000001</v>
       </c>
     </row>
     <row r="497">
@@ -39751,9 +41242,12 @@
         <v>0.04601</v>
       </c>
       <c r="X497" s="1" t="n">
+        <v>0.04584</v>
+      </c>
+      <c r="Y497" s="1" t="n">
         <v>0.04665</v>
       </c>
-      <c r="Y497" s="1" t="n">
+      <c r="Z497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -39830,9 +41324,12 @@
         <v>0.006351</v>
       </c>
       <c r="X498" s="1" t="n">
+        <v>0.006363</v>
+      </c>
+      <c r="Y498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="Y498" s="1" t="n">
+      <c r="Z498" s="1" t="n">
         <v>0.006338</v>
       </c>
     </row>
@@ -39909,9 +41406,12 @@
         <v>0.01023</v>
       </c>
       <c r="X499" s="1" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="Y499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="Y499" s="1" t="n">
+      <c r="Z499" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -39988,10 +41488,13 @@
         <v>0.5061</v>
       </c>
       <c r="X500" s="1" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="Y500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="Y500" s="1" t="n">
-        <v>0.5061</v>
+      <c r="Z500" s="1" t="n">
+        <v>0.5058</v>
       </c>
     </row>
     <row r="501">
@@ -40067,9 +41570,12 @@
         <v>0.03208</v>
       </c>
       <c r="X501" s="1" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="Y501" s="1" t="n">
         <v>0.03213</v>
       </c>
-      <c r="Y501" s="1" t="n">
+      <c r="Z501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -40146,9 +41652,12 @@
         <v>0.4344</v>
       </c>
       <c r="X502" s="1" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="Y502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="Y502" s="1" t="n">
+      <c r="Z502" s="1" t="n">
         <v>0.4326</v>
       </c>
     </row>
@@ -40225,9 +41734,12 @@
         <v>0.999342</v>
       </c>
       <c r="X503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="Y503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="Y503" s="1" t="n">
+      <c r="Z503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -40304,9 +41816,12 @@
         <v>0.03515</v>
       </c>
       <c r="X504" s="1" t="n">
+        <v>0.03526</v>
+      </c>
+      <c r="Y504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="Y504" s="1" t="n">
+      <c r="Z504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -40383,9 +41898,12 @@
         <v>0.004893</v>
       </c>
       <c r="X505" s="1" t="n">
+        <v>0.004906</v>
+      </c>
+      <c r="Y505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="Y505" s="1" t="n">
+      <c r="Z505" s="1" t="n">
         <v>0.004892</v>
       </c>
     </row>
@@ -40462,9 +41980,12 @@
         <v>0.01382</v>
       </c>
       <c r="X506" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="Y506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="Y506" s="1" t="n">
+      <c r="Z506" s="1" t="n">
         <v>0.0138</v>
       </c>
     </row>
@@ -40541,10 +42062,13 @@
         <v>0.003456</v>
       </c>
       <c r="X507" s="1" t="n">
+        <v>0.003449</v>
+      </c>
+      <c r="Y507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="Y507" s="1" t="n">
-        <v>0.003453</v>
+      <c r="Z507" s="1" t="n">
+        <v>0.003449</v>
       </c>
     </row>
     <row r="508">
@@ -40620,9 +42144,12 @@
         <v>1.411</v>
       </c>
       <c r="X508" s="1" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="Y508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="Y508" s="1" t="n">
+      <c r="Z508" s="1" t="n">
         <v>1.411</v>
       </c>
     </row>
@@ -40699,9 +42226,12 @@
         <v>0.005042</v>
       </c>
       <c r="X509" s="1" t="n">
+        <v>0.005038</v>
+      </c>
+      <c r="Y509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="Y509" s="1" t="n">
+      <c r="Z509" s="1" t="n">
         <v>0.005026</v>
       </c>
     </row>
@@ -40778,10 +42308,13 @@
         <v>0.01565</v>
       </c>
       <c r="X510" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="Y510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="Y510" s="1" t="n">
-        <v>0.0156</v>
+      <c r="Z510" s="1" t="n">
+        <v>0.01556</v>
       </c>
     </row>
     <row r="511">
@@ -40857,9 +42390,12 @@
         <v>0.08149000000000001</v>
       </c>
       <c r="X511" s="1" t="n">
+        <v>0.08147</v>
+      </c>
+      <c r="Y511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="Y511" s="1" t="n">
+      <c r="Z511" s="1" t="n">
         <v>0.08119</v>
       </c>
     </row>
@@ -40936,9 +42472,12 @@
         <v>0.007067</v>
       </c>
       <c r="X512" s="1" t="n">
+        <v>0.007072</v>
+      </c>
+      <c r="Y512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="Y512" s="1" t="n">
+      <c r="Z512" s="1" t="n">
         <v>0.007066</v>
       </c>
     </row>
@@ -41015,9 +42554,12 @@
         <v>0.01479</v>
       </c>
       <c r="X513" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="Y513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="Y513" s="1" t="n">
+      <c r="Z513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -41094,9 +42636,12 @@
         <v>0.04707</v>
       </c>
       <c r="X514" s="1" t="n">
+        <v>0.04705</v>
+      </c>
+      <c r="Y514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="Y514" s="1" t="n">
+      <c r="Z514" s="1" t="n">
         <v>0.04688</v>
       </c>
     </row>
@@ -41173,9 +42718,12 @@
         <v>0.01802</v>
       </c>
       <c r="X515" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="Y515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="Y515" s="1" t="n">
+      <c r="Z515" s="1" t="n">
         <v>0.01796</v>
       </c>
     </row>
@@ -41252,9 +42800,12 @@
         <v>0.0005791</v>
       </c>
       <c r="X516" s="1" t="n">
+        <v>0.0005781</v>
+      </c>
+      <c r="Y516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="Y516" s="1" t="n">
+      <c r="Z516" s="1" t="n">
         <v>0.000578</v>
       </c>
     </row>
@@ -41331,9 +42882,12 @@
         <v>0.07832</v>
       </c>
       <c r="X517" s="1" t="n">
+        <v>0.07838000000000001</v>
+      </c>
+      <c r="Y517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="Y517" s="1" t="n">
+      <c r="Z517" s="1" t="n">
         <v>0.07817</v>
       </c>
     </row>
@@ -41410,9 +42964,12 @@
         <v>0.006353</v>
       </c>
       <c r="X518" s="1" t="n">
+        <v>0.006358</v>
+      </c>
+      <c r="Y518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="Y518" s="1" t="n">
+      <c r="Z518" s="1" t="n">
         <v>0.006348</v>
       </c>
     </row>
@@ -41489,9 +43046,12 @@
         <v>0.05745</v>
       </c>
       <c r="X519" s="1" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="Y519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="Y519" s="1" t="n">
+      <c r="Z519" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -41568,9 +43128,12 @@
         <v>0.1039</v>
       </c>
       <c r="X520" s="1" t="n">
+        <v>0.10362</v>
+      </c>
+      <c r="Y520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="Y520" s="1" t="n">
+      <c r="Z520" s="1" t="n">
         <v>0.10321</v>
       </c>
     </row>
@@ -41647,9 +43210,12 @@
         <v>0.01789</v>
       </c>
       <c r="X521" s="1" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="Y521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="Y521" s="1" t="n">
+      <c r="Z521" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -41726,9 +43292,12 @@
         <v>0.01624</v>
       </c>
       <c r="X522" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="Y522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="Y522" s="1" t="n">
+      <c r="Z522" s="1" t="n">
         <v>0.01602</v>
       </c>
     </row>
@@ -41805,9 +43374,12 @@
         <v>0.01076</v>
       </c>
       <c r="X523" s="1" t="n">
+        <v>0.01084</v>
+      </c>
+      <c r="Y523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="Y523" s="1" t="n">
+      <c r="Z523" s="1" t="n">
         <v>0.01076</v>
       </c>
     </row>
@@ -41884,9 +43456,12 @@
         <v>0.007435</v>
       </c>
       <c r="X524" s="1" t="n">
+        <v>0.007429</v>
+      </c>
+      <c r="Y524" s="1" t="n">
         <v>0.007435</v>
       </c>
-      <c r="Y524" s="1" t="n">
+      <c r="Z524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -41963,9 +43538,12 @@
         <v>0.005766</v>
       </c>
       <c r="X525" s="1" t="n">
+        <v>0.005777</v>
+      </c>
+      <c r="Y525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="Y525" s="1" t="n">
+      <c r="Z525" s="1" t="n">
         <v>0.005766</v>
       </c>
     </row>
@@ -42042,9 +43620,12 @@
         <v>0.001428</v>
       </c>
       <c r="X526" s="1" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="Y526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="Y526" s="1" t="n">
+      <c r="Z526" s="1" t="n">
         <v>0.001428</v>
       </c>
     </row>
@@ -42121,9 +43702,12 @@
         <v>0.373</v>
       </c>
       <c r="X527" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="Y527" s="1" t="n">
         <v>0.375</v>
       </c>
-      <c r="Y527" s="1" t="n">
+      <c r="Z527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -42200,9 +43784,12 @@
         <v>0.005256</v>
       </c>
       <c r="X528" s="1" t="n">
+        <v>0.005288</v>
+      </c>
+      <c r="Y528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="Y528" s="1" t="n">
+      <c r="Z528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -42279,9 +43866,12 @@
         <v>2.943</v>
       </c>
       <c r="X529" s="1" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="Y529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="Y529" s="1" t="n">
+      <c r="Z529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -42358,9 +43948,12 @@
         <v>0.1522</v>
       </c>
       <c r="X530" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="Y530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="Y530" s="1" t="n">
+      <c r="Z530" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -42437,9 +44030,12 @@
         <v>2580</v>
       </c>
       <c r="X531" s="1" t="n">
-        <v>2584</v>
+        <v>2595</v>
       </c>
       <c r="Y531" s="1" t="n">
+        <v>2595</v>
+      </c>
+      <c r="Z531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -42516,9 +44112,12 @@
         <v>0.03904</v>
       </c>
       <c r="X532" s="1" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="Y532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="Y532" s="1" t="n">
+      <c r="Z532" s="1" t="n">
         <v>0.03893</v>
       </c>
     </row>
@@ -42595,9 +44194,12 @@
         <v>0.02191</v>
       </c>
       <c r="X533" s="1" t="n">
-        <v>0.02192</v>
+        <v>0.02193</v>
       </c>
       <c r="Y533" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="Z533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -42674,9 +44276,12 @@
         <v>0.0728</v>
       </c>
       <c r="X534" s="1" t="n">
+        <v>0.07289</v>
+      </c>
+      <c r="Y534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="Y534" s="1" t="n">
+      <c r="Z534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -42753,9 +44358,12 @@
         <v>0.007802</v>
       </c>
       <c r="X535" s="1" t="n">
+        <v>0.007837999999999999</v>
+      </c>
+      <c r="Y535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="Y535" s="1" t="n">
+      <c r="Z535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -42832,9 +44440,12 @@
         <v>0.04976</v>
       </c>
       <c r="X536" s="1" t="n">
+        <v>0.04979</v>
+      </c>
+      <c r="Y536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="Y536" s="1" t="n">
+      <c r="Z536" s="1" t="n">
         <v>0.04976</v>
       </c>
     </row>
@@ -42911,9 +44522,12 @@
         <v>0.004</v>
       </c>
       <c r="X537" s="1" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="Y537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="Y537" s="1" t="n">
+      <c r="Z537" s="1" t="n">
         <v>0.00397</v>
       </c>
     </row>
@@ -42990,9 +44604,12 @@
         <v>0.08261</v>
       </c>
       <c r="X538" s="1" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="Y538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="Y538" s="1" t="n">
+      <c r="Z538" s="1" t="n">
         <v>0.08252</v>
       </c>
     </row>
@@ -43069,10 +44686,13 @@
         <v>0.02464</v>
       </c>
       <c r="X539" s="1" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="Y539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="Y539" s="1" t="n">
-        <v>0.02464</v>
+      <c r="Z539" s="1" t="n">
+        <v>0.0246</v>
       </c>
     </row>
     <row r="540">
@@ -43148,9 +44768,12 @@
         <v>0.0843</v>
       </c>
       <c r="X540" s="1" t="n">
+        <v>0.08423</v>
+      </c>
+      <c r="Y540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="Y540" s="1" t="n">
+      <c r="Z540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -43227,9 +44850,12 @@
         <v>0.01882</v>
       </c>
       <c r="X541" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="Y541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="Y541" s="1" t="n">
+      <c r="Z541" s="1" t="n">
         <v>0.0188</v>
       </c>
     </row>
@@ -43306,9 +44932,12 @@
         <v>0.01673</v>
       </c>
       <c r="X542" s="1" t="n">
+        <v>0.01673</v>
+      </c>
+      <c r="Y542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="Y542" s="1" t="n">
+      <c r="Z542" s="1" t="n">
         <v>0.01673</v>
       </c>
     </row>
@@ -43385,9 +45014,12 @@
         <v>0.1044</v>
       </c>
       <c r="X543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="Y543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="Y543" s="1" t="n">
+      <c r="Z543" s="1" t="n">
         <v>0.1044</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z543"/>
+  <dimension ref="A1:AA543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -443,8 +443,9 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,10 +571,15 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>price_06:00</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -655,9 +661,12 @@
         <v>70721.8</v>
       </c>
       <c r="Y2" s="1" t="n">
+        <v>70749.7</v>
+      </c>
+      <c r="Z2" s="1" t="n">
         <v>70796.5</v>
       </c>
-      <c r="Z2" s="1" t="n">
+      <c r="AA2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -737,9 +746,12 @@
         <v>2084.38</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>2084.79</v>
+        <v>2085.47</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>2085.47</v>
+      </c>
+      <c r="AA3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -819,9 +831,12 @@
         <v>87.06</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>87.06</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="Z4" s="1" t="n">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="AA4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -901,9 +916,12 @@
         <v>4</v>
       </c>
       <c r="Y5" s="1" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="Z5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="AA5" s="1" t="n">
         <v>3.967</v>
       </c>
     </row>
@@ -983,9 +1001,12 @@
         <v>0.09481000000000001</v>
       </c>
       <c r="Y6" s="1" t="n">
+        <v>0.09499</v>
+      </c>
+      <c r="Z6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="AA6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -1065,9 +1086,12 @@
         <v>1.3943</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.3943</v>
+        <v>1.3945</v>
       </c>
       <c r="Z7" s="1" t="n">
+        <v>1.3945</v>
+      </c>
+      <c r="AA7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -1147,9 +1171,12 @@
         <v>21.94</v>
       </c>
       <c r="Y8" s="1" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="Z8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="Z8" s="1" t="n">
+      <c r="AA8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1229,9 +1256,12 @@
         <v>0.00201</v>
       </c>
       <c r="Y9" s="1" t="n">
+        <v>0.002013</v>
+      </c>
+      <c r="Z9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="AA9" s="1" t="n">
         <v>0.001951</v>
       </c>
     </row>
@@ -1311,9 +1341,12 @@
         <v>0.009830999999999999</v>
       </c>
       <c r="Y10" s="1" t="n">
+        <v>0.009691999999999999</v>
+      </c>
+      <c r="Z10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="AA10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1393,9 +1426,12 @@
         <v>0.15476</v>
       </c>
       <c r="Y11" s="1" t="n">
+        <v>0.15205</v>
+      </c>
+      <c r="Z11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="Z11" s="1" t="n">
+      <c r="AA11" s="1" t="n">
         <v>0.13631</v>
       </c>
     </row>
@@ -1475,9 +1511,12 @@
         <v>0.011095</v>
       </c>
       <c r="Y12" s="1" t="n">
+        <v>0.011401</v>
+      </c>
+      <c r="Z12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="Z12" s="1" t="n">
+      <c r="AA12" s="1" t="n">
         <v>0.010924</v>
       </c>
     </row>
@@ -1557,9 +1596,12 @@
         <v>37.75</v>
       </c>
       <c r="Y13" s="1" t="n">
+        <v>37.985</v>
+      </c>
+      <c r="Z13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="Z13" s="1" t="n">
+      <c r="AA13" s="1" t="n">
         <v>37.748</v>
       </c>
     </row>
@@ -1639,9 +1681,12 @@
         <v>654.1</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>654.13</v>
+        <v>654.65</v>
       </c>
       <c r="Z14" s="1" t="n">
+        <v>654.65</v>
+      </c>
+      <c r="AA14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1721,9 +1766,12 @@
         <v>210.54</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>210.54</v>
+        <v>211.44</v>
       </c>
       <c r="Z15" s="1" t="n">
+        <v>211.44</v>
+      </c>
+      <c r="AA15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1803,9 +1851,12 @@
         <v>0.0033262</v>
       </c>
       <c r="Y16" s="1" t="n">
+        <v>0.0033309</v>
+      </c>
+      <c r="Z16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="Z16" s="1" t="n">
+      <c r="AA16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1885,9 +1936,12 @@
         <v>244.53</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>244.53</v>
+        <v>246.56</v>
       </c>
       <c r="Z17" s="1" t="n">
+        <v>246.56</v>
+      </c>
+      <c r="AA17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1967,9 +2021,12 @@
         <v>0.9903999999999999</v>
       </c>
       <c r="Y18" s="1" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="Z18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="Z18" s="1" t="n">
+      <c r="AA18" s="1" t="n">
         <v>0.9858</v>
       </c>
     </row>
@@ -2049,9 +2106,12 @@
         <v>0.9887</v>
       </c>
       <c r="Y19" s="1" t="n">
+        <v>0.9902</v>
+      </c>
+      <c r="Z19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="Z19" s="1" t="n">
+      <c r="AA19" s="1" t="n">
         <v>0.9887</v>
       </c>
     </row>
@@ -2131,9 +2191,12 @@
         <v>0.2598</v>
       </c>
       <c r="Y20" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Z20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="Z20" s="1" t="n">
+      <c r="AA20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -2213,10 +2276,13 @@
         <v>0.58548</v>
       </c>
       <c r="Y21" s="1" t="n">
+        <v>0.58081</v>
+      </c>
+      <c r="Z21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="Z21" s="1" t="n">
-        <v>0.58548</v>
+      <c r="AA21" s="1" t="n">
+        <v>0.58081</v>
       </c>
     </row>
     <row r="22">
@@ -2295,9 +2361,12 @@
         <v>9.066000000000001</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>9.066000000000001</v>
+        <v>9.086</v>
       </c>
       <c r="Z22" s="1" t="n">
+        <v>9.086</v>
+      </c>
+      <c r="AA22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -2377,9 +2446,12 @@
         <v>0.02373</v>
       </c>
       <c r="Y23" s="1" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="Z23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="Z23" s="1" t="n">
+      <c r="AA23" s="1" t="n">
         <v>0.02359</v>
       </c>
     </row>
@@ -2459,9 +2531,12 @@
         <v>9.581</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>9.599</v>
+        <v>9.606999999999999</v>
       </c>
       <c r="Z24" s="1" t="n">
+        <v>9.606999999999999</v>
+      </c>
+      <c r="AA24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2541,9 +2616,12 @@
         <v>1.218</v>
       </c>
       <c r="Y25" s="1" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="Z25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z25" s="1" t="n">
+      <c r="AA25" s="1" t="n">
         <v>1.216</v>
       </c>
     </row>
@@ -2623,9 +2701,12 @@
         <v>0.07199</v>
       </c>
       <c r="Y26" s="1" t="n">
+        <v>0.07167999999999999</v>
+      </c>
+      <c r="Z26" s="1" t="n">
         <v>0.07317</v>
       </c>
-      <c r="Z26" s="1" t="n">
+      <c r="AA26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2705,9 +2786,12 @@
         <v>1.409</v>
       </c>
       <c r="Y27" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z27" s="1" t="n">
+      <c r="AA27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2787,9 +2871,12 @@
         <v>1.304</v>
       </c>
       <c r="Y28" s="1" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="Z28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="Z28" s="1" t="n">
+      <c r="AA28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2869,9 +2956,12 @@
         <v>464.45</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>464.45</v>
+        <v>465.03</v>
       </c>
       <c r="Z29" s="1" t="n">
+        <v>465.03</v>
+      </c>
+      <c r="AA29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2951,9 +3041,12 @@
         <v>1.2894</v>
       </c>
       <c r="Y30" s="1" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="Z30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="Z30" s="1" t="n">
+      <c r="AA30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -3033,9 +3126,12 @@
         <v>5020.52</v>
       </c>
       <c r="Y31" s="1" t="n">
+        <v>5020.55</v>
+      </c>
+      <c r="Z31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="Z31" s="1" t="n">
+      <c r="AA31" s="1" t="n">
         <v>5019.32</v>
       </c>
     </row>
@@ -3115,9 +3211,12 @@
         <v>0.876</v>
       </c>
       <c r="Y32" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="Z32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="Z32" s="1" t="n">
+      <c r="AA32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -3197,9 +3296,12 @@
         <v>0.001966</v>
       </c>
       <c r="Y33" s="1" t="n">
+        <v>0.001968</v>
+      </c>
+      <c r="Z33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="Z33" s="1" t="n">
+      <c r="AA33" s="1" t="n">
         <v>0.001965</v>
       </c>
     </row>
@@ -3279,9 +3381,12 @@
         <v>0.17411</v>
       </c>
       <c r="Y34" s="1" t="n">
+        <v>0.17223</v>
+      </c>
+      <c r="Z34" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="Z34" s="1" t="n">
+      <c r="AA34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -3361,9 +3466,12 @@
         <v>0.29715</v>
       </c>
       <c r="Y35" s="1" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="Z35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="Z35" s="1" t="n">
+      <c r="AA35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -3443,9 +3551,12 @@
         <v>1.794</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>1.798</v>
+        <v>1.812</v>
       </c>
       <c r="Z36" s="1" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="AA36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -3525,9 +3636,12 @@
         <v>110.35</v>
       </c>
       <c r="Y37" s="1" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="Z37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="Z37" s="1" t="n">
+      <c r="AA37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -3607,9 +3721,12 @@
         <v>0.22009</v>
       </c>
       <c r="Y38" s="1" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="Z38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="Z38" s="1" t="n">
+      <c r="AA38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -3689,9 +3806,12 @@
         <v>0.1067</v>
       </c>
       <c r="Y39" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="Z39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="Z39" s="1" t="n">
+      <c r="AA39" s="1" t="n">
         <v>0.1063</v>
       </c>
     </row>
@@ -3771,10 +3891,13 @@
         <v>0.36777</v>
       </c>
       <c r="Y40" s="1" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="Z40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="Z40" s="1" t="n">
-        <v>0.36777</v>
+      <c r="AA40" s="1" t="n">
+        <v>0.36747</v>
       </c>
     </row>
     <row r="41">
@@ -3853,9 +3976,12 @@
         <v>54.58</v>
       </c>
       <c r="Y41" s="1" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="Z41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="Z41" s="1" t="n">
+      <c r="AA41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3935,9 +4061,12 @@
         <v>0.0010563</v>
       </c>
       <c r="Y42" s="1" t="n">
+        <v>0.0010557</v>
+      </c>
+      <c r="Z42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="Z42" s="1" t="n">
+      <c r="AA42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -4017,9 +4146,12 @@
         <v>6.462</v>
       </c>
       <c r="Y43" s="1" t="n">
+        <v>6.479</v>
+      </c>
+      <c r="Z43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="Z43" s="1" t="n">
+      <c r="AA43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -4099,9 +4231,12 @@
         <v>0.6278</v>
       </c>
       <c r="Y44" s="1" t="n">
+        <v>0.6298</v>
+      </c>
+      <c r="Z44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="Z44" s="1" t="n">
+      <c r="AA44" s="1" t="n">
         <v>0.6213</v>
       </c>
     </row>
@@ -4181,9 +4316,12 @@
         <v>0.3524</v>
       </c>
       <c r="Y45" s="1" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="Z45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="Z45" s="1" t="n">
+      <c r="AA45" s="1" t="n">
         <v>0.3512</v>
       </c>
     </row>
@@ -4263,9 +4401,12 @@
         <v>0.03318</v>
       </c>
       <c r="Y46" s="1" t="n">
+        <v>0.03296</v>
+      </c>
+      <c r="Z46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="Z46" s="1" t="n">
+      <c r="AA46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -4345,9 +4486,12 @@
         <v>0.06763</v>
       </c>
       <c r="Y47" s="1" t="n">
+        <v>0.06882000000000001</v>
+      </c>
+      <c r="Z47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="Z47" s="1" t="n">
+      <c r="AA47" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -4427,9 +4571,12 @@
         <v>0.7108</v>
       </c>
       <c r="Y48" s="1" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="Z48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="Z48" s="1" t="n">
+      <c r="AA48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -4509,9 +4656,12 @@
         <v>0.004291</v>
       </c>
       <c r="Y49" s="1" t="n">
+        <v>0.004292</v>
+      </c>
+      <c r="Z49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="Z49" s="1" t="n">
+      <c r="AA49" s="1" t="n">
         <v>0.004224</v>
       </c>
     </row>
@@ -4591,9 +4741,12 @@
         <v>0.1034</v>
       </c>
       <c r="Y50" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="Z50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="Z50" s="1" t="n">
+      <c r="AA50" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -4673,9 +4826,12 @@
         <v>0.03999</v>
       </c>
       <c r="Y51" s="1" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="Z51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="Z51" s="1" t="n">
+      <c r="AA51" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -4755,9 +4911,12 @@
         <v>0.1643</v>
       </c>
       <c r="Y52" s="1" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="Z52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="Z52" s="1" t="n">
+      <c r="AA52" s="1" t="n">
         <v>0.1641</v>
       </c>
     </row>
@@ -4837,9 +4996,12 @@
         <v>0.01954</v>
       </c>
       <c r="Y53" s="1" t="n">
+        <v>0.01923</v>
+      </c>
+      <c r="Z53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="Z53" s="1" t="n">
+      <c r="AA53" s="1" t="n">
         <v>0.01922</v>
       </c>
     </row>
@@ -4919,9 +5081,12 @@
         <v>0.007175</v>
       </c>
       <c r="Y54" s="1" t="n">
+        <v>0.007191</v>
+      </c>
+      <c r="Z54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="Z54" s="1" t="n">
+      <c r="AA54" s="1" t="n">
         <v>0.007168</v>
       </c>
     </row>
@@ -5001,9 +5166,12 @@
         <v>3.914</v>
       </c>
       <c r="Y55" s="1" t="n">
+        <v>3.921</v>
+      </c>
+      <c r="Z55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="Z55" s="1" t="n">
+      <c r="AA55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -5083,10 +5251,13 @@
         <v>0.016759</v>
       </c>
       <c r="Y56" s="1" t="n">
+        <v>0.016749</v>
+      </c>
+      <c r="Z56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="Z56" s="1" t="n">
-        <v>0.016759</v>
+      <c r="AA56" s="1" t="n">
+        <v>0.016749</v>
       </c>
     </row>
     <row r="57">
@@ -5165,9 +5336,12 @@
         <v>0.1082</v>
       </c>
       <c r="Y57" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="Z57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="Z57" s="1" t="n">
+      <c r="AA57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -5247,9 +5421,12 @@
         <v>2.656</v>
       </c>
       <c r="Y58" s="1" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="Z58" s="1" t="n">
+      <c r="AA58" s="1" t="n">
         <v>2.639</v>
       </c>
     </row>
@@ -5329,9 +5506,12 @@
         <v>0.1573</v>
       </c>
       <c r="Y59" s="1" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="Z59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="Z59" s="1" t="n">
+      <c r="AA59" s="1" t="n">
         <v>0.157</v>
       </c>
     </row>
@@ -5411,9 +5591,12 @@
         <v>0.005841</v>
       </c>
       <c r="Y60" s="1" t="n">
+        <v>0.005842</v>
+      </c>
+      <c r="Z60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="Z60" s="1" t="n">
+      <c r="AA60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -5493,9 +5676,12 @@
         <v>0.09203</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.09215</v>
+        <v>0.09234000000000001</v>
       </c>
       <c r="Z61" s="1" t="n">
+        <v>0.09234000000000001</v>
+      </c>
+      <c r="AA61" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5575,9 +5761,12 @@
         <v>0.9112</v>
       </c>
       <c r="Y62" s="1" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="Z62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="Z62" s="1" t="n">
+      <c r="AA62" s="1" t="n">
         <v>0.9101</v>
       </c>
     </row>
@@ -5657,9 +5846,12 @@
         <v>0.778</v>
       </c>
       <c r="Y63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="Z63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="Z63" s="1" t="n">
+      <c r="AA63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -5739,10 +5931,13 @@
         <v>0.04563</v>
       </c>
       <c r="Y64" s="1" t="n">
+        <v>0.04559</v>
+      </c>
+      <c r="Z64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="Z64" s="1" t="n">
-        <v>0.04563</v>
+      <c r="AA64" s="1" t="n">
+        <v>0.04559</v>
       </c>
     </row>
     <row r="65">
@@ -5821,9 +6016,12 @@
         <v>358.13</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>358.18</v>
+        <v>358.88</v>
       </c>
       <c r="Z65" s="1" t="n">
+        <v>358.88</v>
+      </c>
+      <c r="AA65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -5903,9 +6101,12 @@
         <v>0.12514</v>
       </c>
       <c r="Y66" s="1" t="n">
+        <v>0.12557</v>
+      </c>
+      <c r="Z66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="Z66" s="1" t="n">
+      <c r="AA66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -5985,9 +6186,12 @@
         <v>0.2307</v>
       </c>
       <c r="Y67" s="1" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="Z67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="Z67" s="1" t="n">
+      <c r="AA67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -6067,9 +6271,12 @@
         <v>0.00336</v>
       </c>
       <c r="Y68" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="Z68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="Z68" s="1" t="n">
+      <c r="AA68" s="1" t="n">
         <v>0.00335</v>
       </c>
     </row>
@@ -6149,9 +6356,12 @@
         <v>0.1745</v>
       </c>
       <c r="Y69" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="Z69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="Z69" s="1" t="n">
+      <c r="AA69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -6231,9 +6441,12 @@
         <v>0.16385</v>
       </c>
       <c r="Y70" s="1" t="n">
+        <v>0.16446</v>
+      </c>
+      <c r="Z70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="Z70" s="1" t="n">
+      <c r="AA70" s="1" t="n">
         <v>0.16358</v>
       </c>
     </row>
@@ -6313,9 +6526,12 @@
         <v>0.3544</v>
       </c>
       <c r="Y71" s="1" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="Z71" s="1" t="n">
         <v>0.3599</v>
       </c>
-      <c r="Z71" s="1" t="n">
+      <c r="AA71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -6395,9 +6611,12 @@
         <v>0.7074</v>
       </c>
       <c r="Y72" s="1" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="Z72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="Z72" s="1" t="n">
+      <c r="AA72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -6477,9 +6696,12 @@
         <v>0.00868</v>
       </c>
       <c r="Y73" s="1" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="Z73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="Z73" s="1" t="n">
+      <c r="AA73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -6559,9 +6781,12 @@
         <v>0.005977</v>
       </c>
       <c r="Y74" s="1" t="n">
+        <v>0.005985</v>
+      </c>
+      <c r="Z74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="Z74" s="1" t="n">
+      <c r="AA74" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -6641,9 +6866,12 @@
         <v>0.229</v>
       </c>
       <c r="Y75" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="Z75" s="1" t="n">
         <v>0.23</v>
       </c>
-      <c r="Z75" s="1" t="n">
+      <c r="AA75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -6723,9 +6951,12 @@
         <v>0.3342</v>
       </c>
       <c r="Y76" s="1" t="n">
-        <v>0.3342</v>
+        <v>0.3354</v>
       </c>
       <c r="Z76" s="1" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AA76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -6805,9 +7036,12 @@
         <v>0.1001</v>
       </c>
       <c r="Y77" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="Z77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="Z77" s="1" t="n">
+      <c r="AA77" s="1" t="n">
         <v>0.0999</v>
       </c>
     </row>
@@ -6887,9 +7121,12 @@
         <v>0.1227</v>
       </c>
       <c r="Y78" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="Z78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="Z78" s="1" t="n">
+      <c r="AA78" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -6969,9 +7206,12 @@
         <v>0.07444000000000001</v>
       </c>
       <c r="Y79" s="1" t="n">
+        <v>0.07484</v>
+      </c>
+      <c r="Z79" s="1" t="n">
         <v>0.07549</v>
       </c>
-      <c r="Z79" s="1" t="n">
+      <c r="AA79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -7051,9 +7291,12 @@
         <v>0.04629</v>
       </c>
       <c r="Y80" s="1" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="Z80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="Z80" s="1" t="n">
+      <c r="AA80" s="1" t="n">
         <v>0.04605</v>
       </c>
     </row>
@@ -7133,9 +7376,12 @@
         <v>0.000234</v>
       </c>
       <c r="Y81" s="1" t="n">
+        <v>0.000236</v>
+      </c>
+      <c r="Z81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="Z81" s="1" t="n">
+      <c r="AA81" s="1" t="n">
         <v>0.000228</v>
       </c>
     </row>
@@ -7215,9 +7461,12 @@
         <v>8.207000000000001</v>
       </c>
       <c r="Y82" s="1" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="Z82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="Z82" s="1" t="n">
+      <c r="AA82" s="1" t="n">
         <v>8.183999999999999</v>
       </c>
     </row>
@@ -7297,10 +7546,13 @@
         <v>0.0005679</v>
       </c>
       <c r="Y83" s="1" t="n">
+        <v>0.0005655</v>
+      </c>
+      <c r="Z83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="Z83" s="1" t="n">
-        <v>0.0005668</v>
+      <c r="AA83" s="1" t="n">
+        <v>0.0005655</v>
       </c>
     </row>
     <row r="84">
@@ -7379,9 +7631,12 @@
         <v>0.4511</v>
       </c>
       <c r="Y84" s="1" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="Z84" s="1" t="n">
         <v>0.4511</v>
       </c>
-      <c r="Z84" s="1" t="n">
+      <c r="AA84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -7461,9 +7716,12 @@
         <v>0.0625</v>
       </c>
       <c r="Y85" s="1" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="Z85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="Z85" s="1" t="n">
+      <c r="AA85" s="1" t="n">
         <v>0.0623</v>
       </c>
     </row>
@@ -7543,10 +7801,13 @@
         <v>0.05421</v>
       </c>
       <c r="Y86" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="Z86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="Z86" s="1" t="n">
-        <v>0.05403</v>
+      <c r="AA86" s="1" t="n">
+        <v>0.054</v>
       </c>
     </row>
     <row r="87">
@@ -7625,9 +7886,12 @@
         <v>0.003349</v>
       </c>
       <c r="Y87" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="Z87" s="1" t="n">
         <v>0.003368</v>
       </c>
-      <c r="Z87" s="1" t="n">
+      <c r="AA87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -7707,9 +7971,12 @@
         <v>0.04995</v>
       </c>
       <c r="Y88" s="1" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="Z88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="Z88" s="1" t="n">
+      <c r="AA88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -7789,9 +8056,12 @@
         <v>0.03178</v>
       </c>
       <c r="Y89" s="1" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="Z89" s="1" t="n">
         <v>0.03198</v>
       </c>
-      <c r="Z89" s="1" t="n">
+      <c r="AA89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -7871,9 +8141,12 @@
         <v>0.3443</v>
       </c>
       <c r="Y90" s="1" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Z90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="Z90" s="1" t="n">
+      <c r="AA90" s="1" t="n">
         <v>0.3436</v>
       </c>
     </row>
@@ -7953,9 +8226,12 @@
         <v>0.07826</v>
       </c>
       <c r="Y91" s="1" t="n">
+        <v>0.07732</v>
+      </c>
+      <c r="Z91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="Z91" s="1" t="n">
+      <c r="AA91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -8035,9 +8311,12 @@
         <v>0.353</v>
       </c>
       <c r="Y92" s="1" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="Z92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="Z92" s="1" t="n">
+      <c r="AA92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -8117,9 +8396,12 @@
         <v>1.9564</v>
       </c>
       <c r="Y93" s="1" t="n">
+        <v>1.9607</v>
+      </c>
+      <c r="Z93" s="1" t="n">
         <v>1.9816</v>
       </c>
-      <c r="Z93" s="1" t="n">
+      <c r="AA93" s="1" t="n">
         <v>1.9564</v>
       </c>
     </row>
@@ -8199,9 +8481,12 @@
         <v>0.2586</v>
       </c>
       <c r="Y94" s="1" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="Z94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="Z94" s="1" t="n">
+      <c r="AA94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -8281,9 +8566,12 @@
         <v>0.04525</v>
       </c>
       <c r="Y95" s="1" t="n">
+        <v>0.04539</v>
+      </c>
+      <c r="Z95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="Z95" s="1" t="n">
+      <c r="AA95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -8363,9 +8651,12 @@
         <v>0.006119</v>
       </c>
       <c r="Y96" s="1" t="n">
+        <v>0.006237</v>
+      </c>
+      <c r="Z96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="Z96" s="1" t="n">
+      <c r="AA96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -8445,9 +8736,12 @@
         <v>0.001716</v>
       </c>
       <c r="Y97" s="1" t="n">
+        <v>0.001721</v>
+      </c>
+      <c r="Z97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="Z97" s="1" t="n">
+      <c r="AA97" s="1" t="n">
         <v>0.001706</v>
       </c>
     </row>
@@ -8527,9 +8821,12 @@
         <v>5.256</v>
       </c>
       <c r="Y98" s="1" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="Z98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="Z98" s="1" t="n">
+      <c r="AA98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -8609,9 +8906,12 @@
         <v>0.01512</v>
       </c>
       <c r="Y99" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="Z99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="Z99" s="1" t="n">
+      <c r="AA99" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -8691,9 +8991,12 @@
         <v>0.5501</v>
       </c>
       <c r="Y100" s="1" t="n">
+        <v>0.5513</v>
+      </c>
+      <c r="Z100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="Z100" s="1" t="n">
+      <c r="AA100" s="1" t="n">
         <v>0.5501</v>
       </c>
     </row>
@@ -8773,9 +9076,12 @@
         <v>0.0898</v>
       </c>
       <c r="Y101" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="Z101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="Z101" s="1" t="n">
+      <c r="AA101" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -8855,9 +9161,12 @@
         <v>32.31</v>
       </c>
       <c r="Y102" s="1" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="Z102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="Z102" s="1" t="n">
+      <c r="AA102" s="1" t="n">
         <v>32.25</v>
       </c>
     </row>
@@ -8937,9 +9246,12 @@
         <v>0.0318</v>
       </c>
       <c r="Y103" s="1" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="Z103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="Z103" s="1" t="n">
+      <c r="AA103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -9019,9 +9331,12 @@
         <v>0.06559</v>
       </c>
       <c r="Y104" s="1" t="n">
+        <v>0.06579</v>
+      </c>
+      <c r="Z104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="Z104" s="1" t="n">
+      <c r="AA104" s="1" t="n">
         <v>0.06548</v>
       </c>
     </row>
@@ -9101,9 +9416,12 @@
         <v>1.2997</v>
       </c>
       <c r="Y105" s="1" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="Z105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="Z105" s="1" t="n">
+      <c r="AA105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -9183,9 +9501,12 @@
         <v>0.1192</v>
       </c>
       <c r="Y106" s="1" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="Z106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="Z106" s="1" t="n">
+      <c r="AA106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -9268,6 +9589,9 @@
         <v>0.121</v>
       </c>
       <c r="Z107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AA107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -9347,9 +9671,12 @@
         <v>0.09571</v>
       </c>
       <c r="Y108" s="1" t="n">
+        <v>0.09601</v>
+      </c>
+      <c r="Z108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="Z108" s="1" t="n">
+      <c r="AA108" s="1" t="n">
         <v>0.09566</v>
       </c>
     </row>
@@ -9429,9 +9756,12 @@
         <v>0.13954</v>
       </c>
       <c r="Y109" s="1" t="n">
+        <v>0.13929</v>
+      </c>
+      <c r="Z109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="Z109" s="1" t="n">
+      <c r="AA109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -9511,9 +9841,12 @@
         <v>5.583</v>
       </c>
       <c r="Y110" s="1" t="n">
-        <v>5.583</v>
+        <v>5.611</v>
       </c>
       <c r="Z110" s="1" t="n">
+        <v>5.611</v>
+      </c>
+      <c r="AA110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -9593,9 +9926,12 @@
         <v>1.094</v>
       </c>
       <c r="Y111" s="1" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="Z111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="Z111" s="1" t="n">
+      <c r="AA111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -9675,9 +10011,12 @@
         <v>0.028713</v>
       </c>
       <c r="Y112" s="1" t="n">
+        <v>0.028804</v>
+      </c>
+      <c r="Z112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="Z112" s="1" t="n">
+      <c r="AA112" s="1" t="n">
         <v>0.028712</v>
       </c>
     </row>
@@ -9757,9 +10096,12 @@
         <v>1.863</v>
       </c>
       <c r="Y113" s="1" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="Z113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="Z113" s="1" t="n">
+      <c r="AA113" s="1" t="n">
         <v>1.859</v>
       </c>
     </row>
@@ -9839,9 +10181,12 @@
         <v>0.05874</v>
       </c>
       <c r="Y114" s="1" t="n">
+        <v>0.05885</v>
+      </c>
+      <c r="Z114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="Z114" s="1" t="n">
+      <c r="AA114" s="1" t="n">
         <v>0.0584</v>
       </c>
     </row>
@@ -9921,10 +10266,13 @@
         <v>0.12712</v>
       </c>
       <c r="Y115" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="Z115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="Z115" s="1" t="n">
-        <v>0.12712</v>
+      <c r="AA115" s="1" t="n">
+        <v>0.1271</v>
       </c>
     </row>
     <row r="116">
@@ -10003,9 +10351,12 @@
         <v>1.0957</v>
       </c>
       <c r="Y116" s="1" t="n">
+        <v>1.0947</v>
+      </c>
+      <c r="Z116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="Z116" s="1" t="n">
+      <c r="AA116" s="1" t="n">
         <v>1.0937</v>
       </c>
     </row>
@@ -10085,9 +10436,12 @@
         <v>0.1541</v>
       </c>
       <c r="Y117" s="1" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="Z117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="Z117" s="1" t="n">
+      <c r="AA117" s="1" t="n">
         <v>0.1484</v>
       </c>
     </row>
@@ -10167,9 +10521,12 @@
         <v>0.1585</v>
       </c>
       <c r="Y118" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="Z118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="Z118" s="1" t="n">
+      <c r="AA118" s="1" t="n">
         <v>0.1572</v>
       </c>
     </row>
@@ -10249,9 +10606,12 @@
         <v>0.04783</v>
       </c>
       <c r="Y119" s="1" t="n">
-        <v>0.04783</v>
+        <v>0.04831</v>
       </c>
       <c r="Z119" s="1" t="n">
+        <v>0.04831</v>
+      </c>
+      <c r="AA119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -10331,9 +10691,12 @@
         <v>3.015</v>
       </c>
       <c r="Y120" s="1" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="Z120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="Z120" s="1" t="n">
+      <c r="AA120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -10413,9 +10776,12 @@
         <v>0.2967</v>
       </c>
       <c r="Y121" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="Z121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="Z121" s="1" t="n">
+      <c r="AA121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -10495,9 +10861,12 @@
         <v>0.5775</v>
       </c>
       <c r="Y122" s="1" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="Z122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="Z122" s="1" t="n">
+      <c r="AA122" s="1" t="n">
         <v>0.5767</v>
       </c>
     </row>
@@ -10577,9 +10946,12 @@
         <v>0.01247</v>
       </c>
       <c r="Y123" s="1" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="Z123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="Z123" s="1" t="n">
+      <c r="AA123" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -10659,9 +11031,12 @@
         <v>0.1583</v>
       </c>
       <c r="Y124" s="1" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="Z124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="Z124" s="1" t="n">
+      <c r="AA124" s="1" t="n">
         <v>0.1566</v>
       </c>
     </row>
@@ -10741,9 +11116,12 @@
         <v>0.00179</v>
       </c>
       <c r="Y125" s="1" t="n">
-        <v>0.00179</v>
+        <v>0.001794</v>
       </c>
       <c r="Z125" s="1" t="n">
+        <v>0.001794</v>
+      </c>
+      <c r="AA125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -10823,9 +11201,12 @@
         <v>0.0004829</v>
       </c>
       <c r="Y126" s="1" t="n">
+        <v>0.0004819</v>
+      </c>
+      <c r="Z126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="Z126" s="1" t="n">
+      <c r="AA126" s="1" t="n">
         <v>0.0004808</v>
       </c>
     </row>
@@ -10905,9 +11286,12 @@
         <v>0.02925</v>
       </c>
       <c r="Y127" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="Z127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="Z127" s="1" t="n">
+      <c r="AA127" s="1" t="n">
         <v>0.02922</v>
       </c>
     </row>
@@ -10987,9 +11371,12 @@
         <v>0.04124</v>
       </c>
       <c r="Y128" s="1" t="n">
+        <v>0.04127</v>
+      </c>
+      <c r="Z128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="Z128" s="1" t="n">
+      <c r="AA128" s="1" t="n">
         <v>0.04116</v>
       </c>
     </row>
@@ -11069,9 +11456,12 @@
         <v>0.04971</v>
       </c>
       <c r="Y129" s="1" t="n">
+        <v>0.04948</v>
+      </c>
+      <c r="Z129" s="1" t="n">
         <v>0.04971</v>
       </c>
-      <c r="Z129" s="1" t="n">
+      <c r="AA129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -11151,9 +11541,12 @@
         <v>1.21e-05</v>
       </c>
       <c r="Y130" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="Z130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="Z130" s="1" t="n">
+      <c r="AA130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -11233,9 +11626,12 @@
         <v>7.3e-06</v>
       </c>
       <c r="Y131" s="1" t="n">
+        <v>7.3e-06</v>
+      </c>
+      <c r="Z131" s="1" t="n">
         <v>7.5e-06</v>
       </c>
-      <c r="Z131" s="1" t="n">
+      <c r="AA131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -11315,9 +11711,12 @@
         <v>0.00699</v>
       </c>
       <c r="Y132" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="Z132" s="1" t="n">
         <v>0.00705</v>
       </c>
-      <c r="Z132" s="1" t="n">
+      <c r="AA132" s="1" t="n">
         <v>0.00697</v>
       </c>
     </row>
@@ -11397,9 +11796,12 @@
         <v>0.0965</v>
       </c>
       <c r="Y133" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="Z133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="Z133" s="1" t="n">
+      <c r="AA133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -11479,9 +11881,12 @@
         <v>0.0004116</v>
       </c>
       <c r="Y134" s="1" t="n">
-        <v>0.0004116</v>
+        <v>0.0004119</v>
       </c>
       <c r="Z134" s="1" t="n">
+        <v>0.0004119</v>
+      </c>
+      <c r="AA134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -11561,9 +11966,12 @@
         <v>0.08196000000000001</v>
       </c>
       <c r="Y135" s="1" t="n">
+        <v>0.08203000000000001</v>
+      </c>
+      <c r="Z135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="Z135" s="1" t="n">
+      <c r="AA135" s="1" t="n">
         <v>0.08148</v>
       </c>
     </row>
@@ -11643,10 +12051,13 @@
         <v>0.007752</v>
       </c>
       <c r="Y136" s="1" t="n">
+        <v>0.007746</v>
+      </c>
+      <c r="Z136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="Z136" s="1" t="n">
-        <v>0.007748</v>
+      <c r="AA136" s="1" t="n">
+        <v>0.007746</v>
       </c>
     </row>
     <row r="137">
@@ -11725,9 +12136,12 @@
         <v>0.0007983000000000001</v>
       </c>
       <c r="Y137" s="1" t="n">
+        <v>0.0007986</v>
+      </c>
+      <c r="Z137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="Z137" s="1" t="n">
+      <c r="AA137" s="1" t="n">
         <v>0.0007981</v>
       </c>
     </row>
@@ -11807,9 +12221,12 @@
         <v>0.146</v>
       </c>
       <c r="Y138" s="1" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="Z138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="Z138" s="1" t="n">
+      <c r="AA138" s="1" t="n">
         <v>0.1453</v>
       </c>
     </row>
@@ -11889,9 +12306,12 @@
         <v>0.006649</v>
       </c>
       <c r="Y139" s="1" t="n">
+        <v>0.006656</v>
+      </c>
+      <c r="Z139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="Z139" s="1" t="n">
+      <c r="AA139" s="1" t="n">
         <v>0.006649</v>
       </c>
     </row>
@@ -11971,9 +12391,12 @@
         <v>0.01376</v>
       </c>
       <c r="Y140" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="Z140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="Z140" s="1" t="n">
+      <c r="AA140" s="1" t="n">
         <v>0.01373</v>
       </c>
     </row>
@@ -12053,10 +12476,13 @@
         <v>0.09583999999999999</v>
       </c>
       <c r="Y141" s="1" t="n">
+        <v>0.09561</v>
+      </c>
+      <c r="Z141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="Z141" s="1" t="n">
-        <v>0.09583999999999999</v>
+      <c r="AA141" s="1" t="n">
+        <v>0.09561</v>
       </c>
     </row>
     <row r="142">
@@ -12135,10 +12561,13 @@
         <v>0.05413</v>
       </c>
       <c r="Y142" s="1" t="n">
+        <v>0.05402</v>
+      </c>
+      <c r="Z142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="Z142" s="1" t="n">
-        <v>0.05405</v>
+      <c r="AA142" s="1" t="n">
+        <v>0.05402</v>
       </c>
     </row>
     <row r="143">
@@ -12217,9 +12646,12 @@
         <v>0.323</v>
       </c>
       <c r="Y143" s="1" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="Z143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="Z143" s="1" t="n">
+      <c r="AA143" s="1" t="n">
         <v>0.3219</v>
       </c>
     </row>
@@ -12299,9 +12731,12 @@
         <v>0.02559</v>
       </c>
       <c r="Y144" s="1" t="n">
+        <v>0.02569</v>
+      </c>
+      <c r="Z144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="Z144" s="1" t="n">
+      <c r="AA144" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -12381,9 +12816,12 @@
         <v>0.2367</v>
       </c>
       <c r="Y145" s="1" t="n">
+        <v>0.2374</v>
+      </c>
+      <c r="Z145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="Z145" s="1" t="n">
+      <c r="AA145" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -12463,9 +12901,12 @@
         <v>0.007025</v>
       </c>
       <c r="Y146" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="Z146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="Z146" s="1" t="n">
+      <c r="AA146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -12545,9 +12986,12 @@
         <v>0.08579000000000001</v>
       </c>
       <c r="Y147" s="1" t="n">
+        <v>0.08641</v>
+      </c>
+      <c r="Z147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="Z147" s="1" t="n">
+      <c r="AA147" s="1" t="n">
         <v>0.08579000000000001</v>
       </c>
     </row>
@@ -12627,9 +13071,12 @@
         <v>0.05252</v>
       </c>
       <c r="Y148" s="1" t="n">
-        <v>0.05289</v>
+        <v>0.05294</v>
       </c>
       <c r="Z148" s="1" t="n">
+        <v>0.05294</v>
+      </c>
+      <c r="AA148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -12709,9 +13156,12 @@
         <v>0.02386</v>
       </c>
       <c r="Y149" s="1" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="Z149" s="1" t="n">
         <v>0.02402</v>
       </c>
-      <c r="Z149" s="1" t="n">
+      <c r="AA149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -12791,9 +13241,12 @@
         <v>0.08577</v>
       </c>
       <c r="Y150" s="1" t="n">
+        <v>0.08574</v>
+      </c>
+      <c r="Z150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="Z150" s="1" t="n">
+      <c r="AA150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -12873,9 +13326,12 @@
         <v>0.02306</v>
       </c>
       <c r="Y151" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="Z151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="Z151" s="1" t="n">
+      <c r="AA151" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -12955,9 +13411,12 @@
         <v>0.02519</v>
       </c>
       <c r="Y152" s="1" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="Z152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="Z152" s="1" t="n">
+      <c r="AA152" s="1" t="n">
         <v>0.02515</v>
       </c>
     </row>
@@ -13037,9 +13496,12 @@
         <v>0.0002116</v>
       </c>
       <c r="Y153" s="1" t="n">
+        <v>0.0002127</v>
+      </c>
+      <c r="Z153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="Z153" s="1" t="n">
+      <c r="AA153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -13119,9 +13581,12 @@
         <v>0.4426</v>
       </c>
       <c r="Y154" s="1" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="Z154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="Z154" s="1" t="n">
+      <c r="AA154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -13201,9 +13666,12 @@
         <v>0.06732</v>
       </c>
       <c r="Y155" s="1" t="n">
+        <v>0.06748</v>
+      </c>
+      <c r="Z155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="Z155" s="1" t="n">
+      <c r="AA155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -13283,9 +13751,12 @@
         <v>0.13246</v>
       </c>
       <c r="Y156" s="1" t="n">
+        <v>0.13334</v>
+      </c>
+      <c r="Z156" s="1" t="n">
         <v>0.13403</v>
       </c>
-      <c r="Z156" s="1" t="n">
+      <c r="AA156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -13365,9 +13836,12 @@
         <v>0.4815</v>
       </c>
       <c r="Y157" s="1" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="Z157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="Z157" s="1" t="n">
+      <c r="AA157" s="1" t="n">
         <v>0.4815</v>
       </c>
     </row>
@@ -13447,9 +13921,12 @@
         <v>0.4469</v>
       </c>
       <c r="Y158" s="1" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="Z158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="Z158" s="1" t="n">
+      <c r="AA158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -13529,9 +14006,12 @@
         <v>0.007406</v>
       </c>
       <c r="Y159" s="1" t="n">
+        <v>0.007442</v>
+      </c>
+      <c r="Z159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="Z159" s="1" t="n">
+      <c r="AA159" s="1" t="n">
         <v>0.007406</v>
       </c>
     </row>
@@ -13611,9 +14091,12 @@
         <v>0.004658</v>
       </c>
       <c r="Y160" s="1" t="n">
+        <v>0.004667</v>
+      </c>
+      <c r="Z160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="Z160" s="1" t="n">
+      <c r="AA160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -13693,9 +14176,12 @@
         <v>0.004303</v>
       </c>
       <c r="Y161" s="1" t="n">
+        <v>0.004308</v>
+      </c>
+      <c r="Z161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="Z161" s="1" t="n">
+      <c r="AA161" s="1" t="n">
         <v>0.004276</v>
       </c>
     </row>
@@ -13775,9 +14261,12 @@
         <v>0.0951</v>
       </c>
       <c r="Y162" s="1" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="Z162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="Z162" s="1" t="n">
+      <c r="AA162" s="1" t="n">
         <v>0.0951</v>
       </c>
     </row>
@@ -13857,9 +14346,12 @@
         <v>0.2843</v>
       </c>
       <c r="Y163" s="1" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Z163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="Z163" s="1" t="n">
+      <c r="AA163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -13939,9 +14431,12 @@
         <v>0.1135</v>
       </c>
       <c r="Y164" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="Z164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="Z164" s="1" t="n">
+      <c r="AA164" s="1" t="n">
         <v>0.1131</v>
       </c>
     </row>
@@ -14021,9 +14516,12 @@
         <v>0.1751</v>
       </c>
       <c r="Y165" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="Z165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="Z165" s="1" t="n">
+      <c r="AA165" s="1" t="n">
         <v>0.1747</v>
       </c>
     </row>
@@ -14103,10 +14601,13 @@
         <v>0.01006</v>
       </c>
       <c r="Y166" s="1" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="Z166" s="1" t="n">
         <v>0.01055</v>
       </c>
-      <c r="Z166" s="1" t="n">
-        <v>0.01004</v>
+      <c r="AA166" s="1" t="n">
+        <v>0.01002</v>
       </c>
     </row>
     <row r="167">
@@ -14185,9 +14686,12 @@
         <v>1.814</v>
       </c>
       <c r="Y167" s="1" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="Z167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="Z167" s="1" t="n">
+      <c r="AA167" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -14267,9 +14771,12 @@
         <v>1.338</v>
       </c>
       <c r="Y168" s="1" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="Z168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="Z168" s="1" t="n">
+      <c r="AA168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -14349,9 +14856,12 @@
         <v>0.00728</v>
       </c>
       <c r="Y169" s="1" t="n">
+        <v>0.007318</v>
+      </c>
+      <c r="Z169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="Z169" s="1" t="n">
+      <c r="AA169" s="1" t="n">
         <v>0.007276</v>
       </c>
     </row>
@@ -14431,9 +14941,12 @@
         <v>0.0115</v>
       </c>
       <c r="Y170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="Z170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="Z170" s="1" t="n">
+      <c r="AA170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -14513,9 +15026,12 @@
         <v>0.005751</v>
       </c>
       <c r="Y171" s="1" t="n">
+        <v>0.005751</v>
+      </c>
+      <c r="Z171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="Z171" s="1" t="n">
+      <c r="AA171" s="1" t="n">
         <v>0.005737</v>
       </c>
     </row>
@@ -14595,9 +15111,12 @@
         <v>0.14875</v>
       </c>
       <c r="Y172" s="1" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="Z172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="Z172" s="1" t="n">
+      <c r="AA172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -14677,9 +15196,12 @@
         <v>4.892</v>
       </c>
       <c r="Y173" s="1" t="n">
+        <v>4.909</v>
+      </c>
+      <c r="Z173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="Z173" s="1" t="n">
+      <c r="AA173" s="1" t="n">
         <v>4.868</v>
       </c>
     </row>
@@ -14759,9 +15281,12 @@
         <v>0.07795000000000001</v>
       </c>
       <c r="Y174" s="1" t="n">
+        <v>0.07818</v>
+      </c>
+      <c r="Z174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="Z174" s="1" t="n">
+      <c r="AA174" s="1" t="n">
         <v>0.07785</v>
       </c>
     </row>
@@ -14841,9 +15366,12 @@
         <v>0.00742</v>
       </c>
       <c r="Y175" s="1" t="n">
+        <v>0.007412</v>
+      </c>
+      <c r="Z175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="Z175" s="1" t="n">
+      <c r="AA175" s="1" t="n">
         <v>0.007403</v>
       </c>
     </row>
@@ -14923,9 +15451,12 @@
         <v>0.1986</v>
       </c>
       <c r="Y176" s="1" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="Z176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="Z176" s="1" t="n">
+      <c r="AA176" s="1" t="n">
         <v>0.1983</v>
       </c>
     </row>
@@ -15005,9 +15536,12 @@
         <v>0.05183</v>
       </c>
       <c r="Y177" s="1" t="n">
+        <v>0.05188</v>
+      </c>
+      <c r="Z177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="Z177" s="1" t="n">
+      <c r="AA177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -15087,9 +15621,12 @@
         <v>0.0544</v>
       </c>
       <c r="Y178" s="1" t="n">
+        <v>0.05454</v>
+      </c>
+      <c r="Z178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="Z178" s="1" t="n">
+      <c r="AA178" s="1" t="n">
         <v>0.0544</v>
       </c>
     </row>
@@ -15169,9 +15706,12 @@
         <v>0.02332</v>
       </c>
       <c r="Y179" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="Z179" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="Z179" s="1" t="n">
+      <c r="AA179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -15251,9 +15791,12 @@
         <v>0.6973</v>
       </c>
       <c r="Y180" s="1" t="n">
-        <v>0.6994</v>
+        <v>0.7013</v>
       </c>
       <c r="Z180" s="1" t="n">
+        <v>0.7013</v>
+      </c>
+      <c r="AA180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -15333,9 +15876,12 @@
         <v>0.0003744</v>
       </c>
       <c r="Y181" s="1" t="n">
+        <v>0.0003728</v>
+      </c>
+      <c r="Z181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="Z181" s="1" t="n">
+      <c r="AA181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -15415,9 +15961,12 @@
         <v>0.01274</v>
       </c>
       <c r="Y182" s="1" t="n">
+        <v>0.01276</v>
+      </c>
+      <c r="Z182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="Z182" s="1" t="n">
+      <c r="AA182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -15497,9 +16046,12 @@
         <v>4.192</v>
       </c>
       <c r="Y183" s="1" t="n">
+        <v>4.185</v>
+      </c>
+      <c r="Z183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="Z183" s="1" t="n">
+      <c r="AA183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -15579,9 +16131,12 @@
         <v>0.2331</v>
       </c>
       <c r="Y184" s="1" t="n">
+        <v>0.2333</v>
+      </c>
+      <c r="Z184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="Z184" s="1" t="n">
+      <c r="AA184" s="1" t="n">
         <v>0.2331</v>
       </c>
     </row>
@@ -15661,9 +16216,12 @@
         <v>0.03677</v>
       </c>
       <c r="Y185" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="Z185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="Z185" s="1" t="n">
+      <c r="AA185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -15743,9 +16301,12 @@
         <v>0.11546</v>
       </c>
       <c r="Y186" s="1" t="n">
+        <v>0.11581</v>
+      </c>
+      <c r="Z186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="Z186" s="1" t="n">
+      <c r="AA186" s="1" t="n">
         <v>0.11535</v>
       </c>
     </row>
@@ -15825,9 +16386,12 @@
         <v>0.009063</v>
       </c>
       <c r="Y187" s="1" t="n">
+        <v>0.009145</v>
+      </c>
+      <c r="Z187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="Z187" s="1" t="n">
+      <c r="AA187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -15907,9 +16471,12 @@
         <v>0.0974</v>
       </c>
       <c r="Y188" s="1" t="n">
-        <v>0.0978</v>
+        <v>0.0984</v>
       </c>
       <c r="Z188" s="1" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="AA188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -15989,9 +16556,12 @@
         <v>0.02722</v>
       </c>
       <c r="Y189" s="1" t="n">
+        <v>0.02732</v>
+      </c>
+      <c r="Z189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="Z189" s="1" t="n">
+      <c r="AA189" s="1" t="n">
         <v>0.02702</v>
       </c>
     </row>
@@ -16071,9 +16641,12 @@
         <v>0.00865</v>
       </c>
       <c r="Y190" s="1" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="Z190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="Z190" s="1" t="n">
+      <c r="AA190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -16153,9 +16726,12 @@
         <v>0.001964</v>
       </c>
       <c r="Y191" s="1" t="n">
-        <v>0.001964</v>
+        <v>0.001965</v>
       </c>
       <c r="Z191" s="1" t="n">
+        <v>0.001965</v>
+      </c>
+      <c r="AA191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -16235,10 +16811,13 @@
         <v>0.0998</v>
       </c>
       <c r="Y192" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="Z192" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="Z192" s="1" t="n">
-        <v>0.09959999999999999</v>
+      <c r="AA192" s="1" t="n">
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="193">
@@ -16317,9 +16896,12 @@
         <v>0.02338</v>
       </c>
       <c r="Y193" s="1" t="n">
+        <v>0.02337</v>
+      </c>
+      <c r="Z193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="Z193" s="1" t="n">
+      <c r="AA193" s="1" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -16399,9 +16981,12 @@
         <v>0.01345</v>
       </c>
       <c r="Y194" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="Z194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="Z194" s="1" t="n">
+      <c r="AA194" s="1" t="n">
         <v>0.0134</v>
       </c>
     </row>
@@ -16481,9 +17066,12 @@
         <v>0.02078</v>
       </c>
       <c r="Y195" s="1" t="n">
+        <v>0.02082</v>
+      </c>
+      <c r="Z195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="Z195" s="1" t="n">
+      <c r="AA195" s="1" t="n">
         <v>0.02071</v>
       </c>
     </row>
@@ -16563,9 +17151,12 @@
         <v>0.17567</v>
       </c>
       <c r="Y196" s="1" t="n">
+        <v>0.17599</v>
+      </c>
+      <c r="Z196" s="1" t="n">
         <v>0.17767</v>
       </c>
-      <c r="Z196" s="1" t="n">
+      <c r="AA196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -16645,9 +17236,12 @@
         <v>0.007264</v>
       </c>
       <c r="Y197" s="1" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="Z197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="Z197" s="1" t="n">
+      <c r="AA197" s="1" t="n">
         <v>0.007264</v>
       </c>
     </row>
@@ -16727,9 +17321,12 @@
         <v>0.01902</v>
       </c>
       <c r="Y198" s="1" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="Z198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="Z198" s="1" t="n">
+      <c r="AA198" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -16809,9 +17406,12 @@
         <v>0.01642</v>
       </c>
       <c r="Y199" s="1" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="Z199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="Z199" s="1" t="n">
+      <c r="AA199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -16891,9 +17491,12 @@
         <v>0.297</v>
       </c>
       <c r="Y200" s="1" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="Z200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="Z200" s="1" t="n">
+      <c r="AA200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -16973,9 +17576,12 @@
         <v>0.006236</v>
       </c>
       <c r="Y201" s="1" t="n">
+        <v>0.006222</v>
+      </c>
+      <c r="Z201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="Z201" s="1" t="n">
+      <c r="AA201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -17055,9 +17661,12 @@
         <v>0.0004384</v>
       </c>
       <c r="Y202" s="1" t="n">
+        <v>0.0004397</v>
+      </c>
+      <c r="Z202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="Z202" s="1" t="n">
+      <c r="AA202" s="1" t="n">
         <v>0.0004378</v>
       </c>
     </row>
@@ -17137,10 +17746,13 @@
         <v>0.007241</v>
       </c>
       <c r="Y203" s="1" t="n">
+        <v>0.007236</v>
+      </c>
+      <c r="Z203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="Z203" s="1" t="n">
-        <v>0.007241</v>
+      <c r="AA203" s="1" t="n">
+        <v>0.007236</v>
       </c>
     </row>
     <row r="204">
@@ -17219,9 +17831,12 @@
         <v>0.13</v>
       </c>
       <c r="Y204" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="Z204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="Z204" s="1" t="n">
+      <c r="AA204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -17301,9 +17916,12 @@
         <v>0.01415</v>
       </c>
       <c r="Y205" s="1" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="Z205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="Z205" s="1" t="n">
+      <c r="AA205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -17383,9 +18001,12 @@
         <v>0.003551</v>
       </c>
       <c r="Y206" s="1" t="n">
+        <v>0.003569</v>
+      </c>
+      <c r="Z206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="Z206" s="1" t="n">
+      <c r="AA206" s="1" t="n">
         <v>0.003551</v>
       </c>
     </row>
@@ -17465,9 +18086,12 @@
         <v>0.05873</v>
       </c>
       <c r="Y207" s="1" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="Z207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="Z207" s="1" t="n">
+      <c r="AA207" s="1" t="n">
         <v>0.05873</v>
       </c>
     </row>
@@ -17547,9 +18171,12 @@
         <v>15.55</v>
       </c>
       <c r="Y208" s="1" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="Z208" s="1" t="n">
         <v>15.56</v>
       </c>
-      <c r="Z208" s="1" t="n">
+      <c r="AA208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -17629,10 +18256,13 @@
         <v>5181.4</v>
       </c>
       <c r="Y209" s="1" t="n">
+        <v>5179.7</v>
+      </c>
+      <c r="Z209" s="1" t="n">
         <v>5194.4</v>
       </c>
-      <c r="Z209" s="1" t="n">
-        <v>5181.4</v>
+      <c r="AA209" s="1" t="n">
+        <v>5179.7</v>
       </c>
     </row>
     <row r="210">
@@ -17711,9 +18341,12 @@
         <v>0.11979</v>
       </c>
       <c r="Y210" s="1" t="n">
+        <v>0.1196</v>
+      </c>
+      <c r="Z210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="Z210" s="1" t="n">
+      <c r="AA210" s="1" t="n">
         <v>0.11941</v>
       </c>
     </row>
@@ -17793,10 +18426,13 @@
         <v>0.1801</v>
       </c>
       <c r="Y211" s="1" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="Z211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="Z211" s="1" t="n">
-        <v>0.1801</v>
+      <c r="AA211" s="1" t="n">
+        <v>0.1791</v>
       </c>
     </row>
     <row r="212">
@@ -17875,9 +18511,12 @@
         <v>0.0299</v>
       </c>
       <c r="Y212" s="1" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="Z212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="Z212" s="1" t="n">
+      <c r="AA212" s="1" t="n">
         <v>0.0297</v>
       </c>
     </row>
@@ -17957,9 +18596,12 @@
         <v>1.3999</v>
       </c>
       <c r="Y213" s="1" t="n">
-        <v>1.3999</v>
+        <v>1.4007</v>
       </c>
       <c r="Z213" s="1" t="n">
+        <v>1.4007</v>
+      </c>
+      <c r="AA213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -18039,9 +18681,12 @@
         <v>0.05661</v>
       </c>
       <c r="Y214" s="1" t="n">
+        <v>0.05667</v>
+      </c>
+      <c r="Z214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="Z214" s="1" t="n">
+      <c r="AA214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -18121,9 +18766,12 @@
         <v>0.04372</v>
       </c>
       <c r="Y215" s="1" t="n">
+        <v>0.04377</v>
+      </c>
+      <c r="Z215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="Z215" s="1" t="n">
+      <c r="AA215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -18203,9 +18851,12 @@
         <v>0.15096</v>
       </c>
       <c r="Y216" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="Z216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="Z216" s="1" t="n">
+      <c r="AA216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -18288,6 +18939,9 @@
         <v>0.074</v>
       </c>
       <c r="Z217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AA217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -18367,9 +19021,12 @@
         <v>0.00268</v>
       </c>
       <c r="Y218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="Z218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="Z218" s="1" t="n">
+      <c r="AA218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -18449,9 +19106,12 @@
         <v>0.01696</v>
       </c>
       <c r="Y219" s="1" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="Z219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="Z219" s="1" t="n">
+      <c r="AA219" s="1" t="n">
         <v>0.01693</v>
       </c>
     </row>
@@ -18531,9 +19191,12 @@
         <v>0.05522</v>
       </c>
       <c r="Y220" s="1" t="n">
+        <v>0.05532</v>
+      </c>
+      <c r="Z220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="Z220" s="1" t="n">
+      <c r="AA220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -18613,9 +19276,12 @@
         <v>0.02181</v>
       </c>
       <c r="Y221" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="Z221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="Z221" s="1" t="n">
+      <c r="AA221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -18695,9 +19361,12 @@
         <v>0.00925</v>
       </c>
       <c r="Y222" s="1" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="Z222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="Z222" s="1" t="n">
+      <c r="AA222" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -18777,9 +19446,12 @@
         <v>0.0164</v>
       </c>
       <c r="Y223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="Z223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="Z223" s="1" t="n">
+      <c r="AA223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -18859,9 +19531,12 @@
         <v>0.03825</v>
       </c>
       <c r="Y224" s="1" t="n">
+        <v>0.03837</v>
+      </c>
+      <c r="Z224" s="1" t="n">
         <v>0.03846</v>
       </c>
-      <c r="Z224" s="1" t="n">
+      <c r="AA224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -18941,9 +19616,12 @@
         <v>0.001519</v>
       </c>
       <c r="Y225" s="1" t="n">
+        <v>0.001521</v>
+      </c>
+      <c r="Z225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="Z225" s="1" t="n">
+      <c r="AA225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -19023,9 +19701,12 @@
         <v>27.13</v>
       </c>
       <c r="Y226" s="1" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="Z226" s="1" t="n">
         <v>27.31</v>
       </c>
-      <c r="Z226" s="1" t="n">
+      <c r="AA226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -19105,9 +19786,12 @@
         <v>0.07006999999999999</v>
       </c>
       <c r="Y227" s="1" t="n">
+        <v>0.07022</v>
+      </c>
+      <c r="Z227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="Z227" s="1" t="n">
+      <c r="AA227" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -19187,9 +19871,12 @@
         <v>0.3117</v>
       </c>
       <c r="Y228" s="1" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="Z228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="Z228" s="1" t="n">
+      <c r="AA228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -19269,9 +19956,12 @@
         <v>18.39</v>
       </c>
       <c r="Y229" s="1" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="Z229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="Z229" s="1" t="n">
+      <c r="AA229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -19351,9 +20041,12 @@
         <v>0.01917</v>
       </c>
       <c r="Y230" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="Z230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="Z230" s="1" t="n">
+      <c r="AA230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -19433,9 +20126,12 @@
         <v>0.01216</v>
       </c>
       <c r="Y231" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="Z231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="Z231" s="1" t="n">
+      <c r="AA231" s="1" t="n">
         <v>0.01212</v>
       </c>
     </row>
@@ -19515,9 +20211,12 @@
         <v>0.2277</v>
       </c>
       <c r="Y232" s="1" t="n">
+        <v>0.2282</v>
+      </c>
+      <c r="Z232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="Z232" s="1" t="n">
+      <c r="AA232" s="1" t="n">
         <v>0.2269</v>
       </c>
     </row>
@@ -19597,9 +20296,12 @@
         <v>0.07068000000000001</v>
       </c>
       <c r="Y233" s="1" t="n">
+        <v>0.07092</v>
+      </c>
+      <c r="Z233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="Z233" s="1" t="n">
+      <c r="AA233" s="1" t="n">
         <v>0.07068000000000001</v>
       </c>
     </row>
@@ -19679,9 +20381,12 @@
         <v>0.1701</v>
       </c>
       <c r="Y234" s="1" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="Z234" s="1" t="n">
         <v>0.1709</v>
       </c>
-      <c r="Z234" s="1" t="n">
+      <c r="AA234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -19761,9 +20466,12 @@
         <v>0.0251</v>
       </c>
       <c r="Y235" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="Z235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="Z235" s="1" t="n">
+      <c r="AA235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -19843,9 +20551,12 @@
         <v>0.02991</v>
       </c>
       <c r="Y236" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="Z236" s="1" t="n">
+      <c r="AA236" s="1" t="n">
         <v>0.02991</v>
       </c>
     </row>
@@ -19925,9 +20636,12 @@
         <v>2.034</v>
       </c>
       <c r="Y237" s="1" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z237" s="1" t="n">
         <v>2.049</v>
       </c>
-      <c r="Z237" s="1" t="n">
+      <c r="AA237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -20007,9 +20721,12 @@
         <v>0.4184</v>
       </c>
       <c r="Y238" s="1" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="Z238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="Z238" s="1" t="n">
+      <c r="AA238" s="1" t="n">
         <v>0.4172</v>
       </c>
     </row>
@@ -20089,10 +20806,13 @@
         <v>0.03301</v>
       </c>
       <c r="Y239" s="1" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="Z239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="Z239" s="1" t="n">
-        <v>0.03297</v>
+      <c r="AA239" s="1" t="n">
+        <v>0.0329</v>
       </c>
     </row>
     <row r="240">
@@ -20171,9 +20891,12 @@
         <v>0.03404</v>
       </c>
       <c r="Y240" s="1" t="n">
-        <v>0.0341</v>
+        <v>0.03416</v>
       </c>
       <c r="Z240" s="1" t="n">
+        <v>0.03416</v>
+      </c>
+      <c r="AA240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -20253,9 +20976,12 @@
         <v>0.0007483</v>
       </c>
       <c r="Y241" s="1" t="n">
+        <v>0.0007485</v>
+      </c>
+      <c r="Z241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="Z241" s="1" t="n">
+      <c r="AA241" s="1" t="n">
         <v>0.0007452</v>
       </c>
     </row>
@@ -20335,9 +21061,12 @@
         <v>0.1815</v>
       </c>
       <c r="Y242" s="1" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="Z242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="Z242" s="1" t="n">
+      <c r="AA242" s="1" t="n">
         <v>0.1815</v>
       </c>
     </row>
@@ -20417,10 +21146,13 @@
         <v>0.014685</v>
       </c>
       <c r="Y243" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="Z243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="Z243" s="1" t="n">
-        <v>0.014685</v>
+      <c r="AA243" s="1" t="n">
+        <v>0.01467</v>
       </c>
     </row>
     <row r="244">
@@ -20499,9 +21231,12 @@
         <v>3e-05</v>
       </c>
       <c r="Y244" s="1" t="n">
+        <v>3.03e-05</v>
+      </c>
+      <c r="Z244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="Z244" s="1" t="n">
+      <c r="AA244" s="1" t="n">
         <v>2.99e-05</v>
       </c>
     </row>
@@ -20581,9 +21316,12 @@
         <v>0.03521</v>
       </c>
       <c r="Y245" s="1" t="n">
+        <v>0.03514</v>
+      </c>
+      <c r="Z245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="Z245" s="1" t="n">
+      <c r="AA245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -20663,9 +21401,12 @@
         <v>0.07971</v>
       </c>
       <c r="Y246" s="1" t="n">
+        <v>0.08025</v>
+      </c>
+      <c r="Z246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="Z246" s="1" t="n">
+      <c r="AA246" s="1" t="n">
         <v>0.07971</v>
       </c>
     </row>
@@ -20745,9 +21486,12 @@
         <v>0.007084</v>
       </c>
       <c r="Y247" s="1" t="n">
+        <v>0.007134</v>
+      </c>
+      <c r="Z247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="Z247" s="1" t="n">
+      <c r="AA247" s="1" t="n">
         <v>0.00707</v>
       </c>
     </row>
@@ -20827,9 +21571,12 @@
         <v>0.09428</v>
       </c>
       <c r="Y248" s="1" t="n">
+        <v>0.09492</v>
+      </c>
+      <c r="Z248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="Z248" s="1" t="n">
+      <c r="AA248" s="1" t="n">
         <v>0.09239</v>
       </c>
     </row>
@@ -20909,9 +21656,12 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="Y249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Z249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="Z249" s="1" t="n">
+      <c r="AA249" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
     </row>
@@ -20991,9 +21741,12 @@
         <v>0.0348</v>
       </c>
       <c r="Y250" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="Z250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="Z250" s="1" t="n">
+      <c r="AA250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -21073,10 +21826,13 @@
         <v>0.03868</v>
       </c>
       <c r="Y251" s="1" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="Z251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="Z251" s="1" t="n">
-        <v>0.03859</v>
+      <c r="AA251" s="1" t="n">
+        <v>0.03838</v>
       </c>
     </row>
     <row r="252">
@@ -21155,9 +21911,12 @@
         <v>0.0881</v>
       </c>
       <c r="Y252" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="Z252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="Z252" s="1" t="n">
+      <c r="AA252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -21237,9 +21996,12 @@
         <v>4.059</v>
       </c>
       <c r="Y253" s="1" t="n">
+        <v>4.077</v>
+      </c>
+      <c r="Z253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="Z253" s="1" t="n">
+      <c r="AA253" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -21319,9 +22081,12 @@
         <v>0.1869</v>
       </c>
       <c r="Y254" s="1" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="Z254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="Z254" s="1" t="n">
+      <c r="AA254" s="1" t="n">
         <v>0.1865</v>
       </c>
     </row>
@@ -21401,9 +22166,12 @@
         <v>0.07196</v>
       </c>
       <c r="Y255" s="1" t="n">
+        <v>0.07217</v>
+      </c>
+      <c r="Z255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="Z255" s="1" t="n">
+      <c r="AA255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -21483,9 +22251,12 @@
         <v>0.01831</v>
       </c>
       <c r="Y256" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="Z256" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="Z256" s="1" t="n">
+      <c r="AA256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -21565,9 +22336,12 @@
         <v>5.947</v>
       </c>
       <c r="Y257" s="1" t="n">
+        <v>5.952</v>
+      </c>
+      <c r="Z257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="Z257" s="1" t="n">
+      <c r="AA257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -21647,9 +22421,12 @@
         <v>0.2593</v>
       </c>
       <c r="Y258" s="1" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="Z258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="Z258" s="1" t="n">
+      <c r="AA258" s="1" t="n">
         <v>0.2582</v>
       </c>
     </row>
@@ -21729,9 +22506,12 @@
         <v>0.1358</v>
       </c>
       <c r="Y259" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="Z259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="Z259" s="1" t="n">
+      <c r="AA259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -21811,9 +22591,12 @@
         <v>0.30734</v>
       </c>
       <c r="Y260" s="1" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="Z260" s="1" t="n">
+      <c r="AA260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -21893,9 +22676,12 @@
         <v>0.0982</v>
       </c>
       <c r="Y261" s="1" t="n">
+        <v>0.09866999999999999</v>
+      </c>
+      <c r="Z261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="Z261" s="1" t="n">
+      <c r="AA261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -21975,9 +22761,12 @@
         <v>0.5409</v>
       </c>
       <c r="Y262" s="1" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="Z262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="Z262" s="1" t="n">
+      <c r="AA262" s="1" t="n">
         <v>0.5377999999999999</v>
       </c>
     </row>
@@ -22057,9 +22846,12 @@
         <v>0.2898</v>
       </c>
       <c r="Y263" s="1" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="Z263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="Z263" s="1" t="n">
+      <c r="AA263" s="1" t="n">
         <v>0.2877</v>
       </c>
     </row>
@@ -22139,9 +22931,12 @@
         <v>0.981</v>
       </c>
       <c r="Y264" s="1" t="n">
-        <v>0.989</v>
+        <v>0.99</v>
       </c>
       <c r="Z264" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AA264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -22221,9 +23016,12 @@
         <v>0.5347</v>
       </c>
       <c r="Y265" s="1" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="Z265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="Z265" s="1" t="n">
+      <c r="AA265" s="1" t="n">
         <v>0.5339</v>
       </c>
     </row>
@@ -22303,9 +23101,12 @@
         <v>0.07346</v>
       </c>
       <c r="Y266" s="1" t="n">
+        <v>0.07355</v>
+      </c>
+      <c r="Z266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="Z266" s="1" t="n">
+      <c r="AA266" s="1" t="n">
         <v>0.07339</v>
       </c>
     </row>
@@ -22385,10 +23186,13 @@
         <v>0.02121</v>
       </c>
       <c r="Y267" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="Z267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="Z267" s="1" t="n">
-        <v>0.02116</v>
+      <c r="AA267" s="1" t="n">
+        <v>0.02113</v>
       </c>
     </row>
     <row r="268">
@@ -22467,9 +23271,12 @@
         <v>0.01617</v>
       </c>
       <c r="Y268" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="Z268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="Z268" s="1" t="n">
+      <c r="AA268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -22549,9 +23356,12 @@
         <v>0.003796</v>
       </c>
       <c r="Y269" s="1" t="n">
+        <v>0.003793</v>
+      </c>
+      <c r="Z269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="Z269" s="1" t="n">
+      <c r="AA269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -22631,9 +23441,12 @@
         <v>0.00766</v>
       </c>
       <c r="Y270" s="1" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="Z270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="Z270" s="1" t="n">
+      <c r="AA270" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -22713,9 +23526,12 @@
         <v>0.05477</v>
       </c>
       <c r="Y271" s="1" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="Z271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="Z271" s="1" t="n">
+      <c r="AA271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -22795,9 +23611,12 @@
         <v>2.288</v>
       </c>
       <c r="Y272" s="1" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="Z272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="Z272" s="1" t="n">
+      <c r="AA272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -22877,9 +23696,12 @@
         <v>0.05445</v>
       </c>
       <c r="Y273" s="1" t="n">
+        <v>0.05447</v>
+      </c>
+      <c r="Z273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="Z273" s="1" t="n">
+      <c r="AA273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -22959,9 +23781,12 @@
         <v>0.02357</v>
       </c>
       <c r="Y274" s="1" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="Z274" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="Z274" s="1" t="n">
+      <c r="AA274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -23041,9 +23866,12 @@
         <v>1.168</v>
       </c>
       <c r="Y275" s="1" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="Z275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="Z275" s="1" t="n">
+      <c r="AA275" s="1" t="n">
         <v>1.168</v>
       </c>
     </row>
@@ -23123,9 +23951,12 @@
         <v>0.2718</v>
       </c>
       <c r="Y276" s="1" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="Z276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="Z276" s="1" t="n">
+      <c r="AA276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -23205,9 +24036,12 @@
         <v>0.922</v>
       </c>
       <c r="Y277" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="Z277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="Z277" s="1" t="n">
+      <c r="AA277" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -23287,9 +24121,12 @@
         <v>0.6251</v>
       </c>
       <c r="Y278" s="1" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="Z278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="Z278" s="1" t="n">
+      <c r="AA278" s="1" t="n">
         <v>0.6218</v>
       </c>
     </row>
@@ -23369,9 +24206,12 @@
         <v>0.001305</v>
       </c>
       <c r="Y279" s="1" t="n">
+        <v>0.001316</v>
+      </c>
+      <c r="Z279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="Z279" s="1" t="n">
+      <c r="AA279" s="1" t="n">
         <v>0.001305</v>
       </c>
     </row>
@@ -23451,9 +24291,12 @@
         <v>0.005552</v>
       </c>
       <c r="Y280" s="1" t="n">
+        <v>0.005541</v>
+      </c>
+      <c r="Z280" s="1" t="n">
         <v>0.005613</v>
       </c>
-      <c r="Z280" s="1" t="n">
+      <c r="AA280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -23533,9 +24376,12 @@
         <v>1.526</v>
       </c>
       <c r="Y281" s="1" t="n">
-        <v>1.526</v>
+        <v>1.528</v>
       </c>
       <c r="Z281" s="1" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="AA281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -23615,9 +24461,12 @@
         <v>28.28</v>
       </c>
       <c r="Y282" s="1" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Z282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="Z282" s="1" t="n">
+      <c r="AA282" s="1" t="n">
         <v>28.2</v>
       </c>
     </row>
@@ -23697,9 +24546,12 @@
         <v>0.12914</v>
       </c>
       <c r="Y283" s="1" t="n">
+        <v>0.12918</v>
+      </c>
+      <c r="Z283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="Z283" s="1" t="n">
+      <c r="AA283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -23779,9 +24631,12 @@
         <v>0.01102</v>
       </c>
       <c r="Y284" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="Z284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="Z284" s="1" t="n">
+      <c r="AA284" s="1" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -23861,9 +24716,12 @@
         <v>6.568</v>
       </c>
       <c r="Y285" s="1" t="n">
+        <v>6.591</v>
+      </c>
+      <c r="Z285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="Z285" s="1" t="n">
+      <c r="AA285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -23943,9 +24801,12 @@
         <v>0.01838</v>
       </c>
       <c r="Y286" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="Z286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="Z286" s="1" t="n">
+      <c r="AA286" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -24025,9 +24886,12 @@
         <v>0.008392</v>
       </c>
       <c r="Y287" s="1" t="n">
+        <v>0.008381</v>
+      </c>
+      <c r="Z287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="Z287" s="1" t="n">
+      <c r="AA287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -24107,9 +24971,12 @@
         <v>0.3713</v>
       </c>
       <c r="Y288" s="1" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="Z288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="Z288" s="1" t="n">
+      <c r="AA288" s="1" t="n">
         <v>0.3713</v>
       </c>
     </row>
@@ -24189,9 +25056,12 @@
         <v>0.009717999999999999</v>
       </c>
       <c r="Y289" s="1" t="n">
+        <v>0.009757999999999999</v>
+      </c>
+      <c r="Z289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="Z289" s="1" t="n">
+      <c r="AA289" s="1" t="n">
         <v>0.009717999999999999</v>
       </c>
     </row>
@@ -24271,9 +25141,12 @@
         <v>0.02591</v>
       </c>
       <c r="Y290" s="1" t="n">
+        <v>0.02596</v>
+      </c>
+      <c r="Z290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="Z290" s="1" t="n">
+      <c r="AA290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -24353,9 +25226,12 @@
         <v>0.095</v>
       </c>
       <c r="Y291" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="Z291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="Z291" s="1" t="n">
+      <c r="AA291" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -24435,9 +25311,12 @@
         <v>0.28654</v>
       </c>
       <c r="Y292" s="1" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="Z292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="Z292" s="1" t="n">
+      <c r="AA292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -24517,10 +25396,13 @@
         <v>0.01515</v>
       </c>
       <c r="Y293" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="Z293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="Z293" s="1" t="n">
-        <v>0.01515</v>
+      <c r="AA293" s="1" t="n">
+        <v>0.01512</v>
       </c>
     </row>
     <row r="294">
@@ -24599,9 +25481,12 @@
         <v>0.003433</v>
       </c>
       <c r="Y294" s="1" t="n">
+        <v>0.003446</v>
+      </c>
+      <c r="Z294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="Z294" s="1" t="n">
+      <c r="AA294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -24681,10 +25566,13 @@
         <v>0.042073</v>
       </c>
       <c r="Y295" s="1" t="n">
+        <v>0.04152</v>
+      </c>
+      <c r="Z295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="Z295" s="1" t="n">
-        <v>0.042061</v>
+      <c r="AA295" s="1" t="n">
+        <v>0.04152</v>
       </c>
     </row>
     <row r="296">
@@ -24763,10 +25651,13 @@
         <v>0.02844</v>
       </c>
       <c r="Y296" s="1" t="n">
+        <v>0.02828</v>
+      </c>
+      <c r="Z296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="Z296" s="1" t="n">
-        <v>0.02844</v>
+      <c r="AA296" s="1" t="n">
+        <v>0.02828</v>
       </c>
     </row>
     <row r="297">
@@ -24845,9 +25736,12 @@
         <v>0.03788</v>
       </c>
       <c r="Y297" s="1" t="n">
+        <v>0.03798</v>
+      </c>
+      <c r="Z297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="Z297" s="1" t="n">
+      <c r="AA297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -24927,9 +25821,12 @@
         <v>0.08253000000000001</v>
       </c>
       <c r="Y298" s="1" t="n">
+        <v>0.08261</v>
+      </c>
+      <c r="Z298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="Z298" s="1" t="n">
+      <c r="AA298" s="1" t="n">
         <v>0.08239</v>
       </c>
     </row>
@@ -25009,9 +25906,12 @@
         <v>0.00762</v>
       </c>
       <c r="Y299" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="Z299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="Z299" s="1" t="n">
+      <c r="AA299" s="1" t="n">
         <v>0.0076</v>
       </c>
     </row>
@@ -25091,9 +25991,12 @@
         <v>0.01487</v>
       </c>
       <c r="Y300" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="Z300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="Z300" s="1" t="n">
+      <c r="AA300" s="1" t="n">
         <v>0.01486</v>
       </c>
     </row>
@@ -25173,9 +26076,12 @@
         <v>0.1404</v>
       </c>
       <c r="Y301" s="1" t="n">
+        <v>0.1405</v>
+      </c>
+      <c r="Z301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="Z301" s="1" t="n">
+      <c r="AA301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -25255,9 +26161,12 @@
         <v>0.0006244</v>
       </c>
       <c r="Y302" s="1" t="n">
+        <v>0.0006229</v>
+      </c>
+      <c r="Z302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="Z302" s="1" t="n">
+      <c r="AA302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -25337,9 +26246,12 @@
         <v>0.06224</v>
       </c>
       <c r="Y303" s="1" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="Z303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="Z303" s="1" t="n">
+      <c r="AA303" s="1" t="n">
         <v>0.06207</v>
       </c>
     </row>
@@ -25419,9 +26331,12 @@
         <v>0.0001615</v>
       </c>
       <c r="Y304" s="1" t="n">
+        <v>0.0001617</v>
+      </c>
+      <c r="Z304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="Z304" s="1" t="n">
+      <c r="AA304" s="1" t="n">
         <v>0.0001615</v>
       </c>
     </row>
@@ -25501,9 +26416,12 @@
         <v>0.06091</v>
       </c>
       <c r="Y305" s="1" t="n">
+        <v>0.06096</v>
+      </c>
+      <c r="Z305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="Z305" s="1" t="n">
+      <c r="AA305" s="1" t="n">
         <v>0.0606</v>
       </c>
     </row>
@@ -25583,9 +26501,12 @@
         <v>0.022342</v>
       </c>
       <c r="Y306" s="1" t="n">
+        <v>0.022429</v>
+      </c>
+      <c r="Z306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="Z306" s="1" t="n">
+      <c r="AA306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -25665,9 +26586,12 @@
         <v>0.02305</v>
       </c>
       <c r="Y307" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="Z307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="Z307" s="1" t="n">
+      <c r="AA307" s="1" t="n">
         <v>0.02278</v>
       </c>
     </row>
@@ -25747,9 +26671,12 @@
         <v>0.00041</v>
       </c>
       <c r="Y308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="Z308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="Z308" s="1" t="n">
+      <c r="AA308" s="1" t="n">
         <v>0.000409</v>
       </c>
     </row>
@@ -25832,6 +26759,9 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="Z309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AA309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -25911,9 +26841,12 @@
         <v>0.3713</v>
       </c>
       <c r="Y310" s="1" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="Z310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="Z310" s="1" t="n">
+      <c r="AA310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -25993,9 +26926,12 @@
         <v>0.0354</v>
       </c>
       <c r="Y311" s="1" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="Z311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="Z311" s="1" t="n">
+      <c r="AA311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -26075,9 +27011,12 @@
         <v>0.02432</v>
       </c>
       <c r="Y312" s="1" t="n">
+        <v>0.02427</v>
+      </c>
+      <c r="Z312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="Z312" s="1" t="n">
+      <c r="AA312" s="1" t="n">
         <v>0.02415</v>
       </c>
     </row>
@@ -26157,9 +27096,12 @@
         <v>0.04081</v>
       </c>
       <c r="Y313" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="Z313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="Z313" s="1" t="n">
+      <c r="AA313" s="1" t="n">
         <v>0.0408</v>
       </c>
     </row>
@@ -26239,9 +27181,12 @@
         <v>3.953</v>
       </c>
       <c r="Y314" s="1" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Z314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="Z314" s="1" t="n">
+      <c r="AA314" s="1" t="n">
         <v>3.932</v>
       </c>
     </row>
@@ -26321,9 +27266,12 @@
         <v>0.1592</v>
       </c>
       <c r="Y315" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="Z315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="Z315" s="1" t="n">
+      <c r="AA315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -26403,9 +27351,12 @@
         <v>0.09173000000000001</v>
       </c>
       <c r="Y316" s="1" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="Z316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="Z316" s="1" t="n">
+      <c r="AA316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -26485,9 +27436,12 @@
         <v>0.06791</v>
       </c>
       <c r="Y317" s="1" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="Z317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="Z317" s="1" t="n">
+      <c r="AA317" s="1" t="n">
         <v>0.06783</v>
       </c>
     </row>
@@ -26567,9 +27521,12 @@
         <v>0.012563</v>
       </c>
       <c r="Y318" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="Z318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="Z318" s="1" t="n">
+      <c r="AA318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -26649,9 +27606,12 @@
         <v>0.001131</v>
       </c>
       <c r="Y319" s="1" t="n">
+        <v>0.001131</v>
+      </c>
+      <c r="Z319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="Z319" s="1" t="n">
+      <c r="AA319" s="1" t="n">
         <v>0.001128</v>
       </c>
     </row>
@@ -26731,9 +27691,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="Y320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="Z320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="Z320" s="1" t="n">
+      <c r="AA320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -26813,10 +27776,13 @@
         <v>0.00518</v>
       </c>
       <c r="Y321" s="1" t="n">
+        <v>0.00517</v>
+      </c>
+      <c r="Z321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="Z321" s="1" t="n">
-        <v>0.00518</v>
+      <c r="AA321" s="1" t="n">
+        <v>0.00517</v>
       </c>
     </row>
     <row r="322">
@@ -26895,9 +27861,12 @@
         <v>0.1113</v>
       </c>
       <c r="Y322" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="Z322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="Z322" s="1" t="n">
+      <c r="AA322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -26977,9 +27946,12 @@
         <v>0.04339</v>
       </c>
       <c r="Y323" s="1" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="Z323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="Z323" s="1" t="n">
+      <c r="AA323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -27059,9 +28031,12 @@
         <v>0.01775</v>
       </c>
       <c r="Y324" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="Z324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="Z324" s="1" t="n">
+      <c r="AA324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -27141,9 +28116,12 @@
         <v>0.005641</v>
       </c>
       <c r="Y325" s="1" t="n">
+        <v>0.005647</v>
+      </c>
+      <c r="Z325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="Z325" s="1" t="n">
+      <c r="AA325" s="1" t="n">
         <v>0.005628</v>
       </c>
     </row>
@@ -27223,9 +28201,12 @@
         <v>0.001746</v>
       </c>
       <c r="Y326" s="1" t="n">
+        <v>0.001745</v>
+      </c>
+      <c r="Z326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="Z326" s="1" t="n">
+      <c r="AA326" s="1" t="n">
         <v>0.001733</v>
       </c>
     </row>
@@ -27305,9 +28286,12 @@
         <v>0.04035</v>
       </c>
       <c r="Y327" s="1" t="n">
+        <v>0.04031</v>
+      </c>
+      <c r="Z327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="Z327" s="1" t="n">
+      <c r="AA327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -27387,9 +28371,12 @@
         <v>0.0536</v>
       </c>
       <c r="Y328" s="1" t="n">
+        <v>0.053558</v>
+      </c>
+      <c r="Z328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="Z328" s="1" t="n">
+      <c r="AA328" s="1" t="n">
         <v>0.053472</v>
       </c>
     </row>
@@ -27469,9 +28456,12 @@
         <v>0.2768</v>
       </c>
       <c r="Y329" s="1" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="Z329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="Z329" s="1" t="n">
+      <c r="AA329" s="1" t="n">
         <v>0.2768</v>
       </c>
     </row>
@@ -27551,9 +28541,12 @@
         <v>0.1587</v>
       </c>
       <c r="Y330" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="Z330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="Z330" s="1" t="n">
+      <c r="AA330" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -27633,9 +28626,12 @@
         <v>0.05382</v>
       </c>
       <c r="Y331" s="1" t="n">
-        <v>0.05385</v>
+        <v>0.05393</v>
       </c>
       <c r="Z331" s="1" t="n">
+        <v>0.05393</v>
+      </c>
+      <c r="AA331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -27715,9 +28711,12 @@
         <v>0.3619</v>
       </c>
       <c r="Y332" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="Z332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="Z332" s="1" t="n">
+      <c r="AA332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -27797,9 +28796,12 @@
         <v>0.0306</v>
       </c>
       <c r="Y333" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="Z333" s="1" t="n">
         <v>0.03063</v>
       </c>
-      <c r="Z333" s="1" t="n">
+      <c r="AA333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -27879,9 +28881,12 @@
         <v>0.01742</v>
       </c>
       <c r="Y334" s="1" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="Z334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="Z334" s="1" t="n">
+      <c r="AA334" s="1" t=